--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -1813,7 +1813,7 @@
         </row>
         <row r="4">
           <cell r="F4">
-            <v>439950.57</v>
+            <v>518715.62</v>
           </cell>
         </row>
         <row r="4">
@@ -1836,7 +1836,7 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>0.264527581357623</v>
+            <v>0.311886374805742</v>
           </cell>
         </row>
         <row r="5">
@@ -1914,7 +1914,7 @@
             <v>439950.57</v>
           </cell>
           <cell r="G7">
-            <v>0</v>
+            <v>78765.05</v>
           </cell>
           <cell r="H7">
             <v>0</v>
@@ -1938,7 +1938,7 @@
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>1648964.91</v>
+            <v>1727729.96</v>
           </cell>
         </row>
         <row r="8">
@@ -1958,7 +1958,7 @@
             <v>0.737368736976622</v>
           </cell>
           <cell r="G8">
-            <v>0</v>
+            <v>0.150168436832698</v>
           </cell>
           <cell r="H8">
             <v>0</v>
@@ -1982,7 +1982,7 @@
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0.245381683655917</v>
+            <v>0.257102673268875</v>
           </cell>
         </row>
         <row r="10">
@@ -2046,7 +2046,7 @@
             <v>38346</v>
           </cell>
           <cell r="G11">
-            <v>0</v>
+            <v>6179</v>
           </cell>
           <cell r="H11">
             <v>0</v>
@@ -2070,7 +2070,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>134457</v>
+            <v>140636</v>
           </cell>
         </row>
         <row r="12">
@@ -2090,7 +2090,7 @@
             <v>1.02909129944716</v>
           </cell>
           <cell r="G12">
-            <v>0</v>
+            <v>0.188364046519426</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -2114,7 +2114,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.318622787085039</v>
+            <v>0.33326516495602</v>
           </cell>
         </row>
         <row r="14">
@@ -2178,7 +2178,7 @@
             <v>10231</v>
           </cell>
           <cell r="G15">
-            <v>0</v>
+            <v>1619</v>
           </cell>
           <cell r="H15">
             <v>0</v>
@@ -2202,7 +2202,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>36558</v>
+            <v>38177</v>
           </cell>
         </row>
         <row r="16">
@@ -2222,7 +2222,7 @@
             <v>0.854268345977926</v>
           </cell>
           <cell r="G16">
-            <v>0</v>
+            <v>0.154529037927066</v>
           </cell>
           <cell r="H16">
             <v>0</v>
@@ -2246,7 +2246,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.27194383809843</v>
+            <v>0.283987086467634</v>
           </cell>
         </row>
         <row r="18">
@@ -2310,7 +2310,7 @@
             <v>171823742</v>
           </cell>
           <cell r="G19">
-            <v>0</v>
+            <v>25066020</v>
           </cell>
           <cell r="H19">
             <v>0</v>
@@ -2334,7 +2334,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>602826040</v>
+            <v>627892060</v>
           </cell>
         </row>
         <row r="20">
@@ -2354,7 +2354,7 @@
             <v>1.14727804597092</v>
           </cell>
           <cell r="G20">
-            <v>0</v>
+            <v>0.189421947074659</v>
           </cell>
           <cell r="H20">
             <v>0</v>
@@ -2378,7 +2378,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.354000397318717</v>
+            <v>0.368720035241456</v>
           </cell>
         </row>
         <row r="22">
@@ -2442,7 +2442,7 @@
             <v>4070034.85</v>
           </cell>
           <cell r="G23">
-            <v>0</v>
+            <v>673938.58</v>
           </cell>
           <cell r="H23">
             <v>0</v>
@@ -2466,7 +2466,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>14245570.54</v>
+            <v>14919509.12</v>
           </cell>
         </row>
         <row r="24">
@@ -2486,7 +2486,7 @@
             <v>1.05573509321019</v>
           </cell>
           <cell r="G24">
-            <v>0</v>
+            <v>0.197850227036404</v>
           </cell>
           <cell r="H24">
             <v>0</v>
@@ -2510,7 +2510,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.32498469819241</v>
+            <v>0.340359282552267</v>
           </cell>
         </row>
         <row r="26">
@@ -2529,8 +2529,8 @@
           <cell r="F26">
             <v>0.70390916276867</v>
           </cell>
-          <cell r="G26" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G26">
+            <v>0.663918234725736</v>
           </cell>
           <cell r="H26" t="e">
             <v>#DIV/0!</v>
@@ -2554,7 +2554,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.704608593633414</v>
+            <v>0.702984197634224</v>
           </cell>
         </row>
         <row r="27">
@@ -2573,8 +2573,8 @@
           <cell r="F27">
             <v>0.733192510300944</v>
           </cell>
-          <cell r="G27" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G27">
+            <v>0.73798349247451</v>
           </cell>
           <cell r="H27" t="e">
             <v>#DIV/0!</v>
@@ -2598,7 +2598,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.728106383453446</v>
+            <v>0.728540345288546</v>
           </cell>
         </row>
         <row r="28">
@@ -2617,8 +2617,8 @@
           <cell r="F28">
             <v>0.108095037564605</v>
           </cell>
-          <cell r="G28" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G28">
+            <v>0.116872742320227</v>
           </cell>
           <cell r="H28" t="e">
             <v>#DIV/0!</v>
@@ -2642,7 +2642,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.115752816313667</v>
+            <v>0.115803405199433</v>
           </cell>
         </row>
         <row r="30">
@@ -2665,7 +2665,7 @@
             <v>51410.92</v>
           </cell>
           <cell r="G30">
-            <v>0</v>
+            <v>9785.19</v>
           </cell>
           <cell r="H30">
             <v>0</v>
@@ -2689,7 +2689,7 @@
             <v>0</v>
           </cell>
           <cell r="O30">
-            <v>295886.16</v>
+            <v>305671.35</v>
           </cell>
         </row>
         <row r="31">
@@ -2709,7 +2709,7 @@
             <v>8430</v>
           </cell>
           <cell r="G31">
-            <v>0</v>
+            <v>1241</v>
           </cell>
           <cell r="H31">
             <v>0</v>
@@ -2733,7 +2733,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>35938</v>
+            <v>37179</v>
           </cell>
         </row>
         <row r="32">
@@ -2753,7 +2753,7 @@
             <v>2131</v>
           </cell>
           <cell r="G32">
-            <v>0</v>
+            <v>327</v>
           </cell>
           <cell r="H32">
             <v>0</v>
@@ -2777,7 +2777,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>9242</v>
+            <v>9569</v>
           </cell>
         </row>
         <row r="33">
@@ -2797,7 +2797,7 @@
             <v>35782129</v>
           </cell>
           <cell r="G33">
-            <v>0</v>
+            <v>5149714</v>
           </cell>
           <cell r="H33">
             <v>0</v>
@@ -2821,7 +2821,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>154282420</v>
+            <v>159432134</v>
           </cell>
         </row>
         <row r="34">
@@ -2841,7 +2841,7 @@
             <v>833536.12</v>
           </cell>
           <cell r="G34">
-            <v>0</v>
+            <v>132662.14</v>
           </cell>
           <cell r="H34">
             <v>0</v>
@@ -2865,7 +2865,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>3522312.49</v>
+            <v>3654974.63</v>
           </cell>
         </row>
         <row r="35">
@@ -2884,8 +2884,8 @@
           <cell r="F35">
             <v>0.708815495578813</v>
           </cell>
-          <cell r="G35" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G35">
+            <v>0.677986631878974</v>
           </cell>
           <cell r="H35" t="e">
             <v>#DIV/0!</v>
@@ -2909,7 +2909,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.714621366938631</v>
+            <v>0.713438052111878</v>
           </cell>
         </row>
         <row r="36">
@@ -2928,8 +2928,8 @@
           <cell r="F36">
             <v>0.747212336892052</v>
           </cell>
-          <cell r="G36" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G36">
+            <v>0.736502820306205</v>
           </cell>
           <cell r="H36" t="e">
             <v>#DIV/0!</v>
@@ -2953,7 +2953,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.74283488229729</v>
+            <v>0.742623524032384</v>
           </cell>
         </row>
         <row r="37">
@@ -2972,8 +2972,8 @@
           <cell r="F37">
             <v>0.0616780950056489</v>
           </cell>
-          <cell r="G37" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G37">
+            <v>0.0737602303113759</v>
           </cell>
           <cell r="H37" t="e">
             <v>#DIV/0!</v>
@@ -2997,7 +2997,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.0840033815398361</v>
+            <v>0.0836315928135457</v>
           </cell>
         </row>
         <row r="38">
@@ -3020,7 +3020,7 @@
             <v>99083.11</v>
           </cell>
           <cell r="G38">
-            <v>0</v>
+            <v>26838.4</v>
           </cell>
           <cell r="H38">
             <v>0</v>
@@ -3044,7 +3044,7 @@
             <v>0</v>
           </cell>
           <cell r="O38">
-            <v>458849.93</v>
+            <v>485688.33</v>
           </cell>
         </row>
         <row r="39">
@@ -3064,7 +3064,7 @@
             <v>8877</v>
           </cell>
           <cell r="G39">
-            <v>0</v>
+            <v>1476</v>
           </cell>
           <cell r="H39">
             <v>0</v>
@@ -3088,7 +3088,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>34382</v>
+            <v>35858</v>
           </cell>
         </row>
         <row r="40">
@@ -3108,7 +3108,7 @@
             <v>2609</v>
           </cell>
           <cell r="G40">
-            <v>0</v>
+            <v>438</v>
           </cell>
           <cell r="H40">
             <v>0</v>
@@ -3132,7 +3132,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>9857</v>
+            <v>10295</v>
           </cell>
         </row>
         <row r="41">
@@ -3152,7 +3152,7 @@
             <v>40066145</v>
           </cell>
           <cell r="G41">
-            <v>0</v>
+            <v>5837821</v>
           </cell>
           <cell r="H41">
             <v>0</v>
@@ -3176,7 +3176,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>153367464</v>
+            <v>159205285</v>
           </cell>
         </row>
         <row r="42">
@@ -3196,7 +3196,7 @@
             <v>1044149.57</v>
           </cell>
           <cell r="G42">
-            <v>0</v>
+            <v>183166.43</v>
           </cell>
           <cell r="H42">
             <v>0</v>
@@ -3220,7 +3220,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>3873994.64</v>
+            <v>4057161.07</v>
           </cell>
         </row>
         <row r="43">
@@ -3239,8 +3239,8 @@
           <cell r="F43">
             <v>0.674241941045239</v>
           </cell>
-          <cell r="G43" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G43">
+            <v>0.607802230489767</v>
           </cell>
           <cell r="H43" t="e">
             <v>#DIV/0!</v>
@@ -3264,7 +3264,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.684255501544969</v>
+            <v>0.681452073811494</v>
           </cell>
         </row>
         <row r="44">
@@ -3283,8 +3283,8 @@
           <cell r="F44">
             <v>0.706094401261687</v>
           </cell>
-          <cell r="G44" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G44">
+            <v>0.703252032520325</v>
           </cell>
           <cell r="H44" t="e">
             <v>#DIV/0!</v>
@@ -3308,7 +3308,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.713309289744634</v>
+            <v>0.712895309275476</v>
           </cell>
         </row>
         <row r="45">
@@ -3327,8 +3327,8 @@
           <cell r="F45">
             <v>0.0948935984334122</v>
           </cell>
-          <cell r="G45" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G45">
+            <v>0.146524666119223</v>
           </cell>
           <cell r="H45" t="e">
             <v>#DIV/0!</v>
@@ -3352,7 +3352,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.118443615089772</v>
+            <v>0.119711374929465</v>
           </cell>
         </row>
         <row r="46">
@@ -3375,7 +3375,7 @@
             <v>80999.07</v>
           </cell>
           <cell r="G46">
-            <v>0</v>
+            <v>11212.49</v>
           </cell>
           <cell r="H46">
             <v>0</v>
@@ -3399,7 +3399,7 @@
             <v>0</v>
           </cell>
           <cell r="O46">
-            <v>144581</v>
+            <v>155793.49</v>
           </cell>
         </row>
         <row r="47">
@@ -3419,7 +3419,7 @@
             <v>6433</v>
           </cell>
           <cell r="G47">
-            <v>0</v>
+            <v>988</v>
           </cell>
           <cell r="H47">
             <v>0</v>
@@ -3443,7 +3443,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>18116</v>
+            <v>19104</v>
           </cell>
         </row>
         <row r="48">
@@ -3463,7 +3463,7 @@
             <v>1816</v>
           </cell>
           <cell r="G48">
-            <v>0</v>
+            <v>256</v>
           </cell>
           <cell r="H48">
             <v>0</v>
@@ -3487,7 +3487,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>4932</v>
+            <v>5188</v>
           </cell>
         </row>
         <row r="49">
@@ -3507,7 +3507,7 @@
             <v>26000920</v>
           </cell>
           <cell r="G49">
-            <v>0</v>
+            <v>3403246</v>
           </cell>
           <cell r="H49">
             <v>0</v>
@@ -3531,7 +3531,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>76776689</v>
+            <v>80179935</v>
           </cell>
         </row>
         <row r="50">
@@ -3551,7 +3551,7 @@
             <v>658949.99</v>
           </cell>
           <cell r="G50">
-            <v>0</v>
+            <v>96010.5</v>
           </cell>
           <cell r="H50">
             <v>0</v>
@@ -3575,7 +3575,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>1823158.3</v>
+            <v>1919168.8</v>
           </cell>
         </row>
         <row r="51">
@@ -3594,8 +3594,8 @@
           <cell r="F51">
             <v>0.683208329743717</v>
           </cell>
-          <cell r="G51" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G51">
+            <v>0.647356891038732</v>
           </cell>
           <cell r="H51" t="e">
             <v>#DIV/0!</v>
@@ -3619,7 +3619,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.703171899611352</v>
+            <v>0.70080282554482</v>
           </cell>
         </row>
         <row r="52">
@@ -3638,8 +3638,8 @@
           <cell r="F52">
             <v>0.717705580600031</v>
           </cell>
-          <cell r="G52" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G52">
+            <v>0.740890688259109</v>
           </cell>
           <cell r="H52" t="e">
             <v>#DIV/0!</v>
@@ -3663,7 +3663,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.727754471185692</v>
+            <v>0.728433835845896</v>
           </cell>
         </row>
         <row r="53">
@@ -3682,8 +3682,8 @@
           <cell r="F53">
             <v>0.122921422307025</v>
           </cell>
-          <cell r="G53" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G53">
+            <v>0.116783997583598</v>
           </cell>
           <cell r="H53" t="e">
             <v>#DIV/0!</v>
@@ -3707,7 +3707,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.0793024939194803</v>
+            <v>0.0811775858382024</v>
           </cell>
         </row>
         <row r="54">
@@ -3730,7 +3730,7 @@
             <v>53475.37</v>
           </cell>
           <cell r="G54">
-            <v>0</v>
+            <v>9115.55</v>
           </cell>
           <cell r="H54">
             <v>0</v>
@@ -3754,7 +3754,7 @@
             <v>0</v>
           </cell>
           <cell r="O54">
-            <v>320946.42</v>
+            <v>330061.97</v>
           </cell>
         </row>
         <row r="55">
@@ -3774,7 +3774,7 @@
             <v>3410</v>
           </cell>
           <cell r="G55">
-            <v>0</v>
+            <v>425</v>
           </cell>
           <cell r="H55">
             <v>0</v>
@@ -3798,7 +3798,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>15774</v>
+            <v>16199</v>
           </cell>
         </row>
         <row r="56">
@@ -3818,7 +3818,7 @@
             <v>1234</v>
           </cell>
           <cell r="G56">
-            <v>0</v>
+            <v>162</v>
           </cell>
           <cell r="H56">
             <v>0</v>
@@ -3842,7 +3842,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>5727</v>
+            <v>5889</v>
           </cell>
         </row>
         <row r="57">
@@ -3862,7 +3862,7 @@
             <v>13881751</v>
           </cell>
           <cell r="G57">
-            <v>0</v>
+            <v>1725641</v>
           </cell>
           <cell r="H57">
             <v>0</v>
@@ -3886,7 +3886,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>63716504</v>
+            <v>65442145</v>
           </cell>
         </row>
         <row r="58">
@@ -3906,7 +3906,7 @@
             <v>463880.75</v>
           </cell>
           <cell r="G58">
-            <v>0</v>
+            <v>63977.49</v>
           </cell>
           <cell r="H58">
             <v>0</v>
@@ -3930,7 +3930,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2108653.48</v>
+            <v>2172630.97</v>
           </cell>
         </row>
         <row r="59">
@@ -3949,8 +3949,8 @@
           <cell r="F59">
             <v>0.582292653498827</v>
           </cell>
-          <cell r="G59" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G59">
+            <v>0.536567208938592</v>
           </cell>
           <cell r="H59" t="e">
             <v>#DIV/0!</v>
@@ -3974,7 +3974,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.586321175122854</v>
+            <v>0.585009215009685</v>
           </cell>
         </row>
         <row r="60">
@@ -3993,8 +3993,8 @@
           <cell r="F60">
             <v>0.638123167155425</v>
           </cell>
-          <cell r="G60" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G60">
+            <v>0.618823529411765</v>
           </cell>
           <cell r="H60" t="e">
             <v>#DIV/0!</v>
@@ -4018,7 +4018,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.636934195511601</v>
+            <v>0.636459040681524</v>
           </cell>
         </row>
         <row r="61">
@@ -4037,8 +4037,8 @@
           <cell r="F61">
             <v>0.115278269253467</v>
           </cell>
-          <cell r="G61" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G61">
+            <v>0.142480581842145</v>
           </cell>
           <cell r="H61" t="e">
             <v>#DIV/0!</v>
@@ -4062,7 +4062,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.152204439014797</v>
+            <v>0.151918100477045</v>
           </cell>
         </row>
         <row r="62">
@@ -4085,7 +4085,7 @@
             <v>154982.1</v>
           </cell>
           <cell r="G62">
-            <v>0</v>
+            <v>21813.42</v>
           </cell>
           <cell r="H62">
             <v>0</v>
@@ -4109,7 +4109,7 @@
             <v>0</v>
           </cell>
           <cell r="O62">
-            <v>428701.4</v>
+            <v>450514.82</v>
           </cell>
         </row>
         <row r="63">
@@ -4129,7 +4129,7 @@
             <v>11196</v>
           </cell>
           <cell r="G63">
-            <v>0</v>
+            <v>2049</v>
           </cell>
           <cell r="H63">
             <v>0</v>
@@ -4153,7 +4153,7 @@
             <v>0</v>
           </cell>
           <cell r="O63">
-            <v>30247</v>
+            <v>32296</v>
           </cell>
         </row>
         <row r="64">
@@ -4173,7 +4173,7 @@
             <v>2441</v>
           </cell>
           <cell r="G64">
-            <v>0</v>
+            <v>436</v>
           </cell>
           <cell r="H64">
             <v>0</v>
@@ -4197,7 +4197,7 @@
             <v>0</v>
           </cell>
           <cell r="O64">
-            <v>6800</v>
+            <v>7236</v>
           </cell>
         </row>
         <row r="65">
@@ -4217,7 +4217,7 @@
             <v>56092797</v>
           </cell>
           <cell r="G65">
-            <v>0</v>
+            <v>8949598</v>
           </cell>
           <cell r="H65">
             <v>0</v>
@@ -4241,7 +4241,7 @@
             <v>0</v>
           </cell>
           <cell r="O65">
-            <v>154682963</v>
+            <v>163632561</v>
           </cell>
         </row>
         <row r="66">
@@ -4261,7 +4261,7 @@
             <v>1069518.42</v>
           </cell>
           <cell r="G66">
-            <v>0</v>
+            <v>198122.02</v>
           </cell>
           <cell r="H66">
             <v>0</v>
@@ -4285,7 +4285,7 @@
             <v>0</v>
           </cell>
           <cell r="O66">
-            <v>2917451.63</v>
+            <v>3115573.65</v>
           </cell>
         </row>
         <row r="67">
@@ -4304,8 +4304,8 @@
           <cell r="F67">
             <v>0.761663155253249</v>
           </cell>
-          <cell r="G67" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G67">
+            <v>0.723280838982935</v>
           </cell>
           <cell r="H67" t="e">
             <v>#DIV/0!</v>
@@ -4329,7 +4329,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O67">
-            <v>0.76423941804761</v>
+            <v>0.761999259884468</v>
           </cell>
         </row>
         <row r="68">
@@ -4348,8 +4348,8 @@
           <cell r="F68">
             <v>0.781975705609146</v>
           </cell>
-          <cell r="G68" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G68">
+            <v>0.78721327476818</v>
           </cell>
           <cell r="H68" t="e">
             <v>#DIV/0!</v>
@@ -4373,7 +4373,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O68">
-            <v>0.775184315799914</v>
+            <v>0.77594748575675</v>
           </cell>
         </row>
         <row r="69">
@@ -4392,8 +4392,8 @@
           <cell r="F69">
             <v>0.144908303683073</v>
           </cell>
-          <cell r="G69" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G69">
+            <v>0.11010093678633</v>
           </cell>
           <cell r="H69" t="e">
             <v>#DIV/0!</v>
@@ -4417,7 +4417,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O69">
-            <v>0.146943790118639</v>
+            <v>0.144600921246076</v>
           </cell>
         </row>
         <row r="70">
@@ -6925,7 +6925,7 @@
             <v>56073.62</v>
           </cell>
           <cell r="G126">
-            <v>0</v>
+            <v>9383.18</v>
           </cell>
           <cell r="H126">
             <v>0</v>
@@ -6949,7 +6949,7 @@
             <v>0</v>
           </cell>
           <cell r="O126">
-            <v>285029.35</v>
+            <v>294412.53</v>
           </cell>
         </row>
         <row r="127">
@@ -6969,7 +6969,7 @@
             <v>3125</v>
           </cell>
           <cell r="G127">
-            <v>0</v>
+            <v>392</v>
           </cell>
           <cell r="H127">
             <v>0</v>
@@ -6993,7 +6993,7 @@
             <v>0</v>
           </cell>
           <cell r="O127">
-            <v>13376</v>
+            <v>13768</v>
           </cell>
         </row>
         <row r="128">
@@ -7013,7 +7013,7 @@
             <v>1163</v>
           </cell>
           <cell r="G128">
-            <v>0</v>
+            <v>152</v>
           </cell>
           <cell r="H128">
             <v>0</v>
@@ -7037,7 +7037,7 @@
             <v>0</v>
           </cell>
           <cell r="O128">
-            <v>4974</v>
+            <v>5126</v>
           </cell>
         </row>
         <row r="129">
@@ -7057,7 +7057,7 @@
             <v>12576283</v>
           </cell>
           <cell r="G129">
-            <v>0</v>
+            <v>1566038</v>
           </cell>
           <cell r="H129">
             <v>0</v>
@@ -7081,7 +7081,7 @@
             <v>0</v>
           </cell>
           <cell r="O129">
-            <v>53903724</v>
+            <v>55469762</v>
           </cell>
         </row>
         <row r="130">
@@ -7101,7 +7101,7 @@
             <v>435667.29</v>
           </cell>
           <cell r="G130">
-            <v>0</v>
+            <v>59649.73</v>
           </cell>
           <cell r="H130">
             <v>0</v>
@@ -7125,7 +7125,7 @@
             <v>0</v>
           </cell>
           <cell r="O130">
-            <v>1808831.59</v>
+            <v>1868481.32</v>
           </cell>
         </row>
         <row r="131">
@@ -7144,8 +7144,8 @@
           <cell r="F131">
             <v>0.433024696168176</v>
           </cell>
-          <cell r="G131" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G131">
+            <v>0.47611975252197</v>
           </cell>
           <cell r="H131" t="e">
             <v>#DIV/0!</v>
@@ -7169,7 +7169,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O131">
-            <v>0.0335567091802414</v>
+            <v>0.0336846824761931</v>
           </cell>
         </row>
         <row r="132">
@@ -7188,8 +7188,8 @@
           <cell r="F132">
             <v>0.62784</v>
           </cell>
-          <cell r="G132" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G132">
+            <v>0.612244897959184</v>
           </cell>
           <cell r="H132" t="e">
             <v>#DIV/0!</v>
@@ -7213,7 +7213,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O132">
-            <v>0.62813995215311</v>
+            <v>0.627687391051714</v>
           </cell>
         </row>
         <row r="133">
@@ -7232,8 +7232,8 @@
           <cell r="F133">
             <v>0.128707436355849</v>
           </cell>
-          <cell r="G133" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G133">
+            <v>0.157304651672355</v>
           </cell>
           <cell r="H133" t="e">
             <v>#DIV/0!</v>
@@ -7257,7 +7257,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O133">
-            <v>0.157576499424139</v>
+            <v>0.157567820908159</v>
           </cell>
         </row>
       </sheetData>
@@ -7273,8 +7273,8 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="周度汇总分析报告"/>
       <sheetName val="2026年度男装数据汇总分析--俄罗斯"/>
-      <sheetName val="周度汇总分析报告"/>
       <sheetName val="2026年月度数据汇总--俄罗斯"/>
       <sheetName val="2026年数据登记--俄罗斯"/>
       <sheetName val="2026目标拆解--俄罗斯"/>
@@ -7285,7 +7285,8 @@
       <sheetName val="2025年数据源"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
         <row r="1">
           <cell r="A1" t="str">
             <v>2026年度WB男装进度</v>
@@ -7371,7 +7372,7 @@
         </row>
         <row r="4">
           <cell r="F4">
-            <v>685537.218</v>
+            <v>782699.5281</v>
           </cell>
         </row>
         <row r="4">
@@ -7472,7 +7473,7 @@
             <v>706739.4</v>
           </cell>
           <cell r="G7">
-            <v>0</v>
+            <v>100167.33</v>
           </cell>
           <cell r="H7">
             <v>0</v>
@@ -7496,7 +7497,7 @@
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>2518797.87</v>
+            <v>2618965.2</v>
           </cell>
         </row>
         <row r="8">
@@ -7510,13 +7511,13 @@
             <v>1.33194260161362</v>
           </cell>
           <cell r="E8">
-            <v>1.31577889268891</v>
+            <v>1.3157788926889</v>
           </cell>
           <cell r="F8">
             <v>1.52310341168606</v>
           </cell>
           <cell r="G8">
-            <v>0</v>
+            <v>0.184404202252453</v>
           </cell>
           <cell r="H8">
             <v>0</v>
@@ -7540,7 +7541,7 @@
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0.28768932935122</v>
+            <v>0.299130133051202</v>
           </cell>
         </row>
         <row r="10">
@@ -7604,7 +7605,7 @@
             <v>33812</v>
           </cell>
           <cell r="G11">
-            <v>0</v>
+            <v>5553</v>
           </cell>
           <cell r="H11">
             <v>0</v>
@@ -7628,7 +7629,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>129003</v>
+            <v>134556</v>
           </cell>
         </row>
         <row r="12">
@@ -7648,7 +7649,7 @@
             <v>1.05894143438772</v>
           </cell>
           <cell r="G12">
-            <v>0</v>
+            <v>0.15425</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -7672,7 +7673,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.2220850720985</v>
+            <v>0.231644837416849</v>
           </cell>
         </row>
         <row r="14">
@@ -7736,7 +7737,7 @@
             <v>12177</v>
           </cell>
           <cell r="G15">
-            <v>0</v>
+            <v>1865</v>
           </cell>
           <cell r="H15">
             <v>0</v>
@@ -7760,7 +7761,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>46064</v>
+            <v>47929</v>
           </cell>
         </row>
         <row r="16">
@@ -7780,7 +7781,7 @@
             <v>1.23021124839619</v>
           </cell>
           <cell r="G16">
-            <v>0</v>
+            <v>0.167114695340502</v>
           </cell>
           <cell r="H16">
             <v>0</v>
@@ -7804,7 +7805,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.255811174212385</v>
+            <v>0.266168239163456</v>
           </cell>
         </row>
         <row r="18">
@@ -7865,10 +7866,10 @@
             <v>12268567.6984</v>
           </cell>
           <cell r="F19">
-            <v>113914619.8752</v>
+            <v>13661971.3112</v>
           </cell>
           <cell r="G19">
-            <v>0</v>
+            <v>2247713.1192</v>
           </cell>
           <cell r="H19">
             <v>0</v>
@@ -7892,7 +7893,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>149625301.111</v>
+            <v>51620365.6662</v>
           </cell>
         </row>
         <row r="20">
@@ -7909,10 +7910,10 @@
             <v>1.18826201944832</v>
           </cell>
           <cell r="F20">
-            <v>10.2369767028764</v>
+            <v>1.22773777572485</v>
           </cell>
           <cell r="G20">
-            <v>0</v>
+            <v>0.179587177948226</v>
           </cell>
           <cell r="H20">
             <v>0</v>
@@ -7936,7 +7937,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.741831472049483</v>
+            <v>0.255930057052861</v>
           </cell>
         </row>
         <row r="22">
@@ -8000,7 +8001,7 @@
             <v>4382797.99</v>
           </cell>
           <cell r="G23">
-            <v>0</v>
+            <v>684372.3</v>
           </cell>
           <cell r="H23">
             <v>0</v>
@@ -8024,7 +8025,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>16442530.11</v>
+            <v>17126902.41</v>
           </cell>
         </row>
         <row r="24">
@@ -8044,7 +8045,7 @@
             <v>1.23081767747956</v>
           </cell>
           <cell r="G24">
-            <v>0</v>
+            <v>0.170874355824545</v>
           </cell>
           <cell r="H24">
             <v>0</v>
@@ -8068,7 +8069,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.254752752065274</v>
+            <v>0.265356091435546</v>
           </cell>
         </row>
         <row r="26">
@@ -8085,10 +8086,10 @@
             <v>0.335256721983644</v>
           </cell>
           <cell r="F26">
-            <v>0.0384744117550636</v>
-          </cell>
-          <cell r="G26" t="e">
-            <v>#DIV/0!</v>
+            <v>0.320802751679548</v>
+          </cell>
+          <cell r="G26">
+            <v>0.304474932389762</v>
           </cell>
           <cell r="H26" t="e">
             <v>#DIV/0!</v>
@@ -8112,7 +8113,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.109891375241424</v>
+            <v>0.331785763021326</v>
           </cell>
         </row>
         <row r="27">
@@ -8131,8 +8132,8 @@
           <cell r="F27">
             <v>0.639861587602035</v>
           </cell>
-          <cell r="G27" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G27">
+            <v>0.664145506933189</v>
           </cell>
           <cell r="H27" t="e">
             <v>#DIV/0!</v>
@@ -8156,7 +8157,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.642923032797687</v>
+            <v>0.64379886441333</v>
           </cell>
         </row>
         <row r="28">
@@ -8175,8 +8176,8 @@
           <cell r="F28">
             <v>0.161253017276299</v>
           </cell>
-          <cell r="G28" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G28">
+            <v>0.146363799353071</v>
           </cell>
           <cell r="H28" t="e">
             <v>#DIV/0!</v>
@@ -8200,7 +8201,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.153187973696829</v>
+            <v>0.152915287149114</v>
           </cell>
         </row>
         <row r="30">
@@ -8223,7 +8224,7 @@
             <v>364348.74</v>
           </cell>
           <cell r="G30">
-            <v>0</v>
+            <v>48925.87</v>
           </cell>
           <cell r="H30">
             <v>0</v>
@@ -8247,7 +8248,7 @@
             <v>0</v>
           </cell>
           <cell r="O30">
-            <v>1558473.42</v>
+            <v>1607399.29</v>
           </cell>
         </row>
         <row r="31">
@@ -8267,7 +8268,7 @@
             <v>17188</v>
           </cell>
           <cell r="G31">
-            <v>0</v>
+            <v>2331</v>
           </cell>
           <cell r="H31">
             <v>0</v>
@@ -8291,7 +8292,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>65851</v>
+            <v>68182</v>
           </cell>
         </row>
         <row r="32">
@@ -8311,7 +8312,7 @@
             <v>6412</v>
           </cell>
           <cell r="G32">
-            <v>0</v>
+            <v>866</v>
           </cell>
           <cell r="H32">
             <v>0</v>
@@ -8335,7 +8336,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>24552</v>
+            <v>25418</v>
           </cell>
         </row>
         <row r="33">
@@ -8352,10 +8353,10 @@
             <v>6430144.456</v>
           </cell>
           <cell r="F33">
-            <v>58337318.9976</v>
+            <v>7017450.9096</v>
           </cell>
           <cell r="G33">
-            <v>0</v>
+            <v>981973.6656</v>
           </cell>
           <cell r="H33">
             <v>0</v>
@@ -8379,7 +8380,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>78195863.6061</v>
+            <v>27857969.1837</v>
           </cell>
         </row>
         <row r="34">
@@ -8399,7 +8400,7 @@
             <v>2348681.79</v>
           </cell>
           <cell r="G34">
-            <v>0</v>
+            <v>332705.62</v>
           </cell>
           <cell r="H34">
             <v>0</v>
@@ -8423,7 +8424,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>8981287.63</v>
+            <v>9313993.25</v>
           </cell>
         </row>
         <row r="35">
@@ -8440,10 +8441,10 @@
             <v>0.352381240500081</v>
           </cell>
           <cell r="F35">
-            <v>0.0402603655834205</v>
-          </cell>
-          <cell r="G35" t="e">
-            <v>#DIV/0!</v>
+            <v>0.334691588192938</v>
+          </cell>
+          <cell r="G35">
+            <v>0.338813179675966</v>
           </cell>
           <cell r="H35" t="e">
             <v>#DIV/0!</v>
@@ -8467,7 +8468,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.114856300778797</v>
+            <v>0.334338558154832</v>
           </cell>
         </row>
         <row r="36">
@@ -8486,8 +8487,8 @@
           <cell r="F36">
             <v>0.626949034209914</v>
           </cell>
-          <cell r="G36" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G36">
+            <v>0.628485628485629</v>
           </cell>
           <cell r="H36" t="e">
             <v>#DIV/0!</v>
@@ -8511,7 +8512,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.627158281575071</v>
+            <v>0.627203660790238</v>
           </cell>
         </row>
         <row r="37">
@@ -8530,8 +8531,8 @@
           <cell r="F37">
             <v>0.155129035168276</v>
           </cell>
-          <cell r="G37" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G37">
+            <v>0.147054534275676</v>
           </cell>
           <cell r="H37" t="e">
             <v>#DIV/0!</v>
@@ -8555,7 +8556,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.173524497177249</v>
+            <v>0.172578962304917</v>
           </cell>
         </row>
         <row r="38">
@@ -8578,7 +8579,7 @@
             <v>149415.87</v>
           </cell>
           <cell r="G38">
-            <v>0</v>
+            <v>13496.52</v>
           </cell>
           <cell r="H38">
             <v>0</v>
@@ -8602,7 +8603,7 @@
             <v>0</v>
           </cell>
           <cell r="O38">
-            <v>477565.86</v>
+            <v>491062.38</v>
           </cell>
         </row>
         <row r="39">
@@ -8622,7 +8623,7 @@
             <v>6965</v>
           </cell>
           <cell r="G39">
-            <v>0</v>
+            <v>1689</v>
           </cell>
           <cell r="H39">
             <v>0</v>
@@ -8646,7 +8647,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>27658</v>
+            <v>29347</v>
           </cell>
         </row>
         <row r="40">
@@ -8666,7 +8667,7 @@
             <v>2459</v>
           </cell>
           <cell r="G40">
-            <v>0</v>
+            <v>350</v>
           </cell>
           <cell r="H40">
             <v>0</v>
@@ -8690,7 +8691,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>9274</v>
+            <v>9624</v>
           </cell>
         </row>
         <row r="41">
@@ -8707,10 +8708,10 @@
             <v>2614149.1856</v>
           </cell>
           <cell r="F41">
-            <v>22042814.7656</v>
+            <v>2746120.052</v>
           </cell>
           <cell r="G41">
-            <v>0</v>
+            <v>489604.2696</v>
           </cell>
           <cell r="H41">
             <v>0</v>
@@ -8734,7 +8735,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>29036903.9346</v>
+            <v>10229813.4906</v>
           </cell>
         </row>
         <row r="42">
@@ -8754,7 +8755,7 @@
             <v>861340.47</v>
           </cell>
           <cell r="G42">
-            <v>0</v>
+            <v>123275.95</v>
           </cell>
           <cell r="H42">
             <v>0</v>
@@ -8778,7 +8779,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>3023164.98</v>
+            <v>3146440.93</v>
           </cell>
         </row>
         <row r="43">
@@ -8795,10 +8796,10 @@
             <v>0.308543117754343</v>
           </cell>
           <cell r="F43">
-            <v>0.039075793139822</v>
-          </cell>
-          <cell r="G43" t="e">
-            <v>#DIV/0!</v>
+            <v>0.313657252301364</v>
+          </cell>
+          <cell r="G43">
+            <v>0.251786917832058</v>
           </cell>
           <cell r="H43" t="e">
             <v>#DIV/0!</v>
@@ -8822,7 +8823,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.104114577325775</v>
+            <v>0.307575590981322</v>
           </cell>
         </row>
         <row r="44">
@@ -8841,8 +8842,8 @@
           <cell r="F44">
             <v>0.646949030868629</v>
           </cell>
-          <cell r="G44" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G44">
+            <v>0.792776791000592</v>
           </cell>
           <cell r="H44" t="e">
             <v>#DIV/0!</v>
@@ -8866,7 +8867,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.664690143900499</v>
+            <v>0.672061880260333</v>
           </cell>
         </row>
         <row r="45">
@@ -8885,8 +8886,8 @@
           <cell r="F45">
             <v>0.173469000011111</v>
           </cell>
-          <cell r="G45" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G45">
+            <v>0.109482182047674</v>
           </cell>
           <cell r="H45" t="e">
             <v>#DIV/0!</v>
@@ -8910,7 +8911,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.157968838339746</v>
+            <v>0.156069155889095</v>
           </cell>
         </row>
         <row r="46">
@@ -8933,7 +8934,7 @@
             <v>169881.56</v>
           </cell>
           <cell r="G46">
-            <v>0</v>
+            <v>36628.56</v>
           </cell>
           <cell r="H46">
             <v>0</v>
@@ -8957,7 +8958,7 @@
             <v>0</v>
           </cell>
           <cell r="O46">
-            <v>365885.72</v>
+            <v>402514.28</v>
           </cell>
         </row>
         <row r="47">
@@ -8977,7 +8978,7 @@
             <v>7019</v>
           </cell>
           <cell r="G47">
-            <v>0</v>
+            <v>1222</v>
           </cell>
           <cell r="H47">
             <v>0</v>
@@ -9001,7 +9002,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>20285</v>
+            <v>21507</v>
           </cell>
         </row>
         <row r="48">
@@ -9021,7 +9022,7 @@
             <v>2410</v>
           </cell>
           <cell r="G48">
-            <v>0</v>
+            <v>519</v>
           </cell>
           <cell r="H48">
             <v>0</v>
@@ -9045,7 +9046,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>6750</v>
+            <v>7269</v>
           </cell>
         </row>
         <row r="49">
@@ -9062,10 +9063,10 @@
             <v>2306985.484</v>
           </cell>
           <cell r="F49">
-            <v>24515919.3072</v>
+            <v>2869544.286</v>
           </cell>
           <cell r="G49">
-            <v>0</v>
+            <v>654324.9576</v>
           </cell>
           <cell r="H49">
             <v>0</v>
@@ -9089,7 +9090,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>29123079.3618</v>
+            <v>8131029.2982</v>
           </cell>
         </row>
         <row r="50">
@@ -9109,7 +9110,7 @@
             <v>863626.8</v>
           </cell>
           <cell r="G50">
-            <v>0</v>
+            <v>186429.08</v>
           </cell>
           <cell r="H50">
             <v>0</v>
@@ -9133,7 +9134,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>2312644.35</v>
+            <v>2499073.43</v>
           </cell>
         </row>
         <row r="51">
@@ -9150,10 +9151,10 @@
             <v>0.315128372086454</v>
           </cell>
           <cell r="F51">
-            <v>0.0352271839851571</v>
-          </cell>
-          <cell r="G51" t="e">
-            <v>#DIV/0!</v>
+            <v>0.300963049852021</v>
+          </cell>
+          <cell r="G51">
+            <v>0.28491818603986</v>
           </cell>
           <cell r="H51" t="e">
             <v>#DIV/0!</v>
@@ -9177,7 +9178,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.0794093344755787</v>
+            <v>0.307350193726793</v>
           </cell>
         </row>
         <row r="52">
@@ -9196,8 +9197,8 @@
           <cell r="F52">
             <v>0.656646245903975</v>
           </cell>
-          <cell r="G52" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G52">
+            <v>0.575286415711948</v>
           </cell>
           <cell r="H52" t="e">
             <v>#DIV/0!</v>
@@ -9221,7 +9222,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.667241804288883</v>
+            <v>0.662017017715163</v>
           </cell>
         </row>
         <row r="53">
@@ -9240,8 +9241,8 @@
           <cell r="F53">
             <v>0.196707142483304</v>
           </cell>
-          <cell r="G53" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G53">
+            <v>0.196474498506349</v>
           </cell>
           <cell r="H53" t="e">
             <v>#DIV/0!</v>
@@ -9265,7 +9266,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.158210976106205</v>
+            <v>0.161065407349795</v>
           </cell>
         </row>
         <row r="54">
@@ -9288,7 +9289,7 @@
             <v>23093.23</v>
           </cell>
           <cell r="G54">
-            <v>0</v>
+            <v>1116.38</v>
           </cell>
           <cell r="H54">
             <v>0</v>
@@ -9312,7 +9313,7 @@
             <v>0</v>
           </cell>
           <cell r="O54">
-            <v>116872.87</v>
+            <v>117989.25</v>
           </cell>
         </row>
         <row r="55">
@@ -9332,7 +9333,7 @@
             <v>2640</v>
           </cell>
           <cell r="G55">
-            <v>0</v>
+            <v>311</v>
           </cell>
           <cell r="H55">
             <v>0</v>
@@ -9356,7 +9357,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>15209</v>
+            <v>15520</v>
           </cell>
         </row>
         <row r="56">
@@ -9376,7 +9377,7 @@
             <v>896</v>
           </cell>
           <cell r="G56">
-            <v>0</v>
+            <v>130</v>
           </cell>
           <cell r="H56">
             <v>0</v>
@@ -9400,7 +9401,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>5488</v>
+            <v>5618</v>
           </cell>
         </row>
         <row r="57">
@@ -9417,10 +9418,10 @@
             <v>917288.5728</v>
           </cell>
           <cell r="F57">
-            <v>9018566.8048</v>
+            <v>1028856.0636</v>
           </cell>
           <cell r="G57">
-            <v>0</v>
+            <v>121810.2264</v>
           </cell>
           <cell r="H57">
             <v>0</v>
@@ -9444,7 +9445,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>13269454.2085</v>
+            <v>5401553.6937</v>
           </cell>
         </row>
         <row r="58">
@@ -9464,7 +9465,7 @@
             <v>309148.93</v>
           </cell>
           <cell r="G58">
-            <v>0</v>
+            <v>41961.65</v>
           </cell>
           <cell r="H58">
             <v>0</v>
@@ -9488,7 +9489,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2125433.15</v>
+            <v>2167394.8</v>
           </cell>
         </row>
         <row r="59">
@@ -9505,10 +9506,10 @@
             <v>0.341967837931841</v>
           </cell>
           <cell r="F59">
-            <v>0.0342791639393811</v>
-          </cell>
-          <cell r="G59" t="e">
-            <v>#DIV/0!</v>
+            <v>0.300478308810543</v>
+          </cell>
+          <cell r="G59">
+            <v>0.344483802716255</v>
           </cell>
           <cell r="H59" t="e">
             <v>#DIV/0!</v>
@@ -9532,7 +9533,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.160174873555727</v>
+            <v>0.40125395819501</v>
           </cell>
         </row>
         <row r="60">
@@ -9551,8 +9552,8 @@
           <cell r="F60">
             <v>0.660606060606061</v>
           </cell>
-          <cell r="G60" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G60">
+            <v>0.581993569131833</v>
           </cell>
           <cell r="H60" t="e">
             <v>#DIV/0!</v>
@@ -9576,7 +9577,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.63916102307844</v>
+            <v>0.638015463917526</v>
           </cell>
         </row>
         <row r="61">
@@ -9595,8 +9596,8 @@
           <cell r="F61">
             <v>0.074699369006388</v>
           </cell>
-          <cell r="G61" t="e">
-            <v>#DIV/0!</v>
+          <cell r="G61">
+            <v>0.0266047688782495</v>
           </cell>
           <cell r="H61" t="e">
             <v>#DIV/0!</v>
@@ -9620,7 +9621,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.0549877891948754</v>
+            <v>0.0544382823101726</v>
           </cell>
         </row>
         <row r="62">
@@ -12464,7 +12465,6 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -13005,7 +13005,7 @@
       </c>
       <c r="F4" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!F4</f>
-        <v>439950.57</v>
+        <v>518715.62</v>
       </c>
       <c r="G4" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G4</f>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="F5" s="63">
         <f>'[1]特别隐藏版（勿动、勿看）'!F5</f>
-        <v>0.264527581357623</v>
+        <v>0.311886374805742</v>
       </c>
       <c r="G5" s="63">
         <f>'[1]特别隐藏版（勿动、勿看）'!G5</f>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="G7" s="13">
         <f>'[1]特别隐藏版（勿动、勿看）'!G7</f>
-        <v>0</v>
+        <v>78765.05</v>
       </c>
       <c r="H7" s="13">
         <f>'[1]特别隐藏版（勿动、勿看）'!H7</f>
@@ -13280,7 +13280,7 @@
       </c>
       <c r="O7" s="13">
         <f>'[1]特别隐藏版（勿动、勿看）'!O7</f>
-        <v>1648964.91</v>
+        <v>1727729.96</v>
       </c>
       <c r="P7" s="76"/>
       <c r="Q7" s="79"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="G8" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G8</f>
-        <v>0</v>
+        <v>0.150168436832698</v>
       </c>
       <c r="H8" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!H8</f>
@@ -13360,7 +13360,7 @@
       </c>
       <c r="O8" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O8</f>
-        <v>0.245381683655917</v>
+        <v>0.257102673268875</v>
       </c>
       <c r="P8" s="76"/>
       <c r="Q8" s="76"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="G11" s="12">
         <f>'[1]特别隐藏版（勿动、勿看）'!G11</f>
-        <v>0</v>
+        <v>6179</v>
       </c>
       <c r="H11" s="12">
         <f>'[1]特别隐藏版（勿动、勿看）'!H11</f>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="O11" s="12">
         <f>'[1]特别隐藏版（勿动、勿看）'!O11</f>
-        <v>134457</v>
+        <v>140636</v>
       </c>
       <c r="P11" s="60"/>
       <c r="BP11" s="81"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="G12" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!G12</f>
-        <v>0</v>
+        <v>0.188364046519426</v>
       </c>
       <c r="H12" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!H12</f>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="O12" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!O12</f>
-        <v>0.318622787085039</v>
+        <v>0.33326516495602</v>
       </c>
       <c r="BP12" s="81"/>
       <c r="BQ12" s="82"/>
@@ -13881,7 +13881,7 @@
       </c>
       <c r="G15" s="12">
         <f>'[1]特别隐藏版（勿动、勿看）'!G15</f>
-        <v>0</v>
+        <v>1619</v>
       </c>
       <c r="H15" s="12">
         <f>'[1]特别隐藏版（勿动、勿看）'!H15</f>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="O15" s="12">
         <f>'[1]特别隐藏版（勿动、勿看）'!O15</f>
-        <v>36558</v>
+        <v>38177</v>
       </c>
       <c r="P15" s="60"/>
       <c r="BP15" s="81"/>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="G16" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!G16</f>
-        <v>0</v>
+        <v>0.154529037927066</v>
       </c>
       <c r="H16" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!H16</f>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="O16" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!O16</f>
-        <v>0.27194383809843</v>
+        <v>0.283987086467634</v>
       </c>
       <c r="BP16" s="81"/>
       <c r="BQ16" s="82"/>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G19" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G19</f>
-        <v>0</v>
+        <v>25066020</v>
       </c>
       <c r="H19" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H19</f>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="O19" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O19</f>
-        <v>602826040</v>
+        <v>627892060</v>
       </c>
       <c r="P19" s="60"/>
       <c r="BP19" s="85"/>
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G20" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!G20</f>
-        <v>0</v>
+        <v>0.189421947074659</v>
       </c>
       <c r="H20" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!H20</f>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="O20" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!O20</f>
-        <v>0.354000397318717</v>
+        <v>0.368720035241456</v>
       </c>
       <c r="BP20" s="87"/>
       <c r="BQ20" s="88"/>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="G23" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!G23</f>
-        <v>0</v>
+        <v>673938.58</v>
       </c>
       <c r="H23" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!H23</f>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="O23" s="13">
         <f>'[1]特别隐藏版（勿动、勿看）'!O23</f>
-        <v>14245570.54</v>
+        <v>14919509.12</v>
       </c>
       <c r="P23" s="60"/>
       <c r="BP23" s="89"/>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="G24" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!G24</f>
-        <v>0</v>
+        <v>0.197850227036404</v>
       </c>
       <c r="H24" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!H24</f>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="O24" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!O24</f>
-        <v>0.32498469819241</v>
+        <v>0.340359282552267</v>
       </c>
       <c r="BP24" s="84"/>
       <c r="BQ24" s="84"/>
@@ -14741,9 +14741,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F26</f>
         <v>0.70390916276867</v>
       </c>
-      <c r="G26" s="66" t="e">
+      <c r="G26" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G26</f>
-        <v>#DIV/0!</v>
+        <v>0.663918234725736</v>
       </c>
       <c r="H26" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H26</f>
@@ -14775,7 +14775,7 @@
       </c>
       <c r="O26" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O26</f>
-        <v>0.704608593633414</v>
+        <v>0.702984197634224</v>
       </c>
       <c r="BP26" s="84"/>
       <c r="BQ26" s="91"/>
@@ -14819,9 +14819,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F27</f>
         <v>0.733192510300944</v>
       </c>
-      <c r="G27" s="66" t="e">
+      <c r="G27" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G27</f>
-        <v>#DIV/0!</v>
+        <v>0.73798349247451</v>
       </c>
       <c r="H27" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H27</f>
@@ -14853,7 +14853,7 @@
       </c>
       <c r="O27" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O27</f>
-        <v>0.728106383453446</v>
+        <v>0.728540345288546</v>
       </c>
       <c r="BP27" s="84"/>
       <c r="BQ27" s="91"/>
@@ -14897,9 +14897,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F28</f>
         <v>0.108095037564605</v>
       </c>
-      <c r="G28" s="66" t="e">
+      <c r="G28" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G28</f>
-        <v>#DIV/0!</v>
+        <v>0.116872742320227</v>
       </c>
       <c r="H28" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H28</f>
@@ -14931,7 +14931,7 @@
       </c>
       <c r="O28" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O28</f>
-        <v>0.115752816313667</v>
+        <v>0.115803405199433</v>
       </c>
       <c r="BP28" s="84"/>
       <c r="BQ28" s="91"/>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="G30" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G30</f>
-        <v>0</v>
+        <v>9785.19</v>
       </c>
       <c r="H30" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H30</f>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="O30" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O30</f>
-        <v>295886.16</v>
+        <v>305671.35</v>
       </c>
       <c r="BP30" s="89"/>
       <c r="BQ30" s="93"/>
@@ -15133,7 +15133,7 @@
       </c>
       <c r="G31" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G31</f>
-        <v>0</v>
+        <v>1241</v>
       </c>
       <c r="H31" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H31</f>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="O31" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O31</f>
-        <v>35938</v>
+        <v>37179</v>
       </c>
       <c r="BP31" s="89"/>
       <c r="BQ31" s="94"/>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="G32" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G32</f>
-        <v>0</v>
+        <v>327</v>
       </c>
       <c r="H32" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H32</f>
@@ -15243,7 +15243,7 @@
       </c>
       <c r="O32" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O32</f>
-        <v>9242</v>
+        <v>9569</v>
       </c>
       <c r="BP32" s="89"/>
       <c r="BQ32" s="94"/>
@@ -15289,7 +15289,7 @@
       </c>
       <c r="G33" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!G33</f>
-        <v>0</v>
+        <v>5149714</v>
       </c>
       <c r="H33" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!H33</f>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="O33" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!O33</f>
-        <v>154282420</v>
+        <v>159432134</v>
       </c>
       <c r="BP33" s="84"/>
       <c r="BQ33" s="95"/>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="G34" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G34</f>
-        <v>0</v>
+        <v>132662.14</v>
       </c>
       <c r="H34" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H34</f>
@@ -15399,7 +15399,7 @@
       </c>
       <c r="O34" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O34</f>
-        <v>3522312.49</v>
+        <v>3654974.63</v>
       </c>
       <c r="Q34" s="60"/>
       <c r="BP34" s="81"/>
@@ -15444,9 +15444,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F35</f>
         <v>0.708815495578813</v>
       </c>
-      <c r="G35" s="66" t="e">
+      <c r="G35" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G35</f>
-        <v>#DIV/0!</v>
+        <v>0.677986631878974</v>
       </c>
       <c r="H35" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H35</f>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="O35" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O35</f>
-        <v>0.714621366938631</v>
+        <v>0.713438052111878</v>
       </c>
       <c r="BP35" s="97"/>
       <c r="BQ35" s="98"/>
@@ -15522,9 +15522,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F36</f>
         <v>0.747212336892052</v>
       </c>
-      <c r="G36" s="66" t="e">
+      <c r="G36" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G36</f>
-        <v>#DIV/0!</v>
+        <v>0.736502820306205</v>
       </c>
       <c r="H36" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H36</f>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="O36" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O36</f>
-        <v>0.74283488229729</v>
+        <v>0.742623524032384</v>
       </c>
       <c r="BP36" s="97"/>
       <c r="BQ36" s="98"/>
@@ -15600,9 +15600,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F37</f>
         <v>0.0616780950056489</v>
       </c>
-      <c r="G37" s="66" t="e">
+      <c r="G37" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G37</f>
-        <v>#DIV/0!</v>
+        <v>0.0737602303113759</v>
       </c>
       <c r="H37" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H37</f>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="O37" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O37</f>
-        <v>0.0840033815398361</v>
+        <v>0.0836315928135457</v>
       </c>
       <c r="BP37" s="97"/>
       <c r="BQ37" s="98"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="G38" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G38</f>
-        <v>0</v>
+        <v>26838.4</v>
       </c>
       <c r="H38" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H38</f>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="O38" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O38</f>
-        <v>458849.93</v>
+        <v>485688.33</v>
       </c>
     </row>
     <row r="39" s="59" customFormat="1" spans="1:15">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="G39" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G39</f>
-        <v>0</v>
+        <v>1476</v>
       </c>
       <c r="H39" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H39</f>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="O39" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O39</f>
-        <v>34382</v>
+        <v>35858</v>
       </c>
     </row>
     <row r="40" s="59" customFormat="1" ht="17.4" spans="1:83">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="G40" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G40</f>
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="H40" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H40</f>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="O40" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O40</f>
-        <v>9857</v>
+        <v>10295</v>
       </c>
       <c r="BP40" s="80"/>
       <c r="BQ40" s="80"/>
@@ -15882,7 +15882,7 @@
       </c>
       <c r="G41" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!G41</f>
-        <v>0</v>
+        <v>5837821</v>
       </c>
       <c r="H41" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!H41</f>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="O41" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!O41</f>
-        <v>153367464</v>
+        <v>159205285</v>
       </c>
       <c r="Q41" s="61"/>
       <c r="BP41" s="62"/>
@@ -15961,7 +15961,7 @@
       </c>
       <c r="G42" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G42</f>
-        <v>0</v>
+        <v>183166.43</v>
       </c>
       <c r="H42" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H42</f>
@@ -15993,7 +15993,7 @@
       </c>
       <c r="O42" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O42</f>
-        <v>3873994.64</v>
+        <v>4057161.07</v>
       </c>
       <c r="Q42" s="60"/>
       <c r="BP42" s="62"/>
@@ -16038,9 +16038,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F43</f>
         <v>0.674241941045239</v>
       </c>
-      <c r="G43" s="66" t="e">
+      <c r="G43" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G43</f>
-        <v>#DIV/0!</v>
+        <v>0.607802230489767</v>
       </c>
       <c r="H43" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H43</f>
@@ -16072,7 +16072,7 @@
       </c>
       <c r="O43" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O43</f>
-        <v>0.684255501544969</v>
+        <v>0.681452073811494</v>
       </c>
       <c r="BP43" s="62"/>
       <c r="BQ43" s="62"/>
@@ -16116,9 +16116,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F44</f>
         <v>0.706094401261687</v>
       </c>
-      <c r="G44" s="66" t="e">
+      <c r="G44" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G44</f>
-        <v>#DIV/0!</v>
+        <v>0.703252032520325</v>
       </c>
       <c r="H44" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H44</f>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="O44" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O44</f>
-        <v>0.713309289744634</v>
+        <v>0.712895309275476</v>
       </c>
       <c r="BP44" s="62"/>
       <c r="BQ44" s="99"/>
@@ -16194,9 +16194,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F45</f>
         <v>0.0948935984334122</v>
       </c>
-      <c r="G45" s="66" t="e">
+      <c r="G45" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G45</f>
-        <v>#DIV/0!</v>
+        <v>0.146524666119223</v>
       </c>
       <c r="H45" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H45</f>
@@ -16228,7 +16228,7 @@
       </c>
       <c r="O45" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O45</f>
-        <v>0.118443615089772</v>
+        <v>0.119711374929465</v>
       </c>
       <c r="BP45" s="100"/>
       <c r="BQ45" s="101"/>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="G46" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G46</f>
-        <v>0</v>
+        <v>11212.49</v>
       </c>
       <c r="H46" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H46</f>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="O46" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O46</f>
-        <v>144581</v>
+        <v>155793.49</v>
       </c>
       <c r="BP46" s="62"/>
       <c r="BQ46" s="68"/>
@@ -16350,7 +16350,7 @@
       </c>
       <c r="G47" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G47</f>
-        <v>0</v>
+        <v>988</v>
       </c>
       <c r="H47" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H47</f>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="O47" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O47</f>
-        <v>18116</v>
+        <v>19104</v>
       </c>
       <c r="BP47" s="100"/>
       <c r="BQ47" s="102"/>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="G48" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G48</f>
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="H48" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H48</f>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="O48" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O48</f>
-        <v>4932</v>
+        <v>5188</v>
       </c>
       <c r="BP48" s="100"/>
       <c r="BQ48" s="100"/>
@@ -16504,7 +16504,7 @@
       </c>
       <c r="G49" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!G49</f>
-        <v>0</v>
+        <v>3403246</v>
       </c>
       <c r="H49" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!H49</f>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="O49" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!O49</f>
-        <v>76776689</v>
+        <v>80179935</v>
       </c>
       <c r="Q49" s="61"/>
       <c r="BP49" s="103"/>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="G50" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G50</f>
-        <v>0</v>
+        <v>96010.5</v>
       </c>
       <c r="H50" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H50</f>
@@ -16614,7 +16614,7 @@
       </c>
       <c r="O50" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O50</f>
-        <v>1823158.3</v>
+        <v>1919168.8</v>
       </c>
       <c r="Q50" s="60"/>
       <c r="BP50" s="103"/>
@@ -16658,9 +16658,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F51</f>
         <v>0.683208329743717</v>
       </c>
-      <c r="G51" s="66" t="e">
+      <c r="G51" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G51</f>
-        <v>#DIV/0!</v>
+        <v>0.647356891038732</v>
       </c>
       <c r="H51" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H51</f>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="O51" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O51</f>
-        <v>0.703171899611352</v>
+        <v>0.70080282554482</v>
       </c>
       <c r="BP51" s="103"/>
       <c r="BQ51" s="104"/>
@@ -16733,9 +16733,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F52</f>
         <v>0.717705580600031</v>
       </c>
-      <c r="G52" s="66" t="e">
+      <c r="G52" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G52</f>
-        <v>#DIV/0!</v>
+        <v>0.740890688259109</v>
       </c>
       <c r="H52" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H52</f>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="O52" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O52</f>
-        <v>0.727754471185692</v>
+        <v>0.728433835845896</v>
       </c>
     </row>
     <row r="53" s="59" customFormat="1" spans="1:15">
@@ -16795,9 +16795,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F53</f>
         <v>0.122921422307025</v>
       </c>
-      <c r="G53" s="66" t="e">
+      <c r="G53" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G53</f>
-        <v>#DIV/0!</v>
+        <v>0.116783997583598</v>
       </c>
       <c r="H53" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H53</f>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="O53" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O53</f>
-        <v>0.0793024939194803</v>
+        <v>0.0811775858382024</v>
       </c>
     </row>
     <row r="54" s="59" customFormat="1" spans="1:15">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="G54" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G54</f>
-        <v>0</v>
+        <v>9115.55</v>
       </c>
       <c r="H54" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H54</f>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="O54" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O54</f>
-        <v>320946.42</v>
+        <v>330061.97</v>
       </c>
     </row>
     <row r="55" s="59" customFormat="1" spans="1:15">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="G55" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G55</f>
-        <v>0</v>
+        <v>425</v>
       </c>
       <c r="H55" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H55</f>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="O55" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O55</f>
-        <v>15774</v>
+        <v>16199</v>
       </c>
     </row>
     <row r="56" s="59" customFormat="1" spans="1:15">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="G56" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G56</f>
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="H56" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H56</f>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="O56" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O56</f>
-        <v>5727</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="57" s="59" customFormat="1" spans="1:17">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="G57" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!G57</f>
-        <v>0</v>
+        <v>1725641</v>
       </c>
       <c r="H57" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!H57</f>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="O57" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!O57</f>
-        <v>63716504</v>
+        <v>65442145</v>
       </c>
       <c r="Q57" s="61"/>
     </row>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="G58" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G58</f>
-        <v>0</v>
+        <v>63977.49</v>
       </c>
       <c r="H58" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H58</f>
@@ -17140,7 +17140,7 @@
       </c>
       <c r="O58" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O58</f>
-        <v>2108653.48</v>
+        <v>2172630.97</v>
       </c>
       <c r="Q58" s="60"/>
     </row>
@@ -17169,9 +17169,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F59</f>
         <v>0.582292653498827</v>
       </c>
-      <c r="G59" s="66" t="e">
+      <c r="G59" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G59</f>
-        <v>#DIV/0!</v>
+        <v>0.536567208938592</v>
       </c>
       <c r="H59" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H59</f>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="O59" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O59</f>
-        <v>0.586321175122854</v>
+        <v>0.585009215009685</v>
       </c>
     </row>
     <row r="60" s="59" customFormat="1" spans="1:15">
@@ -17231,9 +17231,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F60</f>
         <v>0.638123167155425</v>
       </c>
-      <c r="G60" s="66" t="e">
+      <c r="G60" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G60</f>
-        <v>#DIV/0!</v>
+        <v>0.618823529411765</v>
       </c>
       <c r="H60" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H60</f>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="O60" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O60</f>
-        <v>0.636934195511601</v>
+        <v>0.636459040681524</v>
       </c>
     </row>
     <row r="61" s="59" customFormat="1" spans="1:15">
@@ -17293,9 +17293,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F61</f>
         <v>0.115278269253467</v>
       </c>
-      <c r="G61" s="66" t="e">
+      <c r="G61" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G61</f>
-        <v>#DIV/0!</v>
+        <v>0.142480581842145</v>
       </c>
       <c r="H61" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H61</f>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="O61" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O61</f>
-        <v>0.152204439014797</v>
+        <v>0.151918100477045</v>
       </c>
     </row>
     <row r="62" s="59" customFormat="1" spans="1:15">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="G62" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G62</f>
-        <v>0</v>
+        <v>21813.42</v>
       </c>
       <c r="H62" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H62</f>
@@ -17389,7 +17389,7 @@
       </c>
       <c r="O62" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O62</f>
-        <v>428701.4</v>
+        <v>450514.82</v>
       </c>
     </row>
     <row r="63" s="59" customFormat="1" spans="1:15">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="G63" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G63</f>
-        <v>0</v>
+        <v>2049</v>
       </c>
       <c r="H63" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H63</f>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="O63" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O63</f>
-        <v>30247</v>
+        <v>32296</v>
       </c>
     </row>
     <row r="64" s="59" customFormat="1" spans="1:15">
@@ -17481,7 +17481,7 @@
       </c>
       <c r="G64" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G64</f>
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="H64" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H64</f>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="O64" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O64</f>
-        <v>6800</v>
+        <v>7236</v>
       </c>
     </row>
     <row r="65" s="59" customFormat="1" spans="1:17">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="G65" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!G65</f>
-        <v>0</v>
+        <v>8949598</v>
       </c>
       <c r="H65" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!H65</f>
@@ -17575,7 +17575,7 @@
       </c>
       <c r="O65" s="70">
         <f>'[1]特别隐藏版（勿动、勿看）'!O65</f>
-        <v>154682963</v>
+        <v>163632561</v>
       </c>
       <c r="Q65" s="61"/>
     </row>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="G66" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G66</f>
-        <v>0</v>
+        <v>198122.02</v>
       </c>
       <c r="H66" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!H66</f>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="O66" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!O66</f>
-        <v>2917451.63</v>
+        <v>3115573.65</v>
       </c>
       <c r="Q66" s="60"/>
     </row>
@@ -17667,9 +17667,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F67</f>
         <v>0.761663155253249</v>
       </c>
-      <c r="G67" s="66" t="e">
+      <c r="G67" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G67</f>
-        <v>#DIV/0!</v>
+        <v>0.723280838982935</v>
       </c>
       <c r="H67" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H67</f>
@@ -17701,7 +17701,7 @@
       </c>
       <c r="O67" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O67</f>
-        <v>0.76423941804761</v>
+        <v>0.761999259884468</v>
       </c>
     </row>
     <row r="68" s="59" customFormat="1" spans="1:15">
@@ -17729,9 +17729,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F68</f>
         <v>0.781975705609146</v>
       </c>
-      <c r="G68" s="66" t="e">
+      <c r="G68" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G68</f>
-        <v>#DIV/0!</v>
+        <v>0.78721327476818</v>
       </c>
       <c r="H68" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H68</f>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="O68" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O68</f>
-        <v>0.775184315799914</v>
+        <v>0.77594748575675</v>
       </c>
     </row>
     <row r="69" s="59" customFormat="1" spans="1:15">
@@ -17791,9 +17791,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F69</f>
         <v>0.144908303683073</v>
       </c>
-      <c r="G69" s="66" t="e">
+      <c r="G69" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!G69</f>
-        <v>#DIV/0!</v>
+        <v>0.11010093678633</v>
       </c>
       <c r="H69" s="66" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H69</f>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="O69" s="66">
         <f>'[1]特别隐藏版（勿动、勿看）'!O69</f>
-        <v>0.146943790118639</v>
+        <v>0.144600921246076</v>
       </c>
     </row>
     <row r="70" s="59" customFormat="1" spans="1:15">
@@ -21327,7 +21327,7 @@
       </c>
       <c r="G126" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G126</f>
-        <v>0</v>
+        <v>9383.18</v>
       </c>
       <c r="H126" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H126</f>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="O126" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O126</f>
-        <v>285029.35</v>
+        <v>294412.53</v>
       </c>
     </row>
     <row r="127" s="59" customFormat="1" spans="1:15">
@@ -21389,7 +21389,7 @@
       </c>
       <c r="G127" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G127</f>
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="H127" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H127</f>
@@ -21421,7 +21421,7 @@
       </c>
       <c r="O127" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O127</f>
-        <v>13376</v>
+        <v>13768</v>
       </c>
     </row>
     <row r="128" s="59" customFormat="1" spans="1:15">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="G128" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G128</f>
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="H128" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H128</f>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="O128" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O128</f>
-        <v>4974</v>
+        <v>5126</v>
       </c>
     </row>
     <row r="129" s="59" customFormat="1" spans="1:15">
@@ -21513,7 +21513,7 @@
       </c>
       <c r="G129" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G129</f>
-        <v>0</v>
+        <v>1566038</v>
       </c>
       <c r="H129" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H129</f>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="O129" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O129</f>
-        <v>53903724</v>
+        <v>55469762</v>
       </c>
     </row>
     <row r="130" s="59" customFormat="1" spans="1:15">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="G130" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!G130</f>
-        <v>0</v>
+        <v>59649.73</v>
       </c>
       <c r="H130" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!H130</f>
@@ -21607,7 +21607,7 @@
       </c>
       <c r="O130" s="62">
         <f>'[1]特别隐藏版（勿动、勿看）'!O130</f>
-        <v>1808831.59</v>
+        <v>1868481.32</v>
       </c>
     </row>
     <row r="131" s="59" customFormat="1" spans="1:15">
@@ -21635,9 +21635,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F131</f>
         <v>0.433024696168176</v>
       </c>
-      <c r="G131" s="14" t="e">
+      <c r="G131" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!G131</f>
-        <v>#DIV/0!</v>
+        <v>0.47611975252197</v>
       </c>
       <c r="H131" s="14" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H131</f>
@@ -21669,7 +21669,7 @@
       </c>
       <c r="O131" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!O131</f>
-        <v>0.0335567091802414</v>
+        <v>0.0336846824761931</v>
       </c>
     </row>
     <row r="132" s="59" customFormat="1" spans="1:15">
@@ -21697,9 +21697,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F132</f>
         <v>0.62784</v>
       </c>
-      <c r="G132" s="14" t="e">
+      <c r="G132" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!G132</f>
-        <v>#DIV/0!</v>
+        <v>0.612244897959184</v>
       </c>
       <c r="H132" s="14" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H132</f>
@@ -21731,7 +21731,7 @@
       </c>
       <c r="O132" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!O132</f>
-        <v>0.62813995215311</v>
+        <v>0.627687391051714</v>
       </c>
     </row>
     <row r="133" s="59" customFormat="1" spans="1:15">
@@ -21759,9 +21759,9 @@
         <f>'[1]特别隐藏版（勿动、勿看）'!F133</f>
         <v>0.128707436355849</v>
       </c>
-      <c r="G133" s="14" t="e">
+      <c r="G133" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!G133</f>
-        <v>#DIV/0!</v>
+        <v>0.157304651672355</v>
       </c>
       <c r="H133" s="14" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H133</f>
@@ -21793,7 +21793,7 @@
       </c>
       <c r="O133" s="14">
         <f>'[1]特别隐藏版（勿动、勿看）'!O133</f>
-        <v>0.157576499424139</v>
+        <v>0.157567820908159</v>
       </c>
     </row>
     <row r="134" spans="1:15">
@@ -24518,7 +24518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{05654565-5192-4bb6-b78d-10eab50def63}</x14:id>
+          <x14:id>{b5c5f5fa-5257-4f42-9d58-f665da43dfc2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24532,7 +24532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f3c4205-ed6d-488b-b838-77b80fce4483}</x14:id>
+          <x14:id>{dcd8244d-9c73-4ec4-a81a-9bea880b86ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24546,7 +24546,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e08c6043-b4d6-45bb-86ef-1f7486d4e376}</x14:id>
+          <x14:id>{c815b58d-47b6-4670-ac89-c0a9b3518073}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24560,7 +24560,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{133a7019-e100-4eff-86cc-10f1cb30071b}</x14:id>
+          <x14:id>{af60c89b-8868-4dae-b56b-0a4f1026b02e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24574,7 +24574,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ac105a2-705a-4dd1-81ab-3d4aeeeb8e78}</x14:id>
+          <x14:id>{ac8634e1-dc23-4a7f-8a35-444cb431671e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24588,7 +24588,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e01665e5-936b-4e81-b914-8d63579d73b2}</x14:id>
+          <x14:id>{c6f28e9d-2c80-4d4f-9178-dbd2e08050c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24602,7 +24602,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{439e90c5-bafc-4525-8a31-2661f7aab031}</x14:id>
+          <x14:id>{45e4cb60-da89-4e0e-9738-6263c7dba569}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24616,7 +24616,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34dae263-36c9-46c2-94f2-e08a4f114eb4}</x14:id>
+          <x14:id>{ba934f2b-5b8b-4054-b523-b4e35a4d0964}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24630,7 +24630,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{270dcf95-64d7-489a-9d3d-6ac33ba88550}</x14:id>
+          <x14:id>{755ce089-ae7c-4b88-84c6-9005ab02e6fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24644,7 +24644,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3e1ce8b7-131d-4f96-a8c4-594d5b373ce8}</x14:id>
+          <x14:id>{1d9a4045-4cd2-475e-9ea1-89ae4a479a06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24658,7 +24658,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e1019aa-1c02-4c96-8e9d-e0420bfd11ad}</x14:id>
+          <x14:id>{3d114b53-4c56-4ab7-97bb-3f42b546e1b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24672,7 +24672,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b3d796e-5c13-478f-88fd-662a2cb8cf33}</x14:id>
+          <x14:id>{d634cf07-3e34-4154-bff7-f030a89bdd67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24686,7 +24686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84abec3f-59cf-48f8-900d-cc02568fcada}</x14:id>
+          <x14:id>{17681e2e-4ebe-4ead-b057-873d8186c741}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24708,7 +24708,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c53d5acd-8f00-48e2-a37f-35ed72c426f0}</x14:id>
+          <x14:id>{6f571827-6e4d-49fa-968f-5b5407c7f774}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24738,7 +24738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b567df2-7489-4e5f-a23d-45c149032609}</x14:id>
+          <x14:id>{f219ea5c-7eae-4c9e-9e46-13429c14516d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24768,7 +24768,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77e13d68-3bef-4d68-b8d8-dc96e3bb88e4}</x14:id>
+          <x14:id>{2e948bf5-6e4e-4164-9260-c68de0b15637}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24798,7 +24798,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f630d693-156c-49b8-b0f9-bec266d3eb3e}</x14:id>
+          <x14:id>{1dbb3393-8f2d-41ad-9cdb-f52c186711fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24828,7 +24828,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{28fabc61-1ca2-497f-9da8-77ca133c6964}</x14:id>
+          <x14:id>{1088b95a-b82c-4691-b3e4-3d7131d182aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24858,7 +24858,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3aee5052-23e0-4a67-a0ca-ccc2f4b1f2ba}</x14:id>
+          <x14:id>{f859ec85-79c8-41f5-a202-d147e656aed0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24888,7 +24888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c92e5cd9-ad13-4abd-a251-dbd1128f9761}</x14:id>
+          <x14:id>{d83b2322-d8d5-49b3-a8a5-a0af0a359f94}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24918,7 +24918,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a55e3e8a-e187-4990-8e05-7e8b600b4787}</x14:id>
+          <x14:id>{46fd2ed6-f61d-4465-b184-9a9998e40872}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24940,7 +24940,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8891f041-594d-4059-89a6-a4bd69ded8cf}</x14:id>
+          <x14:id>{a148812f-2ad7-4d32-83f4-8da74d81bda0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24962,7 +24962,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2d28a96-75cd-46e4-b6a4-499dc3d52b9f}</x14:id>
+          <x14:id>{9284a6f8-0fd8-49c2-bc22-4b1a1a075837}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24984,7 +24984,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{21884b58-8249-44f2-9f26-df917775d0f5}</x14:id>
+          <x14:id>{ad7eb133-f7a4-4159-87dd-4d472d4cc591}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25006,7 +25006,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72d27891-d52a-4464-b39f-a5d5f930eed5}</x14:id>
+          <x14:id>{fe0d6447-a6d8-4020-8ef7-645577080a35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25028,7 +25028,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d13aec96-82fc-496b-b2da-580d87c90cc8}</x14:id>
+          <x14:id>{bb62124b-8ec5-4ec6-8e6f-9ef864246818}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25050,7 +25050,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{40b18692-7888-477b-9297-fb7d6577908b}</x14:id>
+          <x14:id>{c68e9d7b-b605-4642-8777-6faaa0803da9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25072,7 +25072,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9729da13-8643-453b-9558-5220e408e4af}</x14:id>
+          <x14:id>{8e43f611-6be1-41cb-b675-41b11ece3b8c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25094,7 +25094,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ccc59ee-f6c6-49a6-898e-59be294bd857}</x14:id>
+          <x14:id>{bc837f4e-39a9-40d1-88ff-062324ff9941}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25116,7 +25116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbe9cec5-7002-49d6-a4ff-b88be4f5c61a}</x14:id>
+          <x14:id>{d6962a74-d583-4e1e-a029-e3ee4fa19850}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25138,7 +25138,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{08126eed-3a0b-4729-9f30-6efcba9e4cb8}</x14:id>
+          <x14:id>{0cd63c1a-e672-4c0c-ae44-c90f847699b2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25160,7 +25160,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4139a940-b610-412d-92e8-33ba27f8f373}</x14:id>
+          <x14:id>{382ea263-e402-4125-b5b5-a9bc018b1a39}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25182,7 +25182,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2caa9af2-fe50-4683-b3cf-e07c5cafb5d9}</x14:id>
+          <x14:id>{6e0f0d5d-af6b-42a3-848a-82e9d3195829}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25201,7 +25201,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{05654565-5192-4bb6-b78d-10eab50def63}">
+          <x14:cfRule type="dataBar" id="{b5c5f5fa-5257-4f42-9d58-f665da43dfc2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25214,7 +25214,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5f3c4205-ed6d-488b-b838-77b80fce4483}">
+          <x14:cfRule type="dataBar" id="{dcd8244d-9c73-4ec4-a81a-9bea880b86ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25227,7 +25227,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e08c6043-b4d6-45bb-86ef-1f7486d4e376}">
+          <x14:cfRule type="dataBar" id="{c815b58d-47b6-4670-ac89-c0a9b3518073}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25240,7 +25240,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{133a7019-e100-4eff-86cc-10f1cb30071b}">
+          <x14:cfRule type="dataBar" id="{af60c89b-8868-4dae-b56b-0a4f1026b02e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25253,7 +25253,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2ac105a2-705a-4dd1-81ab-3d4aeeeb8e78}">
+          <x14:cfRule type="dataBar" id="{ac8634e1-dc23-4a7f-8a35-444cb431671e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25266,7 +25266,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e01665e5-936b-4e81-b914-8d63579d73b2}">
+          <x14:cfRule type="dataBar" id="{c6f28e9d-2c80-4d4f-9178-dbd2e08050c6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25279,7 +25279,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{439e90c5-bafc-4525-8a31-2661f7aab031}">
+          <x14:cfRule type="dataBar" id="{45e4cb60-da89-4e0e-9738-6263c7dba569}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25292,7 +25292,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{34dae263-36c9-46c2-94f2-e08a4f114eb4}">
+          <x14:cfRule type="dataBar" id="{ba934f2b-5b8b-4054-b523-b4e35a4d0964}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25305,7 +25305,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{270dcf95-64d7-489a-9d3d-6ac33ba88550}">
+          <x14:cfRule type="dataBar" id="{755ce089-ae7c-4b88-84c6-9005ab02e6fc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25318,7 +25318,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3e1ce8b7-131d-4f96-a8c4-594d5b373ce8}">
+          <x14:cfRule type="dataBar" id="{1d9a4045-4cd2-475e-9ea1-89ae4a479a06}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25331,7 +25331,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1e1019aa-1c02-4c96-8e9d-e0420bfd11ad}">
+          <x14:cfRule type="dataBar" id="{3d114b53-4c56-4ab7-97bb-3f42b546e1b5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25344,7 +25344,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b3d796e-5c13-478f-88fd-662a2cb8cf33}">
+          <x14:cfRule type="dataBar" id="{d634cf07-3e34-4154-bff7-f030a89bdd67}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25357,7 +25357,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{84abec3f-59cf-48f8-900d-cc02568fcada}">
+          <x14:cfRule type="dataBar" id="{17681e2e-4ebe-4ead-b057-873d8186c741}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25370,7 +25370,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c53d5acd-8f00-48e2-a37f-35ed72c426f0}">
+          <x14:cfRule type="dataBar" id="{6f571827-6e4d-49fa-968f-5b5407c7f774}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25383,7 +25383,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b567df2-7489-4e5f-a23d-45c149032609}">
+          <x14:cfRule type="dataBar" id="{f219ea5c-7eae-4c9e-9e46-13429c14516d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25396,7 +25396,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{77e13d68-3bef-4d68-b8d8-dc96e3bb88e4}">
+          <x14:cfRule type="dataBar" id="{2e948bf5-6e4e-4164-9260-c68de0b15637}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25409,7 +25409,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f630d693-156c-49b8-b0f9-bec266d3eb3e}">
+          <x14:cfRule type="dataBar" id="{1dbb3393-8f2d-41ad-9cdb-f52c186711fb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25422,7 +25422,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{28fabc61-1ca2-497f-9da8-77ca133c6964}">
+          <x14:cfRule type="dataBar" id="{1088b95a-b82c-4691-b3e4-3d7131d182aa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25435,7 +25435,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3aee5052-23e0-4a67-a0ca-ccc2f4b1f2ba}">
+          <x14:cfRule type="dataBar" id="{f859ec85-79c8-41f5-a202-d147e656aed0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25448,7 +25448,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c92e5cd9-ad13-4abd-a251-dbd1128f9761}">
+          <x14:cfRule type="dataBar" id="{d83b2322-d8d5-49b3-a8a5-a0af0a359f94}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25461,7 +25461,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a55e3e8a-e187-4990-8e05-7e8b600b4787}">
+          <x14:cfRule type="dataBar" id="{46fd2ed6-f61d-4465-b184-9a9998e40872}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25474,7 +25474,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8891f041-594d-4059-89a6-a4bd69ded8cf}">
+          <x14:cfRule type="dataBar" id="{a148812f-2ad7-4d32-83f4-8da74d81bda0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25487,7 +25487,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b2d28a96-75cd-46e4-b6a4-499dc3d52b9f}">
+          <x14:cfRule type="dataBar" id="{9284a6f8-0fd8-49c2-bc22-4b1a1a075837}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25500,7 +25500,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{21884b58-8249-44f2-9f26-df917775d0f5}">
+          <x14:cfRule type="dataBar" id="{ad7eb133-f7a4-4159-87dd-4d472d4cc591}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25513,7 +25513,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72d27891-d52a-4464-b39f-a5d5f930eed5}">
+          <x14:cfRule type="dataBar" id="{fe0d6447-a6d8-4020-8ef7-645577080a35}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25526,7 +25526,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d13aec96-82fc-496b-b2da-580d87c90cc8}">
+          <x14:cfRule type="dataBar" id="{bb62124b-8ec5-4ec6-8e6f-9ef864246818}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25539,7 +25539,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{40b18692-7888-477b-9297-fb7d6577908b}">
+          <x14:cfRule type="dataBar" id="{c68e9d7b-b605-4642-8777-6faaa0803da9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25552,7 +25552,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9729da13-8643-453b-9558-5220e408e4af}">
+          <x14:cfRule type="dataBar" id="{8e43f611-6be1-41cb-b675-41b11ece3b8c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25565,7 +25565,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ccc59ee-f6c6-49a6-898e-59be294bd857}">
+          <x14:cfRule type="dataBar" id="{bc837f4e-39a9-40d1-88ff-062324ff9941}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25578,7 +25578,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dbe9cec5-7002-49d6-a4ff-b88be4f5c61a}">
+          <x14:cfRule type="dataBar" id="{d6962a74-d583-4e1e-a029-e3ee4fa19850}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25591,7 +25591,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{08126eed-3a0b-4729-9f30-6efcba9e4cb8}">
+          <x14:cfRule type="dataBar" id="{0cd63c1a-e672-4c0c-ae44-c90f847699b2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25604,7 +25604,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4139a940-b610-412d-92e8-33ba27f8f373}">
+          <x14:cfRule type="dataBar" id="{382ea263-e402-4125-b5b5-a9bc018b1a39}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25617,7 +25617,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2caa9af2-fe50-4683-b3cf-e07c5cafb5d9}">
+          <x14:cfRule type="dataBar" id="{6e0f0d5d-af6b-42a3-848a-82e9d3195829}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="F4" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F4</f>
-        <v>685537.218</v>
+        <v>782699.5281</v>
       </c>
       <c r="G4" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G4</f>
@@ -26049,7 +26049,7 @@
       </c>
       <c r="G7" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G7</f>
-        <v>0</v>
+        <v>100167.33</v>
       </c>
       <c r="H7" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H7</f>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="O7" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O7</f>
-        <v>2518797.87</v>
+        <v>2618965.2</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:15">
@@ -26103,7 +26103,7 @@
       </c>
       <c r="E8" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!E8</f>
-        <v>1.31577889268891</v>
+        <v>1.3157788926889</v>
       </c>
       <c r="F8" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F8</f>
@@ -26111,7 +26111,7 @@
       </c>
       <c r="G8" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G8</f>
-        <v>0</v>
+        <v>0.184404202252453</v>
       </c>
       <c r="H8" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H8</f>
@@ -26143,7 +26143,7 @@
       </c>
       <c r="O8" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O8</f>
-        <v>0.28768932935122</v>
+        <v>0.299130133051202</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:15">
@@ -26297,7 +26297,7 @@
       </c>
       <c r="G11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G11</f>
-        <v>0</v>
+        <v>5553</v>
       </c>
       <c r="H11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H11</f>
@@ -26329,7 +26329,7 @@
       </c>
       <c r="O11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O11</f>
-        <v>129003</v>
+        <v>134556</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:15">
@@ -26359,7 +26359,7 @@
       </c>
       <c r="G12" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G12</f>
-        <v>0</v>
+        <v>0.15425</v>
       </c>
       <c r="H12" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H12</f>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="O12" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O12</f>
-        <v>0.2220850720985</v>
+        <v>0.231644837416849</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:15">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="G15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G15</f>
-        <v>0</v>
+        <v>1865</v>
       </c>
       <c r="H15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H15</f>
@@ -26577,7 +26577,7 @@
       </c>
       <c r="O15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O15</f>
-        <v>46064</v>
+        <v>47929</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:15">
@@ -26607,7 +26607,7 @@
       </c>
       <c r="G16" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G16</f>
-        <v>0</v>
+        <v>0.167114695340502</v>
       </c>
       <c r="H16" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H16</f>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="O16" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O16</f>
-        <v>0.255811174212385</v>
+        <v>0.266168239163456</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:15">
@@ -26789,11 +26789,11 @@
       </c>
       <c r="F19" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F19</f>
-        <v>113914619.8752</v>
+        <v>13661971.3112</v>
       </c>
       <c r="G19" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G19</f>
-        <v>0</v>
+        <v>2247713.1192</v>
       </c>
       <c r="H19" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H19</f>
@@ -26825,7 +26825,7 @@
       </c>
       <c r="O19" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O19</f>
-        <v>149625301.111</v>
+        <v>51620365.6662</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:15">
@@ -26851,11 +26851,11 @@
       </c>
       <c r="F20" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F20</f>
-        <v>10.2369767028764</v>
+        <v>1.22773777572485</v>
       </c>
       <c r="G20" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G20</f>
-        <v>0</v>
+        <v>0.179587177948226</v>
       </c>
       <c r="H20" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H20</f>
@@ -26887,7 +26887,7 @@
       </c>
       <c r="O20" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O20</f>
-        <v>0.741831472049483</v>
+        <v>0.255930057052861</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:15">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="G23" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G23</f>
-        <v>0</v>
+        <v>684372.3</v>
       </c>
       <c r="H23" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H23</f>
@@ -27073,7 +27073,7 @@
       </c>
       <c r="O23" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O23</f>
-        <v>16442530.11</v>
+        <v>17126902.41</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:15">
@@ -27103,7 +27103,7 @@
       </c>
       <c r="G24" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G24</f>
-        <v>0</v>
+        <v>0.170874355824545</v>
       </c>
       <c r="H24" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H24</f>
@@ -27135,7 +27135,7 @@
       </c>
       <c r="O24" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O24</f>
-        <v>0.254752752065274</v>
+        <v>0.265356091435546</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:15">
@@ -27223,11 +27223,11 @@
       </c>
       <c r="F26" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F26</f>
-        <v>0.0384744117550636</v>
-      </c>
-      <c r="G26" s="14" t="e">
+        <v>0.320802751679548</v>
+      </c>
+      <c r="G26" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G26</f>
-        <v>#DIV/0!</v>
+        <v>0.304474932389762</v>
       </c>
       <c r="H26" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H26</f>
@@ -27259,7 +27259,7 @@
       </c>
       <c r="O26" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O26</f>
-        <v>0.109891375241424</v>
+        <v>0.331785763021326</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:15">
@@ -27287,9 +27287,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F27</f>
         <v>0.639861587602035</v>
       </c>
-      <c r="G27" s="14" t="e">
+      <c r="G27" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G27</f>
-        <v>#DIV/0!</v>
+        <v>0.664145506933189</v>
       </c>
       <c r="H27" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H27</f>
@@ -27321,7 +27321,7 @@
       </c>
       <c r="O27" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O27</f>
-        <v>0.642923032797687</v>
+        <v>0.64379886441333</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:15">
@@ -27349,9 +27349,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F28</f>
         <v>0.161253017276299</v>
       </c>
-      <c r="G28" s="14" t="e">
+      <c r="G28" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G28</f>
-        <v>#DIV/0!</v>
+        <v>0.146363799353071</v>
       </c>
       <c r="H28" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H28</f>
@@ -27383,7 +27383,7 @@
       </c>
       <c r="O28" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O28</f>
-        <v>0.153187973696829</v>
+        <v>0.152915287149114</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:15">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="G30" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G30</f>
-        <v>0</v>
+        <v>48925.87</v>
       </c>
       <c r="H30" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H30</f>
@@ -27507,7 +27507,7 @@
       </c>
       <c r="O30" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O30</f>
-        <v>1558473.42</v>
+        <v>1607399.29</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:15">
@@ -27537,7 +27537,7 @@
       </c>
       <c r="G31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G31</f>
-        <v>0</v>
+        <v>2331</v>
       </c>
       <c r="H31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H31</f>
@@ -27569,7 +27569,7 @@
       </c>
       <c r="O31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O31</f>
-        <v>65851</v>
+        <v>68182</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:15">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="G32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G32</f>
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="H32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H32</f>
@@ -27631,7 +27631,7 @@
       </c>
       <c r="O32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O32</f>
-        <v>24552</v>
+        <v>25418</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:15">
@@ -27657,11 +27657,11 @@
       </c>
       <c r="F33" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F33</f>
-        <v>58337318.9976</v>
+        <v>7017450.9096</v>
       </c>
       <c r="G33" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G33</f>
-        <v>0</v>
+        <v>981973.6656</v>
       </c>
       <c r="H33" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H33</f>
@@ -27693,7 +27693,7 @@
       </c>
       <c r="O33" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O33</f>
-        <v>78195863.6061</v>
+        <v>27857969.1837</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:15">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="G34" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G34</f>
-        <v>0</v>
+        <v>332705.62</v>
       </c>
       <c r="H34" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H34</f>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="O34" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O34</f>
-        <v>8981287.63</v>
+        <v>9313993.25</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:15">
@@ -27781,11 +27781,11 @@
       </c>
       <c r="F35" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F35</f>
-        <v>0.0402603655834205</v>
-      </c>
-      <c r="G35" s="14" t="e">
+        <v>0.334691588192938</v>
+      </c>
+      <c r="G35" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G35</f>
-        <v>#DIV/0!</v>
+        <v>0.338813179675966</v>
       </c>
       <c r="H35" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H35</f>
@@ -27817,7 +27817,7 @@
       </c>
       <c r="O35" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O35</f>
-        <v>0.114856300778797</v>
+        <v>0.334338558154832</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:15">
@@ -27845,9 +27845,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F36</f>
         <v>0.626949034209914</v>
       </c>
-      <c r="G36" s="14" t="e">
+      <c r="G36" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G36</f>
-        <v>#DIV/0!</v>
+        <v>0.628485628485629</v>
       </c>
       <c r="H36" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H36</f>
@@ -27879,7 +27879,7 @@
       </c>
       <c r="O36" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O36</f>
-        <v>0.627158281575071</v>
+        <v>0.627203660790238</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:15">
@@ -27907,9 +27907,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F37</f>
         <v>0.155129035168276</v>
       </c>
-      <c r="G37" s="14" t="e">
+      <c r="G37" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G37</f>
-        <v>#DIV/0!</v>
+        <v>0.147054534275676</v>
       </c>
       <c r="H37" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H37</f>
@@ -27941,7 +27941,7 @@
       </c>
       <c r="O37" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O37</f>
-        <v>0.173524497177249</v>
+        <v>0.172578962304917</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:15">
@@ -27971,7 +27971,7 @@
       </c>
       <c r="G38" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G38</f>
-        <v>0</v>
+        <v>13496.52</v>
       </c>
       <c r="H38" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H38</f>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="O38" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O38</f>
-        <v>477565.86</v>
+        <v>491062.38</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:15">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="G39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G39</f>
-        <v>0</v>
+        <v>1689</v>
       </c>
       <c r="H39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H39</f>
@@ -28065,7 +28065,7 @@
       </c>
       <c r="O39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O39</f>
-        <v>27658</v>
+        <v>29347</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:15">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="G40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G40</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="H40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H40</f>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="O40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O40</f>
-        <v>9274</v>
+        <v>9624</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:15">
@@ -28153,11 +28153,11 @@
       </c>
       <c r="F41" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F41</f>
-        <v>22042814.7656</v>
+        <v>2746120.052</v>
       </c>
       <c r="G41" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G41</f>
-        <v>0</v>
+        <v>489604.2696</v>
       </c>
       <c r="H41" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H41</f>
@@ -28189,7 +28189,7 @@
       </c>
       <c r="O41" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O41</f>
-        <v>29036903.9346</v>
+        <v>10229813.4906</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:15">
@@ -28219,7 +28219,7 @@
       </c>
       <c r="G42" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G42</f>
-        <v>0</v>
+        <v>123275.95</v>
       </c>
       <c r="H42" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H42</f>
@@ -28251,7 +28251,7 @@
       </c>
       <c r="O42" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O42</f>
-        <v>3023164.98</v>
+        <v>3146440.93</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:15">
@@ -28277,11 +28277,11 @@
       </c>
       <c r="F43" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F43</f>
-        <v>0.039075793139822</v>
-      </c>
-      <c r="G43" s="14" t="e">
+        <v>0.313657252301364</v>
+      </c>
+      <c r="G43" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G43</f>
-        <v>#DIV/0!</v>
+        <v>0.251786917832058</v>
       </c>
       <c r="H43" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H43</f>
@@ -28313,7 +28313,7 @@
       </c>
       <c r="O43" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O43</f>
-        <v>0.104114577325775</v>
+        <v>0.307575590981322</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:15">
@@ -28341,9 +28341,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F44</f>
         <v>0.646949030868629</v>
       </c>
-      <c r="G44" s="14" t="e">
+      <c r="G44" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G44</f>
-        <v>#DIV/0!</v>
+        <v>0.792776791000592</v>
       </c>
       <c r="H44" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H44</f>
@@ -28375,7 +28375,7 @@
       </c>
       <c r="O44" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O44</f>
-        <v>0.664690143900499</v>
+        <v>0.672061880260333</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:15">
@@ -28403,9 +28403,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F45</f>
         <v>0.173469000011111</v>
       </c>
-      <c r="G45" s="14" t="e">
+      <c r="G45" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G45</f>
-        <v>#DIV/0!</v>
+        <v>0.109482182047674</v>
       </c>
       <c r="H45" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H45</f>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="O45" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O45</f>
-        <v>0.157968838339746</v>
+        <v>0.156069155889095</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:15">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="G46" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G46</f>
-        <v>0</v>
+        <v>36628.56</v>
       </c>
       <c r="H46" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H46</f>
@@ -28499,7 +28499,7 @@
       </c>
       <c r="O46" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O46</f>
-        <v>365885.72</v>
+        <v>402514.28</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:15">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="G47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G47</f>
-        <v>0</v>
+        <v>1222</v>
       </c>
       <c r="H47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H47</f>
@@ -28561,7 +28561,7 @@
       </c>
       <c r="O47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O47</f>
-        <v>20285</v>
+        <v>21507</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:15">
@@ -28591,7 +28591,7 @@
       </c>
       <c r="G48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G48</f>
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="H48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H48</f>
@@ -28623,7 +28623,7 @@
       </c>
       <c r="O48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O48</f>
-        <v>6750</v>
+        <v>7269</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:15">
@@ -28649,11 +28649,11 @@
       </c>
       <c r="F49" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F49</f>
-        <v>24515919.3072</v>
+        <v>2869544.286</v>
       </c>
       <c r="G49" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G49</f>
-        <v>0</v>
+        <v>654324.9576</v>
       </c>
       <c r="H49" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H49</f>
@@ -28685,7 +28685,7 @@
       </c>
       <c r="O49" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O49</f>
-        <v>29123079.3618</v>
+        <v>8131029.2982</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:15">
@@ -28715,7 +28715,7 @@
       </c>
       <c r="G50" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G50</f>
-        <v>0</v>
+        <v>186429.08</v>
       </c>
       <c r="H50" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H50</f>
@@ -28747,7 +28747,7 @@
       </c>
       <c r="O50" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O50</f>
-        <v>2312644.35</v>
+        <v>2499073.43</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:15">
@@ -28773,11 +28773,11 @@
       </c>
       <c r="F51" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F51</f>
-        <v>0.0352271839851571</v>
-      </c>
-      <c r="G51" s="14" t="e">
+        <v>0.300963049852021</v>
+      </c>
+      <c r="G51" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G51</f>
-        <v>#DIV/0!</v>
+        <v>0.28491818603986</v>
       </c>
       <c r="H51" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H51</f>
@@ -28809,7 +28809,7 @@
       </c>
       <c r="O51" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O51</f>
-        <v>0.0794093344755787</v>
+        <v>0.307350193726793</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:15">
@@ -28837,9 +28837,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F52</f>
         <v>0.656646245903975</v>
       </c>
-      <c r="G52" s="14" t="e">
+      <c r="G52" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G52</f>
-        <v>#DIV/0!</v>
+        <v>0.575286415711948</v>
       </c>
       <c r="H52" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H52</f>
@@ -28871,7 +28871,7 @@
       </c>
       <c r="O52" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O52</f>
-        <v>0.667241804288883</v>
+        <v>0.662017017715163</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:15">
@@ -28899,9 +28899,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F53</f>
         <v>0.196707142483304</v>
       </c>
-      <c r="G53" s="14" t="e">
+      <c r="G53" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G53</f>
-        <v>#DIV/0!</v>
+        <v>0.196474498506349</v>
       </c>
       <c r="H53" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H53</f>
@@ -28933,7 +28933,7 @@
       </c>
       <c r="O53" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O53</f>
-        <v>0.158210976106205</v>
+        <v>0.161065407349795</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:15">
@@ -28963,7 +28963,7 @@
       </c>
       <c r="G54" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G54</f>
-        <v>0</v>
+        <v>1116.38</v>
       </c>
       <c r="H54" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H54</f>
@@ -28995,7 +28995,7 @@
       </c>
       <c r="O54" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O54</f>
-        <v>116872.87</v>
+        <v>117989.25</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:15">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="G55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G55</f>
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="H55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H55</f>
@@ -29057,7 +29057,7 @@
       </c>
       <c r="O55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O55</f>
-        <v>15209</v>
+        <v>15520</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:15">
@@ -29087,7 +29087,7 @@
       </c>
       <c r="G56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G56</f>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H56</f>
@@ -29119,7 +29119,7 @@
       </c>
       <c r="O56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O56</f>
-        <v>5488</v>
+        <v>5618</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:15">
@@ -29145,11 +29145,11 @@
       </c>
       <c r="F57" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F57</f>
-        <v>9018566.8048</v>
+        <v>1028856.0636</v>
       </c>
       <c r="G57" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G57</f>
-        <v>0</v>
+        <v>121810.2264</v>
       </c>
       <c r="H57" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H57</f>
@@ -29181,7 +29181,7 @@
       </c>
       <c r="O57" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O57</f>
-        <v>13269454.2085</v>
+        <v>5401553.6937</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:15">
@@ -29211,7 +29211,7 @@
       </c>
       <c r="G58" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G58</f>
-        <v>0</v>
+        <v>41961.65</v>
       </c>
       <c r="H58" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H58</f>
@@ -29243,7 +29243,7 @@
       </c>
       <c r="O58" s="19">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O58</f>
-        <v>2125433.15</v>
+        <v>2167394.8</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:15">
@@ -29269,11 +29269,11 @@
       </c>
       <c r="F59" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F59</f>
-        <v>0.0342791639393811</v>
-      </c>
-      <c r="G59" s="14" t="e">
+        <v>0.300478308810543</v>
+      </c>
+      <c r="G59" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G59</f>
-        <v>#DIV/0!</v>
+        <v>0.344483802716255</v>
       </c>
       <c r="H59" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H59</f>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="O59" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O59</f>
-        <v>0.160174873555727</v>
+        <v>0.40125395819501</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:15">
@@ -29333,9 +29333,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F60</f>
         <v>0.660606060606061</v>
       </c>
-      <c r="G60" s="14" t="e">
+      <c r="G60" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G60</f>
-        <v>#DIV/0!</v>
+        <v>0.581993569131833</v>
       </c>
       <c r="H60" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H60</f>
@@ -29367,7 +29367,7 @@
       </c>
       <c r="O60" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O60</f>
-        <v>0.63916102307844</v>
+        <v>0.638015463917526</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:15">
@@ -29395,9 +29395,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F61</f>
         <v>0.074699369006388</v>
       </c>
-      <c r="G61" s="14" t="e">
+      <c r="G61" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G61</f>
-        <v>#DIV/0!</v>
+        <v>0.0266047688782495</v>
       </c>
       <c r="H61" s="14" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H61</f>
@@ -29429,7 +29429,7 @@
       </c>
       <c r="O61" s="14">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O61</f>
-        <v>0.0549877891948754</v>
+        <v>0.0544382823101726</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="1:15">
@@ -36229,7 +36229,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1d961a23-ceb1-4794-9a36-e1f4cbe2b7d6}</x14:id>
+          <x14:id>{70f983cf-4ab4-4ec6-b13b-f25fbdab1c7b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36243,7 +36243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c7a63e4-8c8c-42cc-aea7-d4ff546ba3ff}</x14:id>
+          <x14:id>{5e0b9453-0441-4fcc-b728-52c6b64bb3c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36257,7 +36257,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d46df2b4-573f-4a44-aebd-4271bc588efb}</x14:id>
+          <x14:id>{b03fccc2-a2bc-4e96-b29e-e1570232fc6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36271,7 +36271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{479ce472-8a2b-49a3-b526-27c18ebc227e}</x14:id>
+          <x14:id>{f03e4c4b-b708-4db3-8601-2a6cf4b42f31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36285,7 +36285,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{08907a97-b132-4a7e-8176-08813d1ee9be}</x14:id>
+          <x14:id>{f345559f-b9bb-4038-bfc7-7eab45ec4ec9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36299,7 +36299,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9598073e-aa13-4d6d-8b39-dfebb33030b8}</x14:id>
+          <x14:id>{1a3130d3-2985-4125-9945-0f980d6b04ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36319,7 +36319,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bdd50d23-c722-48e8-a672-60c4b24d45b6}</x14:id>
+          <x14:id>{e22f4090-7079-4390-b279-d380d4e18108}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36333,7 +36333,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17843945-cc5e-49af-a203-0044730a968b}</x14:id>
+          <x14:id>{dd09a4e5-3f13-466b-9ea5-d64d667da2d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36347,7 +36347,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6eecb643-a87a-41a3-b1d2-9e762da0c85d}</x14:id>
+          <x14:id>{ab717dff-df37-4deb-b2e5-cfa2bed4a78f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36361,7 +36361,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e31c794a-a991-48c3-bc9f-24dadcae4657}</x14:id>
+          <x14:id>{79db9a86-91dc-4399-ab7f-6a9ada55c931}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36375,7 +36375,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84fddcd8-516f-44d3-a6ca-aa83179e24d3}</x14:id>
+          <x14:id>{ae406aa4-3042-403c-93ac-d86c8267ea2c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36389,7 +36389,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c9e7a9d3-151a-4ef2-9606-288a95cab902}</x14:id>
+          <x14:id>{7d928f9a-2db1-4a96-9c68-beca5005710e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36411,7 +36411,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{751fae57-7905-410a-9220-7ea9c0bc7baa}</x14:id>
+          <x14:id>{09f5528b-a418-4e8c-881a-01f910ba160e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36441,7 +36441,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa36e72d-0e9d-4756-b121-78293dfc7ab7}</x14:id>
+          <x14:id>{17aeecdd-24f3-462e-8d49-9977814fb04d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36471,7 +36471,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d09f2e4-45af-444f-b93a-d12ca1b8063f}</x14:id>
+          <x14:id>{66517f99-9164-40a1-a1fb-d5e84c30f1fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36501,7 +36501,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{370faf8e-2948-46a2-8551-583e367fa899}</x14:id>
+          <x14:id>{11df2b99-fa5c-4f86-882e-1970ea74b193}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36531,7 +36531,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56f75acd-1a59-4d98-8d52-e39852766fff}</x14:id>
+          <x14:id>{4238c860-4c68-41ee-b8c7-2bf7db020061}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36561,7 +36561,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa762f7c-6624-4425-b0f4-7f723089a075}</x14:id>
+          <x14:id>{1dabb9ea-2fd4-4ffa-b57f-e32de18f5f96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36583,7 +36583,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3cb69851-192a-433a-92e9-dc589cc8c92c}</x14:id>
+          <x14:id>{ce37e0ff-9ea5-46c9-952d-140cb2deb6ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36605,7 +36605,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1a7aedf3-3e15-4237-9629-d9961506cb43}</x14:id>
+          <x14:id>{ad4cf937-a38a-43f0-9d24-d558bf1f05e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36627,7 +36627,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7524d1a0-388d-432a-9648-3797680e78ed}</x14:id>
+          <x14:id>{054e4fd8-1ff0-4661-9f7c-ed6fbf943ac9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36649,7 +36649,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{084646c8-c8b6-47f3-83da-2e70831a47ad}</x14:id>
+          <x14:id>{716d5071-35c9-41df-8f79-8173441db015}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36671,7 +36671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a73bb7de-3d82-47d3-86f1-f18e00f0885a}</x14:id>
+          <x14:id>{ee4b566e-98f4-4521-bb64-82f05a85f7a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36693,7 +36693,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{748ec694-cce2-4f8a-9b8e-8360077de4e0}</x14:id>
+          <x14:id>{edc20665-872b-4dfe-8299-53666f8ab50a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36715,7 +36715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e9ff217-ba86-44ef-a050-f3326183c7e1}</x14:id>
+          <x14:id>{6e640c64-1ad9-4d61-8397-6e8ad15b71aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36737,7 +36737,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b6eb220-8529-47ad-a603-1f43338386af}</x14:id>
+          <x14:id>{bbcf0224-9faa-4c79-b5b5-92d0e68263c1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36759,7 +36759,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba3da7c1-e451-41dc-92a3-102e7d4cd934}</x14:id>
+          <x14:id>{d12b246a-7dee-4670-8fb3-7ef53508cfa7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36781,7 +36781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be841577-34b1-4ff1-bfdc-8f52a76f6e02}</x14:id>
+          <x14:id>{e32fc64a-e4b1-4ac6-a022-b35762943b14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36803,7 +36803,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ea7d9fb-3a7a-446b-a913-feb67e526dba}</x14:id>
+          <x14:id>{c313516c-5ac7-42d4-a9c7-46b62fef2eb7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36825,7 +36825,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{056def2c-4423-4803-a965-f9ffbc363609}</x14:id>
+          <x14:id>{6c059cbb-33f1-4d6f-9732-0035cac1994b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36847,7 +36847,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1f47ce1-270f-4980-8b31-dcb30677c198}</x14:id>
+          <x14:id>{eab451e8-b87a-4c02-97e8-b758bf11ff05}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36869,7 +36869,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e78221f7-3b3f-42da-a290-63590b6669a5}</x14:id>
+          <x14:id>{c4300205-acca-4bc3-8294-a356c0e5119b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36888,7 +36888,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1d961a23-ceb1-4794-9a36-e1f4cbe2b7d6}">
+          <x14:cfRule type="dataBar" id="{70f983cf-4ab4-4ec6-b13b-f25fbdab1c7b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36901,7 +36901,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3c7a63e4-8c8c-42cc-aea7-d4ff546ba3ff}">
+          <x14:cfRule type="dataBar" id="{5e0b9453-0441-4fcc-b728-52c6b64bb3c5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36914,7 +36914,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d46df2b4-573f-4a44-aebd-4271bc588efb}">
+          <x14:cfRule type="dataBar" id="{b03fccc2-a2bc-4e96-b29e-e1570232fc6d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36927,7 +36927,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{479ce472-8a2b-49a3-b526-27c18ebc227e}">
+          <x14:cfRule type="dataBar" id="{f03e4c4b-b708-4db3-8601-2a6cf4b42f31}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36940,7 +36940,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{08907a97-b132-4a7e-8176-08813d1ee9be}">
+          <x14:cfRule type="dataBar" id="{f345559f-b9bb-4038-bfc7-7eab45ec4ec9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36953,7 +36953,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9598073e-aa13-4d6d-8b39-dfebb33030b8}">
+          <x14:cfRule type="dataBar" id="{1a3130d3-2985-4125-9945-0f980d6b04ac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36966,7 +36966,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bdd50d23-c722-48e8-a672-60c4b24d45b6}">
+          <x14:cfRule type="dataBar" id="{e22f4090-7079-4390-b279-d380d4e18108}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36979,7 +36979,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17843945-cc5e-49af-a203-0044730a968b}">
+          <x14:cfRule type="dataBar" id="{dd09a4e5-3f13-466b-9ea5-d64d667da2d5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36992,7 +36992,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6eecb643-a87a-41a3-b1d2-9e762da0c85d}">
+          <x14:cfRule type="dataBar" id="{ab717dff-df37-4deb-b2e5-cfa2bed4a78f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37005,7 +37005,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e31c794a-a991-48c3-bc9f-24dadcae4657}">
+          <x14:cfRule type="dataBar" id="{79db9a86-91dc-4399-ab7f-6a9ada55c931}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37018,7 +37018,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{84fddcd8-516f-44d3-a6ca-aa83179e24d3}">
+          <x14:cfRule type="dataBar" id="{ae406aa4-3042-403c-93ac-d86c8267ea2c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37031,7 +37031,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c9e7a9d3-151a-4ef2-9606-288a95cab902}">
+          <x14:cfRule type="dataBar" id="{7d928f9a-2db1-4a96-9c68-beca5005710e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37044,7 +37044,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{751fae57-7905-410a-9220-7ea9c0bc7baa}">
+          <x14:cfRule type="dataBar" id="{09f5528b-a418-4e8c-881a-01f910ba160e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37057,7 +37057,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aa36e72d-0e9d-4756-b121-78293dfc7ab7}">
+          <x14:cfRule type="dataBar" id="{17aeecdd-24f3-462e-8d49-9977814fb04d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37070,7 +37070,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2d09f2e4-45af-444f-b93a-d12ca1b8063f}">
+          <x14:cfRule type="dataBar" id="{66517f99-9164-40a1-a1fb-d5e84c30f1fb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37083,7 +37083,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{370faf8e-2948-46a2-8551-583e367fa899}">
+          <x14:cfRule type="dataBar" id="{11df2b99-fa5c-4f86-882e-1970ea74b193}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37096,7 +37096,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{56f75acd-1a59-4d98-8d52-e39852766fff}">
+          <x14:cfRule type="dataBar" id="{4238c860-4c68-41ee-b8c7-2bf7db020061}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37109,7 +37109,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aa762f7c-6624-4425-b0f4-7f723089a075}">
+          <x14:cfRule type="dataBar" id="{1dabb9ea-2fd4-4ffa-b57f-e32de18f5f96}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37122,7 +37122,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3cb69851-192a-433a-92e9-dc589cc8c92c}">
+          <x14:cfRule type="dataBar" id="{ce37e0ff-9ea5-46c9-952d-140cb2deb6ae}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37135,7 +37135,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1a7aedf3-3e15-4237-9629-d9961506cb43}">
+          <x14:cfRule type="dataBar" id="{ad4cf937-a38a-43f0-9d24-d558bf1f05e0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37148,7 +37148,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7524d1a0-388d-432a-9648-3797680e78ed}">
+          <x14:cfRule type="dataBar" id="{054e4fd8-1ff0-4661-9f7c-ed6fbf943ac9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37161,7 +37161,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{084646c8-c8b6-47f3-83da-2e70831a47ad}">
+          <x14:cfRule type="dataBar" id="{716d5071-35c9-41df-8f79-8173441db015}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37174,7 +37174,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a73bb7de-3d82-47d3-86f1-f18e00f0885a}">
+          <x14:cfRule type="dataBar" id="{ee4b566e-98f4-4521-bb64-82f05a85f7a0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37187,7 +37187,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{748ec694-cce2-4f8a-9b8e-8360077de4e0}">
+          <x14:cfRule type="dataBar" id="{edc20665-872b-4dfe-8299-53666f8ab50a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37200,7 +37200,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4e9ff217-ba86-44ef-a050-f3326183c7e1}">
+          <x14:cfRule type="dataBar" id="{6e640c64-1ad9-4d61-8397-6e8ad15b71aa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37213,7 +37213,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b6eb220-8529-47ad-a603-1f43338386af}">
+          <x14:cfRule type="dataBar" id="{bbcf0224-9faa-4c79-b5b5-92d0e68263c1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37226,7 +37226,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba3da7c1-e451-41dc-92a3-102e7d4cd934}">
+          <x14:cfRule type="dataBar" id="{d12b246a-7dee-4670-8fb3-7ef53508cfa7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37239,7 +37239,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{be841577-34b1-4ff1-bfdc-8f52a76f6e02}">
+          <x14:cfRule type="dataBar" id="{e32fc64a-e4b1-4ac6-a022-b35762943b14}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37252,7 +37252,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2ea7d9fb-3a7a-446b-a913-feb67e526dba}">
+          <x14:cfRule type="dataBar" id="{c313516c-5ac7-42d4-a9c7-46b62fef2eb7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37265,7 +37265,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{056def2c-4423-4803-a965-f9ffbc363609}">
+          <x14:cfRule type="dataBar" id="{6c059cbb-33f1-4d6f-9732-0035cac1994b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37278,7 +37278,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a1f47ce1-270f-4980-8b31-dcb30677c198}">
+          <x14:cfRule type="dataBar" id="{eab451e8-b87a-4c02-97e8-b758bf11ff05}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37291,7 +37291,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e78221f7-3b3f-42da-a290-63590b6669a5}">
+          <x14:cfRule type="dataBar" id="{c4300205-acca-4bc3-8294-a356c0e5119b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -24518,7 +24518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5c5f5fa-5257-4f42-9d58-f665da43dfc2}</x14:id>
+          <x14:id>{cc952ab2-f13f-46e3-ba59-f6636b080730}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24532,7 +24532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dcd8244d-9c73-4ec4-a81a-9bea880b86ee}</x14:id>
+          <x14:id>{ac8a0e0e-c9d8-4a2a-ba72-868d43cc2624}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24546,7 +24546,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c815b58d-47b6-4670-ac89-c0a9b3518073}</x14:id>
+          <x14:id>{973ce373-6416-4593-9f67-f983f8e8a295}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24560,7 +24560,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af60c89b-8868-4dae-b56b-0a4f1026b02e}</x14:id>
+          <x14:id>{4cd145a5-282b-4d5d-bccf-4faa8346d629}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24574,7 +24574,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac8634e1-dc23-4a7f-8a35-444cb431671e}</x14:id>
+          <x14:id>{9ce32a68-1ac6-4700-9bdc-8a7b55314a43}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24588,7 +24588,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6f28e9d-2c80-4d4f-9178-dbd2e08050c6}</x14:id>
+          <x14:id>{8da7395c-807b-4839-8702-3e6a0b7be7ef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24602,7 +24602,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45e4cb60-da89-4e0e-9738-6263c7dba569}</x14:id>
+          <x14:id>{0b782d53-3663-4857-b8fc-afe837f0e892}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24616,7 +24616,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba934f2b-5b8b-4054-b523-b4e35a4d0964}</x14:id>
+          <x14:id>{910ad63e-b33d-46c0-9c9c-efb3c3765e3b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24630,7 +24630,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{755ce089-ae7c-4b88-84c6-9005ab02e6fc}</x14:id>
+          <x14:id>{2fa2f3bc-466c-4109-a353-e4a97ea39d0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24644,7 +24644,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1d9a4045-4cd2-475e-9ea1-89ae4a479a06}</x14:id>
+          <x14:id>{45c53d20-353e-459b-aadf-ba5ccdd89a1e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24658,7 +24658,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d114b53-4c56-4ab7-97bb-3f42b546e1b5}</x14:id>
+          <x14:id>{62cd513b-1a60-4c0e-a955-94f35d86e90f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24672,7 +24672,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d634cf07-3e34-4154-bff7-f030a89bdd67}</x14:id>
+          <x14:id>{043ee45d-7706-46ee-bf8d-d8ce799a713a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24686,7 +24686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17681e2e-4ebe-4ead-b057-873d8186c741}</x14:id>
+          <x14:id>{2a31febd-8e72-4270-9fb4-c4e1bec2a1c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24708,7 +24708,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f571827-6e4d-49fa-968f-5b5407c7f774}</x14:id>
+          <x14:id>{b925f540-ec44-4c29-9e75-a648f7da3867}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24738,7 +24738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f219ea5c-7eae-4c9e-9e46-13429c14516d}</x14:id>
+          <x14:id>{fe36181f-253e-4074-b1de-ab8f886785b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24768,7 +24768,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e948bf5-6e4e-4164-9260-c68de0b15637}</x14:id>
+          <x14:id>{9cac237e-62b8-4be9-bb08-345879202a9c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24798,7 +24798,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1dbb3393-8f2d-41ad-9cdb-f52c186711fb}</x14:id>
+          <x14:id>{557078f0-4e27-4607-b19f-41887a1faac1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24828,7 +24828,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1088b95a-b82c-4691-b3e4-3d7131d182aa}</x14:id>
+          <x14:id>{3685915c-0118-49a8-bb04-11af7ff94411}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24858,7 +24858,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f859ec85-79c8-41f5-a202-d147e656aed0}</x14:id>
+          <x14:id>{700d420c-4604-4617-9f67-f91186ae46af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24888,7 +24888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d83b2322-d8d5-49b3-a8a5-a0af0a359f94}</x14:id>
+          <x14:id>{2af20659-47a4-40e0-994f-f3def945ef9e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24918,7 +24918,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{46fd2ed6-f61d-4465-b184-9a9998e40872}</x14:id>
+          <x14:id>{144897cb-3f29-4c18-9f76-5cc93df6630b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24940,7 +24940,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a148812f-2ad7-4d32-83f4-8da74d81bda0}</x14:id>
+          <x14:id>{a38097ee-716a-4ace-812a-ac29957b4c96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24962,7 +24962,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9284a6f8-0fd8-49c2-bc22-4b1a1a075837}</x14:id>
+          <x14:id>{88a19822-61b6-4ac7-a000-86fce3c1487c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24984,7 +24984,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad7eb133-f7a4-4159-87dd-4d472d4cc591}</x14:id>
+          <x14:id>{7a55aee0-d6a9-4184-8ed4-88227a77ec9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25006,7 +25006,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe0d6447-a6d8-4020-8ef7-645577080a35}</x14:id>
+          <x14:id>{5ae418da-a9e3-4c9b-980e-a93600d9b231}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25028,7 +25028,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bb62124b-8ec5-4ec6-8e6f-9ef864246818}</x14:id>
+          <x14:id>{6a85ed11-dfcb-4c12-81ab-5ca2d984c126}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25050,7 +25050,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c68e9d7b-b605-4642-8777-6faaa0803da9}</x14:id>
+          <x14:id>{61eeddfd-f218-4858-aa2c-65383eb56f06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25072,7 +25072,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e43f611-6be1-41cb-b675-41b11ece3b8c}</x14:id>
+          <x14:id>{09f4e841-2fca-47fc-935a-1348dc654d19}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25094,7 +25094,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bc837f4e-39a9-40d1-88ff-062324ff9941}</x14:id>
+          <x14:id>{6d1c304f-962e-403e-a6aa-e50a5de3d5aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25116,7 +25116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6962a74-d583-4e1e-a029-e3ee4fa19850}</x14:id>
+          <x14:id>{e5f8ca43-0c2b-46df-b2c6-fdf0b606e37e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25138,7 +25138,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0cd63c1a-e672-4c0c-ae44-c90f847699b2}</x14:id>
+          <x14:id>{4fccdfc5-b5fa-4ae2-bb76-6c26e8bb78cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25160,7 +25160,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{382ea263-e402-4125-b5b5-a9bc018b1a39}</x14:id>
+          <x14:id>{6d5e8edc-d135-4044-9871-05d4f646ef8a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25182,7 +25182,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e0f0d5d-af6b-42a3-848a-82e9d3195829}</x14:id>
+          <x14:id>{747175fa-4f05-4679-a9f0-f1e061f54ef0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25201,7 +25201,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b5c5f5fa-5257-4f42-9d58-f665da43dfc2}">
+          <x14:cfRule type="dataBar" id="{cc952ab2-f13f-46e3-ba59-f6636b080730}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25214,7 +25214,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dcd8244d-9c73-4ec4-a81a-9bea880b86ee}">
+          <x14:cfRule type="dataBar" id="{ac8a0e0e-c9d8-4a2a-ba72-868d43cc2624}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25227,7 +25227,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c815b58d-47b6-4670-ac89-c0a9b3518073}">
+          <x14:cfRule type="dataBar" id="{973ce373-6416-4593-9f67-f983f8e8a295}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25240,7 +25240,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af60c89b-8868-4dae-b56b-0a4f1026b02e}">
+          <x14:cfRule type="dataBar" id="{4cd145a5-282b-4d5d-bccf-4faa8346d629}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25253,7 +25253,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ac8634e1-dc23-4a7f-8a35-444cb431671e}">
+          <x14:cfRule type="dataBar" id="{9ce32a68-1ac6-4700-9bdc-8a7b55314a43}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25266,7 +25266,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c6f28e9d-2c80-4d4f-9178-dbd2e08050c6}">
+          <x14:cfRule type="dataBar" id="{8da7395c-807b-4839-8702-3e6a0b7be7ef}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25279,7 +25279,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{45e4cb60-da89-4e0e-9738-6263c7dba569}">
+          <x14:cfRule type="dataBar" id="{0b782d53-3663-4857-b8fc-afe837f0e892}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25292,7 +25292,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba934f2b-5b8b-4054-b523-b4e35a4d0964}">
+          <x14:cfRule type="dataBar" id="{910ad63e-b33d-46c0-9c9c-efb3c3765e3b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25305,7 +25305,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{755ce089-ae7c-4b88-84c6-9005ab02e6fc}">
+          <x14:cfRule type="dataBar" id="{2fa2f3bc-466c-4109-a353-e4a97ea39d0d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25318,7 +25318,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1d9a4045-4cd2-475e-9ea1-89ae4a479a06}">
+          <x14:cfRule type="dataBar" id="{45c53d20-353e-459b-aadf-ba5ccdd89a1e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25331,7 +25331,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3d114b53-4c56-4ab7-97bb-3f42b546e1b5}">
+          <x14:cfRule type="dataBar" id="{62cd513b-1a60-4c0e-a955-94f35d86e90f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25344,7 +25344,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d634cf07-3e34-4154-bff7-f030a89bdd67}">
+          <x14:cfRule type="dataBar" id="{043ee45d-7706-46ee-bf8d-d8ce799a713a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25357,7 +25357,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17681e2e-4ebe-4ead-b057-873d8186c741}">
+          <x14:cfRule type="dataBar" id="{2a31febd-8e72-4270-9fb4-c4e1bec2a1c5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25370,7 +25370,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6f571827-6e4d-49fa-968f-5b5407c7f774}">
+          <x14:cfRule type="dataBar" id="{b925f540-ec44-4c29-9e75-a648f7da3867}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25383,7 +25383,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f219ea5c-7eae-4c9e-9e46-13429c14516d}">
+          <x14:cfRule type="dataBar" id="{fe36181f-253e-4074-b1de-ab8f886785b9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25396,7 +25396,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2e948bf5-6e4e-4164-9260-c68de0b15637}">
+          <x14:cfRule type="dataBar" id="{9cac237e-62b8-4be9-bb08-345879202a9c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25409,7 +25409,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1dbb3393-8f2d-41ad-9cdb-f52c186711fb}">
+          <x14:cfRule type="dataBar" id="{557078f0-4e27-4607-b19f-41887a1faac1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25422,7 +25422,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1088b95a-b82c-4691-b3e4-3d7131d182aa}">
+          <x14:cfRule type="dataBar" id="{3685915c-0118-49a8-bb04-11af7ff94411}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25435,7 +25435,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f859ec85-79c8-41f5-a202-d147e656aed0}">
+          <x14:cfRule type="dataBar" id="{700d420c-4604-4617-9f67-f91186ae46af}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25448,7 +25448,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d83b2322-d8d5-49b3-a8a5-a0af0a359f94}">
+          <x14:cfRule type="dataBar" id="{2af20659-47a4-40e0-994f-f3def945ef9e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25461,7 +25461,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{46fd2ed6-f61d-4465-b184-9a9998e40872}">
+          <x14:cfRule type="dataBar" id="{144897cb-3f29-4c18-9f76-5cc93df6630b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25474,7 +25474,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a148812f-2ad7-4d32-83f4-8da74d81bda0}">
+          <x14:cfRule type="dataBar" id="{a38097ee-716a-4ace-812a-ac29957b4c96}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25487,7 +25487,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9284a6f8-0fd8-49c2-bc22-4b1a1a075837}">
+          <x14:cfRule type="dataBar" id="{88a19822-61b6-4ac7-a000-86fce3c1487c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25500,7 +25500,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ad7eb133-f7a4-4159-87dd-4d472d4cc591}">
+          <x14:cfRule type="dataBar" id="{7a55aee0-d6a9-4184-8ed4-88227a77ec9d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25513,7 +25513,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fe0d6447-a6d8-4020-8ef7-645577080a35}">
+          <x14:cfRule type="dataBar" id="{5ae418da-a9e3-4c9b-980e-a93600d9b231}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25526,7 +25526,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bb62124b-8ec5-4ec6-8e6f-9ef864246818}">
+          <x14:cfRule type="dataBar" id="{6a85ed11-dfcb-4c12-81ab-5ca2d984c126}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25539,7 +25539,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c68e9d7b-b605-4642-8777-6faaa0803da9}">
+          <x14:cfRule type="dataBar" id="{61eeddfd-f218-4858-aa2c-65383eb56f06}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25552,7 +25552,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e43f611-6be1-41cb-b675-41b11ece3b8c}">
+          <x14:cfRule type="dataBar" id="{09f4e841-2fca-47fc-935a-1348dc654d19}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25565,7 +25565,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bc837f4e-39a9-40d1-88ff-062324ff9941}">
+          <x14:cfRule type="dataBar" id="{6d1c304f-962e-403e-a6aa-e50a5de3d5aa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25578,7 +25578,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6962a74-d583-4e1e-a029-e3ee4fa19850}">
+          <x14:cfRule type="dataBar" id="{e5f8ca43-0c2b-46df-b2c6-fdf0b606e37e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25591,7 +25591,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0cd63c1a-e672-4c0c-ae44-c90f847699b2}">
+          <x14:cfRule type="dataBar" id="{4fccdfc5-b5fa-4ae2-bb76-6c26e8bb78cf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25604,7 +25604,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{382ea263-e402-4125-b5b5-a9bc018b1a39}">
+          <x14:cfRule type="dataBar" id="{6d5e8edc-d135-4044-9871-05d4f646ef8a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25617,7 +25617,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e0f0d5d-af6b-42a3-848a-82e9d3195829}">
+          <x14:cfRule type="dataBar" id="{747175fa-4f05-4679-a9f0-f1e061f54ef0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36229,7 +36229,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70f983cf-4ab4-4ec6-b13b-f25fbdab1c7b}</x14:id>
+          <x14:id>{615d1184-3684-4cf0-acd0-31455b7e9879}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36243,7 +36243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e0b9453-0441-4fcc-b728-52c6b64bb3c5}</x14:id>
+          <x14:id>{635de2a9-d42e-40df-94ab-ed75f0603034}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36257,7 +36257,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b03fccc2-a2bc-4e96-b29e-e1570232fc6d}</x14:id>
+          <x14:id>{44951f9b-58b1-45fa-84d8-f9410685cc92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36271,7 +36271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f03e4c4b-b708-4db3-8601-2a6cf4b42f31}</x14:id>
+          <x14:id>{560b0269-9821-4ce1-93cf-d762bd074e4a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36285,7 +36285,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f345559f-b9bb-4038-bfc7-7eab45ec4ec9}</x14:id>
+          <x14:id>{0aee6b4d-dea3-4418-8a02-2d1a9b28d41e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36299,7 +36299,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1a3130d3-2985-4125-9945-0f980d6b04ac}</x14:id>
+          <x14:id>{ab7f564e-0868-47aa-8510-cbc299ac6f53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36319,7 +36319,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e22f4090-7079-4390-b279-d380d4e18108}</x14:id>
+          <x14:id>{2c581d43-5682-4b2e-9208-7990713c21c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36333,7 +36333,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd09a4e5-3f13-466b-9ea5-d64d667da2d5}</x14:id>
+          <x14:id>{2d744d2b-fb6d-455f-95d2-8d54bd58df04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36347,7 +36347,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab717dff-df37-4deb-b2e5-cfa2bed4a78f}</x14:id>
+          <x14:id>{74a430b5-df40-4ff9-9c72-6f58f8d4fe88}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36361,7 +36361,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79db9a86-91dc-4399-ab7f-6a9ada55c931}</x14:id>
+          <x14:id>{65b9f54e-2854-404a-9685-35a09493feaa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36375,7 +36375,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae406aa4-3042-403c-93ac-d86c8267ea2c}</x14:id>
+          <x14:id>{41465f2f-6c13-44ed-8bd8-d86a9262d67b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36389,7 +36389,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7d928f9a-2db1-4a96-9c68-beca5005710e}</x14:id>
+          <x14:id>{22a7f9b5-35d6-4072-ac1a-3cf83b9c4124}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36411,7 +36411,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{09f5528b-a418-4e8c-881a-01f910ba160e}</x14:id>
+          <x14:id>{d4ba52a4-cffb-4364-b9e5-85291c8a25c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36441,7 +36441,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17aeecdd-24f3-462e-8d49-9977814fb04d}</x14:id>
+          <x14:id>{8720afd3-ea2d-456c-8c96-ecf4b47867a9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36471,7 +36471,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66517f99-9164-40a1-a1fb-d5e84c30f1fb}</x14:id>
+          <x14:id>{40ffab0c-0751-4bd5-b06d-0df3facdb68b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36501,7 +36501,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11df2b99-fa5c-4f86-882e-1970ea74b193}</x14:id>
+          <x14:id>{248d5037-02eb-44eb-9619-d8fc835abd48}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36531,7 +36531,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4238c860-4c68-41ee-b8c7-2bf7db020061}</x14:id>
+          <x14:id>{1dfc70b7-dc25-4e8f-8803-b4fe3e7bb45d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36561,7 +36561,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1dabb9ea-2fd4-4ffa-b57f-e32de18f5f96}</x14:id>
+          <x14:id>{2c145692-d935-4220-8736-53e44f1cf54f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36583,7 +36583,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce37e0ff-9ea5-46c9-952d-140cb2deb6ae}</x14:id>
+          <x14:id>{52c22cff-717b-494a-91c9-bd38501d4b03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36605,7 +36605,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad4cf937-a38a-43f0-9d24-d558bf1f05e0}</x14:id>
+          <x14:id>{c325fe2a-c645-4098-af55-fb9b552dc138}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36627,7 +36627,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{054e4fd8-1ff0-4661-9f7c-ed6fbf943ac9}</x14:id>
+          <x14:id>{2588615e-cff0-4d62-aeca-9cbf3d209eb0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36649,7 +36649,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{716d5071-35c9-41df-8f79-8173441db015}</x14:id>
+          <x14:id>{191129c9-5481-4ed2-869e-f98a4a54b0d2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36671,7 +36671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee4b566e-98f4-4521-bb64-82f05a85f7a0}</x14:id>
+          <x14:id>{42776ec9-eb43-487d-83ee-a18d82884b47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36693,7 +36693,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{edc20665-872b-4dfe-8299-53666f8ab50a}</x14:id>
+          <x14:id>{6d6cf6fa-5e66-421e-b002-8a4b76b15a95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36715,7 +36715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e640c64-1ad9-4d61-8397-6e8ad15b71aa}</x14:id>
+          <x14:id>{525b005e-810a-4c51-a93b-f4d3df84626e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36737,7 +36737,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bbcf0224-9faa-4c79-b5b5-92d0e68263c1}</x14:id>
+          <x14:id>{275e8af0-7952-4471-ab3a-742bc2953711}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36759,7 +36759,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d12b246a-7dee-4670-8fb3-7ef53508cfa7}</x14:id>
+          <x14:id>{4abdd106-e6ea-4ed3-937b-e355e009fb8d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36781,7 +36781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e32fc64a-e4b1-4ac6-a022-b35762943b14}</x14:id>
+          <x14:id>{6d1aefb6-d082-49a0-b9ef-46da7234e28a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36803,7 +36803,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c313516c-5ac7-42d4-a9c7-46b62fef2eb7}</x14:id>
+          <x14:id>{e449da04-bf7d-4018-a890-80b78832894c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36825,7 +36825,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6c059cbb-33f1-4d6f-9732-0035cac1994b}</x14:id>
+          <x14:id>{199849a3-1958-4f84-a234-5e89664f25e2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36847,7 +36847,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eab451e8-b87a-4c02-97e8-b758bf11ff05}</x14:id>
+          <x14:id>{ac4d439b-bda9-4056-96e9-6f686ed6d375}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36869,7 +36869,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4300205-acca-4bc3-8294-a356c0e5119b}</x14:id>
+          <x14:id>{cef35d91-d3cb-4983-980b-93d82fb1d902}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36888,7 +36888,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70f983cf-4ab4-4ec6-b13b-f25fbdab1c7b}">
+          <x14:cfRule type="dataBar" id="{615d1184-3684-4cf0-acd0-31455b7e9879}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36901,7 +36901,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5e0b9453-0441-4fcc-b728-52c6b64bb3c5}">
+          <x14:cfRule type="dataBar" id="{635de2a9-d42e-40df-94ab-ed75f0603034}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36914,7 +36914,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b03fccc2-a2bc-4e96-b29e-e1570232fc6d}">
+          <x14:cfRule type="dataBar" id="{44951f9b-58b1-45fa-84d8-f9410685cc92}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36927,7 +36927,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f03e4c4b-b708-4db3-8601-2a6cf4b42f31}">
+          <x14:cfRule type="dataBar" id="{560b0269-9821-4ce1-93cf-d762bd074e4a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36940,7 +36940,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f345559f-b9bb-4038-bfc7-7eab45ec4ec9}">
+          <x14:cfRule type="dataBar" id="{0aee6b4d-dea3-4418-8a02-2d1a9b28d41e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36953,7 +36953,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1a3130d3-2985-4125-9945-0f980d6b04ac}">
+          <x14:cfRule type="dataBar" id="{ab7f564e-0868-47aa-8510-cbc299ac6f53}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36966,7 +36966,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e22f4090-7079-4390-b279-d380d4e18108}">
+          <x14:cfRule type="dataBar" id="{2c581d43-5682-4b2e-9208-7990713c21c4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36979,7 +36979,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd09a4e5-3f13-466b-9ea5-d64d667da2d5}">
+          <x14:cfRule type="dataBar" id="{2d744d2b-fb6d-455f-95d2-8d54bd58df04}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36992,7 +36992,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ab717dff-df37-4deb-b2e5-cfa2bed4a78f}">
+          <x14:cfRule type="dataBar" id="{74a430b5-df40-4ff9-9c72-6f58f8d4fe88}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37005,7 +37005,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79db9a86-91dc-4399-ab7f-6a9ada55c931}">
+          <x14:cfRule type="dataBar" id="{65b9f54e-2854-404a-9685-35a09493feaa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37018,7 +37018,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ae406aa4-3042-403c-93ac-d86c8267ea2c}">
+          <x14:cfRule type="dataBar" id="{41465f2f-6c13-44ed-8bd8-d86a9262d67b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37031,7 +37031,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7d928f9a-2db1-4a96-9c68-beca5005710e}">
+          <x14:cfRule type="dataBar" id="{22a7f9b5-35d6-4072-ac1a-3cf83b9c4124}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37044,7 +37044,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{09f5528b-a418-4e8c-881a-01f910ba160e}">
+          <x14:cfRule type="dataBar" id="{d4ba52a4-cffb-4364-b9e5-85291c8a25c6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37057,7 +37057,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17aeecdd-24f3-462e-8d49-9977814fb04d}">
+          <x14:cfRule type="dataBar" id="{8720afd3-ea2d-456c-8c96-ecf4b47867a9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37070,7 +37070,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66517f99-9164-40a1-a1fb-d5e84c30f1fb}">
+          <x14:cfRule type="dataBar" id="{40ffab0c-0751-4bd5-b06d-0df3facdb68b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37083,7 +37083,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11df2b99-fa5c-4f86-882e-1970ea74b193}">
+          <x14:cfRule type="dataBar" id="{248d5037-02eb-44eb-9619-d8fc835abd48}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37096,7 +37096,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4238c860-4c68-41ee-b8c7-2bf7db020061}">
+          <x14:cfRule type="dataBar" id="{1dfc70b7-dc25-4e8f-8803-b4fe3e7bb45d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37109,7 +37109,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1dabb9ea-2fd4-4ffa-b57f-e32de18f5f96}">
+          <x14:cfRule type="dataBar" id="{2c145692-d935-4220-8736-53e44f1cf54f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37122,7 +37122,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce37e0ff-9ea5-46c9-952d-140cb2deb6ae}">
+          <x14:cfRule type="dataBar" id="{52c22cff-717b-494a-91c9-bd38501d4b03}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37135,7 +37135,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ad4cf937-a38a-43f0-9d24-d558bf1f05e0}">
+          <x14:cfRule type="dataBar" id="{c325fe2a-c645-4098-af55-fb9b552dc138}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37148,7 +37148,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{054e4fd8-1ff0-4661-9f7c-ed6fbf943ac9}">
+          <x14:cfRule type="dataBar" id="{2588615e-cff0-4d62-aeca-9cbf3d209eb0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37161,7 +37161,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{716d5071-35c9-41df-8f79-8173441db015}">
+          <x14:cfRule type="dataBar" id="{191129c9-5481-4ed2-869e-f98a4a54b0d2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37174,7 +37174,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee4b566e-98f4-4521-bb64-82f05a85f7a0}">
+          <x14:cfRule type="dataBar" id="{42776ec9-eb43-487d-83ee-a18d82884b47}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37187,7 +37187,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{edc20665-872b-4dfe-8299-53666f8ab50a}">
+          <x14:cfRule type="dataBar" id="{6d6cf6fa-5e66-421e-b002-8a4b76b15a95}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37200,7 +37200,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e640c64-1ad9-4d61-8397-6e8ad15b71aa}">
+          <x14:cfRule type="dataBar" id="{525b005e-810a-4c51-a93b-f4d3df84626e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37213,7 +37213,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bbcf0224-9faa-4c79-b5b5-92d0e68263c1}">
+          <x14:cfRule type="dataBar" id="{275e8af0-7952-4471-ab3a-742bc2953711}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37226,7 +37226,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d12b246a-7dee-4670-8fb3-7ef53508cfa7}">
+          <x14:cfRule type="dataBar" id="{4abdd106-e6ea-4ed3-937b-e355e009fb8d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37239,7 +37239,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e32fc64a-e4b1-4ac6-a022-b35762943b14}">
+          <x14:cfRule type="dataBar" id="{6d1aefb6-d082-49a0-b9ef-46da7234e28a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37252,7 +37252,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c313516c-5ac7-42d4-a9c7-46b62fef2eb7}">
+          <x14:cfRule type="dataBar" id="{e449da04-bf7d-4018-a890-80b78832894c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37265,7 +37265,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6c059cbb-33f1-4d6f-9732-0035cac1994b}">
+          <x14:cfRule type="dataBar" id="{199849a3-1958-4f84-a234-5e89664f25e2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37278,7 +37278,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eab451e8-b87a-4c02-97e8-b758bf11ff05}">
+          <x14:cfRule type="dataBar" id="{ac4d439b-bda9-4056-96e9-6f686ed6d375}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37291,7 +37291,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c4300205-acca-4bc3-8294-a356c0e5119b}">
+          <x14:cfRule type="dataBar" id="{cef35d91-d3cb-4983-980b-93d82fb1d902}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -2121,7 +2121,7 @@
         </row>
         <row r="4">
           <cell r="F4">
-            <v>518715.62</v>
+            <v>593659.75</v>
           </cell>
         </row>
         <row r="4">
@@ -2144,7 +2144,7 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>0.311886374805742</v>
+            <v>0.356947776694257</v>
           </cell>
         </row>
         <row r="5">
@@ -2222,7 +2222,7 @@
             <v>439950.57</v>
           </cell>
           <cell r="G7">
-            <v>78765.05</v>
+            <v>153709.18</v>
           </cell>
           <cell r="H7">
             <v>0</v>
@@ -2246,7 +2246,7 @@
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>1727729.96</v>
+            <v>1802674.09</v>
           </cell>
         </row>
         <row r="8">
@@ -2266,7 +2266,7 @@
             <v>0.737368736976622</v>
           </cell>
           <cell r="G8">
-            <v>0.150168436832698</v>
+            <v>0.293052150508833</v>
           </cell>
           <cell r="H8">
             <v>0</v>
@@ -2290,7 +2290,7 @@
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0.257102673268875</v>
+            <v>0.268255073594681</v>
           </cell>
         </row>
         <row r="10">
@@ -2354,7 +2354,7 @@
             <v>38346</v>
           </cell>
           <cell r="G11">
-            <v>6179</v>
+            <v>12161</v>
           </cell>
           <cell r="H11">
             <v>0</v>
@@ -2378,7 +2378,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>140636</v>
+            <v>146618</v>
           </cell>
         </row>
         <row r="12">
@@ -2398,7 +2398,7 @@
             <v>1.02909129944716</v>
           </cell>
           <cell r="G12">
-            <v>0.188364046519426</v>
+            <v>0.370722636304053</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -2422,7 +2422,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.33326516495602</v>
+            <v>0.347440711876914</v>
           </cell>
         </row>
         <row r="14">
@@ -2486,7 +2486,7 @@
             <v>10231</v>
           </cell>
           <cell r="G15">
-            <v>1619</v>
+            <v>3303</v>
           </cell>
           <cell r="H15">
             <v>0</v>
@@ -2510,7 +2510,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>38177</v>
+            <v>39861</v>
           </cell>
         </row>
         <row r="16">
@@ -2530,7 +2530,7 @@
             <v>0.854268345977926</v>
           </cell>
           <cell r="G16">
-            <v>0.154529037927066</v>
+            <v>0.315262144702347</v>
           </cell>
           <cell r="H16">
             <v>0</v>
@@ -2554,7 +2554,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.283987086467634</v>
+            <v>0.296513850058578</v>
           </cell>
         </row>
         <row r="18">
@@ -2618,7 +2618,7 @@
             <v>171823742</v>
           </cell>
           <cell r="G19">
-            <v>25066020</v>
+            <v>52162719</v>
           </cell>
           <cell r="H19">
             <v>0</v>
@@ -2642,7 +2642,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>627892060</v>
+            <v>654988759</v>
           </cell>
         </row>
         <row r="20">
@@ -2662,7 +2662,7 @@
             <v>1.14727804597092</v>
           </cell>
           <cell r="G20">
-            <v>0.189421947074659</v>
+            <v>0.394189576075033</v>
           </cell>
           <cell r="H20">
             <v>0</v>
@@ -2686,7 +2686,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.368720035241456</v>
+            <v>0.384632158433788</v>
           </cell>
         </row>
         <row r="22">
@@ -2750,7 +2750,7 @@
             <v>4070034.85</v>
           </cell>
           <cell r="G23">
-            <v>673938.58</v>
+            <v>1371955.91</v>
           </cell>
           <cell r="H23">
             <v>0</v>
@@ -2774,7 +2774,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>14919509.12</v>
+            <v>15617526.45</v>
           </cell>
         </row>
         <row r="24">
@@ -2794,7 +2794,7 @@
             <v>1.05573509321019</v>
           </cell>
           <cell r="G24">
-            <v>0.197850227036404</v>
+            <v>0.402769326957713</v>
           </cell>
           <cell r="H24">
             <v>0</v>
@@ -2818,7 +2818,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.340359282552267</v>
+            <v>0.356283176276717</v>
           </cell>
         </row>
         <row r="26">
@@ -2838,7 +2838,7 @@
             <v>0.70390916276867</v>
           </cell>
           <cell r="G26">
-            <v>0.663918234725736</v>
+            <v>0.671231691833395</v>
           </cell>
           <cell r="H26" t="e">
             <v>#DIV/0!</v>
@@ -2862,7 +2862,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.702984197634224</v>
+            <v>0.701950487023549</v>
           </cell>
         </row>
         <row r="27">
@@ -2882,7 +2882,7 @@
             <v>0.733192510300944</v>
           </cell>
           <cell r="G27">
-            <v>0.73798349247451</v>
+            <v>0.728394046542225</v>
           </cell>
           <cell r="H27" t="e">
             <v>#DIV/0!</v>
@@ -2906,7 +2906,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.728540345288546</v>
+            <v>0.728130243217068</v>
           </cell>
         </row>
         <row r="28">
@@ -2926,7 +2926,7 @@
             <v>0.108095037564605</v>
           </cell>
           <cell r="G28">
-            <v>0.116872742320227</v>
+            <v>0.112036530386753</v>
           </cell>
           <cell r="H28" t="e">
             <v>#DIV/0!</v>
@@ -2950,7 +2950,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.115803405199433</v>
+            <v>0.11542635101476</v>
           </cell>
         </row>
         <row r="30">
@@ -2973,7 +2973,7 @@
             <v>51410.92</v>
           </cell>
           <cell r="G30">
-            <v>9785.19</v>
+            <v>22183.88</v>
           </cell>
           <cell r="H30">
             <v>0</v>
@@ -2997,7 +2997,7 @@
             <v>0</v>
           </cell>
           <cell r="O30">
-            <v>305671.35</v>
+            <v>318070.04</v>
           </cell>
         </row>
         <row r="31">
@@ -3017,7 +3017,7 @@
             <v>8430</v>
           </cell>
           <cell r="G31">
-            <v>1241</v>
+            <v>2494</v>
           </cell>
           <cell r="H31">
             <v>0</v>
@@ -3041,7 +3041,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>37179</v>
+            <v>38432</v>
           </cell>
         </row>
         <row r="32">
@@ -3061,7 +3061,7 @@
             <v>2131</v>
           </cell>
           <cell r="G32">
-            <v>327</v>
+            <v>690</v>
           </cell>
           <cell r="H32">
             <v>0</v>
@@ -3085,7 +3085,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>9569</v>
+            <v>9932</v>
           </cell>
         </row>
         <row r="33">
@@ -3105,7 +3105,7 @@
             <v>35782129</v>
           </cell>
           <cell r="G33">
-            <v>5149714</v>
+            <v>10868656</v>
           </cell>
           <cell r="H33">
             <v>0</v>
@@ -3129,7 +3129,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>159432134</v>
+            <v>165151076</v>
           </cell>
         </row>
         <row r="34">
@@ -3149,7 +3149,7 @@
             <v>833536.12</v>
           </cell>
           <cell r="G34">
-            <v>132662.14</v>
+            <v>280388.84</v>
           </cell>
           <cell r="H34">
             <v>0</v>
@@ -3173,7 +3173,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>3654974.63</v>
+            <v>3802701.33</v>
           </cell>
         </row>
         <row r="35">
@@ -3193,7 +3193,7 @@
             <v>0.708815495578813</v>
           </cell>
           <cell r="G35">
-            <v>0.677986631878974</v>
+            <v>0.677525859683111</v>
           </cell>
           <cell r="H35" t="e">
             <v>#DIV/0!</v>
@@ -3217,7 +3217,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.713438052111878</v>
+            <v>0.712180097300728</v>
           </cell>
         </row>
         <row r="36">
@@ -3237,7 +3237,7 @@
             <v>0.747212336892052</v>
           </cell>
           <cell r="G36">
-            <v>0.736502820306205</v>
+            <v>0.723336006415397</v>
           </cell>
           <cell r="H36" t="e">
             <v>#DIV/0!</v>
@@ -3261,7 +3261,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.742623524032384</v>
+            <v>0.741569525395504</v>
           </cell>
         </row>
         <row r="37">
@@ -3281,7 +3281,7 @@
             <v>0.0616780950056489</v>
           </cell>
           <cell r="G37">
-            <v>0.0737602303113759</v>
+            <v>0.0791182701850758</v>
           </cell>
           <cell r="H37" t="e">
             <v>#DIV/0!</v>
@@ -3305,7 +3305,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.0836315928135457</v>
+            <v>0.0836431821480968</v>
           </cell>
         </row>
         <row r="38">
@@ -3328,7 +3328,7 @@
             <v>99083.11</v>
           </cell>
           <cell r="G38">
-            <v>26838.4</v>
+            <v>51107.18</v>
           </cell>
           <cell r="H38">
             <v>0</v>
@@ -3352,7 +3352,7 @@
             <v>0</v>
           </cell>
           <cell r="O38">
-            <v>485688.33</v>
+            <v>509957.11</v>
           </cell>
         </row>
         <row r="39">
@@ -3372,7 +3372,7 @@
             <v>8877</v>
           </cell>
           <cell r="G39">
-            <v>1476</v>
+            <v>2859</v>
           </cell>
           <cell r="H39">
             <v>0</v>
@@ -3396,7 +3396,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>35858</v>
+            <v>37241</v>
           </cell>
         </row>
         <row r="40">
@@ -3416,7 +3416,7 @@
             <v>2609</v>
           </cell>
           <cell r="G40">
-            <v>438</v>
+            <v>849</v>
           </cell>
           <cell r="H40">
             <v>0</v>
@@ -3440,7 +3440,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>10295</v>
+            <v>10706</v>
           </cell>
         </row>
         <row r="41">
@@ -3460,7 +3460,7 @@
             <v>40066145</v>
           </cell>
           <cell r="G41">
-            <v>5837821</v>
+            <v>12095330</v>
           </cell>
           <cell r="H41">
             <v>0</v>
@@ -3484,7 +3484,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>159205285</v>
+            <v>165462794</v>
           </cell>
         </row>
         <row r="42">
@@ -3504,7 +3504,7 @@
             <v>1044149.57</v>
           </cell>
           <cell r="G42">
-            <v>183166.43</v>
+            <v>354397</v>
           </cell>
           <cell r="H42">
             <v>0</v>
@@ -3528,7 +3528,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>4057161.07</v>
+            <v>4228391.64</v>
           </cell>
         </row>
         <row r="43">
@@ -3548,7 +3548,7 @@
             <v>0.674241941045239</v>
           </cell>
           <cell r="G43">
-            <v>0.607802230489767</v>
+            <v>0.633746040827328</v>
           </cell>
           <cell r="H43" t="e">
             <v>#DIV/0!</v>
@@ -3572,7 +3572,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.681452073811494</v>
+            <v>0.6805632600402</v>
           </cell>
         </row>
         <row r="44">
@@ -3592,7 +3592,7 @@
             <v>0.706094401261687</v>
           </cell>
           <cell r="G44">
-            <v>0.703252032520325</v>
+            <v>0.703043022035677</v>
           </cell>
           <cell r="H44" t="e">
             <v>#DIV/0!</v>
@@ -3616,7 +3616,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.712895309275476</v>
+            <v>0.71252114604871</v>
           </cell>
         </row>
         <row r="45">
@@ -3636,7 +3636,7 @@
             <v>0.0948935984334122</v>
           </cell>
           <cell r="G45">
-            <v>0.146524666119223</v>
+            <v>0.14420883923961</v>
           </cell>
           <cell r="H45" t="e">
             <v>#DIV/0!</v>
@@ -3660,7 +3660,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.119711374929465</v>
+            <v>0.120603092952856</v>
           </cell>
         </row>
         <row r="46">
@@ -3683,7 +3683,7 @@
             <v>80999.07</v>
           </cell>
           <cell r="G46">
-            <v>11212.49</v>
+            <v>26904.78</v>
           </cell>
           <cell r="H46">
             <v>0</v>
@@ -3707,7 +3707,7 @@
             <v>0</v>
           </cell>
           <cell r="O46">
-            <v>155793.49</v>
+            <v>171485.78</v>
           </cell>
         </row>
         <row r="47">
@@ -3727,7 +3727,7 @@
             <v>6433</v>
           </cell>
           <cell r="G47">
-            <v>988</v>
+            <v>1885</v>
           </cell>
           <cell r="H47">
             <v>0</v>
@@ -3751,7 +3751,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>19104</v>
+            <v>20001</v>
           </cell>
         </row>
         <row r="48">
@@ -3771,7 +3771,7 @@
             <v>1816</v>
           </cell>
           <cell r="G48">
-            <v>256</v>
+            <v>537</v>
           </cell>
           <cell r="H48">
             <v>0</v>
@@ -3795,7 +3795,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>5188</v>
+            <v>5469</v>
           </cell>
         </row>
         <row r="49">
@@ -3815,7 +3815,7 @@
             <v>26000920</v>
           </cell>
           <cell r="G49">
-            <v>3403246</v>
+            <v>7193090</v>
           </cell>
           <cell r="H49">
             <v>0</v>
@@ -3839,7 +3839,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>80179935</v>
+            <v>83969779</v>
           </cell>
         </row>
         <row r="50">
@@ -3859,7 +3859,7 @@
             <v>658949.99</v>
           </cell>
           <cell r="G50">
-            <v>96010.5</v>
+            <v>201578.32</v>
           </cell>
           <cell r="H50">
             <v>0</v>
@@ -3883,7 +3883,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>1919168.8</v>
+            <v>2024736.62</v>
           </cell>
         </row>
         <row r="51">
@@ -3903,7 +3903,7 @@
             <v>0.683208329743717</v>
           </cell>
           <cell r="G51">
-            <v>0.647356891038732</v>
+            <v>0.649701449585644</v>
           </cell>
           <cell r="H51" t="e">
             <v>#DIV/0!</v>
@@ -3927,7 +3927,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.70080282554482</v>
+            <v>0.698591468842618</v>
           </cell>
         </row>
         <row r="52">
@@ -3947,7 +3947,7 @@
             <v>0.717705580600031</v>
           </cell>
           <cell r="G52">
-            <v>0.740890688259109</v>
+            <v>0.715119363395226</v>
           </cell>
           <cell r="H52" t="e">
             <v>#DIV/0!</v>
@@ -3971,7 +3971,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.728433835845896</v>
+            <v>0.726563671816409</v>
           </cell>
         </row>
         <row r="53">
@@ -3991,7 +3991,7 @@
             <v>0.122921422307025</v>
           </cell>
           <cell r="G53">
-            <v>0.116783997583598</v>
+            <v>0.133470603386317</v>
           </cell>
           <cell r="H53" t="e">
             <v>#DIV/0!</v>
@@ -4015,7 +4015,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.0811775858382024</v>
+            <v>0.0846953516354142</v>
           </cell>
         </row>
         <row r="54">
@@ -4038,7 +4038,7 @@
             <v>53475.37</v>
           </cell>
           <cell r="G54">
-            <v>9115.55</v>
+            <v>19796.35</v>
           </cell>
           <cell r="H54">
             <v>0</v>
@@ -4062,7 +4062,7 @@
             <v>0</v>
           </cell>
           <cell r="O54">
-            <v>330061.97</v>
+            <v>340742.77</v>
           </cell>
         </row>
         <row r="55">
@@ -4082,7 +4082,7 @@
             <v>3410</v>
           </cell>
           <cell r="G55">
-            <v>425</v>
+            <v>878</v>
           </cell>
           <cell r="H55">
             <v>0</v>
@@ -4106,7 +4106,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>16199</v>
+            <v>16652</v>
           </cell>
         </row>
         <row r="56">
@@ -4126,7 +4126,7 @@
             <v>1234</v>
           </cell>
           <cell r="G56">
-            <v>162</v>
+            <v>340</v>
           </cell>
           <cell r="H56">
             <v>0</v>
@@ -4150,7 +4150,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>5889</v>
+            <v>6067</v>
           </cell>
         </row>
         <row r="57">
@@ -4170,7 +4170,7 @@
             <v>13881751</v>
           </cell>
           <cell r="G57">
-            <v>1725641</v>
+            <v>3628095</v>
           </cell>
           <cell r="H57">
             <v>0</v>
@@ -4194,7 +4194,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>65442145</v>
+            <v>67344599</v>
           </cell>
         </row>
         <row r="58">
@@ -4214,7 +4214,7 @@
             <v>463880.75</v>
           </cell>
           <cell r="G58">
-            <v>63977.49</v>
+            <v>134480.18</v>
           </cell>
           <cell r="H58">
             <v>0</v>
@@ -4238,7 +4238,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2172630.97</v>
+            <v>2243133.66</v>
           </cell>
         </row>
         <row r="59">
@@ -4258,7 +4258,7 @@
             <v>0.582292653498827</v>
           </cell>
           <cell r="G59">
-            <v>0.536567208938592</v>
+            <v>0.536670828630452</v>
           </cell>
           <cell r="H59" t="e">
             <v>#DIV/0!</v>
@@ -4282,7 +4282,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.585009215009685</v>
+            <v>0.583646332944977</v>
           </cell>
         </row>
         <row r="60">
@@ -4302,7 +4302,7 @@
             <v>0.638123167155425</v>
           </cell>
           <cell r="G60">
-            <v>0.618823529411765</v>
+            <v>0.612756264236902</v>
           </cell>
           <cell r="H60" t="e">
             <v>#DIV/0!</v>
@@ -4326,7 +4326,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.636459040681524</v>
+            <v>0.635659380254624</v>
           </cell>
         </row>
         <row r="61">
@@ -4346,7 +4346,7 @@
             <v>0.115278269253467</v>
           </cell>
           <cell r="G61">
-            <v>0.142480581842145</v>
+            <v>0.147206450794459</v>
           </cell>
           <cell r="H61" t="e">
             <v>#DIV/0!</v>
@@ -4370,7 +4370,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.151918100477045</v>
+            <v>0.151904800001976</v>
           </cell>
         </row>
         <row r="62">
@@ -4393,7 +4393,7 @@
             <v>154982.1</v>
           </cell>
           <cell r="G62">
-            <v>21813.42</v>
+            <v>33716.99</v>
           </cell>
           <cell r="H62">
             <v>0</v>
@@ -4417,7 +4417,7 @@
             <v>0</v>
           </cell>
           <cell r="O62">
-            <v>450514.82</v>
+            <v>462418.39</v>
           </cell>
         </row>
         <row r="63">
@@ -4437,7 +4437,7 @@
             <v>11196</v>
           </cell>
           <cell r="G63">
-            <v>2049</v>
+            <v>4045</v>
           </cell>
           <cell r="H63">
             <v>0</v>
@@ -4461,7 +4461,7 @@
             <v>0</v>
           </cell>
           <cell r="O63">
-            <v>32296</v>
+            <v>34292</v>
           </cell>
         </row>
         <row r="64">
@@ -4481,7 +4481,7 @@
             <v>2441</v>
           </cell>
           <cell r="G64">
-            <v>436</v>
+            <v>887</v>
           </cell>
           <cell r="H64">
             <v>0</v>
@@ -4505,7 +4505,7 @@
             <v>0</v>
           </cell>
           <cell r="O64">
-            <v>7236</v>
+            <v>7687</v>
           </cell>
         </row>
         <row r="65">
@@ -4525,7 +4525,7 @@
             <v>56092797</v>
           </cell>
           <cell r="G65">
-            <v>8949598</v>
+            <v>18377548</v>
           </cell>
           <cell r="H65">
             <v>0</v>
@@ -4549,7 +4549,7 @@
             <v>0</v>
           </cell>
           <cell r="O65">
-            <v>163632561</v>
+            <v>173060511</v>
           </cell>
         </row>
         <row r="66">
@@ -4569,7 +4569,7 @@
             <v>1069518.42</v>
           </cell>
           <cell r="G66">
-            <v>198122.02</v>
+            <v>401111.57</v>
           </cell>
           <cell r="H66">
             <v>0</v>
@@ -4593,7 +4593,7 @@
             <v>0</v>
           </cell>
           <cell r="O66">
-            <v>3115573.65</v>
+            <v>3318563.2</v>
           </cell>
         </row>
         <row r="67">
@@ -4613,7 +4613,7 @@
             <v>0.761663155253249</v>
           </cell>
           <cell r="G67">
-            <v>0.723280838982935</v>
+            <v>0.727172818430402</v>
           </cell>
           <cell r="H67" t="e">
             <v>#DIV/0!</v>
@@ -4637,7 +4637,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O67">
-            <v>0.761999259884468</v>
+            <v>0.760303261788011</v>
           </cell>
         </row>
         <row r="68">
@@ -4657,7 +4657,7 @@
             <v>0.781975705609146</v>
           </cell>
           <cell r="G68">
-            <v>0.78721327476818</v>
+            <v>0.780716934487021</v>
           </cell>
           <cell r="H68" t="e">
             <v>#DIV/0!</v>
@@ -4681,7 +4681,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O68">
-            <v>0.77594748575675</v>
+            <v>0.775836929896186</v>
           </cell>
         </row>
         <row r="69">
@@ -4701,7 +4701,7 @@
             <v>0.144908303683073</v>
           </cell>
           <cell r="G69">
-            <v>0.11010093678633</v>
+            <v>0.084058881672249</v>
           </cell>
           <cell r="H69" t="e">
             <v>#DIV/0!</v>
@@ -4725,7 +4725,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O69">
-            <v>0.144600921246076</v>
+            <v>0.139342951190443</v>
           </cell>
         </row>
         <row r="70">
@@ -7233,7 +7233,7 @@
             <v>56073.62</v>
           </cell>
           <cell r="G126">
-            <v>9383.18</v>
+            <v>19872.02</v>
           </cell>
           <cell r="H126">
             <v>0</v>
@@ -7257,7 +7257,7 @@
             <v>0</v>
           </cell>
           <cell r="O126">
-            <v>294412.53</v>
+            <v>304901.37</v>
           </cell>
         </row>
         <row r="127">
@@ -7277,7 +7277,7 @@
             <v>3125</v>
           </cell>
           <cell r="G127">
-            <v>392</v>
+            <v>809</v>
           </cell>
           <cell r="H127">
             <v>0</v>
@@ -7301,7 +7301,7 @@
             <v>0</v>
           </cell>
           <cell r="O127">
-            <v>13768</v>
+            <v>14185</v>
           </cell>
         </row>
         <row r="128">
@@ -7321,7 +7321,7 @@
             <v>1163</v>
           </cell>
           <cell r="G128">
-            <v>152</v>
+            <v>317</v>
           </cell>
           <cell r="H128">
             <v>0</v>
@@ -7345,7 +7345,7 @@
             <v>0</v>
           </cell>
           <cell r="O128">
-            <v>5126</v>
+            <v>5291</v>
           </cell>
         </row>
         <row r="129">
@@ -7365,7 +7365,7 @@
             <v>12576283</v>
           </cell>
           <cell r="G129">
-            <v>1566038</v>
+            <v>3277409</v>
           </cell>
           <cell r="H129">
             <v>0</v>
@@ -7389,7 +7389,7 @@
             <v>0</v>
           </cell>
           <cell r="O129">
-            <v>55469762</v>
+            <v>57181133</v>
           </cell>
         </row>
         <row r="130">
@@ -7409,7 +7409,7 @@
             <v>435667.29</v>
           </cell>
           <cell r="G130">
-            <v>59649.73</v>
+            <v>124500.65</v>
           </cell>
           <cell r="H130">
             <v>0</v>
@@ -7433,7 +7433,7 @@
             <v>0</v>
           </cell>
           <cell r="O130">
-            <v>1868481.32</v>
+            <v>1933332.24</v>
           </cell>
         </row>
         <row r="131">
@@ -7453,7 +7453,7 @@
             <v>0.433024696168176</v>
           </cell>
           <cell r="G131">
-            <v>0.47611975252197</v>
+            <v>0.4748440383852</v>
           </cell>
           <cell r="H131" t="e">
             <v>#DIV/0!</v>
@@ -7477,7 +7477,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O131">
-            <v>0.0336846824761931</v>
+            <v>0.0338106668855267</v>
           </cell>
         </row>
         <row r="132">
@@ -7497,7 +7497,7 @@
             <v>0.62784</v>
           </cell>
           <cell r="G132">
-            <v>0.612244897959184</v>
+            <v>0.608158220024722</v>
           </cell>
           <cell r="H132" t="e">
             <v>#DIV/0!</v>
@@ -7521,7 +7521,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O132">
-            <v>0.627687391051714</v>
+            <v>0.627000352485019</v>
           </cell>
         </row>
         <row r="133">
@@ -7541,7 +7541,7 @@
             <v>0.128707436355849</v>
           </cell>
           <cell r="G133">
-            <v>0.157304651672355</v>
+            <v>0.159613785148913</v>
           </cell>
           <cell r="H133" t="e">
             <v>#DIV/0!</v>
@@ -7565,7 +7565,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O133">
-            <v>0.157567820908159</v>
+            <v>0.157707694358834</v>
           </cell>
         </row>
       </sheetData>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="F4" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!F4</f>
-        <v>518715.62</v>
+        <v>593659.75</v>
       </c>
       <c r="G4" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G4</f>
@@ -13798,7 +13798,7 @@
       </c>
       <c r="F5" s="8">
         <f>'[1]特别隐藏版（勿动、勿看）'!F5</f>
-        <v>0.311886374805742</v>
+        <v>0.356947776694257</v>
       </c>
       <c r="G5" s="8">
         <f>'[1]特别隐藏版（勿动、勿看）'!G5</f>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="G7" s="36">
         <f>'[1]特别隐藏版（勿动、勿看）'!G7</f>
-        <v>78765.05</v>
+        <v>153709.18</v>
       </c>
       <c r="H7" s="36">
         <f>'[1]特别隐藏版（勿动、勿看）'!H7</f>
@@ -13995,7 +13995,7 @@
       </c>
       <c r="O7" s="36">
         <f>'[1]特别隐藏版（勿动、勿看）'!O7</f>
-        <v>1727729.96</v>
+        <v>1802674.09</v>
       </c>
       <c r="P7" s="82"/>
       <c r="Q7" s="84"/>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="G8" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G8</f>
-        <v>0.150168436832698</v>
+        <v>0.293052150508833</v>
       </c>
       <c r="H8" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!H8</f>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="O8" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O8</f>
-        <v>0.257102673268875</v>
+        <v>0.268255073594681</v>
       </c>
       <c r="P8" s="82"/>
       <c r="Q8" s="82"/>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="G11" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!G11</f>
-        <v>6179</v>
+        <v>12161</v>
       </c>
       <c r="H11" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!H11</f>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="O11" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!O11</f>
-        <v>140636</v>
+        <v>146618</v>
       </c>
       <c r="P11" s="69"/>
       <c r="BP11" s="86"/>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="G12" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G12</f>
-        <v>0.188364046519426</v>
+        <v>0.370722636304053</v>
       </c>
       <c r="H12" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!H12</f>
@@ -14394,7 +14394,7 @@
       </c>
       <c r="O12" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O12</f>
-        <v>0.33326516495602</v>
+        <v>0.347440711876914</v>
       </c>
       <c r="BP12" s="86"/>
       <c r="BQ12" s="87"/>
@@ -14596,7 +14596,7 @@
       </c>
       <c r="G15" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!G15</f>
-        <v>1619</v>
+        <v>3303</v>
       </c>
       <c r="H15" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!H15</f>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="O15" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!O15</f>
-        <v>38177</v>
+        <v>39861</v>
       </c>
       <c r="P15" s="69"/>
       <c r="BP15" s="86"/>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="G16" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G16</f>
-        <v>0.154529037927066</v>
+        <v>0.315262144702347</v>
       </c>
       <c r="H16" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!H16</f>
@@ -14707,7 +14707,7 @@
       </c>
       <c r="O16" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O16</f>
-        <v>0.283987086467634</v>
+        <v>0.296513850058578</v>
       </c>
       <c r="BP16" s="86"/>
       <c r="BQ16" s="87"/>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="G19" s="23">
         <f>'[1]特别隐藏版（勿动、勿看）'!G19</f>
-        <v>25066020</v>
+        <v>52162719</v>
       </c>
       <c r="H19" s="23">
         <f>'[1]特别隐藏版（勿动、勿看）'!H19</f>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="O19" s="23">
         <f>'[1]特别隐藏版（勿动、勿看）'!O19</f>
-        <v>627892060</v>
+        <v>654988759</v>
       </c>
       <c r="P19" s="69"/>
       <c r="BP19" s="90"/>
@@ -14989,7 +14989,7 @@
       </c>
       <c r="G20" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G20</f>
-        <v>0.189421947074659</v>
+        <v>0.394189576075033</v>
       </c>
       <c r="H20" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!H20</f>
@@ -15021,7 +15021,7 @@
       </c>
       <c r="O20" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O20</f>
-        <v>0.368720035241456</v>
+        <v>0.384632158433788</v>
       </c>
       <c r="BP20" s="92"/>
       <c r="BQ20" s="93"/>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="G23" s="25">
         <f>'[1]特别隐藏版（勿动、勿看）'!G23</f>
-        <v>673938.58</v>
+        <v>1371955.91</v>
       </c>
       <c r="H23" s="25">
         <f>'[1]特别隐藏版（勿动、勿看）'!H23</f>
@@ -15255,7 +15255,7 @@
       </c>
       <c r="O23" s="36">
         <f>'[1]特别隐藏版（勿动、勿看）'!O23</f>
-        <v>14919509.12</v>
+        <v>15617526.45</v>
       </c>
       <c r="P23" s="69"/>
       <c r="BP23" s="94"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="G24" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G24</f>
-        <v>0.197850227036404</v>
+        <v>0.402769326957713</v>
       </c>
       <c r="H24" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!H24</f>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="O24" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O24</f>
-        <v>0.340359282552267</v>
+        <v>0.356283176276717</v>
       </c>
       <c r="BP24" s="89"/>
       <c r="BQ24" s="89"/>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="G26" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G26</f>
-        <v>0.663918234725736</v>
+        <v>0.671231691833395</v>
       </c>
       <c r="H26" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H26</f>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="O26" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O26</f>
-        <v>0.702984197634224</v>
+        <v>0.701950487023549</v>
       </c>
       <c r="BP26" s="89"/>
       <c r="BQ26" s="96"/>
@@ -15536,7 +15536,7 @@
       </c>
       <c r="G27" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G27</f>
-        <v>0.73798349247451</v>
+        <v>0.728394046542225</v>
       </c>
       <c r="H27" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H27</f>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="O27" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O27</f>
-        <v>0.728540345288546</v>
+        <v>0.728130243217068</v>
       </c>
       <c r="BP27" s="89"/>
       <c r="BQ27" s="96"/>
@@ -15614,7 +15614,7 @@
       </c>
       <c r="G28" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G28</f>
-        <v>0.116872742320227</v>
+        <v>0.112036530386753</v>
       </c>
       <c r="H28" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H28</f>
@@ -15646,7 +15646,7 @@
       </c>
       <c r="O28" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O28</f>
-        <v>0.115803405199433</v>
+        <v>0.11542635101476</v>
       </c>
       <c r="BP28" s="89"/>
       <c r="BQ28" s="96"/>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="G30" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G30</f>
-        <v>9785.19</v>
+        <v>22183.88</v>
       </c>
       <c r="H30" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H30</f>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="O30" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O30</f>
-        <v>305671.35</v>
+        <v>318070.04</v>
       </c>
       <c r="BP30" s="94"/>
       <c r="BQ30" s="98"/>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="G31" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G31</f>
-        <v>1241</v>
+        <v>2494</v>
       </c>
       <c r="H31" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H31</f>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="O31" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O31</f>
-        <v>37179</v>
+        <v>38432</v>
       </c>
       <c r="BP31" s="94"/>
       <c r="BQ31" s="99"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="G32" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G32</f>
-        <v>327</v>
+        <v>690</v>
       </c>
       <c r="H32" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H32</f>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="O32" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O32</f>
-        <v>9569</v>
+        <v>9932</v>
       </c>
       <c r="BP32" s="94"/>
       <c r="BQ32" s="99"/>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="G33" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G33</f>
-        <v>5149714</v>
+        <v>10868656</v>
       </c>
       <c r="H33" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H33</f>
@@ -16036,7 +16036,7 @@
       </c>
       <c r="O33" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O33</f>
-        <v>159432134</v>
+        <v>165151076</v>
       </c>
       <c r="BP33" s="89"/>
       <c r="BQ33" s="100"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="G34" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G34</f>
-        <v>132662.14</v>
+        <v>280388.84</v>
       </c>
       <c r="H34" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H34</f>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="O34" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O34</f>
-        <v>3654974.63</v>
+        <v>3802701.33</v>
       </c>
       <c r="Q34" s="69"/>
       <c r="BP34" s="86"/>
@@ -16161,7 +16161,7 @@
       </c>
       <c r="G35" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G35</f>
-        <v>0.677986631878974</v>
+        <v>0.677525859683111</v>
       </c>
       <c r="H35" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H35</f>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="O35" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O35</f>
-        <v>0.713438052111878</v>
+        <v>0.712180097300728</v>
       </c>
       <c r="BP35" s="102"/>
       <c r="BQ35" s="103"/>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="G36" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G36</f>
-        <v>0.736502820306205</v>
+        <v>0.723336006415397</v>
       </c>
       <c r="H36" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H36</f>
@@ -16271,7 +16271,7 @@
       </c>
       <c r="O36" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O36</f>
-        <v>0.742623524032384</v>
+        <v>0.741569525395504</v>
       </c>
       <c r="BP36" s="102"/>
       <c r="BQ36" s="103"/>
@@ -16317,7 +16317,7 @@
       </c>
       <c r="G37" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G37</f>
-        <v>0.0737602303113759</v>
+        <v>0.0791182701850758</v>
       </c>
       <c r="H37" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H37</f>
@@ -16349,7 +16349,7 @@
       </c>
       <c r="O37" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O37</f>
-        <v>0.0836315928135457</v>
+        <v>0.0836431821480968</v>
       </c>
       <c r="BP37" s="102"/>
       <c r="BQ37" s="103"/>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="G38" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G38</f>
-        <v>26838.4</v>
+        <v>51107.18</v>
       </c>
       <c r="H38" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H38</f>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="O38" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O38</f>
-        <v>485688.33</v>
+        <v>509957.11</v>
       </c>
     </row>
     <row r="39" s="68" customFormat="1" spans="1:15">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="G39" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G39</f>
-        <v>1476</v>
+        <v>2859</v>
       </c>
       <c r="H39" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H39</f>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="O39" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O39</f>
-        <v>35858</v>
+        <v>37241</v>
       </c>
     </row>
     <row r="40" s="68" customFormat="1" ht="17.4" spans="1:83">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="G40" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G40</f>
-        <v>438</v>
+        <v>849</v>
       </c>
       <c r="H40" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H40</f>
@@ -16551,7 +16551,7 @@
       </c>
       <c r="O40" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O40</f>
-        <v>10295</v>
+        <v>10706</v>
       </c>
       <c r="BP40" s="85"/>
       <c r="BQ40" s="85"/>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="G41" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G41</f>
-        <v>5837821</v>
+        <v>12095330</v>
       </c>
       <c r="H41" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H41</f>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="O41" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O41</f>
-        <v>159205285</v>
+        <v>165462794</v>
       </c>
       <c r="Q41" s="70"/>
       <c r="BP41" s="71"/>
@@ -16676,7 +16676,7 @@
       </c>
       <c r="G42" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G42</f>
-        <v>183166.43</v>
+        <v>354397</v>
       </c>
       <c r="H42" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H42</f>
@@ -16708,7 +16708,7 @@
       </c>
       <c r="O42" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O42</f>
-        <v>4057161.07</v>
+        <v>4228391.64</v>
       </c>
       <c r="Q42" s="69"/>
       <c r="BP42" s="71"/>
@@ -16755,7 +16755,7 @@
       </c>
       <c r="G43" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G43</f>
-        <v>0.607802230489767</v>
+        <v>0.633746040827328</v>
       </c>
       <c r="H43" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H43</f>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="O43" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O43</f>
-        <v>0.681452073811494</v>
+        <v>0.6805632600402</v>
       </c>
       <c r="BP43" s="71"/>
       <c r="BQ43" s="71"/>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="G44" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G44</f>
-        <v>0.703252032520325</v>
+        <v>0.703043022035677</v>
       </c>
       <c r="H44" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H44</f>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="O44" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O44</f>
-        <v>0.712895309275476</v>
+        <v>0.71252114604871</v>
       </c>
       <c r="BP44" s="71"/>
       <c r="BQ44" s="104"/>
@@ -16911,7 +16911,7 @@
       </c>
       <c r="G45" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G45</f>
-        <v>0.146524666119223</v>
+        <v>0.14420883923961</v>
       </c>
       <c r="H45" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H45</f>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="O45" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O45</f>
-        <v>0.119711374929465</v>
+        <v>0.120603092952856</v>
       </c>
       <c r="BP45" s="105"/>
       <c r="BQ45" s="106"/>
@@ -16988,7 +16988,7 @@
       </c>
       <c r="G46" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G46</f>
-        <v>11212.49</v>
+        <v>26904.78</v>
       </c>
       <c r="H46" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H46</f>
@@ -17020,7 +17020,7 @@
       </c>
       <c r="O46" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O46</f>
-        <v>155793.49</v>
+        <v>171485.78</v>
       </c>
       <c r="BP46" s="71"/>
       <c r="BQ46" s="37"/>
@@ -17065,7 +17065,7 @@
       </c>
       <c r="G47" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G47</f>
-        <v>988</v>
+        <v>1885</v>
       </c>
       <c r="H47" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H47</f>
@@ -17097,7 +17097,7 @@
       </c>
       <c r="O47" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O47</f>
-        <v>19104</v>
+        <v>20001</v>
       </c>
       <c r="BP47" s="105"/>
       <c r="BQ47" s="107"/>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="G48" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G48</f>
-        <v>256</v>
+        <v>537</v>
       </c>
       <c r="H48" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H48</f>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="O48" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O48</f>
-        <v>5188</v>
+        <v>5469</v>
       </c>
       <c r="BP48" s="105"/>
       <c r="BQ48" s="105"/>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="G49" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G49</f>
-        <v>3403246</v>
+        <v>7193090</v>
       </c>
       <c r="H49" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H49</f>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="O49" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O49</f>
-        <v>80179935</v>
+        <v>83969779</v>
       </c>
       <c r="Q49" s="70"/>
       <c r="BP49" s="108"/>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="G50" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G50</f>
-        <v>96010.5</v>
+        <v>201578.32</v>
       </c>
       <c r="H50" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H50</f>
@@ -17329,7 +17329,7 @@
       </c>
       <c r="O50" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O50</f>
-        <v>1919168.8</v>
+        <v>2024736.62</v>
       </c>
       <c r="Q50" s="69"/>
       <c r="BP50" s="108"/>
@@ -17375,7 +17375,7 @@
       </c>
       <c r="G51" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G51</f>
-        <v>0.647356891038732</v>
+        <v>0.649701449585644</v>
       </c>
       <c r="H51" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H51</f>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="O51" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O51</f>
-        <v>0.70080282554482</v>
+        <v>0.698591468842618</v>
       </c>
       <c r="BP51" s="108"/>
       <c r="BQ51" s="109"/>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="G52" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G52</f>
-        <v>0.740890688259109</v>
+        <v>0.715119363395226</v>
       </c>
       <c r="H52" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H52</f>
@@ -17482,7 +17482,7 @@
       </c>
       <c r="O52" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O52</f>
-        <v>0.728433835845896</v>
+        <v>0.726563671816409</v>
       </c>
     </row>
     <row r="53" s="68" customFormat="1" spans="1:15">
@@ -17512,7 +17512,7 @@
       </c>
       <c r="G53" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G53</f>
-        <v>0.116783997583598</v>
+        <v>0.133470603386317</v>
       </c>
       <c r="H53" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H53</f>
@@ -17544,7 +17544,7 @@
       </c>
       <c r="O53" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O53</f>
-        <v>0.0811775858382024</v>
+        <v>0.0846953516354142</v>
       </c>
     </row>
     <row r="54" s="68" customFormat="1" spans="1:15">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="G54" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G54</f>
-        <v>9115.55</v>
+        <v>19796.35</v>
       </c>
       <c r="H54" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H54</f>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="O54" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O54</f>
-        <v>330061.97</v>
+        <v>340742.77</v>
       </c>
     </row>
     <row r="55" s="68" customFormat="1" spans="1:15">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="G55" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G55</f>
-        <v>425</v>
+        <v>878</v>
       </c>
       <c r="H55" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H55</f>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="O55" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O55</f>
-        <v>16199</v>
+        <v>16652</v>
       </c>
     </row>
     <row r="56" s="68" customFormat="1" spans="1:15">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="G56" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G56</f>
-        <v>162</v>
+        <v>340</v>
       </c>
       <c r="H56" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H56</f>
@@ -17730,7 +17730,7 @@
       </c>
       <c r="O56" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O56</f>
-        <v>5889</v>
+        <v>6067</v>
       </c>
     </row>
     <row r="57" s="68" customFormat="1" spans="1:17">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="G57" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G57</f>
-        <v>1725641</v>
+        <v>3628095</v>
       </c>
       <c r="H57" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H57</f>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="O57" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O57</f>
-        <v>65442145</v>
+        <v>67344599</v>
       </c>
       <c r="Q57" s="70"/>
     </row>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="G58" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G58</f>
-        <v>63977.49</v>
+        <v>134480.18</v>
       </c>
       <c r="H58" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H58</f>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="O58" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O58</f>
-        <v>2172630.97</v>
+        <v>2243133.66</v>
       </c>
       <c r="Q58" s="69"/>
     </row>
@@ -17886,7 +17886,7 @@
       </c>
       <c r="G59" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G59</f>
-        <v>0.536567208938592</v>
+        <v>0.536670828630452</v>
       </c>
       <c r="H59" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H59</f>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="O59" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O59</f>
-        <v>0.585009215009685</v>
+        <v>0.583646332944977</v>
       </c>
     </row>
     <row r="60" s="68" customFormat="1" spans="1:15">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="G60" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G60</f>
-        <v>0.618823529411765</v>
+        <v>0.612756264236902</v>
       </c>
       <c r="H60" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H60</f>
@@ -17980,7 +17980,7 @@
       </c>
       <c r="O60" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O60</f>
-        <v>0.636459040681524</v>
+        <v>0.635659380254624</v>
       </c>
     </row>
     <row r="61" s="68" customFormat="1" spans="1:15">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="G61" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G61</f>
-        <v>0.142480581842145</v>
+        <v>0.147206450794459</v>
       </c>
       <c r="H61" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H61</f>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="O61" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O61</f>
-        <v>0.151918100477045</v>
+        <v>0.151904800001976</v>
       </c>
     </row>
     <row r="62" s="68" customFormat="1" spans="1:15">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="G62" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G62</f>
-        <v>21813.42</v>
+        <v>33716.99</v>
       </c>
       <c r="H62" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H62</f>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="O62" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O62</f>
-        <v>450514.82</v>
+        <v>462418.39</v>
       </c>
     </row>
     <row r="63" s="68" customFormat="1" spans="1:15">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="G63" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G63</f>
-        <v>2049</v>
+        <v>4045</v>
       </c>
       <c r="H63" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H63</f>
@@ -18166,7 +18166,7 @@
       </c>
       <c r="O63" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O63</f>
-        <v>32296</v>
+        <v>34292</v>
       </c>
     </row>
     <row r="64" s="68" customFormat="1" spans="1:15">
@@ -18196,7 +18196,7 @@
       </c>
       <c r="G64" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G64</f>
-        <v>436</v>
+        <v>887</v>
       </c>
       <c r="H64" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H64</f>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="O64" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O64</f>
-        <v>7236</v>
+        <v>7687</v>
       </c>
     </row>
     <row r="65" s="68" customFormat="1" spans="1:17">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="G65" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G65</f>
-        <v>8949598</v>
+        <v>18377548</v>
       </c>
       <c r="H65" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H65</f>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="O65" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O65</f>
-        <v>163632561</v>
+        <v>173060511</v>
       </c>
       <c r="Q65" s="70"/>
     </row>
@@ -18321,7 +18321,7 @@
       </c>
       <c r="G66" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G66</f>
-        <v>198122.02</v>
+        <v>401111.57</v>
       </c>
       <c r="H66" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H66</f>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="O66" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O66</f>
-        <v>3115573.65</v>
+        <v>3318563.2</v>
       </c>
       <c r="Q66" s="69"/>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="G67" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G67</f>
-        <v>0.723280838982935</v>
+        <v>0.727172818430402</v>
       </c>
       <c r="H67" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H67</f>
@@ -18416,7 +18416,7 @@
       </c>
       <c r="O67" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O67</f>
-        <v>0.761999259884468</v>
+        <v>0.760303261788011</v>
       </c>
     </row>
     <row r="68" s="68" customFormat="1" spans="1:15">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="G68" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G68</f>
-        <v>0.78721327476818</v>
+        <v>0.780716934487021</v>
       </c>
       <c r="H68" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H68</f>
@@ -18478,7 +18478,7 @@
       </c>
       <c r="O68" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O68</f>
-        <v>0.77594748575675</v>
+        <v>0.775836929896186</v>
       </c>
     </row>
     <row r="69" s="68" customFormat="1" spans="1:15">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="G69" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G69</f>
-        <v>0.11010093678633</v>
+        <v>0.084058881672249</v>
       </c>
       <c r="H69" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H69</f>
@@ -18540,7 +18540,7 @@
       </c>
       <c r="O69" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O69</f>
-        <v>0.144600921246076</v>
+        <v>0.139342951190443</v>
       </c>
     </row>
     <row r="70" s="68" customFormat="1" spans="1:15">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="G126" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G126</f>
-        <v>9383.18</v>
+        <v>19872.02</v>
       </c>
       <c r="H126" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H126</f>
@@ -22074,7 +22074,7 @@
       </c>
       <c r="O126" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O126</f>
-        <v>294412.53</v>
+        <v>304901.37</v>
       </c>
     </row>
     <row r="127" s="68" customFormat="1" spans="1:15">
@@ -22104,7 +22104,7 @@
       </c>
       <c r="G127" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G127</f>
-        <v>392</v>
+        <v>809</v>
       </c>
       <c r="H127" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H127</f>
@@ -22136,7 +22136,7 @@
       </c>
       <c r="O127" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O127</f>
-        <v>13768</v>
+        <v>14185</v>
       </c>
     </row>
     <row r="128" s="68" customFormat="1" spans="1:15">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="G128" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G128</f>
-        <v>152</v>
+        <v>317</v>
       </c>
       <c r="H128" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H128</f>
@@ -22198,7 +22198,7 @@
       </c>
       <c r="O128" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O128</f>
-        <v>5126</v>
+        <v>5291</v>
       </c>
     </row>
     <row r="129" s="68" customFormat="1" spans="1:15">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="G129" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G129</f>
-        <v>1566038</v>
+        <v>3277409</v>
       </c>
       <c r="H129" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H129</f>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="O129" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O129</f>
-        <v>55469762</v>
+        <v>57181133</v>
       </c>
     </row>
     <row r="130" s="68" customFormat="1" spans="1:15">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="G130" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G130</f>
-        <v>59649.73</v>
+        <v>124500.65</v>
       </c>
       <c r="H130" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H130</f>
@@ -22322,7 +22322,7 @@
       </c>
       <c r="O130" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O130</f>
-        <v>1868481.32</v>
+        <v>1933332.24</v>
       </c>
     </row>
     <row r="131" s="68" customFormat="1" spans="1:15">
@@ -22352,7 +22352,7 @@
       </c>
       <c r="G131" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G131</f>
-        <v>0.47611975252197</v>
+        <v>0.4748440383852</v>
       </c>
       <c r="H131" s="6" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H131</f>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="O131" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O131</f>
-        <v>0.0336846824761931</v>
+        <v>0.0338106668855267</v>
       </c>
     </row>
     <row r="132" s="68" customFormat="1" spans="1:15">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="G132" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G132</f>
-        <v>0.612244897959184</v>
+        <v>0.608158220024722</v>
       </c>
       <c r="H132" s="6" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H132</f>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="O132" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O132</f>
-        <v>0.627687391051714</v>
+        <v>0.627000352485019</v>
       </c>
     </row>
     <row r="133" s="68" customFormat="1" spans="1:15">
@@ -22476,7 +22476,7 @@
       </c>
       <c r="G133" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G133</f>
-        <v>0.157304651672355</v>
+        <v>0.159613785148913</v>
       </c>
       <c r="H133" s="6" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H133</f>
@@ -22508,7 +22508,7 @@
       </c>
       <c r="O133" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O133</f>
-        <v>0.157567820908159</v>
+        <v>0.157707694358834</v>
       </c>
     </row>
   </sheetData>
@@ -22629,7 +22629,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13b69e8c-015a-4a5c-a3d7-696564f4d7fe}</x14:id>
+          <x14:id>{53274e36-5cb1-486f-9c51-6a238bb572b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22643,7 +22643,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9f2d107-49b7-4af4-9b85-a635c65cc504}</x14:id>
+          <x14:id>{8f95c0ff-3ff0-4952-9b13-eb2240d96e2f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22657,7 +22657,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{01909df2-68a8-4385-959a-35a1504192cd}</x14:id>
+          <x14:id>{08685781-db06-4bd7-9629-51c72f8ccb45}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22671,7 +22671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63826b9e-0c1d-4834-beab-01c532eaf262}</x14:id>
+          <x14:id>{38017cf9-797a-4e03-b1a1-8a3b71cdc2ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22685,7 +22685,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f453bd4-aaef-4c2e-a4bd-04b0d82780b8}</x14:id>
+          <x14:id>{ec96260b-b351-439f-87ca-a82c5a36a78e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22699,7 +22699,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1a4de9c2-da8b-4123-b722-33df594c5dfc}</x14:id>
+          <x14:id>{1d3de1db-0fb8-4cad-844a-92ecfcb568f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22713,7 +22713,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f6beb7e-1435-4800-baba-17ee6b2e995f}</x14:id>
+          <x14:id>{fd8bedd3-dd6c-4f66-a678-2f55e9b76739}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22727,7 +22727,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66d859ac-186e-484b-80a8-916e62a42393}</x14:id>
+          <x14:id>{9148fd7c-b9da-43d0-97d0-a70bc81e9684}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22741,7 +22741,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e1fa67a8-d1c6-473a-8e04-bff493ab41da}</x14:id>
+          <x14:id>{df7070b4-b6c8-4033-b1f3-04bb7ba99d38}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22755,7 +22755,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0bc12d0b-47de-4ab5-80c4-133b9904065c}</x14:id>
+          <x14:id>{9ddae40d-8aff-4ee4-af4e-9b2665d230bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22769,7 +22769,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{708c4319-df62-4e01-8eb7-0312733de4d8}</x14:id>
+          <x14:id>{1bf7153e-2e55-4a68-977d-4585546e5d9f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22783,7 +22783,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24432474-4da7-450e-826b-b9a0355b3c3d}</x14:id>
+          <x14:id>{e485598a-291b-4c5e-9229-67406c227950}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22797,7 +22797,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91c4df36-3d7f-4b99-bfa9-b0e7a3b52c11}</x14:id>
+          <x14:id>{b298eb82-8571-41ac-8f19-bb87ee7cf69a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22819,7 +22819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec41d785-d1f0-48d9-94eb-758f05983782}</x14:id>
+          <x14:id>{233e0a11-b587-46db-994f-336323aac803}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22849,7 +22849,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4fd8437d-d081-4039-b2f4-5b579d0a5ccd}</x14:id>
+          <x14:id>{26fb4a24-43c1-4b4c-89f7-b877a3ba10ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22879,7 +22879,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf54741d-5051-4844-96c6-194e5267ee13}</x14:id>
+          <x14:id>{6d8f7f6e-64e6-4cd4-9c92-f480ed67faa4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22909,7 +22909,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6de4fb8a-0866-45f8-afaf-9b2d29363ba2}</x14:id>
+          <x14:id>{dd861fd3-88ae-48ca-87cb-8366ba174dbb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22939,7 +22939,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d36b5076-9ca5-4012-9e88-f411c1351faf}</x14:id>
+          <x14:id>{70c99161-322d-414b-8c3f-d4d771712a0b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22969,7 +22969,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7e9157e-42af-4bb5-a507-08a0865bfed4}</x14:id>
+          <x14:id>{23f91689-935a-4a0b-9d23-97fa2908b13a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22999,7 +22999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5fddd249-fba5-497d-854f-59177d62f09f}</x14:id>
+          <x14:id>{d613d811-9901-45a9-886a-10fee96c1049}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23029,7 +23029,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34bd00e7-96c8-434d-be3b-fc7794289c8e}</x14:id>
+          <x14:id>{1fe9be13-7d27-44a0-a746-31ca1d246259}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23051,7 +23051,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29d66be1-8447-46ee-8191-e8edf30eb026}</x14:id>
+          <x14:id>{9e2a6be7-c252-4147-8568-f659e1a85b81}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23073,7 +23073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c25a8ea3-e2ed-48f7-87fd-4fbfeb96bc8c}</x14:id>
+          <x14:id>{3c7c37f4-b154-4d81-9853-209e844fefbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23095,7 +23095,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76869235-3dc1-45a6-8fb9-b7c5e33c36e1}</x14:id>
+          <x14:id>{0f386d68-dda1-479f-a2d0-2d646577485d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23117,7 +23117,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c96a1508-c0cd-4337-97a2-7ed22092ee42}</x14:id>
+          <x14:id>{cc9f0f80-89ca-439d-9ced-637c8de60ddd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23139,7 +23139,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99a78f7d-6673-4d89-b5a2-c77da2022263}</x14:id>
+          <x14:id>{f9a83834-b977-46b2-b196-b2429f6397df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23161,7 +23161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56d1b296-02d2-45b2-b594-d2f5381585d9}</x14:id>
+          <x14:id>{6d3ef4b3-f0a2-4894-8295-c550a1813217}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23183,7 +23183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c51b62e5-751c-4c4b-af8f-2cb7fd7f5fb4}</x14:id>
+          <x14:id>{bd7602ea-93f3-44db-8277-a29bf3ebfc1c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23205,7 +23205,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4d41e3e-b06e-40fd-a76a-0a1d61fca851}</x14:id>
+          <x14:id>{78668496-bdd7-4435-97c8-10e79324acfa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23227,7 +23227,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{263c36a2-3fea-4e38-add9-1e2dfeaa07b3}</x14:id>
+          <x14:id>{55f77087-de2f-4e8a-88b1-882bc32fffab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23249,7 +23249,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af32807a-c742-447e-bf9a-4cd63e5dc0d2}</x14:id>
+          <x14:id>{0068d450-c605-40ba-9339-f50ac51a9618}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23271,7 +23271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71fc9a15-f23e-49fc-8dd8-0dcefc3fd3fe}</x14:id>
+          <x14:id>{fac5eb48-5db7-4701-97ea-1479a0116814}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23293,7 +23293,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2220b0d5-3b2c-44a6-8be5-cd08faeb8ad7}</x14:id>
+          <x14:id>{d13997e6-87bf-493b-bebc-5da74afe0b4a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23312,7 +23312,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{13b69e8c-015a-4a5c-a3d7-696564f4d7fe}">
+          <x14:cfRule type="dataBar" id="{53274e36-5cb1-486f-9c51-6a238bb572b5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23325,7 +23325,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a9f2d107-49b7-4af4-9b85-a635c65cc504}">
+          <x14:cfRule type="dataBar" id="{8f95c0ff-3ff0-4952-9b13-eb2240d96e2f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23338,7 +23338,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{01909df2-68a8-4385-959a-35a1504192cd}">
+          <x14:cfRule type="dataBar" id="{08685781-db06-4bd7-9629-51c72f8ccb45}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23351,7 +23351,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{63826b9e-0c1d-4834-beab-01c532eaf262}">
+          <x14:cfRule type="dataBar" id="{38017cf9-797a-4e03-b1a1-8a3b71cdc2ff}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23364,7 +23364,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1f453bd4-aaef-4c2e-a4bd-04b0d82780b8}">
+          <x14:cfRule type="dataBar" id="{ec96260b-b351-439f-87ca-a82c5a36a78e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23377,7 +23377,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1a4de9c2-da8b-4123-b722-33df594c5dfc}">
+          <x14:cfRule type="dataBar" id="{1d3de1db-0fb8-4cad-844a-92ecfcb568f0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23390,7 +23390,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8f6beb7e-1435-4800-baba-17ee6b2e995f}">
+          <x14:cfRule type="dataBar" id="{fd8bedd3-dd6c-4f66-a678-2f55e9b76739}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23403,7 +23403,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66d859ac-186e-484b-80a8-916e62a42393}">
+          <x14:cfRule type="dataBar" id="{9148fd7c-b9da-43d0-97d0-a70bc81e9684}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23416,7 +23416,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e1fa67a8-d1c6-473a-8e04-bff493ab41da}">
+          <x14:cfRule type="dataBar" id="{df7070b4-b6c8-4033-b1f3-04bb7ba99d38}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23429,7 +23429,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0bc12d0b-47de-4ab5-80c4-133b9904065c}">
+          <x14:cfRule type="dataBar" id="{9ddae40d-8aff-4ee4-af4e-9b2665d230bd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23442,7 +23442,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{708c4319-df62-4e01-8eb7-0312733de4d8}">
+          <x14:cfRule type="dataBar" id="{1bf7153e-2e55-4a68-977d-4585546e5d9f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23455,7 +23455,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{24432474-4da7-450e-826b-b9a0355b3c3d}">
+          <x14:cfRule type="dataBar" id="{e485598a-291b-4c5e-9229-67406c227950}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23468,7 +23468,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{91c4df36-3d7f-4b99-bfa9-b0e7a3b52c11}">
+          <x14:cfRule type="dataBar" id="{b298eb82-8571-41ac-8f19-bb87ee7cf69a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23481,7 +23481,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec41d785-d1f0-48d9-94eb-758f05983782}">
+          <x14:cfRule type="dataBar" id="{233e0a11-b587-46db-994f-336323aac803}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23494,7 +23494,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4fd8437d-d081-4039-b2f4-5b579d0a5ccd}">
+          <x14:cfRule type="dataBar" id="{26fb4a24-43c1-4b4c-89f7-b877a3ba10ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23507,7 +23507,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf54741d-5051-4844-96c6-194e5267ee13}">
+          <x14:cfRule type="dataBar" id="{6d8f7f6e-64e6-4cd4-9c92-f480ed67faa4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23520,7 +23520,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6de4fb8a-0866-45f8-afaf-9b2d29363ba2}">
+          <x14:cfRule type="dataBar" id="{dd861fd3-88ae-48ca-87cb-8366ba174dbb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23533,7 +23533,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d36b5076-9ca5-4012-9e88-f411c1351faf}">
+          <x14:cfRule type="dataBar" id="{70c99161-322d-414b-8c3f-d4d771712a0b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23546,7 +23546,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b7e9157e-42af-4bb5-a507-08a0865bfed4}">
+          <x14:cfRule type="dataBar" id="{23f91689-935a-4a0b-9d23-97fa2908b13a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23559,7 +23559,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5fddd249-fba5-497d-854f-59177d62f09f}">
+          <x14:cfRule type="dataBar" id="{d613d811-9901-45a9-886a-10fee96c1049}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23572,7 +23572,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{34bd00e7-96c8-434d-be3b-fc7794289c8e}">
+          <x14:cfRule type="dataBar" id="{1fe9be13-7d27-44a0-a746-31ca1d246259}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23585,7 +23585,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{29d66be1-8447-46ee-8191-e8edf30eb026}">
+          <x14:cfRule type="dataBar" id="{9e2a6be7-c252-4147-8568-f659e1a85b81}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23598,7 +23598,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c25a8ea3-e2ed-48f7-87fd-4fbfeb96bc8c}">
+          <x14:cfRule type="dataBar" id="{3c7c37f4-b154-4d81-9853-209e844fefbd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23611,7 +23611,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{76869235-3dc1-45a6-8fb9-b7c5e33c36e1}">
+          <x14:cfRule type="dataBar" id="{0f386d68-dda1-479f-a2d0-2d646577485d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23624,7 +23624,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c96a1508-c0cd-4337-97a2-7ed22092ee42}">
+          <x14:cfRule type="dataBar" id="{cc9f0f80-89ca-439d-9ced-637c8de60ddd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23637,7 +23637,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99a78f7d-6673-4d89-b5a2-c77da2022263}">
+          <x14:cfRule type="dataBar" id="{f9a83834-b977-46b2-b196-b2429f6397df}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23650,7 +23650,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{56d1b296-02d2-45b2-b594-d2f5381585d9}">
+          <x14:cfRule type="dataBar" id="{6d3ef4b3-f0a2-4894-8295-c550a1813217}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23663,7 +23663,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c51b62e5-751c-4c4b-af8f-2cb7fd7f5fb4}">
+          <x14:cfRule type="dataBar" id="{bd7602ea-93f3-44db-8277-a29bf3ebfc1c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23676,7 +23676,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c4d41e3e-b06e-40fd-a76a-0a1d61fca851}">
+          <x14:cfRule type="dataBar" id="{78668496-bdd7-4435-97c8-10e79324acfa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23689,7 +23689,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{263c36a2-3fea-4e38-add9-1e2dfeaa07b3}">
+          <x14:cfRule type="dataBar" id="{55f77087-de2f-4e8a-88b1-882bc32fffab}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23702,7 +23702,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af32807a-c742-447e-bf9a-4cd63e5dc0d2}">
+          <x14:cfRule type="dataBar" id="{0068d450-c605-40ba-9339-f50ac51a9618}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23715,7 +23715,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71fc9a15-f23e-49fc-8dd8-0dcefc3fd3fe}">
+          <x14:cfRule type="dataBar" id="{fac5eb48-5db7-4701-97ea-1479a0116814}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23728,7 +23728,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2220b0d5-3b2c-44a6-8be5-cd08faeb8ad7}">
+          <x14:cfRule type="dataBar" id="{d13997e6-87bf-493b-bebc-5da74afe0b4a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34292,7 +34292,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03baf36e-e182-4ca3-9ebf-6e3f3c6528be}</x14:id>
+          <x14:id>{2cf451f7-2db4-4d50-b076-22f142702417}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34306,7 +34306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f3fa8824-82b1-4152-92ae-bcef9f074c04}</x14:id>
+          <x14:id>{933fcbd3-a72c-4454-be1d-a440a2d73431}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34320,7 +34320,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7102597a-9b43-45ef-b732-8cf830424a8d}</x14:id>
+          <x14:id>{773255a1-e747-4633-8486-98a3981228fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34334,7 +34334,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d2e4132-c8b4-4d68-9629-0e5e1da2dc82}</x14:id>
+          <x14:id>{94589fc5-982c-4543-91a0-84e3dbc07811}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34348,7 +34348,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8149353b-a9ef-41f0-9a28-62aa62cf1505}</x14:id>
+          <x14:id>{2552086b-25ab-4b07-8729-b046498c2da6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34362,7 +34362,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d299e30-5c84-450a-b201-a2a88fedd2c5}</x14:id>
+          <x14:id>{a57bc5a1-046d-4cd8-8385-adc17dde9b05}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34382,7 +34382,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a33ee047-a273-425f-9496-45d73d3af920}</x14:id>
+          <x14:id>{275b8704-45e9-4456-b24e-3662f480cb87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34396,7 +34396,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57ed2890-5cc1-4c8e-adcd-40e52c0bb0ec}</x14:id>
+          <x14:id>{d0e7a319-05d7-4b2b-a3a8-b52eecfb80a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34410,7 +34410,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf44b3bf-908e-439b-b1f0-a1bb2bb51cbc}</x14:id>
+          <x14:id>{fed74bf4-0f19-4cf8-9c5a-297adaa90373}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34424,7 +34424,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e760845f-acc4-4a43-99b1-1c4971ff4a24}</x14:id>
+          <x14:id>{6ed394a7-9c6a-40d5-bc0a-4f86ab0690f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34438,7 +34438,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{add1bc7e-5b4b-4564-bc61-2208d1254bc9}</x14:id>
+          <x14:id>{41dd1893-1901-4ede-a2a4-a5f5811c40bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34452,7 +34452,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5cc3e562-de99-4c7e-b9db-3273ad72bb02}</x14:id>
+          <x14:id>{52f14bec-95a0-4ce3-bfd9-944bddd4a3f4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34474,7 +34474,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6c0d86d6-6814-4edd-a2b9-82bab7eab5f3}</x14:id>
+          <x14:id>{0d629bb9-dec5-4604-92d5-2a7e08503790}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34504,7 +34504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a8ce639d-2931-43da-bcde-a8d940f8ab4d}</x14:id>
+          <x14:id>{35b4cace-b6ab-4a35-b36b-c32b4fd979b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34534,7 +34534,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d05fb45-3199-4daf-8b4e-1240f80969dd}</x14:id>
+          <x14:id>{de989245-0974-4817-9dea-8be79c4acbac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34564,7 +34564,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18584d9e-0407-43ec-bd7f-a2765d62db6b}</x14:id>
+          <x14:id>{8ed89cc0-c790-46be-9468-a862e9983f45}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34594,7 +34594,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d2d0b61-cc9c-4929-bc47-488647a6f4e8}</x14:id>
+          <x14:id>{885e1af7-5a18-4036-b6b3-799ccb47eab7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34624,7 +34624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae348601-f1a4-4654-81da-0dd144f20970}</x14:id>
+          <x14:id>{d925aec4-c75b-4967-967c-7deda0369f92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34646,7 +34646,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a5d9063-970d-40f8-9a5b-8dce61e420ba}</x14:id>
+          <x14:id>{65a47e18-5c93-4596-8422-7212dda98c4f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34668,7 +34668,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a1b6ed4-0bcb-4826-bef2-4a50b3ce7cb8}</x14:id>
+          <x14:id>{b4cee69c-0960-45db-9ce1-c938703ae7fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34690,7 +34690,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{68a73315-c52b-4027-8434-26ec0f4539b8}</x14:id>
+          <x14:id>{13b63f48-83cd-4150-a8d5-061fb2136ce2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34712,7 +34712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{43ff6a34-c8ea-44dc-b119-a2e51d74fd5d}</x14:id>
+          <x14:id>{0830ca3b-e91e-4712-a764-ac856bb35305}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34734,7 +34734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3e72b620-e767-48fd-843b-7ac389cdd44b}</x14:id>
+          <x14:id>{ce7eb6a6-9a2d-4ea0-b795-001f7b66c442}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34756,7 +34756,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee05b2f4-5562-44dc-b894-67b5eac6aebb}</x14:id>
+          <x14:id>{58917a2e-9388-4297-8e9b-bfb7ca26405e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34778,7 +34778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b200a3ce-9a76-449c-9f92-05c379ff9eb3}</x14:id>
+          <x14:id>{5eeed15d-bb98-4b7e-9ebe-23b4ca077c50}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34800,7 +34800,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5689f34a-62f5-4806-b887-de98b74eda09}</x14:id>
+          <x14:id>{5242aec1-0e9f-4244-a305-a9bb86dbc0ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34822,7 +34822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a1d0bd3-2665-430d-8b13-de593b937879}</x14:id>
+          <x14:id>{e99480d6-4faa-4683-bb7e-4712ddca0498}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34844,7 +34844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7a88deb-3c85-4d90-ad9a-d919de80ae03}</x14:id>
+          <x14:id>{c32be782-b4a5-4855-a4a0-f1ff8a7e6a87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34866,7 +34866,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f4f4690-d632-453d-892d-2e9a28b02662}</x14:id>
+          <x14:id>{cee179d5-bc18-4d5f-b88c-041aa863abe6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34888,7 +34888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ce3d236-06f2-4de6-b804-b5de045f3afd}</x14:id>
+          <x14:id>{152f3476-9410-4e76-a623-f471da208116}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34910,7 +34910,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2984445-06ed-49b6-9305-0eccf177fc71}</x14:id>
+          <x14:id>{121e8c13-d131-4c20-b088-b4c2a47513c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34932,7 +34932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5bd62270-d6d3-4834-9d9a-afc22a252ef7}</x14:id>
+          <x14:id>{48f3ac86-f30c-469c-97d7-0f6c5fe17f9f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34951,7 +34951,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{03baf36e-e182-4ca3-9ebf-6e3f3c6528be}">
+          <x14:cfRule type="dataBar" id="{2cf451f7-2db4-4d50-b076-22f142702417}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34964,7 +34964,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f3fa8824-82b1-4152-92ae-bcef9f074c04}">
+          <x14:cfRule type="dataBar" id="{933fcbd3-a72c-4454-be1d-a440a2d73431}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34977,7 +34977,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7102597a-9b43-45ef-b732-8cf830424a8d}">
+          <x14:cfRule type="dataBar" id="{773255a1-e747-4633-8486-98a3981228fa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34990,7 +34990,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4d2e4132-c8b4-4d68-9629-0e5e1da2dc82}">
+          <x14:cfRule type="dataBar" id="{94589fc5-982c-4543-91a0-84e3dbc07811}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35003,7 +35003,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8149353b-a9ef-41f0-9a28-62aa62cf1505}">
+          <x14:cfRule type="dataBar" id="{2552086b-25ab-4b07-8729-b046498c2da6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35016,7 +35016,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d299e30-5c84-450a-b201-a2a88fedd2c5}">
+          <x14:cfRule type="dataBar" id="{a57bc5a1-046d-4cd8-8385-adc17dde9b05}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35029,7 +35029,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a33ee047-a273-425f-9496-45d73d3af920}">
+          <x14:cfRule type="dataBar" id="{275b8704-45e9-4456-b24e-3662f480cb87}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35042,7 +35042,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{57ed2890-5cc1-4c8e-adcd-40e52c0bb0ec}">
+          <x14:cfRule type="dataBar" id="{d0e7a319-05d7-4b2b-a3a8-b52eecfb80a3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35055,7 +35055,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf44b3bf-908e-439b-b1f0-a1bb2bb51cbc}">
+          <x14:cfRule type="dataBar" id="{fed74bf4-0f19-4cf8-9c5a-297adaa90373}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35068,7 +35068,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e760845f-acc4-4a43-99b1-1c4971ff4a24}">
+          <x14:cfRule type="dataBar" id="{6ed394a7-9c6a-40d5-bc0a-4f86ab0690f0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35081,7 +35081,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{add1bc7e-5b4b-4564-bc61-2208d1254bc9}">
+          <x14:cfRule type="dataBar" id="{41dd1893-1901-4ede-a2a4-a5f5811c40bc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35094,7 +35094,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5cc3e562-de99-4c7e-b9db-3273ad72bb02}">
+          <x14:cfRule type="dataBar" id="{52f14bec-95a0-4ce3-bfd9-944bddd4a3f4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35107,7 +35107,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6c0d86d6-6814-4edd-a2b9-82bab7eab5f3}">
+          <x14:cfRule type="dataBar" id="{0d629bb9-dec5-4604-92d5-2a7e08503790}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35120,7 +35120,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a8ce639d-2931-43da-bcde-a8d940f8ab4d}">
+          <x14:cfRule type="dataBar" id="{35b4cace-b6ab-4a35-b36b-c32b4fd979b5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35133,7 +35133,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d05fb45-3199-4daf-8b4e-1240f80969dd}">
+          <x14:cfRule type="dataBar" id="{de989245-0974-4817-9dea-8be79c4acbac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35146,7 +35146,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18584d9e-0407-43ec-bd7f-a2765d62db6b}">
+          <x14:cfRule type="dataBar" id="{8ed89cc0-c790-46be-9468-a862e9983f45}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35159,7 +35159,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d2d0b61-cc9c-4929-bc47-488647a6f4e8}">
+          <x14:cfRule type="dataBar" id="{885e1af7-5a18-4036-b6b3-799ccb47eab7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35172,7 +35172,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ae348601-f1a4-4654-81da-0dd144f20970}">
+          <x14:cfRule type="dataBar" id="{d925aec4-c75b-4967-967c-7deda0369f92}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35185,7 +35185,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0a5d9063-970d-40f8-9a5b-8dce61e420ba}">
+          <x14:cfRule type="dataBar" id="{65a47e18-5c93-4596-8422-7212dda98c4f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35198,7 +35198,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a1b6ed4-0bcb-4826-bef2-4a50b3ce7cb8}">
+          <x14:cfRule type="dataBar" id="{b4cee69c-0960-45db-9ce1-c938703ae7fa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35211,7 +35211,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{68a73315-c52b-4027-8434-26ec0f4539b8}">
+          <x14:cfRule type="dataBar" id="{13b63f48-83cd-4150-a8d5-061fb2136ce2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35224,7 +35224,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{43ff6a34-c8ea-44dc-b119-a2e51d74fd5d}">
+          <x14:cfRule type="dataBar" id="{0830ca3b-e91e-4712-a764-ac856bb35305}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35237,7 +35237,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3e72b620-e767-48fd-843b-7ac389cdd44b}">
+          <x14:cfRule type="dataBar" id="{ce7eb6a6-9a2d-4ea0-b795-001f7b66c442}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35250,7 +35250,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee05b2f4-5562-44dc-b894-67b5eac6aebb}">
+          <x14:cfRule type="dataBar" id="{58917a2e-9388-4297-8e9b-bfb7ca26405e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35263,7 +35263,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b200a3ce-9a76-449c-9f92-05c379ff9eb3}">
+          <x14:cfRule type="dataBar" id="{5eeed15d-bb98-4b7e-9ebe-23b4ca077c50}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35276,7 +35276,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5689f34a-62f5-4806-b887-de98b74eda09}">
+          <x14:cfRule type="dataBar" id="{5242aec1-0e9f-4244-a305-a9bb86dbc0ec}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35289,7 +35289,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7a1d0bd3-2665-430d-8b13-de593b937879}">
+          <x14:cfRule type="dataBar" id="{e99480d6-4faa-4683-bb7e-4712ddca0498}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35302,7 +35302,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a7a88deb-3c85-4d90-ad9a-d919de80ae03}">
+          <x14:cfRule type="dataBar" id="{c32be782-b4a5-4855-a4a0-f1ff8a7e6a87}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35315,7 +35315,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7f4f4690-d632-453d-892d-2e9a28b02662}">
+          <x14:cfRule type="dataBar" id="{cee179d5-bc18-4d5f-b88c-041aa863abe6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35328,7 +35328,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ce3d236-06f2-4de6-b804-b5de045f3afd}">
+          <x14:cfRule type="dataBar" id="{152f3476-9410-4e76-a623-f471da208116}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35341,7 +35341,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b2984445-06ed-49b6-9305-0eccf177fc71}">
+          <x14:cfRule type="dataBar" id="{121e8c13-d131-4c20-b088-b4c2a47513c6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35354,7 +35354,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5bd62270-d6d3-4834-9d9a-afc22a252ef7}">
+          <x14:cfRule type="dataBar" id="{48f3ac86-f30c-469c-97d7-0f6c5fe17f9f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -39278,7 +39278,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>176795.52</v>
+        <v>188699.09</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -39309,7 +39309,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.690843422044038</v>
+        <v>0.737357626891201</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -39410,7 +39410,7 @@
       </c>
       <c r="G7" s="36">
         <f>毛立新!G62</f>
-        <v>21813.42</v>
+        <v>33716.99</v>
       </c>
       <c r="H7" s="36">
         <f>毛立新!H62</f>
@@ -39442,7 +39442,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>450514.82</v>
+        <v>462418.39</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -39468,7 +39468,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.26139586006367</v>
+        <v>0.404039421594971</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -39500,7 +39500,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.392628053890527</v>
+        <v>0.403002131092803</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -39601,7 +39601,7 @@
       </c>
       <c r="G11" s="20">
         <f>毛立新!G63</f>
-        <v>2049</v>
+        <v>4045</v>
       </c>
       <c r="H11" s="20">
         <f>毛立新!H63</f>
@@ -39633,7 +39633,7 @@
       </c>
       <c r="O11" s="20">
         <f t="shared" si="1"/>
-        <v>32296</v>
+        <v>34292</v>
       </c>
     </row>
     <row r="12" ht="15.6" spans="1:15">
@@ -39659,7 +39659,7 @@
       </c>
       <c r="G12" s="15">
         <f t="shared" si="2"/>
-        <v>0.3415</v>
+        <v>0.674166666666667</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="2"/>
@@ -39691,7 +39691,7 @@
       </c>
       <c r="O12" s="15">
         <f t="shared" si="2"/>
-        <v>0.391466666666667</v>
+        <v>0.415660606060606</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:15">
@@ -39792,7 +39792,7 @@
       </c>
       <c r="G15" s="20">
         <f>毛立新!G64</f>
-        <v>436</v>
+        <v>887</v>
       </c>
       <c r="H15" s="20">
         <f>毛立新!H64</f>
@@ -39824,7 +39824,7 @@
       </c>
       <c r="O15" s="20">
         <f t="shared" si="1"/>
-        <v>7236</v>
+        <v>7687</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:15">
@@ -39850,7 +39850,7 @@
       </c>
       <c r="G16" s="15">
         <f t="shared" si="3"/>
-        <v>0.277332420403971</v>
+        <v>0.564206093803491</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="3"/>
@@ -39882,7 +39882,7 @@
       </c>
       <c r="O16" s="15">
         <f t="shared" si="3"/>
-        <v>0.334741850549314</v>
+        <v>0.355605390432915</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:15">
@@ -39983,7 +39983,7 @@
       </c>
       <c r="G19" s="23">
         <f>毛立新!G65</f>
-        <v>8949598</v>
+        <v>18377548</v>
       </c>
       <c r="H19" s="23">
         <f>毛立新!H65</f>
@@ -40015,7 +40015,7 @@
       </c>
       <c r="O19" s="23">
         <f>SUM(C19:N19)</f>
-        <v>163632561</v>
+        <v>173060511</v>
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:15">
@@ -40041,7 +40041,7 @@
       </c>
       <c r="G20" s="15">
         <f t="shared" si="4"/>
-        <v>0.342243687067646</v>
+        <v>0.702780145743154</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="4"/>
@@ -40073,7 +40073,7 @@
       </c>
       <c r="O20" s="15">
         <f t="shared" si="4"/>
-        <v>0.455091734041819</v>
+        <v>0.481312567400038</v>
       </c>
     </row>
     <row r="21" ht="15.6" spans="1:15">
@@ -40174,7 +40174,7 @@
       </c>
       <c r="G23" s="25">
         <f>毛立新!G66</f>
-        <v>198122.02</v>
+        <v>401111.57</v>
       </c>
       <c r="H23" s="25">
         <f>毛立新!H66</f>
@@ -40206,7 +40206,7 @@
       </c>
       <c r="O23" s="36">
         <f>SUM(C23:N23)</f>
-        <v>3115573.65</v>
+        <v>3318563.2</v>
       </c>
     </row>
     <row r="24" ht="15.6" spans="1:15">
@@ -40232,7 +40232,7 @@
       </c>
       <c r="G24" s="15">
         <f t="shared" si="6"/>
-        <v>0.29595433108983</v>
+        <v>0.5991797700818</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="6"/>
@@ -40264,7 +40264,7 @@
       </c>
       <c r="O24" s="15">
         <f t="shared" si="6"/>
-        <v>0.338475529757544</v>
+        <v>0.360528288956959</v>
       </c>
     </row>
     <row r="25" ht="15.6" spans="1:15">
@@ -40307,7 +40307,7 @@
       </c>
       <c r="G26" s="15">
         <f t="shared" si="7"/>
-        <v>0.723280838982935</v>
+        <v>0.727172818430402</v>
       </c>
       <c r="H26" s="15" t="e">
         <f t="shared" si="7"/>
@@ -40339,7 +40339,7 @@
       </c>
       <c r="O26" s="15">
         <f t="shared" si="7"/>
-        <v>0.761999259884468</v>
+        <v>0.760303261788011</v>
       </c>
     </row>
     <row r="27" ht="15.6" spans="1:15">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="G27" s="15">
         <f t="shared" si="8"/>
-        <v>0.78721327476818</v>
+        <v>0.780716934487021</v>
       </c>
       <c r="H27" s="15" t="e">
         <f t="shared" si="8"/>
@@ -40397,7 +40397,7 @@
       </c>
       <c r="O27" s="15">
         <f t="shared" si="8"/>
-        <v>0.77594748575675</v>
+        <v>0.775836929896186</v>
       </c>
     </row>
     <row r="28" ht="15.6" spans="1:15">
@@ -40423,7 +40423,7 @@
       </c>
       <c r="G28" s="15">
         <f t="shared" si="9"/>
-        <v>0.11010093678633</v>
+        <v>0.0840588816722489</v>
       </c>
       <c r="H28" s="15" t="e">
         <f t="shared" si="9"/>
@@ -40455,7 +40455,7 @@
       </c>
       <c r="O28" s="15">
         <f t="shared" si="9"/>
-        <v>0.144600921246076</v>
+        <v>0.139342951190443</v>
       </c>
     </row>
     <row r="29" ht="15.6" spans="1:15">
@@ -40503,7 +40503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ffa4e67-df53-4192-a72f-2280d729eb85}</x14:id>
+          <x14:id>{7e2b52ac-d943-429e-ab16-9f1559bc7ac4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40514,7 +40514,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ffa4e67-df53-4192-a72f-2280d729eb85}">
+          <x14:cfRule type="dataBar" id="{7e2b52ac-d943-429e-ab16-9f1559bc7ac4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -22629,7 +22629,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53274e36-5cb1-486f-9c51-6a238bb572b5}</x14:id>
+          <x14:id>{0d484c65-8101-46e3-9cab-592cdca2097c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22643,7 +22643,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f95c0ff-3ff0-4952-9b13-eb2240d96e2f}</x14:id>
+          <x14:id>{bc43b08f-aae5-4cb4-a995-0ee248139003}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22657,7 +22657,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{08685781-db06-4bd7-9629-51c72f8ccb45}</x14:id>
+          <x14:id>{5e37f353-f467-4de3-b0c6-3ce6ac5a0044}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22671,7 +22671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38017cf9-797a-4e03-b1a1-8a3b71cdc2ff}</x14:id>
+          <x14:id>{606f8dfa-5e01-4ddf-b88c-53f8178214f7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22685,7 +22685,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec96260b-b351-439f-87ca-a82c5a36a78e}</x14:id>
+          <x14:id>{0e6757d6-1645-43ec-9dbe-0de3fde7eadb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22699,7 +22699,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1d3de1db-0fb8-4cad-844a-92ecfcb568f0}</x14:id>
+          <x14:id>{9d09f23f-fe54-461c-a06d-346929ae27b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22713,7 +22713,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fd8bedd3-dd6c-4f66-a678-2f55e9b76739}</x14:id>
+          <x14:id>{c72fb5a8-d14b-45c2-88ae-28fb2224dabd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22727,7 +22727,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9148fd7c-b9da-43d0-97d0-a70bc81e9684}</x14:id>
+          <x14:id>{cdd2d606-6e0e-47c9-b7bb-e403ca5c41be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22741,7 +22741,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{df7070b4-b6c8-4033-b1f3-04bb7ba99d38}</x14:id>
+          <x14:id>{87505910-c941-4ef8-af14-eeaaa25d972d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22755,7 +22755,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ddae40d-8aff-4ee4-af4e-9b2665d230bd}</x14:id>
+          <x14:id>{c2cceb36-aed9-41bd-826a-de6f5eafef87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22769,7 +22769,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1bf7153e-2e55-4a68-977d-4585546e5d9f}</x14:id>
+          <x14:id>{6b9598b1-da8f-4bfc-ae17-ef8090072a8e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22783,7 +22783,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e485598a-291b-4c5e-9229-67406c227950}</x14:id>
+          <x14:id>{614ae890-a144-4c77-b75d-67b185aea7a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22797,7 +22797,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b298eb82-8571-41ac-8f19-bb87ee7cf69a}</x14:id>
+          <x14:id>{993b9a7d-02a7-409b-a322-25a34db81e8f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22819,7 +22819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{233e0a11-b587-46db-994f-336323aac803}</x14:id>
+          <x14:id>{6f17514d-4efe-458e-acba-cf5cfac3c8d9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22849,7 +22849,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26fb4a24-43c1-4b4c-89f7-b877a3ba10ee}</x14:id>
+          <x14:id>{8a854c91-83e8-460f-99ed-98a7108b5c58}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22879,7 +22879,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d8f7f6e-64e6-4cd4-9c92-f480ed67faa4}</x14:id>
+          <x14:id>{df00900a-3bf6-4ef5-80f1-c03cc2197ee4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22909,7 +22909,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd861fd3-88ae-48ca-87cb-8366ba174dbb}</x14:id>
+          <x14:id>{928673f0-9ff0-4110-a81b-87de4d8715f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22939,7 +22939,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70c99161-322d-414b-8c3f-d4d771712a0b}</x14:id>
+          <x14:id>{5451c986-d455-4d55-ac51-c17376a5173b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22969,7 +22969,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23f91689-935a-4a0b-9d23-97fa2908b13a}</x14:id>
+          <x14:id>{cacfea30-feca-498b-8476-3242a42572da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22999,7 +22999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d613d811-9901-45a9-886a-10fee96c1049}</x14:id>
+          <x14:id>{13c2e93d-44f7-4c88-9136-4aa01b4d5629}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23029,7 +23029,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1fe9be13-7d27-44a0-a746-31ca1d246259}</x14:id>
+          <x14:id>{fe1377a1-5f4d-4237-8dac-979f468bb639}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23051,7 +23051,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e2a6be7-c252-4147-8568-f659e1a85b81}</x14:id>
+          <x14:id>{d29c5a5c-b708-42b6-ad27-1c29700c6e04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23073,7 +23073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c7c37f4-b154-4d81-9853-209e844fefbd}</x14:id>
+          <x14:id>{e6b5fe06-6fba-4ac8-8fe5-156c97a9365c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23095,7 +23095,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f386d68-dda1-479f-a2d0-2d646577485d}</x14:id>
+          <x14:id>{27e9dd39-89a9-4875-9995-82e941b140f3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23117,7 +23117,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cc9f0f80-89ca-439d-9ced-637c8de60ddd}</x14:id>
+          <x14:id>{bd331c9e-05bc-4a7f-af0d-e9e62c60a991}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23139,7 +23139,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9a83834-b977-46b2-b196-b2429f6397df}</x14:id>
+          <x14:id>{4308deae-a5ac-4053-b25a-495881be62fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23161,7 +23161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d3ef4b3-f0a2-4894-8295-c550a1813217}</x14:id>
+          <x14:id>{57c37003-c8d4-4cfe-af6f-41587f446a85}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23183,7 +23183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd7602ea-93f3-44db-8277-a29bf3ebfc1c}</x14:id>
+          <x14:id>{e1e33c71-eb07-40ea-be27-30281fbbadab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23205,7 +23205,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78668496-bdd7-4435-97c8-10e79324acfa}</x14:id>
+          <x14:id>{84d383b8-5092-4e89-83f1-bdcbf185f7a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23227,7 +23227,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55f77087-de2f-4e8a-88b1-882bc32fffab}</x14:id>
+          <x14:id>{a6e5b16b-5863-4351-b3e0-46ab2f819fe2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23249,7 +23249,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0068d450-c605-40ba-9339-f50ac51a9618}</x14:id>
+          <x14:id>{20325cb1-3489-4186-9897-7d5eab339486}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23271,7 +23271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fac5eb48-5db7-4701-97ea-1479a0116814}</x14:id>
+          <x14:id>{f8c04c54-9f17-4baa-bba2-b3b514b51952}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23293,7 +23293,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d13997e6-87bf-493b-bebc-5da74afe0b4a}</x14:id>
+          <x14:id>{b996e842-f8d2-4773-9a41-80ebfa91aa1c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23312,7 +23312,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{53274e36-5cb1-486f-9c51-6a238bb572b5}">
+          <x14:cfRule type="dataBar" id="{0d484c65-8101-46e3-9cab-592cdca2097c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23325,7 +23325,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8f95c0ff-3ff0-4952-9b13-eb2240d96e2f}">
+          <x14:cfRule type="dataBar" id="{bc43b08f-aae5-4cb4-a995-0ee248139003}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23338,7 +23338,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{08685781-db06-4bd7-9629-51c72f8ccb45}">
+          <x14:cfRule type="dataBar" id="{5e37f353-f467-4de3-b0c6-3ce6ac5a0044}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23351,7 +23351,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38017cf9-797a-4e03-b1a1-8a3b71cdc2ff}">
+          <x14:cfRule type="dataBar" id="{606f8dfa-5e01-4ddf-b88c-53f8178214f7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23364,7 +23364,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec96260b-b351-439f-87ca-a82c5a36a78e}">
+          <x14:cfRule type="dataBar" id="{0e6757d6-1645-43ec-9dbe-0de3fde7eadb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23377,7 +23377,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1d3de1db-0fb8-4cad-844a-92ecfcb568f0}">
+          <x14:cfRule type="dataBar" id="{9d09f23f-fe54-461c-a06d-346929ae27b5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23390,7 +23390,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fd8bedd3-dd6c-4f66-a678-2f55e9b76739}">
+          <x14:cfRule type="dataBar" id="{c72fb5a8-d14b-45c2-88ae-28fb2224dabd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23403,7 +23403,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9148fd7c-b9da-43d0-97d0-a70bc81e9684}">
+          <x14:cfRule type="dataBar" id="{cdd2d606-6e0e-47c9-b7bb-e403ca5c41be}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23416,7 +23416,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{df7070b4-b6c8-4033-b1f3-04bb7ba99d38}">
+          <x14:cfRule type="dataBar" id="{87505910-c941-4ef8-af14-eeaaa25d972d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23429,7 +23429,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9ddae40d-8aff-4ee4-af4e-9b2665d230bd}">
+          <x14:cfRule type="dataBar" id="{c2cceb36-aed9-41bd-826a-de6f5eafef87}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23442,7 +23442,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1bf7153e-2e55-4a68-977d-4585546e5d9f}">
+          <x14:cfRule type="dataBar" id="{6b9598b1-da8f-4bfc-ae17-ef8090072a8e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23455,7 +23455,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e485598a-291b-4c5e-9229-67406c227950}">
+          <x14:cfRule type="dataBar" id="{614ae890-a144-4c77-b75d-67b185aea7a1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23468,7 +23468,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b298eb82-8571-41ac-8f19-bb87ee7cf69a}">
+          <x14:cfRule type="dataBar" id="{993b9a7d-02a7-409b-a322-25a34db81e8f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23481,7 +23481,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{233e0a11-b587-46db-994f-336323aac803}">
+          <x14:cfRule type="dataBar" id="{6f17514d-4efe-458e-acba-cf5cfac3c8d9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23494,7 +23494,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{26fb4a24-43c1-4b4c-89f7-b877a3ba10ee}">
+          <x14:cfRule type="dataBar" id="{8a854c91-83e8-460f-99ed-98a7108b5c58}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23507,7 +23507,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d8f7f6e-64e6-4cd4-9c92-f480ed67faa4}">
+          <x14:cfRule type="dataBar" id="{df00900a-3bf6-4ef5-80f1-c03cc2197ee4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23520,7 +23520,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd861fd3-88ae-48ca-87cb-8366ba174dbb}">
+          <x14:cfRule type="dataBar" id="{928673f0-9ff0-4110-a81b-87de4d8715f2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23533,7 +23533,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70c99161-322d-414b-8c3f-d4d771712a0b}">
+          <x14:cfRule type="dataBar" id="{5451c986-d455-4d55-ac51-c17376a5173b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23546,7 +23546,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23f91689-935a-4a0b-9d23-97fa2908b13a}">
+          <x14:cfRule type="dataBar" id="{cacfea30-feca-498b-8476-3242a42572da}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23559,7 +23559,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d613d811-9901-45a9-886a-10fee96c1049}">
+          <x14:cfRule type="dataBar" id="{13c2e93d-44f7-4c88-9136-4aa01b4d5629}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23572,7 +23572,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1fe9be13-7d27-44a0-a746-31ca1d246259}">
+          <x14:cfRule type="dataBar" id="{fe1377a1-5f4d-4237-8dac-979f468bb639}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23585,7 +23585,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9e2a6be7-c252-4147-8568-f659e1a85b81}">
+          <x14:cfRule type="dataBar" id="{d29c5a5c-b708-42b6-ad27-1c29700c6e04}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23598,7 +23598,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3c7c37f4-b154-4d81-9853-209e844fefbd}">
+          <x14:cfRule type="dataBar" id="{e6b5fe06-6fba-4ac8-8fe5-156c97a9365c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23611,7 +23611,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0f386d68-dda1-479f-a2d0-2d646577485d}">
+          <x14:cfRule type="dataBar" id="{27e9dd39-89a9-4875-9995-82e941b140f3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23624,7 +23624,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cc9f0f80-89ca-439d-9ced-637c8de60ddd}">
+          <x14:cfRule type="dataBar" id="{bd331c9e-05bc-4a7f-af0d-e9e62c60a991}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23637,7 +23637,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f9a83834-b977-46b2-b196-b2429f6397df}">
+          <x14:cfRule type="dataBar" id="{4308deae-a5ac-4053-b25a-495881be62fb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23650,7 +23650,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d3ef4b3-f0a2-4894-8295-c550a1813217}">
+          <x14:cfRule type="dataBar" id="{57c37003-c8d4-4cfe-af6f-41587f446a85}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23663,7 +23663,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd7602ea-93f3-44db-8277-a29bf3ebfc1c}">
+          <x14:cfRule type="dataBar" id="{e1e33c71-eb07-40ea-be27-30281fbbadab}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23676,7 +23676,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{78668496-bdd7-4435-97c8-10e79324acfa}">
+          <x14:cfRule type="dataBar" id="{84d383b8-5092-4e89-83f1-bdcbf185f7a1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23689,7 +23689,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55f77087-de2f-4e8a-88b1-882bc32fffab}">
+          <x14:cfRule type="dataBar" id="{a6e5b16b-5863-4351-b3e0-46ab2f819fe2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23702,7 +23702,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0068d450-c605-40ba-9339-f50ac51a9618}">
+          <x14:cfRule type="dataBar" id="{20325cb1-3489-4186-9897-7d5eab339486}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23715,7 +23715,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fac5eb48-5db7-4701-97ea-1479a0116814}">
+          <x14:cfRule type="dataBar" id="{f8c04c54-9f17-4baa-bba2-b3b514b51952}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23728,7 +23728,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d13997e6-87bf-493b-bebc-5da74afe0b4a}">
+          <x14:cfRule type="dataBar" id="{b996e842-f8d2-4773-9a41-80ebfa91aa1c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34292,7 +34292,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2cf451f7-2db4-4d50-b076-22f142702417}</x14:id>
+          <x14:id>{bdb6e576-3e14-40b7-9152-c83f4cd7acb6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34306,7 +34306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{933fcbd3-a72c-4454-be1d-a440a2d73431}</x14:id>
+          <x14:id>{fa240528-50d4-4eed-9e2c-d441faa9716d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34320,7 +34320,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{773255a1-e747-4633-8486-98a3981228fa}</x14:id>
+          <x14:id>{6141b4f4-c628-40f4-ab81-b6910c3cbbca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34334,7 +34334,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94589fc5-982c-4543-91a0-84e3dbc07811}</x14:id>
+          <x14:id>{1ef8f99d-8e19-4ee4-ab1c-90d93123a2f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34348,7 +34348,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2552086b-25ab-4b07-8729-b046498c2da6}</x14:id>
+          <x14:id>{37e7c8b6-2c2e-48d9-a79b-07c74bc1cb07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34362,7 +34362,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a57bc5a1-046d-4cd8-8385-adc17dde9b05}</x14:id>
+          <x14:id>{32f7db83-4805-445b-a743-00e58cc4454c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34382,7 +34382,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{275b8704-45e9-4456-b24e-3662f480cb87}</x14:id>
+          <x14:id>{125d7bd3-0e23-42bf-b1d6-900e7ae46bc2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34396,7 +34396,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0e7a319-05d7-4b2b-a3a8-b52eecfb80a3}</x14:id>
+          <x14:id>{b8e4d029-3662-4b98-8a06-1c4d361c89ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34410,7 +34410,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fed74bf4-0f19-4cf8-9c5a-297adaa90373}</x14:id>
+          <x14:id>{98a74125-ad99-4f4d-953e-64943663a308}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34424,7 +34424,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ed394a7-9c6a-40d5-bc0a-4f86ab0690f0}</x14:id>
+          <x14:id>{ac1f99b0-503e-4d35-a8cb-f6ff028e6c68}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34438,7 +34438,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41dd1893-1901-4ede-a2a4-a5f5811c40bc}</x14:id>
+          <x14:id>{125b8881-08d6-4d42-883c-57ed026190be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34452,7 +34452,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52f14bec-95a0-4ce3-bfd9-944bddd4a3f4}</x14:id>
+          <x14:id>{4e46a78c-3086-4600-ac5b-a46ef468d01f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34474,7 +34474,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d629bb9-dec5-4604-92d5-2a7e08503790}</x14:id>
+          <x14:id>{adc663a3-46bb-44ff-9899-bc545571d950}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34504,7 +34504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{35b4cace-b6ab-4a35-b36b-c32b4fd979b5}</x14:id>
+          <x14:id>{a812cf56-27eb-4675-8804-3dc88ba54ea6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34534,7 +34534,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{de989245-0974-4817-9dea-8be79c4acbac}</x14:id>
+          <x14:id>{6e7ee328-44bb-43e6-aa46-94fcf3d72a1c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34564,7 +34564,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ed89cc0-c790-46be-9468-a862e9983f45}</x14:id>
+          <x14:id>{4a91a165-4601-48cc-bb71-d9ade802400b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34594,7 +34594,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{885e1af7-5a18-4036-b6b3-799ccb47eab7}</x14:id>
+          <x14:id>{fd113e4b-3b32-477c-8d35-3744895c832e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34624,7 +34624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d925aec4-c75b-4967-967c-7deda0369f92}</x14:id>
+          <x14:id>{05e8d6c1-d1d5-4762-bc81-807afdc0eacf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34646,7 +34646,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65a47e18-5c93-4596-8422-7212dda98c4f}</x14:id>
+          <x14:id>{467fe571-8a51-4070-9b72-9cf1d3d6d6d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34668,7 +34668,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4cee69c-0960-45db-9ce1-c938703ae7fa}</x14:id>
+          <x14:id>{e76a069d-5dc6-4527-aca7-b18910e7a85f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34690,7 +34690,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13b63f48-83cd-4150-a8d5-061fb2136ce2}</x14:id>
+          <x14:id>{ae73ba54-ad44-4b65-b42a-282fb355a8c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34712,7 +34712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0830ca3b-e91e-4712-a764-ac856bb35305}</x14:id>
+          <x14:id>{71928f70-6fe6-488a-9312-1d9e85233333}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34734,7 +34734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce7eb6a6-9a2d-4ea0-b795-001f7b66c442}</x14:id>
+          <x14:id>{ba18497a-6216-4246-8218-687f0f98ee36}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34756,7 +34756,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{58917a2e-9388-4297-8e9b-bfb7ca26405e}</x14:id>
+          <x14:id>{6d87238d-a375-4e33-8626-03d686193683}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34778,7 +34778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5eeed15d-bb98-4b7e-9ebe-23b4ca077c50}</x14:id>
+          <x14:id>{2ee22c21-d97e-42c1-966d-51e58e418098}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34800,7 +34800,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5242aec1-0e9f-4244-a305-a9bb86dbc0ec}</x14:id>
+          <x14:id>{74af01eb-e29b-4a92-bbfa-934f137405bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34822,7 +34822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e99480d6-4faa-4683-bb7e-4712ddca0498}</x14:id>
+          <x14:id>{4f40472f-1b14-45bb-836d-cb20e10b130d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34844,7 +34844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c32be782-b4a5-4855-a4a0-f1ff8a7e6a87}</x14:id>
+          <x14:id>{b1c96755-b566-451e-9f37-2e45aeee1b51}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34866,7 +34866,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cee179d5-bc18-4d5f-b88c-041aa863abe6}</x14:id>
+          <x14:id>{5493a66b-ee68-4f1a-a24b-4889bac05a91}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34888,7 +34888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{152f3476-9410-4e76-a623-f471da208116}</x14:id>
+          <x14:id>{2d520bbe-b530-433e-8604-bab0a035168b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34910,7 +34910,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{121e8c13-d131-4c20-b088-b4c2a47513c6}</x14:id>
+          <x14:id>{bf1ddc36-c6fa-4cdf-ae2c-21b20ca6103f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34932,7 +34932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{48f3ac86-f30c-469c-97d7-0f6c5fe17f9f}</x14:id>
+          <x14:id>{52d36c07-4a4e-447d-be7c-b37725a61d59}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34951,7 +34951,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2cf451f7-2db4-4d50-b076-22f142702417}">
+          <x14:cfRule type="dataBar" id="{bdb6e576-3e14-40b7-9152-c83f4cd7acb6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34964,7 +34964,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{933fcbd3-a72c-4454-be1d-a440a2d73431}">
+          <x14:cfRule type="dataBar" id="{fa240528-50d4-4eed-9e2c-d441faa9716d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34977,7 +34977,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{773255a1-e747-4633-8486-98a3981228fa}">
+          <x14:cfRule type="dataBar" id="{6141b4f4-c628-40f4-ab81-b6910c3cbbca}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34990,7 +34990,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94589fc5-982c-4543-91a0-84e3dbc07811}">
+          <x14:cfRule type="dataBar" id="{1ef8f99d-8e19-4ee4-ab1c-90d93123a2f5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35003,7 +35003,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2552086b-25ab-4b07-8729-b046498c2da6}">
+          <x14:cfRule type="dataBar" id="{37e7c8b6-2c2e-48d9-a79b-07c74bc1cb07}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35016,7 +35016,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a57bc5a1-046d-4cd8-8385-adc17dde9b05}">
+          <x14:cfRule type="dataBar" id="{32f7db83-4805-445b-a743-00e58cc4454c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35029,7 +35029,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{275b8704-45e9-4456-b24e-3662f480cb87}">
+          <x14:cfRule type="dataBar" id="{125d7bd3-0e23-42bf-b1d6-900e7ae46bc2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35042,7 +35042,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d0e7a319-05d7-4b2b-a3a8-b52eecfb80a3}">
+          <x14:cfRule type="dataBar" id="{b8e4d029-3662-4b98-8a06-1c4d361c89ce}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35055,7 +35055,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fed74bf4-0f19-4cf8-9c5a-297adaa90373}">
+          <x14:cfRule type="dataBar" id="{98a74125-ad99-4f4d-953e-64943663a308}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35068,7 +35068,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ed394a7-9c6a-40d5-bc0a-4f86ab0690f0}">
+          <x14:cfRule type="dataBar" id="{ac1f99b0-503e-4d35-a8cb-f6ff028e6c68}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35081,7 +35081,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41dd1893-1901-4ede-a2a4-a5f5811c40bc}">
+          <x14:cfRule type="dataBar" id="{125b8881-08d6-4d42-883c-57ed026190be}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35094,7 +35094,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52f14bec-95a0-4ce3-bfd9-944bddd4a3f4}">
+          <x14:cfRule type="dataBar" id="{4e46a78c-3086-4600-ac5b-a46ef468d01f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35107,7 +35107,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d629bb9-dec5-4604-92d5-2a7e08503790}">
+          <x14:cfRule type="dataBar" id="{adc663a3-46bb-44ff-9899-bc545571d950}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35120,7 +35120,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{35b4cace-b6ab-4a35-b36b-c32b4fd979b5}">
+          <x14:cfRule type="dataBar" id="{a812cf56-27eb-4675-8804-3dc88ba54ea6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35133,7 +35133,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{de989245-0974-4817-9dea-8be79c4acbac}">
+          <x14:cfRule type="dataBar" id="{6e7ee328-44bb-43e6-aa46-94fcf3d72a1c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35146,7 +35146,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ed89cc0-c790-46be-9468-a862e9983f45}">
+          <x14:cfRule type="dataBar" id="{4a91a165-4601-48cc-bb71-d9ade802400b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35159,7 +35159,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{885e1af7-5a18-4036-b6b3-799ccb47eab7}">
+          <x14:cfRule type="dataBar" id="{fd113e4b-3b32-477c-8d35-3744895c832e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35172,7 +35172,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d925aec4-c75b-4967-967c-7deda0369f92}">
+          <x14:cfRule type="dataBar" id="{05e8d6c1-d1d5-4762-bc81-807afdc0eacf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35185,7 +35185,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{65a47e18-5c93-4596-8422-7212dda98c4f}">
+          <x14:cfRule type="dataBar" id="{467fe571-8a51-4070-9b72-9cf1d3d6d6d5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35198,7 +35198,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b4cee69c-0960-45db-9ce1-c938703ae7fa}">
+          <x14:cfRule type="dataBar" id="{e76a069d-5dc6-4527-aca7-b18910e7a85f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35211,7 +35211,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{13b63f48-83cd-4150-a8d5-061fb2136ce2}">
+          <x14:cfRule type="dataBar" id="{ae73ba54-ad44-4b65-b42a-282fb355a8c7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35224,7 +35224,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0830ca3b-e91e-4712-a764-ac856bb35305}">
+          <x14:cfRule type="dataBar" id="{71928f70-6fe6-488a-9312-1d9e85233333}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35237,7 +35237,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce7eb6a6-9a2d-4ea0-b795-001f7b66c442}">
+          <x14:cfRule type="dataBar" id="{ba18497a-6216-4246-8218-687f0f98ee36}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35250,7 +35250,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{58917a2e-9388-4297-8e9b-bfb7ca26405e}">
+          <x14:cfRule type="dataBar" id="{6d87238d-a375-4e33-8626-03d686193683}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35263,7 +35263,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5eeed15d-bb98-4b7e-9ebe-23b4ca077c50}">
+          <x14:cfRule type="dataBar" id="{2ee22c21-d97e-42c1-966d-51e58e418098}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35276,7 +35276,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5242aec1-0e9f-4244-a305-a9bb86dbc0ec}">
+          <x14:cfRule type="dataBar" id="{74af01eb-e29b-4a92-bbfa-934f137405bd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35289,7 +35289,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e99480d6-4faa-4683-bb7e-4712ddca0498}">
+          <x14:cfRule type="dataBar" id="{4f40472f-1b14-45bb-836d-cb20e10b130d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35302,7 +35302,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c32be782-b4a5-4855-a4a0-f1ff8a7e6a87}">
+          <x14:cfRule type="dataBar" id="{b1c96755-b566-451e-9f37-2e45aeee1b51}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35315,7 +35315,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cee179d5-bc18-4d5f-b88c-041aa863abe6}">
+          <x14:cfRule type="dataBar" id="{5493a66b-ee68-4f1a-a24b-4889bac05a91}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35328,7 +35328,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{152f3476-9410-4e76-a623-f471da208116}">
+          <x14:cfRule type="dataBar" id="{2d520bbe-b530-433e-8604-bab0a035168b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35341,7 +35341,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{121e8c13-d131-4c20-b088-b4c2a47513c6}">
+          <x14:cfRule type="dataBar" id="{bf1ddc36-c6fa-4cdf-ae2c-21b20ca6103f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35354,7 +35354,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{48f3ac86-f30c-469c-97d7-0f6c5fe17f9f}">
+          <x14:cfRule type="dataBar" id="{52d36c07-4a4e-447d-be7c-b37725a61d59}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -40503,7 +40503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e2b52ac-d943-429e-ab16-9f1559bc7ac4}</x14:id>
+          <x14:id>{259c1ac8-5c78-48be-aec1-fc95dea6aeb8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40514,7 +40514,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e2b52ac-d943-429e-ab16-9f1559bc7ac4}">
+          <x14:cfRule type="dataBar" id="{259c1ac8-5c78-48be-aec1-fc95dea6aeb8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -7745,7 +7745,7 @@
             <v>706739.4</v>
           </cell>
           <cell r="G7">
-            <v>100167.33</v>
+            <v>273743.76</v>
           </cell>
           <cell r="H7">
             <v>0</v>
@@ -7769,7 +7769,7 @@
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>2618965.2</v>
+            <v>2792541.63</v>
           </cell>
         </row>
         <row r="8">
@@ -7789,7 +7789,7 @@
             <v>1.52310341168606</v>
           </cell>
           <cell r="G8">
-            <v>0.184404202252453</v>
+            <v>0.503951734406688</v>
           </cell>
           <cell r="H8">
             <v>0</v>
@@ -7813,7 +7813,7 @@
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0.299130133051202</v>
+            <v>0.318955497893947</v>
           </cell>
         </row>
         <row r="10">
@@ -7877,7 +7877,7 @@
             <v>33812</v>
           </cell>
           <cell r="G11">
-            <v>5553</v>
+            <v>12697</v>
           </cell>
           <cell r="H11">
             <v>0</v>
@@ -7901,7 +7901,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>134556</v>
+            <v>141700</v>
           </cell>
         </row>
         <row r="12">
@@ -7921,7 +7921,7 @@
             <v>1.05894143438772</v>
           </cell>
           <cell r="G12">
-            <v>0.15425</v>
+            <v>0.352694444444444</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -7945,7 +7945,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.231644837416849</v>
+            <v>0.243943588260408</v>
           </cell>
         </row>
         <row r="14">
@@ -8009,7 +8009,7 @@
             <v>12177</v>
           </cell>
           <cell r="G15">
-            <v>1865</v>
+            <v>4263</v>
           </cell>
           <cell r="H15">
             <v>0</v>
@@ -8033,7 +8033,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>47929</v>
+            <v>50327</v>
           </cell>
         </row>
         <row r="16">
@@ -8053,7 +8053,7 @@
             <v>1.23021124839619</v>
           </cell>
           <cell r="G16">
-            <v>0.167114695340502</v>
+            <v>0.381989247311828</v>
           </cell>
           <cell r="H16">
             <v>0</v>
@@ -8077,7 +8077,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.266168239163456</v>
+            <v>0.279485258869979</v>
           </cell>
         </row>
         <row r="18">
@@ -8141,7 +8141,7 @@
             <v>13661971.3112</v>
           </cell>
           <cell r="G19">
-            <v>2247713.1192</v>
+            <v>5158465.7808</v>
           </cell>
           <cell r="H19">
             <v>0</v>
@@ -8165,7 +8165,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>51620365.6662</v>
+            <v>54531118.3278</v>
           </cell>
         </row>
         <row r="20">
@@ -8185,7 +8185,7 @@
             <v>1.22773777572485</v>
           </cell>
           <cell r="G20">
-            <v>0.179587177948226</v>
+            <v>0.412149710834132</v>
           </cell>
           <cell r="H20">
             <v>0</v>
@@ -8209,7 +8209,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.255930057052861</v>
+            <v>0.270361359216957</v>
           </cell>
         </row>
         <row r="22">
@@ -8273,7 +8273,7 @@
             <v>4382797.99</v>
           </cell>
           <cell r="G23">
-            <v>684372.3</v>
+            <v>1581454.25</v>
           </cell>
           <cell r="H23">
             <v>0</v>
@@ -8297,7 +8297,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>17126902.41</v>
+            <v>18023984.36</v>
           </cell>
         </row>
         <row r="24">
@@ -8317,7 +8317,7 @@
             <v>1.23081767747956</v>
           </cell>
           <cell r="G24">
-            <v>0.170874355824545</v>
+            <v>0.394858144075583</v>
           </cell>
           <cell r="H24">
             <v>0</v>
@@ -8341,7 +8341,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.265356091435546</v>
+            <v>0.279255053095443</v>
           </cell>
         </row>
         <row r="26">
@@ -8361,7 +8361,7 @@
             <v>0.320802751679548</v>
           </cell>
           <cell r="G26">
-            <v>0.304474932389762</v>
+            <v>0.30657453537566</v>
           </cell>
           <cell r="H26" t="e">
             <v>#DIV/0!</v>
@@ -8385,7 +8385,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.331785763021326</v>
+            <v>0.330526585786365</v>
           </cell>
         </row>
         <row r="27">
@@ -8405,7 +8405,7 @@
             <v>0.639861587602035</v>
           </cell>
           <cell r="G27">
-            <v>0.664145506933189</v>
+            <v>0.664251397968024</v>
           </cell>
           <cell r="H27" t="e">
             <v>#DIV/0!</v>
@@ -8429,7 +8429,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.64379886441333</v>
+            <v>0.644834156669019</v>
           </cell>
         </row>
         <row r="28">
@@ -8449,7 +8449,7 @@
             <v>0.161253017276299</v>
           </cell>
           <cell r="G28">
-            <v>0.146363799353071</v>
+            <v>0.173096224566724</v>
           </cell>
           <cell r="H28" t="e">
             <v>#DIV/0!</v>
@@ -8473,7 +8473,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.152915287149114</v>
+            <v>0.154934756612272</v>
           </cell>
         </row>
         <row r="30">
@@ -8496,7 +8496,7 @@
             <v>364348.74</v>
           </cell>
           <cell r="G30">
-            <v>48925.87</v>
+            <v>100586.14</v>
           </cell>
           <cell r="H30">
             <v>0</v>
@@ -8520,7 +8520,7 @@
             <v>0</v>
           </cell>
           <cell r="O30">
-            <v>1607399.29</v>
+            <v>1659059.56</v>
           </cell>
         </row>
         <row r="31">
@@ -8540,7 +8540,7 @@
             <v>17188</v>
           </cell>
           <cell r="G31">
-            <v>2331</v>
+            <v>4873</v>
           </cell>
           <cell r="H31">
             <v>0</v>
@@ -8564,7 +8564,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>68182</v>
+            <v>70724</v>
           </cell>
         </row>
         <row r="32">
@@ -8584,7 +8584,7 @@
             <v>6412</v>
           </cell>
           <cell r="G32">
-            <v>866</v>
+            <v>1719</v>
           </cell>
           <cell r="H32">
             <v>0</v>
@@ -8608,7 +8608,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>25418</v>
+            <v>26271</v>
           </cell>
         </row>
         <row r="33">
@@ -8628,7 +8628,7 @@
             <v>7017450.9096</v>
           </cell>
           <cell r="G33">
-            <v>981973.6656</v>
+            <v>2064206.2944</v>
           </cell>
           <cell r="H33">
             <v>0</v>
@@ -8652,7 +8652,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>27857969.1837</v>
+            <v>28940201.8125</v>
           </cell>
         </row>
         <row r="34">
@@ -8672,7 +8672,7 @@
             <v>2348681.79</v>
           </cell>
           <cell r="G34">
-            <v>332705.62</v>
+            <v>671916.1</v>
           </cell>
           <cell r="H34">
             <v>0</v>
@@ -8696,7 +8696,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>9313993.25</v>
+            <v>9653203.73</v>
           </cell>
         </row>
         <row r="35">
@@ -8716,7 +8716,7 @@
             <v>0.334691588192938</v>
           </cell>
           <cell r="G35">
-            <v>0.338813179675966</v>
+            <v>0.325508211956744</v>
           </cell>
           <cell r="H35" t="e">
             <v>#DIV/0!</v>
@@ -8740,7 +8740,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.334338558154832</v>
+            <v>0.333556890602972</v>
           </cell>
         </row>
         <row r="36">
@@ -8760,7 +8760,7 @@
             <v>0.626949034209914</v>
           </cell>
           <cell r="G36">
-            <v>0.628485628485629</v>
+            <v>0.647239893289555</v>
           </cell>
           <cell r="H36" t="e">
             <v>#DIV/0!</v>
@@ -8784,7 +8784,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.627203660790238</v>
+            <v>0.628541937673209</v>
           </cell>
         </row>
         <row r="37">
@@ -8804,7 +8804,7 @@
             <v>0.155129035168276</v>
           </cell>
           <cell r="G37">
-            <v>0.147054534275676</v>
+            <v>0.149700446231308</v>
           </cell>
           <cell r="H37" t="e">
             <v>#DIV/0!</v>
@@ -8828,7 +8828,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.172578962304917</v>
+            <v>0.171866212130592</v>
           </cell>
         </row>
         <row r="38">
@@ -8851,7 +8851,7 @@
             <v>149415.87</v>
           </cell>
           <cell r="G38">
-            <v>13496.52</v>
+            <v>36247.76</v>
           </cell>
           <cell r="H38">
             <v>0</v>
@@ -8875,7 +8875,7 @@
             <v>0</v>
           </cell>
           <cell r="O38">
-            <v>491062.38</v>
+            <v>513813.62</v>
           </cell>
         </row>
         <row r="39">
@@ -8895,7 +8895,7 @@
             <v>6965</v>
           </cell>
           <cell r="G39">
-            <v>1689</v>
+            <v>3195</v>
           </cell>
           <cell r="H39">
             <v>0</v>
@@ -8919,7 +8919,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>29347</v>
+            <v>30853</v>
           </cell>
         </row>
         <row r="40">
@@ -8939,7 +8939,7 @@
             <v>2459</v>
           </cell>
           <cell r="G40">
-            <v>350</v>
+            <v>797</v>
           </cell>
           <cell r="H40">
             <v>0</v>
@@ -8963,7 +8963,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>9624</v>
+            <v>10071</v>
           </cell>
         </row>
         <row r="41">
@@ -8983,7 +8983,7 @@
             <v>2746120.052</v>
           </cell>
           <cell r="G41">
-            <v>489604.2696</v>
+            <v>1096038.732</v>
           </cell>
           <cell r="H41">
             <v>0</v>
@@ -9007,7 +9007,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>10229813.4906</v>
+            <v>10836247.953</v>
           </cell>
         </row>
         <row r="42">
@@ -9027,7 +9027,7 @@
             <v>861340.47</v>
           </cell>
           <cell r="G42">
-            <v>123275.95</v>
+            <v>288652.65</v>
           </cell>
           <cell r="H42">
             <v>0</v>
@@ -9051,7 +9051,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>3146440.93</v>
+            <v>3311817.63</v>
           </cell>
         </row>
         <row r="43">
@@ -9071,7 +9071,7 @@
             <v>0.313657252301364</v>
           </cell>
           <cell r="G43">
-            <v>0.251786917832058</v>
+            <v>0.263359899219328</v>
           </cell>
           <cell r="H43" t="e">
             <v>#DIV/0!</v>
@@ -9095,7 +9095,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.307575590981322</v>
+            <v>0.305624017128837</v>
           </cell>
         </row>
         <row r="44">
@@ -9115,7 +9115,7 @@
             <v>0.646949030868629</v>
           </cell>
           <cell r="G44">
-            <v>0.792776791000592</v>
+            <v>0.750547730829421</v>
           </cell>
           <cell r="H44" t="e">
             <v>#DIV/0!</v>
@@ -9139,7 +9139,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.672061880260333</v>
+            <v>0.673581175250381</v>
           </cell>
         </row>
         <row r="45">
@@ -9159,7 +9159,7 @@
             <v>0.173469000011111</v>
           </cell>
           <cell r="G45">
-            <v>0.109482182047674</v>
+            <v>0.125575704917312</v>
           </cell>
           <cell r="H45" t="e">
             <v>#DIV/0!</v>
@@ -9183,7 +9183,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.156069155889095</v>
+            <v>0.155145505400308</v>
           </cell>
         </row>
         <row r="46">
@@ -9206,7 +9206,7 @@
             <v>169881.56</v>
           </cell>
           <cell r="G46">
-            <v>36628.56</v>
+            <v>126542.79</v>
           </cell>
           <cell r="H46">
             <v>0</v>
@@ -9230,7 +9230,7 @@
             <v>0</v>
           </cell>
           <cell r="O46">
-            <v>402514.28</v>
+            <v>492428.51</v>
           </cell>
         </row>
         <row r="47">
@@ -9250,7 +9250,7 @@
             <v>7019</v>
           </cell>
           <cell r="G47">
-            <v>1222</v>
+            <v>3874</v>
           </cell>
           <cell r="H47">
             <v>0</v>
@@ -9274,7 +9274,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>21507</v>
+            <v>24159</v>
           </cell>
         </row>
         <row r="48">
@@ -9294,7 +9294,7 @@
             <v>2410</v>
           </cell>
           <cell r="G48">
-            <v>519</v>
+            <v>1469</v>
           </cell>
           <cell r="H48">
             <v>0</v>
@@ -9318,7 +9318,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>7269</v>
+            <v>8219</v>
           </cell>
         </row>
         <row r="49">
@@ -9338,7 +9338,7 @@
             <v>2869544.286</v>
           </cell>
           <cell r="G49">
-            <v>654324.9576</v>
+            <v>1706169.636</v>
           </cell>
           <cell r="H49">
             <v>0</v>
@@ -9362,7 +9362,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>8131029.2982</v>
+            <v>9182873.9766</v>
           </cell>
         </row>
         <row r="50">
@@ -9382,7 +9382,7 @@
             <v>863626.8</v>
           </cell>
           <cell r="G50">
-            <v>186429.08</v>
+            <v>529319.03</v>
           </cell>
           <cell r="H50">
             <v>0</v>
@@ -9406,7 +9406,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>2499073.43</v>
+            <v>2841963.38</v>
           </cell>
         </row>
         <row r="51">
@@ -9426,7 +9426,7 @@
             <v>0.300963049852021</v>
           </cell>
           <cell r="G51">
-            <v>0.28491818603986</v>
+            <v>0.310238219477961</v>
           </cell>
           <cell r="H51" t="e">
             <v>#DIV/0!</v>
@@ -9450,7 +9450,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.307350193726793</v>
+            <v>0.309485177215973</v>
           </cell>
         </row>
         <row r="52">
@@ -9470,7 +9470,7 @@
             <v>0.656646245903975</v>
           </cell>
           <cell r="G52">
-            <v>0.575286415711948</v>
+            <v>0.620805369127517</v>
           </cell>
           <cell r="H52" t="e">
             <v>#DIV/0!</v>
@@ -9494,7 +9494,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.662017017715163</v>
+            <v>0.659795521337804</v>
           </cell>
         </row>
         <row r="53">
@@ -9514,7 +9514,7 @@
             <v>0.196707142483304</v>
           </cell>
           <cell r="G53">
-            <v>0.196474498506349</v>
+            <v>0.239067146329502</v>
           </cell>
           <cell r="H53" t="e">
             <v>#DIV/0!</v>
@@ -9538,7 +9538,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.161065407349795</v>
+            <v>0.173270533134034</v>
           </cell>
         </row>
         <row r="54">
@@ -9561,7 +9561,7 @@
             <v>23093.23</v>
           </cell>
           <cell r="G54">
-            <v>1116.38</v>
+            <v>10367.07</v>
           </cell>
           <cell r="H54">
             <v>0</v>
@@ -9585,7 +9585,7 @@
             <v>0</v>
           </cell>
           <cell r="O54">
-            <v>117989.25</v>
+            <v>127239.94</v>
           </cell>
         </row>
         <row r="55">
@@ -9605,7 +9605,7 @@
             <v>2640</v>
           </cell>
           <cell r="G55">
-            <v>311</v>
+            <v>755</v>
           </cell>
           <cell r="H55">
             <v>0</v>
@@ -9629,7 +9629,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>15520</v>
+            <v>15964</v>
           </cell>
         </row>
         <row r="56">
@@ -9649,7 +9649,7 @@
             <v>896</v>
           </cell>
           <cell r="G56">
-            <v>130</v>
+            <v>278</v>
           </cell>
           <cell r="H56">
             <v>0</v>
@@ -9673,7 +9673,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>5618</v>
+            <v>5766</v>
           </cell>
         </row>
         <row r="57">
@@ -9693,7 +9693,7 @@
             <v>1028856.0636</v>
           </cell>
           <cell r="G57">
-            <v>121810.2264</v>
+            <v>292051.1184</v>
           </cell>
           <cell r="H57">
             <v>0</v>
@@ -9717,7 +9717,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>5401553.6937</v>
+            <v>5571794.5857</v>
           </cell>
         </row>
         <row r="58">
@@ -9737,7 +9737,7 @@
             <v>309148.93</v>
           </cell>
           <cell r="G58">
-            <v>41961.65</v>
+            <v>91566.47</v>
           </cell>
           <cell r="H58">
             <v>0</v>
@@ -9761,7 +9761,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2167394.8</v>
+            <v>2216999.62</v>
           </cell>
         </row>
         <row r="59">
@@ -9781,7 +9781,7 @@
             <v>0.300478308810543</v>
           </cell>
           <cell r="G59">
-            <v>0.344483802716255</v>
+            <v>0.313528914053287</v>
           </cell>
           <cell r="H59" t="e">
             <v>#DIV/0!</v>
@@ -9805,7 +9805,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.40125395819501</v>
+            <v>0.397896868935177</v>
           </cell>
         </row>
         <row r="60">
@@ -9825,7 +9825,7 @@
             <v>0.660606060606061</v>
           </cell>
           <cell r="G60">
-            <v>0.581993569131833</v>
+            <v>0.631788079470199</v>
           </cell>
           <cell r="H60" t="e">
             <v>#DIV/0!</v>
@@ -9849,7 +9849,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.638015463917526</v>
+            <v>0.638812327737409</v>
           </cell>
         </row>
         <row r="61">
@@ -9869,7 +9869,7 @@
             <v>0.074699369006388</v>
           </cell>
           <cell r="G61">
-            <v>0.0266047688782495</v>
+            <v>0.113219063703122</v>
           </cell>
           <cell r="H61" t="e">
             <v>#DIV/0!</v>
@@ -9893,7 +9893,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.0544382823101726</v>
+            <v>0.0573928560258391</v>
           </cell>
         </row>
         <row r="62">
@@ -22629,7 +22629,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d484c65-8101-46e3-9cab-592cdca2097c}</x14:id>
+          <x14:id>{6ffea380-36e5-4c0d-adc3-3fd7ad93975e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22643,7 +22643,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bc43b08f-aae5-4cb4-a995-0ee248139003}</x14:id>
+          <x14:id>{a13ec597-9d68-42f7-acf2-e52300cd8705}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22657,7 +22657,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e37f353-f467-4de3-b0c6-3ce6ac5a0044}</x14:id>
+          <x14:id>{42fa6338-1aee-44e3-8860-439b2c5171ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22671,7 +22671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{606f8dfa-5e01-4ddf-b88c-53f8178214f7}</x14:id>
+          <x14:id>{ac3c9d90-8699-4441-ab49-ad51bcce59dc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22685,7 +22685,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e6757d6-1645-43ec-9dbe-0de3fde7eadb}</x14:id>
+          <x14:id>{290cf15a-0fcc-4aad-8a7c-c45667f0d1cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22699,7 +22699,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d09f23f-fe54-461c-a06d-346929ae27b5}</x14:id>
+          <x14:id>{a626aaba-3375-40c9-ac90-47a317d146c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22713,7 +22713,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c72fb5a8-d14b-45c2-88ae-28fb2224dabd}</x14:id>
+          <x14:id>{eab2637e-d059-4694-80e1-855420a3ec4e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22727,7 +22727,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cdd2d606-6e0e-47c9-b7bb-e403ca5c41be}</x14:id>
+          <x14:id>{dc4a0168-47e5-441f-85d0-62afefcac8fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22741,7 +22741,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{87505910-c941-4ef8-af14-eeaaa25d972d}</x14:id>
+          <x14:id>{fdff7faf-03ec-4915-b406-940a37760fc3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22755,7 +22755,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c2cceb36-aed9-41bd-826a-de6f5eafef87}</x14:id>
+          <x14:id>{bfd848a9-d156-4824-94ef-7a18d67e33cb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22769,7 +22769,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6b9598b1-da8f-4bfc-ae17-ef8090072a8e}</x14:id>
+          <x14:id>{f7ac1dbb-4e4e-4a29-ab6f-29d0ac6d7691}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22783,7 +22783,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{614ae890-a144-4c77-b75d-67b185aea7a1}</x14:id>
+          <x14:id>{a0020f2c-f9d1-4e10-b05e-3dbe42b34b67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22797,7 +22797,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{993b9a7d-02a7-409b-a322-25a34db81e8f}</x14:id>
+          <x14:id>{98646ec0-1ef6-47eb-acad-321394bfa240}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22819,7 +22819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f17514d-4efe-458e-acba-cf5cfac3c8d9}</x14:id>
+          <x14:id>{f4bcd725-1338-4d12-8d1b-11a772f5e1bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22849,7 +22849,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a854c91-83e8-460f-99ed-98a7108b5c58}</x14:id>
+          <x14:id>{26099d4d-8a06-4cab-8167-005fe25b1261}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22879,7 +22879,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{df00900a-3bf6-4ef5-80f1-c03cc2197ee4}</x14:id>
+          <x14:id>{bbd341d2-9344-4b32-9224-c818b5693aef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22909,7 +22909,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{928673f0-9ff0-4110-a81b-87de4d8715f2}</x14:id>
+          <x14:id>{d88f7aed-a11f-4a92-8307-9f8ce27ed1cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22939,7 +22939,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5451c986-d455-4d55-ac51-c17376a5173b}</x14:id>
+          <x14:id>{b844d3fb-df6a-4580-871d-e57c39ae0db4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22969,7 +22969,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cacfea30-feca-498b-8476-3242a42572da}</x14:id>
+          <x14:id>{31e13c90-a31e-4353-8d5e-d594ed1692ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22999,7 +22999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13c2e93d-44f7-4c88-9136-4aa01b4d5629}</x14:id>
+          <x14:id>{e85ba726-3c28-4998-8625-06a709b163d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23029,7 +23029,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe1377a1-5f4d-4237-8dac-979f468bb639}</x14:id>
+          <x14:id>{a1f34a55-7273-467e-be9a-e5e3288b3cbb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23051,7 +23051,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d29c5a5c-b708-42b6-ad27-1c29700c6e04}</x14:id>
+          <x14:id>{b24c92b6-c9ba-4071-964d-91abf7ddbd43}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23073,7 +23073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e6b5fe06-6fba-4ac8-8fe5-156c97a9365c}</x14:id>
+          <x14:id>{24407811-2bc1-4304-ab65-03dcce433132}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23095,7 +23095,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27e9dd39-89a9-4875-9995-82e941b140f3}</x14:id>
+          <x14:id>{f4fdb71c-b08a-4223-b7e0-c7e3de230a31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23117,7 +23117,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd331c9e-05bc-4a7f-af0d-e9e62c60a991}</x14:id>
+          <x14:id>{c0b499ee-56ae-4cf1-8aee-db515701210f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23139,7 +23139,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4308deae-a5ac-4053-b25a-495881be62fb}</x14:id>
+          <x14:id>{17848a21-2369-4827-bfde-36fb103f5244}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23161,7 +23161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57c37003-c8d4-4cfe-af6f-41587f446a85}</x14:id>
+          <x14:id>{ab82fabc-9fce-4a0d-a3fc-f66ecebdba21}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23183,7 +23183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e1e33c71-eb07-40ea-be27-30281fbbadab}</x14:id>
+          <x14:id>{2015d494-b7db-411d-8cff-16041404a430}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23205,7 +23205,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84d383b8-5092-4e89-83f1-bdcbf185f7a1}</x14:id>
+          <x14:id>{7f99d502-a5f6-475d-9c07-0f13d8abeb46}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23227,7 +23227,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6e5b16b-5863-4351-b3e0-46ab2f819fe2}</x14:id>
+          <x14:id>{ec990ce2-843f-479e-be46-5b6634f31943}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23249,7 +23249,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20325cb1-3489-4186-9897-7d5eab339486}</x14:id>
+          <x14:id>{948452d4-f3fd-4993-b5c3-c207e6cc3af9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23271,7 +23271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8c04c54-9f17-4baa-bba2-b3b514b51952}</x14:id>
+          <x14:id>{af0eacbd-761b-4f99-abe2-809629a1c91a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23293,7 +23293,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b996e842-f8d2-4773-9a41-80ebfa91aa1c}</x14:id>
+          <x14:id>{6fbe6821-bbd6-446f-adf2-8cd2d2719713}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23312,7 +23312,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d484c65-8101-46e3-9cab-592cdca2097c}">
+          <x14:cfRule type="dataBar" id="{6ffea380-36e5-4c0d-adc3-3fd7ad93975e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23325,7 +23325,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bc43b08f-aae5-4cb4-a995-0ee248139003}">
+          <x14:cfRule type="dataBar" id="{a13ec597-9d68-42f7-acf2-e52300cd8705}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23338,7 +23338,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5e37f353-f467-4de3-b0c6-3ce6ac5a0044}">
+          <x14:cfRule type="dataBar" id="{42fa6338-1aee-44e3-8860-439b2c5171ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23351,7 +23351,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{606f8dfa-5e01-4ddf-b88c-53f8178214f7}">
+          <x14:cfRule type="dataBar" id="{ac3c9d90-8699-4441-ab49-ad51bcce59dc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23364,7 +23364,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e6757d6-1645-43ec-9dbe-0de3fde7eadb}">
+          <x14:cfRule type="dataBar" id="{290cf15a-0fcc-4aad-8a7c-c45667f0d1cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23377,7 +23377,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9d09f23f-fe54-461c-a06d-346929ae27b5}">
+          <x14:cfRule type="dataBar" id="{a626aaba-3375-40c9-ac90-47a317d146c3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23390,7 +23390,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c72fb5a8-d14b-45c2-88ae-28fb2224dabd}">
+          <x14:cfRule type="dataBar" id="{eab2637e-d059-4694-80e1-855420a3ec4e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23403,7 +23403,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cdd2d606-6e0e-47c9-b7bb-e403ca5c41be}">
+          <x14:cfRule type="dataBar" id="{dc4a0168-47e5-441f-85d0-62afefcac8fc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23416,7 +23416,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{87505910-c941-4ef8-af14-eeaaa25d972d}">
+          <x14:cfRule type="dataBar" id="{fdff7faf-03ec-4915-b406-940a37760fc3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23429,7 +23429,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c2cceb36-aed9-41bd-826a-de6f5eafef87}">
+          <x14:cfRule type="dataBar" id="{bfd848a9-d156-4824-94ef-7a18d67e33cb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23442,7 +23442,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6b9598b1-da8f-4bfc-ae17-ef8090072a8e}">
+          <x14:cfRule type="dataBar" id="{f7ac1dbb-4e4e-4a29-ab6f-29d0ac6d7691}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23455,7 +23455,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{614ae890-a144-4c77-b75d-67b185aea7a1}">
+          <x14:cfRule type="dataBar" id="{a0020f2c-f9d1-4e10-b05e-3dbe42b34b67}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23468,7 +23468,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{993b9a7d-02a7-409b-a322-25a34db81e8f}">
+          <x14:cfRule type="dataBar" id="{98646ec0-1ef6-47eb-acad-321394bfa240}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23481,7 +23481,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6f17514d-4efe-458e-acba-cf5cfac3c8d9}">
+          <x14:cfRule type="dataBar" id="{f4bcd725-1338-4d12-8d1b-11a772f5e1bf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23494,7 +23494,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a854c91-83e8-460f-99ed-98a7108b5c58}">
+          <x14:cfRule type="dataBar" id="{26099d4d-8a06-4cab-8167-005fe25b1261}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23507,7 +23507,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{df00900a-3bf6-4ef5-80f1-c03cc2197ee4}">
+          <x14:cfRule type="dataBar" id="{bbd341d2-9344-4b32-9224-c818b5693aef}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23520,7 +23520,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{928673f0-9ff0-4110-a81b-87de4d8715f2}">
+          <x14:cfRule type="dataBar" id="{d88f7aed-a11f-4a92-8307-9f8ce27ed1cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23533,7 +23533,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5451c986-d455-4d55-ac51-c17376a5173b}">
+          <x14:cfRule type="dataBar" id="{b844d3fb-df6a-4580-871d-e57c39ae0db4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23546,7 +23546,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cacfea30-feca-498b-8476-3242a42572da}">
+          <x14:cfRule type="dataBar" id="{31e13c90-a31e-4353-8d5e-d594ed1692ac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23559,7 +23559,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{13c2e93d-44f7-4c88-9136-4aa01b4d5629}">
+          <x14:cfRule type="dataBar" id="{e85ba726-3c28-4998-8625-06a709b163d5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23572,7 +23572,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fe1377a1-5f4d-4237-8dac-979f468bb639}">
+          <x14:cfRule type="dataBar" id="{a1f34a55-7273-467e-be9a-e5e3288b3cbb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23585,7 +23585,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d29c5a5c-b708-42b6-ad27-1c29700c6e04}">
+          <x14:cfRule type="dataBar" id="{b24c92b6-c9ba-4071-964d-91abf7ddbd43}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23598,7 +23598,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e6b5fe06-6fba-4ac8-8fe5-156c97a9365c}">
+          <x14:cfRule type="dataBar" id="{24407811-2bc1-4304-ab65-03dcce433132}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23611,7 +23611,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{27e9dd39-89a9-4875-9995-82e941b140f3}">
+          <x14:cfRule type="dataBar" id="{f4fdb71c-b08a-4223-b7e0-c7e3de230a31}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23624,7 +23624,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd331c9e-05bc-4a7f-af0d-e9e62c60a991}">
+          <x14:cfRule type="dataBar" id="{c0b499ee-56ae-4cf1-8aee-db515701210f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23637,7 +23637,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4308deae-a5ac-4053-b25a-495881be62fb}">
+          <x14:cfRule type="dataBar" id="{17848a21-2369-4827-bfde-36fb103f5244}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23650,7 +23650,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{57c37003-c8d4-4cfe-af6f-41587f446a85}">
+          <x14:cfRule type="dataBar" id="{ab82fabc-9fce-4a0d-a3fc-f66ecebdba21}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23663,7 +23663,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e1e33c71-eb07-40ea-be27-30281fbbadab}">
+          <x14:cfRule type="dataBar" id="{2015d494-b7db-411d-8cff-16041404a430}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23676,7 +23676,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{84d383b8-5092-4e89-83f1-bdcbf185f7a1}">
+          <x14:cfRule type="dataBar" id="{7f99d502-a5f6-475d-9c07-0f13d8abeb46}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23689,7 +23689,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a6e5b16b-5863-4351-b3e0-46ab2f819fe2}">
+          <x14:cfRule type="dataBar" id="{ec990ce2-843f-479e-be46-5b6634f31943}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23702,7 +23702,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20325cb1-3489-4186-9897-7d5eab339486}">
+          <x14:cfRule type="dataBar" id="{948452d4-f3fd-4993-b5c3-c207e6cc3af9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23715,7 +23715,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f8c04c54-9f17-4baa-bba2-b3b514b51952}">
+          <x14:cfRule type="dataBar" id="{af0eacbd-761b-4f99-abe2-809629a1c91a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23728,7 +23728,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b996e842-f8d2-4773-9a41-80ebfa91aa1c}">
+          <x14:cfRule type="dataBar" id="{6fbe6821-bbd6-446f-adf2-8cd2d2719713}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23963,7 +23963,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>806906.73</v>
+        <v>980483.16</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -24001,7 +24001,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.499970956849738</v>
+        <v>0.607521396779346</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -24112,7 +24112,7 @@
       </c>
       <c r="G7" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G7</f>
-        <v>100167.33</v>
+        <v>273743.76</v>
       </c>
       <c r="H7" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H7</f>
@@ -24144,7 +24144,7 @@
       </c>
       <c r="O7" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O7</f>
-        <v>2618965.2</v>
+        <v>2792541.63</v>
       </c>
     </row>
     <row r="8" s="38" customFormat="1" spans="1:15">
@@ -24174,7 +24174,7 @@
       </c>
       <c r="G8" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G8</f>
-        <v>0.184404202252453</v>
+        <v>0.503951734406688</v>
       </c>
       <c r="H8" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H8</f>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="O8" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O8</f>
-        <v>0.299130133051202</v>
+        <v>0.318955497893947</v>
       </c>
     </row>
     <row r="9" s="38" customFormat="1" spans="1:15">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="G11" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G11</f>
-        <v>5553</v>
+        <v>12697</v>
       </c>
       <c r="H11" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H11</f>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="O11" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O11</f>
-        <v>134556</v>
+        <v>141700</v>
       </c>
     </row>
     <row r="12" s="38" customFormat="1" spans="1:15">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="G12" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G12</f>
-        <v>0.15425</v>
+        <v>0.352694444444444</v>
       </c>
       <c r="H12" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H12</f>
@@ -24454,7 +24454,7 @@
       </c>
       <c r="O12" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O12</f>
-        <v>0.231644837416849</v>
+        <v>0.243943588260408</v>
       </c>
     </row>
     <row r="13" s="38" customFormat="1" spans="1:15">
@@ -24608,7 +24608,7 @@
       </c>
       <c r="G15" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G15</f>
-        <v>1865</v>
+        <v>4263</v>
       </c>
       <c r="H15" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H15</f>
@@ -24640,7 +24640,7 @@
       </c>
       <c r="O15" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O15</f>
-        <v>47929</v>
+        <v>50327</v>
       </c>
     </row>
     <row r="16" s="38" customFormat="1" spans="1:15">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="G16" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G16</f>
-        <v>0.167114695340502</v>
+        <v>0.381989247311828</v>
       </c>
       <c r="H16" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H16</f>
@@ -24702,7 +24702,7 @@
       </c>
       <c r="O16" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O16</f>
-        <v>0.266168239163456</v>
+        <v>0.279485258869979</v>
       </c>
     </row>
     <row r="17" s="38" customFormat="1" spans="1:15">
@@ -24856,7 +24856,7 @@
       </c>
       <c r="G19" s="25">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G19</f>
-        <v>2247713.1192</v>
+        <v>5158465.7808</v>
       </c>
       <c r="H19" s="25">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H19</f>
@@ -24888,7 +24888,7 @@
       </c>
       <c r="O19" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O19</f>
-        <v>51620365.6662</v>
+        <v>54531118.3278</v>
       </c>
     </row>
     <row r="20" s="38" customFormat="1" spans="1:15">
@@ -24918,7 +24918,7 @@
       </c>
       <c r="G20" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G20</f>
-        <v>0.179587177948226</v>
+        <v>0.412149710834132</v>
       </c>
       <c r="H20" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H20</f>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="O20" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O20</f>
-        <v>0.255930057052861</v>
+        <v>0.270361359216957</v>
       </c>
     </row>
     <row r="21" s="38" customFormat="1" spans="1:15">
@@ -25104,7 +25104,7 @@
       </c>
       <c r="G23" s="25">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G23</f>
-        <v>684372.3</v>
+        <v>1581454.25</v>
       </c>
       <c r="H23" s="25">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H23</f>
@@ -25136,7 +25136,7 @@
       </c>
       <c r="O23" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O23</f>
-        <v>17126902.41</v>
+        <v>18023984.36</v>
       </c>
     </row>
     <row r="24" s="38" customFormat="1" spans="1:15">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="G24" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G24</f>
-        <v>0.170874355824545</v>
+        <v>0.394858144075583</v>
       </c>
       <c r="H24" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H24</f>
@@ -25198,7 +25198,7 @@
       </c>
       <c r="O24" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O24</f>
-        <v>0.265356091435546</v>
+        <v>0.279255053095443</v>
       </c>
     </row>
     <row r="25" s="38" customFormat="1" spans="1:15">
@@ -25290,7 +25290,7 @@
       </c>
       <c r="G26" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G26</f>
-        <v>0.304474932389762</v>
+        <v>0.30657453537566</v>
       </c>
       <c r="H26" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H26</f>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="O26" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O26</f>
-        <v>0.331785763021326</v>
+        <v>0.330526585786365</v>
       </c>
     </row>
     <row r="27" s="38" customFormat="1" spans="1:15">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="G27" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G27</f>
-        <v>0.664145506933189</v>
+        <v>0.664251397968024</v>
       </c>
       <c r="H27" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H27</f>
@@ -25384,7 +25384,7 @@
       </c>
       <c r="O27" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O27</f>
-        <v>0.64379886441333</v>
+        <v>0.644834156669019</v>
       </c>
     </row>
     <row r="28" s="38" customFormat="1" spans="1:15">
@@ -25414,7 +25414,7 @@
       </c>
       <c r="G28" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G28</f>
-        <v>0.146363799353071</v>
+        <v>0.173096224566724</v>
       </c>
       <c r="H28" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H28</f>
@@ -25446,7 +25446,7 @@
       </c>
       <c r="O28" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O28</f>
-        <v>0.152915287149114</v>
+        <v>0.154934756612272</v>
       </c>
     </row>
     <row r="29" s="38" customFormat="1" spans="1:15">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="G30" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G30</f>
-        <v>48925.87</v>
+        <v>100586.14</v>
       </c>
       <c r="H30" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H30</f>
@@ -25570,7 +25570,7 @@
       </c>
       <c r="O30" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O30</f>
-        <v>1607399.29</v>
+        <v>1659059.56</v>
       </c>
     </row>
     <row r="31" s="38" customFormat="1" spans="1:15">
@@ -25600,7 +25600,7 @@
       </c>
       <c r="G31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G31</f>
-        <v>2331</v>
+        <v>4873</v>
       </c>
       <c r="H31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H31</f>
@@ -25632,7 +25632,7 @@
       </c>
       <c r="O31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O31</f>
-        <v>68182</v>
+        <v>70724</v>
       </c>
     </row>
     <row r="32" s="38" customFormat="1" spans="1:15">
@@ -25662,7 +25662,7 @@
       </c>
       <c r="G32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G32</f>
-        <v>866</v>
+        <v>1719</v>
       </c>
       <c r="H32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H32</f>
@@ -25694,7 +25694,7 @@
       </c>
       <c r="O32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O32</f>
-        <v>25418</v>
+        <v>26271</v>
       </c>
     </row>
     <row r="33" s="38" customFormat="1" spans="1:15">
@@ -25724,7 +25724,7 @@
       </c>
       <c r="G33" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G33</f>
-        <v>981973.6656</v>
+        <v>2064206.2944</v>
       </c>
       <c r="H33" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H33</f>
@@ -25756,7 +25756,7 @@
       </c>
       <c r="O33" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O33</f>
-        <v>27857969.1837</v>
+        <v>28940201.8125</v>
       </c>
     </row>
     <row r="34" s="38" customFormat="1" spans="1:15">
@@ -25786,7 +25786,7 @@
       </c>
       <c r="G34" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G34</f>
-        <v>332705.62</v>
+        <v>671916.1</v>
       </c>
       <c r="H34" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H34</f>
@@ -25818,7 +25818,7 @@
       </c>
       <c r="O34" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O34</f>
-        <v>9313993.25</v>
+        <v>9653203.73</v>
       </c>
     </row>
     <row r="35" s="38" customFormat="1" spans="1:15">
@@ -25848,7 +25848,7 @@
       </c>
       <c r="G35" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G35</f>
-        <v>0.338813179675966</v>
+        <v>0.325508211956744</v>
       </c>
       <c r="H35" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H35</f>
@@ -25880,7 +25880,7 @@
       </c>
       <c r="O35" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O35</f>
-        <v>0.334338558154832</v>
+        <v>0.333556890602972</v>
       </c>
     </row>
     <row r="36" s="38" customFormat="1" spans="1:15">
@@ -25910,7 +25910,7 @@
       </c>
       <c r="G36" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G36</f>
-        <v>0.628485628485629</v>
+        <v>0.647239893289555</v>
       </c>
       <c r="H36" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H36</f>
@@ -25942,7 +25942,7 @@
       </c>
       <c r="O36" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O36</f>
-        <v>0.627203660790238</v>
+        <v>0.628541937673209</v>
       </c>
     </row>
     <row r="37" s="38" customFormat="1" spans="1:15">
@@ -25972,7 +25972,7 @@
       </c>
       <c r="G37" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G37</f>
-        <v>0.147054534275676</v>
+        <v>0.149700446231308</v>
       </c>
       <c r="H37" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H37</f>
@@ -26004,7 +26004,7 @@
       </c>
       <c r="O37" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O37</f>
-        <v>0.172578962304917</v>
+        <v>0.171866212130592</v>
       </c>
     </row>
     <row r="38" s="38" customFormat="1" spans="1:15">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="G38" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G38</f>
-        <v>13496.52</v>
+        <v>36247.76</v>
       </c>
       <c r="H38" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H38</f>
@@ -26066,7 +26066,7 @@
       </c>
       <c r="O38" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O38</f>
-        <v>491062.38</v>
+        <v>513813.62</v>
       </c>
     </row>
     <row r="39" s="38" customFormat="1" spans="1:15">
@@ -26096,7 +26096,7 @@
       </c>
       <c r="G39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G39</f>
-        <v>1689</v>
+        <v>3195</v>
       </c>
       <c r="H39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H39</f>
@@ -26128,7 +26128,7 @@
       </c>
       <c r="O39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O39</f>
-        <v>29347</v>
+        <v>30853</v>
       </c>
     </row>
     <row r="40" s="38" customFormat="1" spans="1:15">
@@ -26158,7 +26158,7 @@
       </c>
       <c r="G40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G40</f>
-        <v>350</v>
+        <v>797</v>
       </c>
       <c r="H40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H40</f>
@@ -26190,7 +26190,7 @@
       </c>
       <c r="O40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O40</f>
-        <v>9624</v>
+        <v>10071</v>
       </c>
     </row>
     <row r="41" s="38" customFormat="1" spans="1:15">
@@ -26220,7 +26220,7 @@
       </c>
       <c r="G41" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G41</f>
-        <v>489604.2696</v>
+        <v>1096038.732</v>
       </c>
       <c r="H41" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H41</f>
@@ -26252,7 +26252,7 @@
       </c>
       <c r="O41" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O41</f>
-        <v>10229813.4906</v>
+        <v>10836247.953</v>
       </c>
     </row>
     <row r="42" s="38" customFormat="1" spans="1:15">
@@ -26282,7 +26282,7 @@
       </c>
       <c r="G42" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G42</f>
-        <v>123275.95</v>
+        <v>288652.65</v>
       </c>
       <c r="H42" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H42</f>
@@ -26314,7 +26314,7 @@
       </c>
       <c r="O42" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O42</f>
-        <v>3146440.93</v>
+        <v>3311817.63</v>
       </c>
     </row>
     <row r="43" s="38" customFormat="1" spans="1:15">
@@ -26344,7 +26344,7 @@
       </c>
       <c r="G43" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G43</f>
-        <v>0.251786917832058</v>
+        <v>0.263359899219328</v>
       </c>
       <c r="H43" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H43</f>
@@ -26376,7 +26376,7 @@
       </c>
       <c r="O43" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O43</f>
-        <v>0.307575590981322</v>
+        <v>0.305624017128837</v>
       </c>
     </row>
     <row r="44" s="38" customFormat="1" spans="1:15">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="G44" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G44</f>
-        <v>0.792776791000592</v>
+        <v>0.750547730829421</v>
       </c>
       <c r="H44" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H44</f>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="O44" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O44</f>
-        <v>0.672061880260333</v>
+        <v>0.673581175250381</v>
       </c>
     </row>
     <row r="45" s="38" customFormat="1" spans="1:15">
@@ -26468,7 +26468,7 @@
       </c>
       <c r="G45" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G45</f>
-        <v>0.109482182047674</v>
+        <v>0.125575704917312</v>
       </c>
       <c r="H45" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H45</f>
@@ -26500,7 +26500,7 @@
       </c>
       <c r="O45" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O45</f>
-        <v>0.156069155889095</v>
+        <v>0.155145505400308</v>
       </c>
     </row>
     <row r="46" s="38" customFormat="1" spans="1:15">
@@ -26530,7 +26530,7 @@
       </c>
       <c r="G46" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G46</f>
-        <v>36628.56</v>
+        <v>126542.79</v>
       </c>
       <c r="H46" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H46</f>
@@ -26562,7 +26562,7 @@
       </c>
       <c r="O46" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O46</f>
-        <v>402514.28</v>
+        <v>492428.51</v>
       </c>
     </row>
     <row r="47" s="38" customFormat="1" spans="1:15">
@@ -26592,7 +26592,7 @@
       </c>
       <c r="G47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G47</f>
-        <v>1222</v>
+        <v>3874</v>
       </c>
       <c r="H47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H47</f>
@@ -26624,7 +26624,7 @@
       </c>
       <c r="O47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O47</f>
-        <v>21507</v>
+        <v>24159</v>
       </c>
     </row>
     <row r="48" s="38" customFormat="1" spans="1:15">
@@ -26654,7 +26654,7 @@
       </c>
       <c r="G48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G48</f>
-        <v>519</v>
+        <v>1469</v>
       </c>
       <c r="H48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H48</f>
@@ -26686,7 +26686,7 @@
       </c>
       <c r="O48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O48</f>
-        <v>7269</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="49" s="38" customFormat="1" spans="1:15">
@@ -26716,7 +26716,7 @@
       </c>
       <c r="G49" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G49</f>
-        <v>654324.9576</v>
+        <v>1706169.636</v>
       </c>
       <c r="H49" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H49</f>
@@ -26748,7 +26748,7 @@
       </c>
       <c r="O49" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O49</f>
-        <v>8131029.2982</v>
+        <v>9182873.9766</v>
       </c>
     </row>
     <row r="50" s="38" customFormat="1" spans="1:15">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="G50" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G50</f>
-        <v>186429.08</v>
+        <v>529319.03</v>
       </c>
       <c r="H50" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H50</f>
@@ -26810,7 +26810,7 @@
       </c>
       <c r="O50" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O50</f>
-        <v>2499073.43</v>
+        <v>2841963.38</v>
       </c>
     </row>
     <row r="51" s="38" customFormat="1" spans="1:15">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="G51" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G51</f>
-        <v>0.28491818603986</v>
+        <v>0.310238219477961</v>
       </c>
       <c r="H51" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H51</f>
@@ -26872,7 +26872,7 @@
       </c>
       <c r="O51" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O51</f>
-        <v>0.307350193726793</v>
+        <v>0.309485177215973</v>
       </c>
     </row>
     <row r="52" s="38" customFormat="1" spans="1:15">
@@ -26902,7 +26902,7 @@
       </c>
       <c r="G52" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G52</f>
-        <v>0.575286415711948</v>
+        <v>0.620805369127517</v>
       </c>
       <c r="H52" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H52</f>
@@ -26934,7 +26934,7 @@
       </c>
       <c r="O52" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O52</f>
-        <v>0.662017017715163</v>
+        <v>0.659795521337804</v>
       </c>
     </row>
     <row r="53" s="38" customFormat="1" spans="1:15">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="G53" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G53</f>
-        <v>0.196474498506349</v>
+        <v>0.239067146329502</v>
       </c>
       <c r="H53" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H53</f>
@@ -26996,7 +26996,7 @@
       </c>
       <c r="O53" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O53</f>
-        <v>0.161065407349795</v>
+        <v>0.173270533134034</v>
       </c>
     </row>
     <row r="54" s="38" customFormat="1" spans="1:15">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G54" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G54</f>
-        <v>1116.38</v>
+        <v>10367.07</v>
       </c>
       <c r="H54" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H54</f>
@@ -27058,7 +27058,7 @@
       </c>
       <c r="O54" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O54</f>
-        <v>117989.25</v>
+        <v>127239.94</v>
       </c>
     </row>
     <row r="55" s="38" customFormat="1" spans="1:15">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="G55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G55</f>
-        <v>311</v>
+        <v>755</v>
       </c>
       <c r="H55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H55</f>
@@ -27120,7 +27120,7 @@
       </c>
       <c r="O55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O55</f>
-        <v>15520</v>
+        <v>15964</v>
       </c>
     </row>
     <row r="56" s="38" customFormat="1" spans="1:15">
@@ -27150,7 +27150,7 @@
       </c>
       <c r="G56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G56</f>
-        <v>130</v>
+        <v>278</v>
       </c>
       <c r="H56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H56</f>
@@ -27182,7 +27182,7 @@
       </c>
       <c r="O56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O56</f>
-        <v>5618</v>
+        <v>5766</v>
       </c>
     </row>
     <row r="57" s="38" customFormat="1" spans="1:15">
@@ -27212,7 +27212,7 @@
       </c>
       <c r="G57" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G57</f>
-        <v>121810.2264</v>
+        <v>292051.1184</v>
       </c>
       <c r="H57" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H57</f>
@@ -27244,7 +27244,7 @@
       </c>
       <c r="O57" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O57</f>
-        <v>5401553.6937</v>
+        <v>5571794.5857</v>
       </c>
     </row>
     <row r="58" s="38" customFormat="1" spans="1:15">
@@ -27274,7 +27274,7 @@
       </c>
       <c r="G58" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G58</f>
-        <v>41961.65</v>
+        <v>91566.47</v>
       </c>
       <c r="H58" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H58</f>
@@ -27306,7 +27306,7 @@
       </c>
       <c r="O58" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O58</f>
-        <v>2167394.8</v>
+        <v>2216999.62</v>
       </c>
     </row>
     <row r="59" s="38" customFormat="1" spans="1:15">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="G59" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G59</f>
-        <v>0.344483802716255</v>
+        <v>0.313528914053287</v>
       </c>
       <c r="H59" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H59</f>
@@ -27368,7 +27368,7 @@
       </c>
       <c r="O59" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O59</f>
-        <v>0.40125395819501</v>
+        <v>0.397896868935177</v>
       </c>
     </row>
     <row r="60" s="38" customFormat="1" spans="1:15">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="G60" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G60</f>
-        <v>0.581993569131833</v>
+        <v>0.631788079470199</v>
       </c>
       <c r="H60" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H60</f>
@@ -27430,7 +27430,7 @@
       </c>
       <c r="O60" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O60</f>
-        <v>0.638015463917526</v>
+        <v>0.638812327737409</v>
       </c>
     </row>
     <row r="61" s="38" customFormat="1" spans="1:15">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="G61" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G61</f>
-        <v>0.0266047688782495</v>
+        <v>0.113219063703122</v>
       </c>
       <c r="H61" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H61</f>
@@ -27492,7 +27492,7 @@
       </c>
       <c r="O61" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O61</f>
-        <v>0.0544382823101726</v>
+        <v>0.0573928560258391</v>
       </c>
     </row>
     <row r="62" s="38" customFormat="1" spans="1:15">
@@ -34292,7 +34292,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bdb6e576-3e14-40b7-9152-c83f4cd7acb6}</x14:id>
+          <x14:id>{2b372ea0-c8c3-4025-ac02-95ef43bd7aa4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34306,7 +34306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa240528-50d4-4eed-9e2c-d441faa9716d}</x14:id>
+          <x14:id>{3631410c-2496-49ab-9717-18e104bb7b9c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34320,7 +34320,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6141b4f4-c628-40f4-ab81-b6910c3cbbca}</x14:id>
+          <x14:id>{b71e021a-732f-4807-b25a-ded3c58f7b5c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34334,7 +34334,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ef8f99d-8e19-4ee4-ab1c-90d93123a2f5}</x14:id>
+          <x14:id>{5b20273a-088c-434e-ace2-ecd804034422}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34348,7 +34348,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37e7c8b6-2c2e-48d9-a79b-07c74bc1cb07}</x14:id>
+          <x14:id>{86391aa7-d2de-4240-990d-70d40416d7f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34362,7 +34362,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32f7db83-4805-445b-a743-00e58cc4454c}</x14:id>
+          <x14:id>{128e276d-40ab-47a1-a841-20a7ecfaa466}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34382,7 +34382,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{125d7bd3-0e23-42bf-b1d6-900e7ae46bc2}</x14:id>
+          <x14:id>{31143cc1-3ec0-4c1b-889b-0827eb0f2f5e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34396,7 +34396,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8e4d029-3662-4b98-8a06-1c4d361c89ce}</x14:id>
+          <x14:id>{6ff30b59-e48e-47d6-9c04-1a5526f34a3b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34410,7 +34410,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98a74125-ad99-4f4d-953e-64943663a308}</x14:id>
+          <x14:id>{a75f5154-167c-4694-822e-e28188d575e2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34424,7 +34424,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac1f99b0-503e-4d35-a8cb-f6ff028e6c68}</x14:id>
+          <x14:id>{0764e775-d1d6-4b3f-9128-4bd099a8fa3e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34438,7 +34438,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{125b8881-08d6-4d42-883c-57ed026190be}</x14:id>
+          <x14:id>{c597c3b8-9d74-4b28-ae5b-9e5290bcea12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34452,7 +34452,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e46a78c-3086-4600-ac5b-a46ef468d01f}</x14:id>
+          <x14:id>{8c0fa425-5e8a-45d5-baba-8772e10e3002}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34474,7 +34474,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{adc663a3-46bb-44ff-9899-bc545571d950}</x14:id>
+          <x14:id>{7558eb0f-0043-4e3d-b950-f00b92ba6b80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34504,7 +34504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a812cf56-27eb-4675-8804-3dc88ba54ea6}</x14:id>
+          <x14:id>{f86e63ff-70d9-4f26-8248-1c7f5f23349f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34534,7 +34534,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e7ee328-44bb-43e6-aa46-94fcf3d72a1c}</x14:id>
+          <x14:id>{dccbc567-38b6-4ea7-9b6c-977d6ec4d1cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34564,7 +34564,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a91a165-4601-48cc-bb71-d9ade802400b}</x14:id>
+          <x14:id>{06019503-b0d5-44be-8513-284581630bc8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34594,7 +34594,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fd113e4b-3b32-477c-8d35-3744895c832e}</x14:id>
+          <x14:id>{b0bf7b27-5383-4098-81fe-e2ec9e55a2ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34624,7 +34624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{05e8d6c1-d1d5-4762-bc81-807afdc0eacf}</x14:id>
+          <x14:id>{9c36ea44-7366-4430-92ed-5a690ec43b57}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34646,7 +34646,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{467fe571-8a51-4070-9b72-9cf1d3d6d6d5}</x14:id>
+          <x14:id>{f9105e5a-2d4e-4ea7-af2f-82c3976e0d32}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34668,7 +34668,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e76a069d-5dc6-4527-aca7-b18910e7a85f}</x14:id>
+          <x14:id>{dcdd1138-6bdf-4e13-9e87-99497a53b9ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34690,7 +34690,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae73ba54-ad44-4b65-b42a-282fb355a8c7}</x14:id>
+          <x14:id>{daf4fc40-9e01-46d4-8784-121d6c17fe8e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34712,7 +34712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71928f70-6fe6-488a-9312-1d9e85233333}</x14:id>
+          <x14:id>{8a86aeb5-3fb2-4638-8314-87cca6e8e285}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34734,7 +34734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba18497a-6216-4246-8218-687f0f98ee36}</x14:id>
+          <x14:id>{b6882efa-a013-49b2-bfea-b15bb5604fcd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34756,7 +34756,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d87238d-a375-4e33-8626-03d686193683}</x14:id>
+          <x14:id>{97a772f8-17f5-4dcf-a9eb-f797c1ed9acc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34778,7 +34778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ee22c21-d97e-42c1-966d-51e58e418098}</x14:id>
+          <x14:id>{e91465e4-9677-46e9-a7c0-79b2df9721cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34800,7 +34800,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74af01eb-e29b-4a92-bbfa-934f137405bd}</x14:id>
+          <x14:id>{5b0c355f-6356-46e3-b3bb-263ce215eb35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34822,7 +34822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f40472f-1b14-45bb-836d-cb20e10b130d}</x14:id>
+          <x14:id>{dc66bd22-1ad1-4dc3-891a-c4b9dc441d47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34844,7 +34844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b1c96755-b566-451e-9f37-2e45aeee1b51}</x14:id>
+          <x14:id>{a72ac834-f008-4864-9f0e-9afa47fd9f96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34866,7 +34866,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5493a66b-ee68-4f1a-a24b-4889bac05a91}</x14:id>
+          <x14:id>{aabd55cc-5f8b-411e-bb2b-45b627cb3427}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34888,7 +34888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d520bbe-b530-433e-8604-bab0a035168b}</x14:id>
+          <x14:id>{dceea5a4-6f98-488e-b3c9-631b0c7375aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34910,7 +34910,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bf1ddc36-c6fa-4cdf-ae2c-21b20ca6103f}</x14:id>
+          <x14:id>{afa9176d-cb45-4bdc-a0fb-7c057f35387c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34932,7 +34932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52d36c07-4a4e-447d-be7c-b37725a61d59}</x14:id>
+          <x14:id>{1c79e514-5174-4171-acce-1eb583805675}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34951,7 +34951,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bdb6e576-3e14-40b7-9152-c83f4cd7acb6}">
+          <x14:cfRule type="dataBar" id="{2b372ea0-c8c3-4025-ac02-95ef43bd7aa4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34964,7 +34964,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa240528-50d4-4eed-9e2c-d441faa9716d}">
+          <x14:cfRule type="dataBar" id="{3631410c-2496-49ab-9717-18e104bb7b9c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34977,7 +34977,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6141b4f4-c628-40f4-ab81-b6910c3cbbca}">
+          <x14:cfRule type="dataBar" id="{b71e021a-732f-4807-b25a-ded3c58f7b5c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34990,7 +34990,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ef8f99d-8e19-4ee4-ab1c-90d93123a2f5}">
+          <x14:cfRule type="dataBar" id="{5b20273a-088c-434e-ace2-ecd804034422}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35003,7 +35003,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{37e7c8b6-2c2e-48d9-a79b-07c74bc1cb07}">
+          <x14:cfRule type="dataBar" id="{86391aa7-d2de-4240-990d-70d40416d7f1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35016,7 +35016,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32f7db83-4805-445b-a743-00e58cc4454c}">
+          <x14:cfRule type="dataBar" id="{128e276d-40ab-47a1-a841-20a7ecfaa466}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35029,7 +35029,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{125d7bd3-0e23-42bf-b1d6-900e7ae46bc2}">
+          <x14:cfRule type="dataBar" id="{31143cc1-3ec0-4c1b-889b-0827eb0f2f5e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35042,7 +35042,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b8e4d029-3662-4b98-8a06-1c4d361c89ce}">
+          <x14:cfRule type="dataBar" id="{6ff30b59-e48e-47d6-9c04-1a5526f34a3b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35055,7 +35055,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98a74125-ad99-4f4d-953e-64943663a308}">
+          <x14:cfRule type="dataBar" id="{a75f5154-167c-4694-822e-e28188d575e2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35068,7 +35068,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ac1f99b0-503e-4d35-a8cb-f6ff028e6c68}">
+          <x14:cfRule type="dataBar" id="{0764e775-d1d6-4b3f-9128-4bd099a8fa3e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35081,7 +35081,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{125b8881-08d6-4d42-883c-57ed026190be}">
+          <x14:cfRule type="dataBar" id="{c597c3b8-9d74-4b28-ae5b-9e5290bcea12}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35094,7 +35094,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4e46a78c-3086-4600-ac5b-a46ef468d01f}">
+          <x14:cfRule type="dataBar" id="{8c0fa425-5e8a-45d5-baba-8772e10e3002}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35107,7 +35107,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{adc663a3-46bb-44ff-9899-bc545571d950}">
+          <x14:cfRule type="dataBar" id="{7558eb0f-0043-4e3d-b950-f00b92ba6b80}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35120,7 +35120,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a812cf56-27eb-4675-8804-3dc88ba54ea6}">
+          <x14:cfRule type="dataBar" id="{f86e63ff-70d9-4f26-8248-1c7f5f23349f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35133,7 +35133,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e7ee328-44bb-43e6-aa46-94fcf3d72a1c}">
+          <x14:cfRule type="dataBar" id="{dccbc567-38b6-4ea7-9b6c-977d6ec4d1cf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35146,7 +35146,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a91a165-4601-48cc-bb71-d9ade802400b}">
+          <x14:cfRule type="dataBar" id="{06019503-b0d5-44be-8513-284581630bc8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35159,7 +35159,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fd113e4b-3b32-477c-8d35-3744895c832e}">
+          <x14:cfRule type="dataBar" id="{b0bf7b27-5383-4098-81fe-e2ec9e55a2ba}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35172,7 +35172,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{05e8d6c1-d1d5-4762-bc81-807afdc0eacf}">
+          <x14:cfRule type="dataBar" id="{9c36ea44-7366-4430-92ed-5a690ec43b57}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35185,7 +35185,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{467fe571-8a51-4070-9b72-9cf1d3d6d6d5}">
+          <x14:cfRule type="dataBar" id="{f9105e5a-2d4e-4ea7-af2f-82c3976e0d32}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35198,7 +35198,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e76a069d-5dc6-4527-aca7-b18910e7a85f}">
+          <x14:cfRule type="dataBar" id="{dcdd1138-6bdf-4e13-9e87-99497a53b9ec}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35211,7 +35211,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ae73ba54-ad44-4b65-b42a-282fb355a8c7}">
+          <x14:cfRule type="dataBar" id="{daf4fc40-9e01-46d4-8784-121d6c17fe8e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35224,7 +35224,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71928f70-6fe6-488a-9312-1d9e85233333}">
+          <x14:cfRule type="dataBar" id="{8a86aeb5-3fb2-4638-8314-87cca6e8e285}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35237,7 +35237,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba18497a-6216-4246-8218-687f0f98ee36}">
+          <x14:cfRule type="dataBar" id="{b6882efa-a013-49b2-bfea-b15bb5604fcd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35250,7 +35250,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d87238d-a375-4e33-8626-03d686193683}">
+          <x14:cfRule type="dataBar" id="{97a772f8-17f5-4dcf-a9eb-f797c1ed9acc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35263,7 +35263,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2ee22c21-d97e-42c1-966d-51e58e418098}">
+          <x14:cfRule type="dataBar" id="{e91465e4-9677-46e9-a7c0-79b2df9721cf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35276,7 +35276,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{74af01eb-e29b-4a92-bbfa-934f137405bd}">
+          <x14:cfRule type="dataBar" id="{5b0c355f-6356-46e3-b3bb-263ce215eb35}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35289,7 +35289,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4f40472f-1b14-45bb-836d-cb20e10b130d}">
+          <x14:cfRule type="dataBar" id="{dc66bd22-1ad1-4dc3-891a-c4b9dc441d47}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35302,7 +35302,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b1c96755-b566-451e-9f37-2e45aeee1b51}">
+          <x14:cfRule type="dataBar" id="{a72ac834-f008-4864-9f0e-9afa47fd9f96}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35315,7 +35315,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5493a66b-ee68-4f1a-a24b-4889bac05a91}">
+          <x14:cfRule type="dataBar" id="{aabd55cc-5f8b-411e-bb2b-45b627cb3427}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35328,7 +35328,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2d520bbe-b530-433e-8604-bab0a035168b}">
+          <x14:cfRule type="dataBar" id="{dceea5a4-6f98-488e-b3c9-631b0c7375aa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35341,7 +35341,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bf1ddc36-c6fa-4cdf-ae2c-21b20ca6103f}">
+          <x14:cfRule type="dataBar" id="{afa9176d-cb45-4bdc-a0fb-7c057f35387c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35354,7 +35354,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52d36c07-4a4e-447d-be7c-b37725a61d59}">
+          <x14:cfRule type="dataBar" id="{1c79e514-5174-4171-acce-1eb583805675}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -40503,7 +40503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{259c1ac8-5c78-48be-aec1-fc95dea6aeb8}</x14:id>
+          <x14:id>{92d4e91a-35ed-4381-8654-e0d0bc145abe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40514,7 +40514,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{259c1ac8-5c78-48be-aec1-fc95dea6aeb8}">
+          <x14:cfRule type="dataBar" id="{92d4e91a-35ed-4381-8654-e0d0bc145abe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -12754,6 +12754,7 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="总目标"/>
       <sheetName val="江凯伦"/>
       <sheetName val="陈敏华--作废"/>
       <sheetName val="敏华新"/>
@@ -12761,7 +12762,6 @@
       <sheetName val="杨皓"/>
       <sheetName val="陈欣诺"/>
       <sheetName val="林梓蕾"/>
-      <sheetName val="总目标"/>
       <sheetName val="周度汇总分析报告"/>
       <sheetName val="m"/>
       <sheetName val="mu"/>
@@ -12786,53 +12786,7 @@
       <sheetName val="敏华xin"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="103">
-          <cell r="B103">
-            <v>11594</v>
-          </cell>
-          <cell r="C103">
-            <v>93152.4590163934</v>
-          </cell>
-          <cell r="D103">
-            <v>57264.3442622951</v>
-          </cell>
-          <cell r="E103">
-            <v>54027.6639344262</v>
-          </cell>
-          <cell r="F103">
-            <v>58559.0163934426</v>
-          </cell>
-          <cell r="G103">
-            <v>56188.7704918033</v>
-          </cell>
-          <cell r="H103">
-            <v>70184.5081967213</v>
-          </cell>
-          <cell r="I103">
-            <v>67920.4918032787</v>
-          </cell>
-          <cell r="J103">
-            <v>67920.4918032787</v>
-          </cell>
-          <cell r="K103">
-            <v>61347.5409836066</v>
-          </cell>
-          <cell r="L103">
-            <v>63392.4590163934</v>
-          </cell>
-          <cell r="M103">
-            <v>47338.5245901639</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
+      <sheetData sheetId="0">
         <row r="18">
           <cell r="B18">
             <v>622242.554098361</v>
@@ -12954,7 +12908,12 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>51320.92</v>
+            <v>33154.43</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33">
+            <v>95210.94</v>
           </cell>
         </row>
         <row r="44">
@@ -12997,7 +12956,12 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>100441.56</v>
+            <v>100423.98</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="F46">
+            <v>159761.43</v>
           </cell>
         </row>
         <row r="58">
@@ -13052,7 +13016,7 @@
             <v>58296.43</v>
           </cell>
           <cell r="F59">
-            <v>45526.36</v>
+            <v>37248.15</v>
           </cell>
         </row>
         <row r="60">
@@ -13062,6 +13026,9 @@
           <cell r="E60">
             <v>97059.95</v>
           </cell>
+          <cell r="F60">
+            <v>66068.28</v>
+          </cell>
         </row>
         <row r="61">
           <cell r="D61">
@@ -13133,7 +13100,7 @@
             <v>-1579</v>
           </cell>
           <cell r="F71">
-            <v>12060.24</v>
+            <v>3973.7</v>
           </cell>
         </row>
         <row r="72">
@@ -13143,6 +13110,9 @@
           <cell r="E72">
             <v>17659.06</v>
           </cell>
+          <cell r="F72">
+            <v>10854.18</v>
+          </cell>
         </row>
         <row r="73">
           <cell r="D73">
@@ -13166,6 +13136,52 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="103">
+          <cell r="B103">
+            <v>11594</v>
+          </cell>
+          <cell r="C103">
+            <v>93152.4590163934</v>
+          </cell>
+          <cell r="D103">
+            <v>57264.3442622951</v>
+          </cell>
+          <cell r="E103">
+            <v>54027.6639344262</v>
+          </cell>
+          <cell r="F103">
+            <v>58559.0163934426</v>
+          </cell>
+          <cell r="G103">
+            <v>56188.7704918033</v>
+          </cell>
+          <cell r="H103">
+            <v>70184.5081967213</v>
+          </cell>
+          <cell r="I103">
+            <v>67920.4918032787</v>
+          </cell>
+          <cell r="J103">
+            <v>67920.4918032787</v>
+          </cell>
+          <cell r="K103">
+            <v>61347.5409836066</v>
+          </cell>
+          <cell r="L103">
+            <v>63392.4590163934</v>
+          </cell>
+          <cell r="M103">
+            <v>47338.5245901639</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
       <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9" refreshError="1"/>
       <sheetData sheetId="10" refreshError="1"/>
@@ -22629,7 +22645,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ffea380-36e5-4c0d-adc3-3fd7ad93975e}</x14:id>
+          <x14:id>{441caa18-3984-44fd-ab5c-475e08fdb1ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22643,7 +22659,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a13ec597-9d68-42f7-acf2-e52300cd8705}</x14:id>
+          <x14:id>{84f5b97e-28cc-4adf-83d4-2067a37f8c7c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22657,7 +22673,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42fa6338-1aee-44e3-8860-439b2c5171ee}</x14:id>
+          <x14:id>{02a3b66d-5dd4-4c38-92c1-37d396796232}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22671,7 +22687,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac3c9d90-8699-4441-ab49-ad51bcce59dc}</x14:id>
+          <x14:id>{e823004d-fea1-4b91-a74f-864809548dc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22685,7 +22701,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{290cf15a-0fcc-4aad-8a7c-c45667f0d1cd}</x14:id>
+          <x14:id>{2854665e-094c-4962-988a-c9fa72d81bee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22699,7 +22715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a626aaba-3375-40c9-ac90-47a317d146c3}</x14:id>
+          <x14:id>{21702da6-bcfc-48fb-8727-846cb8c0b091}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22713,7 +22729,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eab2637e-d059-4694-80e1-855420a3ec4e}</x14:id>
+          <x14:id>{6045cd6d-72c0-4da4-a94d-37f0498a1da7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22727,7 +22743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc4a0168-47e5-441f-85d0-62afefcac8fc}</x14:id>
+          <x14:id>{087d7567-87be-4f1a-97f0-4981aa737d2e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22741,7 +22757,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fdff7faf-03ec-4915-b406-940a37760fc3}</x14:id>
+          <x14:id>{529fc87a-ab26-4b3c-aeb9-69e44db7adee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22755,7 +22771,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bfd848a9-d156-4824-94ef-7a18d67e33cb}</x14:id>
+          <x14:id>{46d1a7e9-7892-4f02-adde-1b38118277db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22769,7 +22785,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7ac1dbb-4e4e-4a29-ab6f-29d0ac6d7691}</x14:id>
+          <x14:id>{c1a75805-6cc7-40df-9f00-f1fdb4a65bff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22783,7 +22799,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0020f2c-f9d1-4e10-b05e-3dbe42b34b67}</x14:id>
+          <x14:id>{98e04a55-6e2c-41b9-8fb6-d9e7ad35af44}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22797,7 +22813,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98646ec0-1ef6-47eb-acad-321394bfa240}</x14:id>
+          <x14:id>{c88929bb-5552-4aca-a1d7-62f80ef9cc6e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22819,7 +22835,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4bcd725-1338-4d12-8d1b-11a772f5e1bf}</x14:id>
+          <x14:id>{6a543ee3-cd3b-4f48-b7ac-586d3a8e9d7d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22849,7 +22865,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26099d4d-8a06-4cab-8167-005fe25b1261}</x14:id>
+          <x14:id>{5bf450ec-c0cb-4bc0-90f0-e2e1acae1783}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22879,7 +22895,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bbd341d2-9344-4b32-9224-c818b5693aef}</x14:id>
+          <x14:id>{152fc664-b7ed-4a44-8c09-304728896be6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22909,7 +22925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d88f7aed-a11f-4a92-8307-9f8ce27ed1cd}</x14:id>
+          <x14:id>{badeace3-ad15-4072-bd17-b5bc69d19870}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22939,7 +22955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b844d3fb-df6a-4580-871d-e57c39ae0db4}</x14:id>
+          <x14:id>{23f21ef8-6a57-43da-9d86-14d027bb935d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22969,7 +22985,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31e13c90-a31e-4353-8d5e-d594ed1692ac}</x14:id>
+          <x14:id>{03a6ecb6-529f-467d-b6ae-5cf20b3478e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22999,7 +23015,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e85ba726-3c28-4998-8625-06a709b163d5}</x14:id>
+          <x14:id>{2bc47293-5270-4144-8d97-db6463cb2215}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23029,7 +23045,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1f34a55-7273-467e-be9a-e5e3288b3cbb}</x14:id>
+          <x14:id>{be9775c1-3ae6-45f0-9cdb-00e0b167d0d2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23051,7 +23067,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b24c92b6-c9ba-4071-964d-91abf7ddbd43}</x14:id>
+          <x14:id>{a71a036a-ae3a-4f6a-a3e6-f57d3c69da84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23073,7 +23089,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24407811-2bc1-4304-ab65-03dcce433132}</x14:id>
+          <x14:id>{023554ef-8348-4313-b2e3-516c2ba1b06b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23095,7 +23111,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4fdb71c-b08a-4223-b7e0-c7e3de230a31}</x14:id>
+          <x14:id>{b3a158a3-91a1-4c10-96bc-49bec9c5b9e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23117,7 +23133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0b499ee-56ae-4cf1-8aee-db515701210f}</x14:id>
+          <x14:id>{c580add1-1fda-4344-ae32-a7ac5a207fdb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23139,7 +23155,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17848a21-2369-4827-bfde-36fb103f5244}</x14:id>
+          <x14:id>{75b77aca-6c8e-4ba1-835e-339794222b05}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23161,7 +23177,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab82fabc-9fce-4a0d-a3fc-f66ecebdba21}</x14:id>
+          <x14:id>{0fc18f7d-82e7-4e45-912a-033c07a7d3e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23183,7 +23199,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2015d494-b7db-411d-8cff-16041404a430}</x14:id>
+          <x14:id>{84faed7e-692a-4169-8601-365a4fb4ea28}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23205,7 +23221,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f99d502-a5f6-475d-9c07-0f13d8abeb46}</x14:id>
+          <x14:id>{62e62921-34d7-498a-99cc-a1a674fe2f53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23227,7 +23243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec990ce2-843f-479e-be46-5b6634f31943}</x14:id>
+          <x14:id>{6a7cd340-6297-410a-8a5d-a2a37a22b873}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23249,7 +23265,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{948452d4-f3fd-4993-b5c3-c207e6cc3af9}</x14:id>
+          <x14:id>{b114736c-4117-454c-8ef3-a8ac69ac4d40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23271,7 +23287,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af0eacbd-761b-4f99-abe2-809629a1c91a}</x14:id>
+          <x14:id>{4c930bee-07fc-4ce0-a35a-ab61eb6777ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23293,7 +23309,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6fbe6821-bbd6-446f-adf2-8cd2d2719713}</x14:id>
+          <x14:id>{a050d28a-e48a-42dd-8b6d-e7e08009a353}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23312,7 +23328,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ffea380-36e5-4c0d-adc3-3fd7ad93975e}">
+          <x14:cfRule type="dataBar" id="{441caa18-3984-44fd-ab5c-475e08fdb1ea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23325,7 +23341,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a13ec597-9d68-42f7-acf2-e52300cd8705}">
+          <x14:cfRule type="dataBar" id="{84f5b97e-28cc-4adf-83d4-2067a37f8c7c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23338,7 +23354,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42fa6338-1aee-44e3-8860-439b2c5171ee}">
+          <x14:cfRule type="dataBar" id="{02a3b66d-5dd4-4c38-92c1-37d396796232}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23351,7 +23367,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ac3c9d90-8699-4441-ab49-ad51bcce59dc}">
+          <x14:cfRule type="dataBar" id="{e823004d-fea1-4b91-a74f-864809548dc9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23364,7 +23380,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{290cf15a-0fcc-4aad-8a7c-c45667f0d1cd}">
+          <x14:cfRule type="dataBar" id="{2854665e-094c-4962-988a-c9fa72d81bee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23377,7 +23393,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a626aaba-3375-40c9-ac90-47a317d146c3}">
+          <x14:cfRule type="dataBar" id="{21702da6-bcfc-48fb-8727-846cb8c0b091}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23390,7 +23406,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eab2637e-d059-4694-80e1-855420a3ec4e}">
+          <x14:cfRule type="dataBar" id="{6045cd6d-72c0-4da4-a94d-37f0498a1da7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23403,7 +23419,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc4a0168-47e5-441f-85d0-62afefcac8fc}">
+          <x14:cfRule type="dataBar" id="{087d7567-87be-4f1a-97f0-4981aa737d2e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23416,7 +23432,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fdff7faf-03ec-4915-b406-940a37760fc3}">
+          <x14:cfRule type="dataBar" id="{529fc87a-ab26-4b3c-aeb9-69e44db7adee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23429,7 +23445,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bfd848a9-d156-4824-94ef-7a18d67e33cb}">
+          <x14:cfRule type="dataBar" id="{46d1a7e9-7892-4f02-adde-1b38118277db}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23442,7 +23458,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7ac1dbb-4e4e-4a29-ab6f-29d0ac6d7691}">
+          <x14:cfRule type="dataBar" id="{c1a75805-6cc7-40df-9f00-f1fdb4a65bff}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23455,7 +23471,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a0020f2c-f9d1-4e10-b05e-3dbe42b34b67}">
+          <x14:cfRule type="dataBar" id="{98e04a55-6e2c-41b9-8fb6-d9e7ad35af44}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23468,7 +23484,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98646ec0-1ef6-47eb-acad-321394bfa240}">
+          <x14:cfRule type="dataBar" id="{c88929bb-5552-4aca-a1d7-62f80ef9cc6e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23481,7 +23497,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f4bcd725-1338-4d12-8d1b-11a772f5e1bf}">
+          <x14:cfRule type="dataBar" id="{6a543ee3-cd3b-4f48-b7ac-586d3a8e9d7d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23494,7 +23510,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{26099d4d-8a06-4cab-8167-005fe25b1261}">
+          <x14:cfRule type="dataBar" id="{5bf450ec-c0cb-4bc0-90f0-e2e1acae1783}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23507,7 +23523,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bbd341d2-9344-4b32-9224-c818b5693aef}">
+          <x14:cfRule type="dataBar" id="{152fc664-b7ed-4a44-8c09-304728896be6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23520,7 +23536,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d88f7aed-a11f-4a92-8307-9f8ce27ed1cd}">
+          <x14:cfRule type="dataBar" id="{badeace3-ad15-4072-bd17-b5bc69d19870}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23533,7 +23549,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b844d3fb-df6a-4580-871d-e57c39ae0db4}">
+          <x14:cfRule type="dataBar" id="{23f21ef8-6a57-43da-9d86-14d027bb935d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23546,7 +23562,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{31e13c90-a31e-4353-8d5e-d594ed1692ac}">
+          <x14:cfRule type="dataBar" id="{03a6ecb6-529f-467d-b6ae-5cf20b3478e8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23559,7 +23575,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e85ba726-3c28-4998-8625-06a709b163d5}">
+          <x14:cfRule type="dataBar" id="{2bc47293-5270-4144-8d97-db6463cb2215}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23572,7 +23588,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a1f34a55-7273-467e-be9a-e5e3288b3cbb}">
+          <x14:cfRule type="dataBar" id="{be9775c1-3ae6-45f0-9cdb-00e0b167d0d2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23585,7 +23601,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b24c92b6-c9ba-4071-964d-91abf7ddbd43}">
+          <x14:cfRule type="dataBar" id="{a71a036a-ae3a-4f6a-a3e6-f57d3c69da84}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23598,7 +23614,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{24407811-2bc1-4304-ab65-03dcce433132}">
+          <x14:cfRule type="dataBar" id="{023554ef-8348-4313-b2e3-516c2ba1b06b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23611,7 +23627,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f4fdb71c-b08a-4223-b7e0-c7e3de230a31}">
+          <x14:cfRule type="dataBar" id="{b3a158a3-91a1-4c10-96bc-49bec9c5b9e6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23624,7 +23640,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c0b499ee-56ae-4cf1-8aee-db515701210f}">
+          <x14:cfRule type="dataBar" id="{c580add1-1fda-4344-ae32-a7ac5a207fdb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23637,7 +23653,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17848a21-2369-4827-bfde-36fb103f5244}">
+          <x14:cfRule type="dataBar" id="{75b77aca-6c8e-4ba1-835e-339794222b05}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23650,7 +23666,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ab82fabc-9fce-4a0d-a3fc-f66ecebdba21}">
+          <x14:cfRule type="dataBar" id="{0fc18f7d-82e7-4e45-912a-033c07a7d3e7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23663,7 +23679,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2015d494-b7db-411d-8cff-16041404a430}">
+          <x14:cfRule type="dataBar" id="{84faed7e-692a-4169-8601-365a4fb4ea28}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23676,7 +23692,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7f99d502-a5f6-475d-9c07-0f13d8abeb46}">
+          <x14:cfRule type="dataBar" id="{62e62921-34d7-498a-99cc-a1a674fe2f53}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23689,7 +23705,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec990ce2-843f-479e-be46-5b6634f31943}">
+          <x14:cfRule type="dataBar" id="{6a7cd340-6297-410a-8a5d-a2a37a22b873}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23702,7 +23718,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{948452d4-f3fd-4993-b5c3-c207e6cc3af9}">
+          <x14:cfRule type="dataBar" id="{b114736c-4117-454c-8ef3-a8ac69ac4d40}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23715,7 +23731,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af0eacbd-761b-4f99-abe2-809629a1c91a}">
+          <x14:cfRule type="dataBar" id="{4c930bee-07fc-4ce0-a35a-ab61eb6777ae}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23728,7 +23744,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6fbe6821-bbd6-446f-adf2-8cd2d2719713}">
+          <x14:cfRule type="dataBar" id="{a050d28a-e48a-42dd-8b6d-e7e08009a353}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34292,7 +34308,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b372ea0-c8c3-4025-ac02-95ef43bd7aa4}</x14:id>
+          <x14:id>{c66c34d8-42e3-4fd2-a437-013d0d51c7c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34306,7 +34322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3631410c-2496-49ab-9717-18e104bb7b9c}</x14:id>
+          <x14:id>{71281b02-bb53-4eae-91b4-c7512c992a7f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34320,7 +34336,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b71e021a-732f-4807-b25a-ded3c58f7b5c}</x14:id>
+          <x14:id>{07fd883f-0910-4556-9971-9237229fc13a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34334,7 +34350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b20273a-088c-434e-ace2-ecd804034422}</x14:id>
+          <x14:id>{477549b2-32be-4d87-be90-471ec5daac6f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34348,7 +34364,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86391aa7-d2de-4240-990d-70d40416d7f1}</x14:id>
+          <x14:id>{55f993d2-dbda-4389-8cfe-2c3616821598}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34362,7 +34378,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{128e276d-40ab-47a1-a841-20a7ecfaa466}</x14:id>
+          <x14:id>{a92d7651-804e-42e0-b4b3-4d02d3d4623f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34382,7 +34398,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31143cc1-3ec0-4c1b-889b-0827eb0f2f5e}</x14:id>
+          <x14:id>{74340dfa-ae4b-430c-919d-fe193f0f5c27}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34396,7 +34412,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ff30b59-e48e-47d6-9c04-1a5526f34a3b}</x14:id>
+          <x14:id>{a132e647-b7de-499c-abe5-d99308cb7d98}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34410,7 +34426,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a75f5154-167c-4694-822e-e28188d575e2}</x14:id>
+          <x14:id>{319440c2-b417-4447-a80f-9715efabb5a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34424,7 +34440,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0764e775-d1d6-4b3f-9128-4bd099a8fa3e}</x14:id>
+          <x14:id>{e3be99c9-0579-4a76-8126-76bb62038bda}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34438,7 +34454,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c597c3b8-9d74-4b28-ae5b-9e5290bcea12}</x14:id>
+          <x14:id>{6ca5ba9b-9368-49c7-ae1f-22e399276695}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34452,7 +34468,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c0fa425-5e8a-45d5-baba-8772e10e3002}</x14:id>
+          <x14:id>{a9154d54-b61b-406e-bfdd-a4043eca2256}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34474,7 +34490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7558eb0f-0043-4e3d-b950-f00b92ba6b80}</x14:id>
+          <x14:id>{1b5ed58f-423c-490d-a9af-c6d8cc461d6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34504,7 +34520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f86e63ff-70d9-4f26-8248-1c7f5f23349f}</x14:id>
+          <x14:id>{6bfedf94-ce14-473e-94b7-701ea742e258}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34534,7 +34550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dccbc567-38b6-4ea7-9b6c-977d6ec4d1cf}</x14:id>
+          <x14:id>{1002119b-e37e-4d01-b43d-fc9f9b5fd223}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34564,7 +34580,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06019503-b0d5-44be-8513-284581630bc8}</x14:id>
+          <x14:id>{ff4e9bb1-2e61-4330-a000-68f8dbcc3fe7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34594,7 +34610,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b0bf7b27-5383-4098-81fe-e2ec9e55a2ba}</x14:id>
+          <x14:id>{9398cef7-719c-44d2-aefb-d7f2af7ba778}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34624,7 +34640,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c36ea44-7366-4430-92ed-5a690ec43b57}</x14:id>
+          <x14:id>{90abb60f-2161-48d3-9198-3cf88649f2ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34646,7 +34662,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9105e5a-2d4e-4ea7-af2f-82c3976e0d32}</x14:id>
+          <x14:id>{12e6087e-fdf2-40bb-98f7-67e1476624a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34668,7 +34684,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dcdd1138-6bdf-4e13-9e87-99497a53b9ec}</x14:id>
+          <x14:id>{cadfbfa6-5b7e-4375-b287-b1700f291b50}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34690,7 +34706,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{daf4fc40-9e01-46d4-8784-121d6c17fe8e}</x14:id>
+          <x14:id>{e45a22f0-6dda-46ef-a991-87c1d42bbf9f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34712,7 +34728,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a86aeb5-3fb2-4638-8314-87cca6e8e285}</x14:id>
+          <x14:id>{b37b0669-1ceb-46dd-972b-53f6e183d37d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34734,7 +34750,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b6882efa-a013-49b2-bfea-b15bb5604fcd}</x14:id>
+          <x14:id>{062eb8fb-4b8c-4fd6-8430-9e7626515874}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34756,7 +34772,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97a772f8-17f5-4dcf-a9eb-f797c1ed9acc}</x14:id>
+          <x14:id>{1dc959e4-6611-4a23-8645-e8978268e15e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34778,7 +34794,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e91465e4-9677-46e9-a7c0-79b2df9721cf}</x14:id>
+          <x14:id>{387e25c9-6589-44fd-aed4-0f87bb25d089}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34800,7 +34816,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b0c355f-6356-46e3-b3bb-263ce215eb35}</x14:id>
+          <x14:id>{73cccead-f693-4f43-96d7-fc40c955bf34}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34822,7 +34838,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc66bd22-1ad1-4dc3-891a-c4b9dc441d47}</x14:id>
+          <x14:id>{593c8eee-d3c7-49c0-ab72-4018a4cf05e4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34844,7 +34860,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a72ac834-f008-4864-9f0e-9afa47fd9f96}</x14:id>
+          <x14:id>{580cfa89-22cf-4e7e-bc02-1e377432a31e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34866,7 +34882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aabd55cc-5f8b-411e-bb2b-45b627cb3427}</x14:id>
+          <x14:id>{d384058b-dde2-4846-92e3-75b60686b6ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34888,7 +34904,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dceea5a4-6f98-488e-b3c9-631b0c7375aa}</x14:id>
+          <x14:id>{7f2c284b-6441-48b3-8847-5b7191cbb28c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34910,7 +34926,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{afa9176d-cb45-4bdc-a0fb-7c057f35387c}</x14:id>
+          <x14:id>{940e93fb-05d1-4da0-9de4-eb48c48ea6d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34932,7 +34948,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1c79e514-5174-4171-acce-1eb583805675}</x14:id>
+          <x14:id>{c0f46bfa-84c5-41ec-85ef-a7a2f6017360}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34951,7 +34967,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2b372ea0-c8c3-4025-ac02-95ef43bd7aa4}">
+          <x14:cfRule type="dataBar" id="{c66c34d8-42e3-4fd2-a437-013d0d51c7c7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34964,7 +34980,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3631410c-2496-49ab-9717-18e104bb7b9c}">
+          <x14:cfRule type="dataBar" id="{71281b02-bb53-4eae-91b4-c7512c992a7f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34977,7 +34993,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b71e021a-732f-4807-b25a-ded3c58f7b5c}">
+          <x14:cfRule type="dataBar" id="{07fd883f-0910-4556-9971-9237229fc13a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34990,7 +35006,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b20273a-088c-434e-ace2-ecd804034422}">
+          <x14:cfRule type="dataBar" id="{477549b2-32be-4d87-be90-471ec5daac6f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35003,7 +35019,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86391aa7-d2de-4240-990d-70d40416d7f1}">
+          <x14:cfRule type="dataBar" id="{55f993d2-dbda-4389-8cfe-2c3616821598}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35016,7 +35032,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{128e276d-40ab-47a1-a841-20a7ecfaa466}">
+          <x14:cfRule type="dataBar" id="{a92d7651-804e-42e0-b4b3-4d02d3d4623f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35029,7 +35045,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{31143cc1-3ec0-4c1b-889b-0827eb0f2f5e}">
+          <x14:cfRule type="dataBar" id="{74340dfa-ae4b-430c-919d-fe193f0f5c27}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35042,7 +35058,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ff30b59-e48e-47d6-9c04-1a5526f34a3b}">
+          <x14:cfRule type="dataBar" id="{a132e647-b7de-499c-abe5-d99308cb7d98}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35055,7 +35071,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a75f5154-167c-4694-822e-e28188d575e2}">
+          <x14:cfRule type="dataBar" id="{319440c2-b417-4447-a80f-9715efabb5a4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35068,7 +35084,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0764e775-d1d6-4b3f-9128-4bd099a8fa3e}">
+          <x14:cfRule type="dataBar" id="{e3be99c9-0579-4a76-8126-76bb62038bda}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35081,7 +35097,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c597c3b8-9d74-4b28-ae5b-9e5290bcea12}">
+          <x14:cfRule type="dataBar" id="{6ca5ba9b-9368-49c7-ae1f-22e399276695}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35094,7 +35110,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8c0fa425-5e8a-45d5-baba-8772e10e3002}">
+          <x14:cfRule type="dataBar" id="{a9154d54-b61b-406e-bfdd-a4043eca2256}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35107,7 +35123,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7558eb0f-0043-4e3d-b950-f00b92ba6b80}">
+          <x14:cfRule type="dataBar" id="{1b5ed58f-423c-490d-a9af-c6d8cc461d6a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35120,7 +35136,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f86e63ff-70d9-4f26-8248-1c7f5f23349f}">
+          <x14:cfRule type="dataBar" id="{6bfedf94-ce14-473e-94b7-701ea742e258}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35133,7 +35149,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dccbc567-38b6-4ea7-9b6c-977d6ec4d1cf}">
+          <x14:cfRule type="dataBar" id="{1002119b-e37e-4d01-b43d-fc9f9b5fd223}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35146,7 +35162,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{06019503-b0d5-44be-8513-284581630bc8}">
+          <x14:cfRule type="dataBar" id="{ff4e9bb1-2e61-4330-a000-68f8dbcc3fe7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35159,7 +35175,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b0bf7b27-5383-4098-81fe-e2ec9e55a2ba}">
+          <x14:cfRule type="dataBar" id="{9398cef7-719c-44d2-aefb-d7f2af7ba778}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35172,7 +35188,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c36ea44-7366-4430-92ed-5a690ec43b57}">
+          <x14:cfRule type="dataBar" id="{90abb60f-2161-48d3-9198-3cf88649f2ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35185,7 +35201,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f9105e5a-2d4e-4ea7-af2f-82c3976e0d32}">
+          <x14:cfRule type="dataBar" id="{12e6087e-fdf2-40bb-98f7-67e1476624a1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35198,7 +35214,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dcdd1138-6bdf-4e13-9e87-99497a53b9ec}">
+          <x14:cfRule type="dataBar" id="{cadfbfa6-5b7e-4375-b287-b1700f291b50}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35211,7 +35227,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{daf4fc40-9e01-46d4-8784-121d6c17fe8e}">
+          <x14:cfRule type="dataBar" id="{e45a22f0-6dda-46ef-a991-87c1d42bbf9f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35224,7 +35240,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a86aeb5-3fb2-4638-8314-87cca6e8e285}">
+          <x14:cfRule type="dataBar" id="{b37b0669-1ceb-46dd-972b-53f6e183d37d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35237,7 +35253,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b6882efa-a013-49b2-bfea-b15bb5604fcd}">
+          <x14:cfRule type="dataBar" id="{062eb8fb-4b8c-4fd6-8430-9e7626515874}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35250,7 +35266,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{97a772f8-17f5-4dcf-a9eb-f797c1ed9acc}">
+          <x14:cfRule type="dataBar" id="{1dc959e4-6611-4a23-8645-e8978268e15e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35263,7 +35279,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e91465e4-9677-46e9-a7c0-79b2df9721cf}">
+          <x14:cfRule type="dataBar" id="{387e25c9-6589-44fd-aed4-0f87bb25d089}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35276,7 +35292,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b0c355f-6356-46e3-b3bb-263ce215eb35}">
+          <x14:cfRule type="dataBar" id="{73cccead-f693-4f43-96d7-fc40c955bf34}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35289,7 +35305,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc66bd22-1ad1-4dc3-891a-c4b9dc441d47}">
+          <x14:cfRule type="dataBar" id="{593c8eee-d3c7-49c0-ab72-4018a4cf05e4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35302,7 +35318,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a72ac834-f008-4864-9f0e-9afa47fd9f96}">
+          <x14:cfRule type="dataBar" id="{580cfa89-22cf-4e7e-bc02-1e377432a31e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35315,7 +35331,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aabd55cc-5f8b-411e-bb2b-45b627cb3427}">
+          <x14:cfRule type="dataBar" id="{d384058b-dde2-4846-92e3-75b60686b6ad}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35328,7 +35344,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dceea5a4-6f98-488e-b3c9-631b0c7375aa}">
+          <x14:cfRule type="dataBar" id="{7f2c284b-6441-48b3-8847-5b7191cbb28c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35341,7 +35357,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{afa9176d-cb45-4bdc-a0fb-7c057f35387c}">
+          <x14:cfRule type="dataBar" id="{940e93fb-05d1-4da0-9de4-eb48c48ea6d4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35354,7 +35370,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1c79e514-5174-4171-acce-1eb583805675}">
+          <x14:cfRule type="dataBar" id="{c0f46bfa-84c5-41ec-85ef-a7a2f6017360}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36249,7 +36265,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>51320.92</v>
+        <v>128365.37</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -36280,7 +36296,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.0492570860468194</v>
+        <v>0.123203248802278</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -36381,7 +36397,7 @@
       </c>
       <c r="G7" s="36">
         <f>[3]总目标!F32+[3]总目标!F33+[3]总目标!F34+[3]总目标!F35+[3]总目标!F36</f>
-        <v>51320.92</v>
+        <v>128365.37</v>
       </c>
       <c r="H7" s="36">
         <f>[3]总目标!G32+[3]总目标!G33+[3]总目标!G34+[3]总目标!G35+[3]总目标!G36</f>
@@ -36413,7 +36429,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>51320.92</v>
+        <v>128365.37</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -36439,7 +36455,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.203860891393204</v>
+        <v>0.509902759970367</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -36471,7 +36487,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.00951244667571283</v>
+        <v>0.0237928068540694</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -37006,7 +37022,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>100441.56</v>
+        <v>260185.41</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -37037,7 +37053,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.0808026776592133</v>
+        <v>0.209312537717059</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -37137,8 +37153,8 @@
         <v>0</v>
       </c>
       <c r="G7" s="36">
-        <f>[3]总目标!F45+[3]总目标!F46+[3]总目标!F47+[3]总目标!F48+[3]总目标!F49</f>
-        <v>100441.56</v>
+        <f>SUM([3]总目标!F45:F49)</f>
+        <v>260185.41</v>
       </c>
       <c r="H7" s="36">
         <f>[3]总目标!G45+[3]总目标!G46+[3]总目标!G47+[3]总目标!G48+[3]总目标!G49</f>
@@ -37170,7 +37186,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>100441.56</v>
+        <v>260185.41</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -37196,7 +37212,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.229146692928868</v>
+        <v>0.59358522756757</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -37228,7 +37244,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.0186093164517658</v>
+        <v>0.0482058684753844</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -37763,7 +37779,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>408656.49</v>
+        <v>466446.56</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -37794,7 +37810,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.274515558265613</v>
+        <v>0.313336117137097</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -37895,7 +37911,7 @@
       </c>
       <c r="G7" s="36">
         <f>[3]总目标!F59+[3]总目标!F60+[3]总目标!F61+[3]总目标!F62+[3]总目标!F63</f>
-        <v>45526.36</v>
+        <v>103316.43</v>
       </c>
       <c r="H7" s="36">
         <f>[3]总目标!G59+[3]总目标!G60+[3]总目标!G61+[3]总目标!G62+[3]总目标!G63</f>
@@ -37927,7 +37943,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>1776765.27</v>
+        <v>1834555.34</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -37953,7 +37969,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.0890312722609601</v>
+        <v>0.202045434960327</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -37985,7 +38001,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.300907437028025</v>
+        <v>0.310694583446848</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -38520,7 +38536,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>61883.12</v>
+        <v>64650.76</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -38551,7 +38567,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.125716501652577</v>
+        <v>0.131339004503658</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -38652,7 +38668,7 @@
       </c>
       <c r="G7" s="36">
         <f>[3]总目标!F71+[3]总目标!F72+[3]总目标!F73+[3]总目标!F74+[3]总目标!F75</f>
-        <v>12060.24</v>
+        <v>14827.88</v>
       </c>
       <c r="H7" s="36">
         <f>[3]总目标!G71+[3]总目标!G72+[3]总目标!G73+[3]总目标!G74+[3]总目标!G75</f>
@@ -38684,7 +38700,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>128503.9</v>
+        <v>131271.54</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -38710,7 +38726,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.0617502234032139</v>
+        <v>0.0759209520371109</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -38742,7 +38758,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.0696826234837611</v>
+        <v>0.0711834060752513</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -40503,7 +40519,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{92d4e91a-35ed-4381-8654-e0d0bc145abe}</x14:id>
+          <x14:id>{a73d7887-8f77-479c-888d-59ec51df57c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40514,7 +40530,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{92d4e91a-35ed-4381-8654-e0d0bc145abe}">
+          <x14:cfRule type="dataBar" id="{a73d7887-8f77-479c-888d-59ec51df57c7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -22645,7 +22645,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{441caa18-3984-44fd-ab5c-475e08fdb1ea}</x14:id>
+          <x14:id>{1804f7e3-3366-4bb1-bf39-66ab8996a6c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22659,7 +22659,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84f5b97e-28cc-4adf-83d4-2067a37f8c7c}</x14:id>
+          <x14:id>{478c92f3-5af4-4236-a0d1-46fa000a0afa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22673,7 +22673,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{02a3b66d-5dd4-4c38-92c1-37d396796232}</x14:id>
+          <x14:id>{2f43dc17-1637-4c9a-b593-768fea077ece}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22687,7 +22687,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e823004d-fea1-4b91-a74f-864809548dc9}</x14:id>
+          <x14:id>{97d36a74-fa09-4b0a-9d09-b474d578411b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22701,7 +22701,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2854665e-094c-4962-988a-c9fa72d81bee}</x14:id>
+          <x14:id>{73e15cdd-ea1b-448b-a75a-3beaaf62dc6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22715,7 +22715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{21702da6-bcfc-48fb-8727-846cb8c0b091}</x14:id>
+          <x14:id>{4e0de5d3-b5a2-4807-a072-33dc520608e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22729,7 +22729,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6045cd6d-72c0-4da4-a94d-37f0498a1da7}</x14:id>
+          <x14:id>{5212b628-9392-42ea-ad1c-27276b59a803}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22743,7 +22743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{087d7567-87be-4f1a-97f0-4981aa737d2e}</x14:id>
+          <x14:id>{d0b20bab-eb5a-4cba-90f5-3e69e1b03680}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22757,7 +22757,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{529fc87a-ab26-4b3c-aeb9-69e44db7adee}</x14:id>
+          <x14:id>{2ec5c191-ad8d-4adb-9027-7a02aa9e90c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22771,7 +22771,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{46d1a7e9-7892-4f02-adde-1b38118277db}</x14:id>
+          <x14:id>{d6679753-be64-49a4-bbf6-276f187c3dee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22785,7 +22785,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1a75805-6cc7-40df-9f00-f1fdb4a65bff}</x14:id>
+          <x14:id>{107b4a17-2882-459a-a56a-7242f0ba89aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22799,7 +22799,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98e04a55-6e2c-41b9-8fb6-d9e7ad35af44}</x14:id>
+          <x14:id>{99aee82d-93d9-4c0c-ab63-84e6c87cbaef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22813,7 +22813,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c88929bb-5552-4aca-a1d7-62f80ef9cc6e}</x14:id>
+          <x14:id>{650dbb92-fd84-47e3-89bb-f3eec0b8ac41}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22835,7 +22835,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a543ee3-cd3b-4f48-b7ac-586d3a8e9d7d}</x14:id>
+          <x14:id>{e4b0ab3e-96e8-4b9e-a4a9-895f91ada549}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22865,7 +22865,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5bf450ec-c0cb-4bc0-90f0-e2e1acae1783}</x14:id>
+          <x14:id>{16562431-39cb-4400-a883-a9f4e425f633}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22895,7 +22895,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{152fc664-b7ed-4a44-8c09-304728896be6}</x14:id>
+          <x14:id>{ff576e64-7f60-4d19-b816-d2fa2534fafa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22925,7 +22925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{badeace3-ad15-4072-bd17-b5bc69d19870}</x14:id>
+          <x14:id>{f58e48f7-3ae8-4de9-9028-61685d049b0e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22955,7 +22955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23f21ef8-6a57-43da-9d86-14d027bb935d}</x14:id>
+          <x14:id>{63691d63-f48d-4f5a-91f9-d99c8eede18e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22985,7 +22985,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03a6ecb6-529f-467d-b6ae-5cf20b3478e8}</x14:id>
+          <x14:id>{9c5647c6-f4aa-4796-ad42-369de0bbc81b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23015,7 +23015,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2bc47293-5270-4144-8d97-db6463cb2215}</x14:id>
+          <x14:id>{12dfcd1a-935a-42d5-9827-1f6cbd2ae787}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23045,7 +23045,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be9775c1-3ae6-45f0-9cdb-00e0b167d0d2}</x14:id>
+          <x14:id>{dd357165-ca75-4f95-a7b4-87e3437de8e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23067,7 +23067,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a71a036a-ae3a-4f6a-a3e6-f57d3c69da84}</x14:id>
+          <x14:id>{752cedfa-91b1-4653-ac34-2892ae09d839}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23089,7 +23089,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{023554ef-8348-4313-b2e3-516c2ba1b06b}</x14:id>
+          <x14:id>{9e3b5057-6f06-47bf-a181-5ba17fc798ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23111,7 +23111,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b3a158a3-91a1-4c10-96bc-49bec9c5b9e6}</x14:id>
+          <x14:id>{c9955b47-50e3-4bb5-890f-33b8ba2b50ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23133,7 +23133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c580add1-1fda-4344-ae32-a7ac5a207fdb}</x14:id>
+          <x14:id>{1534b01c-7953-4901-947c-127152edabaa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23155,7 +23155,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75b77aca-6c8e-4ba1-835e-339794222b05}</x14:id>
+          <x14:id>{0e8fe23c-d2ff-489b-ba25-bd45c1722a8c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23177,7 +23177,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0fc18f7d-82e7-4e45-912a-033c07a7d3e7}</x14:id>
+          <x14:id>{9db9b713-1254-463d-992f-e3208e55daff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23199,7 +23199,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84faed7e-692a-4169-8601-365a4fb4ea28}</x14:id>
+          <x14:id>{51623147-37b1-4c1c-9879-1db827bca8d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23221,7 +23221,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62e62921-34d7-498a-99cc-a1a674fe2f53}</x14:id>
+          <x14:id>{aba5af49-bfba-4cfe-afbb-dde443802d9e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23243,7 +23243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a7cd340-6297-410a-8a5d-a2a37a22b873}</x14:id>
+          <x14:id>{29f6ad11-8775-4b95-b84c-60378be1e9f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23265,7 +23265,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b114736c-4117-454c-8ef3-a8ac69ac4d40}</x14:id>
+          <x14:id>{49a72d66-9c5b-4fda-bf11-1424d576c5e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23287,7 +23287,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4c930bee-07fc-4ce0-a35a-ab61eb6777ae}</x14:id>
+          <x14:id>{cf920bbb-c2ef-4d98-b6ac-e28ab3a8d955}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23309,7 +23309,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a050d28a-e48a-42dd-8b6d-e7e08009a353}</x14:id>
+          <x14:id>{1b914219-4efa-438a-a333-22e433e2c85e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23328,7 +23328,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{441caa18-3984-44fd-ab5c-475e08fdb1ea}">
+          <x14:cfRule type="dataBar" id="{1804f7e3-3366-4bb1-bf39-66ab8996a6c3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23341,7 +23341,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{84f5b97e-28cc-4adf-83d4-2067a37f8c7c}">
+          <x14:cfRule type="dataBar" id="{478c92f3-5af4-4236-a0d1-46fa000a0afa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23354,7 +23354,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{02a3b66d-5dd4-4c38-92c1-37d396796232}">
+          <x14:cfRule type="dataBar" id="{2f43dc17-1637-4c9a-b593-768fea077ece}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23367,7 +23367,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e823004d-fea1-4b91-a74f-864809548dc9}">
+          <x14:cfRule type="dataBar" id="{97d36a74-fa09-4b0a-9d09-b474d578411b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23380,7 +23380,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2854665e-094c-4962-988a-c9fa72d81bee}">
+          <x14:cfRule type="dataBar" id="{73e15cdd-ea1b-448b-a75a-3beaaf62dc6c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23393,7 +23393,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{21702da6-bcfc-48fb-8727-846cb8c0b091}">
+          <x14:cfRule type="dataBar" id="{4e0de5d3-b5a2-4807-a072-33dc520608e5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23406,7 +23406,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6045cd6d-72c0-4da4-a94d-37f0498a1da7}">
+          <x14:cfRule type="dataBar" id="{5212b628-9392-42ea-ad1c-27276b59a803}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23419,7 +23419,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{087d7567-87be-4f1a-97f0-4981aa737d2e}">
+          <x14:cfRule type="dataBar" id="{d0b20bab-eb5a-4cba-90f5-3e69e1b03680}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23432,7 +23432,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{529fc87a-ab26-4b3c-aeb9-69e44db7adee}">
+          <x14:cfRule type="dataBar" id="{2ec5c191-ad8d-4adb-9027-7a02aa9e90c4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23445,7 +23445,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{46d1a7e9-7892-4f02-adde-1b38118277db}">
+          <x14:cfRule type="dataBar" id="{d6679753-be64-49a4-bbf6-276f187c3dee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23458,7 +23458,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c1a75805-6cc7-40df-9f00-f1fdb4a65bff}">
+          <x14:cfRule type="dataBar" id="{107b4a17-2882-459a-a56a-7242f0ba89aa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23471,7 +23471,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98e04a55-6e2c-41b9-8fb6-d9e7ad35af44}">
+          <x14:cfRule type="dataBar" id="{99aee82d-93d9-4c0c-ab63-84e6c87cbaef}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23484,7 +23484,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c88929bb-5552-4aca-a1d7-62f80ef9cc6e}">
+          <x14:cfRule type="dataBar" id="{650dbb92-fd84-47e3-89bb-f3eec0b8ac41}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23497,7 +23497,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6a543ee3-cd3b-4f48-b7ac-586d3a8e9d7d}">
+          <x14:cfRule type="dataBar" id="{e4b0ab3e-96e8-4b9e-a4a9-895f91ada549}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23510,7 +23510,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5bf450ec-c0cb-4bc0-90f0-e2e1acae1783}">
+          <x14:cfRule type="dataBar" id="{16562431-39cb-4400-a883-a9f4e425f633}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23523,7 +23523,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{152fc664-b7ed-4a44-8c09-304728896be6}">
+          <x14:cfRule type="dataBar" id="{ff576e64-7f60-4d19-b816-d2fa2534fafa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23536,7 +23536,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{badeace3-ad15-4072-bd17-b5bc69d19870}">
+          <x14:cfRule type="dataBar" id="{f58e48f7-3ae8-4de9-9028-61685d049b0e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23549,7 +23549,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23f21ef8-6a57-43da-9d86-14d027bb935d}">
+          <x14:cfRule type="dataBar" id="{63691d63-f48d-4f5a-91f9-d99c8eede18e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23562,7 +23562,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{03a6ecb6-529f-467d-b6ae-5cf20b3478e8}">
+          <x14:cfRule type="dataBar" id="{9c5647c6-f4aa-4796-ad42-369de0bbc81b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23575,7 +23575,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2bc47293-5270-4144-8d97-db6463cb2215}">
+          <x14:cfRule type="dataBar" id="{12dfcd1a-935a-42d5-9827-1f6cbd2ae787}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23588,7 +23588,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{be9775c1-3ae6-45f0-9cdb-00e0b167d0d2}">
+          <x14:cfRule type="dataBar" id="{dd357165-ca75-4f95-a7b4-87e3437de8e8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23601,7 +23601,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a71a036a-ae3a-4f6a-a3e6-f57d3c69da84}">
+          <x14:cfRule type="dataBar" id="{752cedfa-91b1-4653-ac34-2892ae09d839}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23614,7 +23614,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{023554ef-8348-4313-b2e3-516c2ba1b06b}">
+          <x14:cfRule type="dataBar" id="{9e3b5057-6f06-47bf-a181-5ba17fc798ce}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23627,7 +23627,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b3a158a3-91a1-4c10-96bc-49bec9c5b9e6}">
+          <x14:cfRule type="dataBar" id="{c9955b47-50e3-4bb5-890f-33b8ba2b50ed}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23640,7 +23640,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c580add1-1fda-4344-ae32-a7ac5a207fdb}">
+          <x14:cfRule type="dataBar" id="{1534b01c-7953-4901-947c-127152edabaa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23653,7 +23653,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75b77aca-6c8e-4ba1-835e-339794222b05}">
+          <x14:cfRule type="dataBar" id="{0e8fe23c-d2ff-489b-ba25-bd45c1722a8c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23666,7 +23666,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0fc18f7d-82e7-4e45-912a-033c07a7d3e7}">
+          <x14:cfRule type="dataBar" id="{9db9b713-1254-463d-992f-e3208e55daff}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23679,7 +23679,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{84faed7e-692a-4169-8601-365a4fb4ea28}">
+          <x14:cfRule type="dataBar" id="{51623147-37b1-4c1c-9879-1db827bca8d4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23692,7 +23692,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62e62921-34d7-498a-99cc-a1a674fe2f53}">
+          <x14:cfRule type="dataBar" id="{aba5af49-bfba-4cfe-afbb-dde443802d9e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23705,7 +23705,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6a7cd340-6297-410a-8a5d-a2a37a22b873}">
+          <x14:cfRule type="dataBar" id="{29f6ad11-8775-4b95-b84c-60378be1e9f1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23718,7 +23718,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b114736c-4117-454c-8ef3-a8ac69ac4d40}">
+          <x14:cfRule type="dataBar" id="{49a72d66-9c5b-4fda-bf11-1424d576c5e3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23731,7 +23731,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4c930bee-07fc-4ce0-a35a-ab61eb6777ae}">
+          <x14:cfRule type="dataBar" id="{cf920bbb-c2ef-4d98-b6ac-e28ab3a8d955}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23744,7 +23744,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a050d28a-e48a-42dd-8b6d-e7e08009a353}">
+          <x14:cfRule type="dataBar" id="{1b914219-4efa-438a-a333-22e433e2c85e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34308,7 +34308,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c66c34d8-42e3-4fd2-a437-013d0d51c7c7}</x14:id>
+          <x14:id>{062a3a6d-72b6-4230-bb4d-fa9666034505}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34322,7 +34322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71281b02-bb53-4eae-91b4-c7512c992a7f}</x14:id>
+          <x14:id>{b36333ca-9fd5-47a9-89e4-71ffa5a4aed6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34336,7 +34336,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{07fd883f-0910-4556-9971-9237229fc13a}</x14:id>
+          <x14:id>{f34c8460-4591-4af7-96ff-f70c1e64e2fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34350,7 +34350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{477549b2-32be-4d87-be90-471ec5daac6f}</x14:id>
+          <x14:id>{4a170552-a4cf-48c5-84f5-01aba45dd39a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34364,7 +34364,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55f993d2-dbda-4389-8cfe-2c3616821598}</x14:id>
+          <x14:id>{d229eb8e-b1c9-42a3-8714-5e62fcfdb59f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34378,7 +34378,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a92d7651-804e-42e0-b4b3-4d02d3d4623f}</x14:id>
+          <x14:id>{6bbb3c63-ab75-4259-a608-cc436ddfec84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34398,7 +34398,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74340dfa-ae4b-430c-919d-fe193f0f5c27}</x14:id>
+          <x14:id>{1ca4d0ad-9e00-4726-b503-71376030acaa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34412,7 +34412,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a132e647-b7de-499c-abe5-d99308cb7d98}</x14:id>
+          <x14:id>{94b061ee-bff8-4234-9b69-035f98693438}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34426,7 +34426,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{319440c2-b417-4447-a80f-9715efabb5a4}</x14:id>
+          <x14:id>{52ac152c-e6e2-4e1b-99af-7dbfc1981505}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34440,7 +34440,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3be99c9-0579-4a76-8126-76bb62038bda}</x14:id>
+          <x14:id>{345ffe5b-b48f-429d-b47f-320b29bc0360}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34454,7 +34454,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ca5ba9b-9368-49c7-ae1f-22e399276695}</x14:id>
+          <x14:id>{b7cd9f26-3e27-4e8e-ae61-89989088a932}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34468,7 +34468,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9154d54-b61b-406e-bfdd-a4043eca2256}</x14:id>
+          <x14:id>{e536f0fc-29d4-4100-938f-ae3b51b1f4db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34490,7 +34490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b5ed58f-423c-490d-a9af-c6d8cc461d6a}</x14:id>
+          <x14:id>{fff15cc7-a51e-4958-ad6b-d6a06e1c0b38}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34520,7 +34520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6bfedf94-ce14-473e-94b7-701ea742e258}</x14:id>
+          <x14:id>{dbcb3dfd-4001-44ea-b584-001c8b1ffd79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34550,7 +34550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1002119b-e37e-4d01-b43d-fc9f9b5fd223}</x14:id>
+          <x14:id>{b38aa4dd-b213-4e49-a128-3f7c1e397d9f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34580,7 +34580,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ff4e9bb1-2e61-4330-a000-68f8dbcc3fe7}</x14:id>
+          <x14:id>{5f4ff00d-dbaa-4f7e-9fd9-95e112173f8a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34610,7 +34610,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9398cef7-719c-44d2-aefb-d7f2af7ba778}</x14:id>
+          <x14:id>{47363c4c-c339-4ec1-a5dd-d1791ae68057}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34640,7 +34640,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90abb60f-2161-48d3-9198-3cf88649f2ee}</x14:id>
+          <x14:id>{5a1d23d1-0a64-4892-bdce-228f660268c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34662,7 +34662,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12e6087e-fdf2-40bb-98f7-67e1476624a1}</x14:id>
+          <x14:id>{462c3fad-25e8-4ae3-a95c-b7770fee264a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34684,7 +34684,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cadfbfa6-5b7e-4375-b287-b1700f291b50}</x14:id>
+          <x14:id>{f979b91f-a2a4-47b2-81d2-382f1b9ef82f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34706,7 +34706,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e45a22f0-6dda-46ef-a991-87c1d42bbf9f}</x14:id>
+          <x14:id>{70d60f34-1578-4270-ad9c-89f55a59b83f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34728,7 +34728,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b37b0669-1ceb-46dd-972b-53f6e183d37d}</x14:id>
+          <x14:id>{48e6612c-97df-43fb-87f1-a0b9bf531f6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34750,7 +34750,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{062eb8fb-4b8c-4fd6-8430-9e7626515874}</x14:id>
+          <x14:id>{f10672a5-5024-4401-9d40-3bbfaaaff302}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34772,7 +34772,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1dc959e4-6611-4a23-8645-e8978268e15e}</x14:id>
+          <x14:id>{93e36254-ad4c-4422-9e8c-97a296409f69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34794,7 +34794,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{387e25c9-6589-44fd-aed4-0f87bb25d089}</x14:id>
+          <x14:id>{2686627b-7afc-40d9-8abd-800c5da752bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34816,7 +34816,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73cccead-f693-4f43-96d7-fc40c955bf34}</x14:id>
+          <x14:id>{11099acc-46b9-4b7c-9686-188e715cf273}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34838,7 +34838,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{593c8eee-d3c7-49c0-ab72-4018a4cf05e4}</x14:id>
+          <x14:id>{975a1405-eb3e-4f78-886b-f2a0532f2841}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34860,7 +34860,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{580cfa89-22cf-4e7e-bc02-1e377432a31e}</x14:id>
+          <x14:id>{727c82c2-c91d-483f-8ece-57f3e7ae5a14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34882,7 +34882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d384058b-dde2-4846-92e3-75b60686b6ad}</x14:id>
+          <x14:id>{8ecfbbb0-c27c-42f6-bf88-efa7bd9b5a99}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34904,7 +34904,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f2c284b-6441-48b3-8847-5b7191cbb28c}</x14:id>
+          <x14:id>{6e4eef42-2b6f-4726-92ee-09695918e9e4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34926,7 +34926,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{940e93fb-05d1-4da0-9de4-eb48c48ea6d4}</x14:id>
+          <x14:id>{fdb95b6c-53cb-4857-8bbc-5040202e9834}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34948,7 +34948,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0f46bfa-84c5-41ec-85ef-a7a2f6017360}</x14:id>
+          <x14:id>{e1f65c02-9738-4732-a8c5-2bbd9c5ce6f3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34967,7 +34967,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c66c34d8-42e3-4fd2-a437-013d0d51c7c7}">
+          <x14:cfRule type="dataBar" id="{062a3a6d-72b6-4230-bb4d-fa9666034505}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34980,7 +34980,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71281b02-bb53-4eae-91b4-c7512c992a7f}">
+          <x14:cfRule type="dataBar" id="{b36333ca-9fd5-47a9-89e4-71ffa5a4aed6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34993,7 +34993,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{07fd883f-0910-4556-9971-9237229fc13a}">
+          <x14:cfRule type="dataBar" id="{f34c8460-4591-4af7-96ff-f70c1e64e2fb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35006,7 +35006,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{477549b2-32be-4d87-be90-471ec5daac6f}">
+          <x14:cfRule type="dataBar" id="{4a170552-a4cf-48c5-84f5-01aba45dd39a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35019,7 +35019,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55f993d2-dbda-4389-8cfe-2c3616821598}">
+          <x14:cfRule type="dataBar" id="{d229eb8e-b1c9-42a3-8714-5e62fcfdb59f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35032,7 +35032,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a92d7651-804e-42e0-b4b3-4d02d3d4623f}">
+          <x14:cfRule type="dataBar" id="{6bbb3c63-ab75-4259-a608-cc436ddfec84}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35045,7 +35045,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{74340dfa-ae4b-430c-919d-fe193f0f5c27}">
+          <x14:cfRule type="dataBar" id="{1ca4d0ad-9e00-4726-b503-71376030acaa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35058,7 +35058,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a132e647-b7de-499c-abe5-d99308cb7d98}">
+          <x14:cfRule type="dataBar" id="{94b061ee-bff8-4234-9b69-035f98693438}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35071,7 +35071,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{319440c2-b417-4447-a80f-9715efabb5a4}">
+          <x14:cfRule type="dataBar" id="{52ac152c-e6e2-4e1b-99af-7dbfc1981505}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35084,7 +35084,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3be99c9-0579-4a76-8126-76bb62038bda}">
+          <x14:cfRule type="dataBar" id="{345ffe5b-b48f-429d-b47f-320b29bc0360}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35097,7 +35097,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ca5ba9b-9368-49c7-ae1f-22e399276695}">
+          <x14:cfRule type="dataBar" id="{b7cd9f26-3e27-4e8e-ae61-89989088a932}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35110,7 +35110,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a9154d54-b61b-406e-bfdd-a4043eca2256}">
+          <x14:cfRule type="dataBar" id="{e536f0fc-29d4-4100-938f-ae3b51b1f4db}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35123,7 +35123,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b5ed58f-423c-490d-a9af-c6d8cc461d6a}">
+          <x14:cfRule type="dataBar" id="{fff15cc7-a51e-4958-ad6b-d6a06e1c0b38}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35136,7 +35136,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6bfedf94-ce14-473e-94b7-701ea742e258}">
+          <x14:cfRule type="dataBar" id="{dbcb3dfd-4001-44ea-b584-001c8b1ffd79}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35149,7 +35149,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1002119b-e37e-4d01-b43d-fc9f9b5fd223}">
+          <x14:cfRule type="dataBar" id="{b38aa4dd-b213-4e49-a128-3f7c1e397d9f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35162,7 +35162,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ff4e9bb1-2e61-4330-a000-68f8dbcc3fe7}">
+          <x14:cfRule type="dataBar" id="{5f4ff00d-dbaa-4f7e-9fd9-95e112173f8a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35175,7 +35175,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9398cef7-719c-44d2-aefb-d7f2af7ba778}">
+          <x14:cfRule type="dataBar" id="{47363c4c-c339-4ec1-a5dd-d1791ae68057}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35188,7 +35188,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90abb60f-2161-48d3-9198-3cf88649f2ee}">
+          <x14:cfRule type="dataBar" id="{5a1d23d1-0a64-4892-bdce-228f660268c0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35201,7 +35201,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{12e6087e-fdf2-40bb-98f7-67e1476624a1}">
+          <x14:cfRule type="dataBar" id="{462c3fad-25e8-4ae3-a95c-b7770fee264a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35214,7 +35214,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cadfbfa6-5b7e-4375-b287-b1700f291b50}">
+          <x14:cfRule type="dataBar" id="{f979b91f-a2a4-47b2-81d2-382f1b9ef82f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35227,7 +35227,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e45a22f0-6dda-46ef-a991-87c1d42bbf9f}">
+          <x14:cfRule type="dataBar" id="{70d60f34-1578-4270-ad9c-89f55a59b83f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35240,7 +35240,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b37b0669-1ceb-46dd-972b-53f6e183d37d}">
+          <x14:cfRule type="dataBar" id="{48e6612c-97df-43fb-87f1-a0b9bf531f6a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35253,7 +35253,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{062eb8fb-4b8c-4fd6-8430-9e7626515874}">
+          <x14:cfRule type="dataBar" id="{f10672a5-5024-4401-9d40-3bbfaaaff302}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35266,7 +35266,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1dc959e4-6611-4a23-8645-e8978268e15e}">
+          <x14:cfRule type="dataBar" id="{93e36254-ad4c-4422-9e8c-97a296409f69}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35279,7 +35279,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{387e25c9-6589-44fd-aed4-0f87bb25d089}">
+          <x14:cfRule type="dataBar" id="{2686627b-7afc-40d9-8abd-800c5da752bb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35292,7 +35292,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{73cccead-f693-4f43-96d7-fc40c955bf34}">
+          <x14:cfRule type="dataBar" id="{11099acc-46b9-4b7c-9686-188e715cf273}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35305,7 +35305,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{593c8eee-d3c7-49c0-ab72-4018a4cf05e4}">
+          <x14:cfRule type="dataBar" id="{975a1405-eb3e-4f78-886b-f2a0532f2841}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35318,7 +35318,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{580cfa89-22cf-4e7e-bc02-1e377432a31e}">
+          <x14:cfRule type="dataBar" id="{727c82c2-c91d-483f-8ece-57f3e7ae5a14}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35331,7 +35331,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d384058b-dde2-4846-92e3-75b60686b6ad}">
+          <x14:cfRule type="dataBar" id="{8ecfbbb0-c27c-42f6-bf88-efa7bd9b5a99}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35344,7 +35344,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7f2c284b-6441-48b3-8847-5b7191cbb28c}">
+          <x14:cfRule type="dataBar" id="{6e4eef42-2b6f-4726-92ee-09695918e9e4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35357,7 +35357,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{940e93fb-05d1-4da0-9de4-eb48c48ea6d4}">
+          <x14:cfRule type="dataBar" id="{fdb95b6c-53cb-4857-8bbc-5040202e9834}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35370,7 +35370,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c0f46bfa-84c5-41ec-85ef-a7a2f6017360}">
+          <x14:cfRule type="dataBar" id="{e1f65c02-9738-4732-a8c5-2bbd9c5ce6f3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -40519,7 +40519,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a73d7887-8f77-479c-888d-59ec51df57c7}</x14:id>
+          <x14:id>{abfec66d-841e-4daa-82fa-0a6ea9484560}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40530,7 +40530,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a73d7887-8f77-479c-888d-59ec51df57c7}">
+          <x14:cfRule type="dataBar" id="{abfec66d-841e-4daa-82fa-0a6ea9484560}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="6"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -2121,7 +2121,7 @@
         </row>
         <row r="4">
           <cell r="F4">
-            <v>593659.75</v>
+            <v>685638.02</v>
           </cell>
         </row>
         <row r="4">
@@ -2144,7 +2144,7 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>0.356947776694257</v>
+            <v>0.41225123794573</v>
           </cell>
         </row>
         <row r="5">
@@ -2222,7 +2222,7 @@
             <v>439950.57</v>
           </cell>
           <cell r="G7">
-            <v>153709.18</v>
+            <v>245687.45</v>
           </cell>
           <cell r="H7">
             <v>0</v>
@@ -2246,7 +2246,7 @@
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>1802674.09</v>
+            <v>1894652.36</v>
           </cell>
         </row>
         <row r="8">
@@ -2266,7 +2266,7 @@
             <v>0.737368736976622</v>
           </cell>
           <cell r="G8">
-            <v>0.293052150508833</v>
+            <v>0.468412072561518</v>
           </cell>
           <cell r="H8">
             <v>0</v>
@@ -2290,7 +2290,7 @@
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0.268255073594681</v>
+            <v>0.2819423161888</v>
           </cell>
         </row>
         <row r="10">
@@ -2354,7 +2354,7 @@
             <v>38346</v>
           </cell>
           <cell r="G11">
-            <v>12161</v>
+            <v>18360</v>
           </cell>
           <cell r="H11">
             <v>0</v>
@@ -2378,7 +2378,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>146618</v>
+            <v>152817</v>
           </cell>
         </row>
         <row r="12">
@@ -2398,7 +2398,7 @@
             <v>1.02909129944716</v>
           </cell>
           <cell r="G12">
-            <v>0.370722636304053</v>
+            <v>0.559696373862545</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -2422,7 +2422,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.347440711876914</v>
+            <v>0.36213048375298</v>
           </cell>
         </row>
         <row r="14">
@@ -2486,7 +2486,7 @@
             <v>10231</v>
           </cell>
           <cell r="G15">
-            <v>3303</v>
+            <v>5125</v>
           </cell>
           <cell r="H15">
             <v>0</v>
@@ -2510,7 +2510,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>39861</v>
+            <v>41683</v>
           </cell>
         </row>
         <row r="16">
@@ -2530,7 +2530,7 @@
             <v>0.854268345977926</v>
           </cell>
           <cell r="G16">
-            <v>0.315262144702347</v>
+            <v>0.489166966878452</v>
           </cell>
           <cell r="H16">
             <v>0</v>
@@ -2554,7 +2554,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.296513850058578</v>
+            <v>0.310067153658757</v>
           </cell>
         </row>
         <row r="18">
@@ -2618,7 +2618,7 @@
             <v>171823742</v>
           </cell>
           <cell r="G19">
-            <v>52162719</v>
+            <v>80026082</v>
           </cell>
           <cell r="H19">
             <v>0</v>
@@ -2642,7 +2642,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>654988759</v>
+            <v>682852122</v>
           </cell>
         </row>
         <row r="20">
@@ -2662,7 +2662,7 @@
             <v>1.14727804597092</v>
           </cell>
           <cell r="G20">
-            <v>0.394189576075033</v>
+            <v>0.604750824789748</v>
           </cell>
           <cell r="H20">
             <v>0</v>
@@ -2686,7 +2686,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.384632158433788</v>
+            <v>0.400994493366492</v>
           </cell>
         </row>
         <row r="22">
@@ -2750,7 +2750,7 @@
             <v>4070034.85</v>
           </cell>
           <cell r="G23">
-            <v>1371955.91</v>
+            <v>2129119.94</v>
           </cell>
           <cell r="H23">
             <v>0</v>
@@ -2774,7 +2774,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>15617526.45</v>
+            <v>16374690.48</v>
           </cell>
         </row>
         <row r="24">
@@ -2794,7 +2794,7 @@
             <v>1.05573509321019</v>
           </cell>
           <cell r="G24">
-            <v>0.402769326957713</v>
+            <v>0.625052305978292</v>
           </cell>
           <cell r="H24">
             <v>0</v>
@@ -2818,7 +2818,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.356283176276717</v>
+            <v>0.373556385733704</v>
           </cell>
         </row>
         <row r="26">
@@ -2838,7 +2838,7 @@
             <v>0.70390916276867</v>
           </cell>
           <cell r="G26">
-            <v>0.671231691833395</v>
+            <v>0.667433434389553</v>
           </cell>
           <cell r="H26" t="e">
             <v>#DIV/0!</v>
@@ -2862,7 +2862,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.701950487023549</v>
+            <v>0.700251892898123</v>
           </cell>
         </row>
         <row r="27">
@@ -2882,7 +2882,7 @@
             <v>0.733192510300944</v>
           </cell>
           <cell r="G27">
-            <v>0.728394046542225</v>
+            <v>0.720860566448802</v>
           </cell>
           <cell r="H27" t="e">
             <v>#DIV/0!</v>
@@ -2906,7 +2906,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.728130243217068</v>
+            <v>0.72723584417964</v>
           </cell>
         </row>
         <row r="28">
@@ -2926,7 +2926,7 @@
             <v>0.108095037564605</v>
           </cell>
           <cell r="G28">
-            <v>0.112036530386753</v>
+            <v>0.115393898382258</v>
           </cell>
           <cell r="H28" t="e">
             <v>#DIV/0!</v>
@@ -2950,7 +2950,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.11542635101476</v>
+            <v>0.115706147991873</v>
           </cell>
         </row>
         <row r="30">
@@ -2973,7 +2973,7 @@
             <v>51410.92</v>
           </cell>
           <cell r="G30">
-            <v>22183.88</v>
+            <v>40404.92</v>
           </cell>
           <cell r="H30">
             <v>0</v>
@@ -2997,7 +2997,7 @@
             <v>0</v>
           </cell>
           <cell r="O30">
-            <v>318070.04</v>
+            <v>336291.08</v>
           </cell>
         </row>
         <row r="31">
@@ -3017,7 +3017,7 @@
             <v>8430</v>
           </cell>
           <cell r="G31">
-            <v>2494</v>
+            <v>3924</v>
           </cell>
           <cell r="H31">
             <v>0</v>
@@ -3041,7 +3041,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>38432</v>
+            <v>39862</v>
           </cell>
         </row>
         <row r="32">
@@ -3061,7 +3061,7 @@
             <v>2131</v>
           </cell>
           <cell r="G32">
-            <v>690</v>
+            <v>1102</v>
           </cell>
           <cell r="H32">
             <v>0</v>
@@ -3085,7 +3085,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>9932</v>
+            <v>10344</v>
           </cell>
         </row>
         <row r="33">
@@ -3105,7 +3105,7 @@
             <v>35782129</v>
           </cell>
           <cell r="G33">
-            <v>10868656</v>
+            <v>17401062</v>
           </cell>
           <cell r="H33">
             <v>0</v>
@@ -3129,7 +3129,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>165151076</v>
+            <v>171683482</v>
           </cell>
         </row>
         <row r="34">
@@ -3149,7 +3149,7 @@
             <v>833536.12</v>
           </cell>
           <cell r="G34">
-            <v>280388.84</v>
+            <v>448257.72</v>
           </cell>
           <cell r="H34">
             <v>0</v>
@@ -3173,7 +3173,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>3802701.33</v>
+            <v>3970570.21</v>
           </cell>
         </row>
         <row r="35">
@@ -3193,7 +3193,7 @@
             <v>0.708815495578813</v>
           </cell>
           <cell r="G35">
-            <v>0.677525859683111</v>
+            <v>0.677995429244491</v>
           </cell>
           <cell r="H35" t="e">
             <v>#DIV/0!</v>
@@ -3217,7 +3217,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.712180097300728</v>
+            <v>0.710909127384777</v>
           </cell>
         </row>
         <row r="36">
@@ -3237,7 +3237,7 @@
             <v>0.747212336892052</v>
           </cell>
           <cell r="G36">
-            <v>0.723336006415397</v>
+            <v>0.719164118246687</v>
           </cell>
           <cell r="H36" t="e">
             <v>#DIV/0!</v>
@@ -3261,7 +3261,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.741569525395504</v>
+            <v>0.740504741357684</v>
           </cell>
         </row>
         <row r="37">
@@ -3281,7 +3281,7 @@
             <v>0.0616780950056489</v>
           </cell>
           <cell r="G37">
-            <v>0.0791182701850758</v>
+            <v>0.0901377002497581</v>
           </cell>
           <cell r="H37" t="e">
             <v>#DIV/0!</v>
@@ -3305,7 +3305,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.0836431821480968</v>
+            <v>0.0846959157536217</v>
           </cell>
         </row>
         <row r="38">
@@ -3328,7 +3328,7 @@
             <v>99083.11</v>
           </cell>
           <cell r="G38">
-            <v>51107.18</v>
+            <v>82894.22</v>
           </cell>
           <cell r="H38">
             <v>0</v>
@@ -3352,7 +3352,7 @@
             <v>0</v>
           </cell>
           <cell r="O38">
-            <v>509957.11</v>
+            <v>541744.15</v>
           </cell>
         </row>
         <row r="39">
@@ -3372,7 +3372,7 @@
             <v>8877</v>
           </cell>
           <cell r="G39">
-            <v>2859</v>
+            <v>4306</v>
           </cell>
           <cell r="H39">
             <v>0</v>
@@ -3396,7 +3396,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>37241</v>
+            <v>38688</v>
           </cell>
         </row>
         <row r="40">
@@ -3416,7 +3416,7 @@
             <v>2609</v>
           </cell>
           <cell r="G40">
-            <v>849</v>
+            <v>1321</v>
           </cell>
           <cell r="H40">
             <v>0</v>
@@ -3440,7 +3440,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>10706</v>
+            <v>11178</v>
           </cell>
         </row>
         <row r="41">
@@ -3460,7 +3460,7 @@
             <v>40066145</v>
           </cell>
           <cell r="G41">
-            <v>12095330</v>
+            <v>19014831</v>
           </cell>
           <cell r="H41">
             <v>0</v>
@@ -3484,7 +3484,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>165462794</v>
+            <v>172382295</v>
           </cell>
         </row>
         <row r="42">
@@ -3504,7 +3504,7 @@
             <v>1044149.57</v>
           </cell>
           <cell r="G42">
-            <v>354397</v>
+            <v>550511.23</v>
           </cell>
           <cell r="H42">
             <v>0</v>
@@ -3528,7 +3528,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>4228391.64</v>
+            <v>4424505.87</v>
           </cell>
         </row>
         <row r="43">
@@ -3548,7 +3548,7 @@
             <v>0.674241941045239</v>
           </cell>
           <cell r="G43">
-            <v>0.633746040827328</v>
+            <v>0.638104047572129</v>
           </cell>
           <cell r="H43" t="e">
             <v>#DIV/0!</v>
@@ -3572,7 +3572,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.6805632600402</v>
+            <v>0.679164711346951</v>
           </cell>
         </row>
         <row r="44">
@@ -3592,7 +3592,7 @@
             <v>0.706094401261687</v>
           </cell>
           <cell r="G44">
-            <v>0.703043022035677</v>
+            <v>0.693218764514631</v>
           </cell>
           <cell r="H44" t="e">
             <v>#DIV/0!</v>
@@ -3616,7 +3616,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.71252114604871</v>
+            <v>0.711073200992556</v>
           </cell>
         </row>
         <row r="45">
@@ -3636,7 +3636,7 @@
             <v>0.0948935984334122</v>
           </cell>
           <cell r="G45">
-            <v>0.14420883923961</v>
+            <v>0.150576801130833</v>
           </cell>
           <cell r="H45" t="e">
             <v>#DIV/0!</v>
@@ -3660,7 +3660,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.120603092952856</v>
+            <v>0.122441729295299</v>
           </cell>
         </row>
         <row r="46">
@@ -3683,7 +3683,7 @@
             <v>80999.07</v>
           </cell>
           <cell r="G46">
-            <v>26904.78</v>
+            <v>43907.28</v>
           </cell>
           <cell r="H46">
             <v>0</v>
@@ -3707,7 +3707,7 @@
             <v>0</v>
           </cell>
           <cell r="O46">
-            <v>171485.78</v>
+            <v>188488.28</v>
           </cell>
         </row>
         <row r="47">
@@ -3727,7 +3727,7 @@
             <v>6433</v>
           </cell>
           <cell r="G47">
-            <v>1885</v>
+            <v>2763</v>
           </cell>
           <cell r="H47">
             <v>0</v>
@@ -3751,7 +3751,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>20001</v>
+            <v>20879</v>
           </cell>
         </row>
         <row r="48">
@@ -3771,7 +3771,7 @@
             <v>1816</v>
           </cell>
           <cell r="G48">
-            <v>537</v>
+            <v>817</v>
           </cell>
           <cell r="H48">
             <v>0</v>
@@ -3795,7 +3795,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>5469</v>
+            <v>5749</v>
           </cell>
         </row>
         <row r="49">
@@ -3815,7 +3815,7 @@
             <v>26000920</v>
           </cell>
           <cell r="G49">
-            <v>7193090</v>
+            <v>10271075</v>
           </cell>
           <cell r="H49">
             <v>0</v>
@@ -3839,7 +3839,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>83969779</v>
+            <v>87047764</v>
           </cell>
         </row>
         <row r="50">
@@ -3859,7 +3859,7 @@
             <v>658949.99</v>
           </cell>
           <cell r="G50">
-            <v>201578.32</v>
+            <v>308382.58</v>
           </cell>
           <cell r="H50">
             <v>0</v>
@@ -3883,7 +3883,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>2024736.62</v>
+            <v>2131540.88</v>
           </cell>
         </row>
         <row r="51">
@@ -3903,7 +3903,7 @@
             <v>0.683208329743717</v>
           </cell>
           <cell r="G51">
-            <v>0.649701449585644</v>
+            <v>0.624695345910725</v>
           </cell>
           <cell r="H51" t="e">
             <v>#DIV/0!</v>
@@ -3927,7 +3927,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.698591468842618</v>
+            <v>0.69391217217251</v>
           </cell>
         </row>
         <row r="52">
@@ -3947,7 +3947,7 @@
             <v>0.717705580600031</v>
           </cell>
           <cell r="G52">
-            <v>0.715119363395226</v>
+            <v>0.704306912775968</v>
           </cell>
           <cell r="H52" t="e">
             <v>#DIV/0!</v>
@@ -3971,7 +3971,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.726563671816409</v>
+            <v>0.724651563772211</v>
           </cell>
         </row>
         <row r="53">
@@ -3991,7 +3991,7 @@
             <v>0.122921422307025</v>
           </cell>
           <cell r="G53">
-            <v>0.133470603386317</v>
+            <v>0.142379248529538</v>
           </cell>
           <cell r="H53" t="e">
             <v>#DIV/0!</v>
@@ -4015,7 +4015,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.0846953516354142</v>
+            <v>0.0884281797119462</v>
           </cell>
         </row>
         <row r="54">
@@ -4038,7 +4038,7 @@
             <v>53475.37</v>
           </cell>
           <cell r="G54">
-            <v>19796.35</v>
+            <v>36275.43</v>
           </cell>
           <cell r="H54">
             <v>0</v>
@@ -4062,7 +4062,7 @@
             <v>0</v>
           </cell>
           <cell r="O54">
-            <v>340742.77</v>
+            <v>357221.85</v>
           </cell>
         </row>
         <row r="55">
@@ -4082,7 +4082,7 @@
             <v>3410</v>
           </cell>
           <cell r="G55">
-            <v>878</v>
+            <v>1336</v>
           </cell>
           <cell r="H55">
             <v>0</v>
@@ -4106,7 +4106,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>16652</v>
+            <v>17110</v>
           </cell>
         </row>
         <row r="56">
@@ -4126,7 +4126,7 @@
             <v>1234</v>
           </cell>
           <cell r="G56">
-            <v>340</v>
+            <v>544</v>
           </cell>
           <cell r="H56">
             <v>0</v>
@@ -4150,7 +4150,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>6067</v>
+            <v>6271</v>
           </cell>
         </row>
         <row r="57">
@@ -4170,7 +4170,7 @@
             <v>13881751</v>
           </cell>
           <cell r="G57">
-            <v>3628095</v>
+            <v>5676332</v>
           </cell>
           <cell r="H57">
             <v>0</v>
@@ -4194,7 +4194,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>67344599</v>
+            <v>69392836</v>
           </cell>
         </row>
         <row r="58">
@@ -4214,7 +4214,7 @@
             <v>463880.75</v>
           </cell>
           <cell r="G58">
-            <v>134480.18</v>
+            <v>215716.27</v>
           </cell>
           <cell r="H58">
             <v>0</v>
@@ -4238,7 +4238,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2243133.66</v>
+            <v>2324369.75</v>
           </cell>
         </row>
         <row r="59">
@@ -4258,7 +4258,7 @@
             <v>0.582292653498827</v>
           </cell>
           <cell r="G59">
-            <v>0.536670828630452</v>
+            <v>0.524965527914858</v>
           </cell>
           <cell r="H59" t="e">
             <v>#DIV/0!</v>
@@ -4282,7 +4282,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.583646332944977</v>
+            <v>0.581302284936157</v>
           </cell>
         </row>
         <row r="60">
@@ -4302,7 +4302,7 @@
             <v>0.638123167155425</v>
           </cell>
           <cell r="G60">
-            <v>0.612756264236902</v>
+            <v>0.592814371257485</v>
           </cell>
           <cell r="H60" t="e">
             <v>#DIV/0!</v>
@@ -4326,7 +4326,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.635659380254624</v>
+            <v>0.633489187609585</v>
           </cell>
         </row>
         <row r="61">
@@ -4346,7 +4346,7 @@
             <v>0.115278269253467</v>
           </cell>
           <cell r="G61">
-            <v>0.147206450794459</v>
+            <v>0.168162698159022</v>
           </cell>
           <cell r="H61" t="e">
             <v>#DIV/0!</v>
@@ -4370,7 +4370,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.151904800001976</v>
+            <v>0.153685466780834</v>
           </cell>
         </row>
         <row r="62">
@@ -4393,7 +4393,7 @@
             <v>154982.1</v>
           </cell>
           <cell r="G62">
-            <v>33716.99</v>
+            <v>42205.6</v>
           </cell>
           <cell r="H62">
             <v>0</v>
@@ -4417,7 +4417,7 @@
             <v>0</v>
           </cell>
           <cell r="O62">
-            <v>462418.39</v>
+            <v>470907</v>
           </cell>
         </row>
         <row r="63">
@@ -4437,7 +4437,7 @@
             <v>11196</v>
           </cell>
           <cell r="G63">
-            <v>4045</v>
+            <v>6031</v>
           </cell>
           <cell r="H63">
             <v>0</v>
@@ -4461,7 +4461,7 @@
             <v>0</v>
           </cell>
           <cell r="O63">
-            <v>34292</v>
+            <v>36278</v>
           </cell>
         </row>
         <row r="64">
@@ -4481,7 +4481,7 @@
             <v>2441</v>
           </cell>
           <cell r="G64">
-            <v>887</v>
+            <v>1341</v>
           </cell>
           <cell r="H64">
             <v>0</v>
@@ -4505,7 +4505,7 @@
             <v>0</v>
           </cell>
           <cell r="O64">
-            <v>7687</v>
+            <v>8141</v>
           </cell>
         </row>
         <row r="65">
@@ -4525,7 +4525,7 @@
             <v>56092797</v>
           </cell>
           <cell r="G65">
-            <v>18377548</v>
+            <v>27662782</v>
           </cell>
           <cell r="H65">
             <v>0</v>
@@ -4549,7 +4549,7 @@
             <v>0</v>
           </cell>
           <cell r="O65">
-            <v>173060511</v>
+            <v>182345745</v>
           </cell>
         </row>
         <row r="66">
@@ -4569,7 +4569,7 @@
             <v>1069518.42</v>
           </cell>
           <cell r="G66">
-            <v>401111.57</v>
+            <v>606252.14</v>
           </cell>
           <cell r="H66">
             <v>0</v>
@@ -4593,7 +4593,7 @@
             <v>0</v>
           </cell>
           <cell r="O66">
-            <v>3318563.2</v>
+            <v>3523703.77</v>
           </cell>
         </row>
         <row r="67">
@@ -4613,7 +4613,7 @@
             <v>0.761663155253249</v>
           </cell>
           <cell r="G67">
-            <v>0.727172818430402</v>
+            <v>0.726052435723927</v>
           </cell>
           <cell r="H67" t="e">
             <v>#DIV/0!</v>
@@ -4637,7 +4637,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O67">
-            <v>0.760303261788011</v>
+            <v>0.758446257547715</v>
           </cell>
         </row>
         <row r="68">
@@ -4657,7 +4657,7 @@
             <v>0.781975705609146</v>
           </cell>
           <cell r="G68">
-            <v>0.780716934487021</v>
+            <v>0.77764881445863</v>
           </cell>
           <cell r="H68" t="e">
             <v>#DIV/0!</v>
@@ -4681,7 +4681,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O68">
-            <v>0.775836929896186</v>
+            <v>0.775594023926347</v>
           </cell>
         </row>
         <row r="69">
@@ -4701,7 +4701,7 @@
             <v>0.144908303683073</v>
           </cell>
           <cell r="G69">
-            <v>0.084058881672249</v>
+            <v>0.0696172387944066</v>
           </cell>
           <cell r="H69" t="e">
             <v>#DIV/0!</v>
@@ -4725,7 +4725,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O69">
-            <v>0.139342951190443</v>
+            <v>0.133639780962632</v>
           </cell>
         </row>
         <row r="70">
@@ -7233,7 +7233,7 @@
             <v>56073.62</v>
           </cell>
           <cell r="G126">
-            <v>19872.02</v>
+            <v>37401.13</v>
           </cell>
           <cell r="H126">
             <v>0</v>
@@ -7257,7 +7257,7 @@
             <v>0</v>
           </cell>
           <cell r="O126">
-            <v>304901.37</v>
+            <v>322430.48</v>
           </cell>
         </row>
         <row r="127">
@@ -7277,7 +7277,7 @@
             <v>3125</v>
           </cell>
           <cell r="G127">
-            <v>809</v>
+            <v>1233</v>
           </cell>
           <cell r="H127">
             <v>0</v>
@@ -7301,7 +7301,7 @@
             <v>0</v>
           </cell>
           <cell r="O127">
-            <v>14185</v>
+            <v>14609</v>
           </cell>
         </row>
         <row r="128">
@@ -7321,7 +7321,7 @@
             <v>1163</v>
           </cell>
           <cell r="G128">
-            <v>317</v>
+            <v>515</v>
           </cell>
           <cell r="H128">
             <v>0</v>
@@ -7345,7 +7345,7 @@
             <v>0</v>
           </cell>
           <cell r="O128">
-            <v>5291</v>
+            <v>5489</v>
           </cell>
         </row>
         <row r="129">
@@ -7365,7 +7365,7 @@
             <v>12576283</v>
           </cell>
           <cell r="G129">
-            <v>3277409</v>
+            <v>5122656</v>
           </cell>
           <cell r="H129">
             <v>0</v>
@@ -7389,7 +7389,7 @@
             <v>0</v>
           </cell>
           <cell r="O129">
-            <v>57181133</v>
+            <v>59026380</v>
           </cell>
         </row>
         <row r="130">
@@ -7409,7 +7409,7 @@
             <v>435667.29</v>
           </cell>
           <cell r="G130">
-            <v>124500.65</v>
+            <v>203016.22</v>
           </cell>
           <cell r="H130">
             <v>0</v>
@@ -7433,7 +7433,7 @@
             <v>0</v>
           </cell>
           <cell r="O130">
-            <v>1933332.24</v>
+            <v>2011847.81</v>
           </cell>
         </row>
         <row r="131">
@@ -7453,7 +7453,7 @@
             <v>0.433024696168176</v>
           </cell>
           <cell r="G131">
-            <v>0.4748440383852</v>
+            <v>0.495388085789872</v>
           </cell>
           <cell r="H131" t="e">
             <v>#DIV/0!</v>
@@ -7477,7 +7477,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O131">
-            <v>0.0338106668855267</v>
+            <v>0.0340838758873575</v>
           </cell>
         </row>
         <row r="132">
@@ -7497,7 +7497,7 @@
             <v>0.62784</v>
           </cell>
           <cell r="G132">
-            <v>0.608158220024722</v>
+            <v>0.582319545823195</v>
           </cell>
           <cell r="H132" t="e">
             <v>#DIV/0!</v>
@@ -7521,7 +7521,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O132">
-            <v>0.627000352485019</v>
+            <v>0.624272708604285</v>
           </cell>
         </row>
         <row r="133">
@@ -7541,7 +7541,7 @@
             <v>0.128707436355849</v>
           </cell>
           <cell r="G133">
-            <v>0.159613785148913</v>
+            <v>0.184227299670933</v>
           </cell>
           <cell r="H133" t="e">
             <v>#DIV/0!</v>
@@ -7565,7 +7565,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O133">
-            <v>0.157707694358834</v>
+            <v>0.160265840386803</v>
           </cell>
         </row>
       </sheetData>
@@ -7745,7 +7745,7 @@
             <v>706739.4</v>
           </cell>
           <cell r="G7">
-            <v>273743.76</v>
+            <v>417900.96</v>
           </cell>
           <cell r="H7">
             <v>0</v>
@@ -7769,7 +7769,7 @@
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>2792541.63</v>
+            <v>2936698.83</v>
           </cell>
         </row>
         <row r="8">
@@ -7789,7 +7789,7 @@
             <v>1.52310341168606</v>
           </cell>
           <cell r="G8">
-            <v>0.503951734406688</v>
+            <v>0.769339595548113</v>
           </cell>
           <cell r="H8">
             <v>0</v>
@@ -7813,7 +7813,7 @@
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0.318955497893947</v>
+            <v>0.335420688961125</v>
           </cell>
         </row>
         <row r="10">
@@ -7877,7 +7877,7 @@
             <v>33812</v>
           </cell>
           <cell r="G11">
-            <v>12697</v>
+            <v>19507</v>
           </cell>
           <cell r="H11">
             <v>0</v>
@@ -7901,7 +7901,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>141700</v>
+            <v>148510</v>
           </cell>
         </row>
         <row r="12">
@@ -7921,7 +7921,7 @@
             <v>1.05894143438772</v>
           </cell>
           <cell r="G12">
-            <v>0.352694444444444</v>
+            <v>0.541861111111111</v>
           </cell>
           <cell r="H12">
             <v>0</v>
@@ -7945,7 +7945,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.243943588260408</v>
+            <v>0.255667341514137</v>
           </cell>
         </row>
         <row r="14">
@@ -8009,7 +8009,7 @@
             <v>12177</v>
           </cell>
           <cell r="G15">
-            <v>4263</v>
+            <v>6663</v>
           </cell>
           <cell r="H15">
             <v>0</v>
@@ -8033,7 +8033,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>50327</v>
+            <v>52727</v>
           </cell>
         </row>
         <row r="16">
@@ -8053,7 +8053,7 @@
             <v>1.23021124839619</v>
           </cell>
           <cell r="G16">
-            <v>0.381989247311828</v>
+            <v>0.597043010752688</v>
           </cell>
           <cell r="H16">
             <v>0</v>
@@ -8077,7 +8077,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.279485258869979</v>
+            <v>0.292813385348568</v>
           </cell>
         </row>
         <row r="18">
@@ -8141,7 +8141,7 @@
             <v>13661971.3112</v>
           </cell>
           <cell r="G19">
-            <v>5158465.7808</v>
+            <v>8525559.1932</v>
           </cell>
           <cell r="H19">
             <v>0</v>
@@ -8165,7 +8165,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>54531118.3278</v>
+            <v>57898211.7402</v>
           </cell>
         </row>
         <row r="20">
@@ -8185,7 +8185,7 @@
             <v>1.22773777572485</v>
           </cell>
           <cell r="G20">
-            <v>0.412149710834132</v>
+            <v>0.681172834228188</v>
           </cell>
           <cell r="H20">
             <v>0</v>
@@ -8209,7 +8209,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.270361359216957</v>
+            <v>0.287055165973581</v>
           </cell>
         </row>
         <row r="22">
@@ -8273,7 +8273,7 @@
             <v>4382797.99</v>
           </cell>
           <cell r="G23">
-            <v>1581454.25</v>
+            <v>2475732.63</v>
           </cell>
           <cell r="H23">
             <v>0</v>
@@ -8297,7 +8297,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>18023984.36</v>
+            <v>18918262.74</v>
           </cell>
         </row>
         <row r="24">
@@ -8317,7 +8317,7 @@
             <v>1.23081767747956</v>
           </cell>
           <cell r="G24">
-            <v>0.394858144075583</v>
+            <v>0.618141935822148</v>
           </cell>
           <cell r="H24">
             <v>0</v>
@@ -8341,7 +8341,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.279255053095443</v>
+            <v>0.293110577573328</v>
           </cell>
         </row>
         <row r="26">
@@ -8361,7 +8361,7 @@
             <v>0.320802751679548</v>
           </cell>
           <cell r="G26">
-            <v>0.30657453537566</v>
+            <v>0.290389471692912</v>
           </cell>
           <cell r="H26" t="e">
             <v>#DIV/0!</v>
@@ -8385,7 +8385,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.330526585786365</v>
+            <v>0.326750380907959</v>
           </cell>
         </row>
         <row r="27">
@@ -8405,7 +8405,7 @@
             <v>0.639861587602035</v>
           </cell>
           <cell r="G27">
-            <v>0.664251397968024</v>
+            <v>0.658430307069257</v>
           </cell>
           <cell r="H27" t="e">
             <v>#DIV/0!</v>
@@ -8429,7 +8429,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.644834156669019</v>
+            <v>0.644959935357888</v>
           </cell>
         </row>
         <row r="28">
@@ -8449,7 +8449,7 @@
             <v>0.161253017276299</v>
           </cell>
           <cell r="G28">
-            <v>0.173096224566724</v>
+            <v>0.168798906204989</v>
           </cell>
           <cell r="H28" t="e">
             <v>#DIV/0!</v>
@@ -8473,7 +8473,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.154934756612272</v>
+            <v>0.15523089357411</v>
           </cell>
         </row>
         <row r="30">
@@ -8496,7 +8496,7 @@
             <v>364348.74</v>
           </cell>
           <cell r="G30">
-            <v>100586.14</v>
+            <v>152182.56</v>
           </cell>
           <cell r="H30">
             <v>0</v>
@@ -8520,7 +8520,7 @@
             <v>0</v>
           </cell>
           <cell r="O30">
-            <v>1659059.56</v>
+            <v>1710655.98</v>
           </cell>
         </row>
         <row r="31">
@@ -8540,7 +8540,7 @@
             <v>17188</v>
           </cell>
           <cell r="G31">
-            <v>4873</v>
+            <v>7613</v>
           </cell>
           <cell r="H31">
             <v>0</v>
@@ -8564,7 +8564,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>70724</v>
+            <v>73464</v>
           </cell>
         </row>
         <row r="32">
@@ -8584,7 +8584,7 @@
             <v>6412</v>
           </cell>
           <cell r="G32">
-            <v>1719</v>
+            <v>2603</v>
           </cell>
           <cell r="H32">
             <v>0</v>
@@ -8608,7 +8608,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>26271</v>
+            <v>27155</v>
           </cell>
         </row>
         <row r="33">
@@ -8628,7 +8628,7 @@
             <v>7017450.9096</v>
           </cell>
           <cell r="G33">
-            <v>2064206.2944</v>
+            <v>3228770.922</v>
           </cell>
           <cell r="H33">
             <v>0</v>
@@ -8652,7 +8652,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>28940201.8125</v>
+            <v>30104766.4401</v>
           </cell>
         </row>
         <row r="34">
@@ -8672,7 +8672,7 @@
             <v>2348681.79</v>
           </cell>
           <cell r="G34">
-            <v>671916.1</v>
+            <v>1016044.96</v>
           </cell>
           <cell r="H34">
             <v>0</v>
@@ -8696,7 +8696,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>9653203.73</v>
+            <v>9997332.59</v>
           </cell>
         </row>
         <row r="35">
@@ -8716,7 +8716,7 @@
             <v>0.334691588192938</v>
           </cell>
           <cell r="G35">
-            <v>0.325508211956744</v>
+            <v>0.314684746779939</v>
           </cell>
           <cell r="H35" t="e">
             <v>#DIV/0!</v>
@@ -8740,7 +8740,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.333556890602972</v>
+            <v>0.332084708575696</v>
           </cell>
         </row>
         <row r="36">
@@ -8760,7 +8760,7 @@
             <v>0.626949034209914</v>
           </cell>
           <cell r="G36">
-            <v>0.647239893289555</v>
+            <v>0.65808485485354</v>
           </cell>
           <cell r="H36" t="e">
             <v>#DIV/0!</v>
@@ -8784,7 +8784,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.628541937673209</v>
+            <v>0.63036317107699</v>
           </cell>
         </row>
         <row r="37">
@@ -8804,7 +8804,7 @@
             <v>0.155129035168276</v>
           </cell>
           <cell r="G37">
-            <v>0.149700446231308</v>
+            <v>0.149779356220615</v>
           </cell>
           <cell r="H37" t="e">
             <v>#DIV/0!</v>
@@ -8828,7 +8828,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.171866212130592</v>
+            <v>0.171111240383371</v>
           </cell>
         </row>
         <row r="38">
@@ -8851,7 +8851,7 @@
             <v>149415.87</v>
           </cell>
           <cell r="G38">
-            <v>36247.76</v>
+            <v>49611.32</v>
           </cell>
           <cell r="H38">
             <v>0</v>
@@ -8875,7 +8875,7 @@
             <v>0</v>
           </cell>
           <cell r="O38">
-            <v>513813.62</v>
+            <v>527177.18</v>
           </cell>
         </row>
         <row r="39">
@@ -8895,7 +8895,7 @@
             <v>6965</v>
           </cell>
           <cell r="G39">
-            <v>3195</v>
+            <v>4716</v>
           </cell>
           <cell r="H39">
             <v>0</v>
@@ -8919,7 +8919,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>30853</v>
+            <v>32374</v>
           </cell>
         </row>
         <row r="40">
@@ -8939,7 +8939,7 @@
             <v>2459</v>
           </cell>
           <cell r="G40">
-            <v>797</v>
+            <v>1269</v>
           </cell>
           <cell r="H40">
             <v>0</v>
@@ -8963,7 +8963,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>10071</v>
+            <v>10543</v>
           </cell>
         </row>
         <row r="41">
@@ -8983,7 +8983,7 @@
             <v>2746120.052</v>
           </cell>
           <cell r="G41">
-            <v>1096038.732</v>
+            <v>2260603.3596</v>
           </cell>
           <cell r="H41">
             <v>0</v>
@@ -9007,7 +9007,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>10836247.953</v>
+            <v>12000812.5806</v>
           </cell>
         </row>
         <row r="42">
@@ -9027,7 +9027,7 @@
             <v>861340.47</v>
           </cell>
           <cell r="G42">
-            <v>288652.65</v>
+            <v>457818.36</v>
           </cell>
           <cell r="H42">
             <v>0</v>
@@ -9051,7 +9051,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>3311817.63</v>
+            <v>3480983.34</v>
           </cell>
         </row>
         <row r="43">
@@ -9071,7 +9071,7 @@
             <v>0.313657252301364</v>
           </cell>
           <cell r="G43">
-            <v>0.263359899219328</v>
+            <v>0.202520428033429</v>
           </cell>
           <cell r="H43" t="e">
             <v>#DIV/0!</v>
@@ -9095,7 +9095,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.305624017128837</v>
+            <v>0.290062303416621</v>
           </cell>
         </row>
         <row r="44">
@@ -9115,7 +9115,7 @@
             <v>0.646949030868629</v>
           </cell>
           <cell r="G44">
-            <v>0.750547730829421</v>
+            <v>0.730916030534351</v>
           </cell>
           <cell r="H44" t="e">
             <v>#DIV/0!</v>
@@ -9139,7 +9139,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.673581175250381</v>
+            <v>0.674337431272008</v>
           </cell>
         </row>
         <row r="45">
@@ -9159,7 +9159,7 @@
             <v>0.173469000011111</v>
           </cell>
           <cell r="G45">
-            <v>0.125575704917312</v>
+            <v>0.108364636140849</v>
           </cell>
           <cell r="H45" t="e">
             <v>#DIV/0!</v>
@@ -9183,7 +9183,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.155145505400308</v>
+            <v>0.151444901773072</v>
           </cell>
         </row>
         <row r="46">
@@ -9206,7 +9206,7 @@
             <v>169881.56</v>
           </cell>
           <cell r="G46">
-            <v>126542.79</v>
+            <v>198150.01</v>
           </cell>
           <cell r="H46">
             <v>0</v>
@@ -9230,7 +9230,7 @@
             <v>0</v>
           </cell>
           <cell r="O46">
-            <v>492428.51</v>
+            <v>564035.73</v>
           </cell>
         </row>
         <row r="47">
@@ -9250,7 +9250,7 @@
             <v>7019</v>
           </cell>
           <cell r="G47">
-            <v>3874</v>
+            <v>6112</v>
           </cell>
           <cell r="H47">
             <v>0</v>
@@ -9274,7 +9274,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>24159</v>
+            <v>26397</v>
           </cell>
         </row>
         <row r="48">
@@ -9294,7 +9294,7 @@
             <v>2410</v>
           </cell>
           <cell r="G48">
-            <v>1469</v>
+            <v>2380</v>
           </cell>
           <cell r="H48">
             <v>0</v>
@@ -9318,7 +9318,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>8219</v>
+            <v>9130</v>
           </cell>
         </row>
         <row r="49">
@@ -9338,7 +9338,7 @@
             <v>2869544.286</v>
           </cell>
           <cell r="G49">
-            <v>1706169.636</v>
+            <v>2625809.1732</v>
           </cell>
           <cell r="H49">
             <v>0</v>
@@ -9362,7 +9362,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>9182873.9766</v>
+            <v>10102513.5138</v>
           </cell>
         </row>
         <row r="50">
@@ -9382,7 +9382,7 @@
             <v>863626.8</v>
           </cell>
           <cell r="G50">
-            <v>529319.03</v>
+            <v>864768.09</v>
           </cell>
           <cell r="H50">
             <v>0</v>
@@ -9406,7 +9406,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>2841963.38</v>
+            <v>3177412.44</v>
           </cell>
         </row>
         <row r="51">
@@ -9426,7 +9426,7 @@
             <v>0.300963049852021</v>
           </cell>
           <cell r="G51">
-            <v>0.310238219477961</v>
+            <v>0.32933394354249</v>
           </cell>
           <cell r="H51" t="e">
             <v>#DIV/0!</v>
@@ -9450,7 +9450,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.309485177215973</v>
+            <v>0.314517019517931</v>
           </cell>
         </row>
         <row r="52">
@@ -9470,7 +9470,7 @@
             <v>0.656646245903975</v>
           </cell>
           <cell r="G52">
-            <v>0.620805369127517</v>
+            <v>0.610602094240838</v>
           </cell>
           <cell r="H52" t="e">
             <v>#DIV/0!</v>
@@ -9494,7 +9494,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.659795521337804</v>
+            <v>0.654127362957912</v>
           </cell>
         </row>
         <row r="53">
@@ -9514,7 +9514,7 @@
             <v>0.196707142483304</v>
           </cell>
           <cell r="G53">
-            <v>0.239067146329502</v>
+            <v>0.229136588515888</v>
           </cell>
           <cell r="H53" t="e">
             <v>#DIV/0!</v>
@@ -9538,7 +9538,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.173270533134034</v>
+            <v>0.17751416935977</v>
           </cell>
         </row>
         <row r="54">
@@ -9561,7 +9561,7 @@
             <v>23093.23</v>
           </cell>
           <cell r="G54">
-            <v>10367.07</v>
+            <v>17957.07</v>
           </cell>
           <cell r="H54">
             <v>0</v>
@@ -9585,7 +9585,7 @@
             <v>0</v>
           </cell>
           <cell r="O54">
-            <v>127239.94</v>
+            <v>134829.94</v>
           </cell>
         </row>
         <row r="55">
@@ -9605,7 +9605,7 @@
             <v>2640</v>
           </cell>
           <cell r="G55">
-            <v>755</v>
+            <v>1066</v>
           </cell>
           <cell r="H55">
             <v>0</v>
@@ -9629,7 +9629,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>15964</v>
+            <v>16275</v>
           </cell>
         </row>
         <row r="56">
@@ -9649,7 +9649,7 @@
             <v>896</v>
           </cell>
           <cell r="G56">
-            <v>278</v>
+            <v>411</v>
           </cell>
           <cell r="H56">
             <v>0</v>
@@ -9673,7 +9673,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>5766</v>
+            <v>5899</v>
           </cell>
         </row>
         <row r="57">
@@ -9693,7 +9693,7 @@
             <v>1028856.0636</v>
           </cell>
           <cell r="G57">
-            <v>292051.1184</v>
+            <v>410375.7384</v>
           </cell>
           <cell r="H57">
             <v>0</v>
@@ -9717,7 +9717,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>5571794.5857</v>
+            <v>5690119.2057</v>
           </cell>
         </row>
         <row r="58">
@@ -9737,7 +9737,7 @@
             <v>309148.93</v>
           </cell>
           <cell r="G58">
-            <v>91566.47</v>
+            <v>137101.22</v>
           </cell>
           <cell r="H58">
             <v>0</v>
@@ -9761,7 +9761,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2216999.62</v>
+            <v>2262534.37</v>
           </cell>
         </row>
         <row r="59">
@@ -9781,7 +9781,7 @@
             <v>0.300478308810543</v>
           </cell>
           <cell r="G59">
-            <v>0.313528914053287</v>
+            <v>0.334087050405415</v>
           </cell>
           <cell r="H59" t="e">
             <v>#DIV/0!</v>
@@ -9805,7 +9805,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.397896868935177</v>
+            <v>0.397625126681623</v>
           </cell>
         </row>
         <row r="60">
@@ -9825,7 +9825,7 @@
             <v>0.660606060606061</v>
           </cell>
           <cell r="G60">
-            <v>0.631788079470199</v>
+            <v>0.614446529080675</v>
           </cell>
           <cell r="H60" t="e">
             <v>#DIV/0!</v>
@@ -9849,7 +9849,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.638812327737409</v>
+            <v>0.637542242703533</v>
           </cell>
         </row>
         <row r="61">
@@ -9869,7 +9869,7 @@
             <v>0.074699369006388</v>
           </cell>
           <cell r="G61">
-            <v>0.113219063703122</v>
+            <v>0.130976733832128</v>
           </cell>
           <cell r="H61" t="e">
             <v>#DIV/0!</v>
@@ -9893,7 +9893,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.0573928560258391</v>
+            <v>0.0595924383681296</v>
           </cell>
         </row>
         <row r="62">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="F4" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!F4</f>
-        <v>593659.75</v>
+        <v>685638.02</v>
       </c>
       <c r="G4" s="72">
         <f>'[1]特别隐藏版（勿动、勿看）'!G4</f>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="F5" s="8">
         <f>'[1]特别隐藏版（勿动、勿看）'!F5</f>
-        <v>0.356947776694257</v>
+        <v>0.41225123794573</v>
       </c>
       <c r="G5" s="8">
         <f>'[1]特别隐藏版（勿动、勿看）'!G5</f>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="G7" s="36">
         <f>'[1]特别隐藏版（勿动、勿看）'!G7</f>
-        <v>153709.18</v>
+        <v>245687.45</v>
       </c>
       <c r="H7" s="36">
         <f>'[1]特别隐藏版（勿动、勿看）'!H7</f>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="O7" s="36">
         <f>'[1]特别隐藏版（勿动、勿看）'!O7</f>
-        <v>1802674.09</v>
+        <v>1894652.36</v>
       </c>
       <c r="P7" s="82"/>
       <c r="Q7" s="84"/>
@@ -14059,7 +14059,7 @@
       </c>
       <c r="G8" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G8</f>
-        <v>0.293052150508833</v>
+        <v>0.468412072561518</v>
       </c>
       <c r="H8" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!H8</f>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="O8" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O8</f>
-        <v>0.268255073594681</v>
+        <v>0.2819423161888</v>
       </c>
       <c r="P8" s="82"/>
       <c r="Q8" s="82"/>
@@ -14299,7 +14299,7 @@
       </c>
       <c r="G11" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!G11</f>
-        <v>12161</v>
+        <v>18360</v>
       </c>
       <c r="H11" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!H11</f>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="O11" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!O11</f>
-        <v>146618</v>
+        <v>152817</v>
       </c>
       <c r="P11" s="69"/>
       <c r="BP11" s="86"/>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="G12" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G12</f>
-        <v>0.370722636304053</v>
+        <v>0.559696373862545</v>
       </c>
       <c r="H12" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!H12</f>
@@ -14410,7 +14410,7 @@
       </c>
       <c r="O12" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O12</f>
-        <v>0.347440711876914</v>
+        <v>0.36213048375298</v>
       </c>
       <c r="BP12" s="86"/>
       <c r="BQ12" s="87"/>
@@ -14612,7 +14612,7 @@
       </c>
       <c r="G15" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!G15</f>
-        <v>3303</v>
+        <v>5125</v>
       </c>
       <c r="H15" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!H15</f>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="O15" s="20">
         <f>'[1]特别隐藏版（勿动、勿看）'!O15</f>
-        <v>39861</v>
+        <v>41683</v>
       </c>
       <c r="P15" s="69"/>
       <c r="BP15" s="86"/>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="G16" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G16</f>
-        <v>0.315262144702347</v>
+        <v>0.489166966878452</v>
       </c>
       <c r="H16" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!H16</f>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="O16" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O16</f>
-        <v>0.296513850058578</v>
+        <v>0.310067153658757</v>
       </c>
       <c r="BP16" s="86"/>
       <c r="BQ16" s="87"/>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="G19" s="23">
         <f>'[1]特别隐藏版（勿动、勿看）'!G19</f>
-        <v>52162719</v>
+        <v>80026082</v>
       </c>
       <c r="H19" s="23">
         <f>'[1]特别隐藏版（勿动、勿看）'!H19</f>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="O19" s="23">
         <f>'[1]特别隐藏版（勿动、勿看）'!O19</f>
-        <v>654988759</v>
+        <v>682852122</v>
       </c>
       <c r="P19" s="69"/>
       <c r="BP19" s="90"/>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="G20" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G20</f>
-        <v>0.394189576075033</v>
+        <v>0.604750824789748</v>
       </c>
       <c r="H20" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!H20</f>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="O20" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O20</f>
-        <v>0.384632158433788</v>
+        <v>0.400994493366492</v>
       </c>
       <c r="BP20" s="92"/>
       <c r="BQ20" s="93"/>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="G23" s="25">
         <f>'[1]特别隐藏版（勿动、勿看）'!G23</f>
-        <v>1371955.91</v>
+        <v>2129119.94</v>
       </c>
       <c r="H23" s="25">
         <f>'[1]特别隐藏版（勿动、勿看）'!H23</f>
@@ -15271,7 +15271,7 @@
       </c>
       <c r="O23" s="36">
         <f>'[1]特别隐藏版（勿动、勿看）'!O23</f>
-        <v>15617526.45</v>
+        <v>16374690.48</v>
       </c>
       <c r="P23" s="69"/>
       <c r="BP23" s="94"/>
@@ -15318,7 +15318,7 @@
       </c>
       <c r="G24" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G24</f>
-        <v>0.402769326957713</v>
+        <v>0.625052305978292</v>
       </c>
       <c r="H24" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!H24</f>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="O24" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O24</f>
-        <v>0.356283176276717</v>
+        <v>0.373556385733704</v>
       </c>
       <c r="BP24" s="89"/>
       <c r="BQ24" s="89"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="G26" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G26</f>
-        <v>0.671231691833395</v>
+        <v>0.667433434389553</v>
       </c>
       <c r="H26" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H26</f>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="O26" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O26</f>
-        <v>0.701950487023549</v>
+        <v>0.700251892898123</v>
       </c>
       <c r="BP26" s="89"/>
       <c r="BQ26" s="96"/>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="G27" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G27</f>
-        <v>0.728394046542225</v>
+        <v>0.720860566448802</v>
       </c>
       <c r="H27" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H27</f>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="O27" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O27</f>
-        <v>0.728130243217068</v>
+        <v>0.72723584417964</v>
       </c>
       <c r="BP27" s="89"/>
       <c r="BQ27" s="96"/>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="G28" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G28</f>
-        <v>0.112036530386753</v>
+        <v>0.115393898382258</v>
       </c>
       <c r="H28" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H28</f>
@@ -15662,7 +15662,7 @@
       </c>
       <c r="O28" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O28</f>
-        <v>0.11542635101476</v>
+        <v>0.115706147991873</v>
       </c>
       <c r="BP28" s="89"/>
       <c r="BQ28" s="96"/>
@@ -15786,7 +15786,7 @@
       </c>
       <c r="G30" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G30</f>
-        <v>22183.88</v>
+        <v>40404.92</v>
       </c>
       <c r="H30" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H30</f>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="O30" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O30</f>
-        <v>318070.04</v>
+        <v>336291.08</v>
       </c>
       <c r="BP30" s="94"/>
       <c r="BQ30" s="98"/>
@@ -15864,7 +15864,7 @@
       </c>
       <c r="G31" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G31</f>
-        <v>2494</v>
+        <v>3924</v>
       </c>
       <c r="H31" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H31</f>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="O31" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O31</f>
-        <v>38432</v>
+        <v>39862</v>
       </c>
       <c r="BP31" s="94"/>
       <c r="BQ31" s="99"/>
@@ -15942,7 +15942,7 @@
       </c>
       <c r="G32" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G32</f>
-        <v>690</v>
+        <v>1102</v>
       </c>
       <c r="H32" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H32</f>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="O32" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O32</f>
-        <v>9932</v>
+        <v>10344</v>
       </c>
       <c r="BP32" s="94"/>
       <c r="BQ32" s="99"/>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="G33" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G33</f>
-        <v>10868656</v>
+        <v>17401062</v>
       </c>
       <c r="H33" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H33</f>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="O33" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O33</f>
-        <v>165151076</v>
+        <v>171683482</v>
       </c>
       <c r="BP33" s="89"/>
       <c r="BQ33" s="100"/>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="G34" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G34</f>
-        <v>280388.84</v>
+        <v>448257.72</v>
       </c>
       <c r="H34" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H34</f>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="O34" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O34</f>
-        <v>3802701.33</v>
+        <v>3970570.21</v>
       </c>
       <c r="Q34" s="69"/>
       <c r="BP34" s="86"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="G35" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G35</f>
-        <v>0.677525859683111</v>
+        <v>0.677995429244491</v>
       </c>
       <c r="H35" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H35</f>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="O35" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O35</f>
-        <v>0.712180097300728</v>
+        <v>0.710909127384777</v>
       </c>
       <c r="BP35" s="102"/>
       <c r="BQ35" s="103"/>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="G36" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G36</f>
-        <v>0.723336006415397</v>
+        <v>0.719164118246687</v>
       </c>
       <c r="H36" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H36</f>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="O36" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O36</f>
-        <v>0.741569525395504</v>
+        <v>0.740504741357684</v>
       </c>
       <c r="BP36" s="102"/>
       <c r="BQ36" s="103"/>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="G37" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G37</f>
-        <v>0.0791182701850758</v>
+        <v>0.0901377002497581</v>
       </c>
       <c r="H37" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H37</f>
@@ -16365,7 +16365,7 @@
       </c>
       <c r="O37" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O37</f>
-        <v>0.0836431821480968</v>
+        <v>0.0846959157536217</v>
       </c>
       <c r="BP37" s="102"/>
       <c r="BQ37" s="103"/>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="G38" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G38</f>
-        <v>51107.18</v>
+        <v>82894.22</v>
       </c>
       <c r="H38" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H38</f>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="O38" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O38</f>
-        <v>509957.11</v>
+        <v>541744.15</v>
       </c>
     </row>
     <row r="39" s="68" customFormat="1" spans="1:15">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="G39" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G39</f>
-        <v>2859</v>
+        <v>4306</v>
       </c>
       <c r="H39" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H39</f>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="O39" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O39</f>
-        <v>37241</v>
+        <v>38688</v>
       </c>
     </row>
     <row r="40" s="68" customFormat="1" ht="17.4" spans="1:83">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="G40" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G40</f>
-        <v>849</v>
+        <v>1321</v>
       </c>
       <c r="H40" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H40</f>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="O40" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O40</f>
-        <v>10706</v>
+        <v>11178</v>
       </c>
       <c r="BP40" s="85"/>
       <c r="BQ40" s="85"/>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="G41" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G41</f>
-        <v>12095330</v>
+        <v>19014831</v>
       </c>
       <c r="H41" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H41</f>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="O41" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O41</f>
-        <v>165462794</v>
+        <v>172382295</v>
       </c>
       <c r="Q41" s="70"/>
       <c r="BP41" s="71"/>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="G42" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G42</f>
-        <v>354397</v>
+        <v>550511.23</v>
       </c>
       <c r="H42" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H42</f>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="O42" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O42</f>
-        <v>4228391.64</v>
+        <v>4424505.87</v>
       </c>
       <c r="Q42" s="69"/>
       <c r="BP42" s="71"/>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="G43" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G43</f>
-        <v>0.633746040827328</v>
+        <v>0.638104047572129</v>
       </c>
       <c r="H43" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H43</f>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="O43" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O43</f>
-        <v>0.6805632600402</v>
+        <v>0.679164711346951</v>
       </c>
       <c r="BP43" s="71"/>
       <c r="BQ43" s="71"/>
@@ -16849,7 +16849,7 @@
       </c>
       <c r="G44" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G44</f>
-        <v>0.703043022035677</v>
+        <v>0.693218764514631</v>
       </c>
       <c r="H44" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H44</f>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="O44" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O44</f>
-        <v>0.71252114604871</v>
+        <v>0.711073200992556</v>
       </c>
       <c r="BP44" s="71"/>
       <c r="BQ44" s="104"/>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="G45" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G45</f>
-        <v>0.14420883923961</v>
+        <v>0.150576801130833</v>
       </c>
       <c r="H45" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H45</f>
@@ -16959,7 +16959,7 @@
       </c>
       <c r="O45" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O45</f>
-        <v>0.120603092952856</v>
+        <v>0.122441729295299</v>
       </c>
       <c r="BP45" s="105"/>
       <c r="BQ45" s="106"/>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="G46" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G46</f>
-        <v>26904.78</v>
+        <v>43907.28</v>
       </c>
       <c r="H46" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H46</f>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="O46" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O46</f>
-        <v>171485.78</v>
+        <v>188488.28</v>
       </c>
       <c r="BP46" s="71"/>
       <c r="BQ46" s="37"/>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="G47" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G47</f>
-        <v>1885</v>
+        <v>2763</v>
       </c>
       <c r="H47" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H47</f>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="O47" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O47</f>
-        <v>20001</v>
+        <v>20879</v>
       </c>
       <c r="BP47" s="105"/>
       <c r="BQ47" s="107"/>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="G48" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G48</f>
-        <v>537</v>
+        <v>817</v>
       </c>
       <c r="H48" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H48</f>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="O48" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O48</f>
-        <v>5469</v>
+        <v>5749</v>
       </c>
       <c r="BP48" s="105"/>
       <c r="BQ48" s="105"/>
@@ -17235,7 +17235,7 @@
       </c>
       <c r="G49" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G49</f>
-        <v>7193090</v>
+        <v>10271075</v>
       </c>
       <c r="H49" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H49</f>
@@ -17267,7 +17267,7 @@
       </c>
       <c r="O49" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O49</f>
-        <v>83969779</v>
+        <v>87047764</v>
       </c>
       <c r="Q49" s="70"/>
       <c r="BP49" s="108"/>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="G50" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G50</f>
-        <v>201578.32</v>
+        <v>308382.58</v>
       </c>
       <c r="H50" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H50</f>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="O50" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O50</f>
-        <v>2024736.62</v>
+        <v>2131540.88</v>
       </c>
       <c r="Q50" s="69"/>
       <c r="BP50" s="108"/>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="G51" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G51</f>
-        <v>0.649701449585644</v>
+        <v>0.624695345910725</v>
       </c>
       <c r="H51" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H51</f>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="O51" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O51</f>
-        <v>0.698591468842618</v>
+        <v>0.69391217217251</v>
       </c>
       <c r="BP51" s="108"/>
       <c r="BQ51" s="109"/>
@@ -17466,7 +17466,7 @@
       </c>
       <c r="G52" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G52</f>
-        <v>0.715119363395226</v>
+        <v>0.704306912775968</v>
       </c>
       <c r="H52" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H52</f>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="O52" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O52</f>
-        <v>0.726563671816409</v>
+        <v>0.724651563772211</v>
       </c>
     </row>
     <row r="53" s="68" customFormat="1" spans="1:15">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="G53" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G53</f>
-        <v>0.133470603386317</v>
+        <v>0.142379248529538</v>
       </c>
       <c r="H53" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H53</f>
@@ -17560,7 +17560,7 @@
       </c>
       <c r="O53" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O53</f>
-        <v>0.0846953516354142</v>
+        <v>0.0884281797119462</v>
       </c>
     </row>
     <row r="54" s="68" customFormat="1" spans="1:15">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="G54" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G54</f>
-        <v>19796.35</v>
+        <v>36275.43</v>
       </c>
       <c r="H54" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H54</f>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="O54" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O54</f>
-        <v>340742.77</v>
+        <v>357221.85</v>
       </c>
     </row>
     <row r="55" s="68" customFormat="1" spans="1:15">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="G55" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G55</f>
-        <v>878</v>
+        <v>1336</v>
       </c>
       <c r="H55" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H55</f>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="O55" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O55</f>
-        <v>16652</v>
+        <v>17110</v>
       </c>
     </row>
     <row r="56" s="68" customFormat="1" spans="1:15">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="G56" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G56</f>
-        <v>340</v>
+        <v>544</v>
       </c>
       <c r="H56" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H56</f>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="O56" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O56</f>
-        <v>6067</v>
+        <v>6271</v>
       </c>
     </row>
     <row r="57" s="68" customFormat="1" spans="1:17">
@@ -17776,7 +17776,7 @@
       </c>
       <c r="G57" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G57</f>
-        <v>3628095</v>
+        <v>5676332</v>
       </c>
       <c r="H57" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H57</f>
@@ -17808,7 +17808,7 @@
       </c>
       <c r="O57" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O57</f>
-        <v>67344599</v>
+        <v>69392836</v>
       </c>
       <c r="Q57" s="70"/>
     </row>
@@ -17839,7 +17839,7 @@
       </c>
       <c r="G58" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G58</f>
-        <v>134480.18</v>
+        <v>215716.27</v>
       </c>
       <c r="H58" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H58</f>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="O58" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O58</f>
-        <v>2243133.66</v>
+        <v>2324369.75</v>
       </c>
       <c r="Q58" s="69"/>
     </row>
@@ -17902,7 +17902,7 @@
       </c>
       <c r="G59" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G59</f>
-        <v>0.536670828630452</v>
+        <v>0.524965527914858</v>
       </c>
       <c r="H59" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H59</f>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="O59" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O59</f>
-        <v>0.583646332944977</v>
+        <v>0.581302284936157</v>
       </c>
     </row>
     <row r="60" s="68" customFormat="1" spans="1:15">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="G60" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G60</f>
-        <v>0.612756264236902</v>
+        <v>0.592814371257485</v>
       </c>
       <c r="H60" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H60</f>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="O60" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O60</f>
-        <v>0.635659380254624</v>
+        <v>0.633489187609585</v>
       </c>
     </row>
     <row r="61" s="68" customFormat="1" spans="1:15">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="G61" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G61</f>
-        <v>0.147206450794459</v>
+        <v>0.168162698159022</v>
       </c>
       <c r="H61" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H61</f>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="O61" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O61</f>
-        <v>0.151904800001976</v>
+        <v>0.153685466780834</v>
       </c>
     </row>
     <row r="62" s="68" customFormat="1" spans="1:15">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="G62" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G62</f>
-        <v>33716.99</v>
+        <v>42205.6</v>
       </c>
       <c r="H62" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H62</f>
@@ -18120,7 +18120,7 @@
       </c>
       <c r="O62" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O62</f>
-        <v>462418.39</v>
+        <v>470907</v>
       </c>
     </row>
     <row r="63" s="68" customFormat="1" spans="1:15">
@@ -18150,7 +18150,7 @@
       </c>
       <c r="G63" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G63</f>
-        <v>4045</v>
+        <v>6031</v>
       </c>
       <c r="H63" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H63</f>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="O63" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O63</f>
-        <v>34292</v>
+        <v>36278</v>
       </c>
     </row>
     <row r="64" s="68" customFormat="1" spans="1:15">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="G64" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G64</f>
-        <v>887</v>
+        <v>1341</v>
       </c>
       <c r="H64" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H64</f>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="O64" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O64</f>
-        <v>7687</v>
+        <v>8141</v>
       </c>
     </row>
     <row r="65" s="68" customFormat="1" spans="1:17">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="G65" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!G65</f>
-        <v>18377548</v>
+        <v>27662782</v>
       </c>
       <c r="H65" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!H65</f>
@@ -18306,7 +18306,7 @@
       </c>
       <c r="O65" s="77">
         <f>'[1]特别隐藏版（勿动、勿看）'!O65</f>
-        <v>173060511</v>
+        <v>182345745</v>
       </c>
       <c r="Q65" s="70"/>
     </row>
@@ -18337,7 +18337,7 @@
       </c>
       <c r="G66" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!G66</f>
-        <v>401111.57</v>
+        <v>606252.14</v>
       </c>
       <c r="H66" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!H66</f>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="O66" s="78">
         <f>'[1]特别隐藏版（勿动、勿看）'!O66</f>
-        <v>3318563.2</v>
+        <v>3523703.77</v>
       </c>
       <c r="Q66" s="69"/>
     </row>
@@ -18400,7 +18400,7 @@
       </c>
       <c r="G67" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G67</f>
-        <v>0.727172818430402</v>
+        <v>0.726052435723927</v>
       </c>
       <c r="H67" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H67</f>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="O67" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O67</f>
-        <v>0.760303261788011</v>
+        <v>0.758446257547715</v>
       </c>
     </row>
     <row r="68" s="68" customFormat="1" spans="1:15">
@@ -18462,7 +18462,7 @@
       </c>
       <c r="G68" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G68</f>
-        <v>0.780716934487021</v>
+        <v>0.77764881445863</v>
       </c>
       <c r="H68" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H68</f>
@@ -18494,7 +18494,7 @@
       </c>
       <c r="O68" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O68</f>
-        <v>0.775836929896186</v>
+        <v>0.775594023926347</v>
       </c>
     </row>
     <row r="69" s="68" customFormat="1" spans="1:15">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="G69" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!G69</f>
-        <v>0.084058881672249</v>
+        <v>0.0696172387944066</v>
       </c>
       <c r="H69" s="15" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H69</f>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="O69" s="15">
         <f>'[1]特别隐藏版（勿动、勿看）'!O69</f>
-        <v>0.139342951190443</v>
+        <v>0.133639780962632</v>
       </c>
     </row>
     <row r="70" s="68" customFormat="1" spans="1:15">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="G126" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G126</f>
-        <v>19872.02</v>
+        <v>37401.13</v>
       </c>
       <c r="H126" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H126</f>
@@ -22090,7 +22090,7 @@
       </c>
       <c r="O126" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O126</f>
-        <v>304901.37</v>
+        <v>322430.48</v>
       </c>
     </row>
     <row r="127" s="68" customFormat="1" spans="1:15">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="G127" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G127</f>
-        <v>809</v>
+        <v>1233</v>
       </c>
       <c r="H127" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H127</f>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="O127" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O127</f>
-        <v>14185</v>
+        <v>14609</v>
       </c>
     </row>
     <row r="128" s="68" customFormat="1" spans="1:15">
@@ -22182,7 +22182,7 @@
       </c>
       <c r="G128" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G128</f>
-        <v>317</v>
+        <v>515</v>
       </c>
       <c r="H128" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H128</f>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="O128" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O128</f>
-        <v>5291</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="129" s="68" customFormat="1" spans="1:15">
@@ -22244,7 +22244,7 @@
       </c>
       <c r="G129" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G129</f>
-        <v>3277409</v>
+        <v>5122656</v>
       </c>
       <c r="H129" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H129</f>
@@ -22276,7 +22276,7 @@
       </c>
       <c r="O129" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O129</f>
-        <v>57181133</v>
+        <v>59026380</v>
       </c>
     </row>
     <row r="130" s="68" customFormat="1" spans="1:15">
@@ -22306,7 +22306,7 @@
       </c>
       <c r="G130" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!G130</f>
-        <v>124500.65</v>
+        <v>203016.22</v>
       </c>
       <c r="H130" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!H130</f>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="O130" s="71">
         <f>'[1]特别隐藏版（勿动、勿看）'!O130</f>
-        <v>1933332.24</v>
+        <v>2011847.81</v>
       </c>
     </row>
     <row r="131" s="68" customFormat="1" spans="1:15">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="G131" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G131</f>
-        <v>0.4748440383852</v>
+        <v>0.495388085789872</v>
       </c>
       <c r="H131" s="6" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H131</f>
@@ -22400,7 +22400,7 @@
       </c>
       <c r="O131" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O131</f>
-        <v>0.0338106668855267</v>
+        <v>0.0340838758873575</v>
       </c>
     </row>
     <row r="132" s="68" customFormat="1" spans="1:15">
@@ -22430,7 +22430,7 @@
       </c>
       <c r="G132" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G132</f>
-        <v>0.608158220024722</v>
+        <v>0.582319545823195</v>
       </c>
       <c r="H132" s="6" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H132</f>
@@ -22462,7 +22462,7 @@
       </c>
       <c r="O132" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O132</f>
-        <v>0.627000352485019</v>
+        <v>0.624272708604285</v>
       </c>
     </row>
     <row r="133" s="68" customFormat="1" spans="1:15">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="G133" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!G133</f>
-        <v>0.159613785148913</v>
+        <v>0.184227299670933</v>
       </c>
       <c r="H133" s="6" t="e">
         <f>'[1]特别隐藏版（勿动、勿看）'!H133</f>
@@ -22524,7 +22524,7 @@
       </c>
       <c r="O133" s="6">
         <f>'[1]特别隐藏版（勿动、勿看）'!O133</f>
-        <v>0.157707694358834</v>
+        <v>0.160265840386803</v>
       </c>
     </row>
   </sheetData>
@@ -22645,7 +22645,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1804f7e3-3366-4bb1-bf39-66ab8996a6c3}</x14:id>
+          <x14:id>{894d8845-8077-4bcb-99f3-7cc035ae6d06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22659,7 +22659,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{478c92f3-5af4-4236-a0d1-46fa000a0afa}</x14:id>
+          <x14:id>{9d812a28-6417-4dc0-98a6-270f5c872930}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22673,7 +22673,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f43dc17-1637-4c9a-b593-768fea077ece}</x14:id>
+          <x14:id>{ee8df4bd-4138-43a1-bffe-1bfa4ba0338b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22687,7 +22687,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97d36a74-fa09-4b0a-9d09-b474d578411b}</x14:id>
+          <x14:id>{96c481e3-e0ba-49b0-83a5-ad6a7a280450}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22701,7 +22701,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73e15cdd-ea1b-448b-a75a-3beaaf62dc6c}</x14:id>
+          <x14:id>{1b1cf017-7c47-4099-9b0b-f3a7b3a9a419}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22715,7 +22715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e0de5d3-b5a2-4807-a072-33dc520608e5}</x14:id>
+          <x14:id>{5bfcbb34-3e97-442e-b539-66b4aaf20d51}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22729,7 +22729,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5212b628-9392-42ea-ad1c-27276b59a803}</x14:id>
+          <x14:id>{54e4f7ce-82e9-4048-a10b-829189d94f17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22743,7 +22743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0b20bab-eb5a-4cba-90f5-3e69e1b03680}</x14:id>
+          <x14:id>{8b9fd152-602b-4b65-a49e-8e0c3cad5ce4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22757,7 +22757,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ec5c191-ad8d-4adb-9027-7a02aa9e90c4}</x14:id>
+          <x14:id>{06d2cb8b-d821-4d1b-847f-c3b70607a09a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22771,7 +22771,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6679753-be64-49a4-bbf6-276f187c3dee}</x14:id>
+          <x14:id>{b0068023-a4aa-47d1-8245-4f7ecccdc6af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22785,7 +22785,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{107b4a17-2882-459a-a56a-7242f0ba89aa}</x14:id>
+          <x14:id>{f45ebaf3-139d-4e94-aa61-6a18f7cc5f13}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22799,7 +22799,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99aee82d-93d9-4c0c-ab63-84e6c87cbaef}</x14:id>
+          <x14:id>{eec48894-ea22-45e4-bc7d-9aaa6995c4a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22813,7 +22813,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{650dbb92-fd84-47e3-89bb-f3eec0b8ac41}</x14:id>
+          <x14:id>{06ba95ac-b624-4fe4-84e3-ad867aaaf8d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22835,7 +22835,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e4b0ab3e-96e8-4b9e-a4a9-895f91ada549}</x14:id>
+          <x14:id>{44f30c6f-98ab-41b2-a04a-be344c77753a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22865,7 +22865,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16562431-39cb-4400-a883-a9f4e425f633}</x14:id>
+          <x14:id>{2de6cf63-2ff2-4d71-878a-a37c920dfcdd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22895,7 +22895,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ff576e64-7f60-4d19-b816-d2fa2534fafa}</x14:id>
+          <x14:id>{1f3aeb7f-9ee0-4dc5-ac76-bf80a1f5bdcc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22925,7 +22925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f58e48f7-3ae8-4de9-9028-61685d049b0e}</x14:id>
+          <x14:id>{faff200a-1fdd-4ef5-a323-7084b79d6196}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22955,7 +22955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63691d63-f48d-4f5a-91f9-d99c8eede18e}</x14:id>
+          <x14:id>{c72a6826-a7c5-4cb7-b5c0-b663710bee6b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22985,7 +22985,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c5647c6-f4aa-4796-ad42-369de0bbc81b}</x14:id>
+          <x14:id>{45a15644-008e-4651-9843-aabbc07ee446}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23015,7 +23015,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12dfcd1a-935a-42d5-9827-1f6cbd2ae787}</x14:id>
+          <x14:id>{61e4207f-5dae-477f-b1f4-f0066d93c9ef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23045,7 +23045,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd357165-ca75-4f95-a7b4-87e3437de8e8}</x14:id>
+          <x14:id>{143c06d3-57f6-4865-a91a-b63576c9ab64}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23067,7 +23067,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{752cedfa-91b1-4653-ac34-2892ae09d839}</x14:id>
+          <x14:id>{89851562-e9dc-40cb-8dcd-18bb06477092}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23089,7 +23089,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e3b5057-6f06-47bf-a181-5ba17fc798ce}</x14:id>
+          <x14:id>{338c4524-f247-4f87-b315-c2e3360c8217}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23111,7 +23111,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c9955b47-50e3-4bb5-890f-33b8ba2b50ed}</x14:id>
+          <x14:id>{66fcda84-60c9-413c-bfc1-0523d3ed90c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23133,7 +23133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1534b01c-7953-4901-947c-127152edabaa}</x14:id>
+          <x14:id>{0160fc17-ec5f-4e49-a468-f27670e078a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23155,7 +23155,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e8fe23c-d2ff-489b-ba25-bd45c1722a8c}</x14:id>
+          <x14:id>{0e839c1b-39da-4486-b205-52b74d4fb5c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23177,7 +23177,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9db9b713-1254-463d-992f-e3208e55daff}</x14:id>
+          <x14:id>{0b804f76-803e-460b-866c-65f180321573}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23199,7 +23199,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51623147-37b1-4c1c-9879-1db827bca8d4}</x14:id>
+          <x14:id>{df98c5e1-2265-4d0b-84b3-0c1c41efc6d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23221,7 +23221,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aba5af49-bfba-4cfe-afbb-dde443802d9e}</x14:id>
+          <x14:id>{892e0eb4-bbe8-4d59-9e89-c439ab467c69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23243,7 +23243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29f6ad11-8775-4b95-b84c-60378be1e9f1}</x14:id>
+          <x14:id>{96be1bf8-fb09-4057-9d48-998b3a099c37}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23265,7 +23265,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49a72d66-9c5b-4fda-bf11-1424d576c5e3}</x14:id>
+          <x14:id>{ea42c463-830a-46eb-af10-62056b7bb2e2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23287,7 +23287,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf920bbb-c2ef-4d98-b6ac-e28ab3a8d955}</x14:id>
+          <x14:id>{289381e6-d045-4751-b35b-9e8795f4e742}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23309,7 +23309,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b914219-4efa-438a-a333-22e433e2c85e}</x14:id>
+          <x14:id>{748b7ac9-d5f1-4d5b-a8ad-932b772f325a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23328,7 +23328,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1804f7e3-3366-4bb1-bf39-66ab8996a6c3}">
+          <x14:cfRule type="dataBar" id="{894d8845-8077-4bcb-99f3-7cc035ae6d06}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23341,7 +23341,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{478c92f3-5af4-4236-a0d1-46fa000a0afa}">
+          <x14:cfRule type="dataBar" id="{9d812a28-6417-4dc0-98a6-270f5c872930}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23354,7 +23354,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2f43dc17-1637-4c9a-b593-768fea077ece}">
+          <x14:cfRule type="dataBar" id="{ee8df4bd-4138-43a1-bffe-1bfa4ba0338b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23367,7 +23367,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{97d36a74-fa09-4b0a-9d09-b474d578411b}">
+          <x14:cfRule type="dataBar" id="{96c481e3-e0ba-49b0-83a5-ad6a7a280450}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23380,7 +23380,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{73e15cdd-ea1b-448b-a75a-3beaaf62dc6c}">
+          <x14:cfRule type="dataBar" id="{1b1cf017-7c47-4099-9b0b-f3a7b3a9a419}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23393,7 +23393,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4e0de5d3-b5a2-4807-a072-33dc520608e5}">
+          <x14:cfRule type="dataBar" id="{5bfcbb34-3e97-442e-b539-66b4aaf20d51}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23406,7 +23406,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5212b628-9392-42ea-ad1c-27276b59a803}">
+          <x14:cfRule type="dataBar" id="{54e4f7ce-82e9-4048-a10b-829189d94f17}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23419,7 +23419,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d0b20bab-eb5a-4cba-90f5-3e69e1b03680}">
+          <x14:cfRule type="dataBar" id="{8b9fd152-602b-4b65-a49e-8e0c3cad5ce4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23432,7 +23432,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2ec5c191-ad8d-4adb-9027-7a02aa9e90c4}">
+          <x14:cfRule type="dataBar" id="{06d2cb8b-d821-4d1b-847f-c3b70607a09a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23445,7 +23445,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6679753-be64-49a4-bbf6-276f187c3dee}">
+          <x14:cfRule type="dataBar" id="{b0068023-a4aa-47d1-8245-4f7ecccdc6af}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23458,7 +23458,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{107b4a17-2882-459a-a56a-7242f0ba89aa}">
+          <x14:cfRule type="dataBar" id="{f45ebaf3-139d-4e94-aa61-6a18f7cc5f13}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23471,7 +23471,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99aee82d-93d9-4c0c-ab63-84e6c87cbaef}">
+          <x14:cfRule type="dataBar" id="{eec48894-ea22-45e4-bc7d-9aaa6995c4a5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23484,7 +23484,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{650dbb92-fd84-47e3-89bb-f3eec0b8ac41}">
+          <x14:cfRule type="dataBar" id="{06ba95ac-b624-4fe4-84e3-ad867aaaf8d5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23497,7 +23497,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e4b0ab3e-96e8-4b9e-a4a9-895f91ada549}">
+          <x14:cfRule type="dataBar" id="{44f30c6f-98ab-41b2-a04a-be344c77753a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23510,7 +23510,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16562431-39cb-4400-a883-a9f4e425f633}">
+          <x14:cfRule type="dataBar" id="{2de6cf63-2ff2-4d71-878a-a37c920dfcdd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23523,7 +23523,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ff576e64-7f60-4d19-b816-d2fa2534fafa}">
+          <x14:cfRule type="dataBar" id="{1f3aeb7f-9ee0-4dc5-ac76-bf80a1f5bdcc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23536,7 +23536,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f58e48f7-3ae8-4de9-9028-61685d049b0e}">
+          <x14:cfRule type="dataBar" id="{faff200a-1fdd-4ef5-a323-7084b79d6196}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23549,7 +23549,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{63691d63-f48d-4f5a-91f9-d99c8eede18e}">
+          <x14:cfRule type="dataBar" id="{c72a6826-a7c5-4cb7-b5c0-b663710bee6b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23562,7 +23562,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c5647c6-f4aa-4796-ad42-369de0bbc81b}">
+          <x14:cfRule type="dataBar" id="{45a15644-008e-4651-9843-aabbc07ee446}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23575,7 +23575,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{12dfcd1a-935a-42d5-9827-1f6cbd2ae787}">
+          <x14:cfRule type="dataBar" id="{61e4207f-5dae-477f-b1f4-f0066d93c9ef}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23588,7 +23588,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd357165-ca75-4f95-a7b4-87e3437de8e8}">
+          <x14:cfRule type="dataBar" id="{143c06d3-57f6-4865-a91a-b63576c9ab64}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23601,7 +23601,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{752cedfa-91b1-4653-ac34-2892ae09d839}">
+          <x14:cfRule type="dataBar" id="{89851562-e9dc-40cb-8dcd-18bb06477092}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23614,7 +23614,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9e3b5057-6f06-47bf-a181-5ba17fc798ce}">
+          <x14:cfRule type="dataBar" id="{338c4524-f247-4f87-b315-c2e3360c8217}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23627,7 +23627,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c9955b47-50e3-4bb5-890f-33b8ba2b50ed}">
+          <x14:cfRule type="dataBar" id="{66fcda84-60c9-413c-bfc1-0523d3ed90c8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23640,7 +23640,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1534b01c-7953-4901-947c-127152edabaa}">
+          <x14:cfRule type="dataBar" id="{0160fc17-ec5f-4e49-a468-f27670e078a3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23653,7 +23653,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e8fe23c-d2ff-489b-ba25-bd45c1722a8c}">
+          <x14:cfRule type="dataBar" id="{0e839c1b-39da-4486-b205-52b74d4fb5c8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23666,7 +23666,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9db9b713-1254-463d-992f-e3208e55daff}">
+          <x14:cfRule type="dataBar" id="{0b804f76-803e-460b-866c-65f180321573}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23679,7 +23679,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{51623147-37b1-4c1c-9879-1db827bca8d4}">
+          <x14:cfRule type="dataBar" id="{df98c5e1-2265-4d0b-84b3-0c1c41efc6d0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23692,7 +23692,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aba5af49-bfba-4cfe-afbb-dde443802d9e}">
+          <x14:cfRule type="dataBar" id="{892e0eb4-bbe8-4d59-9e89-c439ab467c69}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23705,7 +23705,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{29f6ad11-8775-4b95-b84c-60378be1e9f1}">
+          <x14:cfRule type="dataBar" id="{96be1bf8-fb09-4057-9d48-998b3a099c37}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23718,7 +23718,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{49a72d66-9c5b-4fda-bf11-1424d576c5e3}">
+          <x14:cfRule type="dataBar" id="{ea42c463-830a-46eb-af10-62056b7bb2e2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23731,7 +23731,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf920bbb-c2ef-4d98-b6ac-e28ab3a8d955}">
+          <x14:cfRule type="dataBar" id="{289381e6-d045-4751-b35b-9e8795f4e742}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23744,7 +23744,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b914219-4efa-438a-a333-22e433e2c85e}">
+          <x14:cfRule type="dataBar" id="{748b7ac9-d5f1-4d5b-a8ad-932b772f325a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23979,7 +23979,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>980483.16</v>
+        <v>1124640.36</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -24017,7 +24017,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.607521396779346</v>
+        <v>0.696843260807893</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -24128,7 +24128,7 @@
       </c>
       <c r="G7" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G7</f>
-        <v>273743.76</v>
+        <v>417900.96</v>
       </c>
       <c r="H7" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H7</f>
@@ -24160,7 +24160,7 @@
       </c>
       <c r="O7" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O7</f>
-        <v>2792541.63</v>
+        <v>2936698.83</v>
       </c>
     </row>
     <row r="8" s="38" customFormat="1" spans="1:15">
@@ -24190,7 +24190,7 @@
       </c>
       <c r="G8" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G8</f>
-        <v>0.503951734406688</v>
+        <v>0.769339595548113</v>
       </c>
       <c r="H8" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H8</f>
@@ -24222,7 +24222,7 @@
       </c>
       <c r="O8" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O8</f>
-        <v>0.318955497893947</v>
+        <v>0.335420688961125</v>
       </c>
     </row>
     <row r="9" s="38" customFormat="1" spans="1:15">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="G11" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G11</f>
-        <v>12697</v>
+        <v>19507</v>
       </c>
       <c r="H11" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H11</f>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="O11" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O11</f>
-        <v>141700</v>
+        <v>148510</v>
       </c>
     </row>
     <row r="12" s="38" customFormat="1" spans="1:15">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="G12" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G12</f>
-        <v>0.352694444444444</v>
+        <v>0.541861111111111</v>
       </c>
       <c r="H12" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H12</f>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="O12" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O12</f>
-        <v>0.243943588260408</v>
+        <v>0.255667341514137</v>
       </c>
     </row>
     <row r="13" s="38" customFormat="1" spans="1:15">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="G15" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G15</f>
-        <v>4263</v>
+        <v>6663</v>
       </c>
       <c r="H15" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H15</f>
@@ -24656,7 +24656,7 @@
       </c>
       <c r="O15" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O15</f>
-        <v>50327</v>
+        <v>52727</v>
       </c>
     </row>
     <row r="16" s="38" customFormat="1" spans="1:15">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="G16" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G16</f>
-        <v>0.381989247311828</v>
+        <v>0.597043010752688</v>
       </c>
       <c r="H16" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H16</f>
@@ -24718,7 +24718,7 @@
       </c>
       <c r="O16" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O16</f>
-        <v>0.279485258869979</v>
+        <v>0.292813385348568</v>
       </c>
     </row>
     <row r="17" s="38" customFormat="1" spans="1:15">
@@ -24872,7 +24872,7 @@
       </c>
       <c r="G19" s="25">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G19</f>
-        <v>5158465.7808</v>
+        <v>8525559.1932</v>
       </c>
       <c r="H19" s="25">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H19</f>
@@ -24904,7 +24904,7 @@
       </c>
       <c r="O19" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O19</f>
-        <v>54531118.3278</v>
+        <v>57898211.7402</v>
       </c>
     </row>
     <row r="20" s="38" customFormat="1" spans="1:15">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="G20" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G20</f>
-        <v>0.412149710834132</v>
+        <v>0.681172834228188</v>
       </c>
       <c r="H20" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H20</f>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="O20" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O20</f>
-        <v>0.270361359216957</v>
+        <v>0.287055165973581</v>
       </c>
     </row>
     <row r="21" s="38" customFormat="1" spans="1:15">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="G23" s="25">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G23</f>
-        <v>1581454.25</v>
+        <v>2475732.63</v>
       </c>
       <c r="H23" s="25">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H23</f>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="O23" s="36">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O23</f>
-        <v>18023984.36</v>
+        <v>18918262.74</v>
       </c>
     </row>
     <row r="24" s="38" customFormat="1" spans="1:15">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="G24" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G24</f>
-        <v>0.394858144075583</v>
+        <v>0.618141935822148</v>
       </c>
       <c r="H24" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H24</f>
@@ -25214,7 +25214,7 @@
       </c>
       <c r="O24" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O24</f>
-        <v>0.279255053095443</v>
+        <v>0.293110577573328</v>
       </c>
     </row>
     <row r="25" s="38" customFormat="1" spans="1:15">
@@ -25306,7 +25306,7 @@
       </c>
       <c r="G26" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G26</f>
-        <v>0.30657453537566</v>
+        <v>0.290389471692912</v>
       </c>
       <c r="H26" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H26</f>
@@ -25338,7 +25338,7 @@
       </c>
       <c r="O26" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O26</f>
-        <v>0.330526585786365</v>
+        <v>0.326750380907959</v>
       </c>
     </row>
     <row r="27" s="38" customFormat="1" spans="1:15">
@@ -25368,7 +25368,7 @@
       </c>
       <c r="G27" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G27</f>
-        <v>0.664251397968024</v>
+        <v>0.658430307069257</v>
       </c>
       <c r="H27" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H27</f>
@@ -25400,7 +25400,7 @@
       </c>
       <c r="O27" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O27</f>
-        <v>0.644834156669019</v>
+        <v>0.644959935357888</v>
       </c>
     </row>
     <row r="28" s="38" customFormat="1" spans="1:15">
@@ -25430,7 +25430,7 @@
       </c>
       <c r="G28" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G28</f>
-        <v>0.173096224566724</v>
+        <v>0.168798906204989</v>
       </c>
       <c r="H28" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H28</f>
@@ -25462,7 +25462,7 @@
       </c>
       <c r="O28" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O28</f>
-        <v>0.154934756612272</v>
+        <v>0.15523089357411</v>
       </c>
     </row>
     <row r="29" s="38" customFormat="1" spans="1:15">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="G30" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G30</f>
-        <v>100586.14</v>
+        <v>152182.56</v>
       </c>
       <c r="H30" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H30</f>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="O30" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O30</f>
-        <v>1659059.56</v>
+        <v>1710655.98</v>
       </c>
     </row>
     <row r="31" s="38" customFormat="1" spans="1:15">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="G31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G31</f>
-        <v>4873</v>
+        <v>7613</v>
       </c>
       <c r="H31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H31</f>
@@ -25648,7 +25648,7 @@
       </c>
       <c r="O31" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O31</f>
-        <v>70724</v>
+        <v>73464</v>
       </c>
     </row>
     <row r="32" s="38" customFormat="1" spans="1:15">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="G32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G32</f>
-        <v>1719</v>
+        <v>2603</v>
       </c>
       <c r="H32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H32</f>
@@ -25710,7 +25710,7 @@
       </c>
       <c r="O32" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O32</f>
-        <v>26271</v>
+        <v>27155</v>
       </c>
     </row>
     <row r="33" s="38" customFormat="1" spans="1:15">
@@ -25740,7 +25740,7 @@
       </c>
       <c r="G33" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G33</f>
-        <v>2064206.2944</v>
+        <v>3228770.922</v>
       </c>
       <c r="H33" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H33</f>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="O33" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O33</f>
-        <v>28940201.8125</v>
+        <v>30104766.4401</v>
       </c>
     </row>
     <row r="34" s="38" customFormat="1" spans="1:15">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="G34" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G34</f>
-        <v>671916.1</v>
+        <v>1016044.96</v>
       </c>
       <c r="H34" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H34</f>
@@ -25834,7 +25834,7 @@
       </c>
       <c r="O34" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O34</f>
-        <v>9653203.73</v>
+        <v>9997332.59</v>
       </c>
     </row>
     <row r="35" s="38" customFormat="1" spans="1:15">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="G35" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G35</f>
-        <v>0.325508211956744</v>
+        <v>0.314684746779939</v>
       </c>
       <c r="H35" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H35</f>
@@ -25896,7 +25896,7 @@
       </c>
       <c r="O35" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O35</f>
-        <v>0.333556890602972</v>
+        <v>0.332084708575696</v>
       </c>
     </row>
     <row r="36" s="38" customFormat="1" spans="1:15">
@@ -25926,7 +25926,7 @@
       </c>
       <c r="G36" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G36</f>
-        <v>0.647239893289555</v>
+        <v>0.65808485485354</v>
       </c>
       <c r="H36" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H36</f>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="O36" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O36</f>
-        <v>0.628541937673209</v>
+        <v>0.63036317107699</v>
       </c>
     </row>
     <row r="37" s="38" customFormat="1" spans="1:15">
@@ -25988,7 +25988,7 @@
       </c>
       <c r="G37" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G37</f>
-        <v>0.149700446231308</v>
+        <v>0.149779356220615</v>
       </c>
       <c r="H37" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H37</f>
@@ -26020,7 +26020,7 @@
       </c>
       <c r="O37" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O37</f>
-        <v>0.171866212130592</v>
+        <v>0.171111240383371</v>
       </c>
     </row>
     <row r="38" s="38" customFormat="1" spans="1:15">
@@ -26050,7 +26050,7 @@
       </c>
       <c r="G38" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G38</f>
-        <v>36247.76</v>
+        <v>49611.32</v>
       </c>
       <c r="H38" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H38</f>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="O38" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O38</f>
-        <v>513813.62</v>
+        <v>527177.18</v>
       </c>
     </row>
     <row r="39" s="38" customFormat="1" spans="1:15">
@@ -26112,7 +26112,7 @@
       </c>
       <c r="G39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G39</f>
-        <v>3195</v>
+        <v>4716</v>
       </c>
       <c r="H39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H39</f>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="O39" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O39</f>
-        <v>30853</v>
+        <v>32374</v>
       </c>
     </row>
     <row r="40" s="38" customFormat="1" spans="1:15">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="G40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G40</f>
-        <v>797</v>
+        <v>1269</v>
       </c>
       <c r="H40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H40</f>
@@ -26206,7 +26206,7 @@
       </c>
       <c r="O40" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O40</f>
-        <v>10071</v>
+        <v>10543</v>
       </c>
     </row>
     <row r="41" s="38" customFormat="1" spans="1:15">
@@ -26236,7 +26236,7 @@
       </c>
       <c r="G41" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G41</f>
-        <v>1096038.732</v>
+        <v>2260603.3596</v>
       </c>
       <c r="H41" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H41</f>
@@ -26268,7 +26268,7 @@
       </c>
       <c r="O41" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O41</f>
-        <v>10836247.953</v>
+        <v>12000812.5806</v>
       </c>
     </row>
     <row r="42" s="38" customFormat="1" spans="1:15">
@@ -26298,7 +26298,7 @@
       </c>
       <c r="G42" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G42</f>
-        <v>288652.65</v>
+        <v>457818.36</v>
       </c>
       <c r="H42" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H42</f>
@@ -26330,7 +26330,7 @@
       </c>
       <c r="O42" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O42</f>
-        <v>3311817.63</v>
+        <v>3480983.34</v>
       </c>
     </row>
     <row r="43" s="38" customFormat="1" spans="1:15">
@@ -26360,7 +26360,7 @@
       </c>
       <c r="G43" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G43</f>
-        <v>0.263359899219328</v>
+        <v>0.202520428033429</v>
       </c>
       <c r="H43" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H43</f>
@@ -26392,7 +26392,7 @@
       </c>
       <c r="O43" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O43</f>
-        <v>0.305624017128837</v>
+        <v>0.290062303416621</v>
       </c>
     </row>
     <row r="44" s="38" customFormat="1" spans="1:15">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="G44" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G44</f>
-        <v>0.750547730829421</v>
+        <v>0.730916030534351</v>
       </c>
       <c r="H44" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H44</f>
@@ -26454,7 +26454,7 @@
       </c>
       <c r="O44" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O44</f>
-        <v>0.673581175250381</v>
+        <v>0.674337431272008</v>
       </c>
     </row>
     <row r="45" s="38" customFormat="1" spans="1:15">
@@ -26484,7 +26484,7 @@
       </c>
       <c r="G45" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G45</f>
-        <v>0.125575704917312</v>
+        <v>0.108364636140849</v>
       </c>
       <c r="H45" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H45</f>
@@ -26516,7 +26516,7 @@
       </c>
       <c r="O45" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O45</f>
-        <v>0.155145505400308</v>
+        <v>0.151444901773072</v>
       </c>
     </row>
     <row r="46" s="38" customFormat="1" spans="1:15">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="G46" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G46</f>
-        <v>126542.79</v>
+        <v>198150.01</v>
       </c>
       <c r="H46" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H46</f>
@@ -26578,7 +26578,7 @@
       </c>
       <c r="O46" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O46</f>
-        <v>492428.51</v>
+        <v>564035.73</v>
       </c>
     </row>
     <row r="47" s="38" customFormat="1" spans="1:15">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="G47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G47</f>
-        <v>3874</v>
+        <v>6112</v>
       </c>
       <c r="H47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H47</f>
@@ -26640,7 +26640,7 @@
       </c>
       <c r="O47" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O47</f>
-        <v>24159</v>
+        <v>26397</v>
       </c>
     </row>
     <row r="48" s="38" customFormat="1" spans="1:15">
@@ -26670,7 +26670,7 @@
       </c>
       <c r="G48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G48</f>
-        <v>1469</v>
+        <v>2380</v>
       </c>
       <c r="H48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H48</f>
@@ -26702,7 +26702,7 @@
       </c>
       <c r="O48" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O48</f>
-        <v>8219</v>
+        <v>9130</v>
       </c>
     </row>
     <row r="49" s="38" customFormat="1" spans="1:15">
@@ -26732,7 +26732,7 @@
       </c>
       <c r="G49" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G49</f>
-        <v>1706169.636</v>
+        <v>2625809.1732</v>
       </c>
       <c r="H49" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H49</f>
@@ -26764,7 +26764,7 @@
       </c>
       <c r="O49" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O49</f>
-        <v>9182873.9766</v>
+        <v>10102513.5138</v>
       </c>
     </row>
     <row r="50" s="38" customFormat="1" spans="1:15">
@@ -26794,7 +26794,7 @@
       </c>
       <c r="G50" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G50</f>
-        <v>529319.03</v>
+        <v>864768.09</v>
       </c>
       <c r="H50" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H50</f>
@@ -26826,7 +26826,7 @@
       </c>
       <c r="O50" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O50</f>
-        <v>2841963.38</v>
+        <v>3177412.44</v>
       </c>
     </row>
     <row r="51" s="38" customFormat="1" spans="1:15">
@@ -26856,7 +26856,7 @@
       </c>
       <c r="G51" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G51</f>
-        <v>0.310238219477961</v>
+        <v>0.32933394354249</v>
       </c>
       <c r="H51" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H51</f>
@@ -26888,7 +26888,7 @@
       </c>
       <c r="O51" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O51</f>
-        <v>0.309485177215973</v>
+        <v>0.314517019517931</v>
       </c>
     </row>
     <row r="52" s="38" customFormat="1" spans="1:15">
@@ -26918,7 +26918,7 @@
       </c>
       <c r="G52" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G52</f>
-        <v>0.620805369127517</v>
+        <v>0.610602094240838</v>
       </c>
       <c r="H52" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H52</f>
@@ -26950,7 +26950,7 @@
       </c>
       <c r="O52" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O52</f>
-        <v>0.659795521337804</v>
+        <v>0.654127362957912</v>
       </c>
     </row>
     <row r="53" s="38" customFormat="1" spans="1:15">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="G53" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G53</f>
-        <v>0.239067146329502</v>
+        <v>0.229136588515888</v>
       </c>
       <c r="H53" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H53</f>
@@ -27012,7 +27012,7 @@
       </c>
       <c r="O53" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O53</f>
-        <v>0.173270533134034</v>
+        <v>0.17751416935977</v>
       </c>
     </row>
     <row r="54" s="38" customFormat="1" spans="1:15">
@@ -27042,7 +27042,7 @@
       </c>
       <c r="G54" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G54</f>
-        <v>10367.07</v>
+        <v>17957.07</v>
       </c>
       <c r="H54" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H54</f>
@@ -27074,7 +27074,7 @@
       </c>
       <c r="O54" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O54</f>
-        <v>127239.94</v>
+        <v>134829.94</v>
       </c>
     </row>
     <row r="55" s="38" customFormat="1" spans="1:15">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="G55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G55</f>
-        <v>755</v>
+        <v>1066</v>
       </c>
       <c r="H55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H55</f>
@@ -27136,7 +27136,7 @@
       </c>
       <c r="O55" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O55</f>
-        <v>15964</v>
+        <v>16275</v>
       </c>
     </row>
     <row r="56" s="38" customFormat="1" spans="1:15">
@@ -27166,7 +27166,7 @@
       </c>
       <c r="G56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G56</f>
-        <v>278</v>
+        <v>411</v>
       </c>
       <c r="H56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H56</f>
@@ -27198,7 +27198,7 @@
       </c>
       <c r="O56" s="2">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O56</f>
-        <v>5766</v>
+        <v>5899</v>
       </c>
     </row>
     <row r="57" s="38" customFormat="1" spans="1:15">
@@ -27228,7 +27228,7 @@
       </c>
       <c r="G57" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G57</f>
-        <v>292051.1184</v>
+        <v>410375.7384</v>
       </c>
       <c r="H57" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H57</f>
@@ -27260,7 +27260,7 @@
       </c>
       <c r="O57" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O57</f>
-        <v>5571794.5857</v>
+        <v>5690119.2057</v>
       </c>
     </row>
     <row r="58" s="38" customFormat="1" spans="1:15">
@@ -27290,7 +27290,7 @@
       </c>
       <c r="G58" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G58</f>
-        <v>91566.47</v>
+        <v>137101.22</v>
       </c>
       <c r="H58" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H58</f>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="O58" s="24">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O58</f>
-        <v>2216999.62</v>
+        <v>2262534.37</v>
       </c>
     </row>
     <row r="59" s="38" customFormat="1" spans="1:15">
@@ -27352,7 +27352,7 @@
       </c>
       <c r="G59" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G59</f>
-        <v>0.313528914053287</v>
+        <v>0.334087050405415</v>
       </c>
       <c r="H59" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H59</f>
@@ -27384,7 +27384,7 @@
       </c>
       <c r="O59" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O59</f>
-        <v>0.397896868935177</v>
+        <v>0.397625126681623</v>
       </c>
     </row>
     <row r="60" s="38" customFormat="1" spans="1:15">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="G60" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G60</f>
-        <v>0.631788079470199</v>
+        <v>0.614446529080675</v>
       </c>
       <c r="H60" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H60</f>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="O60" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O60</f>
-        <v>0.638812327737409</v>
+        <v>0.637542242703533</v>
       </c>
     </row>
     <row r="61" s="38" customFormat="1" spans="1:15">
@@ -27476,7 +27476,7 @@
       </c>
       <c r="G61" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G61</f>
-        <v>0.113219063703122</v>
+        <v>0.130976733832128</v>
       </c>
       <c r="H61" s="6" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H61</f>
@@ -27508,7 +27508,7 @@
       </c>
       <c r="O61" s="6">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O61</f>
-        <v>0.0573928560258391</v>
+        <v>0.0595924383681296</v>
       </c>
     </row>
     <row r="62" s="38" customFormat="1" spans="1:15">
@@ -34308,7 +34308,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{062a3a6d-72b6-4230-bb4d-fa9666034505}</x14:id>
+          <x14:id>{4e7c62fb-1a80-4f0f-ab77-232ac1b6e736}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34322,7 +34322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b36333ca-9fd5-47a9-89e4-71ffa5a4aed6}</x14:id>
+          <x14:id>{23ad5611-fcb4-4eed-a33c-035351234423}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34336,7 +34336,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f34c8460-4591-4af7-96ff-f70c1e64e2fb}</x14:id>
+          <x14:id>{8378a0b3-9c66-4adb-9ffe-f4d774796200}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34350,7 +34350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a170552-a4cf-48c5-84f5-01aba45dd39a}</x14:id>
+          <x14:id>{b1de088a-4f58-4956-9261-dfe205e64253}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34364,7 +34364,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d229eb8e-b1c9-42a3-8714-5e62fcfdb59f}</x14:id>
+          <x14:id>{925c761e-db78-4b0d-b2ad-f339781e0635}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34378,7 +34378,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6bbb3c63-ab75-4259-a608-cc436ddfec84}</x14:id>
+          <x14:id>{f7a8e535-848c-4253-9c21-603d86f38527}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34398,7 +34398,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ca4d0ad-9e00-4726-b503-71376030acaa}</x14:id>
+          <x14:id>{fc595743-955e-4f09-8989-ea08fbd1b2c9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34412,7 +34412,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94b061ee-bff8-4234-9b69-035f98693438}</x14:id>
+          <x14:id>{23fc40e7-50d7-4640-8b53-b0f881b47ff1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34426,7 +34426,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52ac152c-e6e2-4e1b-99af-7dbfc1981505}</x14:id>
+          <x14:id>{b24efd57-e291-46f4-bc48-84b964c75ae6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34440,7 +34440,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{345ffe5b-b48f-429d-b47f-320b29bc0360}</x14:id>
+          <x14:id>{45e00894-24cc-4ea1-bd92-c84623e4c4fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34454,7 +34454,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7cd9f26-3e27-4e8e-ae61-89989088a932}</x14:id>
+          <x14:id>{4b200c81-e601-4b28-9ea9-5312455cf0ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34468,7 +34468,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e536f0fc-29d4-4100-938f-ae3b51b1f4db}</x14:id>
+          <x14:id>{7d39900a-c9f9-48cc-8605-da605622c716}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34490,7 +34490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fff15cc7-a51e-4958-ad6b-d6a06e1c0b38}</x14:id>
+          <x14:id>{166c63bf-6c1d-44f9-8ce3-635e8609effb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34520,7 +34520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbcb3dfd-4001-44ea-b584-001c8b1ffd79}</x14:id>
+          <x14:id>{ed69ec66-442e-47ab-8f80-3c3681fd47a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34550,7 +34550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b38aa4dd-b213-4e49-a128-3f7c1e397d9f}</x14:id>
+          <x14:id>{a028e7ab-9533-42f0-99c7-0de08964a13b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34580,7 +34580,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f4ff00d-dbaa-4f7e-9fd9-95e112173f8a}</x14:id>
+          <x14:id>{577d159c-efb4-4f48-b305-bc0cdb22604d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34610,7 +34610,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47363c4c-c339-4ec1-a5dd-d1791ae68057}</x14:id>
+          <x14:id>{e8d229fe-5f5a-491d-84cf-bd9b7bfb6fcf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34640,7 +34640,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a1d23d1-0a64-4892-bdce-228f660268c0}</x14:id>
+          <x14:id>{c3d2ee88-d706-4703-8ba5-4c9c3105e9ca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34662,7 +34662,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{462c3fad-25e8-4ae3-a95c-b7770fee264a}</x14:id>
+          <x14:id>{65933897-75ba-4b44-85b5-9578a745f442}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34684,7 +34684,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f979b91f-a2a4-47b2-81d2-382f1b9ef82f}</x14:id>
+          <x14:id>{1466e6d5-de42-4ec6-a106-0d2afa7ebaab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34706,7 +34706,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70d60f34-1578-4270-ad9c-89f55a59b83f}</x14:id>
+          <x14:id>{836339a8-314d-4e11-8253-5428b4c14918}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34728,7 +34728,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{48e6612c-97df-43fb-87f1-a0b9bf531f6a}</x14:id>
+          <x14:id>{5536eb1c-2eaa-49b4-94aa-e0cb2de32dda}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34750,7 +34750,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f10672a5-5024-4401-9d40-3bbfaaaff302}</x14:id>
+          <x14:id>{05a33d5b-2563-44b6-9b0d-7f062b54dbbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34772,7 +34772,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93e36254-ad4c-4422-9e8c-97a296409f69}</x14:id>
+          <x14:id>{429cd1c3-3665-496a-aeec-eae5465b74eb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34794,7 +34794,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2686627b-7afc-40d9-8abd-800c5da752bb}</x14:id>
+          <x14:id>{c334eac3-ff80-4042-9118-2f0b1d193612}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34816,7 +34816,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11099acc-46b9-4b7c-9686-188e715cf273}</x14:id>
+          <x14:id>{db5096fe-f115-4fb5-aac1-f64a124fe748}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34838,7 +34838,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{975a1405-eb3e-4f78-886b-f2a0532f2841}</x14:id>
+          <x14:id>{0de32c3f-0b04-4dd7-8ca7-4431654148b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34860,7 +34860,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{727c82c2-c91d-483f-8ece-57f3e7ae5a14}</x14:id>
+          <x14:id>{9b89200a-1953-4446-a292-617d14e4352d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34882,7 +34882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ecfbbb0-c27c-42f6-bf88-efa7bd9b5a99}</x14:id>
+          <x14:id>{2b97c2fc-8fea-4d0e-b704-fae0e8f3ec74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34904,7 +34904,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e4eef42-2b6f-4726-92ee-09695918e9e4}</x14:id>
+          <x14:id>{2fabc8ea-5dca-4902-aad9-92459e09aac3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34926,7 +34926,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fdb95b6c-53cb-4857-8bbc-5040202e9834}</x14:id>
+          <x14:id>{0dd3cb71-d0dc-48e1-8ca6-d531743c172f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34948,7 +34948,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e1f65c02-9738-4732-a8c5-2bbd9c5ce6f3}</x14:id>
+          <x14:id>{c9ba7fb7-7f59-4c20-8634-c2ff90ae396a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34967,7 +34967,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{062a3a6d-72b6-4230-bb4d-fa9666034505}">
+          <x14:cfRule type="dataBar" id="{4e7c62fb-1a80-4f0f-ab77-232ac1b6e736}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34980,7 +34980,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b36333ca-9fd5-47a9-89e4-71ffa5a4aed6}">
+          <x14:cfRule type="dataBar" id="{23ad5611-fcb4-4eed-a33c-035351234423}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34993,7 +34993,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f34c8460-4591-4af7-96ff-f70c1e64e2fb}">
+          <x14:cfRule type="dataBar" id="{8378a0b3-9c66-4adb-9ffe-f4d774796200}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35006,7 +35006,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a170552-a4cf-48c5-84f5-01aba45dd39a}">
+          <x14:cfRule type="dataBar" id="{b1de088a-4f58-4956-9261-dfe205e64253}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35019,7 +35019,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d229eb8e-b1c9-42a3-8714-5e62fcfdb59f}">
+          <x14:cfRule type="dataBar" id="{925c761e-db78-4b0d-b2ad-f339781e0635}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35032,7 +35032,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6bbb3c63-ab75-4259-a608-cc436ddfec84}">
+          <x14:cfRule type="dataBar" id="{f7a8e535-848c-4253-9c21-603d86f38527}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35045,7 +35045,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ca4d0ad-9e00-4726-b503-71376030acaa}">
+          <x14:cfRule type="dataBar" id="{fc595743-955e-4f09-8989-ea08fbd1b2c9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35058,7 +35058,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94b061ee-bff8-4234-9b69-035f98693438}">
+          <x14:cfRule type="dataBar" id="{23fc40e7-50d7-4640-8b53-b0f881b47ff1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35071,7 +35071,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52ac152c-e6e2-4e1b-99af-7dbfc1981505}">
+          <x14:cfRule type="dataBar" id="{b24efd57-e291-46f4-bc48-84b964c75ae6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35084,7 +35084,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{345ffe5b-b48f-429d-b47f-320b29bc0360}">
+          <x14:cfRule type="dataBar" id="{45e00894-24cc-4ea1-bd92-c84623e4c4fc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35097,7 +35097,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b7cd9f26-3e27-4e8e-ae61-89989088a932}">
+          <x14:cfRule type="dataBar" id="{4b200c81-e601-4b28-9ea9-5312455cf0ed}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35110,7 +35110,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e536f0fc-29d4-4100-938f-ae3b51b1f4db}">
+          <x14:cfRule type="dataBar" id="{7d39900a-c9f9-48cc-8605-da605622c716}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35123,7 +35123,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fff15cc7-a51e-4958-ad6b-d6a06e1c0b38}">
+          <x14:cfRule type="dataBar" id="{166c63bf-6c1d-44f9-8ce3-635e8609effb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35136,7 +35136,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dbcb3dfd-4001-44ea-b584-001c8b1ffd79}">
+          <x14:cfRule type="dataBar" id="{ed69ec66-442e-47ab-8f80-3c3681fd47a7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35149,7 +35149,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b38aa4dd-b213-4e49-a128-3f7c1e397d9f}">
+          <x14:cfRule type="dataBar" id="{a028e7ab-9533-42f0-99c7-0de08964a13b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35162,7 +35162,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5f4ff00d-dbaa-4f7e-9fd9-95e112173f8a}">
+          <x14:cfRule type="dataBar" id="{577d159c-efb4-4f48-b305-bc0cdb22604d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35175,7 +35175,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{47363c4c-c339-4ec1-a5dd-d1791ae68057}">
+          <x14:cfRule type="dataBar" id="{e8d229fe-5f5a-491d-84cf-bd9b7bfb6fcf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35188,7 +35188,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5a1d23d1-0a64-4892-bdce-228f660268c0}">
+          <x14:cfRule type="dataBar" id="{c3d2ee88-d706-4703-8ba5-4c9c3105e9ca}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35201,7 +35201,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{462c3fad-25e8-4ae3-a95c-b7770fee264a}">
+          <x14:cfRule type="dataBar" id="{65933897-75ba-4b44-85b5-9578a745f442}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35214,7 +35214,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f979b91f-a2a4-47b2-81d2-382f1b9ef82f}">
+          <x14:cfRule type="dataBar" id="{1466e6d5-de42-4ec6-a106-0d2afa7ebaab}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35227,7 +35227,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70d60f34-1578-4270-ad9c-89f55a59b83f}">
+          <x14:cfRule type="dataBar" id="{836339a8-314d-4e11-8253-5428b4c14918}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35240,7 +35240,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{48e6612c-97df-43fb-87f1-a0b9bf531f6a}">
+          <x14:cfRule type="dataBar" id="{5536eb1c-2eaa-49b4-94aa-e0cb2de32dda}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35253,7 +35253,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f10672a5-5024-4401-9d40-3bbfaaaff302}">
+          <x14:cfRule type="dataBar" id="{05a33d5b-2563-44b6-9b0d-7f062b54dbbd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35266,7 +35266,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93e36254-ad4c-4422-9e8c-97a296409f69}">
+          <x14:cfRule type="dataBar" id="{429cd1c3-3665-496a-aeec-eae5465b74eb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35279,7 +35279,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2686627b-7afc-40d9-8abd-800c5da752bb}">
+          <x14:cfRule type="dataBar" id="{c334eac3-ff80-4042-9118-2f0b1d193612}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35292,7 +35292,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11099acc-46b9-4b7c-9686-188e715cf273}">
+          <x14:cfRule type="dataBar" id="{db5096fe-f115-4fb5-aac1-f64a124fe748}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35305,7 +35305,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{975a1405-eb3e-4f78-886b-f2a0532f2841}">
+          <x14:cfRule type="dataBar" id="{0de32c3f-0b04-4dd7-8ca7-4431654148b6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35318,7 +35318,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{727c82c2-c91d-483f-8ece-57f3e7ae5a14}">
+          <x14:cfRule type="dataBar" id="{9b89200a-1953-4446-a292-617d14e4352d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35331,7 +35331,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ecfbbb0-c27c-42f6-bf88-efa7bd9b5a99}">
+          <x14:cfRule type="dataBar" id="{2b97c2fc-8fea-4d0e-b704-fae0e8f3ec74}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35344,7 +35344,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e4eef42-2b6f-4726-92ee-09695918e9e4}">
+          <x14:cfRule type="dataBar" id="{2fabc8ea-5dca-4902-aad9-92459e09aac3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35357,7 +35357,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fdb95b6c-53cb-4857-8bbc-5040202e9834}">
+          <x14:cfRule type="dataBar" id="{0dd3cb71-d0dc-48e1-8ca6-d531743c172f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35370,7 +35370,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e1f65c02-9738-4732-a8c5-2bbd9c5ce6f3}">
+          <x14:cfRule type="dataBar" id="{c9ba7fb7-7f59-4c20-8634-c2ff90ae396a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -39294,7 +39294,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>188699.09</v>
+        <v>197187.7</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -39325,7 +39325,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.737357626891201</v>
+        <v>0.770527587197872</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -39426,7 +39426,7 @@
       </c>
       <c r="G7" s="36">
         <f>毛立新!G62</f>
-        <v>33716.99</v>
+        <v>42205.6</v>
       </c>
       <c r="H7" s="36">
         <f>毛立新!H62</f>
@@ -39458,7 +39458,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>462418.39</v>
+        <v>470907</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -39484,7 +39484,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.404039421594971</v>
+        <v>0.505760633202095</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -39516,7 +39516,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.403002131092803</v>
+        <v>0.410400037391503</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -39617,7 +39617,7 @@
       </c>
       <c r="G11" s="20">
         <f>毛立新!G63</f>
-        <v>4045</v>
+        <v>6031</v>
       </c>
       <c r="H11" s="20">
         <f>毛立新!H63</f>
@@ -39649,7 +39649,7 @@
       </c>
       <c r="O11" s="20">
         <f t="shared" si="1"/>
-        <v>34292</v>
+        <v>36278</v>
       </c>
     </row>
     <row r="12" ht="15.6" spans="1:15">
@@ -39675,7 +39675,7 @@
       </c>
       <c r="G12" s="15">
         <f t="shared" si="2"/>
-        <v>0.674166666666667</v>
+        <v>1.00516666666667</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="2"/>
@@ -39707,7 +39707,7 @@
       </c>
       <c r="O12" s="15">
         <f t="shared" si="2"/>
-        <v>0.415660606060606</v>
+        <v>0.439733333333333</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:15">
@@ -39808,7 +39808,7 @@
       </c>
       <c r="G15" s="20">
         <f>毛立新!G64</f>
-        <v>887</v>
+        <v>1341</v>
       </c>
       <c r="H15" s="20">
         <f>毛立新!H64</f>
@@ -39840,7 +39840,7 @@
       </c>
       <c r="O15" s="20">
         <f t="shared" si="1"/>
-        <v>7687</v>
+        <v>8141</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:15">
@@ -39866,7 +39866,7 @@
       </c>
       <c r="G16" s="15">
         <f t="shared" si="3"/>
-        <v>0.564206093803491</v>
+        <v>0.852988017802121</v>
       </c>
       <c r="H16" s="15">
         <f t="shared" si="3"/>
@@ -39898,7 +39898,7 @@
       </c>
       <c r="O16" s="15">
         <f t="shared" si="3"/>
-        <v>0.355605390432915</v>
+        <v>0.37660771217827</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:15">
@@ -39999,7 +39999,7 @@
       </c>
       <c r="G19" s="23">
         <f>毛立新!G65</f>
-        <v>18377548</v>
+        <v>27662782</v>
       </c>
       <c r="H19" s="23">
         <f>毛立新!H65</f>
@@ -40031,7 +40031,7 @@
       </c>
       <c r="O19" s="23">
         <f>SUM(C19:N19)</f>
-        <v>173060511</v>
+        <v>182345745</v>
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:15">
@@ -40057,7 +40057,7 @@
       </c>
       <c r="G20" s="15">
         <f t="shared" si="4"/>
-        <v>0.702780145743154</v>
+        <v>1.05785896821606</v>
       </c>
       <c r="H20" s="15">
         <f t="shared" si="4"/>
@@ -40089,7 +40089,7 @@
       </c>
       <c r="O20" s="15">
         <f t="shared" si="4"/>
-        <v>0.481312567400038</v>
+        <v>0.507136481761703</v>
       </c>
     </row>
     <row r="21" ht="15.6" spans="1:15">
@@ -40190,7 +40190,7 @@
       </c>
       <c r="G23" s="25">
         <f>毛立新!G66</f>
-        <v>401111.57</v>
+        <v>606252.14</v>
       </c>
       <c r="H23" s="25">
         <f>毛立新!H66</f>
@@ -40222,7 +40222,7 @@
       </c>
       <c r="O23" s="36">
         <f>SUM(C23:N23)</f>
-        <v>3318563.2</v>
+        <v>3523703.77</v>
       </c>
     </row>
     <row r="24" ht="15.6" spans="1:15">
@@ -40248,7 +40248,7 @@
       </c>
       <c r="G24" s="15">
         <f t="shared" si="6"/>
-        <v>0.5991797700818</v>
+        <v>0.905618399032466</v>
       </c>
       <c r="H24" s="15">
         <f t="shared" si="6"/>
@@ -40280,7 +40280,7 @@
       </c>
       <c r="O24" s="15">
         <f t="shared" si="6"/>
-        <v>0.360528288956959</v>
+        <v>0.382814734698826</v>
       </c>
     </row>
     <row r="25" ht="15.6" spans="1:15">
@@ -40323,7 +40323,7 @@
       </c>
       <c r="G26" s="15">
         <f t="shared" si="7"/>
-        <v>0.727172818430402</v>
+        <v>0.726052435723927</v>
       </c>
       <c r="H26" s="15" t="e">
         <f t="shared" si="7"/>
@@ -40355,7 +40355,7 @@
       </c>
       <c r="O26" s="15">
         <f t="shared" si="7"/>
-        <v>0.760303261788011</v>
+        <v>0.758446257547715</v>
       </c>
     </row>
     <row r="27" ht="15.6" spans="1:15">
@@ -40381,7 +40381,7 @@
       </c>
       <c r="G27" s="15">
         <f t="shared" si="8"/>
-        <v>0.780716934487021</v>
+        <v>0.77764881445863</v>
       </c>
       <c r="H27" s="15" t="e">
         <f t="shared" si="8"/>
@@ -40413,7 +40413,7 @@
       </c>
       <c r="O27" s="15">
         <f t="shared" si="8"/>
-        <v>0.775836929896186</v>
+        <v>0.775594023926347</v>
       </c>
     </row>
     <row r="28" ht="15.6" spans="1:15">
@@ -40439,7 +40439,7 @@
       </c>
       <c r="G28" s="15">
         <f t="shared" si="9"/>
-        <v>0.0840588816722489</v>
+        <v>0.0696172387944066</v>
       </c>
       <c r="H28" s="15" t="e">
         <f t="shared" si="9"/>
@@ -40471,7 +40471,7 @@
       </c>
       <c r="O28" s="15">
         <f t="shared" si="9"/>
-        <v>0.139342951190443</v>
+        <v>0.133639780962632</v>
       </c>
     </row>
     <row r="29" ht="15.6" spans="1:15">
@@ -40519,7 +40519,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{abfec66d-841e-4daa-82fa-0a6ea9484560}</x14:id>
+          <x14:id>{75818aa9-10d9-4b8b-9b8f-4464d641576d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40530,7 +40530,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{abfec66d-841e-4daa-82fa-0a6ea9484560}">
+          <x14:cfRule type="dataBar" id="{75818aa9-10d9-4b8b-9b8f-4464d641576d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -12906,16 +12906,6 @@
             <v>392105.278688525</v>
           </cell>
         </row>
-        <row r="32">
-          <cell r="F32">
-            <v>33154.43</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="F33">
-            <v>95210.94</v>
-          </cell>
-        </row>
         <row r="44">
           <cell r="B44">
             <v>372843</v>
@@ -12952,16 +12942,6 @@
           </cell>
           <cell r="M44">
             <v>318392.868852459</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="F45">
-            <v>100423.98</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="F46">
-            <v>159761.43</v>
           </cell>
         </row>
         <row r="58">
@@ -13015,9 +12995,6 @@
           <cell r="E59">
             <v>58296.43</v>
           </cell>
-          <cell r="F59">
-            <v>37248.15</v>
-          </cell>
         </row>
         <row r="60">
           <cell r="D60">
@@ -13026,9 +13003,6 @@
           <cell r="E60">
             <v>97059.95</v>
           </cell>
-          <cell r="F60">
-            <v>66068.28</v>
-          </cell>
         </row>
         <row r="61">
           <cell r="D61">
@@ -13099,9 +13073,6 @@
           <cell r="E71">
             <v>-1579</v>
           </cell>
-          <cell r="F71">
-            <v>3973.7</v>
-          </cell>
         </row>
         <row r="72">
           <cell r="D72">
@@ -13109,9 +13080,6 @@
           </cell>
           <cell r="E72">
             <v>17659.06</v>
-          </cell>
-          <cell r="F72">
-            <v>10854.18</v>
           </cell>
         </row>
         <row r="73">
@@ -22645,7 +22613,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{894d8845-8077-4bcb-99f3-7cc035ae6d06}</x14:id>
+          <x14:id>{9265f204-259c-4bec-ae0d-b47cc8f27332}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22659,7 +22627,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d812a28-6417-4dc0-98a6-270f5c872930}</x14:id>
+          <x14:id>{5e4104db-9ef9-49d9-b9be-a4286d26b6c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22673,7 +22641,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee8df4bd-4138-43a1-bffe-1bfa4ba0338b}</x14:id>
+          <x14:id>{bdacad49-4e63-4f27-8c97-d3c8ef5ea113}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22687,7 +22655,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{96c481e3-e0ba-49b0-83a5-ad6a7a280450}</x14:id>
+          <x14:id>{72c3bb80-5e8a-4cb1-8a36-5fc24efecbd2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22701,7 +22669,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b1cf017-7c47-4099-9b0b-f3a7b3a9a419}</x14:id>
+          <x14:id>{e3343502-fcb2-4066-a4ef-e3e07d016517}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22715,7 +22683,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5bfcbb34-3e97-442e-b539-66b4aaf20d51}</x14:id>
+          <x14:id>{e6856cf5-db5a-40e0-9029-0c1e664bc1b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22729,7 +22697,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{54e4f7ce-82e9-4048-a10b-829189d94f17}</x14:id>
+          <x14:id>{6d17bd62-db7d-48ca-a92c-a2c8045f1e63}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22743,7 +22711,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b9fd152-602b-4b65-a49e-8e0c3cad5ce4}</x14:id>
+          <x14:id>{2f91967e-ca7f-4948-9685-612f483e72a8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22757,7 +22725,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06d2cb8b-d821-4d1b-847f-c3b70607a09a}</x14:id>
+          <x14:id>{a7ac2ebc-73bf-4536-a158-d25efec303e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22771,7 +22739,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b0068023-a4aa-47d1-8245-4f7ecccdc6af}</x14:id>
+          <x14:id>{b4d71608-59fb-4f13-a36c-38cd3e8cef2f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22785,7 +22753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f45ebaf3-139d-4e94-aa61-6a18f7cc5f13}</x14:id>
+          <x14:id>{1ff031d3-64bf-4123-bb22-a5aaf8684478}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22799,7 +22767,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eec48894-ea22-45e4-bc7d-9aaa6995c4a5}</x14:id>
+          <x14:id>{76815c33-b02b-44ce-a62d-4064250b1c2c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22813,7 +22781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06ba95ac-b624-4fe4-84e3-ad867aaaf8d5}</x14:id>
+          <x14:id>{f0a8bdde-40e8-478d-8bda-1e4f15d238e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22835,7 +22803,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44f30c6f-98ab-41b2-a04a-be344c77753a}</x14:id>
+          <x14:id>{72eaacc1-5142-4b72-a4b4-a05607f54656}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22865,7 +22833,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2de6cf63-2ff2-4d71-878a-a37c920dfcdd}</x14:id>
+          <x14:id>{600f48f5-a61b-4092-b93f-0df788672287}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22895,7 +22863,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f3aeb7f-9ee0-4dc5-ac76-bf80a1f5bdcc}</x14:id>
+          <x14:id>{5760e5f2-4576-4a90-85b2-0cb7522ffe6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22925,7 +22893,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{faff200a-1fdd-4ef5-a323-7084b79d6196}</x14:id>
+          <x14:id>{a953d099-1168-4610-a4e4-ac5859fdda8d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22955,7 +22923,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c72a6826-a7c5-4cb7-b5c0-b663710bee6b}</x14:id>
+          <x14:id>{16850873-27a2-4354-834e-f84b64e6c5ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22985,7 +22953,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45a15644-008e-4651-9843-aabbc07ee446}</x14:id>
+          <x14:id>{a2d346e7-a893-4bad-85e7-ae1f37bf6946}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23015,7 +22983,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61e4207f-5dae-477f-b1f4-f0066d93c9ef}</x14:id>
+          <x14:id>{49cdc146-8ffd-46c7-b4e6-dead92c8b85a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23045,7 +23013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{143c06d3-57f6-4865-a91a-b63576c9ab64}</x14:id>
+          <x14:id>{0968bf44-462f-42db-8947-bca078138040}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23067,7 +23035,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89851562-e9dc-40cb-8dcd-18bb06477092}</x14:id>
+          <x14:id>{2caf380d-5e11-4f15-899a-2bbe52c6286b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23089,7 +23057,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{338c4524-f247-4f87-b315-c2e3360c8217}</x14:id>
+          <x14:id>{f7dda6d6-f7a6-49ed-848f-66a0b753b51c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23111,7 +23079,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66fcda84-60c9-413c-bfc1-0523d3ed90c8}</x14:id>
+          <x14:id>{99e15e6c-256f-4dde-9ef8-c1107fca42b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23133,7 +23101,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0160fc17-ec5f-4e49-a468-f27670e078a3}</x14:id>
+          <x14:id>{07985bdd-c019-4f6b-a8b7-be8a9bf93389}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23155,7 +23123,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e839c1b-39da-4486-b205-52b74d4fb5c8}</x14:id>
+          <x14:id>{0f080141-1793-4bc4-b4e8-d22d4d63199a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23177,7 +23145,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b804f76-803e-460b-866c-65f180321573}</x14:id>
+          <x14:id>{1eb7ae17-0d28-44f2-92b3-c593981905fd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23199,7 +23167,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{df98c5e1-2265-4d0b-84b3-0c1c41efc6d0}</x14:id>
+          <x14:id>{9853a094-2189-4ca1-afb0-a3446402765d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23221,7 +23189,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{892e0eb4-bbe8-4d59-9e89-c439ab467c69}</x14:id>
+          <x14:id>{097a8368-708c-4cdc-87f7-812a2bd687b4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23243,7 +23211,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{96be1bf8-fb09-4057-9d48-998b3a099c37}</x14:id>
+          <x14:id>{fec691d3-9d13-44db-b9bb-6ad41ea9782b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23265,7 +23233,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea42c463-830a-46eb-af10-62056b7bb2e2}</x14:id>
+          <x14:id>{9b43b6b5-2590-4a34-82f2-d14736c4bc3d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23287,7 +23255,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{289381e6-d045-4751-b35b-9e8795f4e742}</x14:id>
+          <x14:id>{37f97cc0-b8fa-400f-81cf-75f95420e697}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23309,7 +23277,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{748b7ac9-d5f1-4d5b-a8ad-932b772f325a}</x14:id>
+          <x14:id>{98060026-2945-4d2d-a4cb-22de79f9dbb6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23328,7 +23296,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{894d8845-8077-4bcb-99f3-7cc035ae6d06}">
+          <x14:cfRule type="dataBar" id="{9265f204-259c-4bec-ae0d-b47cc8f27332}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23341,7 +23309,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9d812a28-6417-4dc0-98a6-270f5c872930}">
+          <x14:cfRule type="dataBar" id="{5e4104db-9ef9-49d9-b9be-a4286d26b6c0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23354,7 +23322,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee8df4bd-4138-43a1-bffe-1bfa4ba0338b}">
+          <x14:cfRule type="dataBar" id="{bdacad49-4e63-4f27-8c97-d3c8ef5ea113}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23367,7 +23335,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{96c481e3-e0ba-49b0-83a5-ad6a7a280450}">
+          <x14:cfRule type="dataBar" id="{72c3bb80-5e8a-4cb1-8a36-5fc24efecbd2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23380,7 +23348,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b1cf017-7c47-4099-9b0b-f3a7b3a9a419}">
+          <x14:cfRule type="dataBar" id="{e3343502-fcb2-4066-a4ef-e3e07d016517}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23393,7 +23361,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5bfcbb34-3e97-442e-b539-66b4aaf20d51}">
+          <x14:cfRule type="dataBar" id="{e6856cf5-db5a-40e0-9029-0c1e664bc1b1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23406,7 +23374,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{54e4f7ce-82e9-4048-a10b-829189d94f17}">
+          <x14:cfRule type="dataBar" id="{6d17bd62-db7d-48ca-a92c-a2c8045f1e63}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23419,7 +23387,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8b9fd152-602b-4b65-a49e-8e0c3cad5ce4}">
+          <x14:cfRule type="dataBar" id="{2f91967e-ca7f-4948-9685-612f483e72a8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23432,7 +23400,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{06d2cb8b-d821-4d1b-847f-c3b70607a09a}">
+          <x14:cfRule type="dataBar" id="{a7ac2ebc-73bf-4536-a158-d25efec303e1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23445,7 +23413,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b0068023-a4aa-47d1-8245-4f7ecccdc6af}">
+          <x14:cfRule type="dataBar" id="{b4d71608-59fb-4f13-a36c-38cd3e8cef2f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23458,7 +23426,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f45ebaf3-139d-4e94-aa61-6a18f7cc5f13}">
+          <x14:cfRule type="dataBar" id="{1ff031d3-64bf-4123-bb22-a5aaf8684478}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23471,7 +23439,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eec48894-ea22-45e4-bc7d-9aaa6995c4a5}">
+          <x14:cfRule type="dataBar" id="{76815c33-b02b-44ce-a62d-4064250b1c2c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23484,7 +23452,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{06ba95ac-b624-4fe4-84e3-ad867aaaf8d5}">
+          <x14:cfRule type="dataBar" id="{f0a8bdde-40e8-478d-8bda-1e4f15d238e3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23497,7 +23465,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{44f30c6f-98ab-41b2-a04a-be344c77753a}">
+          <x14:cfRule type="dataBar" id="{72eaacc1-5142-4b72-a4b4-a05607f54656}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23510,7 +23478,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2de6cf63-2ff2-4d71-878a-a37c920dfcdd}">
+          <x14:cfRule type="dataBar" id="{600f48f5-a61b-4092-b93f-0df788672287}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23523,7 +23491,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1f3aeb7f-9ee0-4dc5-ac76-bf80a1f5bdcc}">
+          <x14:cfRule type="dataBar" id="{5760e5f2-4576-4a90-85b2-0cb7522ffe6d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23536,7 +23504,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{faff200a-1fdd-4ef5-a323-7084b79d6196}">
+          <x14:cfRule type="dataBar" id="{a953d099-1168-4610-a4e4-ac5859fdda8d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23549,7 +23517,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c72a6826-a7c5-4cb7-b5c0-b663710bee6b}">
+          <x14:cfRule type="dataBar" id="{16850873-27a2-4354-834e-f84b64e6c5ba}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23562,7 +23530,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{45a15644-008e-4651-9843-aabbc07ee446}">
+          <x14:cfRule type="dataBar" id="{a2d346e7-a893-4bad-85e7-ae1f37bf6946}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23575,7 +23543,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{61e4207f-5dae-477f-b1f4-f0066d93c9ef}">
+          <x14:cfRule type="dataBar" id="{49cdc146-8ffd-46c7-b4e6-dead92c8b85a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23588,7 +23556,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{143c06d3-57f6-4865-a91a-b63576c9ab64}">
+          <x14:cfRule type="dataBar" id="{0968bf44-462f-42db-8947-bca078138040}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23601,7 +23569,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{89851562-e9dc-40cb-8dcd-18bb06477092}">
+          <x14:cfRule type="dataBar" id="{2caf380d-5e11-4f15-899a-2bbe52c6286b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23614,7 +23582,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{338c4524-f247-4f87-b315-c2e3360c8217}">
+          <x14:cfRule type="dataBar" id="{f7dda6d6-f7a6-49ed-848f-66a0b753b51c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23627,7 +23595,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66fcda84-60c9-413c-bfc1-0523d3ed90c8}">
+          <x14:cfRule type="dataBar" id="{99e15e6c-256f-4dde-9ef8-c1107fca42b7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23640,7 +23608,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0160fc17-ec5f-4e49-a468-f27670e078a3}">
+          <x14:cfRule type="dataBar" id="{07985bdd-c019-4f6b-a8b7-be8a9bf93389}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23653,7 +23621,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e839c1b-39da-4486-b205-52b74d4fb5c8}">
+          <x14:cfRule type="dataBar" id="{0f080141-1793-4bc4-b4e8-d22d4d63199a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23666,7 +23634,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0b804f76-803e-460b-866c-65f180321573}">
+          <x14:cfRule type="dataBar" id="{1eb7ae17-0d28-44f2-92b3-c593981905fd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23679,7 +23647,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{df98c5e1-2265-4d0b-84b3-0c1c41efc6d0}">
+          <x14:cfRule type="dataBar" id="{9853a094-2189-4ca1-afb0-a3446402765d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23692,7 +23660,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{892e0eb4-bbe8-4d59-9e89-c439ab467c69}">
+          <x14:cfRule type="dataBar" id="{097a8368-708c-4cdc-87f7-812a2bd687b4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23705,7 +23673,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{96be1bf8-fb09-4057-9d48-998b3a099c37}">
+          <x14:cfRule type="dataBar" id="{fec691d3-9d13-44db-b9bb-6ad41ea9782b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23718,7 +23686,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ea42c463-830a-46eb-af10-62056b7bb2e2}">
+          <x14:cfRule type="dataBar" id="{9b43b6b5-2590-4a34-82f2-d14736c4bc3d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23731,7 +23699,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{289381e6-d045-4751-b35b-9e8795f4e742}">
+          <x14:cfRule type="dataBar" id="{37f97cc0-b8fa-400f-81cf-75f95420e697}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23744,7 +23712,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{748b7ac9-d5f1-4d5b-a8ad-932b772f325a}">
+          <x14:cfRule type="dataBar" id="{98060026-2945-4d2d-a4cb-22de79f9dbb6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34308,7 +34276,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e7c62fb-1a80-4f0f-ab77-232ac1b6e736}</x14:id>
+          <x14:id>{0a417cef-a5f8-44ab-b912-131318abc8ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34322,7 +34290,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23ad5611-fcb4-4eed-a33c-035351234423}</x14:id>
+          <x14:id>{72273551-06e5-48c3-a647-fc9c0fbbc5e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34336,7 +34304,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8378a0b3-9c66-4adb-9ffe-f4d774796200}</x14:id>
+          <x14:id>{bf74ee20-8d29-4758-8460-2ab9e1ea198c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34350,7 +34318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b1de088a-4f58-4956-9261-dfe205e64253}</x14:id>
+          <x14:id>{3c447687-5b89-4776-aae5-7a27fcc64a3f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34364,7 +34332,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{925c761e-db78-4b0d-b2ad-f339781e0635}</x14:id>
+          <x14:id>{0f626a0e-e5b2-4840-bb93-cb58b5ed78ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34378,7 +34346,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7a8e535-848c-4253-9c21-603d86f38527}</x14:id>
+          <x14:id>{5354102d-07f5-4808-8c0d-52f86ed05942}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34398,7 +34366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc595743-955e-4f09-8989-ea08fbd1b2c9}</x14:id>
+          <x14:id>{559de02a-d270-4535-a719-dc144cec0f14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34412,7 +34380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23fc40e7-50d7-4640-8b53-b0f881b47ff1}</x14:id>
+          <x14:id>{2fb65f87-a4af-44bb-922e-40028a7a0630}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34426,7 +34394,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b24efd57-e291-46f4-bc48-84b964c75ae6}</x14:id>
+          <x14:id>{a9eac222-db16-4748-8e4b-3a9a2d7d52bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34440,7 +34408,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45e00894-24cc-4ea1-bd92-c84623e4c4fc}</x14:id>
+          <x14:id>{5af5b80f-691b-4772-a2cd-ffd2871350cc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34454,7 +34422,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b200c81-e601-4b28-9ea9-5312455cf0ed}</x14:id>
+          <x14:id>{ed569490-f9da-42b9-85ac-6be6d2dbbf98}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34468,7 +34436,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7d39900a-c9f9-48cc-8605-da605622c716}</x14:id>
+          <x14:id>{8e9569bf-2ad9-49d5-bdc6-c7730f24b6b8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34490,7 +34458,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{166c63bf-6c1d-44f9-8ce3-635e8609effb}</x14:id>
+          <x14:id>{b7a3e63b-9f36-4c09-bdc2-0497c5d1c4d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34520,7 +34488,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed69ec66-442e-47ab-8f80-3c3681fd47a7}</x14:id>
+          <x14:id>{eccc4d28-7e45-477f-bf39-ed9513fd8323}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34550,7 +34518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a028e7ab-9533-42f0-99c7-0de08964a13b}</x14:id>
+          <x14:id>{5750f244-590b-4634-951d-ca85a2b680a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34580,7 +34548,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{577d159c-efb4-4f48-b305-bc0cdb22604d}</x14:id>
+          <x14:id>{ee311c7e-708c-4d33-b490-55da699ba190}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34610,7 +34578,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8d229fe-5f5a-491d-84cf-bd9b7bfb6fcf}</x14:id>
+          <x14:id>{a24c9846-a022-40ea-9a09-ee86ac327c02}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34640,7 +34608,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3d2ee88-d706-4703-8ba5-4c9c3105e9ca}</x14:id>
+          <x14:id>{4c2a6cfa-2216-491f-873a-0bf287dde47d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34662,7 +34630,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65933897-75ba-4b44-85b5-9578a745f442}</x14:id>
+          <x14:id>{fa8187d0-e368-4958-993d-6381e4235c18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34684,7 +34652,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1466e6d5-de42-4ec6-a106-0d2afa7ebaab}</x14:id>
+          <x14:id>{abcdc875-9032-4353-b0b5-d5283770d0e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34706,7 +34674,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{836339a8-314d-4e11-8253-5428b4c14918}</x14:id>
+          <x14:id>{70ad9bdb-0b38-4c28-ba7a-cf417a58e9f4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34728,7 +34696,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5536eb1c-2eaa-49b4-94aa-e0cb2de32dda}</x14:id>
+          <x14:id>{e6a19257-ffc0-43be-a3f6-0cdcf374b31e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34750,7 +34718,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{05a33d5b-2563-44b6-9b0d-7f062b54dbbd}</x14:id>
+          <x14:id>{c668fdb9-a5ba-47a1-ad05-9631c8b71356}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34772,7 +34740,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{429cd1c3-3665-496a-aeec-eae5465b74eb}</x14:id>
+          <x14:id>{d4983e3c-f55f-4033-8f4a-9c78e8496e66}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34794,7 +34762,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c334eac3-ff80-4042-9118-2f0b1d193612}</x14:id>
+          <x14:id>{3251858b-c8d5-4f31-a572-9a5b130e92e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34816,7 +34784,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db5096fe-f115-4fb5-aac1-f64a124fe748}</x14:id>
+          <x14:id>{08437213-ef4d-4df7-8cda-265b766e59c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34838,7 +34806,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0de32c3f-0b04-4dd7-8ca7-4431654148b6}</x14:id>
+          <x14:id>{c873760d-3460-4202-a44a-4fe5c62ffbcd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34860,7 +34828,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b89200a-1953-4446-a292-617d14e4352d}</x14:id>
+          <x14:id>{9a451206-bb11-4648-961f-873797542b6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34882,7 +34850,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b97c2fc-8fea-4d0e-b704-fae0e8f3ec74}</x14:id>
+          <x14:id>{0b3cacf8-2bf7-4bdf-9513-cd1665c81a33}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34904,7 +34872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2fabc8ea-5dca-4902-aad9-92459e09aac3}</x14:id>
+          <x14:id>{67df189d-eb81-479e-8433-538497d1dad7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34926,7 +34894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0dd3cb71-d0dc-48e1-8ca6-d531743c172f}</x14:id>
+          <x14:id>{78dc50b0-59e5-462c-bdbe-3a8f393488e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34948,7 +34916,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c9ba7fb7-7f59-4c20-8634-c2ff90ae396a}</x14:id>
+          <x14:id>{a45cbf9f-b1f9-4139-af79-2672b29d3f96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34967,7 +34935,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4e7c62fb-1a80-4f0f-ab77-232ac1b6e736}">
+          <x14:cfRule type="dataBar" id="{0a417cef-a5f8-44ab-b912-131318abc8ec}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34980,7 +34948,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23ad5611-fcb4-4eed-a33c-035351234423}">
+          <x14:cfRule type="dataBar" id="{72273551-06e5-48c3-a647-fc9c0fbbc5e6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34993,7 +34961,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8378a0b3-9c66-4adb-9ffe-f4d774796200}">
+          <x14:cfRule type="dataBar" id="{bf74ee20-8d29-4758-8460-2ab9e1ea198c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35006,7 +34974,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b1de088a-4f58-4956-9261-dfe205e64253}">
+          <x14:cfRule type="dataBar" id="{3c447687-5b89-4776-aae5-7a27fcc64a3f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35019,7 +34987,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{925c761e-db78-4b0d-b2ad-f339781e0635}">
+          <x14:cfRule type="dataBar" id="{0f626a0e-e5b2-4840-bb93-cb58b5ed78ea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35032,7 +35000,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7a8e535-848c-4253-9c21-603d86f38527}">
+          <x14:cfRule type="dataBar" id="{5354102d-07f5-4808-8c0d-52f86ed05942}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35045,7 +35013,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fc595743-955e-4f09-8989-ea08fbd1b2c9}">
+          <x14:cfRule type="dataBar" id="{559de02a-d270-4535-a719-dc144cec0f14}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35058,7 +35026,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23fc40e7-50d7-4640-8b53-b0f881b47ff1}">
+          <x14:cfRule type="dataBar" id="{2fb65f87-a4af-44bb-922e-40028a7a0630}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35071,7 +35039,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b24efd57-e291-46f4-bc48-84b964c75ae6}">
+          <x14:cfRule type="dataBar" id="{a9eac222-db16-4748-8e4b-3a9a2d7d52bc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35084,7 +35052,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{45e00894-24cc-4ea1-bd92-c84623e4c4fc}">
+          <x14:cfRule type="dataBar" id="{5af5b80f-691b-4772-a2cd-ffd2871350cc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35097,7 +35065,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4b200c81-e601-4b28-9ea9-5312455cf0ed}">
+          <x14:cfRule type="dataBar" id="{ed569490-f9da-42b9-85ac-6be6d2dbbf98}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35110,7 +35078,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7d39900a-c9f9-48cc-8605-da605622c716}">
+          <x14:cfRule type="dataBar" id="{8e9569bf-2ad9-49d5-bdc6-c7730f24b6b8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35123,7 +35091,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{166c63bf-6c1d-44f9-8ce3-635e8609effb}">
+          <x14:cfRule type="dataBar" id="{b7a3e63b-9f36-4c09-bdc2-0497c5d1c4d3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35136,7 +35104,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ed69ec66-442e-47ab-8f80-3c3681fd47a7}">
+          <x14:cfRule type="dataBar" id="{eccc4d28-7e45-477f-bf39-ed9513fd8323}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35149,7 +35117,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a028e7ab-9533-42f0-99c7-0de08964a13b}">
+          <x14:cfRule type="dataBar" id="{5750f244-590b-4634-951d-ca85a2b680a4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35162,7 +35130,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{577d159c-efb4-4f48-b305-bc0cdb22604d}">
+          <x14:cfRule type="dataBar" id="{ee311c7e-708c-4d33-b490-55da699ba190}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35175,7 +35143,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e8d229fe-5f5a-491d-84cf-bd9b7bfb6fcf}">
+          <x14:cfRule type="dataBar" id="{a24c9846-a022-40ea-9a09-ee86ac327c02}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35188,7 +35156,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c3d2ee88-d706-4703-8ba5-4c9c3105e9ca}">
+          <x14:cfRule type="dataBar" id="{4c2a6cfa-2216-491f-873a-0bf287dde47d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35201,7 +35169,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{65933897-75ba-4b44-85b5-9578a745f442}">
+          <x14:cfRule type="dataBar" id="{fa8187d0-e368-4958-993d-6381e4235c18}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35214,7 +35182,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1466e6d5-de42-4ec6-a106-0d2afa7ebaab}">
+          <x14:cfRule type="dataBar" id="{abcdc875-9032-4353-b0b5-d5283770d0e1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35227,7 +35195,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{836339a8-314d-4e11-8253-5428b4c14918}">
+          <x14:cfRule type="dataBar" id="{70ad9bdb-0b38-4c28-ba7a-cf417a58e9f4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35240,7 +35208,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5536eb1c-2eaa-49b4-94aa-e0cb2de32dda}">
+          <x14:cfRule type="dataBar" id="{e6a19257-ffc0-43be-a3f6-0cdcf374b31e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35253,7 +35221,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{05a33d5b-2563-44b6-9b0d-7f062b54dbbd}">
+          <x14:cfRule type="dataBar" id="{c668fdb9-a5ba-47a1-ad05-9631c8b71356}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35266,7 +35234,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{429cd1c3-3665-496a-aeec-eae5465b74eb}">
+          <x14:cfRule type="dataBar" id="{d4983e3c-f55f-4033-8f4a-9c78e8496e66}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35279,7 +35247,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c334eac3-ff80-4042-9118-2f0b1d193612}">
+          <x14:cfRule type="dataBar" id="{3251858b-c8d5-4f31-a572-9a5b130e92e9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35292,7 +35260,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{db5096fe-f115-4fb5-aac1-f64a124fe748}">
+          <x14:cfRule type="dataBar" id="{08437213-ef4d-4df7-8cda-265b766e59c4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35305,7 +35273,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0de32c3f-0b04-4dd7-8ca7-4431654148b6}">
+          <x14:cfRule type="dataBar" id="{c873760d-3460-4202-a44a-4fe5c62ffbcd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35318,7 +35286,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b89200a-1953-4446-a292-617d14e4352d}">
+          <x14:cfRule type="dataBar" id="{9a451206-bb11-4648-961f-873797542b6c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35331,7 +35299,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2b97c2fc-8fea-4d0e-b704-fae0e8f3ec74}">
+          <x14:cfRule type="dataBar" id="{0b3cacf8-2bf7-4bdf-9513-cd1665c81a33}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35344,7 +35312,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2fabc8ea-5dca-4902-aad9-92459e09aac3}">
+          <x14:cfRule type="dataBar" id="{67df189d-eb81-479e-8433-538497d1dad7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35357,7 +35325,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0dd3cb71-d0dc-48e1-8ca6-d531743c172f}">
+          <x14:cfRule type="dataBar" id="{78dc50b0-59e5-462c-bdbe-3a8f393488e0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35370,7 +35338,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c9ba7fb7-7f59-4c20-8634-c2ff90ae396a}">
+          <x14:cfRule type="dataBar" id="{a45cbf9f-b1f9-4139-af79-2672b29d3f96}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -36265,7 +36233,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>128365.37</v>
+        <v>215515.08</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -36296,7 +36264,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.123203248802278</v>
+        <v>0.206848295781665</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -36396,8 +36364,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="36">
-        <f>[3]总目标!F32+[3]总目标!F33+[3]总目标!F34+[3]总目标!F35+[3]总目标!F36</f>
-        <v>128365.37</v>
+        <v>215515.08</v>
       </c>
       <c r="H7" s="36">
         <f>[3]总目标!G32+[3]总目标!G33+[3]总目标!G34+[3]总目标!G35+[3]总目标!G36</f>
@@ -36429,7 +36396,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>128365.37</v>
+        <v>215515.08</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -36455,7 +36422,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.509902759970367</v>
+        <v>0.856085516734259</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -36487,7 +36454,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.0237928068540694</v>
+        <v>0.0399461994506721</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -37022,7 +36989,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>260185.41</v>
+        <v>436243.42</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -37053,7 +37020,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.209312537717059</v>
+        <v>0.350946724117117</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -37153,8 +37120,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="36">
-        <f>SUM([3]总目标!F45:F49)</f>
-        <v>260185.41</v>
+        <v>436243.42</v>
       </c>
       <c r="H7" s="36">
         <f>[3]总目标!G45+[3]总目标!G46+[3]总目标!G47+[3]总目标!G48+[3]总目标!G49</f>
@@ -37186,7 +37152,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>260185.41</v>
+        <v>436243.42</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -37212,7 +37178,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.59358522756757</v>
+        <v>0.995242776047876</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -37244,7 +37210,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.0482058684753844</v>
+        <v>0.0808250275362169</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -37779,7 +37745,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>466446.56</v>
+        <v>507178.22</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -37810,7 +37776,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.313336117137097</v>
+        <v>0.340697665668934</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -37910,8 +37876,7 @@
         <v>363130.13</v>
       </c>
       <c r="G7" s="36">
-        <f>[3]总目标!F59+[3]总目标!F60+[3]总目标!F61+[3]总目标!F62+[3]总目标!F63</f>
-        <v>103316.43</v>
+        <v>144048.09</v>
       </c>
       <c r="H7" s="36">
         <f>[3]总目标!G59+[3]总目标!G60+[3]总目标!G61+[3]总目标!G62+[3]总目标!G63</f>
@@ -37943,7 +37908,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>1834555.34</v>
+        <v>1875287</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -37969,7 +37934,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.202045434960327</v>
+        <v>0.281700200048088</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -38001,7 +37966,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.310694583446848</v>
+        <v>0.317592770631977</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -38536,7 +38501,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>64650.76</v>
+        <v>71602.76</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -38567,7 +38532,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.131339004503658</v>
+        <v>0.1454620984829</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -38667,8 +38632,7 @@
         <v>49822.88</v>
       </c>
       <c r="G7" s="36">
-        <f>[3]总目标!F71+[3]总目标!F72+[3]总目标!F73+[3]总目标!F74+[3]总目标!F75</f>
-        <v>14827.88</v>
+        <v>21779.88</v>
       </c>
       <c r="H7" s="36">
         <f>[3]总目标!G71+[3]总目标!G72+[3]总目标!G73+[3]总目标!G74+[3]总目标!G75</f>
@@ -38700,7 +38664,7 @@
       </c>
       <c r="O7" s="36">
         <f>SUM(C7:N7)</f>
-        <v>131271.54</v>
+        <v>138223.54</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -38726,7 +38690,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>0.0759209520371109</v>
+        <v>0.111516226517481</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -38758,7 +38722,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.0711834060752513</v>
+        <v>0.0749532029332386</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -40519,7 +40483,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75818aa9-10d9-4b8b-9b8f-4464d641576d}</x14:id>
+          <x14:id>{18d372eb-e862-4bba-a136-3c667a84323e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40530,7 +40494,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75818aa9-10d9-4b8b-9b8f-4464d641576d}">
+          <x14:cfRule type="dataBar" id="{18d372eb-e862-4bba-a136-3c667a84323e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -40668,7 +40632,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4">
         <f>(F7+G7+H7)</f>
-        <v>32168</v>
+        <v>-3952.2</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
@@ -40699,7 +40663,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.190596439492672</v>
+        <v>-0.0234169127133467</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -40795,7 +40759,7 @@
         <v>32922</v>
       </c>
       <c r="G7" s="13">
-        <v>-754</v>
+        <v>-36874.2</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
@@ -40806,7 +40770,7 @@
       <c r="N7" s="13"/>
       <c r="O7" s="13">
         <f>SUM(C7:N7)</f>
-        <v>157650</v>
+        <v>121529.8</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -40832,7 +40796,7 @@
       </c>
       <c r="G8" s="15">
         <f t="shared" si="0"/>
-        <v>-0.0128758993309258</v>
+        <v>-0.6296929537247</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="0"/>
@@ -40864,7 +40828,7 @@
       </c>
       <c r="O8" s="15">
         <f t="shared" si="0"/>
-        <v>0.222389848700601</v>
+        <v>0.171436687818676</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -22613,7 +22613,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9265f204-259c-4bec-ae0d-b47cc8f27332}</x14:id>
+          <x14:id>{1054e69f-2f7a-4a23-afbd-3884b513e0ca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22627,7 +22627,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e4104db-9ef9-49d9-b9be-a4286d26b6c0}</x14:id>
+          <x14:id>{981c03dd-b5a3-41cd-91dd-5119ccc55c8b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22641,7 +22641,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bdacad49-4e63-4f27-8c97-d3c8ef5ea113}</x14:id>
+          <x14:id>{4ce2367b-1d99-4641-9b75-829f18893eaa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22655,7 +22655,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72c3bb80-5e8a-4cb1-8a36-5fc24efecbd2}</x14:id>
+          <x14:id>{5d571f6a-7950-4e5b-bed7-2d2a5f756495}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22669,7 +22669,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3343502-fcb2-4066-a4ef-e3e07d016517}</x14:id>
+          <x14:id>{243de982-267f-4d7a-b0a3-c95ea3da5294}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22683,7 +22683,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e6856cf5-db5a-40e0-9029-0c1e664bc1b1}</x14:id>
+          <x14:id>{e00ce940-ae50-4135-9fb3-42bd080a3abd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22697,7 +22697,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d17bd62-db7d-48ca-a92c-a2c8045f1e63}</x14:id>
+          <x14:id>{87dbb917-8afa-4cd8-8d01-9e47c90c8995}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22711,7 +22711,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f91967e-ca7f-4948-9685-612f483e72a8}</x14:id>
+          <x14:id>{663f5af0-d7a5-49db-add2-8885af59a442}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22725,7 +22725,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7ac2ebc-73bf-4536-a158-d25efec303e1}</x14:id>
+          <x14:id>{d36a9388-56cb-48be-9428-a545eb9849fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22739,7 +22739,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4d71608-59fb-4f13-a36c-38cd3e8cef2f}</x14:id>
+          <x14:id>{50489279-4cd9-4363-ba4e-1d3ad47a71cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22753,7 +22753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ff031d3-64bf-4123-bb22-a5aaf8684478}</x14:id>
+          <x14:id>{4b9ea658-3e4f-4d39-818e-5e76a3d2d72e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22767,7 +22767,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76815c33-b02b-44ce-a62d-4064250b1c2c}</x14:id>
+          <x14:id>{9b3600b1-889a-4d63-af5d-12086c640a8f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22781,7 +22781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f0a8bdde-40e8-478d-8bda-1e4f15d238e3}</x14:id>
+          <x14:id>{34b913d2-4d09-44ef-9ac4-f54fcafdecb7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22803,7 +22803,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72eaacc1-5142-4b72-a4b4-a05607f54656}</x14:id>
+          <x14:id>{a3b1401f-9a89-4373-a055-936d0a224c9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22833,7 +22833,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{600f48f5-a61b-4092-b93f-0df788672287}</x14:id>
+          <x14:id>{da948d02-b053-41a1-b468-7dbd2645871a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22863,7 +22863,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5760e5f2-4576-4a90-85b2-0cb7522ffe6d}</x14:id>
+          <x14:id>{3fe7fed2-b1cf-4012-8c20-ba6118ea55ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22893,7 +22893,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a953d099-1168-4610-a4e4-ac5859fdda8d}</x14:id>
+          <x14:id>{a498e1ff-c4ab-4f5c-b462-1b1258df0b2b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22923,7 +22923,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16850873-27a2-4354-834e-f84b64e6c5ba}</x14:id>
+          <x14:id>{fb436dce-c161-4296-83ce-2fb88b8b944b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22953,7 +22953,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a2d346e7-a893-4bad-85e7-ae1f37bf6946}</x14:id>
+          <x14:id>{29e276b4-e426-4cb1-b741-f5ad16f817f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22983,7 +22983,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49cdc146-8ffd-46c7-b4e6-dead92c8b85a}</x14:id>
+          <x14:id>{7483cd84-eb09-458c-b80b-4bf502db0fe9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23013,7 +23013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0968bf44-462f-42db-8947-bca078138040}</x14:id>
+          <x14:id>{acfdff71-e3ad-48c5-b6da-dc28d4114659}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23035,7 +23035,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2caf380d-5e11-4f15-899a-2bbe52c6286b}</x14:id>
+          <x14:id>{647570c6-44b4-4f68-a894-4d52241e04dc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23057,7 +23057,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7dda6d6-f7a6-49ed-848f-66a0b753b51c}</x14:id>
+          <x14:id>{137ec496-f13c-46ee-8243-33d7cc20497b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23079,7 +23079,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99e15e6c-256f-4dde-9ef8-c1107fca42b7}</x14:id>
+          <x14:id>{477bbc9b-60f1-49c6-add4-eb44ecde81f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23101,7 +23101,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{07985bdd-c019-4f6b-a8b7-be8a9bf93389}</x14:id>
+          <x14:id>{a3c5cca8-c0a9-4c7d-b729-ad3ed0105303}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23123,7 +23123,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f080141-1793-4bc4-b4e8-d22d4d63199a}</x14:id>
+          <x14:id>{c4db7b94-317d-4d27-b7f7-27d224e8099f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23145,7 +23145,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1eb7ae17-0d28-44f2-92b3-c593981905fd}</x14:id>
+          <x14:id>{4a0a589f-5e6b-438d-9c25-a69a16353ad0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23167,7 +23167,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9853a094-2189-4ca1-afb0-a3446402765d}</x14:id>
+          <x14:id>{733aae13-c8a1-41be-baee-0e45846e41fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23189,7 +23189,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{097a8368-708c-4cdc-87f7-812a2bd687b4}</x14:id>
+          <x14:id>{0f084c0c-61b1-412a-97ad-5b3eee9c37aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23211,7 +23211,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fec691d3-9d13-44db-b9bb-6ad41ea9782b}</x14:id>
+          <x14:id>{5c0d6a4d-a67c-474e-84aa-c20c51621ac9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23233,7 +23233,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b43b6b5-2590-4a34-82f2-d14736c4bc3d}</x14:id>
+          <x14:id>{78fd8f19-b9e0-4f84-85f8-136e50cfb38b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23255,7 +23255,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37f97cc0-b8fa-400f-81cf-75f95420e697}</x14:id>
+          <x14:id>{bd90acee-1578-41bc-ac97-5a562ba27e69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23277,7 +23277,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98060026-2945-4d2d-a4cb-22de79f9dbb6}</x14:id>
+          <x14:id>{90ee968d-a976-45ba-b327-e67fdbb27f5c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23296,7 +23296,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9265f204-259c-4bec-ae0d-b47cc8f27332}">
+          <x14:cfRule type="dataBar" id="{1054e69f-2f7a-4a23-afbd-3884b513e0ca}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23309,7 +23309,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5e4104db-9ef9-49d9-b9be-a4286d26b6c0}">
+          <x14:cfRule type="dataBar" id="{981c03dd-b5a3-41cd-91dd-5119ccc55c8b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23322,7 +23322,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bdacad49-4e63-4f27-8c97-d3c8ef5ea113}">
+          <x14:cfRule type="dataBar" id="{4ce2367b-1d99-4641-9b75-829f18893eaa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23335,7 +23335,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72c3bb80-5e8a-4cb1-8a36-5fc24efecbd2}">
+          <x14:cfRule type="dataBar" id="{5d571f6a-7950-4e5b-bed7-2d2a5f756495}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23348,7 +23348,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3343502-fcb2-4066-a4ef-e3e07d016517}">
+          <x14:cfRule type="dataBar" id="{243de982-267f-4d7a-b0a3-c95ea3da5294}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23361,7 +23361,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e6856cf5-db5a-40e0-9029-0c1e664bc1b1}">
+          <x14:cfRule type="dataBar" id="{e00ce940-ae50-4135-9fb3-42bd080a3abd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23374,7 +23374,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d17bd62-db7d-48ca-a92c-a2c8045f1e63}">
+          <x14:cfRule type="dataBar" id="{87dbb917-8afa-4cd8-8d01-9e47c90c8995}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23387,7 +23387,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2f91967e-ca7f-4948-9685-612f483e72a8}">
+          <x14:cfRule type="dataBar" id="{663f5af0-d7a5-49db-add2-8885af59a442}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23400,7 +23400,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a7ac2ebc-73bf-4536-a158-d25efec303e1}">
+          <x14:cfRule type="dataBar" id="{d36a9388-56cb-48be-9428-a545eb9849fb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23413,7 +23413,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b4d71608-59fb-4f13-a36c-38cd3e8cef2f}">
+          <x14:cfRule type="dataBar" id="{50489279-4cd9-4363-ba4e-1d3ad47a71cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23426,7 +23426,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ff031d3-64bf-4123-bb22-a5aaf8684478}">
+          <x14:cfRule type="dataBar" id="{4b9ea658-3e4f-4d39-818e-5e76a3d2d72e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23439,7 +23439,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{76815c33-b02b-44ce-a62d-4064250b1c2c}">
+          <x14:cfRule type="dataBar" id="{9b3600b1-889a-4d63-af5d-12086c640a8f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23452,7 +23452,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f0a8bdde-40e8-478d-8bda-1e4f15d238e3}">
+          <x14:cfRule type="dataBar" id="{34b913d2-4d09-44ef-9ac4-f54fcafdecb7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23465,7 +23465,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72eaacc1-5142-4b72-a4b4-a05607f54656}">
+          <x14:cfRule type="dataBar" id="{a3b1401f-9a89-4373-a055-936d0a224c9d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23478,7 +23478,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{600f48f5-a61b-4092-b93f-0df788672287}">
+          <x14:cfRule type="dataBar" id="{da948d02-b053-41a1-b468-7dbd2645871a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23491,7 +23491,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5760e5f2-4576-4a90-85b2-0cb7522ffe6d}">
+          <x14:cfRule type="dataBar" id="{3fe7fed2-b1cf-4012-8c20-ba6118ea55ba}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23504,7 +23504,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a953d099-1168-4610-a4e4-ac5859fdda8d}">
+          <x14:cfRule type="dataBar" id="{a498e1ff-c4ab-4f5c-b462-1b1258df0b2b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23517,7 +23517,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16850873-27a2-4354-834e-f84b64e6c5ba}">
+          <x14:cfRule type="dataBar" id="{fb436dce-c161-4296-83ce-2fb88b8b944b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23530,7 +23530,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a2d346e7-a893-4bad-85e7-ae1f37bf6946}">
+          <x14:cfRule type="dataBar" id="{29e276b4-e426-4cb1-b741-f5ad16f817f1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23543,7 +23543,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{49cdc146-8ffd-46c7-b4e6-dead92c8b85a}">
+          <x14:cfRule type="dataBar" id="{7483cd84-eb09-458c-b80b-4bf502db0fe9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23556,7 +23556,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0968bf44-462f-42db-8947-bca078138040}">
+          <x14:cfRule type="dataBar" id="{acfdff71-e3ad-48c5-b6da-dc28d4114659}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23569,7 +23569,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2caf380d-5e11-4f15-899a-2bbe52c6286b}">
+          <x14:cfRule type="dataBar" id="{647570c6-44b4-4f68-a894-4d52241e04dc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23582,7 +23582,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7dda6d6-f7a6-49ed-848f-66a0b753b51c}">
+          <x14:cfRule type="dataBar" id="{137ec496-f13c-46ee-8243-33d7cc20497b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23595,7 +23595,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99e15e6c-256f-4dde-9ef8-c1107fca42b7}">
+          <x14:cfRule type="dataBar" id="{477bbc9b-60f1-49c6-add4-eb44ecde81f6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23608,7 +23608,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{07985bdd-c019-4f6b-a8b7-be8a9bf93389}">
+          <x14:cfRule type="dataBar" id="{a3c5cca8-c0a9-4c7d-b729-ad3ed0105303}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23621,7 +23621,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0f080141-1793-4bc4-b4e8-d22d4d63199a}">
+          <x14:cfRule type="dataBar" id="{c4db7b94-317d-4d27-b7f7-27d224e8099f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23634,7 +23634,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1eb7ae17-0d28-44f2-92b3-c593981905fd}">
+          <x14:cfRule type="dataBar" id="{4a0a589f-5e6b-438d-9c25-a69a16353ad0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23647,7 +23647,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9853a094-2189-4ca1-afb0-a3446402765d}">
+          <x14:cfRule type="dataBar" id="{733aae13-c8a1-41be-baee-0e45846e41fb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23660,7 +23660,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{097a8368-708c-4cdc-87f7-812a2bd687b4}">
+          <x14:cfRule type="dataBar" id="{0f084c0c-61b1-412a-97ad-5b3eee9c37aa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23673,7 +23673,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fec691d3-9d13-44db-b9bb-6ad41ea9782b}">
+          <x14:cfRule type="dataBar" id="{5c0d6a4d-a67c-474e-84aa-c20c51621ac9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23686,7 +23686,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b43b6b5-2590-4a34-82f2-d14736c4bc3d}">
+          <x14:cfRule type="dataBar" id="{78fd8f19-b9e0-4f84-85f8-136e50cfb38b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23699,7 +23699,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{37f97cc0-b8fa-400f-81cf-75f95420e697}">
+          <x14:cfRule type="dataBar" id="{bd90acee-1578-41bc-ac97-5a562ba27e69}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23712,7 +23712,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98060026-2945-4d2d-a4cb-22de79f9dbb6}">
+          <x14:cfRule type="dataBar" id="{90ee968d-a976-45ba-b327-e67fdbb27f5c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34276,7 +34276,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a417cef-a5f8-44ab-b912-131318abc8ec}</x14:id>
+          <x14:id>{37b4cf6a-1808-4072-a0a7-ecbff381979c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34290,7 +34290,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72273551-06e5-48c3-a647-fc9c0fbbc5e6}</x14:id>
+          <x14:id>{be9fe18a-c2d8-488a-b536-b1c77c15f7d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34304,7 +34304,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bf74ee20-8d29-4758-8460-2ab9e1ea198c}</x14:id>
+          <x14:id>{e71aabf7-ef0c-4b6e-961c-40d63fbe8141}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34318,7 +34318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c447687-5b89-4776-aae5-7a27fcc64a3f}</x14:id>
+          <x14:id>{b39c01d6-657b-4257-9405-33eb62f32816}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34332,7 +34332,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f626a0e-e5b2-4840-bb93-cb58b5ed78ea}</x14:id>
+          <x14:id>{610462a8-73a7-479f-9ee1-7d28bc2071fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34346,7 +34346,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5354102d-07f5-4808-8c0d-52f86ed05942}</x14:id>
+          <x14:id>{add3203e-8fdc-4a24-9a4b-a2a87c69e149}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34366,7 +34366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{559de02a-d270-4535-a719-dc144cec0f14}</x14:id>
+          <x14:id>{028261ba-7800-477d-99d4-efc900c4723b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34380,7 +34380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2fb65f87-a4af-44bb-922e-40028a7a0630}</x14:id>
+          <x14:id>{37397be4-311b-469d-80cc-a5357eac4c7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34394,7 +34394,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9eac222-db16-4748-8e4b-3a9a2d7d52bc}</x14:id>
+          <x14:id>{1ae182f9-8190-4f87-a4ed-041ec8f81f7d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34408,7 +34408,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5af5b80f-691b-4772-a2cd-ffd2871350cc}</x14:id>
+          <x14:id>{2ba0824c-f52b-4dcc-8347-ae440ee6da19}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34422,7 +34422,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed569490-f9da-42b9-85ac-6be6d2dbbf98}</x14:id>
+          <x14:id>{13b6d504-c4ce-49a5-a654-7abb013a5d8c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34436,7 +34436,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e9569bf-2ad9-49d5-bdc6-c7730f24b6b8}</x14:id>
+          <x14:id>{f98fea20-7d7a-465e-b4ac-dfe08f5af8be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34458,7 +34458,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7a3e63b-9f36-4c09-bdc2-0497c5d1c4d3}</x14:id>
+          <x14:id>{794d11de-a650-4e12-b0eb-bb54e416e9df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34488,7 +34488,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eccc4d28-7e45-477f-bf39-ed9513fd8323}</x14:id>
+          <x14:id>{58910e22-0afa-4cb6-ba8a-4a132830ce08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34518,7 +34518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5750f244-590b-4634-951d-ca85a2b680a4}</x14:id>
+          <x14:id>{85f59fcc-63be-4732-a6a8-8a9c797f6151}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34548,7 +34548,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee311c7e-708c-4d33-b490-55da699ba190}</x14:id>
+          <x14:id>{7eb57a5c-7124-43a8-bddd-37f7a11e15c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34578,7 +34578,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a24c9846-a022-40ea-9a09-ee86ac327c02}</x14:id>
+          <x14:id>{09507472-92d1-48ec-a69b-7f7d44c53a6e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34608,7 +34608,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4c2a6cfa-2216-491f-873a-0bf287dde47d}</x14:id>
+          <x14:id>{3c3ea18b-549f-4967-a25c-af7b142030e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34630,7 +34630,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa8187d0-e368-4958-993d-6381e4235c18}</x14:id>
+          <x14:id>{b36236e6-81ac-4613-a6b0-449683f70c79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34652,7 +34652,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{abcdc875-9032-4353-b0b5-d5283770d0e1}</x14:id>
+          <x14:id>{8170bdcc-317b-4bb7-b230-83e6f842a24c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34674,7 +34674,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70ad9bdb-0b38-4c28-ba7a-cf417a58e9f4}</x14:id>
+          <x14:id>{a14663ef-6ca3-489a-8764-dd64bea45c40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34696,7 +34696,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e6a19257-ffc0-43be-a3f6-0cdcf374b31e}</x14:id>
+          <x14:id>{d52088cc-74b1-417b-b96a-e1482f5bf465}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34718,7 +34718,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c668fdb9-a5ba-47a1-ad05-9631c8b71356}</x14:id>
+          <x14:id>{c0faf253-cc75-4a5c-a754-7281e807c8e4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34740,7 +34740,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4983e3c-f55f-4033-8f4a-9c78e8496e66}</x14:id>
+          <x14:id>{d65e3b33-aeae-4ee7-91bb-f78580f39f29}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34762,7 +34762,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3251858b-c8d5-4f31-a572-9a5b130e92e9}</x14:id>
+          <x14:id>{52c066db-a5d6-4898-a5c6-ede2ea23211d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34784,7 +34784,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{08437213-ef4d-4df7-8cda-265b766e59c4}</x14:id>
+          <x14:id>{241d21de-c337-4d06-83ee-516268cb0f21}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34806,7 +34806,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c873760d-3460-4202-a44a-4fe5c62ffbcd}</x14:id>
+          <x14:id>{806fdb81-a199-4bc1-93c3-403474048fa2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34828,7 +34828,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9a451206-bb11-4648-961f-873797542b6c}</x14:id>
+          <x14:id>{dccdf48c-f693-46a3-a165-831c4a31e083}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34850,7 +34850,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b3cacf8-2bf7-4bdf-9513-cd1665c81a33}</x14:id>
+          <x14:id>{88a7a9a8-b902-4f12-b27d-7b37b02b2ee6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34872,7 +34872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67df189d-eb81-479e-8433-538497d1dad7}</x14:id>
+          <x14:id>{c2691c27-f02d-49f7-8b65-0f2921a68e4c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34894,7 +34894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78dc50b0-59e5-462c-bdbe-3a8f393488e0}</x14:id>
+          <x14:id>{fcd04a44-8c24-47b7-ab63-6980a58ca34d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34916,7 +34916,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a45cbf9f-b1f9-4139-af79-2672b29d3f96}</x14:id>
+          <x14:id>{cebd219a-8fcc-488c-9747-329f36f12195}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34935,7 +34935,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0a417cef-a5f8-44ab-b912-131318abc8ec}">
+          <x14:cfRule type="dataBar" id="{37b4cf6a-1808-4072-a0a7-ecbff381979c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34948,7 +34948,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72273551-06e5-48c3-a647-fc9c0fbbc5e6}">
+          <x14:cfRule type="dataBar" id="{be9fe18a-c2d8-488a-b536-b1c77c15f7d5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34961,7 +34961,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bf74ee20-8d29-4758-8460-2ab9e1ea198c}">
+          <x14:cfRule type="dataBar" id="{e71aabf7-ef0c-4b6e-961c-40d63fbe8141}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34974,7 +34974,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3c447687-5b89-4776-aae5-7a27fcc64a3f}">
+          <x14:cfRule type="dataBar" id="{b39c01d6-657b-4257-9405-33eb62f32816}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34987,7 +34987,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0f626a0e-e5b2-4840-bb93-cb58b5ed78ea}">
+          <x14:cfRule type="dataBar" id="{610462a8-73a7-479f-9ee1-7d28bc2071fc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35000,7 +35000,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5354102d-07f5-4808-8c0d-52f86ed05942}">
+          <x14:cfRule type="dataBar" id="{add3203e-8fdc-4a24-9a4b-a2a87c69e149}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35013,7 +35013,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{559de02a-d270-4535-a719-dc144cec0f14}">
+          <x14:cfRule type="dataBar" id="{028261ba-7800-477d-99d4-efc900c4723b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35026,7 +35026,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2fb65f87-a4af-44bb-922e-40028a7a0630}">
+          <x14:cfRule type="dataBar" id="{37397be4-311b-469d-80cc-a5357eac4c7a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35039,7 +35039,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a9eac222-db16-4748-8e4b-3a9a2d7d52bc}">
+          <x14:cfRule type="dataBar" id="{1ae182f9-8190-4f87-a4ed-041ec8f81f7d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35052,7 +35052,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5af5b80f-691b-4772-a2cd-ffd2871350cc}">
+          <x14:cfRule type="dataBar" id="{2ba0824c-f52b-4dcc-8347-ae440ee6da19}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35065,7 +35065,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ed569490-f9da-42b9-85ac-6be6d2dbbf98}">
+          <x14:cfRule type="dataBar" id="{13b6d504-c4ce-49a5-a654-7abb013a5d8c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35078,7 +35078,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e9569bf-2ad9-49d5-bdc6-c7730f24b6b8}">
+          <x14:cfRule type="dataBar" id="{f98fea20-7d7a-465e-b4ac-dfe08f5af8be}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35091,7 +35091,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b7a3e63b-9f36-4c09-bdc2-0497c5d1c4d3}">
+          <x14:cfRule type="dataBar" id="{794d11de-a650-4e12-b0eb-bb54e416e9df}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35104,7 +35104,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eccc4d28-7e45-477f-bf39-ed9513fd8323}">
+          <x14:cfRule type="dataBar" id="{58910e22-0afa-4cb6-ba8a-4a132830ce08}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35117,7 +35117,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5750f244-590b-4634-951d-ca85a2b680a4}">
+          <x14:cfRule type="dataBar" id="{85f59fcc-63be-4732-a6a8-8a9c797f6151}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35130,7 +35130,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee311c7e-708c-4d33-b490-55da699ba190}">
+          <x14:cfRule type="dataBar" id="{7eb57a5c-7124-43a8-bddd-37f7a11e15c2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35143,7 +35143,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a24c9846-a022-40ea-9a09-ee86ac327c02}">
+          <x14:cfRule type="dataBar" id="{09507472-92d1-48ec-a69b-7f7d44c53a6e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35156,7 +35156,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4c2a6cfa-2216-491f-873a-0bf287dde47d}">
+          <x14:cfRule type="dataBar" id="{3c3ea18b-549f-4967-a25c-af7b142030e6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35169,7 +35169,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa8187d0-e368-4958-993d-6381e4235c18}">
+          <x14:cfRule type="dataBar" id="{b36236e6-81ac-4613-a6b0-449683f70c79}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35182,7 +35182,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{abcdc875-9032-4353-b0b5-d5283770d0e1}">
+          <x14:cfRule type="dataBar" id="{8170bdcc-317b-4bb7-b230-83e6f842a24c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35195,7 +35195,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70ad9bdb-0b38-4c28-ba7a-cf417a58e9f4}">
+          <x14:cfRule type="dataBar" id="{a14663ef-6ca3-489a-8764-dd64bea45c40}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35208,7 +35208,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e6a19257-ffc0-43be-a3f6-0cdcf374b31e}">
+          <x14:cfRule type="dataBar" id="{d52088cc-74b1-417b-b96a-e1482f5bf465}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35221,7 +35221,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c668fdb9-a5ba-47a1-ad05-9631c8b71356}">
+          <x14:cfRule type="dataBar" id="{c0faf253-cc75-4a5c-a754-7281e807c8e4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35234,7 +35234,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d4983e3c-f55f-4033-8f4a-9c78e8496e66}">
+          <x14:cfRule type="dataBar" id="{d65e3b33-aeae-4ee7-91bb-f78580f39f29}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35247,7 +35247,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3251858b-c8d5-4f31-a572-9a5b130e92e9}">
+          <x14:cfRule type="dataBar" id="{52c066db-a5d6-4898-a5c6-ede2ea23211d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35260,7 +35260,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{08437213-ef4d-4df7-8cda-265b766e59c4}">
+          <x14:cfRule type="dataBar" id="{241d21de-c337-4d06-83ee-516268cb0f21}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35273,7 +35273,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c873760d-3460-4202-a44a-4fe5c62ffbcd}">
+          <x14:cfRule type="dataBar" id="{806fdb81-a199-4bc1-93c3-403474048fa2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35286,7 +35286,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9a451206-bb11-4648-961f-873797542b6c}">
+          <x14:cfRule type="dataBar" id="{dccdf48c-f693-46a3-a165-831c4a31e083}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35299,7 +35299,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0b3cacf8-2bf7-4bdf-9513-cd1665c81a33}">
+          <x14:cfRule type="dataBar" id="{88a7a9a8-b902-4f12-b27d-7b37b02b2ee6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35312,7 +35312,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67df189d-eb81-479e-8433-538497d1dad7}">
+          <x14:cfRule type="dataBar" id="{c2691c27-f02d-49f7-8b65-0f2921a68e4c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35325,7 +35325,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{78dc50b0-59e5-462c-bdbe-3a8f393488e0}">
+          <x14:cfRule type="dataBar" id="{fcd04a44-8c24-47b7-ab63-6980a58ca34d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35338,7 +35338,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a45cbf9f-b1f9-4139-af79-2672b29d3f96}">
+          <x14:cfRule type="dataBar" id="{cebd219a-8fcc-488c-9747-329f36f12195}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -40483,7 +40483,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18d372eb-e862-4bba-a136-3c667a84323e}</x14:id>
+          <x14:id>{ca5a9f72-d66d-49c0-a23e-6ca9f49a3bf9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40494,7 +40494,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18d372eb-e862-4bba-a136-3c667a84323e}">
+          <x14:cfRule type="dataBar" id="{ca5a9f72-d66d-49c0-a23e-6ca9f49a3bf9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -22613,7 +22613,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1054e69f-2f7a-4a23-afbd-3884b513e0ca}</x14:id>
+          <x14:id>{a016abcd-22d4-466d-8c95-677345e91d28}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22627,7 +22627,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{981c03dd-b5a3-41cd-91dd-5119ccc55c8b}</x14:id>
+          <x14:id>{6fe96348-2dfb-4928-9319-a7a9eed56793}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22641,7 +22641,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ce2367b-1d99-4641-9b75-829f18893eaa}</x14:id>
+          <x14:id>{6502992b-89dc-416c-bbb2-ede50ac97beb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22655,7 +22655,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d571f6a-7950-4e5b-bed7-2d2a5f756495}</x14:id>
+          <x14:id>{a2fde2db-8a92-4d62-bb49-10c10f0f0caf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22669,7 +22669,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{243de982-267f-4d7a-b0a3-c95ea3da5294}</x14:id>
+          <x14:id>{e4ccbbdb-773d-4855-b141-d8d5a1317f3f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22683,7 +22683,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e00ce940-ae50-4135-9fb3-42bd080a3abd}</x14:id>
+          <x14:id>{626854b4-4e4b-4834-aecb-3af61ce6a0ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22697,7 +22697,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{87dbb917-8afa-4cd8-8d01-9e47c90c8995}</x14:id>
+          <x14:id>{7e549c1a-e68b-4869-85ba-3d9890529bd2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22711,7 +22711,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{663f5af0-d7a5-49db-add2-8885af59a442}</x14:id>
+          <x14:id>{2543ade4-5e01-47e9-b848-c030380cb77f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22725,7 +22725,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d36a9388-56cb-48be-9428-a545eb9849fb}</x14:id>
+          <x14:id>{6b744297-fcbc-4411-b311-b775b9802b5f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22739,7 +22739,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50489279-4cd9-4363-ba4e-1d3ad47a71cd}</x14:id>
+          <x14:id>{343d1f63-ed2a-45d7-9051-aa7c1564c26f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22753,7 +22753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b9ea658-3e4f-4d39-818e-5e76a3d2d72e}</x14:id>
+          <x14:id>{af2f9fdf-7b5a-4972-a9ab-5b7d2d56451c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22767,7 +22767,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b3600b1-889a-4d63-af5d-12086c640a8f}</x14:id>
+          <x14:id>{517fc391-1d6b-4c01-aa2e-4b74e8504069}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22781,7 +22781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34b913d2-4d09-44ef-9ac4-f54fcafdecb7}</x14:id>
+          <x14:id>{c18c4523-ca3b-4339-942b-e3ba14fc0e3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22803,7 +22803,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3b1401f-9a89-4373-a055-936d0a224c9d}</x14:id>
+          <x14:id>{b13cc5a6-c7ed-4955-a6e0-a3b6be7982d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22833,7 +22833,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da948d02-b053-41a1-b468-7dbd2645871a}</x14:id>
+          <x14:id>{654b787c-0f28-45d1-906b-1bd22693177d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22863,7 +22863,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3fe7fed2-b1cf-4012-8c20-ba6118ea55ba}</x14:id>
+          <x14:id>{1701f32b-2a7a-4684-ad8a-c0ead8e16efc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22893,7 +22893,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a498e1ff-c4ab-4f5c-b462-1b1258df0b2b}</x14:id>
+          <x14:id>{a4bbfc25-3dee-4fad-a621-0194c12ce8b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22923,7 +22923,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb436dce-c161-4296-83ce-2fb88b8b944b}</x14:id>
+          <x14:id>{a694973c-93d5-41d0-bb80-55cbcca12318}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22953,7 +22953,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29e276b4-e426-4cb1-b741-f5ad16f817f1}</x14:id>
+          <x14:id>{18dd4a86-b6d1-40c9-b28b-4cd3723f1739}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22983,7 +22983,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7483cd84-eb09-458c-b80b-4bf502db0fe9}</x14:id>
+          <x14:id>{909b4df7-a3a6-4d7b-945a-95fd9d5ad9c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23013,7 +23013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{acfdff71-e3ad-48c5-b6da-dc28d4114659}</x14:id>
+          <x14:id>{0dc4fcbc-84b9-44ec-93d6-76ca51215997}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23035,7 +23035,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{647570c6-44b4-4f68-a894-4d52241e04dc}</x14:id>
+          <x14:id>{55bbc241-df66-4a25-852e-1ee954dcea21}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23057,7 +23057,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{137ec496-f13c-46ee-8243-33d7cc20497b}</x14:id>
+          <x14:id>{b83ec02a-a3b2-4ff3-9717-9cf1c077da9a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23079,7 +23079,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{477bbc9b-60f1-49c6-add4-eb44ecde81f6}</x14:id>
+          <x14:id>{c79266ae-d78e-4e8a-b5a4-2f3cd6648cc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23101,7 +23101,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3c5cca8-c0a9-4c7d-b729-ad3ed0105303}</x14:id>
+          <x14:id>{ebaa7727-d357-4647-815c-b32c7cbd3ff3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23123,7 +23123,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4db7b94-317d-4d27-b7f7-27d224e8099f}</x14:id>
+          <x14:id>{767194b9-c723-4ee1-a7c2-65e1c3befab8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23145,7 +23145,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a0a589f-5e6b-438d-9c25-a69a16353ad0}</x14:id>
+          <x14:id>{8b73abb9-83fd-4667-9cbb-e4a293f10223}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23167,7 +23167,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{733aae13-c8a1-41be-baee-0e45846e41fb}</x14:id>
+          <x14:id>{8a1c5415-fdae-40e2-865c-d97e7fed5b15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23189,7 +23189,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f084c0c-61b1-412a-97ad-5b3eee9c37aa}</x14:id>
+          <x14:id>{19a10da5-7bf5-42f8-967e-69d37686fb4e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23211,7 +23211,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5c0d6a4d-a67c-474e-84aa-c20c51621ac9}</x14:id>
+          <x14:id>{dd6d3ddd-be5a-4043-ae26-46f0740f9223}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23233,7 +23233,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78fd8f19-b9e0-4f84-85f8-136e50cfb38b}</x14:id>
+          <x14:id>{7fa22bd8-893d-4b87-9450-94715ccc637c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23255,7 +23255,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd90acee-1578-41bc-ac97-5a562ba27e69}</x14:id>
+          <x14:id>{f798e696-c6ee-4f39-b2b3-fbe48e047023}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23277,7 +23277,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90ee968d-a976-45ba-b327-e67fdbb27f5c}</x14:id>
+          <x14:id>{81ce6cfa-5cc6-475a-b050-4850cb980e67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23296,7 +23296,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1054e69f-2f7a-4a23-afbd-3884b513e0ca}">
+          <x14:cfRule type="dataBar" id="{a016abcd-22d4-466d-8c95-677345e91d28}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23309,7 +23309,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{981c03dd-b5a3-41cd-91dd-5119ccc55c8b}">
+          <x14:cfRule type="dataBar" id="{6fe96348-2dfb-4928-9319-a7a9eed56793}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23322,7 +23322,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ce2367b-1d99-4641-9b75-829f18893eaa}">
+          <x14:cfRule type="dataBar" id="{6502992b-89dc-416c-bbb2-ede50ac97beb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23335,7 +23335,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d571f6a-7950-4e5b-bed7-2d2a5f756495}">
+          <x14:cfRule type="dataBar" id="{a2fde2db-8a92-4d62-bb49-10c10f0f0caf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23348,7 +23348,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{243de982-267f-4d7a-b0a3-c95ea3da5294}">
+          <x14:cfRule type="dataBar" id="{e4ccbbdb-773d-4855-b141-d8d5a1317f3f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23361,7 +23361,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e00ce940-ae50-4135-9fb3-42bd080a3abd}">
+          <x14:cfRule type="dataBar" id="{626854b4-4e4b-4834-aecb-3af61ce6a0ce}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23374,7 +23374,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{87dbb917-8afa-4cd8-8d01-9e47c90c8995}">
+          <x14:cfRule type="dataBar" id="{7e549c1a-e68b-4869-85ba-3d9890529bd2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23387,7 +23387,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{663f5af0-d7a5-49db-add2-8885af59a442}">
+          <x14:cfRule type="dataBar" id="{2543ade4-5e01-47e9-b848-c030380cb77f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23400,7 +23400,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d36a9388-56cb-48be-9428-a545eb9849fb}">
+          <x14:cfRule type="dataBar" id="{6b744297-fcbc-4411-b311-b775b9802b5f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23413,7 +23413,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{50489279-4cd9-4363-ba4e-1d3ad47a71cd}">
+          <x14:cfRule type="dataBar" id="{343d1f63-ed2a-45d7-9051-aa7c1564c26f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23426,7 +23426,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4b9ea658-3e4f-4d39-818e-5e76a3d2d72e}">
+          <x14:cfRule type="dataBar" id="{af2f9fdf-7b5a-4972-a9ab-5b7d2d56451c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23439,7 +23439,7 @@
           <xm:sqref>C68:O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b3600b1-889a-4d63-af5d-12086c640a8f}">
+          <x14:cfRule type="dataBar" id="{517fc391-1d6b-4c01-aa2e-4b74e8504069}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23452,7 +23452,7 @@
           <xm:sqref>C76:O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{34b913d2-4d09-44ef-9ac4-f54fcafdecb7}">
+          <x14:cfRule type="dataBar" id="{c18c4523-ca3b-4339-942b-e3ba14fc0e3a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23465,7 +23465,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3b1401f-9a89-4373-a055-936d0a224c9d}">
+          <x14:cfRule type="dataBar" id="{b13cc5a6-c7ed-4955-a6e0-a3b6be7982d0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23478,7 +23478,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{da948d02-b053-41a1-b468-7dbd2645871a}">
+          <x14:cfRule type="dataBar" id="{654b787c-0f28-45d1-906b-1bd22693177d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23491,7 +23491,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3fe7fed2-b1cf-4012-8c20-ba6118ea55ba}">
+          <x14:cfRule type="dataBar" id="{1701f32b-2a7a-4684-ad8a-c0ead8e16efc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23504,7 +23504,7 @@
           <xm:sqref>C43:O43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a498e1ff-c4ab-4f5c-b462-1b1258df0b2b}">
+          <x14:cfRule type="dataBar" id="{a4bbfc25-3dee-4fad-a621-0194c12ce8b1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23517,7 +23517,7 @@
           <xm:sqref>C51:O51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fb436dce-c161-4296-83ce-2fb88b8b944b}">
+          <x14:cfRule type="dataBar" id="{a694973c-93d5-41d0-bb80-55cbcca12318}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23530,7 +23530,7 @@
           <xm:sqref>C59:O59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{29e276b4-e426-4cb1-b741-f5ad16f817f1}">
+          <x14:cfRule type="dataBar" id="{18dd4a86-b6d1-40c9-b28b-4cd3723f1739}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23543,7 +23543,7 @@
           <xm:sqref>C67:O67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7483cd84-eb09-458c-b80b-4bf502db0fe9}">
+          <x14:cfRule type="dataBar" id="{909b4df7-a3a6-4d7b-945a-95fd9d5ad9c0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23556,7 +23556,7 @@
           <xm:sqref>C75:O75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{acfdff71-e3ad-48c5-b6da-dc28d4114659}">
+          <x14:cfRule type="dataBar" id="{0dc4fcbc-84b9-44ec-93d6-76ca51215997}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23569,7 +23569,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{647570c6-44b4-4f68-a894-4d52241e04dc}">
+          <x14:cfRule type="dataBar" id="{55bbc241-df66-4a25-852e-1ee954dcea21}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23582,7 +23582,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{137ec496-f13c-46ee-8243-33d7cc20497b}">
+          <x14:cfRule type="dataBar" id="{b83ec02a-a3b2-4ff3-9717-9cf1c077da9a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23595,7 +23595,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{477bbc9b-60f1-49c6-add4-eb44ecde81f6}">
+          <x14:cfRule type="dataBar" id="{c79266ae-d78e-4e8a-b5a4-2f3cd6648cc9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23608,7 +23608,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3c5cca8-c0a9-4c7d-b729-ad3ed0105303}">
+          <x14:cfRule type="dataBar" id="{ebaa7727-d357-4647-815c-b32c7cbd3ff3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23621,7 +23621,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c4db7b94-317d-4d27-b7f7-27d224e8099f}">
+          <x14:cfRule type="dataBar" id="{767194b9-c723-4ee1-a7c2-65e1c3befab8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23634,7 +23634,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a0a589f-5e6b-438d-9c25-a69a16353ad0}">
+          <x14:cfRule type="dataBar" id="{8b73abb9-83fd-4667-9cbb-e4a293f10223}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23647,7 +23647,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{733aae13-c8a1-41be-baee-0e45846e41fb}">
+          <x14:cfRule type="dataBar" id="{8a1c5415-fdae-40e2-865c-d97e7fed5b15}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23660,7 +23660,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0f084c0c-61b1-412a-97ad-5b3eee9c37aa}">
+          <x14:cfRule type="dataBar" id="{19a10da5-7bf5-42f8-967e-69d37686fb4e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23673,7 +23673,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5c0d6a4d-a67c-474e-84aa-c20c51621ac9}">
+          <x14:cfRule type="dataBar" id="{dd6d3ddd-be5a-4043-ae26-46f0740f9223}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23686,7 +23686,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{78fd8f19-b9e0-4f84-85f8-136e50cfb38b}">
+          <x14:cfRule type="dataBar" id="{7fa22bd8-893d-4b87-9450-94715ccc637c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23699,7 +23699,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd90acee-1578-41bc-ac97-5a562ba27e69}">
+          <x14:cfRule type="dataBar" id="{f798e696-c6ee-4f39-b2b3-fbe48e047023}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23712,7 +23712,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90ee968d-a976-45ba-b327-e67fdbb27f5c}">
+          <x14:cfRule type="dataBar" id="{81ce6cfa-5cc6-475a-b050-4850cb980e67}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34276,7 +34276,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37b4cf6a-1808-4072-a0a7-ecbff381979c}</x14:id>
+          <x14:id>{65462c0c-7b84-4fbe-b98e-ff79d2c637fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34290,7 +34290,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be9fe18a-c2d8-488a-b536-b1c77c15f7d5}</x14:id>
+          <x14:id>{36bc6679-be8c-4692-be64-b765b9623819}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34304,7 +34304,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e71aabf7-ef0c-4b6e-961c-40d63fbe8141}</x14:id>
+          <x14:id>{c2ba36c0-8c43-4dd3-a86d-af3a09842750}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34318,7 +34318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b39c01d6-657b-4257-9405-33eb62f32816}</x14:id>
+          <x14:id>{7cff423f-95a6-4dda-8da4-62f83672ddc4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34332,7 +34332,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{610462a8-73a7-479f-9ee1-7d28bc2071fc}</x14:id>
+          <x14:id>{191764a0-8d30-41ec-8b5d-2acbcb8a79bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34346,7 +34346,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{add3203e-8fdc-4a24-9a4b-a2a87c69e149}</x14:id>
+          <x14:id>{4251c6c6-7098-4a1d-90b2-35b1dc5e887b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34366,7 +34366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{028261ba-7800-477d-99d4-efc900c4723b}</x14:id>
+          <x14:id>{a680dfff-54fe-4eda-8423-940449a60f07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34380,7 +34380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37397be4-311b-469d-80cc-a5357eac4c7a}</x14:id>
+          <x14:id>{cd793ddd-1034-4dba-a943-39fa46bacb6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34394,7 +34394,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ae182f9-8190-4f87-a4ed-041ec8f81f7d}</x14:id>
+          <x14:id>{b1e3eaeb-8c2f-4a8b-bbd1-d83cc56074c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34408,7 +34408,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ba0824c-f52b-4dcc-8347-ae440ee6da19}</x14:id>
+          <x14:id>{eab9e69c-2be1-44cb-9d34-1dc9dc7c7359}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34422,7 +34422,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13b6d504-c4ce-49a5-a654-7abb013a5d8c}</x14:id>
+          <x14:id>{66a37adb-046b-4a13-b51a-e67b1c2d3784}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34436,7 +34436,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f98fea20-7d7a-465e-b4ac-dfe08f5af8be}</x14:id>
+          <x14:id>{98de2829-249e-4add-ad49-1c6dbca1b224}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34458,7 +34458,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{794d11de-a650-4e12-b0eb-bb54e416e9df}</x14:id>
+          <x14:id>{a33eca60-86f4-4f42-80ae-858301d34a96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34488,7 +34488,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{58910e22-0afa-4cb6-ba8a-4a132830ce08}</x14:id>
+          <x14:id>{24e2c323-81e6-4931-91b2-277e1620a31c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34518,7 +34518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{85f59fcc-63be-4732-a6a8-8a9c797f6151}</x14:id>
+          <x14:id>{fb85fc6e-9983-481c-81d3-283503624b44}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34548,7 +34548,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7eb57a5c-7124-43a8-bddd-37f7a11e15c2}</x14:id>
+          <x14:id>{8880b95d-ba92-4496-b81e-ac2e9eb0cbc7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34578,7 +34578,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{09507472-92d1-48ec-a69b-7f7d44c53a6e}</x14:id>
+          <x14:id>{fc7c09cf-5626-491d-bc29-11310e59de92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34608,7 +34608,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c3ea18b-549f-4967-a25c-af7b142030e6}</x14:id>
+          <x14:id>{de349661-009a-4421-9e42-0f0908b06e01}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34630,7 +34630,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b36236e6-81ac-4613-a6b0-449683f70c79}</x14:id>
+          <x14:id>{0e9a0a42-1380-431c-842b-02bf42abf4cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34652,7 +34652,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8170bdcc-317b-4bb7-b230-83e6f842a24c}</x14:id>
+          <x14:id>{57b2f5c6-fe24-4f90-ad16-15bca24eb9c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34674,7 +34674,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a14663ef-6ca3-489a-8764-dd64bea45c40}</x14:id>
+          <x14:id>{81341fb8-65d3-440d-853d-829e2890b637}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34696,7 +34696,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d52088cc-74b1-417b-b96a-e1482f5bf465}</x14:id>
+          <x14:id>{edad3efa-394b-4cc7-b5ae-2b2d102fb2cb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34718,7 +34718,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0faf253-cc75-4a5c-a754-7281e807c8e4}</x14:id>
+          <x14:id>{0dfc7044-a09e-4b91-a2e5-cb5a50bd90f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34740,7 +34740,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d65e3b33-aeae-4ee7-91bb-f78580f39f29}</x14:id>
+          <x14:id>{88b5b45f-8848-4e70-a0fb-8ed67ef4fbc2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34762,7 +34762,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52c066db-a5d6-4898-a5c6-ede2ea23211d}</x14:id>
+          <x14:id>{e9b3a736-511d-4960-bba5-b5d3328736b2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34784,7 +34784,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{241d21de-c337-4d06-83ee-516268cb0f21}</x14:id>
+          <x14:id>{1711f887-3478-46db-a648-3a1c216995e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34806,7 +34806,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{806fdb81-a199-4bc1-93c3-403474048fa2}</x14:id>
+          <x14:id>{8d85ff60-e1c9-4c5a-af4d-946707eafb02}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34828,7 +34828,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dccdf48c-f693-46a3-a165-831c4a31e083}</x14:id>
+          <x14:id>{04058a32-8600-4a9c-88f6-a92c2f236ae6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34850,7 +34850,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88a7a9a8-b902-4f12-b27d-7b37b02b2ee6}</x14:id>
+          <x14:id>{bf27e5bb-8461-4e74-8b0e-52cc4e86506c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34872,7 +34872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c2691c27-f02d-49f7-8b65-0f2921a68e4c}</x14:id>
+          <x14:id>{d86bb071-e9e1-4ff2-aaf4-fba822caca0b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34894,7 +34894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fcd04a44-8c24-47b7-ab63-6980a58ca34d}</x14:id>
+          <x14:id>{9e8fb8b3-e4fc-4838-9443-95a680cca7ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34916,7 +34916,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cebd219a-8fcc-488c-9747-329f36f12195}</x14:id>
+          <x14:id>{65a22b99-8280-47cc-a2ca-1bb6aaef71d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34935,7 +34935,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{37b4cf6a-1808-4072-a0a7-ecbff381979c}">
+          <x14:cfRule type="dataBar" id="{65462c0c-7b84-4fbe-b98e-ff79d2c637fe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34948,7 +34948,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{be9fe18a-c2d8-488a-b536-b1c77c15f7d5}">
+          <x14:cfRule type="dataBar" id="{36bc6679-be8c-4692-be64-b765b9623819}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34961,7 +34961,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e71aabf7-ef0c-4b6e-961c-40d63fbe8141}">
+          <x14:cfRule type="dataBar" id="{c2ba36c0-8c43-4dd3-a86d-af3a09842750}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34974,7 +34974,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b39c01d6-657b-4257-9405-33eb62f32816}">
+          <x14:cfRule type="dataBar" id="{7cff423f-95a6-4dda-8da4-62f83672ddc4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34987,7 +34987,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{610462a8-73a7-479f-9ee1-7d28bc2071fc}">
+          <x14:cfRule type="dataBar" id="{191764a0-8d30-41ec-8b5d-2acbcb8a79bb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35000,7 +35000,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{add3203e-8fdc-4a24-9a4b-a2a87c69e149}">
+          <x14:cfRule type="dataBar" id="{4251c6c6-7098-4a1d-90b2-35b1dc5e887b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35013,7 +35013,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{028261ba-7800-477d-99d4-efc900c4723b}">
+          <x14:cfRule type="dataBar" id="{a680dfff-54fe-4eda-8423-940449a60f07}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35026,7 +35026,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{37397be4-311b-469d-80cc-a5357eac4c7a}">
+          <x14:cfRule type="dataBar" id="{cd793ddd-1034-4dba-a943-39fa46bacb6a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35039,7 +35039,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ae182f9-8190-4f87-a4ed-041ec8f81f7d}">
+          <x14:cfRule type="dataBar" id="{b1e3eaeb-8c2f-4a8b-bbd1-d83cc56074c0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35052,7 +35052,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2ba0824c-f52b-4dcc-8347-ae440ee6da19}">
+          <x14:cfRule type="dataBar" id="{eab9e69c-2be1-44cb-9d34-1dc9dc7c7359}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35065,7 +35065,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{13b6d504-c4ce-49a5-a654-7abb013a5d8c}">
+          <x14:cfRule type="dataBar" id="{66a37adb-046b-4a13-b51a-e67b1c2d3784}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35078,7 +35078,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f98fea20-7d7a-465e-b4ac-dfe08f5af8be}">
+          <x14:cfRule type="dataBar" id="{98de2829-249e-4add-ad49-1c6dbca1b224}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35091,7 +35091,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{794d11de-a650-4e12-b0eb-bb54e416e9df}">
+          <x14:cfRule type="dataBar" id="{a33eca60-86f4-4f42-80ae-858301d34a96}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35104,7 +35104,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{58910e22-0afa-4cb6-ba8a-4a132830ce08}">
+          <x14:cfRule type="dataBar" id="{24e2c323-81e6-4931-91b2-277e1620a31c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35117,7 +35117,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{85f59fcc-63be-4732-a6a8-8a9c797f6151}">
+          <x14:cfRule type="dataBar" id="{fb85fc6e-9983-481c-81d3-283503624b44}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35130,7 +35130,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7eb57a5c-7124-43a8-bddd-37f7a11e15c2}">
+          <x14:cfRule type="dataBar" id="{8880b95d-ba92-4496-b81e-ac2e9eb0cbc7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35143,7 +35143,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{09507472-92d1-48ec-a69b-7f7d44c53a6e}">
+          <x14:cfRule type="dataBar" id="{fc7c09cf-5626-491d-bc29-11310e59de92}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35156,7 +35156,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3c3ea18b-549f-4967-a25c-af7b142030e6}">
+          <x14:cfRule type="dataBar" id="{de349661-009a-4421-9e42-0f0908b06e01}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35169,7 +35169,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b36236e6-81ac-4613-a6b0-449683f70c79}">
+          <x14:cfRule type="dataBar" id="{0e9a0a42-1380-431c-842b-02bf42abf4cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35182,7 +35182,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8170bdcc-317b-4bb7-b230-83e6f842a24c}">
+          <x14:cfRule type="dataBar" id="{57b2f5c6-fe24-4f90-ad16-15bca24eb9c5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35195,7 +35195,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a14663ef-6ca3-489a-8764-dd64bea45c40}">
+          <x14:cfRule type="dataBar" id="{81341fb8-65d3-440d-853d-829e2890b637}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35208,7 +35208,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d52088cc-74b1-417b-b96a-e1482f5bf465}">
+          <x14:cfRule type="dataBar" id="{edad3efa-394b-4cc7-b5ae-2b2d102fb2cb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35221,7 +35221,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c0faf253-cc75-4a5c-a754-7281e807c8e4}">
+          <x14:cfRule type="dataBar" id="{0dfc7044-a09e-4b91-a2e5-cb5a50bd90f5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35234,7 +35234,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d65e3b33-aeae-4ee7-91bb-f78580f39f29}">
+          <x14:cfRule type="dataBar" id="{88b5b45f-8848-4e70-a0fb-8ed67ef4fbc2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35247,7 +35247,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52c066db-a5d6-4898-a5c6-ede2ea23211d}">
+          <x14:cfRule type="dataBar" id="{e9b3a736-511d-4960-bba5-b5d3328736b2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35260,7 +35260,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{241d21de-c337-4d06-83ee-516268cb0f21}">
+          <x14:cfRule type="dataBar" id="{1711f887-3478-46db-a648-3a1c216995e0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35273,7 +35273,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{806fdb81-a199-4bc1-93c3-403474048fa2}">
+          <x14:cfRule type="dataBar" id="{8d85ff60-e1c9-4c5a-af4d-946707eafb02}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35286,7 +35286,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dccdf48c-f693-46a3-a165-831c4a31e083}">
+          <x14:cfRule type="dataBar" id="{04058a32-8600-4a9c-88f6-a92c2f236ae6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35299,7 +35299,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{88a7a9a8-b902-4f12-b27d-7b37b02b2ee6}">
+          <x14:cfRule type="dataBar" id="{bf27e5bb-8461-4e74-8b0e-52cc4e86506c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35312,7 +35312,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c2691c27-f02d-49f7-8b65-0f2921a68e4c}">
+          <x14:cfRule type="dataBar" id="{d86bb071-e9e1-4ff2-aaf4-fba822caca0b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35325,7 +35325,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fcd04a44-8c24-47b7-ab63-6980a58ca34d}">
+          <x14:cfRule type="dataBar" id="{9e8fb8b3-e4fc-4838-9443-95a680cca7ad}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35338,7 +35338,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cebd219a-8fcc-488c-9747-329f36f12195}">
+          <x14:cfRule type="dataBar" id="{65a22b99-8280-47cc-a2ca-1bb6aaef71d3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -40483,7 +40483,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca5a9f72-d66d-49c0-a23e-6ca9f49a3bf9}</x14:id>
+          <x14:id>{99f1a2b3-c306-4cb7-8d49-ccf10fc43518}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -40494,7 +40494,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ca5a9f72-d66d-49c0-a23e-6ca9f49a3bf9}">
+          <x14:cfRule type="dataBar" id="{99f1a2b3-c306-4cb7-8d49-ccf10fc43518}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -6686,7 +6686,7 @@
             <v>593421.46</v>
           </cell>
           <cell r="H7">
-            <v>0</v>
+            <v>160770.45</v>
           </cell>
           <cell r="I7">
             <v>0</v>
@@ -6707,7 +6707,7 @@
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>3112219.33</v>
+            <v>3272989.78</v>
           </cell>
         </row>
         <row r="8">
@@ -6730,7 +6730,7 @@
             <v>1.09246608580648</v>
           </cell>
           <cell r="H8">
-            <v>0</v>
+            <v>0.264991651123259</v>
           </cell>
           <cell r="I8">
             <v>0</v>
@@ -6751,7 +6751,7 @@
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0.355468099487318</v>
+            <v>0.373830804764655</v>
           </cell>
         </row>
         <row r="10">
@@ -6818,7 +6818,7 @@
             <v>26753</v>
           </cell>
           <cell r="H11">
-            <v>0</v>
+            <v>7111</v>
           </cell>
           <cell r="I11">
             <v>0</v>
@@ -6839,7 +6839,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>155756</v>
+            <v>162867</v>
           </cell>
         </row>
         <row r="12">
@@ -6862,7 +6862,7 @@
             <v>0.743138888888889</v>
           </cell>
           <cell r="H12">
-            <v>0</v>
+            <v>0.176859750789663</v>
           </cell>
           <cell r="I12">
             <v>0</v>
@@ -6883,7 +6883,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.268141690424052</v>
+            <v>0.280383630128496</v>
           </cell>
         </row>
         <row r="14">
@@ -6950,7 +6950,7 @@
             <v>9282</v>
           </cell>
           <cell r="H15">
-            <v>0</v>
+            <v>2512</v>
           </cell>
           <cell r="I15">
             <v>0</v>
@@ -6971,7 +6971,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>55346</v>
+            <v>57858</v>
           </cell>
         </row>
         <row r="16">
@@ -6994,7 +6994,7 @@
             <v>0.831720430107527</v>
           </cell>
           <cell r="H16">
-            <v>0</v>
+            <v>0.201537687627816</v>
           </cell>
           <cell r="I16">
             <v>0</v>
@@ -7015,7 +7015,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.307357703368329</v>
+            <v>0.321307809082585</v>
           </cell>
         </row>
         <row r="18">
@@ -7082,7 +7082,7 @@
             <v>11545368.1632</v>
           </cell>
           <cell r="H19">
-            <v>0</v>
+            <v>2959137.918</v>
           </cell>
           <cell r="I19">
             <v>0</v>
@@ -7103,7 +7103,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>60918020.7102</v>
+            <v>63877158.6282</v>
           </cell>
         </row>
         <row r="20">
@@ -7126,7 +7126,7 @@
             <v>0.922448718696069</v>
           </cell>
           <cell r="H20">
-            <v>0</v>
+            <v>0.211680523237847</v>
           </cell>
           <cell r="I20">
             <v>0</v>
@@ -7147,7 +7147,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.302027161464247</v>
+            <v>0.316698354246535</v>
           </cell>
         </row>
         <row r="22">
@@ -7214,7 +7214,7 @@
             <v>3503371.5464</v>
           </cell>
           <cell r="H23">
-            <v>0</v>
+            <v>889801.365</v>
           </cell>
           <cell r="I23">
             <v>0</v>
@@ -7235,7 +7235,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>19945901.6564</v>
+            <v>20835703.0214</v>
           </cell>
         </row>
         <row r="24">
@@ -7258,7 +7258,7 @@
             <v>0.874723240851709</v>
           </cell>
           <cell r="H24">
-            <v>0</v>
+            <v>0.198910991710651</v>
           </cell>
           <cell r="I24">
             <v>0</v>
@@ -7279,7 +7279,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.309032326861965</v>
+            <v>0.32281848659582</v>
           </cell>
         </row>
         <row r="26">
@@ -7301,8 +7301,8 @@
           <cell r="G26">
             <v>0.30344390034843</v>
           </cell>
-          <cell r="H26" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H26">
+            <v>0.300696145180483</v>
           </cell>
           <cell r="I26" t="e">
             <v>#DIV/0!</v>
@@ -7323,7 +7323,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.327422024285505</v>
+            <v>0.32618393599307</v>
           </cell>
         </row>
         <row r="27">
@@ -7345,8 +7345,8 @@
           <cell r="G27">
             <v>0.653048256270325</v>
           </cell>
-          <cell r="H27" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H27">
+            <v>0.646744480382506</v>
           </cell>
           <cell r="I27" t="e">
             <v>#DIV/0!</v>
@@ -7367,7 +7367,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.644662163897378</v>
+            <v>0.644753080734587</v>
           </cell>
         </row>
         <row r="28">
@@ -7389,8 +7389,8 @@
           <cell r="G28">
             <v>0.16938581938584</v>
           </cell>
-          <cell r="H28" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H28">
+            <v>0.180681280478818</v>
           </cell>
           <cell r="I28" t="e">
             <v>#DIV/0!</v>
@@ -7411,7 +7411,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.156033022904301</v>
+            <v>0.157085641729409</v>
           </cell>
         </row>
         <row r="30">
@@ -7437,7 +7437,7 @@
             <v>213687.24</v>
           </cell>
           <cell r="H30">
-            <v>0</v>
+            <v>52764.41</v>
           </cell>
           <cell r="I30">
             <v>0</v>
@@ -7458,7 +7458,7 @@
             <v>0</v>
           </cell>
           <cell r="O30">
-            <v>1772160.66</v>
+            <v>1824925.07</v>
           </cell>
         </row>
         <row r="31">
@@ -7481,7 +7481,7 @@
             <v>10453</v>
           </cell>
           <cell r="H31">
-            <v>0</v>
+            <v>2716</v>
           </cell>
           <cell r="I31">
             <v>0</v>
@@ -7502,7 +7502,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>76304</v>
+            <v>79020</v>
           </cell>
         </row>
         <row r="32">
@@ -7525,7 +7525,7 @@
             <v>3602</v>
           </cell>
           <cell r="H32">
-            <v>0</v>
+            <v>915</v>
           </cell>
           <cell r="I32">
             <v>0</v>
@@ -7546,7 +7546,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>28154</v>
+            <v>29069</v>
           </cell>
         </row>
         <row r="33">
@@ -7569,7 +7569,7 @@
             <v>4439731.0488</v>
           </cell>
           <cell r="H33">
-            <v>0</v>
+            <v>1166305.44</v>
           </cell>
           <cell r="I33">
             <v>0</v>
@@ -7590,7 +7590,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>31315726.5669</v>
+            <v>32482032.0069</v>
           </cell>
         </row>
         <row r="34">
@@ -7613,7 +7613,7 @@
             <v>1407371.462</v>
           </cell>
           <cell r="H34">
-            <v>0</v>
+            <v>336024.4174</v>
           </cell>
           <cell r="I34">
             <v>0</v>
@@ -7634,7 +7634,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>10388659.092</v>
+            <v>10724683.5094</v>
           </cell>
         </row>
         <row r="35">
@@ -7656,8 +7656,8 @@
           <cell r="G35">
             <v>0.316994756333358</v>
           </cell>
-          <cell r="H35" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H35">
+            <v>0.288110134683072</v>
           </cell>
           <cell r="I35" t="e">
             <v>#DIV/0!</v>
@@ -7678,7 +7678,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.331739360088186</v>
+            <v>0.330172801600645</v>
           </cell>
         </row>
         <row r="36">
@@ -7700,8 +7700,8 @@
           <cell r="G36">
             <v>0.655409930163589</v>
           </cell>
-          <cell r="H36" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H36">
+            <v>0.663107511045655</v>
           </cell>
           <cell r="I36" t="e">
             <v>#DIV/0!</v>
@@ -7722,7 +7722,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.631028517508912</v>
+            <v>0.632131106049101</v>
           </cell>
         </row>
         <row r="37">
@@ -7744,8 +7744,8 @@
           <cell r="G37">
             <v>0.15183428524004</v>
           </cell>
-          <cell r="H37" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H37">
+            <v>0.157025523348173</v>
           </cell>
           <cell r="I37" t="e">
             <v>#DIV/0!</v>
@@ -7766,7 +7766,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.170586082795294</v>
+            <v>0.170161205074302</v>
           </cell>
         </row>
         <row r="38">
@@ -7792,7 +7792,7 @@
             <v>95805.82</v>
           </cell>
           <cell r="H38">
-            <v>0</v>
+            <v>30284.73</v>
           </cell>
           <cell r="I38">
             <v>0</v>
@@ -7813,7 +7813,7 @@
             <v>0</v>
           </cell>
           <cell r="O38">
-            <v>573371.68</v>
+            <v>603656.41</v>
           </cell>
         </row>
         <row r="39">
@@ -7836,7 +7836,7 @@
             <v>6417</v>
           </cell>
           <cell r="H39">
-            <v>0</v>
+            <v>1652</v>
           </cell>
           <cell r="I39">
             <v>0</v>
@@ -7857,7 +7857,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>34075</v>
+            <v>35727</v>
           </cell>
         </row>
         <row r="40">
@@ -7880,7 +7880,7 @@
             <v>1916</v>
           </cell>
           <cell r="H40">
-            <v>0</v>
+            <v>541</v>
           </cell>
           <cell r="I40">
             <v>0</v>
@@ -7901,7 +7901,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>11190</v>
+            <v>11731</v>
           </cell>
         </row>
         <row r="41">
@@ -7924,7 +7924,7 @@
             <v>2954093.3256</v>
           </cell>
           <cell r="H41">
-            <v>0</v>
+            <v>669524.052</v>
           </cell>
           <cell r="I41">
             <v>0</v>
@@ -7945,7 +7945,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>12694302.5466</v>
+            <v>13363826.5986</v>
           </cell>
         </row>
         <row r="42">
@@ -7968,7 +7968,7 @@
             <v>702420.3795</v>
           </cell>
           <cell r="H42">
-            <v>0</v>
+            <v>188985.7344</v>
           </cell>
           <cell r="I42">
             <v>0</v>
@@ -7989,7 +7989,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>3725585.3595</v>
+            <v>3914571.0939</v>
           </cell>
         </row>
         <row r="43">
@@ -8011,8 +8011,8 @@
           <cell r="G43">
             <v>0.237778669147947</v>
           </cell>
-          <cell r="H43" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H43">
+            <v>0.282268775610768</v>
           </cell>
           <cell r="I43" t="e">
             <v>#DIV/0!</v>
@@ -8033,7 +8033,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.293484840606532</v>
+            <v>0.292922918822524</v>
           </cell>
         </row>
         <row r="44">
@@ -8055,8 +8055,8 @@
           <cell r="G44">
             <v>0.701418108150226</v>
           </cell>
-          <cell r="H44" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H44">
+            <v>0.672518159806295</v>
           </cell>
           <cell r="I44" t="e">
             <v>#DIV/0!</v>
@@ -8077,7 +8077,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.671606749816581</v>
+            <v>0.671648892994094</v>
           </cell>
         </row>
         <row r="45">
@@ -8099,8 +8099,8 @@
           <cell r="G45">
             <v>0.136393850173022</v>
           </cell>
-          <cell r="H45" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H45">
+            <v>0.160248762141488</v>
           </cell>
           <cell r="I45" t="e">
             <v>#DIV/0!</v>
@@ -8121,7 +8121,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.153901098665728</v>
+            <v>0.154207548035254</v>
           </cell>
         </row>
         <row r="46">
@@ -8147,7 +8147,7 @@
             <v>267227.4</v>
           </cell>
           <cell r="H46">
-            <v>0</v>
+            <v>70950.96</v>
           </cell>
           <cell r="I46">
             <v>0</v>
@@ -8168,7 +8168,7 @@
             <v>0</v>
           </cell>
           <cell r="O46">
-            <v>633113.12</v>
+            <v>704064.08</v>
           </cell>
         </row>
         <row r="47">
@@ -8191,7 +8191,7 @@
             <v>8516</v>
           </cell>
           <cell r="H47">
-            <v>0</v>
+            <v>2443</v>
           </cell>
           <cell r="I47">
             <v>0</v>
@@ -8212,7 +8212,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>28801</v>
+            <v>31244</v>
           </cell>
         </row>
         <row r="48">
@@ -8235,7 +8235,7 @@
             <v>3226</v>
           </cell>
           <cell r="H48">
-            <v>0</v>
+            <v>936</v>
           </cell>
           <cell r="I48">
             <v>0</v>
@@ -8256,7 +8256,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>9976</v>
+            <v>10912</v>
           </cell>
         </row>
         <row r="49">
@@ -8279,7 +8279,7 @@
             <v>3625780.1448</v>
           </cell>
           <cell r="H49">
-            <v>0</v>
+            <v>1008220.752</v>
           </cell>
           <cell r="I49">
             <v>0</v>
@@ -8300,7 +8300,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>11102484.4854</v>
+            <v>12110705.2374</v>
           </cell>
         </row>
         <row r="50">
@@ -8323,7 +8323,7 @@
             <v>1213786.7552</v>
           </cell>
           <cell r="H50">
-            <v>0</v>
+            <v>328535.4711</v>
           </cell>
           <cell r="I50">
             <v>0</v>
@@ -8344,7 +8344,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>3526431.1052</v>
+            <v>3854966.5763</v>
           </cell>
         </row>
         <row r="51">
@@ -8366,8 +8366,8 @@
           <cell r="G51">
             <v>0.334765679860865</v>
           </cell>
-          <cell r="H51" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H51">
+            <v>0.32585668411237</v>
           </cell>
           <cell r="I51" t="e">
             <v>#DIV/0!</v>
@@ -8388,7 +8388,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.317625402659858</v>
+            <v>0.318310659927151</v>
           </cell>
         </row>
         <row r="52">
@@ -8410,8 +8410,8 @@
           <cell r="G52">
             <v>0.621183654297792</v>
           </cell>
-          <cell r="H52" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H52">
+            <v>0.616864510847319</v>
           </cell>
           <cell r="I52" t="e">
             <v>#DIV/0!</v>
@@ -8432,7 +8432,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.653623138085483</v>
+            <v>0.650748943797209</v>
           </cell>
         </row>
         <row r="53">
@@ -8454,8 +8454,8 @@
           <cell r="G53">
             <v>0.22016008895728</v>
           </cell>
-          <cell r="H53" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H53">
+            <v>0.21596133824589</v>
           </cell>
           <cell r="I53" t="e">
             <v>#DIV/0!</v>
@@ -8476,7 +8476,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.179533670476768</v>
+            <v>0.182638180141048</v>
           </cell>
         </row>
         <row r="54">
@@ -8502,7 +8502,7 @@
             <v>16701</v>
           </cell>
           <cell r="H54">
-            <v>0</v>
+            <v>6770.35</v>
           </cell>
           <cell r="I54">
             <v>0</v>
@@ -8523,7 +8523,7 @@
             <v>0</v>
           </cell>
           <cell r="O54">
-            <v>133573.87</v>
+            <v>140344.22</v>
           </cell>
         </row>
         <row r="55">
@@ -8546,7 +8546,7 @@
             <v>1367</v>
           </cell>
           <cell r="H55">
-            <v>0</v>
+            <v>300</v>
           </cell>
           <cell r="I55">
             <v>0</v>
@@ -8567,7 +8567,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>16576</v>
+            <v>16876</v>
           </cell>
         </row>
         <row r="56">
@@ -8590,7 +8590,7 @@
             <v>538</v>
           </cell>
           <cell r="H56">
-            <v>0</v>
+            <v>120</v>
           </cell>
           <cell r="I56">
             <v>0</v>
@@ -8611,7 +8611,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>6026</v>
+            <v>6146</v>
           </cell>
         </row>
         <row r="57">
@@ -8634,7 +8634,7 @@
             <v>525763.644</v>
           </cell>
           <cell r="H57">
-            <v>0</v>
+            <v>115087.674</v>
           </cell>
           <cell r="I57">
             <v>0</v>
@@ -8655,7 +8655,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>5805507.1113</v>
+            <v>5920594.7853</v>
           </cell>
         </row>
         <row r="58">
@@ -8678,7 +8678,7 @@
             <v>179792.9497</v>
           </cell>
           <cell r="H58">
-            <v>0</v>
+            <v>36255.7421</v>
           </cell>
           <cell r="I58">
             <v>0</v>
@@ -8699,7 +8699,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2305226.0997</v>
+            <v>2341481.8418</v>
           </cell>
         </row>
         <row r="59">
@@ -8721,8 +8721,8 @@
           <cell r="G59">
             <v>0.341965352210622</v>
           </cell>
-          <cell r="H59" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H59">
+            <v>0.315027151387211</v>
           </cell>
           <cell r="I59" t="e">
             <v>#DIV/0!</v>
@@ -8743,7 +8743,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.397075751610578</v>
+            <v>0.395480847230682</v>
           </cell>
         </row>
         <row r="60">
@@ -8765,8 +8765,8 @@
           <cell r="G60">
             <v>0.606437454279444</v>
           </cell>
-          <cell r="H60" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H60">
+            <v>0.6</v>
           </cell>
           <cell r="I60" t="e">
             <v>#DIV/0!</v>
@@ -8787,7 +8787,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.636462355212355</v>
+            <v>0.635814173974875</v>
           </cell>
         </row>
         <row r="61">
@@ -8809,8 +8809,8 @@
           <cell r="G61">
             <v>0.0928901830014306</v>
           </cell>
-          <cell r="H61" t="e">
-            <v>#DIV/0!</v>
+          <cell r="H61">
+            <v>0.186738695937491</v>
           </cell>
           <cell r="I61" t="e">
             <v>#DIV/0!</v>
@@ -8831,7 +8831,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.0579439344441672</v>
+            <v>0.0599382055818597</v>
           </cell>
         </row>
         <row r="62">
@@ -21476,7 +21476,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6507e81b-ebaf-48ea-8ea3-c5f5968b3f4c}</x14:id>
+          <x14:id>{2bbb6288-b622-4729-a9b0-4e8537fffa93}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21490,7 +21490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f798dfee-6018-4c75-a0ae-abfc55230945}</x14:id>
+          <x14:id>{32ac0082-7ab1-439e-9320-bfe14f60fe67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21504,7 +21504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39d364d8-a680-4c84-9cf0-816c70dee50b}</x14:id>
+          <x14:id>{ff8e7c05-7427-4535-a288-8f14c186617e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21518,7 +21518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e942ca31-f618-4df9-b62b-41d9f76ba0ea}</x14:id>
+          <x14:id>{23277241-295f-4337-a375-5c635cd11268}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21532,7 +21532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{893548bd-1f6d-4138-bfab-be037b4b0e2e}</x14:id>
+          <x14:id>{cb3cd9f7-57af-4953-b941-c4c4f34992df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21546,7 +21546,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d48ed04-469d-447a-8839-ac82e3be9ec3}</x14:id>
+          <x14:id>{e32a5be5-972d-41b1-86d6-a4376ec6d945}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21560,7 +21560,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c31914d6-8be7-4988-908e-ce3d6a74f84a}</x14:id>
+          <x14:id>{f5e6d67b-8d33-4825-a84e-c7f3825f21d9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21574,7 +21574,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b19c250-6a95-4496-971d-0e3000446316}</x14:id>
+          <x14:id>{b8a15dcb-f036-4c29-9c7b-494344690f35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21594,7 +21594,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5970b6e3-d1d0-4f21-bc36-ca6aa35f1031}</x14:id>
+          <x14:id>{9c737da8-5ca9-4ceb-8e84-7cd2901706cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21622,7 +21622,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0aa73ce-50fe-442d-bbbd-91a6d2ec3161}</x14:id>
+          <x14:id>{05cfeb75-05b4-40c5-acce-902073474035}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21642,7 +21642,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41935e21-6494-4261-9eaf-606b47bca071}</x14:id>
+          <x14:id>{f76fa017-90c2-4f5e-82d8-0e0117c27bad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21670,7 +21670,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1730d0c5-a67c-4632-805b-f58a9f087067}</x14:id>
+          <x14:id>{4c6f96f7-fb51-4738-b5cb-7b97e77948ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21690,7 +21690,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3799b5ef-5aa8-423f-be92-27aa032fc882}</x14:id>
+          <x14:id>{4888e397-6b45-45a3-bc98-317ba9a3a38d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21718,7 +21718,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e029c47-0c57-4839-9d6a-52c43c86016a}</x14:id>
+          <x14:id>{7ace09eb-8af7-4c9d-a720-d82b54f3edfb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21738,7 +21738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e6ba3483-91a8-4b5f-9658-b352f302cfd8}</x14:id>
+          <x14:id>{7126ecf7-2394-4436-81dc-0f3e4c40213b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21766,7 +21766,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5fec46e1-8327-4171-9a27-a219c17ef2ed}</x14:id>
+          <x14:id>{2743dc60-3ad1-48c8-8bf0-99ddac101d67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21786,7 +21786,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3df1860-aa7f-447f-bba4-b64a6dc7023f}</x14:id>
+          <x14:id>{420f31f9-9079-4608-ab8c-932e15390b8c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21814,7 +21814,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{28464709-a7a2-44a5-abc2-43cd83c35b1c}</x14:id>
+          <x14:id>{a6098526-2c33-49f9-acde-eadabd58665e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21876,7 +21876,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{acfe27b4-7731-4f8d-b8bc-208c70e6b37c}</x14:id>
+          <x14:id>{f8c55493-3091-4dd5-9a69-7e6894a86bcc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21906,7 +21906,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e349c365-9974-47bb-a696-6e5df3674334}</x14:id>
+          <x14:id>{09726e7a-e3fb-4008-8ab9-39c4d8e80d8f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21928,7 +21928,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2173b152-e7e1-41e2-a85b-6c35ddc3783b}</x14:id>
+          <x14:id>{b822ba8e-3278-4f5c-98e5-5b73b95e170e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21948,7 +21948,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f5c95b1-459e-422a-983b-3fef48ae7392}</x14:id>
+          <x14:id>{41546333-64b7-4652-b46b-69f21d162876}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21970,7 +21970,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ca3e508-f9c0-4474-b15c-3a22e1c45ea4}</x14:id>
+          <x14:id>{a78f785e-c053-477d-9435-ad2d849b4a42}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21990,7 +21990,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c4f1ce0-52f6-49af-98a3-0b9ffa0b3bef}</x14:id>
+          <x14:id>{3b89f26d-6426-4c67-9925-d48f768dc042}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22012,7 +22012,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89d48b05-1f79-4537-be32-0f35c17d58d2}</x14:id>
+          <x14:id>{3943dc95-7053-4432-8255-4d1e4fc99d85}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22032,7 +22032,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55cdcb6a-0b01-4853-a01d-8763247bc8ee}</x14:id>
+          <x14:id>{601155aa-1ba4-4680-915a-82703ab62e5c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22054,7 +22054,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{132f7ed8-03db-4ac2-a674-76cfca3ca0b0}</x14:id>
+          <x14:id>{312c435a-47be-4ab2-9e02-8f0951738a7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22074,7 +22074,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94f34998-f28a-44c3-9f94-4d26f9b77747}</x14:id>
+          <x14:id>{e3662691-7345-4bac-9a95-a3c0c4dcea6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22102,7 +22102,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e4ef1586-1b1f-436f-9b0d-eb15b6e30d24}</x14:id>
+          <x14:id>{d360104b-b079-4168-9aba-4e41baff3ac0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22116,7 +22116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7c311ccd-6812-4be5-b0a4-272027661a96}</x14:id>
+          <x14:id>{5a35cc04-d002-4819-8152-292963e6a34a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22146,7 +22146,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{072fdab6-6f8a-4adc-a0d1-e620e9af78e9}</x14:id>
+          <x14:id>{e09bc121-fa96-49ae-92fc-895928c3946e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22168,7 +22168,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{05e23054-faa2-4566-b409-7df378ae49ac}</x14:id>
+          <x14:id>{beb0cab7-f5ec-4788-b955-1a2c13eaf8e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22190,7 +22190,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5298c173-3385-4c8e-8bc7-ca47f00350f6}</x14:id>
+          <x14:id>{e39cb675-4017-42a3-95ad-0e06bf0b22da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22212,7 +22212,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0aacd13-e7fd-49de-b0d6-06968b7848dd}</x14:id>
+          <x14:id>{5422710f-d720-481e-b83c-bf2eae60f4c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22234,7 +22234,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba7b46ff-4c33-4b35-aa48-8d610fe07a8b}</x14:id>
+          <x14:id>{db54a3c6-6508-4ba7-9d89-ef60e47b1f69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22256,7 +22256,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{737caa55-9eef-4e8b-adf6-5b37f1e9ee47}</x14:id>
+          <x14:id>{4a4f627f-4233-40b7-a628-e1973662cbc6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22278,7 +22278,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db56d524-5a43-414c-870c-41ea39125271}</x14:id>
+          <x14:id>{3d4a43e2-01c7-4d3b-a6bc-8a4514ff7e54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22300,7 +22300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{422ab9d9-fd3c-435d-a9a4-0d8c2887fb1c}</x14:id>
+          <x14:id>{72f7c1b6-0c29-497e-8d17-420e705f3eff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22322,7 +22322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e4c3532b-0285-436f-9d2f-18ae8d66d375}</x14:id>
+          <x14:id>{886f586a-0759-4613-aef3-5a92933433a2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22344,7 +22344,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5073bb6f-0ef8-4035-9d25-40fec46d3761}</x14:id>
+          <x14:id>{c3b85e4d-8a81-4414-b7ff-256bb2612a6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22366,7 +22366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8434886d-d5c0-44d9-8f51-e8668e85bd1c}</x14:id>
+          <x14:id>{e5da2aae-0552-4f83-a74a-3f1cc3dfaf91}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22388,7 +22388,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{707240a2-e07e-4487-9a5a-18a411cd17a9}</x14:id>
+          <x14:id>{c945b804-c0ee-41dc-879b-69e29fb04c52}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22410,7 +22410,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d3b04485-164b-46f6-8f59-9755a2b98cd5}</x14:id>
+          <x14:id>{22132809-561d-4bfe-b2f0-0db5213168ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22429,7 +22429,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6507e81b-ebaf-48ea-8ea3-c5f5968b3f4c}">
+          <x14:cfRule type="dataBar" id="{2bbb6288-b622-4729-a9b0-4e8537fffa93}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22442,7 +22442,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f798dfee-6018-4c75-a0ae-abfc55230945}">
+          <x14:cfRule type="dataBar" id="{32ac0082-7ab1-439e-9320-bfe14f60fe67}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22455,7 +22455,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{39d364d8-a680-4c84-9cf0-816c70dee50b}">
+          <x14:cfRule type="dataBar" id="{ff8e7c05-7427-4535-a288-8f14c186617e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22468,7 +22468,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e942ca31-f618-4df9-b62b-41d9f76ba0ea}">
+          <x14:cfRule type="dataBar" id="{23277241-295f-4337-a375-5c635cd11268}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22481,7 +22481,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{893548bd-1f6d-4138-bfab-be037b4b0e2e}">
+          <x14:cfRule type="dataBar" id="{cb3cd9f7-57af-4953-b941-c4c4f34992df}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22494,7 +22494,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3d48ed04-469d-447a-8839-ac82e3be9ec3}">
+          <x14:cfRule type="dataBar" id="{e32a5be5-972d-41b1-86d6-a4376ec6d945}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22507,7 +22507,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c31914d6-8be7-4988-908e-ce3d6a74f84a}">
+          <x14:cfRule type="dataBar" id="{f5e6d67b-8d33-4825-a84e-c7f3825f21d9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22520,7 +22520,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4b19c250-6a95-4496-971d-0e3000446316}">
+          <x14:cfRule type="dataBar" id="{b8a15dcb-f036-4c29-9c7b-494344690f35}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22533,7 +22533,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5970b6e3-d1d0-4f21-bc36-ca6aa35f1031}">
+          <x14:cfRule type="dataBar" id="{9c737da8-5ca9-4ceb-8e84-7cd2901706cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22546,7 +22546,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a0aa73ce-50fe-442d-bbbd-91a6d2ec3161}">
+          <x14:cfRule type="dataBar" id="{05cfeb75-05b4-40c5-acce-902073474035}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22559,7 +22559,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41935e21-6494-4261-9eaf-606b47bca071}">
+          <x14:cfRule type="dataBar" id="{f76fa017-90c2-4f5e-82d8-0e0117c27bad}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22572,7 +22572,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1730d0c5-a67c-4632-805b-f58a9f087067}">
+          <x14:cfRule type="dataBar" id="{4c6f96f7-fb51-4738-b5cb-7b97e77948ac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22585,7 +22585,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3799b5ef-5aa8-423f-be92-27aa032fc882}">
+          <x14:cfRule type="dataBar" id="{4888e397-6b45-45a3-bc98-317ba9a3a38d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22598,7 +22598,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2e029c47-0c57-4839-9d6a-52c43c86016a}">
+          <x14:cfRule type="dataBar" id="{7ace09eb-8af7-4c9d-a720-d82b54f3edfb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22611,7 +22611,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e6ba3483-91a8-4b5f-9658-b352f302cfd8}">
+          <x14:cfRule type="dataBar" id="{7126ecf7-2394-4436-81dc-0f3e4c40213b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22624,7 +22624,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5fec46e1-8327-4171-9a27-a219c17ef2ed}">
+          <x14:cfRule type="dataBar" id="{2743dc60-3ad1-48c8-8bf0-99ddac101d67}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22637,7 +22637,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3df1860-aa7f-447f-bba4-b64a6dc7023f}">
+          <x14:cfRule type="dataBar" id="{420f31f9-9079-4608-ab8c-932e15390b8c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22650,7 +22650,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{28464709-a7a2-44a5-abc2-43cd83c35b1c}">
+          <x14:cfRule type="dataBar" id="{a6098526-2c33-49f9-acde-eadabd58665e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22663,7 +22663,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{acfe27b4-7731-4f8d-b8bc-208c70e6b37c}">
+          <x14:cfRule type="dataBar" id="{f8c55493-3091-4dd5-9a69-7e6894a86bcc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22676,7 +22676,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e349c365-9974-47bb-a696-6e5df3674334}">
+          <x14:cfRule type="dataBar" id="{09726e7a-e3fb-4008-8ab9-39c4d8e80d8f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22689,7 +22689,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2173b152-e7e1-41e2-a85b-6c35ddc3783b}">
+          <x14:cfRule type="dataBar" id="{b822ba8e-3278-4f5c-98e5-5b73b95e170e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22702,7 +22702,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4f5c95b1-459e-422a-983b-3fef48ae7392}">
+          <x14:cfRule type="dataBar" id="{41546333-64b7-4652-b46b-69f21d162876}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22715,7 +22715,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ca3e508-f9c0-4474-b15c-3a22e1c45ea4}">
+          <x14:cfRule type="dataBar" id="{a78f785e-c053-477d-9435-ad2d849b4a42}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22728,7 +22728,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0c4f1ce0-52f6-49af-98a3-0b9ffa0b3bef}">
+          <x14:cfRule type="dataBar" id="{3b89f26d-6426-4c67-9925-d48f768dc042}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22741,7 +22741,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{89d48b05-1f79-4537-be32-0f35c17d58d2}">
+          <x14:cfRule type="dataBar" id="{3943dc95-7053-4432-8255-4d1e4fc99d85}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22754,7 +22754,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55cdcb6a-0b01-4853-a01d-8763247bc8ee}">
+          <x14:cfRule type="dataBar" id="{601155aa-1ba4-4680-915a-82703ab62e5c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22767,7 +22767,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{132f7ed8-03db-4ac2-a674-76cfca3ca0b0}">
+          <x14:cfRule type="dataBar" id="{312c435a-47be-4ab2-9e02-8f0951738a7a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22780,7 +22780,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94f34998-f28a-44c3-9f94-4d26f9b77747}">
+          <x14:cfRule type="dataBar" id="{e3662691-7345-4bac-9a95-a3c0c4dcea6d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22793,7 +22793,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e4ef1586-1b1f-436f-9b0d-eb15b6e30d24}">
+          <x14:cfRule type="dataBar" id="{d360104b-b079-4168-9aba-4e41baff3ac0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22806,7 +22806,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7c311ccd-6812-4be5-b0a4-272027661a96}">
+          <x14:cfRule type="dataBar" id="{5a35cc04-d002-4819-8152-292963e6a34a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22819,7 +22819,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{072fdab6-6f8a-4adc-a0d1-e620e9af78e9}">
+          <x14:cfRule type="dataBar" id="{e09bc121-fa96-49ae-92fc-895928c3946e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22832,7 +22832,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{05e23054-faa2-4566-b409-7df378ae49ac}">
+          <x14:cfRule type="dataBar" id="{beb0cab7-f5ec-4788-b955-1a2c13eaf8e9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22845,7 +22845,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5298c173-3385-4c8e-8bc7-ca47f00350f6}">
+          <x14:cfRule type="dataBar" id="{e39cb675-4017-42a3-95ad-0e06bf0b22da}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22858,7 +22858,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a0aacd13-e7fd-49de-b0d6-06968b7848dd}">
+          <x14:cfRule type="dataBar" id="{5422710f-d720-481e-b83c-bf2eae60f4c2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22871,7 +22871,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba7b46ff-4c33-4b35-aa48-8d610fe07a8b}">
+          <x14:cfRule type="dataBar" id="{db54a3c6-6508-4ba7-9d89-ef60e47b1f69}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22884,7 +22884,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{737caa55-9eef-4e8b-adf6-5b37f1e9ee47}">
+          <x14:cfRule type="dataBar" id="{4a4f627f-4233-40b7-a628-e1973662cbc6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22897,7 +22897,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{db56d524-5a43-414c-870c-41ea39125271}">
+          <x14:cfRule type="dataBar" id="{3d4a43e2-01c7-4d3b-a6bc-8a4514ff7e54}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22910,7 +22910,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{422ab9d9-fd3c-435d-a9a4-0d8c2887fb1c}">
+          <x14:cfRule type="dataBar" id="{72f7c1b6-0c29-497e-8d17-420e705f3eff}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22923,7 +22923,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e4c3532b-0285-436f-9d2f-18ae8d66d375}">
+          <x14:cfRule type="dataBar" id="{886f586a-0759-4613-aef3-5a92933433a2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22936,7 +22936,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5073bb6f-0ef8-4035-9d25-40fec46d3761}">
+          <x14:cfRule type="dataBar" id="{c3b85e4d-8a81-4414-b7ff-256bb2612a6c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22949,7 +22949,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8434886d-d5c0-44d9-8f51-e8668e85bd1c}">
+          <x14:cfRule type="dataBar" id="{e5da2aae-0552-4f83-a74a-3f1cc3dfaf91}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22962,7 +22962,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{707240a2-e07e-4487-9a5a-18a411cd17a9}">
+          <x14:cfRule type="dataBar" id="{c945b804-c0ee-41dc-879b-69e29fb04c52}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22975,7 +22975,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d3b04485-164b-46f6-8f59-9755a2b98cd5}">
+          <x14:cfRule type="dataBar" id="{22132809-561d-4bfe-b2f0-0db5213168ac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23210,7 +23210,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>1300160.86</v>
+        <v>1460931.31</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -23248,7 +23248,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="7">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.805598274329399</v>
+        <v>0.905213945795745</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H7" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H7</f>
-        <v>0</v>
+        <v>160770.45</v>
       </c>
       <c r="I7" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I7</f>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="O7" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O7</f>
-        <v>3112219.33</v>
+        <v>3272989.78</v>
       </c>
     </row>
     <row r="8" s="34" customFormat="1" spans="1:15">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="H8" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H8</f>
-        <v>0</v>
+        <v>0.264991651123259</v>
       </c>
       <c r="I8" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I8</f>
@@ -23453,7 +23453,7 @@
       </c>
       <c r="O8" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O8</f>
-        <v>0.355468099487318</v>
+        <v>0.373830804764655</v>
       </c>
     </row>
     <row r="9" s="34" customFormat="1" spans="1:15">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H11</f>
-        <v>0</v>
+        <v>7111</v>
       </c>
       <c r="I11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I11</f>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="O11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O11</f>
-        <v>155756</v>
+        <v>162867</v>
       </c>
     </row>
     <row r="12" s="34" customFormat="1" spans="1:15">
@@ -23673,7 +23673,7 @@
       </c>
       <c r="H12" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H12</f>
-        <v>0</v>
+        <v>0.176859750789663</v>
       </c>
       <c r="I12" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I12</f>
@@ -23701,7 +23701,7 @@
       </c>
       <c r="O12" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O12</f>
-        <v>0.268141690424052</v>
+        <v>0.280383630128496</v>
       </c>
     </row>
     <row r="13" s="34" customFormat="1" spans="1:15">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="H15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H15</f>
-        <v>0</v>
+        <v>2512</v>
       </c>
       <c r="I15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I15</f>
@@ -23887,7 +23887,7 @@
       </c>
       <c r="O15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O15</f>
-        <v>55346</v>
+        <v>57858</v>
       </c>
     </row>
     <row r="16" s="34" customFormat="1" spans="1:15">
@@ -23921,7 +23921,7 @@
       </c>
       <c r="H16" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H16</f>
-        <v>0</v>
+        <v>0.201537687627816</v>
       </c>
       <c r="I16" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I16</f>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="O16" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O16</f>
-        <v>0.307357703368329</v>
+        <v>0.321307809082585</v>
       </c>
     </row>
     <row r="17" s="34" customFormat="1" spans="1:15">
@@ -24107,7 +24107,7 @@
       </c>
       <c r="H19" s="23">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H19</f>
-        <v>0</v>
+        <v>2959137.918</v>
       </c>
       <c r="I19" s="23">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I19</f>
@@ -24135,7 +24135,7 @@
       </c>
       <c r="O19" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O19</f>
-        <v>60918020.7102</v>
+        <v>63877158.6282</v>
       </c>
     </row>
     <row r="20" s="34" customFormat="1" spans="1:15">
@@ -24169,7 +24169,7 @@
       </c>
       <c r="H20" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H20</f>
-        <v>0</v>
+        <v>0.211680523237847</v>
       </c>
       <c r="I20" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I20</f>
@@ -24197,7 +24197,7 @@
       </c>
       <c r="O20" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O20</f>
-        <v>0.302027161464247</v>
+        <v>0.316698354246535</v>
       </c>
     </row>
     <row r="21" s="34" customFormat="1" spans="1:15">
@@ -24355,7 +24355,7 @@
       </c>
       <c r="H23" s="23">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H23</f>
-        <v>0</v>
+        <v>889801.365</v>
       </c>
       <c r="I23" s="23">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I23</f>
@@ -24383,7 +24383,7 @@
       </c>
       <c r="O23" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O23</f>
-        <v>19945901.6564</v>
+        <v>20835703.0214</v>
       </c>
     </row>
     <row r="24" s="34" customFormat="1" spans="1:15">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="H24" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H24</f>
-        <v>0</v>
+        <v>0.198910991710651</v>
       </c>
       <c r="I24" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I24</f>
@@ -24445,7 +24445,7 @@
       </c>
       <c r="O24" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O24</f>
-        <v>0.309032326861965</v>
+        <v>0.32281848659582</v>
       </c>
     </row>
     <row r="25" s="34" customFormat="1" spans="1:15">
@@ -24539,9 +24539,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G26</f>
         <v>0.30344390034843</v>
       </c>
-      <c r="H26" s="5" t="e">
+      <c r="H26" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H26</f>
-        <v>#DIV/0!</v>
+        <v>0.300696145180483</v>
       </c>
       <c r="I26" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I26</f>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="O26" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O26</f>
-        <v>0.327422024285505</v>
+        <v>0.32618393599307</v>
       </c>
     </row>
     <row r="27" s="34" customFormat="1" spans="1:15">
@@ -24601,9 +24601,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G27</f>
         <v>0.653048256270325</v>
       </c>
-      <c r="H27" s="5" t="e">
+      <c r="H27" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H27</f>
-        <v>#DIV/0!</v>
+        <v>0.646744480382506</v>
       </c>
       <c r="I27" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I27</f>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="O27" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O27</f>
-        <v>0.644662163897378</v>
+        <v>0.644753080734587</v>
       </c>
     </row>
     <row r="28" s="34" customFormat="1" spans="1:15">
@@ -24663,9 +24663,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G28</f>
         <v>0.16938581938584</v>
       </c>
-      <c r="H28" s="5" t="e">
+      <c r="H28" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H28</f>
-        <v>#DIV/0!</v>
+        <v>0.180681280478818</v>
       </c>
       <c r="I28" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I28</f>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="O28" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O28</f>
-        <v>0.156033022904301</v>
+        <v>0.157085641729409</v>
       </c>
     </row>
     <row r="29" s="34" customFormat="1" spans="1:15">
@@ -24789,7 +24789,7 @@
       </c>
       <c r="H30" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H30</f>
-        <v>0</v>
+        <v>52764.41</v>
       </c>
       <c r="I30" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I30</f>
@@ -24817,7 +24817,7 @@
       </c>
       <c r="O30" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O30</f>
-        <v>1772160.66</v>
+        <v>1824925.07</v>
       </c>
     </row>
     <row r="31" s="34" customFormat="1" spans="1:15">
@@ -24851,7 +24851,7 @@
       </c>
       <c r="H31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H31</f>
-        <v>0</v>
+        <v>2716</v>
       </c>
       <c r="I31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I31</f>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="O31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O31</f>
-        <v>76304</v>
+        <v>79020</v>
       </c>
     </row>
     <row r="32" s="34" customFormat="1" spans="1:15">
@@ -24913,7 +24913,7 @@
       </c>
       <c r="H32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H32</f>
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="I32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I32</f>
@@ -24941,7 +24941,7 @@
       </c>
       <c r="O32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O32</f>
-        <v>28154</v>
+        <v>29069</v>
       </c>
     </row>
     <row r="33" s="34" customFormat="1" spans="1:15">
@@ -24975,7 +24975,7 @@
       </c>
       <c r="H33" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H33</f>
-        <v>0</v>
+        <v>1166305.44</v>
       </c>
       <c r="I33" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I33</f>
@@ -25003,7 +25003,7 @@
       </c>
       <c r="O33" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O33</f>
-        <v>31315726.5669</v>
+        <v>32482032.0069</v>
       </c>
     </row>
     <row r="34" s="34" customFormat="1" spans="1:15">
@@ -25037,7 +25037,7 @@
       </c>
       <c r="H34" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H34</f>
-        <v>0</v>
+        <v>336024.4174</v>
       </c>
       <c r="I34" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I34</f>
@@ -25065,7 +25065,7 @@
       </c>
       <c r="O34" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O34</f>
-        <v>10388659.092</v>
+        <v>10724683.5094</v>
       </c>
     </row>
     <row r="35" s="34" customFormat="1" spans="1:15">
@@ -25097,9 +25097,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G35</f>
         <v>0.316994756333358</v>
       </c>
-      <c r="H35" s="5" t="e">
+      <c r="H35" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H35</f>
-        <v>#DIV/0!</v>
+        <v>0.288110134683072</v>
       </c>
       <c r="I35" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I35</f>
@@ -25127,7 +25127,7 @@
       </c>
       <c r="O35" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O35</f>
-        <v>0.331739360088186</v>
+        <v>0.330172801600645</v>
       </c>
     </row>
     <row r="36" s="34" customFormat="1" spans="1:15">
@@ -25159,9 +25159,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G36</f>
         <v>0.655409930163589</v>
       </c>
-      <c r="H36" s="5" t="e">
+      <c r="H36" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H36</f>
-        <v>#DIV/0!</v>
+        <v>0.663107511045655</v>
       </c>
       <c r="I36" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I36</f>
@@ -25189,7 +25189,7 @@
       </c>
       <c r="O36" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O36</f>
-        <v>0.631028517508912</v>
+        <v>0.632131106049101</v>
       </c>
     </row>
     <row r="37" s="34" customFormat="1" spans="1:15">
@@ -25221,9 +25221,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G37</f>
         <v>0.15183428524004</v>
       </c>
-      <c r="H37" s="5" t="e">
+      <c r="H37" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H37</f>
-        <v>#DIV/0!</v>
+        <v>0.157025523348173</v>
       </c>
       <c r="I37" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I37</f>
@@ -25251,7 +25251,7 @@
       </c>
       <c r="O37" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O37</f>
-        <v>0.170586082795294</v>
+        <v>0.170161205074302</v>
       </c>
     </row>
     <row r="38" s="34" customFormat="1" spans="1:15">
@@ -25285,7 +25285,7 @@
       </c>
       <c r="H38" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H38</f>
-        <v>0</v>
+        <v>30284.73</v>
       </c>
       <c r="I38" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I38</f>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="O38" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O38</f>
-        <v>573371.68</v>
+        <v>603656.41</v>
       </c>
     </row>
     <row r="39" s="34" customFormat="1" spans="1:15">
@@ -25347,7 +25347,7 @@
       </c>
       <c r="H39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H39</f>
-        <v>0</v>
+        <v>1652</v>
       </c>
       <c r="I39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I39</f>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="O39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O39</f>
-        <v>34075</v>
+        <v>35727</v>
       </c>
     </row>
     <row r="40" s="34" customFormat="1" spans="1:15">
@@ -25409,7 +25409,7 @@
       </c>
       <c r="H40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H40</f>
-        <v>0</v>
+        <v>541</v>
       </c>
       <c r="I40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I40</f>
@@ -25437,7 +25437,7 @@
       </c>
       <c r="O40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O40</f>
-        <v>11190</v>
+        <v>11731</v>
       </c>
     </row>
     <row r="41" s="34" customFormat="1" spans="1:15">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="H41" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H41</f>
-        <v>0</v>
+        <v>669524.052</v>
       </c>
       <c r="I41" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I41</f>
@@ -25499,7 +25499,7 @@
       </c>
       <c r="O41" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O41</f>
-        <v>12694302.5466</v>
+        <v>13363826.5986</v>
       </c>
     </row>
     <row r="42" s="34" customFormat="1" spans="1:15">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="H42" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H42</f>
-        <v>0</v>
+        <v>188985.7344</v>
       </c>
       <c r="I42" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I42</f>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="O42" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O42</f>
-        <v>3725585.3595</v>
+        <v>3914571.0939</v>
       </c>
     </row>
     <row r="43" s="34" customFormat="1" spans="1:15">
@@ -25593,9 +25593,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G43</f>
         <v>0.237778669147947</v>
       </c>
-      <c r="H43" s="5" t="e">
+      <c r="H43" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H43</f>
-        <v>#DIV/0!</v>
+        <v>0.282268775610768</v>
       </c>
       <c r="I43" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I43</f>
@@ -25623,7 +25623,7 @@
       </c>
       <c r="O43" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O43</f>
-        <v>0.293484840606532</v>
+        <v>0.292922918822524</v>
       </c>
     </row>
     <row r="44" s="34" customFormat="1" spans="1:15">
@@ -25655,9 +25655,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G44</f>
         <v>0.701418108150226</v>
       </c>
-      <c r="H44" s="5" t="e">
+      <c r="H44" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H44</f>
-        <v>#DIV/0!</v>
+        <v>0.672518159806295</v>
       </c>
       <c r="I44" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I44</f>
@@ -25685,7 +25685,7 @@
       </c>
       <c r="O44" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O44</f>
-        <v>0.671606749816581</v>
+        <v>0.671648892994094</v>
       </c>
     </row>
     <row r="45" s="34" customFormat="1" spans="1:15">
@@ -25717,9 +25717,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G45</f>
         <v>0.136393850173022</v>
       </c>
-      <c r="H45" s="5" t="e">
+      <c r="H45" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H45</f>
-        <v>#DIV/0!</v>
+        <v>0.160248762141488</v>
       </c>
       <c r="I45" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I45</f>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="O45" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O45</f>
-        <v>0.153901098665728</v>
+        <v>0.154207548035254</v>
       </c>
     </row>
     <row r="46" s="34" customFormat="1" spans="1:15">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="H46" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H46</f>
-        <v>0</v>
+        <v>70950.96</v>
       </c>
       <c r="I46" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I46</f>
@@ -25809,7 +25809,7 @@
       </c>
       <c r="O46" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O46</f>
-        <v>633113.12</v>
+        <v>704064.08</v>
       </c>
     </row>
     <row r="47" s="34" customFormat="1" spans="1:15">
@@ -25843,7 +25843,7 @@
       </c>
       <c r="H47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H47</f>
-        <v>0</v>
+        <v>2443</v>
       </c>
       <c r="I47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I47</f>
@@ -25871,7 +25871,7 @@
       </c>
       <c r="O47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O47</f>
-        <v>28801</v>
+        <v>31244</v>
       </c>
     </row>
     <row r="48" s="34" customFormat="1" spans="1:15">
@@ -25905,7 +25905,7 @@
       </c>
       <c r="H48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H48</f>
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="I48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I48</f>
@@ -25933,7 +25933,7 @@
       </c>
       <c r="O48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O48</f>
-        <v>9976</v>
+        <v>10912</v>
       </c>
     </row>
     <row r="49" s="34" customFormat="1" spans="1:15">
@@ -25967,7 +25967,7 @@
       </c>
       <c r="H49" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H49</f>
-        <v>0</v>
+        <v>1008220.752</v>
       </c>
       <c r="I49" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I49</f>
@@ -25995,7 +25995,7 @@
       </c>
       <c r="O49" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O49</f>
-        <v>11102484.4854</v>
+        <v>12110705.2374</v>
       </c>
     </row>
     <row r="50" s="34" customFormat="1" spans="1:15">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="H50" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H50</f>
-        <v>0</v>
+        <v>328535.4711</v>
       </c>
       <c r="I50" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I50</f>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O50" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O50</f>
-        <v>3526431.1052</v>
+        <v>3854966.5763</v>
       </c>
     </row>
     <row r="51" s="34" customFormat="1" spans="1:15">
@@ -26089,9 +26089,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G51</f>
         <v>0.334765679860865</v>
       </c>
-      <c r="H51" s="5" t="e">
+      <c r="H51" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H51</f>
-        <v>#DIV/0!</v>
+        <v>0.32585668411237</v>
       </c>
       <c r="I51" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I51</f>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="O51" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O51</f>
-        <v>0.317625402659858</v>
+        <v>0.318310659927151</v>
       </c>
     </row>
     <row r="52" s="34" customFormat="1" spans="1:15">
@@ -26151,9 +26151,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G52</f>
         <v>0.621183654297792</v>
       </c>
-      <c r="H52" s="5" t="e">
+      <c r="H52" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H52</f>
-        <v>#DIV/0!</v>
+        <v>0.616864510847319</v>
       </c>
       <c r="I52" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I52</f>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="O52" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O52</f>
-        <v>0.653623138085483</v>
+        <v>0.650748943797209</v>
       </c>
     </row>
     <row r="53" s="34" customFormat="1" spans="1:15">
@@ -26213,9 +26213,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G53</f>
         <v>0.22016008895728</v>
       </c>
-      <c r="H53" s="5" t="e">
+      <c r="H53" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H53</f>
-        <v>#DIV/0!</v>
+        <v>0.21596133824589</v>
       </c>
       <c r="I53" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I53</f>
@@ -26243,7 +26243,7 @@
       </c>
       <c r="O53" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O53</f>
-        <v>0.179533670476768</v>
+        <v>0.182638180141048</v>
       </c>
     </row>
     <row r="54" s="34" customFormat="1" spans="1:15">
@@ -26277,7 +26277,7 @@
       </c>
       <c r="H54" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H54</f>
-        <v>0</v>
+        <v>6770.35</v>
       </c>
       <c r="I54" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I54</f>
@@ -26305,7 +26305,7 @@
       </c>
       <c r="O54" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O54</f>
-        <v>133573.87</v>
+        <v>140344.22</v>
       </c>
     </row>
     <row r="55" s="34" customFormat="1" spans="1:15">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="H55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H55</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I55</f>
@@ -26367,7 +26367,7 @@
       </c>
       <c r="O55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O55</f>
-        <v>16576</v>
+        <v>16876</v>
       </c>
     </row>
     <row r="56" s="34" customFormat="1" spans="1:15">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="H56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H56</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I56</f>
@@ -26429,7 +26429,7 @@
       </c>
       <c r="O56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O56</f>
-        <v>6026</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="57" s="34" customFormat="1" spans="1:15">
@@ -26463,7 +26463,7 @@
       </c>
       <c r="H57" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H57</f>
-        <v>0</v>
+        <v>115087.674</v>
       </c>
       <c r="I57" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I57</f>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="O57" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O57</f>
-        <v>5805507.1113</v>
+        <v>5920594.7853</v>
       </c>
     </row>
     <row r="58" s="34" customFormat="1" spans="1:15">
@@ -26525,7 +26525,7 @@
       </c>
       <c r="H58" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H58</f>
-        <v>0</v>
+        <v>36255.7421</v>
       </c>
       <c r="I58" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I58</f>
@@ -26553,7 +26553,7 @@
       </c>
       <c r="O58" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O58</f>
-        <v>2305226.0997</v>
+        <v>2341481.8418</v>
       </c>
     </row>
     <row r="59" s="34" customFormat="1" spans="1:15">
@@ -26585,9 +26585,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G59</f>
         <v>0.341965352210622</v>
       </c>
-      <c r="H59" s="5" t="e">
+      <c r="H59" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H59</f>
-        <v>#DIV/0!</v>
+        <v>0.315027151387211</v>
       </c>
       <c r="I59" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I59</f>
@@ -26615,7 +26615,7 @@
       </c>
       <c r="O59" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O59</f>
-        <v>0.397075751610578</v>
+        <v>0.395480847230682</v>
       </c>
     </row>
     <row r="60" s="34" customFormat="1" spans="1:15">
@@ -26647,9 +26647,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G60</f>
         <v>0.606437454279444</v>
       </c>
-      <c r="H60" s="5" t="e">
+      <c r="H60" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H60</f>
-        <v>#DIV/0!</v>
+        <v>0.6</v>
       </c>
       <c r="I60" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I60</f>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="O60" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O60</f>
-        <v>0.636462355212355</v>
+        <v>0.635814173974875</v>
       </c>
     </row>
     <row r="61" s="34" customFormat="1" spans="1:15">
@@ -26709,9 +26709,9 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G61</f>
         <v>0.0928901830014306</v>
       </c>
-      <c r="H61" s="5" t="e">
+      <c r="H61" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H61</f>
-        <v>#DIV/0!</v>
+        <v>0.186738695937491</v>
       </c>
       <c r="I61" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I61</f>
@@ -26739,7 +26739,7 @@
       </c>
       <c r="O61" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O61</f>
-        <v>0.0579439344441672</v>
+        <v>0.0599382055818597</v>
       </c>
     </row>
     <row r="62" s="34" customFormat="1" spans="1:15">
@@ -33539,7 +33539,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8c765b5-f847-4bf7-a82b-77281eed1100}</x14:id>
+          <x14:id>{1a9a62fa-72cf-4e2b-95b9-53a5e891e072}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33553,7 +33553,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49223ce2-6911-4057-9c16-95f9683dbb46}</x14:id>
+          <x14:id>{c36e5be7-f429-4753-8279-18dd4eb2ae1e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33567,7 +33567,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a86cb61-3057-4d49-94b2-9474b9ba081a}</x14:id>
+          <x14:id>{186933ff-1580-436d-a46c-035c9e1f9a39}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33581,7 +33581,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{59725fa8-22ad-454e-97ab-702bee54fd50}</x14:id>
+          <x14:id>{bbe46629-6b15-4248-a477-39fcc91f403e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33595,7 +33595,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6a6fc50-20f8-4953-bab0-97867193f53f}</x14:id>
+          <x14:id>{ef9e71ab-c9e8-462d-ae77-4caf4fe61762}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33609,7 +33609,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37fe7b90-a4ba-478d-9c19-3fa0ae5d0d71}</x14:id>
+          <x14:id>{0206bbd4-548a-44ec-807e-8b72c996eb39}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33629,7 +33629,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99101703-ef75-45ad-a781-e4769f9f364c}</x14:id>
+          <x14:id>{dc574895-793c-468c-9a4b-9b47499c40b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33643,7 +33643,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3f3c6cba-c26b-4d0d-a656-80768b85490b}</x14:id>
+          <x14:id>{70737385-9184-4ccd-84dc-a6007a82000d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33657,7 +33657,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0deae1b-cf45-447a-bd23-479ed755279d}</x14:id>
+          <x14:id>{63c37021-5aff-4e45-b5a9-b7609d07c1b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33671,7 +33671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31b933bd-b2c3-4319-8f8d-f39f65dab991}</x14:id>
+          <x14:id>{a661b910-613e-4711-b5e7-e43abe12c0dd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33685,7 +33685,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9eb932a2-a2d8-4444-a640-d211578664b1}</x14:id>
+          <x14:id>{5a125acd-7a71-4e8b-928e-442c9285b7ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33699,7 +33699,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa6dee83-ff6e-43fe-befa-f4e029e210d3}</x14:id>
+          <x14:id>{25cfda66-b324-49ec-9529-c03eb7b4fb25}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33721,7 +33721,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7c3cffa-58fe-4686-bdb0-a60519bd57d6}</x14:id>
+          <x14:id>{3ac1bb8d-2486-4076-abb5-45ca8eae14bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33751,7 +33751,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8bca2cb1-65b6-43b0-afc1-341dc0ba975e}</x14:id>
+          <x14:id>{1874a651-7503-4436-a7c3-87e9518c3329}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33781,7 +33781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c66254b-246d-484b-9375-2b099d7d5725}</x14:id>
+          <x14:id>{c1cb1ba6-c918-409e-8b72-c0d4fde0295b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33811,7 +33811,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e91677d-e854-4869-a9c1-23991fba8f97}</x14:id>
+          <x14:id>{9c5d148e-ba04-45b5-94a0-17f22dee51ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33841,7 +33841,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{40f1c921-09eb-4277-a38f-514377acc060}</x14:id>
+          <x14:id>{dc6294fb-3ff8-4395-a4e0-b222b4e2898b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33871,7 +33871,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4912f105-0777-4dd9-ad8d-61b8aabc6f92}</x14:id>
+          <x14:id>{f82c9646-4784-43d6-bb32-fb631d3208d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33893,7 +33893,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b06d319-40a2-4b29-9f8f-52c2c6833bff}</x14:id>
+          <x14:id>{36eb1ea4-6c4a-471b-9811-1aab1240256c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33915,7 +33915,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1263fc0f-e373-47e4-9f0b-31a2e8305f92}</x14:id>
+          <x14:id>{a2a59885-ca86-4877-b865-52d3232bf799}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33937,7 +33937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{529d890f-cf97-420d-9724-71801dbf91ac}</x14:id>
+          <x14:id>{ba9aa0ec-65b8-4786-b0c7-050a71097dfc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33959,7 +33959,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f291a20-5934-4f66-bce9-457cece79a55}</x14:id>
+          <x14:id>{e9a860a7-7f81-44a1-b7a0-066b1782a348}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33981,7 +33981,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{de4eef02-b2e3-4fdb-9e11-be5624216d42}</x14:id>
+          <x14:id>{9608fb70-1383-450d-98c9-6fe85b7ca759}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34003,7 +34003,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ca2ef1d-ede3-4e86-a151-531042a916e5}</x14:id>
+          <x14:id>{5f20c2ac-71f2-41c7-b3a2-550041fcbde8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34025,7 +34025,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a93e7c3-045f-4ed6-886b-38f4e23161f0}</x14:id>
+          <x14:id>{42da3622-6ede-44d6-8338-9d518b6b4597}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34047,7 +34047,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ce34fbb-a3fa-4c09-8554-5e96a6458a95}</x14:id>
+          <x14:id>{517ca1c0-7bc4-4be3-baec-f680e57d4179}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34069,7 +34069,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99a199b5-e65d-4777-a3a8-d6193b3a0371}</x14:id>
+          <x14:id>{bb02b5a0-e953-4d15-a76a-0894b17222f7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34091,7 +34091,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ebaec18d-3596-4a02-9e2f-58af2403e424}</x14:id>
+          <x14:id>{98fe5106-7610-4771-a0f2-c236b2543861}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34113,7 +34113,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5fb75b16-1ed7-4e1e-ab25-4b838fdb84e7}</x14:id>
+          <x14:id>{67123c92-7492-46bb-8b9a-666861d3c430}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34135,7 +34135,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cd2dfc7e-5c9e-4337-9005-bf0334d7bb7b}</x14:id>
+          <x14:id>{bd8bc73d-8b18-4ac6-a53e-fe0385d8162c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34157,7 +34157,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ef5d2ea5-82eb-4d56-8dbd-b43542dd4ccf}</x14:id>
+          <x14:id>{f60f1210-a173-4ba1-b8a5-66e88542044e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34179,7 +34179,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31d3c135-6927-4eef-baa9-524067a38955}</x14:id>
+          <x14:id>{42b641fd-bb0f-42c9-b44b-944a9f984771}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34198,7 +34198,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e8c765b5-f847-4bf7-a82b-77281eed1100}">
+          <x14:cfRule type="dataBar" id="{1a9a62fa-72cf-4e2b-95b9-53a5e891e072}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34211,7 +34211,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{49223ce2-6911-4057-9c16-95f9683dbb46}">
+          <x14:cfRule type="dataBar" id="{c36e5be7-f429-4753-8279-18dd4eb2ae1e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34224,7 +34224,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a86cb61-3057-4d49-94b2-9474b9ba081a}">
+          <x14:cfRule type="dataBar" id="{186933ff-1580-436d-a46c-035c9e1f9a39}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34237,7 +34237,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{59725fa8-22ad-454e-97ab-702bee54fd50}">
+          <x14:cfRule type="dataBar" id="{bbe46629-6b15-4248-a477-39fcc91f403e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34250,7 +34250,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6a6fc50-20f8-4953-bab0-97867193f53f}">
+          <x14:cfRule type="dataBar" id="{ef9e71ab-c9e8-462d-ae77-4caf4fe61762}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34263,7 +34263,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{37fe7b90-a4ba-478d-9c19-3fa0ae5d0d71}">
+          <x14:cfRule type="dataBar" id="{0206bbd4-548a-44ec-807e-8b72c996eb39}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34276,7 +34276,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99101703-ef75-45ad-a781-e4769f9f364c}">
+          <x14:cfRule type="dataBar" id="{dc574895-793c-468c-9a4b-9b47499c40b1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34289,7 +34289,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3f3c6cba-c26b-4d0d-a656-80768b85490b}">
+          <x14:cfRule type="dataBar" id="{70737385-9184-4ccd-84dc-a6007a82000d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34302,7 +34302,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d0deae1b-cf45-447a-bd23-479ed755279d}">
+          <x14:cfRule type="dataBar" id="{63c37021-5aff-4e45-b5a9-b7609d07c1b9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34315,7 +34315,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{31b933bd-b2c3-4319-8f8d-f39f65dab991}">
+          <x14:cfRule type="dataBar" id="{a661b910-613e-4711-b5e7-e43abe12c0dd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34328,7 +34328,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9eb932a2-a2d8-4444-a640-d211578664b1}">
+          <x14:cfRule type="dataBar" id="{5a125acd-7a71-4e8b-928e-442c9285b7ec}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34341,7 +34341,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa6dee83-ff6e-43fe-befa-f4e029e210d3}">
+          <x14:cfRule type="dataBar" id="{25cfda66-b324-49ec-9529-c03eb7b4fb25}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34354,7 +34354,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7c3cffa-58fe-4686-bdb0-a60519bd57d6}">
+          <x14:cfRule type="dataBar" id="{3ac1bb8d-2486-4076-abb5-45ca8eae14bf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34367,7 +34367,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8bca2cb1-65b6-43b0-afc1-341dc0ba975e}">
+          <x14:cfRule type="dataBar" id="{1874a651-7503-4436-a7c3-87e9518c3329}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34380,7 +34380,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c66254b-246d-484b-9375-2b099d7d5725}">
+          <x14:cfRule type="dataBar" id="{c1cb1ba6-c918-409e-8b72-c0d4fde0295b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34393,7 +34393,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e91677d-e854-4869-a9c1-23991fba8f97}">
+          <x14:cfRule type="dataBar" id="{9c5d148e-ba04-45b5-94a0-17f22dee51ac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34406,7 +34406,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{40f1c921-09eb-4277-a38f-514377acc060}">
+          <x14:cfRule type="dataBar" id="{dc6294fb-3ff8-4395-a4e0-b222b4e2898b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34419,7 +34419,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4912f105-0777-4dd9-ad8d-61b8aabc6f92}">
+          <x14:cfRule type="dataBar" id="{f82c9646-4784-43d6-bb32-fb631d3208d6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34432,7 +34432,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8b06d319-40a2-4b29-9f8f-52c2c6833bff}">
+          <x14:cfRule type="dataBar" id="{36eb1ea4-6c4a-471b-9811-1aab1240256c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34445,7 +34445,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1263fc0f-e373-47e4-9f0b-31a2e8305f92}">
+          <x14:cfRule type="dataBar" id="{a2a59885-ca86-4877-b865-52d3232bf799}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34458,7 +34458,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{529d890f-cf97-420d-9724-71801dbf91ac}">
+          <x14:cfRule type="dataBar" id="{ba9aa0ec-65b8-4786-b0c7-050a71097dfc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34471,7 +34471,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5f291a20-5934-4f66-bce9-457cece79a55}">
+          <x14:cfRule type="dataBar" id="{e9a860a7-7f81-44a1-b7a0-066b1782a348}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34484,7 +34484,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{de4eef02-b2e3-4fdb-9e11-be5624216d42}">
+          <x14:cfRule type="dataBar" id="{9608fb70-1383-450d-98c9-6fe85b7ca759}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34497,7 +34497,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ca2ef1d-ede3-4e86-a151-531042a916e5}">
+          <x14:cfRule type="dataBar" id="{5f20c2ac-71f2-41c7-b3a2-550041fcbde8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34510,7 +34510,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5a93e7c3-045f-4ed6-886b-38f4e23161f0}">
+          <x14:cfRule type="dataBar" id="{42da3622-6ede-44d6-8338-9d518b6b4597}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34523,7 +34523,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9ce34fbb-a3fa-4c09-8554-5e96a6458a95}">
+          <x14:cfRule type="dataBar" id="{517ca1c0-7bc4-4be3-baec-f680e57d4179}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34536,7 +34536,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99a199b5-e65d-4777-a3a8-d6193b3a0371}">
+          <x14:cfRule type="dataBar" id="{bb02b5a0-e953-4d15-a76a-0894b17222f7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34549,7 +34549,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ebaec18d-3596-4a02-9e2f-58af2403e424}">
+          <x14:cfRule type="dataBar" id="{98fe5106-7610-4771-a0f2-c236b2543861}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34562,7 +34562,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5fb75b16-1ed7-4e1e-ab25-4b838fdb84e7}">
+          <x14:cfRule type="dataBar" id="{67123c92-7492-46bb-8b9a-666861d3c430}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34575,7 +34575,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cd2dfc7e-5c9e-4337-9005-bf0334d7bb7b}">
+          <x14:cfRule type="dataBar" id="{bd8bc73d-8b18-4ac6-a53e-fe0385d8162c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34588,7 +34588,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ef5d2ea5-82eb-4d56-8dbd-b43542dd4ccf}">
+          <x14:cfRule type="dataBar" id="{f60f1210-a173-4ba1-b8a5-66e88542044e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34601,7 +34601,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{31d3c135-6927-4eef-baa9-524067a38955}">
+          <x14:cfRule type="dataBar" id="{42b641fd-bb0f-42c9-b44b-944a9f984771}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -11844,6 +11844,26 @@
             <v>262747.868852459</v>
           </cell>
         </row>
+        <row r="32">
+          <cell r="F32">
+            <v>33154.43</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33">
+            <v>95210.94</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="F34">
+            <v>87149.71</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="F35">
+            <v>95706.53</v>
+          </cell>
+        </row>
         <row r="44">
           <cell r="B44">
             <v>372843</v>
@@ -11880,6 +11900,26 @@
           </cell>
           <cell r="M44">
             <v>318392.868852459</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="F45">
+            <v>100423.98</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="F46">
+            <v>159761.43</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="F47">
+            <v>176058.01</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="F48">
+            <v>157424.67</v>
           </cell>
         </row>
         <row r="58">
@@ -21476,7 +21516,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2bbb6288-b622-4729-a9b0-4e8537fffa93}</x14:id>
+          <x14:id>{88b12b0c-21c5-4df4-88da-c65c40584735}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21490,7 +21530,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32ac0082-7ab1-439e-9320-bfe14f60fe67}</x14:id>
+          <x14:id>{725a36bb-d3fe-4dbf-8f03-3037547e3825}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21504,7 +21544,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ff8e7c05-7427-4535-a288-8f14c186617e}</x14:id>
+          <x14:id>{cc5cdeda-63eb-411d-9f58-b5c893acf903}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21518,7 +21558,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23277241-295f-4337-a375-5c635cd11268}</x14:id>
+          <x14:id>{079ccaf2-92ac-4256-92d2-3963354f1a9e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21532,7 +21572,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb3cd9f7-57af-4953-b941-c4c4f34992df}</x14:id>
+          <x14:id>{bfb570fa-7381-4673-85f5-e707e591997f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21546,7 +21586,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e32a5be5-972d-41b1-86d6-a4376ec6d945}</x14:id>
+          <x14:id>{ca22ab33-094a-4d65-b3c3-613afc1b687c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21560,7 +21600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5e6d67b-8d33-4825-a84e-c7f3825f21d9}</x14:id>
+          <x14:id>{ad02a9a4-671f-4c0c-a0ce-1c70b09a8006}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21574,7 +21614,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8a15dcb-f036-4c29-9c7b-494344690f35}</x14:id>
+          <x14:id>{e5057669-3fbb-48a1-b1bc-741b7ab6334f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21594,7 +21634,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c737da8-5ca9-4ceb-8e84-7cd2901706cd}</x14:id>
+          <x14:id>{7cbbab68-a81e-4287-95ff-7bbea42456a8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21622,7 +21662,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{05cfeb75-05b4-40c5-acce-902073474035}</x14:id>
+          <x14:id>{709d95a4-9190-4099-8174-dc23a602a36b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21642,7 +21682,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f76fa017-90c2-4f5e-82d8-0e0117c27bad}</x14:id>
+          <x14:id>{5308d319-886a-4674-b3c7-dbbdcada47dc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21670,7 +21710,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4c6f96f7-fb51-4738-b5cb-7b97e77948ac}</x14:id>
+          <x14:id>{b861d31b-0f33-45e1-8659-2bfef54c2fc5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21690,7 +21730,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4888e397-6b45-45a3-bc98-317ba9a3a38d}</x14:id>
+          <x14:id>{c8180357-42af-4b79-b934-469a56ff223e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21718,7 +21758,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7ace09eb-8af7-4c9d-a720-d82b54f3edfb}</x14:id>
+          <x14:id>{9c7bfaa0-4223-4423-855c-0dd0e07f7df1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21738,7 +21778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7126ecf7-2394-4436-81dc-0f3e4c40213b}</x14:id>
+          <x14:id>{15b9a962-c435-4a8b-9d79-6299f4732988}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21766,7 +21806,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2743dc60-3ad1-48c8-8bf0-99ddac101d67}</x14:id>
+          <x14:id>{8eb6e413-7d2c-4ac8-9ed8-63f58d8c4d2e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21786,7 +21826,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{420f31f9-9079-4608-ab8c-932e15390b8c}</x14:id>
+          <x14:id>{60ad2c9a-0217-47b5-8646-07e24232958f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21814,7 +21854,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6098526-2c33-49f9-acde-eadabd58665e}</x14:id>
+          <x14:id>{d4ca01bc-de44-47c5-8f43-6014b94165e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21876,7 +21916,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8c55493-3091-4dd5-9a69-7e6894a86bcc}</x14:id>
+          <x14:id>{07c2d317-467c-4c5e-ac92-e12be1758d50}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21906,7 +21946,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{09726e7a-e3fb-4008-8ab9-39c4d8e80d8f}</x14:id>
+          <x14:id>{dd6f502e-19cb-4296-a392-4a010db1affd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21928,7 +21968,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b822ba8e-3278-4f5c-98e5-5b73b95e170e}</x14:id>
+          <x14:id>{ce9ce528-2b87-4ba5-9de1-245cf9deee39}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21948,7 +21988,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41546333-64b7-4652-b46b-69f21d162876}</x14:id>
+          <x14:id>{624283ac-b55c-4212-ac1d-deebee0e7cd7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21970,7 +22010,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a78f785e-c053-477d-9435-ad2d849b4a42}</x14:id>
+          <x14:id>{445ca9c5-33e9-46e7-bc24-56721ea4cb55}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21990,7 +22030,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3b89f26d-6426-4c67-9925-d48f768dc042}</x14:id>
+          <x14:id>{a7679a1a-bad2-4423-8055-e46f8371d6fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22012,7 +22052,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3943dc95-7053-4432-8255-4d1e4fc99d85}</x14:id>
+          <x14:id>{ba036439-0698-4db3-a7e5-968317b6af2b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22032,7 +22072,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{601155aa-1ba4-4680-915a-82703ab62e5c}</x14:id>
+          <x14:id>{4a5ec903-1f95-477e-a46c-796640926a9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22054,7 +22094,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{312c435a-47be-4ab2-9e02-8f0951738a7a}</x14:id>
+          <x14:id>{052df7c0-65d6-4152-a290-8d9fecfbc6af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22074,7 +22114,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3662691-7345-4bac-9a95-a3c0c4dcea6d}</x14:id>
+          <x14:id>{cd1f65d2-ad6c-4f8f-97ca-0fafabc44375}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22102,7 +22142,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d360104b-b079-4168-9aba-4e41baff3ac0}</x14:id>
+          <x14:id>{12f10c76-45dc-4515-930a-5ef78249dd08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22116,7 +22156,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a35cc04-d002-4819-8152-292963e6a34a}</x14:id>
+          <x14:id>{727859f5-4f69-4323-947b-078ba85e2952}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22146,7 +22186,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e09bc121-fa96-49ae-92fc-895928c3946e}</x14:id>
+          <x14:id>{d482a274-eca3-404a-a26a-091bcaa9fdcc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22168,7 +22208,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{beb0cab7-f5ec-4788-b955-1a2c13eaf8e9}</x14:id>
+          <x14:id>{184366a0-76d8-444e-8d28-7f6e139c3beb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22190,7 +22230,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e39cb675-4017-42a3-95ad-0e06bf0b22da}</x14:id>
+          <x14:id>{572fffe6-d08f-44b0-8300-da8dfe6918a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22212,7 +22252,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5422710f-d720-481e-b83c-bf2eae60f4c2}</x14:id>
+          <x14:id>{8de6f208-0689-44aa-a52a-4caf9b6eeaeb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22234,7 +22274,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db54a3c6-6508-4ba7-9d89-ef60e47b1f69}</x14:id>
+          <x14:id>{0895ba25-34d7-4244-a406-7dc512c50cbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22256,7 +22296,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a4f627f-4233-40b7-a628-e1973662cbc6}</x14:id>
+          <x14:id>{8925427e-3d9b-47b0-b03a-451a15829b1a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22278,7 +22318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d4a43e2-01c7-4d3b-a6bc-8a4514ff7e54}</x14:id>
+          <x14:id>{fca8f4e1-8056-4c84-93ef-fd57d609d1ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22300,7 +22340,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72f7c1b6-0c29-497e-8d17-420e705f3eff}</x14:id>
+          <x14:id>{32d36661-12a6-42ef-8eb3-88798e5ab38b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22322,7 +22362,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{886f586a-0759-4613-aef3-5a92933433a2}</x14:id>
+          <x14:id>{3f6eb41d-fd17-423c-947f-7f981954a5ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22344,7 +22384,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3b85e4d-8a81-4414-b7ff-256bb2612a6c}</x14:id>
+          <x14:id>{fa367d15-ecc2-4968-8a0a-7e526023b4bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22366,7 +22406,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5da2aae-0552-4f83-a74a-3f1cc3dfaf91}</x14:id>
+          <x14:id>{38a199a3-b79e-4269-bd50-b1685c03f727}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22388,7 +22428,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c945b804-c0ee-41dc-879b-69e29fb04c52}</x14:id>
+          <x14:id>{bc4d0482-7dcd-4943-9ac1-95dd2fc3e5ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22410,7 +22450,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{22132809-561d-4bfe-b2f0-0db5213168ac}</x14:id>
+          <x14:id>{2d644e01-6cec-4bf9-a7e4-51b92966fd40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22429,7 +22469,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2bbb6288-b622-4729-a9b0-4e8537fffa93}">
+          <x14:cfRule type="dataBar" id="{88b12b0c-21c5-4df4-88da-c65c40584735}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22442,7 +22482,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32ac0082-7ab1-439e-9320-bfe14f60fe67}">
+          <x14:cfRule type="dataBar" id="{725a36bb-d3fe-4dbf-8f03-3037547e3825}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22455,7 +22495,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ff8e7c05-7427-4535-a288-8f14c186617e}">
+          <x14:cfRule type="dataBar" id="{cc5cdeda-63eb-411d-9f58-b5c893acf903}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22468,7 +22508,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23277241-295f-4337-a375-5c635cd11268}">
+          <x14:cfRule type="dataBar" id="{079ccaf2-92ac-4256-92d2-3963354f1a9e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22481,7 +22521,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cb3cd9f7-57af-4953-b941-c4c4f34992df}">
+          <x14:cfRule type="dataBar" id="{bfb570fa-7381-4673-85f5-e707e591997f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22494,7 +22534,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e32a5be5-972d-41b1-86d6-a4376ec6d945}">
+          <x14:cfRule type="dataBar" id="{ca22ab33-094a-4d65-b3c3-613afc1b687c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22507,7 +22547,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f5e6d67b-8d33-4825-a84e-c7f3825f21d9}">
+          <x14:cfRule type="dataBar" id="{ad02a9a4-671f-4c0c-a0ce-1c70b09a8006}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22520,7 +22560,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b8a15dcb-f036-4c29-9c7b-494344690f35}">
+          <x14:cfRule type="dataBar" id="{e5057669-3fbb-48a1-b1bc-741b7ab6334f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22533,7 +22573,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c737da8-5ca9-4ceb-8e84-7cd2901706cd}">
+          <x14:cfRule type="dataBar" id="{7cbbab68-a81e-4287-95ff-7bbea42456a8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22546,7 +22586,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{05cfeb75-05b4-40c5-acce-902073474035}">
+          <x14:cfRule type="dataBar" id="{709d95a4-9190-4099-8174-dc23a602a36b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22559,7 +22599,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f76fa017-90c2-4f5e-82d8-0e0117c27bad}">
+          <x14:cfRule type="dataBar" id="{5308d319-886a-4674-b3c7-dbbdcada47dc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22572,7 +22612,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4c6f96f7-fb51-4738-b5cb-7b97e77948ac}">
+          <x14:cfRule type="dataBar" id="{b861d31b-0f33-45e1-8659-2bfef54c2fc5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22585,7 +22625,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4888e397-6b45-45a3-bc98-317ba9a3a38d}">
+          <x14:cfRule type="dataBar" id="{c8180357-42af-4b79-b934-469a56ff223e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22598,7 +22638,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7ace09eb-8af7-4c9d-a720-d82b54f3edfb}">
+          <x14:cfRule type="dataBar" id="{9c7bfaa0-4223-4423-855c-0dd0e07f7df1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22611,7 +22651,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7126ecf7-2394-4436-81dc-0f3e4c40213b}">
+          <x14:cfRule type="dataBar" id="{15b9a962-c435-4a8b-9d79-6299f4732988}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22624,7 +22664,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2743dc60-3ad1-48c8-8bf0-99ddac101d67}">
+          <x14:cfRule type="dataBar" id="{8eb6e413-7d2c-4ac8-9ed8-63f58d8c4d2e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22637,7 +22677,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{420f31f9-9079-4608-ab8c-932e15390b8c}">
+          <x14:cfRule type="dataBar" id="{60ad2c9a-0217-47b5-8646-07e24232958f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22650,7 +22690,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a6098526-2c33-49f9-acde-eadabd58665e}">
+          <x14:cfRule type="dataBar" id="{d4ca01bc-de44-47c5-8f43-6014b94165e1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22663,7 +22703,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f8c55493-3091-4dd5-9a69-7e6894a86bcc}">
+          <x14:cfRule type="dataBar" id="{07c2d317-467c-4c5e-ac92-e12be1758d50}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22676,7 +22716,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{09726e7a-e3fb-4008-8ab9-39c4d8e80d8f}">
+          <x14:cfRule type="dataBar" id="{dd6f502e-19cb-4296-a392-4a010db1affd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22689,7 +22729,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b822ba8e-3278-4f5c-98e5-5b73b95e170e}">
+          <x14:cfRule type="dataBar" id="{ce9ce528-2b87-4ba5-9de1-245cf9deee39}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22702,7 +22742,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41546333-64b7-4652-b46b-69f21d162876}">
+          <x14:cfRule type="dataBar" id="{624283ac-b55c-4212-ac1d-deebee0e7cd7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22715,7 +22755,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a78f785e-c053-477d-9435-ad2d849b4a42}">
+          <x14:cfRule type="dataBar" id="{445ca9c5-33e9-46e7-bc24-56721ea4cb55}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22728,7 +22768,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3b89f26d-6426-4c67-9925-d48f768dc042}">
+          <x14:cfRule type="dataBar" id="{a7679a1a-bad2-4423-8055-e46f8371d6fa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22741,7 +22781,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3943dc95-7053-4432-8255-4d1e4fc99d85}">
+          <x14:cfRule type="dataBar" id="{ba036439-0698-4db3-a7e5-968317b6af2b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22754,7 +22794,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{601155aa-1ba4-4680-915a-82703ab62e5c}">
+          <x14:cfRule type="dataBar" id="{4a5ec903-1f95-477e-a46c-796640926a9d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22767,7 +22807,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{312c435a-47be-4ab2-9e02-8f0951738a7a}">
+          <x14:cfRule type="dataBar" id="{052df7c0-65d6-4152-a290-8d9fecfbc6af}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22780,7 +22820,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3662691-7345-4bac-9a95-a3c0c4dcea6d}">
+          <x14:cfRule type="dataBar" id="{cd1f65d2-ad6c-4f8f-97ca-0fafabc44375}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22793,7 +22833,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d360104b-b079-4168-9aba-4e41baff3ac0}">
+          <x14:cfRule type="dataBar" id="{12f10c76-45dc-4515-930a-5ef78249dd08}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22806,7 +22846,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5a35cc04-d002-4819-8152-292963e6a34a}">
+          <x14:cfRule type="dataBar" id="{727859f5-4f69-4323-947b-078ba85e2952}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22819,7 +22859,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e09bc121-fa96-49ae-92fc-895928c3946e}">
+          <x14:cfRule type="dataBar" id="{d482a274-eca3-404a-a26a-091bcaa9fdcc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22832,7 +22872,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{beb0cab7-f5ec-4788-b955-1a2c13eaf8e9}">
+          <x14:cfRule type="dataBar" id="{184366a0-76d8-444e-8d28-7f6e139c3beb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22845,7 +22885,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e39cb675-4017-42a3-95ad-0e06bf0b22da}">
+          <x14:cfRule type="dataBar" id="{572fffe6-d08f-44b0-8300-da8dfe6918a7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22858,7 +22898,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5422710f-d720-481e-b83c-bf2eae60f4c2}">
+          <x14:cfRule type="dataBar" id="{8de6f208-0689-44aa-a52a-4caf9b6eeaeb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22871,7 +22911,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{db54a3c6-6508-4ba7-9d89-ef60e47b1f69}">
+          <x14:cfRule type="dataBar" id="{0895ba25-34d7-4244-a406-7dc512c50cbd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22884,7 +22924,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a4f627f-4233-40b7-a628-e1973662cbc6}">
+          <x14:cfRule type="dataBar" id="{8925427e-3d9b-47b0-b03a-451a15829b1a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22897,7 +22937,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3d4a43e2-01c7-4d3b-a6bc-8a4514ff7e54}">
+          <x14:cfRule type="dataBar" id="{fca8f4e1-8056-4c84-93ef-fd57d609d1ec}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22910,7 +22950,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72f7c1b6-0c29-497e-8d17-420e705f3eff}">
+          <x14:cfRule type="dataBar" id="{32d36661-12a6-42ef-8eb3-88798e5ab38b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22923,7 +22963,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{886f586a-0759-4613-aef3-5a92933433a2}">
+          <x14:cfRule type="dataBar" id="{3f6eb41d-fd17-423c-947f-7f981954a5ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22936,7 +22976,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c3b85e4d-8a81-4414-b7ff-256bb2612a6c}">
+          <x14:cfRule type="dataBar" id="{fa367d15-ecc2-4968-8a0a-7e526023b4bf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22949,7 +22989,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e5da2aae-0552-4f83-a74a-3f1cc3dfaf91}">
+          <x14:cfRule type="dataBar" id="{38a199a3-b79e-4269-bd50-b1685c03f727}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22962,7 +23002,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c945b804-c0ee-41dc-879b-69e29fb04c52}">
+          <x14:cfRule type="dataBar" id="{bc4d0482-7dcd-4943-9ac1-95dd2fc3e5ea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22975,7 +23015,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{22132809-561d-4bfe-b2f0-0db5213168ac}">
+          <x14:cfRule type="dataBar" id="{2d644e01-6cec-4bf9-a7e4-51b92966fd40}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -33539,7 +33579,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1a9a62fa-72cf-4e2b-95b9-53a5e891e072}</x14:id>
+          <x14:id>{575977c0-485b-49ed-af65-530757f95155}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33553,7 +33593,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c36e5be7-f429-4753-8279-18dd4eb2ae1e}</x14:id>
+          <x14:id>{7b909218-2030-473f-aa31-6d49ebe4e79a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33567,7 +33607,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{186933ff-1580-436d-a46c-035c9e1f9a39}</x14:id>
+          <x14:id>{4618eebc-353f-4ed9-abe1-c24fa245c72b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33581,7 +33621,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bbe46629-6b15-4248-a477-39fcc91f403e}</x14:id>
+          <x14:id>{6421b208-6385-4726-b6ac-79d82c1447ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33595,7 +33635,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ef9e71ab-c9e8-462d-ae77-4caf4fe61762}</x14:id>
+          <x14:id>{e63af4e6-7a95-4190-aaf4-abf480440b70}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33609,7 +33649,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0206bbd4-548a-44ec-807e-8b72c996eb39}</x14:id>
+          <x14:id>{75dc9f1e-591f-47ae-ba4f-55a7e68fe763}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33629,7 +33669,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc574895-793c-468c-9a4b-9b47499c40b1}</x14:id>
+          <x14:id>{2b2a85c7-e2c5-4257-a2c1-13b777a27cf6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33643,7 +33683,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{70737385-9184-4ccd-84dc-a6007a82000d}</x14:id>
+          <x14:id>{4ff3460f-abba-492b-86cc-b77d39e2945b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33657,7 +33697,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63c37021-5aff-4e45-b5a9-b7609d07c1b9}</x14:id>
+          <x14:id>{11017276-b99e-441e-9728-ce3f556f6d71}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33671,7 +33711,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a661b910-613e-4711-b5e7-e43abe12c0dd}</x14:id>
+          <x14:id>{21f93099-c44f-4fa1-9a46-5a09043e9e7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33685,7 +33725,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a125acd-7a71-4e8b-928e-442c9285b7ec}</x14:id>
+          <x14:id>{31ae1370-eb8a-4aae-8343-29cff01f0c5e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33699,7 +33739,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25cfda66-b324-49ec-9529-c03eb7b4fb25}</x14:id>
+          <x14:id>{f578e8ee-44e4-4878-a65b-32200dd9702d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33721,7 +33761,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ac1bb8d-2486-4076-abb5-45ca8eae14bf}</x14:id>
+          <x14:id>{7a375b69-fd58-4615-a4be-d9d3a84572d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33751,7 +33791,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1874a651-7503-4436-a7c3-87e9518c3329}</x14:id>
+          <x14:id>{ded7706f-9bb2-43f5-8c94-62268343c566}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33781,7 +33821,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1cb1ba6-c918-409e-8b72-c0d4fde0295b}</x14:id>
+          <x14:id>{61b47874-8657-4b75-b9a0-5468e8c26b02}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33811,7 +33851,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c5d148e-ba04-45b5-94a0-17f22dee51ac}</x14:id>
+          <x14:id>{f2c10536-3fc4-4d25-86e3-9aca11bbdf66}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33841,7 +33881,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc6294fb-3ff8-4395-a4e0-b222b4e2898b}</x14:id>
+          <x14:id>{d6f0f821-2a6c-44f7-b01a-c88294649a9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33871,7 +33911,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f82c9646-4784-43d6-bb32-fb631d3208d6}</x14:id>
+          <x14:id>{a12c737a-761f-4591-b8c0-fe6de653feed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33893,7 +33933,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{36eb1ea4-6c4a-471b-9811-1aab1240256c}</x14:id>
+          <x14:id>{052bccaf-b6f0-4c01-84f4-52e6cf72a0c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33915,7 +33955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a2a59885-ca86-4877-b865-52d3232bf799}</x14:id>
+          <x14:id>{f8da0ae5-4a5f-4f39-934a-31fb524f29d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33937,7 +33977,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba9aa0ec-65b8-4786-b0c7-050a71097dfc}</x14:id>
+          <x14:id>{df0c6f4f-7271-4f96-bfdd-7f32d00cefea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33959,7 +33999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e9a860a7-7f81-44a1-b7a0-066b1782a348}</x14:id>
+          <x14:id>{16270ad0-f9de-4043-8591-1326c4e53fa6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33981,7 +34021,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9608fb70-1383-450d-98c9-6fe85b7ca759}</x14:id>
+          <x14:id>{d6296762-eb1b-41b0-bf39-0e14511668a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34003,7 +34043,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f20c2ac-71f2-41c7-b3a2-550041fcbde8}</x14:id>
+          <x14:id>{5ba5dd1f-53a7-4def-9a5e-388622c0b686}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34025,7 +34065,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42da3622-6ede-44d6-8338-9d518b6b4597}</x14:id>
+          <x14:id>{7af441b7-8ded-4497-89fc-535c7357a504}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34047,7 +34087,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{517ca1c0-7bc4-4be3-baec-f680e57d4179}</x14:id>
+          <x14:id>{b5bb4aa7-a9a0-443a-8259-afdd6ec89223}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34069,7 +34109,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bb02b5a0-e953-4d15-a76a-0894b17222f7}</x14:id>
+          <x14:id>{f267439b-a7cf-4394-9727-994980329632}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34091,7 +34131,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98fe5106-7610-4771-a0f2-c236b2543861}</x14:id>
+          <x14:id>{fba51228-c19f-4d39-8a0f-760d59542292}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34113,7 +34153,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67123c92-7492-46bb-8b9a-666861d3c430}</x14:id>
+          <x14:id>{8e762ce6-e593-48cf-8fc1-583b21626a57}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34135,7 +34175,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd8bc73d-8b18-4ac6-a53e-fe0385d8162c}</x14:id>
+          <x14:id>{cb77bde3-17ca-46b7-9a72-bec511f0d1c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34157,7 +34197,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f60f1210-a173-4ba1-b8a5-66e88542044e}</x14:id>
+          <x14:id>{6d4131c6-d063-4cc7-82a0-4110884e45f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34179,7 +34219,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42b641fd-bb0f-42c9-b44b-944a9f984771}</x14:id>
+          <x14:id>{ddf713eb-5328-434b-a440-20a991248afc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34198,7 +34238,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1a9a62fa-72cf-4e2b-95b9-53a5e891e072}">
+          <x14:cfRule type="dataBar" id="{575977c0-485b-49ed-af65-530757f95155}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34211,7 +34251,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c36e5be7-f429-4753-8279-18dd4eb2ae1e}">
+          <x14:cfRule type="dataBar" id="{7b909218-2030-473f-aa31-6d49ebe4e79a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34224,7 +34264,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{186933ff-1580-436d-a46c-035c9e1f9a39}">
+          <x14:cfRule type="dataBar" id="{4618eebc-353f-4ed9-abe1-c24fa245c72b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34237,7 +34277,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bbe46629-6b15-4248-a477-39fcc91f403e}">
+          <x14:cfRule type="dataBar" id="{6421b208-6385-4726-b6ac-79d82c1447ad}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34250,7 +34290,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ef9e71ab-c9e8-462d-ae77-4caf4fe61762}">
+          <x14:cfRule type="dataBar" id="{e63af4e6-7a95-4190-aaf4-abf480440b70}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34263,7 +34303,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0206bbd4-548a-44ec-807e-8b72c996eb39}">
+          <x14:cfRule type="dataBar" id="{75dc9f1e-591f-47ae-ba4f-55a7e68fe763}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34276,7 +34316,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc574895-793c-468c-9a4b-9b47499c40b1}">
+          <x14:cfRule type="dataBar" id="{2b2a85c7-e2c5-4257-a2c1-13b777a27cf6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34289,7 +34329,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{70737385-9184-4ccd-84dc-a6007a82000d}">
+          <x14:cfRule type="dataBar" id="{4ff3460f-abba-492b-86cc-b77d39e2945b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34302,7 +34342,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{63c37021-5aff-4e45-b5a9-b7609d07c1b9}">
+          <x14:cfRule type="dataBar" id="{11017276-b99e-441e-9728-ce3f556f6d71}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34315,7 +34355,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a661b910-613e-4711-b5e7-e43abe12c0dd}">
+          <x14:cfRule type="dataBar" id="{21f93099-c44f-4fa1-9a46-5a09043e9e7a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34328,7 +34368,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5a125acd-7a71-4e8b-928e-442c9285b7ec}">
+          <x14:cfRule type="dataBar" id="{31ae1370-eb8a-4aae-8343-29cff01f0c5e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34341,7 +34381,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{25cfda66-b324-49ec-9529-c03eb7b4fb25}">
+          <x14:cfRule type="dataBar" id="{f578e8ee-44e4-4878-a65b-32200dd9702d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34354,7 +34394,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ac1bb8d-2486-4076-abb5-45ca8eae14bf}">
+          <x14:cfRule type="dataBar" id="{7a375b69-fd58-4615-a4be-d9d3a84572d0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34367,7 +34407,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1874a651-7503-4436-a7c3-87e9518c3329}">
+          <x14:cfRule type="dataBar" id="{ded7706f-9bb2-43f5-8c94-62268343c566}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34380,7 +34420,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c1cb1ba6-c918-409e-8b72-c0d4fde0295b}">
+          <x14:cfRule type="dataBar" id="{61b47874-8657-4b75-b9a0-5468e8c26b02}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34393,7 +34433,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c5d148e-ba04-45b5-94a0-17f22dee51ac}">
+          <x14:cfRule type="dataBar" id="{f2c10536-3fc4-4d25-86e3-9aca11bbdf66}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34406,7 +34446,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc6294fb-3ff8-4395-a4e0-b222b4e2898b}">
+          <x14:cfRule type="dataBar" id="{d6f0f821-2a6c-44f7-b01a-c88294649a9d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34419,7 +34459,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f82c9646-4784-43d6-bb32-fb631d3208d6}">
+          <x14:cfRule type="dataBar" id="{a12c737a-761f-4591-b8c0-fe6de653feed}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34432,7 +34472,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{36eb1ea4-6c4a-471b-9811-1aab1240256c}">
+          <x14:cfRule type="dataBar" id="{052bccaf-b6f0-4c01-84f4-52e6cf72a0c6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34445,7 +34485,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a2a59885-ca86-4877-b865-52d3232bf799}">
+          <x14:cfRule type="dataBar" id="{f8da0ae5-4a5f-4f39-934a-31fb524f29d4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34458,7 +34498,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba9aa0ec-65b8-4786-b0c7-050a71097dfc}">
+          <x14:cfRule type="dataBar" id="{df0c6f4f-7271-4f96-bfdd-7f32d00cefea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34471,7 +34511,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e9a860a7-7f81-44a1-b7a0-066b1782a348}">
+          <x14:cfRule type="dataBar" id="{16270ad0-f9de-4043-8591-1326c4e53fa6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34484,7 +34524,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9608fb70-1383-450d-98c9-6fe85b7ca759}">
+          <x14:cfRule type="dataBar" id="{d6296762-eb1b-41b0-bf39-0e14511668a4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34497,7 +34537,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5f20c2ac-71f2-41c7-b3a2-550041fcbde8}">
+          <x14:cfRule type="dataBar" id="{5ba5dd1f-53a7-4def-9a5e-388622c0b686}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34510,7 +34550,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42da3622-6ede-44d6-8338-9d518b6b4597}">
+          <x14:cfRule type="dataBar" id="{7af441b7-8ded-4497-89fc-535c7357a504}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34523,7 +34563,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{517ca1c0-7bc4-4be3-baec-f680e57d4179}">
+          <x14:cfRule type="dataBar" id="{b5bb4aa7-a9a0-443a-8259-afdd6ec89223}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34536,7 +34576,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bb02b5a0-e953-4d15-a76a-0894b17222f7}">
+          <x14:cfRule type="dataBar" id="{f267439b-a7cf-4394-9727-994980329632}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34549,7 +34589,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{98fe5106-7610-4771-a0f2-c236b2543861}">
+          <x14:cfRule type="dataBar" id="{fba51228-c19f-4d39-8a0f-760d59542292}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34562,7 +34602,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67123c92-7492-46bb-8b9a-666861d3c430}">
+          <x14:cfRule type="dataBar" id="{8e762ce6-e593-48cf-8fc1-583b21626a57}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34575,7 +34615,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd8bc73d-8b18-4ac6-a53e-fe0385d8162c}">
+          <x14:cfRule type="dataBar" id="{cb77bde3-17ca-46b7-9a72-bec511f0d1c8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34588,7 +34628,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f60f1210-a173-4ba1-b8a5-66e88542044e}">
+          <x14:cfRule type="dataBar" id="{6d4131c6-d063-4cc7-82a0-4110884e45f0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34601,7 +34641,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42b641fd-bb0f-42c9-b44b-944a9f984771}">
+          <x14:cfRule type="dataBar" id="{ddf713eb-5328-434b-a440-20a991248afc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35496,7 +35536,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>215515.08</v>
+        <v>311221.61</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -35527,7 +35567,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="7">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.242753570728009</v>
+        <v>0.350556244673086</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -35627,7 +35667,8 @@
         <v>0</v>
       </c>
       <c r="G7" s="13">
-        <v>215515.08</v>
+        <f>[3]总目标!F32+[3]总目标!F33+[3]总目标!F34+[3]总目标!F35+[3]总目标!F36</f>
+        <v>311221.61</v>
       </c>
       <c r="H7" s="13">
         <f>[3]总目标!G32+[3]总目标!G33+[3]总目标!G34+[3]总目标!G35+[3]总目标!G36</f>
@@ -35659,7 +35700,7 @@
       </c>
       <c r="O7" s="13">
         <f>SUM(C7:N7)</f>
-        <v>215515.08</v>
+        <v>311221.61</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -35685,7 +35726,7 @@
       </c>
       <c r="G8" s="14">
         <f t="shared" si="0"/>
-        <v>0.856085516734259</v>
+        <v>1.23625832965247</v>
       </c>
       <c r="H8" s="14">
         <f t="shared" si="0"/>
@@ -35717,7 +35758,7 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" si="0"/>
-        <v>0.0529164405046789</v>
+        <v>0.0764157190732796</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -36252,7 +36293,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>436243.42</v>
+        <v>593668.09</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -36283,7 +36324,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="7">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.350946724117117</v>
+        <v>0.477590862914025</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -36383,7 +36424,8 @@
         <v>0</v>
       </c>
       <c r="G7" s="13">
-        <v>436243.42</v>
+        <f>[3]总目标!F45+[3]总目标!F46+[3]总目标!F47+[3]总目标!F48+[3]总目标!F49</f>
+        <v>593668.09</v>
       </c>
       <c r="H7" s="13">
         <f>[3]总目标!G45+[3]总目标!G46+[3]总目标!G47+[3]总目标!G48+[3]总目标!G49</f>
@@ -36415,7 +36457,7 @@
       </c>
       <c r="O7" s="13">
         <f>SUM(C7:N7)</f>
-        <v>436243.42</v>
+        <v>593668.09</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -36441,7 +36483,7 @@
       </c>
       <c r="G8" s="14">
         <f t="shared" si="0"/>
-        <v>0.995242776047876</v>
+        <v>1.35439034918312</v>
       </c>
       <c r="H8" s="14">
         <f t="shared" si="0"/>
@@ -36473,7 +36515,7 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" si="0"/>
-        <v>0.0808250275362169</v>
+        <v>0.109991893337035</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -14,11 +14,12 @@
     <sheet name="林梓蕾" sheetId="6" r:id="rId5"/>
     <sheet name="陈敏华" sheetId="7" r:id="rId6"/>
     <sheet name="包家豪" sheetId="8" r:id="rId7"/>
+    <sheet name="杨皓" sheetId="9" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="42">
   <si>
     <t>2026年度WB进度</t>
   </si>
@@ -11848,6 +11849,9 @@
           <cell r="F32">
             <v>33154.43</v>
           </cell>
+          <cell r="G32">
+            <v>92959.43</v>
+          </cell>
         </row>
         <row r="33">
           <cell r="F33">
@@ -11906,6 +11910,9 @@
           <cell r="F45">
             <v>100423.98</v>
           </cell>
+          <cell r="G45">
+            <v>185876.7</v>
+          </cell>
         </row>
         <row r="46">
           <cell r="F46">
@@ -12052,6 +12059,11 @@
             <v>-1579</v>
           </cell>
         </row>
+        <row r="71">
+          <cell r="G71">
+            <v>19303.95</v>
+          </cell>
+        </row>
         <row r="72">
           <cell r="D72">
             <v>9339.48</v>
@@ -12079,6 +12091,125 @@
         <row r="75">
           <cell r="E75">
             <v>11832.22</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="B82">
+            <v>249612</v>
+          </cell>
+          <cell r="C82">
+            <v>485112.393442623</v>
+          </cell>
+          <cell r="D82">
+            <v>397534.426229508</v>
+          </cell>
+          <cell r="E82">
+            <v>391039.081967213</v>
+          </cell>
+          <cell r="F82">
+            <v>369194.754098361</v>
+          </cell>
+          <cell r="G82">
+            <v>324188.852459016</v>
+          </cell>
+          <cell r="H82">
+            <v>367365.245901639</v>
+          </cell>
+          <cell r="I82">
+            <v>355514.754098361</v>
+          </cell>
+          <cell r="J82">
+            <v>342618.098360656</v>
+          </cell>
+          <cell r="K82">
+            <v>336998.360655738</v>
+          </cell>
+          <cell r="L82">
+            <v>344526.885245902</v>
+          </cell>
+          <cell r="M82">
+            <v>252862.426229508</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="B83">
+            <v>18798.63</v>
+          </cell>
+          <cell r="C83">
+            <v>70261.4</v>
+          </cell>
+          <cell r="D83">
+            <v>115927.36</v>
+          </cell>
+          <cell r="E83">
+            <v>38311.5</v>
+          </cell>
+          <cell r="F83">
+            <v>25461.43</v>
+          </cell>
+          <cell r="G83">
+            <v>42597.61</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="B84">
+            <v>44358.75</v>
+          </cell>
+          <cell r="C84">
+            <v>135274.74</v>
+          </cell>
+          <cell r="D84">
+            <v>92048.7</v>
+          </cell>
+          <cell r="E84">
+            <v>69082.5</v>
+          </cell>
+          <cell r="F84">
+            <v>56724.2</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="B85">
+            <v>60795.74</v>
+          </cell>
+          <cell r="C85">
+            <v>138404.07</v>
+          </cell>
+          <cell r="D85">
+            <v>69267.05</v>
+          </cell>
+          <cell r="E85">
+            <v>45931.85</v>
+          </cell>
+          <cell r="F85">
+            <v>40273.32</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="B86">
+            <v>68300.77</v>
+          </cell>
+          <cell r="C86">
+            <v>117457.3</v>
+          </cell>
+          <cell r="D86">
+            <v>54071.91</v>
+          </cell>
+          <cell r="E86">
+            <v>71078.3</v>
+          </cell>
+          <cell r="F86">
+            <v>42588.76</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="B87">
+            <v>58973.86</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="E87">
+            <v>21324.35</v>
           </cell>
         </row>
       </sheetData>
@@ -21516,7 +21647,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88b12b0c-21c5-4df4-88da-c65c40584735}</x14:id>
+          <x14:id>{dbf209d6-a4f4-4f77-85fb-97d51526fa7b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21530,7 +21661,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{725a36bb-d3fe-4dbf-8f03-3037547e3825}</x14:id>
+          <x14:id>{80070bec-fb39-4f0f-a108-09b27b92b0c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21544,7 +21675,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cc5cdeda-63eb-411d-9f58-b5c893acf903}</x14:id>
+          <x14:id>{60a9916b-dbc6-48b7-a20d-af55fa30b993}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21558,7 +21689,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{079ccaf2-92ac-4256-92d2-3963354f1a9e}</x14:id>
+          <x14:id>{f5f06e3e-849a-4ac0-bf79-c85560fcb5b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21572,7 +21703,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bfb570fa-7381-4673-85f5-e707e591997f}</x14:id>
+          <x14:id>{a3a211d3-fd0d-4acd-813f-c8d84c0ab347}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21586,7 +21717,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca22ab33-094a-4d65-b3c3-613afc1b687c}</x14:id>
+          <x14:id>{20539eff-fcae-4027-b45a-e5969f19c4a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21600,7 +21731,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad02a9a4-671f-4c0c-a0ce-1c70b09a8006}</x14:id>
+          <x14:id>{62e694bf-fcda-4c99-9d20-c70c106cc266}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21614,7 +21745,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5057669-3fbb-48a1-b1bc-741b7ab6334f}</x14:id>
+          <x14:id>{f361c78b-a76e-4062-a20e-e09b5b9430f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21634,7 +21765,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7cbbab68-a81e-4287-95ff-7bbea42456a8}</x14:id>
+          <x14:id>{7953cbe0-3628-4d47-b55c-d89ac01b6ada}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21662,7 +21793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{709d95a4-9190-4099-8174-dc23a602a36b}</x14:id>
+          <x14:id>{03392e03-ef76-4cac-8cc2-8bd2186e02a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21682,7 +21813,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5308d319-886a-4674-b3c7-dbbdcada47dc}</x14:id>
+          <x14:id>{72596251-f659-407d-aea8-9c22333653e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21710,7 +21841,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b861d31b-0f33-45e1-8659-2bfef54c2fc5}</x14:id>
+          <x14:id>{4ed77bc1-6ebe-419f-ab91-81211d066800}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21730,7 +21861,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8180357-42af-4b79-b934-469a56ff223e}</x14:id>
+          <x14:id>{cfe00b54-13ed-498f-a340-b64766f30308}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21758,7 +21889,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c7bfaa0-4223-4423-855c-0dd0e07f7df1}</x14:id>
+          <x14:id>{efe330e3-c5d4-4800-b576-4b92f01160c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21778,7 +21909,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{15b9a962-c435-4a8b-9d79-6299f4732988}</x14:id>
+          <x14:id>{4da3bddb-17f8-45df-8238-3e75ead1150a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21806,7 +21937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8eb6e413-7d2c-4ac8-9ed8-63f58d8c4d2e}</x14:id>
+          <x14:id>{605932a6-4ea5-4437-a9aa-2e0f8245af6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21826,7 +21957,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60ad2c9a-0217-47b5-8646-07e24232958f}</x14:id>
+          <x14:id>{c043b345-00bf-476b-be5c-f21d1b0ab1f3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21854,7 +21985,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4ca01bc-de44-47c5-8f43-6014b94165e1}</x14:id>
+          <x14:id>{4d0eaca1-7dc7-4975-b1b3-9fbcc931ee21}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21916,7 +22047,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{07c2d317-467c-4c5e-ac92-e12be1758d50}</x14:id>
+          <x14:id>{7a0ba572-8b2d-4d03-8b3f-4f83a68bf685}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21946,7 +22077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd6f502e-19cb-4296-a392-4a010db1affd}</x14:id>
+          <x14:id>{4d643ec0-e58d-43aa-8dc0-ca463afd490e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21968,7 +22099,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce9ce528-2b87-4ba5-9de1-245cf9deee39}</x14:id>
+          <x14:id>{cb91be6a-1d6c-44cd-9a03-1943ff680277}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21988,7 +22119,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{624283ac-b55c-4212-ac1d-deebee0e7cd7}</x14:id>
+          <x14:id>{080e71bc-3398-4480-9ffe-6a78811f5373}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22010,7 +22141,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{445ca9c5-33e9-46e7-bc24-56721ea4cb55}</x14:id>
+          <x14:id>{41008630-0e1e-41dc-b668-23396018b06f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22030,7 +22161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7679a1a-bad2-4423-8055-e46f8371d6fa}</x14:id>
+          <x14:id>{0586850a-67cc-4bb2-a3a8-150e75dfcefe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22052,7 +22183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba036439-0698-4db3-a7e5-968317b6af2b}</x14:id>
+          <x14:id>{67f8ca3f-ece6-43bd-b76e-4edf153c8875}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22072,7 +22203,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a5ec903-1f95-477e-a46c-796640926a9d}</x14:id>
+          <x14:id>{36d20ec0-5fb4-4490-9371-84d7a2fdaa37}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22094,7 +22225,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{052df7c0-65d6-4152-a290-8d9fecfbc6af}</x14:id>
+          <x14:id>{b9319dd8-ee60-45e1-9365-06cb21f1a46e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22114,7 +22245,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cd1f65d2-ad6c-4f8f-97ca-0fafabc44375}</x14:id>
+          <x14:id>{b8dea84b-72d0-45f0-83f3-87601a6351ca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22142,7 +22273,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12f10c76-45dc-4515-930a-5ef78249dd08}</x14:id>
+          <x14:id>{75dbae2d-55d5-4513-9158-95afcbb1b0d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22156,7 +22287,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{727859f5-4f69-4323-947b-078ba85e2952}</x14:id>
+          <x14:id>{3a30091e-81d0-4fc6-a7df-821190afb03f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22186,7 +22317,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d482a274-eca3-404a-a26a-091bcaa9fdcc}</x14:id>
+          <x14:id>{25c9008f-4b7f-4fe4-b464-4c4a32c57c27}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22208,7 +22339,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{184366a0-76d8-444e-8d28-7f6e139c3beb}</x14:id>
+          <x14:id>{8a01ae5f-6083-4100-8018-e3793bcef53a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22230,7 +22361,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{572fffe6-d08f-44b0-8300-da8dfe6918a7}</x14:id>
+          <x14:id>{26e19870-1d55-4e17-909e-6f4f493a417c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22252,7 +22383,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8de6f208-0689-44aa-a52a-4caf9b6eeaeb}</x14:id>
+          <x14:id>{3f1ada4d-e02c-483f-a956-6091bc11237b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22274,7 +22405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0895ba25-34d7-4244-a406-7dc512c50cbd}</x14:id>
+          <x14:id>{6e0d9983-90e4-4f5c-834b-f37cf2ac2038}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22296,7 +22427,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8925427e-3d9b-47b0-b03a-451a15829b1a}</x14:id>
+          <x14:id>{efbdb3ab-2fdb-4f8d-8e57-cf47d91dad21}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22318,7 +22449,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fca8f4e1-8056-4c84-93ef-fd57d609d1ec}</x14:id>
+          <x14:id>{4b1fc2f7-0c26-4ae6-aac3-60163801b541}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22340,7 +22471,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32d36661-12a6-42ef-8eb3-88798e5ab38b}</x14:id>
+          <x14:id>{cc0b9c4c-fc6b-490c-a1ac-1d4d46467c17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22362,7 +22493,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3f6eb41d-fd17-423c-947f-7f981954a5ee}</x14:id>
+          <x14:id>{5faf52e4-dc52-4065-ba90-677708be5b1e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22384,7 +22515,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa367d15-ecc2-4968-8a0a-7e526023b4bf}</x14:id>
+          <x14:id>{b332d3ee-772a-4b1b-bf1c-0a502106379b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22406,7 +22537,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38a199a3-b79e-4269-bd50-b1685c03f727}</x14:id>
+          <x14:id>{c99cecc1-37ec-4f47-a352-c3516d48db0a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22428,7 +22559,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bc4d0482-7dcd-4943-9ac1-95dd2fc3e5ea}</x14:id>
+          <x14:id>{0bb21f6d-60c9-4ee7-b810-c733c17f995d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22450,7 +22581,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d644e01-6cec-4bf9-a7e4-51b92966fd40}</x14:id>
+          <x14:id>{6102d7c0-9dc1-4b3c-bc55-96b640e2d9b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22469,7 +22600,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{88b12b0c-21c5-4df4-88da-c65c40584735}">
+          <x14:cfRule type="dataBar" id="{dbf209d6-a4f4-4f77-85fb-97d51526fa7b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22482,7 +22613,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{725a36bb-d3fe-4dbf-8f03-3037547e3825}">
+          <x14:cfRule type="dataBar" id="{80070bec-fb39-4f0f-a108-09b27b92b0c2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22495,7 +22626,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cc5cdeda-63eb-411d-9f58-b5c893acf903}">
+          <x14:cfRule type="dataBar" id="{60a9916b-dbc6-48b7-a20d-af55fa30b993}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22508,7 +22639,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{079ccaf2-92ac-4256-92d2-3963354f1a9e}">
+          <x14:cfRule type="dataBar" id="{f5f06e3e-849a-4ac0-bf79-c85560fcb5b9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22521,7 +22652,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bfb570fa-7381-4673-85f5-e707e591997f}">
+          <x14:cfRule type="dataBar" id="{a3a211d3-fd0d-4acd-813f-c8d84c0ab347}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22534,7 +22665,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ca22ab33-094a-4d65-b3c3-613afc1b687c}">
+          <x14:cfRule type="dataBar" id="{20539eff-fcae-4027-b45a-e5969f19c4a7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22547,7 +22678,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ad02a9a4-671f-4c0c-a0ce-1c70b09a8006}">
+          <x14:cfRule type="dataBar" id="{62e694bf-fcda-4c99-9d20-c70c106cc266}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22560,7 +22691,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e5057669-3fbb-48a1-b1bc-741b7ab6334f}">
+          <x14:cfRule type="dataBar" id="{f361c78b-a76e-4062-a20e-e09b5b9430f1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22573,7 +22704,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7cbbab68-a81e-4287-95ff-7bbea42456a8}">
+          <x14:cfRule type="dataBar" id="{7953cbe0-3628-4d47-b55c-d89ac01b6ada}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22586,7 +22717,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{709d95a4-9190-4099-8174-dc23a602a36b}">
+          <x14:cfRule type="dataBar" id="{03392e03-ef76-4cac-8cc2-8bd2186e02a1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22599,7 +22730,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5308d319-886a-4674-b3c7-dbbdcada47dc}">
+          <x14:cfRule type="dataBar" id="{72596251-f659-407d-aea8-9c22333653e0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22612,7 +22743,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b861d31b-0f33-45e1-8659-2bfef54c2fc5}">
+          <x14:cfRule type="dataBar" id="{4ed77bc1-6ebe-419f-ab91-81211d066800}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22625,7 +22756,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c8180357-42af-4b79-b934-469a56ff223e}">
+          <x14:cfRule type="dataBar" id="{cfe00b54-13ed-498f-a340-b64766f30308}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22638,7 +22769,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c7bfaa0-4223-4423-855c-0dd0e07f7df1}">
+          <x14:cfRule type="dataBar" id="{efe330e3-c5d4-4800-b576-4b92f01160c3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22651,7 +22782,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{15b9a962-c435-4a8b-9d79-6299f4732988}">
+          <x14:cfRule type="dataBar" id="{4da3bddb-17f8-45df-8238-3e75ead1150a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22664,7 +22795,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8eb6e413-7d2c-4ac8-9ed8-63f58d8c4d2e}">
+          <x14:cfRule type="dataBar" id="{605932a6-4ea5-4437-a9aa-2e0f8245af6c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22677,7 +22808,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{60ad2c9a-0217-47b5-8646-07e24232958f}">
+          <x14:cfRule type="dataBar" id="{c043b345-00bf-476b-be5c-f21d1b0ab1f3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22690,7 +22821,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d4ca01bc-de44-47c5-8f43-6014b94165e1}">
+          <x14:cfRule type="dataBar" id="{4d0eaca1-7dc7-4975-b1b3-9fbcc931ee21}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22703,7 +22834,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{07c2d317-467c-4c5e-ac92-e12be1758d50}">
+          <x14:cfRule type="dataBar" id="{7a0ba572-8b2d-4d03-8b3f-4f83a68bf685}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22716,7 +22847,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd6f502e-19cb-4296-a392-4a010db1affd}">
+          <x14:cfRule type="dataBar" id="{4d643ec0-e58d-43aa-8dc0-ca463afd490e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22729,7 +22860,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce9ce528-2b87-4ba5-9de1-245cf9deee39}">
+          <x14:cfRule type="dataBar" id="{cb91be6a-1d6c-44cd-9a03-1943ff680277}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22742,7 +22873,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{624283ac-b55c-4212-ac1d-deebee0e7cd7}">
+          <x14:cfRule type="dataBar" id="{080e71bc-3398-4480-9ffe-6a78811f5373}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22755,7 +22886,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{445ca9c5-33e9-46e7-bc24-56721ea4cb55}">
+          <x14:cfRule type="dataBar" id="{41008630-0e1e-41dc-b668-23396018b06f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22768,7 +22899,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a7679a1a-bad2-4423-8055-e46f8371d6fa}">
+          <x14:cfRule type="dataBar" id="{0586850a-67cc-4bb2-a3a8-150e75dfcefe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22781,7 +22912,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba036439-0698-4db3-a7e5-968317b6af2b}">
+          <x14:cfRule type="dataBar" id="{67f8ca3f-ece6-43bd-b76e-4edf153c8875}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22794,7 +22925,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a5ec903-1f95-477e-a46c-796640926a9d}">
+          <x14:cfRule type="dataBar" id="{36d20ec0-5fb4-4490-9371-84d7a2fdaa37}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22807,7 +22938,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{052df7c0-65d6-4152-a290-8d9fecfbc6af}">
+          <x14:cfRule type="dataBar" id="{b9319dd8-ee60-45e1-9365-06cb21f1a46e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22820,7 +22951,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cd1f65d2-ad6c-4f8f-97ca-0fafabc44375}">
+          <x14:cfRule type="dataBar" id="{b8dea84b-72d0-45f0-83f3-87601a6351ca}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22833,7 +22964,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{12f10c76-45dc-4515-930a-5ef78249dd08}">
+          <x14:cfRule type="dataBar" id="{75dbae2d-55d5-4513-9158-95afcbb1b0d6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22846,7 +22977,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{727859f5-4f69-4323-947b-078ba85e2952}">
+          <x14:cfRule type="dataBar" id="{3a30091e-81d0-4fc6-a7df-821190afb03f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22859,7 +22990,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d482a274-eca3-404a-a26a-091bcaa9fdcc}">
+          <x14:cfRule type="dataBar" id="{25c9008f-4b7f-4fe4-b464-4c4a32c57c27}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22872,7 +23003,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{184366a0-76d8-444e-8d28-7f6e139c3beb}">
+          <x14:cfRule type="dataBar" id="{8a01ae5f-6083-4100-8018-e3793bcef53a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22885,7 +23016,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{572fffe6-d08f-44b0-8300-da8dfe6918a7}">
+          <x14:cfRule type="dataBar" id="{26e19870-1d55-4e17-909e-6f4f493a417c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22898,7 +23029,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8de6f208-0689-44aa-a52a-4caf9b6eeaeb}">
+          <x14:cfRule type="dataBar" id="{3f1ada4d-e02c-483f-a956-6091bc11237b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22911,7 +23042,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0895ba25-34d7-4244-a406-7dc512c50cbd}">
+          <x14:cfRule type="dataBar" id="{6e0d9983-90e4-4f5c-834b-f37cf2ac2038}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22924,7 +23055,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8925427e-3d9b-47b0-b03a-451a15829b1a}">
+          <x14:cfRule type="dataBar" id="{efbdb3ab-2fdb-4f8d-8e57-cf47d91dad21}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22937,7 +23068,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fca8f4e1-8056-4c84-93ef-fd57d609d1ec}">
+          <x14:cfRule type="dataBar" id="{4b1fc2f7-0c26-4ae6-aac3-60163801b541}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22950,7 +23081,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32d36661-12a6-42ef-8eb3-88798e5ab38b}">
+          <x14:cfRule type="dataBar" id="{cc0b9c4c-fc6b-490c-a1ac-1d4d46467c17}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22963,7 +23094,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3f6eb41d-fd17-423c-947f-7f981954a5ee}">
+          <x14:cfRule type="dataBar" id="{5faf52e4-dc52-4065-ba90-677708be5b1e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22976,7 +23107,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa367d15-ecc2-4968-8a0a-7e526023b4bf}">
+          <x14:cfRule type="dataBar" id="{b332d3ee-772a-4b1b-bf1c-0a502106379b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22989,7 +23120,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38a199a3-b79e-4269-bd50-b1685c03f727}">
+          <x14:cfRule type="dataBar" id="{c99cecc1-37ec-4f47-a352-c3516d48db0a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23002,7 +23133,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bc4d0482-7dcd-4943-9ac1-95dd2fc3e5ea}">
+          <x14:cfRule type="dataBar" id="{0bb21f6d-60c9-4ee7-b810-c733c17f995d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23015,7 +23146,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2d644e01-6cec-4bf9-a7e4-51b92966fd40}">
+          <x14:cfRule type="dataBar" id="{6102d7c0-9dc1-4b3c-bc55-96b640e2d9b9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -33579,7 +33710,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{575977c0-485b-49ed-af65-530757f95155}</x14:id>
+          <x14:id>{7124a651-0157-459a-9e6a-1ba4452143cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33593,7 +33724,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7b909218-2030-473f-aa31-6d49ebe4e79a}</x14:id>
+          <x14:id>{4c703241-81f0-47f2-81ae-d461faa58e4e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33607,7 +33738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4618eebc-353f-4ed9-abe1-c24fa245c72b}</x14:id>
+          <x14:id>{3b07c1b0-a25e-44f4-9d6f-f340c65c198f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33621,7 +33752,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6421b208-6385-4726-b6ac-79d82c1447ad}</x14:id>
+          <x14:id>{6de6c300-3678-4031-a1c2-f078cfdb2670}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33635,7 +33766,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e63af4e6-7a95-4190-aaf4-abf480440b70}</x14:id>
+          <x14:id>{d1ffff48-79b6-49e6-bb97-f330edccfa4b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33649,7 +33780,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75dc9f1e-591f-47ae-ba4f-55a7e68fe763}</x14:id>
+          <x14:id>{4a7c7e8a-8a4a-4d92-9d10-3be28d6e749c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33669,7 +33800,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b2a85c7-e2c5-4257-a2c1-13b777a27cf6}</x14:id>
+          <x14:id>{889e5926-3ddd-454d-aed4-d09c16d744d9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33683,7 +33814,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ff3460f-abba-492b-86cc-b77d39e2945b}</x14:id>
+          <x14:id>{a2376cf5-01f0-43a7-96a4-67114b5fba16}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33697,7 +33828,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11017276-b99e-441e-9728-ce3f556f6d71}</x14:id>
+          <x14:id>{ee304a73-7cbc-4e5d-9409-7ff1aa3e00e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33711,7 +33842,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{21f93099-c44f-4fa1-9a46-5a09043e9e7a}</x14:id>
+          <x14:id>{c6aeeb44-80d7-48d7-9ffd-3c8b1ecb3905}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33725,7 +33856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31ae1370-eb8a-4aae-8343-29cff01f0c5e}</x14:id>
+          <x14:id>{38613a61-5887-4b0a-98f4-f99a7c217d1a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33739,7 +33870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f578e8ee-44e4-4878-a65b-32200dd9702d}</x14:id>
+          <x14:id>{6cd7c06d-f711-4e5d-9924-2199b681cf97}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33761,7 +33892,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a375b69-fd58-4615-a4be-d9d3a84572d0}</x14:id>
+          <x14:id>{458bed35-84d8-4cb8-a390-2836c61d457e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33791,7 +33922,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ded7706f-9bb2-43f5-8c94-62268343c566}</x14:id>
+          <x14:id>{14e187db-b84d-462f-9005-dec2ee964551}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33821,7 +33952,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61b47874-8657-4b75-b9a0-5468e8c26b02}</x14:id>
+          <x14:id>{4a6151bd-1a83-44f1-b173-c1084e77113e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33851,7 +33982,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f2c10536-3fc4-4d25-86e3-9aca11bbdf66}</x14:id>
+          <x14:id>{99f5d465-b29a-4073-a346-b66b1f7838fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33881,7 +34012,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6f0f821-2a6c-44f7-b01a-c88294649a9d}</x14:id>
+          <x14:id>{ac6a121b-f5cb-42a6-8818-de89bbe807bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33911,7 +34042,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a12c737a-761f-4591-b8c0-fe6de653feed}</x14:id>
+          <x14:id>{297e59c6-369f-4ce3-a5e8-1d1c43074593}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33933,7 +34064,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{052bccaf-b6f0-4c01-84f4-52e6cf72a0c6}</x14:id>
+          <x14:id>{247356c1-d4b8-417a-9a45-63af7874bd89}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33955,7 +34086,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8da0ae5-4a5f-4f39-934a-31fb524f29d4}</x14:id>
+          <x14:id>{e057ea98-c8ef-4641-9379-c00c423c66f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33977,7 +34108,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{df0c6f4f-7271-4f96-bfdd-7f32d00cefea}</x14:id>
+          <x14:id>{c656014a-0790-494a-b4f1-1cb7a323b2b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33999,7 +34130,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16270ad0-f9de-4043-8591-1326c4e53fa6}</x14:id>
+          <x14:id>{de7bed76-92cf-4d03-a83a-631ebfd57aff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34021,7 +34152,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6296762-eb1b-41b0-bf39-0e14511668a4}</x14:id>
+          <x14:id>{1c3defc8-2124-4b49-ba34-6c7337f5de97}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34043,7 +34174,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5ba5dd1f-53a7-4def-9a5e-388622c0b686}</x14:id>
+          <x14:id>{a36d024f-4965-47a6-b7b7-8ab724fae106}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34065,7 +34196,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7af441b7-8ded-4497-89fc-535c7357a504}</x14:id>
+          <x14:id>{71e8d685-bf1b-47cb-877a-afceca85a201}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34087,7 +34218,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5bb4aa7-a9a0-443a-8259-afdd6ec89223}</x14:id>
+          <x14:id>{878d29c9-8af7-4ea4-9eb1-e09ad7f35fdf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34109,7 +34240,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f267439b-a7cf-4394-9727-994980329632}</x14:id>
+          <x14:id>{7862722d-dfcf-4b74-b996-94a142807632}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34131,7 +34262,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fba51228-c19f-4d39-8a0f-760d59542292}</x14:id>
+          <x14:id>{e165a39d-fa5b-4b33-8939-d03a201edab1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34153,7 +34284,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e762ce6-e593-48cf-8fc1-583b21626a57}</x14:id>
+          <x14:id>{7e977de6-5ef0-45b9-a3a3-f36d0a6c2477}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34175,7 +34306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb77bde3-17ca-46b7-9a72-bec511f0d1c8}</x14:id>
+          <x14:id>{6ad30ffb-405b-4890-b57e-842079969af8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34197,7 +34328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d4131c6-d063-4cc7-82a0-4110884e45f0}</x14:id>
+          <x14:id>{a5caa7ea-bb57-416b-a34c-8b4f50c219fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34219,7 +34350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ddf713eb-5328-434b-a440-20a991248afc}</x14:id>
+          <x14:id>{b7e24500-1439-4966-b503-435f1cefc1c9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34238,7 +34369,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{575977c0-485b-49ed-af65-530757f95155}">
+          <x14:cfRule type="dataBar" id="{7124a651-0157-459a-9e6a-1ba4452143cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34251,7 +34382,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7b909218-2030-473f-aa31-6d49ebe4e79a}">
+          <x14:cfRule type="dataBar" id="{4c703241-81f0-47f2-81ae-d461faa58e4e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34264,7 +34395,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4618eebc-353f-4ed9-abe1-c24fa245c72b}">
+          <x14:cfRule type="dataBar" id="{3b07c1b0-a25e-44f4-9d6f-f340c65c198f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34277,7 +34408,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6421b208-6385-4726-b6ac-79d82c1447ad}">
+          <x14:cfRule type="dataBar" id="{6de6c300-3678-4031-a1c2-f078cfdb2670}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34290,7 +34421,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e63af4e6-7a95-4190-aaf4-abf480440b70}">
+          <x14:cfRule type="dataBar" id="{d1ffff48-79b6-49e6-bb97-f330edccfa4b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34303,7 +34434,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75dc9f1e-591f-47ae-ba4f-55a7e68fe763}">
+          <x14:cfRule type="dataBar" id="{4a7c7e8a-8a4a-4d92-9d10-3be28d6e749c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34316,7 +34447,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2b2a85c7-e2c5-4257-a2c1-13b777a27cf6}">
+          <x14:cfRule type="dataBar" id="{889e5926-3ddd-454d-aed4-d09c16d744d9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34329,7 +34460,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ff3460f-abba-492b-86cc-b77d39e2945b}">
+          <x14:cfRule type="dataBar" id="{a2376cf5-01f0-43a7-96a4-67114b5fba16}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34342,7 +34473,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11017276-b99e-441e-9728-ce3f556f6d71}">
+          <x14:cfRule type="dataBar" id="{ee304a73-7cbc-4e5d-9409-7ff1aa3e00e7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34355,7 +34486,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{21f93099-c44f-4fa1-9a46-5a09043e9e7a}">
+          <x14:cfRule type="dataBar" id="{c6aeeb44-80d7-48d7-9ffd-3c8b1ecb3905}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34368,7 +34499,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{31ae1370-eb8a-4aae-8343-29cff01f0c5e}">
+          <x14:cfRule type="dataBar" id="{38613a61-5887-4b0a-98f4-f99a7c217d1a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34381,7 +34512,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f578e8ee-44e4-4878-a65b-32200dd9702d}">
+          <x14:cfRule type="dataBar" id="{6cd7c06d-f711-4e5d-9924-2199b681cf97}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34394,7 +34525,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7a375b69-fd58-4615-a4be-d9d3a84572d0}">
+          <x14:cfRule type="dataBar" id="{458bed35-84d8-4cb8-a390-2836c61d457e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34407,7 +34538,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ded7706f-9bb2-43f5-8c94-62268343c566}">
+          <x14:cfRule type="dataBar" id="{14e187db-b84d-462f-9005-dec2ee964551}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34420,7 +34551,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{61b47874-8657-4b75-b9a0-5468e8c26b02}">
+          <x14:cfRule type="dataBar" id="{4a6151bd-1a83-44f1-b173-c1084e77113e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34433,7 +34564,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f2c10536-3fc4-4d25-86e3-9aca11bbdf66}">
+          <x14:cfRule type="dataBar" id="{99f5d465-b29a-4073-a346-b66b1f7838fc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34446,7 +34577,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6f0f821-2a6c-44f7-b01a-c88294649a9d}">
+          <x14:cfRule type="dataBar" id="{ac6a121b-f5cb-42a6-8818-de89bbe807bc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34459,7 +34590,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a12c737a-761f-4591-b8c0-fe6de653feed}">
+          <x14:cfRule type="dataBar" id="{297e59c6-369f-4ce3-a5e8-1d1c43074593}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34472,7 +34603,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{052bccaf-b6f0-4c01-84f4-52e6cf72a0c6}">
+          <x14:cfRule type="dataBar" id="{247356c1-d4b8-417a-9a45-63af7874bd89}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34485,7 +34616,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f8da0ae5-4a5f-4f39-934a-31fb524f29d4}">
+          <x14:cfRule type="dataBar" id="{e057ea98-c8ef-4641-9379-c00c423c66f1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34498,7 +34629,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{df0c6f4f-7271-4f96-bfdd-7f32d00cefea}">
+          <x14:cfRule type="dataBar" id="{c656014a-0790-494a-b4f1-1cb7a323b2b1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34511,7 +34642,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16270ad0-f9de-4043-8591-1326c4e53fa6}">
+          <x14:cfRule type="dataBar" id="{de7bed76-92cf-4d03-a83a-631ebfd57aff}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34524,7 +34655,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6296762-eb1b-41b0-bf39-0e14511668a4}">
+          <x14:cfRule type="dataBar" id="{1c3defc8-2124-4b49-ba34-6c7337f5de97}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34537,7 +34668,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5ba5dd1f-53a7-4def-9a5e-388622c0b686}">
+          <x14:cfRule type="dataBar" id="{a36d024f-4965-47a6-b7b7-8ab724fae106}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34550,7 +34681,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7af441b7-8ded-4497-89fc-535c7357a504}">
+          <x14:cfRule type="dataBar" id="{71e8d685-bf1b-47cb-877a-afceca85a201}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34563,7 +34694,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b5bb4aa7-a9a0-443a-8259-afdd6ec89223}">
+          <x14:cfRule type="dataBar" id="{878d29c9-8af7-4ea4-9eb1-e09ad7f35fdf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34576,7 +34707,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f267439b-a7cf-4394-9727-994980329632}">
+          <x14:cfRule type="dataBar" id="{7862722d-dfcf-4b74-b996-94a142807632}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34589,7 +34720,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fba51228-c19f-4d39-8a0f-760d59542292}">
+          <x14:cfRule type="dataBar" id="{e165a39d-fa5b-4b33-8939-d03a201edab1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34602,7 +34733,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e762ce6-e593-48cf-8fc1-583b21626a57}">
+          <x14:cfRule type="dataBar" id="{7e977de6-5ef0-45b9-a3a3-f36d0a6c2477}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34615,7 +34746,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cb77bde3-17ca-46b7-9a72-bec511f0d1c8}">
+          <x14:cfRule type="dataBar" id="{6ad30ffb-405b-4890-b57e-842079969af8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34628,7 +34759,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d4131c6-d063-4cc7-82a0-4110884e45f0}">
+          <x14:cfRule type="dataBar" id="{a5caa7ea-bb57-416b-a34c-8b4f50c219fe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34641,7 +34772,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ddf713eb-5328-434b-a440-20a991248afc}">
+          <x14:cfRule type="dataBar" id="{b7e24500-1439-4966-b503-435f1cefc1c9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -35426,7 +35557,8 @@
     <col min="3" max="3" width="12.2222222222222" customWidth="1"/>
     <col min="4" max="4" width="17.4444444444444" customWidth="1"/>
     <col min="5" max="7" width="15.5555555555556" customWidth="1"/>
-    <col min="8" max="14" width="12.2222222222222" customWidth="1"/>
+    <col min="8" max="8" width="14.5555555555556" customWidth="1"/>
+    <col min="9" max="14" width="12.2222222222222" customWidth="1"/>
     <col min="15" max="15" width="17.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
@@ -35536,7 +35668,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>311221.61</v>
+        <v>404181.04</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -35567,7 +35699,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="7">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.350556244673086</v>
+        <v>0.455264618515605</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -35672,7 +35804,7 @@
       </c>
       <c r="H7" s="13">
         <f>[3]总目标!G32+[3]总目标!G33+[3]总目标!G34+[3]总目标!G35+[3]总目标!G36</f>
-        <v>0</v>
+        <v>92959.43</v>
       </c>
       <c r="I7" s="13">
         <f>[3]总目标!H32+[3]总目标!H33+[3]总目标!H34+[3]总目标!H35+[3]总目标!H36</f>
@@ -35700,7 +35832,7 @@
       </c>
       <c r="O7" s="13">
         <f>SUM(C7:N7)</f>
-        <v>311221.61</v>
+        <v>404181.04</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -35730,7 +35862,7 @@
       </c>
       <c r="H8" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27030985962088</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" si="0"/>
@@ -35758,7 +35890,7 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" si="0"/>
-        <v>0.0764157190732796</v>
+        <v>0.0992404891401532</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -36183,7 +36315,8 @@
     <col min="3" max="3" width="12.2222222222222" customWidth="1"/>
     <col min="4" max="4" width="17.4444444444444" customWidth="1"/>
     <col min="5" max="7" width="15.5555555555556" customWidth="1"/>
-    <col min="8" max="14" width="12.2222222222222" customWidth="1"/>
+    <col min="8" max="8" width="16.4444444444444" customWidth="1"/>
+    <col min="9" max="14" width="12.2222222222222" customWidth="1"/>
     <col min="15" max="15" width="17.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
@@ -36293,7 +36426,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>593668.09</v>
+        <v>779544.79</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -36324,7 +36457,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="7">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.477590862914025</v>
+        <v>0.627123935423635</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -36429,7 +36562,7 @@
       </c>
       <c r="H7" s="13">
         <f>[3]总目标!G45+[3]总目标!G46+[3]总目标!G47+[3]总目标!G48+[3]总目标!G49</f>
-        <v>0</v>
+        <v>185876.7</v>
       </c>
       <c r="I7" s="13">
         <f>[3]总目标!H45+[3]总目标!H46+[3]总目标!H47+[3]总目标!H48+[3]总目标!H49</f>
@@ -36457,7 +36590,7 @@
       </c>
       <c r="O7" s="13">
         <f>SUM(C7:N7)</f>
-        <v>593668.09</v>
+        <v>779544.79</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -36487,7 +36620,7 @@
       </c>
       <c r="H8" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.49353176407479</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" si="0"/>
@@ -36515,7 +36648,7 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" si="0"/>
-        <v>0.109991893337035</v>
+        <v>0.144430210815476</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -37696,7 +37829,8 @@
     <col min="3" max="3" width="15.5555555555556" customWidth="1"/>
     <col min="4" max="4" width="17.4444444444444" customWidth="1"/>
     <col min="5" max="7" width="15.5555555555556" customWidth="1"/>
-    <col min="8" max="14" width="12.2222222222222" customWidth="1"/>
+    <col min="8" max="8" width="14.4444444444444" customWidth="1"/>
+    <col min="9" max="14" width="12.2222222222222" customWidth="1"/>
     <col min="15" max="15" width="17.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
@@ -37806,7 +37940,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>71602.76</v>
+        <v>90906.71</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -37837,7 +37971,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="7">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.1454620984829</v>
+        <v>0.184678367185517</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -37941,7 +38075,7 @@
       </c>
       <c r="H7" s="13">
         <f>[3]总目标!G71+[3]总目标!G72+[3]总目标!G73+[3]总目标!G74+[3]总目标!G75</f>
-        <v>0</v>
+        <v>19303.95</v>
       </c>
       <c r="I7" s="13">
         <f>[3]总目标!H71+[3]总目标!H72+[3]总目标!H73+[3]总目标!H74+[3]总目标!H75</f>
@@ -37969,7 +38103,7 @@
       </c>
       <c r="O7" s="13">
         <f>SUM(C7:N7)</f>
-        <v>138223.54</v>
+        <v>157527.49</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -37999,7 +38133,7 @@
       </c>
       <c r="H8" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.12398716921414</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" si="0"/>
@@ -38027,7 +38161,758 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" si="0"/>
-        <v>0.0749532029332386</v>
+        <v>0.0854209776824824</v>
+      </c>
+    </row>
+    <row r="9" ht="15.6" spans="1:15">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="30"/>
+    </row>
+    <row r="10" ht="15.6" spans="1:15">
+      <c r="A10" s="11"/>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="31"/>
+    </row>
+    <row r="11" ht="15.6" spans="1:15">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:15">
+      <c r="A12" s="11"/>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+    </row>
+    <row r="13" ht="15.6" spans="1:15">
+      <c r="A13" s="11"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="30"/>
+    </row>
+    <row r="14" ht="15.6" spans="1:15">
+      <c r="A14" s="11"/>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="32"/>
+    </row>
+    <row r="15" ht="15.6" spans="1:15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+    </row>
+    <row r="16" ht="15.6" spans="1:15">
+      <c r="A16" s="11"/>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+    </row>
+    <row r="17" ht="15.6" spans="1:15">
+      <c r="A17" s="11"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="30"/>
+    </row>
+    <row r="18" ht="15.6" spans="1:15">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="33"/>
+    </row>
+    <row r="19" ht="15.6" spans="1:15">
+      <c r="A19" s="19"/>
+      <c r="B19" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+    </row>
+    <row r="20" ht="15.6" spans="1:15">
+      <c r="A20" s="11"/>
+      <c r="B20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+    </row>
+    <row r="21" ht="15.6" spans="1:15">
+      <c r="A21" s="11"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="30"/>
+    </row>
+    <row r="22" ht="15.6" spans="1:15">
+      <c r="A22" s="11"/>
+      <c r="B22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="29"/>
+    </row>
+    <row r="23" ht="15.6" spans="1:15">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="13"/>
+    </row>
+    <row r="24" ht="15.6" spans="1:15">
+      <c r="A24" s="11"/>
+      <c r="B24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+    </row>
+    <row r="25" ht="15.6" spans="1:15">
+      <c r="A25" s="11"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="30"/>
+    </row>
+    <row r="26" ht="15.6" spans="1:15">
+      <c r="A26" s="11"/>
+      <c r="B26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+    </row>
+    <row r="27" ht="15.6" spans="1:15">
+      <c r="A27" s="11"/>
+      <c r="B27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+    </row>
+    <row r="28" ht="15.6" spans="1:15">
+      <c r="A28" s="11"/>
+      <c r="B28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+    </row>
+    <row r="29" ht="15.6" spans="1:15">
+      <c r="A29" s="24"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A29"/>
+    <mergeCell ref="O2:O5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O29"/>
+  <sheetFormatPr defaultColWidth="16.4444444444444" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="16384" width="16.4444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.6" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" ht="15.6" spans="1:15">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="15.6" spans="1:15">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" ht="15.6" spans="1:15">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4">
+        <f>(C7+D7+E7)</f>
+        <v>1043940.28</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3">
+        <f>(F7+G7+H7)</f>
+        <v>453373.82</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="25">
+        <f>(I7+J7+K7)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="26">
+        <f>(L7+M7+N7)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" ht="15.6" spans="1:15">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="6">
+        <f>(C7+D7+E7)/(C6+D6+E6)</f>
+        <v>0.921997922968085</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7">
+        <f>(F7+G7+H7)/(F6+G6+H6)</f>
+        <v>0.418078508313799</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="27">
+        <f>(I7+J7+K7)/(I6+J6+K6)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="28">
+        <f>(L7+M7+N7)/(L6+M6+N6)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" ht="31.2" spans="1:15">
+      <c r="A6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="10">
+        <f>[3]总目标!B82</f>
+        <v>249612</v>
+      </c>
+      <c r="D6" s="10">
+        <f>[3]总目标!C82</f>
+        <v>485112.393442623</v>
+      </c>
+      <c r="E6" s="10">
+        <f>[3]总目标!D82</f>
+        <v>397534.426229508</v>
+      </c>
+      <c r="F6" s="10">
+        <f>[3]总目标!E82</f>
+        <v>391039.081967213</v>
+      </c>
+      <c r="G6" s="10">
+        <f>[3]总目标!F82</f>
+        <v>369194.754098361</v>
+      </c>
+      <c r="H6" s="10">
+        <f>[3]总目标!G82</f>
+        <v>324188.852459016</v>
+      </c>
+      <c r="I6" s="10">
+        <f>[3]总目标!H82</f>
+        <v>367365.245901639</v>
+      </c>
+      <c r="J6" s="10">
+        <f>[3]总目标!I82</f>
+        <v>355514.754098361</v>
+      </c>
+      <c r="K6" s="10">
+        <f>[3]总目标!J82</f>
+        <v>342618.098360656</v>
+      </c>
+      <c r="L6" s="10">
+        <f>[3]总目标!K82</f>
+        <v>336998.360655738</v>
+      </c>
+      <c r="M6" s="10">
+        <f>[3]总目标!L82</f>
+        <v>344526.885245902</v>
+      </c>
+      <c r="N6" s="10">
+        <f>[3]总目标!M82</f>
+        <v>252862.426229508</v>
+      </c>
+      <c r="O6" s="29">
+        <f>SUM(C6:N6)</f>
+        <v>4216567.27868852</v>
+      </c>
+    </row>
+    <row r="7" ht="15.6" spans="1:15">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="13">
+        <f>[3]总目标!B83+[3]总目标!B84+[3]总目标!B85+[3]总目标!B86+[3]总目标!B87</f>
+        <v>251227.75</v>
+      </c>
+      <c r="D7" s="13">
+        <f>[3]总目标!C83+[3]总目标!C84+[3]总目标!C85+[3]总目标!C86+[3]总目标!C87</f>
+        <v>461397.51</v>
+      </c>
+      <c r="E7" s="13">
+        <f>[3]总目标!D83+[3]总目标!D84+[3]总目标!D85+[3]总目标!D86+[3]总目标!D87</f>
+        <v>331315.02</v>
+      </c>
+      <c r="F7" s="13">
+        <f>[3]总目标!E83+[3]总目标!E84+[3]总目标!E85+[3]总目标!E86+[3]总目标!E87</f>
+        <v>245728.5</v>
+      </c>
+      <c r="G7" s="13">
+        <f>[3]总目标!F83+[3]总目标!F84+[3]总目标!F85+[3]总目标!F86+[3]总目标!F87</f>
+        <v>165047.71</v>
+      </c>
+      <c r="H7" s="13">
+        <f>[3]总目标!G83+[3]总目标!G84+[3]总目标!G85+[3]总目标!G86+[3]总目标!G87</f>
+        <v>42597.61</v>
+      </c>
+      <c r="I7" s="13">
+        <f>[3]总目标!H83+[3]总目标!H84+[3]总目标!H85+[3]总目标!H86+[3]总目标!H87</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <f>[3]总目标!I83+[3]总目标!I84+[3]总目标!I85+[3]总目标!I86+[3]总目标!I87</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <f>[3]总目标!J83+[3]总目标!J84+[3]总目标!J85+[3]总目标!J86+[3]总目标!J87</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
+        <f>[3]总目标!K83+[3]总目标!K84+[3]总目标!K85+[3]总目标!K86+[3]总目标!K87</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="13">
+        <f>[3]总目标!L83+[3]总目标!L84+[3]总目标!L85+[3]总目标!L86+[3]总目标!L87</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="13">
+        <f>[3]总目标!M83+[3]总目标!M84+[3]总目标!M85+[3]总目标!M86+[3]总目标!M87</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="13">
+        <f>SUM(C7:N7)</f>
+        <v>1497314.1</v>
+      </c>
+    </row>
+    <row r="8" ht="15.6" spans="1:15">
+      <c r="A8" s="11"/>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="14">
+        <f t="shared" ref="C8:O8" si="0">C7/C6</f>
+        <v>1.00647304616765</v>
+      </c>
+      <c r="D8" s="14">
+        <f t="shared" si="0"/>
+        <v>0.951114661750179</v>
+      </c>
+      <c r="E8" s="14">
+        <f t="shared" si="0"/>
+        <v>0.833424725356295</v>
+      </c>
+      <c r="F8" s="14">
+        <f t="shared" si="0"/>
+        <v>0.628398825927592</v>
+      </c>
+      <c r="G8" s="14">
+        <f t="shared" si="0"/>
+        <v>0.447047820067421</v>
+      </c>
+      <c r="H8" s="14">
+        <f t="shared" si="0"/>
+        <v>0.131397516222077</v>
+      </c>
+      <c r="I8" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="14">
+        <f t="shared" si="0"/>
+        <v>0.355102622829656</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -1967,7 +1967,7 @@
             <v>269170.203815175</v>
           </cell>
           <cell r="H7">
-            <v>82125.1542380092</v>
+            <v>144472.14994548</v>
           </cell>
           <cell r="I7">
             <v>0</v>
@@ -6819,7 +6819,7 @@
             <v>26753</v>
           </cell>
           <cell r="H11">
-            <v>7111</v>
+            <v>15887</v>
           </cell>
           <cell r="I11">
             <v>0</v>
@@ -6840,7 +6840,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>162867</v>
+            <v>171643</v>
           </cell>
         </row>
         <row r="12">
@@ -6863,7 +6863,7 @@
             <v>0.743138888888889</v>
           </cell>
           <cell r="H12">
-            <v>0.176859750789663</v>
+            <v>0.395130201208745</v>
           </cell>
           <cell r="I12">
             <v>0</v>
@@ -6884,7 +6884,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.280383630128496</v>
+            <v>0.295491950033742</v>
           </cell>
         </row>
         <row r="14">
@@ -6951,7 +6951,7 @@
             <v>9282</v>
           </cell>
           <cell r="H15">
-            <v>2512</v>
+            <v>5500</v>
           </cell>
           <cell r="I15">
             <v>0</v>
@@ -6972,7 +6972,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>57858</v>
+            <v>60846</v>
           </cell>
         </row>
         <row r="16">
@@ -6995,7 +6995,7 @@
             <v>0.831720430107527</v>
           </cell>
           <cell r="H16">
-            <v>0.201537687627816</v>
+            <v>0.441264841541795</v>
           </cell>
           <cell r="I16">
             <v>0</v>
@@ -7016,7 +7016,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.321307809082585</v>
+            <v>0.337901326548428</v>
           </cell>
         </row>
         <row r="18">
@@ -7083,7 +7083,7 @@
             <v>11545368.1632</v>
           </cell>
           <cell r="H19">
-            <v>2959137.918</v>
+            <v>6659288.4732</v>
           </cell>
           <cell r="I19">
             <v>0</v>
@@ -7104,7 +7104,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>63877158.6282</v>
+            <v>67577309.1834</v>
           </cell>
         </row>
         <row r="20">
@@ -7127,7 +7127,7 @@
             <v>0.922448718696069</v>
           </cell>
           <cell r="H20">
-            <v>0.211680523237847</v>
+            <v>0.476369032961964</v>
           </cell>
           <cell r="I20">
             <v>0</v>
@@ -7148,7 +7148,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.316698354246535</v>
+            <v>0.335043434341862</v>
           </cell>
         </row>
         <row r="22">
@@ -7215,7 +7215,7 @@
             <v>3503371.5464</v>
           </cell>
           <cell r="H23">
-            <v>889801.365</v>
+            <v>1930982.2827</v>
           </cell>
           <cell r="I23">
             <v>0</v>
@@ -7236,7 +7236,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>20835703.0214</v>
+            <v>21876883.9391</v>
           </cell>
         </row>
         <row r="24">
@@ -7259,7 +7259,7 @@
             <v>0.874723240851709</v>
           </cell>
           <cell r="H24">
-            <v>0.198910991710651</v>
+            <v>0.431662184320827</v>
           </cell>
           <cell r="I24">
             <v>0</v>
@@ -7280,7 +7280,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.32281848659582</v>
+            <v>0.33895004922076</v>
           </cell>
         </row>
         <row r="26">
@@ -7303,7 +7303,7 @@
             <v>0.30344390034843</v>
           </cell>
           <cell r="H26">
-            <v>0.300696145180483</v>
+            <v>0.289968258691773</v>
           </cell>
           <cell r="I26" t="e">
             <v>#DIV/0!</v>
@@ -7324,7 +7324,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.32618393599307</v>
+            <v>0.323731208055765</v>
           </cell>
         </row>
         <row r="27">
@@ -7347,7 +7347,7 @@
             <v>0.653048256270325</v>
           </cell>
           <cell r="H27">
-            <v>0.646744480382506</v>
+            <v>0.653804997796941</v>
           </cell>
           <cell r="I27" t="e">
             <v>#DIV/0!</v>
@@ -7368,7 +7368,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.644753080734587</v>
+            <v>0.645508409897287</v>
           </cell>
         </row>
         <row r="28">
@@ -7391,7 +7391,7 @@
             <v>0.16938581938584</v>
           </cell>
           <cell r="H28">
-            <v>0.180681280478818</v>
+            <v>0.0832583765477135</v>
           </cell>
           <cell r="I28" t="e">
             <v>#DIV/0!</v>
@@ -7412,7 +7412,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.157085641729409</v>
+            <v>0.149609505133876</v>
           </cell>
         </row>
         <row r="30">
@@ -7482,7 +7482,7 @@
             <v>10453</v>
           </cell>
           <cell r="H31">
-            <v>2716</v>
+            <v>5785</v>
           </cell>
           <cell r="I31">
             <v>0</v>
@@ -7503,7 +7503,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>79020</v>
+            <v>82089</v>
           </cell>
         </row>
         <row r="32">
@@ -7526,7 +7526,7 @@
             <v>3602</v>
           </cell>
           <cell r="H32">
-            <v>915</v>
+            <v>1927</v>
           </cell>
           <cell r="I32">
             <v>0</v>
@@ -7547,7 +7547,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>29069</v>
+            <v>30081</v>
           </cell>
         </row>
         <row r="33">
@@ -7570,7 +7570,7 @@
             <v>4439731.0488</v>
           </cell>
           <cell r="H33">
-            <v>1166305.44</v>
+            <v>2511111.222</v>
           </cell>
           <cell r="I33">
             <v>0</v>
@@ -7591,7 +7591,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>32482032.0069</v>
+            <v>33826837.7889</v>
           </cell>
         </row>
         <row r="34">
@@ -7614,7 +7614,7 @@
             <v>1407371.462</v>
           </cell>
           <cell r="H34">
-            <v>336024.4174</v>
+            <v>699411.4057</v>
           </cell>
           <cell r="I34">
             <v>0</v>
@@ -7635,7 +7635,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>10724683.5094</v>
+            <v>11088070.4977</v>
           </cell>
         </row>
         <row r="35">
@@ -7658,7 +7658,7 @@
             <v>0.316994756333358</v>
           </cell>
           <cell r="H35">
-            <v>0.288110134683072</v>
+            <v>0.278526653687186</v>
           </cell>
           <cell r="I35" t="e">
             <v>#DIV/0!</v>
@@ -7679,7 +7679,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.330172801600645</v>
+            <v>0.327789152710528</v>
           </cell>
         </row>
         <row r="36">
@@ -7702,7 +7702,7 @@
             <v>0.655409930163589</v>
           </cell>
           <cell r="H36">
-            <v>0.663107511045655</v>
+            <v>0.666897147796024</v>
           </cell>
           <cell r="I36" t="e">
             <v>#DIV/0!</v>
@@ -7723,7 +7723,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.632131106049101</v>
+            <v>0.633556262105763</v>
           </cell>
         </row>
         <row r="37">
@@ -7746,7 +7746,7 @@
             <v>0.15183428524004</v>
           </cell>
           <cell r="H37">
-            <v>0.157025523348173</v>
+            <v>0.0754411631980625</v>
           </cell>
           <cell r="I37" t="e">
             <v>#DIV/0!</v>
@@ -7767,7 +7767,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.170161205074302</v>
+            <v>0.164584547904754</v>
           </cell>
         </row>
         <row r="38">
@@ -7837,7 +7837,7 @@
             <v>6417</v>
           </cell>
           <cell r="H39">
-            <v>1652</v>
+            <v>4008</v>
           </cell>
           <cell r="I39">
             <v>0</v>
@@ -7858,7 +7858,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>35727</v>
+            <v>38083</v>
           </cell>
         </row>
         <row r="40">
@@ -7881,7 +7881,7 @@
             <v>1916</v>
           </cell>
           <cell r="H40">
-            <v>541</v>
+            <v>1324</v>
           </cell>
           <cell r="I40">
             <v>0</v>
@@ -7902,7 +7902,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>11731</v>
+            <v>12514</v>
           </cell>
         </row>
         <row r="41">
@@ -7925,7 +7925,7 @@
             <v>2954093.3256</v>
           </cell>
           <cell r="H41">
-            <v>669524.052</v>
+            <v>1634730.252</v>
           </cell>
           <cell r="I41">
             <v>0</v>
@@ -7946,7 +7946,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>13363826.5986</v>
+            <v>14329032.7986</v>
           </cell>
         </row>
         <row r="42">
@@ -7969,7 +7969,7 @@
             <v>702420.3795</v>
           </cell>
           <cell r="H42">
-            <v>188985.7344</v>
+            <v>458423.5943</v>
           </cell>
           <cell r="I42">
             <v>0</v>
@@ -7990,7 +7990,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>3914571.0939</v>
+            <v>4184008.9538</v>
           </cell>
         </row>
         <row r="43">
@@ -8013,7 +8013,7 @@
             <v>0.237778669147947</v>
           </cell>
           <cell r="H43">
-            <v>0.282268775610768</v>
+            <v>0.280427669176089</v>
           </cell>
           <cell r="I43" t="e">
             <v>#DIV/0!</v>
@@ -8034,7 +8034,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.292922918822524</v>
+            <v>0.291995210884631</v>
           </cell>
         </row>
         <row r="44">
@@ -8057,7 +8057,7 @@
             <v>0.701418108150226</v>
           </cell>
           <cell r="H44">
-            <v>0.672518159806295</v>
+            <v>0.669660678642715</v>
           </cell>
           <cell r="I44" t="e">
             <v>#DIV/0!</v>
@@ -8078,7 +8078,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.671648892994094</v>
+            <v>0.671401937872542</v>
           </cell>
         </row>
         <row r="45">
@@ -8101,7 +8101,7 @@
             <v>0.136393850173022</v>
           </cell>
           <cell r="H45">
-            <v>0.160248762141488</v>
+            <v>0.0660627646058313</v>
           </cell>
           <cell r="I45" t="e">
             <v>#DIV/0!</v>
@@ -8122,7 +8122,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.154207548035254</v>
+            <v>0.144277035892035</v>
           </cell>
         </row>
         <row r="46">
@@ -8192,7 +8192,7 @@
             <v>8516</v>
           </cell>
           <cell r="H47">
-            <v>2443</v>
+            <v>5471</v>
           </cell>
           <cell r="I47">
             <v>0</v>
@@ -8213,7 +8213,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>31244</v>
+            <v>34272</v>
           </cell>
         </row>
         <row r="48">
@@ -8236,7 +8236,7 @@
             <v>3226</v>
           </cell>
           <cell r="H48">
-            <v>936</v>
+            <v>1994</v>
           </cell>
           <cell r="I48">
             <v>0</v>
@@ -8257,7 +8257,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>10912</v>
+            <v>11970</v>
           </cell>
         </row>
         <row r="49">
@@ -8280,7 +8280,7 @@
             <v>3625780.1448</v>
           </cell>
           <cell r="H49">
-            <v>1008220.752</v>
+            <v>2274149.9952</v>
           </cell>
           <cell r="I49">
             <v>0</v>
@@ -8301,7 +8301,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>12110705.2374</v>
+            <v>13376634.4806</v>
           </cell>
         </row>
         <row r="50">
@@ -8324,7 +8324,7 @@
             <v>1213786.7552</v>
           </cell>
           <cell r="H50">
-            <v>328535.4711</v>
+            <v>692555.2367</v>
           </cell>
           <cell r="I50">
             <v>0</v>
@@ -8345,7 +8345,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>3854966.5763</v>
+            <v>4218986.3419</v>
           </cell>
         </row>
         <row r="51">
@@ -8368,7 +8368,7 @@
             <v>0.334765679860865</v>
           </cell>
           <cell r="H51">
-            <v>0.32585668411237</v>
+            <v>0.304533666715811</v>
           </cell>
           <cell r="I51" t="e">
             <v>#DIV/0!</v>
@@ -8389,7 +8389,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.318310659927151</v>
+            <v>0.315399688017098</v>
           </cell>
         </row>
         <row r="52">
@@ -8412,7 +8412,7 @@
             <v>0.621183654297792</v>
           </cell>
           <cell r="H52">
-            <v>0.616864510847319</v>
+            <v>0.635532809358435</v>
           </cell>
           <cell r="I52" t="e">
             <v>#DIV/0!</v>
@@ -8433,7 +8433,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.650748943797209</v>
+            <v>0.650735294117647</v>
           </cell>
         </row>
         <row r="53">
@@ -8456,7 +8456,7 @@
             <v>0.22016008895728</v>
           </cell>
           <cell r="H53">
-            <v>0.21596133824589</v>
+            <v>0.102448088239255</v>
           </cell>
           <cell r="I53" t="e">
             <v>#DIV/0!</v>
@@ -8477,7 +8477,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.182638180141048</v>
+            <v>0.166879914496933</v>
           </cell>
         </row>
         <row r="54">
@@ -8547,7 +8547,7 @@
             <v>1367</v>
           </cell>
           <cell r="H55">
-            <v>300</v>
+            <v>623</v>
           </cell>
           <cell r="I55">
             <v>0</v>
@@ -8568,7 +8568,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>16876</v>
+            <v>17199</v>
           </cell>
         </row>
         <row r="56">
@@ -8591,7 +8591,7 @@
             <v>538</v>
           </cell>
           <cell r="H56">
-            <v>120</v>
+            <v>255</v>
           </cell>
           <cell r="I56">
             <v>0</v>
@@ -8612,7 +8612,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>6146</v>
+            <v>6281</v>
           </cell>
         </row>
         <row r="57">
@@ -8635,7 +8635,7 @@
             <v>525763.644</v>
           </cell>
           <cell r="H57">
-            <v>115087.674</v>
+            <v>239297.004</v>
           </cell>
           <cell r="I57">
             <v>0</v>
@@ -8656,7 +8656,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>5920594.7853</v>
+            <v>6044804.1153</v>
           </cell>
         </row>
         <row r="58">
@@ -8679,7 +8679,7 @@
             <v>179792.9497</v>
           </cell>
           <cell r="H58">
-            <v>36255.7421</v>
+            <v>80592.046</v>
           </cell>
           <cell r="I58">
             <v>0</v>
@@ -8700,7 +8700,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2341481.8418</v>
+            <v>2385818.1457</v>
           </cell>
         </row>
         <row r="59">
@@ -8723,7 +8723,7 @@
             <v>0.341965352210622</v>
           </cell>
           <cell r="H59">
-            <v>0.315027151387211</v>
+            <v>0.336786690400854</v>
           </cell>
           <cell r="I59" t="e">
             <v>#DIV/0!</v>
@@ -8744,7 +8744,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.395480847230682</v>
+            <v>0.394689075144926</v>
           </cell>
         </row>
         <row r="60">
@@ -8767,7 +8767,7 @@
             <v>0.606437454279444</v>
           </cell>
           <cell r="H60">
-            <v>0.6</v>
+            <v>0.590690208667737</v>
           </cell>
           <cell r="I60" t="e">
             <v>#DIV/0!</v>
@@ -8788,7 +8788,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.635814173974875</v>
+            <v>0.634804349090063</v>
           </cell>
         </row>
         <row r="61">
@@ -8811,7 +8811,7 @@
             <v>0.0928901830014306</v>
           </cell>
           <cell r="H61">
-            <v>0.186738695937491</v>
+            <v>0.0840076699380482</v>
           </cell>
           <cell r="I61" t="e">
             <v>#DIV/0!</v>
@@ -8832,7 +8832,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.0599382055818597</v>
+            <v>0.0588243576958892</v>
           </cell>
         </row>
         <row r="62">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="H7" s="13">
         <f>'[1]2026年度男装汇总分析'!H7</f>
-        <v>82125.1542380092</v>
+        <v>144472.14994548</v>
       </c>
       <c r="I7" s="13">
         <f>'[1]2026年度男装汇总分析'!I7</f>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="O7" s="13">
         <f>SUM(C7:N7)</f>
-        <v>1571558.86805318</v>
+        <v>1633905.86376065</v>
       </c>
       <c r="P7" s="79"/>
       <c r="Q7" s="82"/>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="H8" s="14">
         <f t="shared" si="0"/>
-        <v>0.14955970605506</v>
+        <v>0.263101025251875</v>
       </c>
       <c r="I8" s="14">
         <f t="shared" si="0"/>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="O8" s="14">
         <f t="shared" si="0"/>
-        <v>0.233862934639332</v>
+        <v>0.24314076169277</v>
       </c>
       <c r="P8" s="79"/>
       <c r="Q8" s="79"/>
@@ -21647,7 +21647,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbf209d6-a4f4-4f77-85fb-97d51526fa7b}</x14:id>
+          <x14:id>{7840ccb6-ea7b-4585-94c6-28f431c5cb78}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21661,7 +21661,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80070bec-fb39-4f0f-a108-09b27b92b0c2}</x14:id>
+          <x14:id>{fc791b8c-95ef-49a2-ba07-5dfb700399f9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21675,7 +21675,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60a9916b-dbc6-48b7-a20d-af55fa30b993}</x14:id>
+          <x14:id>{a4617cd8-766a-4aa5-a005-edfdb1fe0c7b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21689,7 +21689,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5f06e3e-849a-4ac0-bf79-c85560fcb5b9}</x14:id>
+          <x14:id>{8f9cea0d-65f6-40af-ba10-e8d0bd3b1474}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21703,7 +21703,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3a211d3-fd0d-4acd-813f-c8d84c0ab347}</x14:id>
+          <x14:id>{00cbf878-519e-466b-a195-b3a2c6c0a8f4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21717,7 +21717,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20539eff-fcae-4027-b45a-e5969f19c4a7}</x14:id>
+          <x14:id>{8a562077-de00-4c2f-bea9-44534a7b342d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21731,7 +21731,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62e694bf-fcda-4c99-9d20-c70c106cc266}</x14:id>
+          <x14:id>{35880de3-26cf-4694-8e6e-8d59b0755f06}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21745,7 +21745,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f361c78b-a76e-4062-a20e-e09b5b9430f1}</x14:id>
+          <x14:id>{125bf857-b926-4185-b096-0ed69b07bea0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21765,7 +21765,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7953cbe0-3628-4d47-b55c-d89ac01b6ada}</x14:id>
+          <x14:id>{a3e53199-9b4c-44c5-9598-d2163ea47a16}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21793,7 +21793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03392e03-ef76-4cac-8cc2-8bd2186e02a1}</x14:id>
+          <x14:id>{d2c1bf36-702c-45a7-8255-f7f39e2dbea4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21813,7 +21813,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72596251-f659-407d-aea8-9c22333653e0}</x14:id>
+          <x14:id>{2f2d82ea-158a-4e52-baf9-b2c5d8f61eaf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21841,7 +21841,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ed77bc1-6ebe-419f-ab91-81211d066800}</x14:id>
+          <x14:id>{4996d82a-78f2-493e-bc3d-ed366a330b97}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21861,7 +21861,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cfe00b54-13ed-498f-a340-b64766f30308}</x14:id>
+          <x14:id>{bb1dde86-37eb-4c68-ad62-f96d3408deaa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21889,7 +21889,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{efe330e3-c5d4-4800-b576-4b92f01160c3}</x14:id>
+          <x14:id>{74be4bcb-37a6-479c-b907-6de492ce9d7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21909,7 +21909,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4da3bddb-17f8-45df-8238-3e75ead1150a}</x14:id>
+          <x14:id>{b719b49e-2a65-4f78-99f3-74894549fb56}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21937,7 +21937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{605932a6-4ea5-4437-a9aa-2e0f8245af6c}</x14:id>
+          <x14:id>{7f57688e-28d7-43ce-863b-47dc1b4e262a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21957,7 +21957,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c043b345-00bf-476b-be5c-f21d1b0ab1f3}</x14:id>
+          <x14:id>{e4100c64-88b6-425d-a28c-e14268cb7d99}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21985,7 +21985,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d0eaca1-7dc7-4975-b1b3-9fbcc931ee21}</x14:id>
+          <x14:id>{840d6bba-3a80-403e-ae65-847c9dcdb317}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22047,7 +22047,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a0ba572-8b2d-4d03-8b3f-4f83a68bf685}</x14:id>
+          <x14:id>{29a48999-a78f-4dcc-9ac5-b62bed5f36f9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22077,7 +22077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d643ec0-e58d-43aa-8dc0-ca463afd490e}</x14:id>
+          <x14:id>{29e2579b-bec1-4c96-9f7d-113273ea3046}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22099,7 +22099,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb91be6a-1d6c-44cd-9a03-1943ff680277}</x14:id>
+          <x14:id>{a5107096-4e87-402e-80ec-ecd0780f5689}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22119,7 +22119,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{080e71bc-3398-4480-9ffe-6a78811f5373}</x14:id>
+          <x14:id>{6bb68e36-f028-49f8-ae59-f29bc238de14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22141,7 +22141,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41008630-0e1e-41dc-b668-23396018b06f}</x14:id>
+          <x14:id>{22ce367a-5bec-43c1-8866-04551d767953}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22161,7 +22161,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0586850a-67cc-4bb2-a3a8-150e75dfcefe}</x14:id>
+          <x14:id>{795773fc-7736-4b06-ae20-6d6bb03006bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22183,7 +22183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67f8ca3f-ece6-43bd-b76e-4edf153c8875}</x14:id>
+          <x14:id>{7e666c86-28a2-400f-ac49-e2d724cf7e41}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22203,7 +22203,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{36d20ec0-5fb4-4490-9371-84d7a2fdaa37}</x14:id>
+          <x14:id>{2d7a155e-70e4-4bd5-bdba-117e342b3d37}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22225,7 +22225,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b9319dd8-ee60-45e1-9365-06cb21f1a46e}</x14:id>
+          <x14:id>{c286c15d-d678-4990-996a-91cd8bfa11a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22245,7 +22245,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8dea84b-72d0-45f0-83f3-87601a6351ca}</x14:id>
+          <x14:id>{2e5660e9-8614-4563-9c7b-17c10a5690f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22273,7 +22273,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75dbae2d-55d5-4513-9158-95afcbb1b0d6}</x14:id>
+          <x14:id>{e2171584-2ffe-4b77-9ea9-cfb30f142394}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22287,7 +22287,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a30091e-81d0-4fc6-a7df-821190afb03f}</x14:id>
+          <x14:id>{f11a1240-4250-4499-9990-91506ab2a461}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22317,7 +22317,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25c9008f-4b7f-4fe4-b464-4c4a32c57c27}</x14:id>
+          <x14:id>{2dfb19e3-49cc-4a95-a42a-4f13ec07e283}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22339,7 +22339,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a01ae5f-6083-4100-8018-e3793bcef53a}</x14:id>
+          <x14:id>{5d1c6ec2-ade7-4fdd-bd20-e5374edc6d34}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22361,7 +22361,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26e19870-1d55-4e17-909e-6f4f493a417c}</x14:id>
+          <x14:id>{7b5363a0-c15f-4da6-a4c1-e6b6bb4e9985}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22383,7 +22383,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3f1ada4d-e02c-483f-a956-6091bc11237b}</x14:id>
+          <x14:id>{bbddf51a-c167-4d9b-b877-be9d09c99401}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22405,7 +22405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e0d9983-90e4-4f5c-834b-f37cf2ac2038}</x14:id>
+          <x14:id>{ec8e362e-746c-4ef2-a1f8-bb49b3dcf8cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22427,7 +22427,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{efbdb3ab-2fdb-4f8d-8e57-cf47d91dad21}</x14:id>
+          <x14:id>{96675eca-5e98-42a2-8796-6c81dcb733ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22449,7 +22449,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b1fc2f7-0c26-4ae6-aac3-60163801b541}</x14:id>
+          <x14:id>{0c3aeab0-ffb0-443e-b4ed-029ce5b30fa5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22471,7 +22471,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cc0b9c4c-fc6b-490c-a1ac-1d4d46467c17}</x14:id>
+          <x14:id>{44ec9529-1187-4aad-ac6e-eef3edcfbb74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22493,7 +22493,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5faf52e4-dc52-4065-ba90-677708be5b1e}</x14:id>
+          <x14:id>{b3708369-e926-478e-9f32-d2c0a70e8539}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22515,7 +22515,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b332d3ee-772a-4b1b-bf1c-0a502106379b}</x14:id>
+          <x14:id>{476dcb2d-1981-456e-901f-54fd6a0194b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22537,7 +22537,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c99cecc1-37ec-4f47-a352-c3516d48db0a}</x14:id>
+          <x14:id>{bfa2b2b9-f99e-4cf5-9c0c-d6a6fa19d1d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22559,7 +22559,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0bb21f6d-60c9-4ee7-b810-c733c17f995d}</x14:id>
+          <x14:id>{77a137fa-b234-402b-b542-997f1475f3eb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22581,7 +22581,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6102d7c0-9dc1-4b3c-bc55-96b640e2d9b9}</x14:id>
+          <x14:id>{f2127832-2e13-4d1d-8898-72879836beaf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22600,7 +22600,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dbf209d6-a4f4-4f77-85fb-97d51526fa7b}">
+          <x14:cfRule type="dataBar" id="{7840ccb6-ea7b-4585-94c6-28f431c5cb78}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22613,7 +22613,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{80070bec-fb39-4f0f-a108-09b27b92b0c2}">
+          <x14:cfRule type="dataBar" id="{fc791b8c-95ef-49a2-ba07-5dfb700399f9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22626,7 +22626,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{60a9916b-dbc6-48b7-a20d-af55fa30b993}">
+          <x14:cfRule type="dataBar" id="{a4617cd8-766a-4aa5-a005-edfdb1fe0c7b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22639,7 +22639,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f5f06e3e-849a-4ac0-bf79-c85560fcb5b9}">
+          <x14:cfRule type="dataBar" id="{8f9cea0d-65f6-40af-ba10-e8d0bd3b1474}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22652,7 +22652,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3a211d3-fd0d-4acd-813f-c8d84c0ab347}">
+          <x14:cfRule type="dataBar" id="{00cbf878-519e-466b-a195-b3a2c6c0a8f4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22665,7 +22665,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20539eff-fcae-4027-b45a-e5969f19c4a7}">
+          <x14:cfRule type="dataBar" id="{8a562077-de00-4c2f-bea9-44534a7b342d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22678,7 +22678,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62e694bf-fcda-4c99-9d20-c70c106cc266}">
+          <x14:cfRule type="dataBar" id="{35880de3-26cf-4694-8e6e-8d59b0755f06}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22691,7 +22691,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f361c78b-a76e-4062-a20e-e09b5b9430f1}">
+          <x14:cfRule type="dataBar" id="{125bf857-b926-4185-b096-0ed69b07bea0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22704,7 +22704,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7953cbe0-3628-4d47-b55c-d89ac01b6ada}">
+          <x14:cfRule type="dataBar" id="{a3e53199-9b4c-44c5-9598-d2163ea47a16}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22717,7 +22717,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{03392e03-ef76-4cac-8cc2-8bd2186e02a1}">
+          <x14:cfRule type="dataBar" id="{d2c1bf36-702c-45a7-8255-f7f39e2dbea4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22730,7 +22730,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72596251-f659-407d-aea8-9c22333653e0}">
+          <x14:cfRule type="dataBar" id="{2f2d82ea-158a-4e52-baf9-b2c5d8f61eaf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22743,7 +22743,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ed77bc1-6ebe-419f-ab91-81211d066800}">
+          <x14:cfRule type="dataBar" id="{4996d82a-78f2-493e-bc3d-ed366a330b97}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22756,7 +22756,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cfe00b54-13ed-498f-a340-b64766f30308}">
+          <x14:cfRule type="dataBar" id="{bb1dde86-37eb-4c68-ad62-f96d3408deaa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22769,7 +22769,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{efe330e3-c5d4-4800-b576-4b92f01160c3}">
+          <x14:cfRule type="dataBar" id="{74be4bcb-37a6-479c-b907-6de492ce9d7a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22782,7 +22782,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4da3bddb-17f8-45df-8238-3e75ead1150a}">
+          <x14:cfRule type="dataBar" id="{b719b49e-2a65-4f78-99f3-74894549fb56}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22795,7 +22795,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{605932a6-4ea5-4437-a9aa-2e0f8245af6c}">
+          <x14:cfRule type="dataBar" id="{7f57688e-28d7-43ce-863b-47dc1b4e262a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22808,7 +22808,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c043b345-00bf-476b-be5c-f21d1b0ab1f3}">
+          <x14:cfRule type="dataBar" id="{e4100c64-88b6-425d-a28c-e14268cb7d99}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22821,7 +22821,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4d0eaca1-7dc7-4975-b1b3-9fbcc931ee21}">
+          <x14:cfRule type="dataBar" id="{840d6bba-3a80-403e-ae65-847c9dcdb317}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22834,7 +22834,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7a0ba572-8b2d-4d03-8b3f-4f83a68bf685}">
+          <x14:cfRule type="dataBar" id="{29a48999-a78f-4dcc-9ac5-b62bed5f36f9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22847,7 +22847,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4d643ec0-e58d-43aa-8dc0-ca463afd490e}">
+          <x14:cfRule type="dataBar" id="{29e2579b-bec1-4c96-9f7d-113273ea3046}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22860,7 +22860,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cb91be6a-1d6c-44cd-9a03-1943ff680277}">
+          <x14:cfRule type="dataBar" id="{a5107096-4e87-402e-80ec-ecd0780f5689}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22873,7 +22873,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{080e71bc-3398-4480-9ffe-6a78811f5373}">
+          <x14:cfRule type="dataBar" id="{6bb68e36-f028-49f8-ae59-f29bc238de14}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22886,7 +22886,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{41008630-0e1e-41dc-b668-23396018b06f}">
+          <x14:cfRule type="dataBar" id="{22ce367a-5bec-43c1-8866-04551d767953}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22899,7 +22899,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0586850a-67cc-4bb2-a3a8-150e75dfcefe}">
+          <x14:cfRule type="dataBar" id="{795773fc-7736-4b06-ae20-6d6bb03006bd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22912,7 +22912,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{67f8ca3f-ece6-43bd-b76e-4edf153c8875}">
+          <x14:cfRule type="dataBar" id="{7e666c86-28a2-400f-ac49-e2d724cf7e41}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22925,7 +22925,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{36d20ec0-5fb4-4490-9371-84d7a2fdaa37}">
+          <x14:cfRule type="dataBar" id="{2d7a155e-70e4-4bd5-bdba-117e342b3d37}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22938,7 +22938,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b9319dd8-ee60-45e1-9365-06cb21f1a46e}">
+          <x14:cfRule type="dataBar" id="{c286c15d-d678-4990-996a-91cd8bfa11a3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22951,7 +22951,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b8dea84b-72d0-45f0-83f3-87601a6351ca}">
+          <x14:cfRule type="dataBar" id="{2e5660e9-8614-4563-9c7b-17c10a5690f0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22964,7 +22964,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75dbae2d-55d5-4513-9158-95afcbb1b0d6}">
+          <x14:cfRule type="dataBar" id="{e2171584-2ffe-4b77-9ea9-cfb30f142394}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22977,7 +22977,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3a30091e-81d0-4fc6-a7df-821190afb03f}">
+          <x14:cfRule type="dataBar" id="{f11a1240-4250-4499-9990-91506ab2a461}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22990,7 +22990,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{25c9008f-4b7f-4fe4-b464-4c4a32c57c27}">
+          <x14:cfRule type="dataBar" id="{2dfb19e3-49cc-4a95-a42a-4f13ec07e283}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23003,7 +23003,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a01ae5f-6083-4100-8018-e3793bcef53a}">
+          <x14:cfRule type="dataBar" id="{5d1c6ec2-ade7-4fdd-bd20-e5374edc6d34}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23016,7 +23016,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{26e19870-1d55-4e17-909e-6f4f493a417c}">
+          <x14:cfRule type="dataBar" id="{7b5363a0-c15f-4da6-a4c1-e6b6bb4e9985}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23029,7 +23029,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3f1ada4d-e02c-483f-a956-6091bc11237b}">
+          <x14:cfRule type="dataBar" id="{bbddf51a-c167-4d9b-b877-be9d09c99401}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23042,7 +23042,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e0d9983-90e4-4f5c-834b-f37cf2ac2038}">
+          <x14:cfRule type="dataBar" id="{ec8e362e-746c-4ef2-a1f8-bb49b3dcf8cf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23055,7 +23055,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{efbdb3ab-2fdb-4f8d-8e57-cf47d91dad21}">
+          <x14:cfRule type="dataBar" id="{96675eca-5e98-42a2-8796-6c81dcb733ab}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23068,7 +23068,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4b1fc2f7-0c26-4ae6-aac3-60163801b541}">
+          <x14:cfRule type="dataBar" id="{0c3aeab0-ffb0-443e-b4ed-029ce5b30fa5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23081,7 +23081,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cc0b9c4c-fc6b-490c-a1ac-1d4d46467c17}">
+          <x14:cfRule type="dataBar" id="{44ec9529-1187-4aad-ac6e-eef3edcfbb74}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23094,7 +23094,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5faf52e4-dc52-4065-ba90-677708be5b1e}">
+          <x14:cfRule type="dataBar" id="{b3708369-e926-478e-9f32-d2c0a70e8539}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23107,7 +23107,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b332d3ee-772a-4b1b-bf1c-0a502106379b}">
+          <x14:cfRule type="dataBar" id="{476dcb2d-1981-456e-901f-54fd6a0194b6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23120,7 +23120,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c99cecc1-37ec-4f47-a352-c3516d48db0a}">
+          <x14:cfRule type="dataBar" id="{bfa2b2b9-f99e-4cf5-9c0c-d6a6fa19d1d5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23133,7 +23133,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0bb21f6d-60c9-4ee7-b810-c733c17f995d}">
+          <x14:cfRule type="dataBar" id="{77a137fa-b234-402b-b542-997f1475f3eb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23146,7 +23146,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6102d7c0-9dc1-4b3c-bc55-96b640e2d9b9}">
+          <x14:cfRule type="dataBar" id="{f2127832-2e13-4d1d-8898-72879836beaf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23782,7 +23782,7 @@
       </c>
       <c r="H11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H11</f>
-        <v>7111</v>
+        <v>15887</v>
       </c>
       <c r="I11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I11</f>
@@ -23810,7 +23810,7 @@
       </c>
       <c r="O11" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O11</f>
-        <v>162867</v>
+        <v>171643</v>
       </c>
     </row>
     <row r="12" s="34" customFormat="1" spans="1:15">
@@ -23844,7 +23844,7 @@
       </c>
       <c r="H12" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H12</f>
-        <v>0.176859750789663</v>
+        <v>0.395130201208745</v>
       </c>
       <c r="I12" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I12</f>
@@ -23872,7 +23872,7 @@
       </c>
       <c r="O12" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O12</f>
-        <v>0.280383630128496</v>
+        <v>0.295491950033742</v>
       </c>
     </row>
     <row r="13" s="34" customFormat="1" spans="1:15">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="H15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H15</f>
-        <v>2512</v>
+        <v>5500</v>
       </c>
       <c r="I15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I15</f>
@@ -24058,7 +24058,7 @@
       </c>
       <c r="O15" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O15</f>
-        <v>57858</v>
+        <v>60846</v>
       </c>
     </row>
     <row r="16" s="34" customFormat="1" spans="1:15">
@@ -24092,7 +24092,7 @@
       </c>
       <c r="H16" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H16</f>
-        <v>0.201537687627816</v>
+        <v>0.441264841541795</v>
       </c>
       <c r="I16" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I16</f>
@@ -24120,7 +24120,7 @@
       </c>
       <c r="O16" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O16</f>
-        <v>0.321307809082585</v>
+        <v>0.337901326548428</v>
       </c>
     </row>
     <row r="17" s="34" customFormat="1" spans="1:15">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H19" s="23">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H19</f>
-        <v>2959137.918</v>
+        <v>6659288.4732</v>
       </c>
       <c r="I19" s="23">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I19</f>
@@ -24306,7 +24306,7 @@
       </c>
       <c r="O19" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O19</f>
-        <v>63877158.6282</v>
+        <v>67577309.1834</v>
       </c>
     </row>
     <row r="20" s="34" customFormat="1" spans="1:15">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="H20" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H20</f>
-        <v>0.211680523237847</v>
+        <v>0.476369032961964</v>
       </c>
       <c r="I20" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I20</f>
@@ -24368,7 +24368,7 @@
       </c>
       <c r="O20" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O20</f>
-        <v>0.316698354246535</v>
+        <v>0.335043434341862</v>
       </c>
     </row>
     <row r="21" s="34" customFormat="1" spans="1:15">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="H23" s="23">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H23</f>
-        <v>889801.365</v>
+        <v>1930982.2827</v>
       </c>
       <c r="I23" s="23">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I23</f>
@@ -24554,7 +24554,7 @@
       </c>
       <c r="O23" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O23</f>
-        <v>20835703.0214</v>
+        <v>21876883.9391</v>
       </c>
     </row>
     <row r="24" s="34" customFormat="1" spans="1:15">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="H24" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H24</f>
-        <v>0.198910991710651</v>
+        <v>0.431662184320827</v>
       </c>
       <c r="I24" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I24</f>
@@ -24616,7 +24616,7 @@
       </c>
       <c r="O24" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O24</f>
-        <v>0.32281848659582</v>
+        <v>0.33895004922076</v>
       </c>
     </row>
     <row r="25" s="34" customFormat="1" spans="1:15">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="H26" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H26</f>
-        <v>0.300696145180483</v>
+        <v>0.289968258691773</v>
       </c>
       <c r="I26" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I26</f>
@@ -24740,7 +24740,7 @@
       </c>
       <c r="O26" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O26</f>
-        <v>0.32618393599307</v>
+        <v>0.323731208055765</v>
       </c>
     </row>
     <row r="27" s="34" customFormat="1" spans="1:15">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="H27" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H27</f>
-        <v>0.646744480382506</v>
+        <v>0.653804997796941</v>
       </c>
       <c r="I27" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I27</f>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="O27" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O27</f>
-        <v>0.644753080734587</v>
+        <v>0.645508409897287</v>
       </c>
     </row>
     <row r="28" s="34" customFormat="1" spans="1:15">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="H28" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H28</f>
-        <v>0.180681280478818</v>
+        <v>0.0832583765477135</v>
       </c>
       <c r="I28" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I28</f>
@@ -24864,7 +24864,7 @@
       </c>
       <c r="O28" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O28</f>
-        <v>0.157085641729409</v>
+        <v>0.149609505133876</v>
       </c>
     </row>
     <row r="29" s="34" customFormat="1" spans="1:15">
@@ -25022,7 +25022,7 @@
       </c>
       <c r="H31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H31</f>
-        <v>2716</v>
+        <v>5785</v>
       </c>
       <c r="I31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I31</f>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="O31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O31</f>
-        <v>79020</v>
+        <v>82089</v>
       </c>
     </row>
     <row r="32" s="34" customFormat="1" spans="1:15">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="H32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H32</f>
-        <v>915</v>
+        <v>1927</v>
       </c>
       <c r="I32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I32</f>
@@ -25112,7 +25112,7 @@
       </c>
       <c r="O32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O32</f>
-        <v>29069</v>
+        <v>30081</v>
       </c>
     </row>
     <row r="33" s="34" customFormat="1" spans="1:15">
@@ -25146,7 +25146,7 @@
       </c>
       <c r="H33" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H33</f>
-        <v>1166305.44</v>
+        <v>2511111.222</v>
       </c>
       <c r="I33" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I33</f>
@@ -25174,7 +25174,7 @@
       </c>
       <c r="O33" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O33</f>
-        <v>32482032.0069</v>
+        <v>33826837.7889</v>
       </c>
     </row>
     <row r="34" s="34" customFormat="1" spans="1:15">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="H34" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H34</f>
-        <v>336024.4174</v>
+        <v>699411.4057</v>
       </c>
       <c r="I34" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I34</f>
@@ -25236,7 +25236,7 @@
       </c>
       <c r="O34" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O34</f>
-        <v>10724683.5094</v>
+        <v>11088070.4977</v>
       </c>
     </row>
     <row r="35" s="34" customFormat="1" spans="1:15">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="H35" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H35</f>
-        <v>0.288110134683072</v>
+        <v>0.278526653687186</v>
       </c>
       <c r="I35" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I35</f>
@@ -25298,7 +25298,7 @@
       </c>
       <c r="O35" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O35</f>
-        <v>0.330172801600645</v>
+        <v>0.327789152710528</v>
       </c>
     </row>
     <row r="36" s="34" customFormat="1" spans="1:15">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="H36" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H36</f>
-        <v>0.663107511045655</v>
+        <v>0.666897147796024</v>
       </c>
       <c r="I36" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I36</f>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="O36" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O36</f>
-        <v>0.632131106049101</v>
+        <v>0.633556262105763</v>
       </c>
     </row>
     <row r="37" s="34" customFormat="1" spans="1:15">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="H37" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H37</f>
-        <v>0.157025523348173</v>
+        <v>0.0754411631980625</v>
       </c>
       <c r="I37" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I37</f>
@@ -25422,7 +25422,7 @@
       </c>
       <c r="O37" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O37</f>
-        <v>0.170161205074302</v>
+        <v>0.164584547904754</v>
       </c>
     </row>
     <row r="38" s="34" customFormat="1" spans="1:15">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="H39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H39</f>
-        <v>1652</v>
+        <v>4008</v>
       </c>
       <c r="I39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I39</f>
@@ -25546,7 +25546,7 @@
       </c>
       <c r="O39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O39</f>
-        <v>35727</v>
+        <v>38083</v>
       </c>
     </row>
     <row r="40" s="34" customFormat="1" spans="1:15">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="H40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H40</f>
-        <v>541</v>
+        <v>1324</v>
       </c>
       <c r="I40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I40</f>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="O40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O40</f>
-        <v>11731</v>
+        <v>12514</v>
       </c>
     </row>
     <row r="41" s="34" customFormat="1" spans="1:15">
@@ -25642,7 +25642,7 @@
       </c>
       <c r="H41" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H41</f>
-        <v>669524.052</v>
+        <v>1634730.252</v>
       </c>
       <c r="I41" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I41</f>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="O41" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O41</f>
-        <v>13363826.5986</v>
+        <v>14329032.7986</v>
       </c>
     </row>
     <row r="42" s="34" customFormat="1" spans="1:15">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="H42" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H42</f>
-        <v>188985.7344</v>
+        <v>458423.5943</v>
       </c>
       <c r="I42" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I42</f>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="O42" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O42</f>
-        <v>3914571.0939</v>
+        <v>4184008.9538</v>
       </c>
     </row>
     <row r="43" s="34" customFormat="1" spans="1:15">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="H43" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H43</f>
-        <v>0.282268775610768</v>
+        <v>0.280427669176089</v>
       </c>
       <c r="I43" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I43</f>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="O43" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O43</f>
-        <v>0.292922918822524</v>
+        <v>0.291995210884631</v>
       </c>
     </row>
     <row r="44" s="34" customFormat="1" spans="1:15">
@@ -25828,7 +25828,7 @@
       </c>
       <c r="H44" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H44</f>
-        <v>0.672518159806295</v>
+        <v>0.669660678642715</v>
       </c>
       <c r="I44" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I44</f>
@@ -25856,7 +25856,7 @@
       </c>
       <c r="O44" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O44</f>
-        <v>0.671648892994094</v>
+        <v>0.671401937872542</v>
       </c>
     </row>
     <row r="45" s="34" customFormat="1" spans="1:15">
@@ -25890,7 +25890,7 @@
       </c>
       <c r="H45" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H45</f>
-        <v>0.160248762141488</v>
+        <v>0.0660627646058313</v>
       </c>
       <c r="I45" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I45</f>
@@ -25918,7 +25918,7 @@
       </c>
       <c r="O45" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O45</f>
-        <v>0.154207548035254</v>
+        <v>0.144277035892035</v>
       </c>
     </row>
     <row r="46" s="34" customFormat="1" spans="1:15">
@@ -26014,7 +26014,7 @@
       </c>
       <c r="H47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H47</f>
-        <v>2443</v>
+        <v>5471</v>
       </c>
       <c r="I47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I47</f>
@@ -26042,7 +26042,7 @@
       </c>
       <c r="O47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O47</f>
-        <v>31244</v>
+        <v>34272</v>
       </c>
     </row>
     <row r="48" s="34" customFormat="1" spans="1:15">
@@ -26076,7 +26076,7 @@
       </c>
       <c r="H48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H48</f>
-        <v>936</v>
+        <v>1994</v>
       </c>
       <c r="I48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I48</f>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="O48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O48</f>
-        <v>10912</v>
+        <v>11970</v>
       </c>
     </row>
     <row r="49" s="34" customFormat="1" spans="1:15">
@@ -26138,7 +26138,7 @@
       </c>
       <c r="H49" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H49</f>
-        <v>1008220.752</v>
+        <v>2274149.9952</v>
       </c>
       <c r="I49" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I49</f>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="O49" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O49</f>
-        <v>12110705.2374</v>
+        <v>13376634.4806</v>
       </c>
     </row>
     <row r="50" s="34" customFormat="1" spans="1:15">
@@ -26200,7 +26200,7 @@
       </c>
       <c r="H50" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H50</f>
-        <v>328535.4711</v>
+        <v>692555.2367</v>
       </c>
       <c r="I50" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I50</f>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="O50" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O50</f>
-        <v>3854966.5763</v>
+        <v>4218986.3419</v>
       </c>
     </row>
     <row r="51" s="34" customFormat="1" spans="1:15">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="H51" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H51</f>
-        <v>0.32585668411237</v>
+        <v>0.304533666715811</v>
       </c>
       <c r="I51" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I51</f>
@@ -26290,7 +26290,7 @@
       </c>
       <c r="O51" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O51</f>
-        <v>0.318310659927151</v>
+        <v>0.315399688017098</v>
       </c>
     </row>
     <row r="52" s="34" customFormat="1" spans="1:15">
@@ -26324,7 +26324,7 @@
       </c>
       <c r="H52" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H52</f>
-        <v>0.616864510847319</v>
+        <v>0.635532809358435</v>
       </c>
       <c r="I52" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I52</f>
@@ -26352,7 +26352,7 @@
       </c>
       <c r="O52" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O52</f>
-        <v>0.650748943797209</v>
+        <v>0.650735294117647</v>
       </c>
     </row>
     <row r="53" s="34" customFormat="1" spans="1:15">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="H53" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H53</f>
-        <v>0.21596133824589</v>
+        <v>0.102448088239255</v>
       </c>
       <c r="I53" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I53</f>
@@ -26414,7 +26414,7 @@
       </c>
       <c r="O53" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O53</f>
-        <v>0.182638180141048</v>
+        <v>0.166879914496933</v>
       </c>
     </row>
     <row r="54" s="34" customFormat="1" spans="1:15">
@@ -26510,7 +26510,7 @@
       </c>
       <c r="H55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H55</f>
-        <v>300</v>
+        <v>623</v>
       </c>
       <c r="I55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I55</f>
@@ -26538,7 +26538,7 @@
       </c>
       <c r="O55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O55</f>
-        <v>16876</v>
+        <v>17199</v>
       </c>
     </row>
     <row r="56" s="34" customFormat="1" spans="1:15">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="H56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H56</f>
-        <v>120</v>
+        <v>255</v>
       </c>
       <c r="I56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I56</f>
@@ -26600,7 +26600,7 @@
       </c>
       <c r="O56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O56</f>
-        <v>6146</v>
+        <v>6281</v>
       </c>
     </row>
     <row r="57" s="34" customFormat="1" spans="1:15">
@@ -26634,7 +26634,7 @@
       </c>
       <c r="H57" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H57</f>
-        <v>115087.674</v>
+        <v>239297.004</v>
       </c>
       <c r="I57" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I57</f>
@@ -26662,7 +26662,7 @@
       </c>
       <c r="O57" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O57</f>
-        <v>5920594.7853</v>
+        <v>6044804.1153</v>
       </c>
     </row>
     <row r="58" s="34" customFormat="1" spans="1:15">
@@ -26696,7 +26696,7 @@
       </c>
       <c r="H58" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H58</f>
-        <v>36255.7421</v>
+        <v>80592.046</v>
       </c>
       <c r="I58" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I58</f>
@@ -26724,7 +26724,7 @@
       </c>
       <c r="O58" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O58</f>
-        <v>2341481.8418</v>
+        <v>2385818.1457</v>
       </c>
     </row>
     <row r="59" s="34" customFormat="1" spans="1:15">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="H59" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H59</f>
-        <v>0.315027151387211</v>
+        <v>0.336786690400854</v>
       </c>
       <c r="I59" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I59</f>
@@ -26786,7 +26786,7 @@
       </c>
       <c r="O59" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O59</f>
-        <v>0.395480847230682</v>
+        <v>0.394689075144926</v>
       </c>
     </row>
     <row r="60" s="34" customFormat="1" spans="1:15">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="H60" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H60</f>
-        <v>0.6</v>
+        <v>0.590690208667737</v>
       </c>
       <c r="I60" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I60</f>
@@ -26848,7 +26848,7 @@
       </c>
       <c r="O60" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O60</f>
-        <v>0.635814173974875</v>
+        <v>0.634804349090063</v>
       </c>
     </row>
     <row r="61" s="34" customFormat="1" spans="1:15">
@@ -26882,7 +26882,7 @@
       </c>
       <c r="H61" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H61</f>
-        <v>0.186738695937491</v>
+        <v>0.0840076699380482</v>
       </c>
       <c r="I61" s="5" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I61</f>
@@ -26910,7 +26910,7 @@
       </c>
       <c r="O61" s="5">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O61</f>
-        <v>0.0599382055818597</v>
+        <v>0.0588243576958892</v>
       </c>
     </row>
     <row r="62" s="34" customFormat="1" spans="1:15">
@@ -33710,7 +33710,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7124a651-0157-459a-9e6a-1ba4452143cd}</x14:id>
+          <x14:id>{e78ee4e9-1c6f-401e-a013-bd763d7b10e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33724,7 +33724,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4c703241-81f0-47f2-81ae-d461faa58e4e}</x14:id>
+          <x14:id>{33efdd23-d786-44a6-bdb1-b60c5a640d8c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33738,7 +33738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3b07c1b0-a25e-44f4-9d6f-f340c65c198f}</x14:id>
+          <x14:id>{0cc7defe-e0b2-4cb4-9661-01258005a83d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33752,7 +33752,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6de6c300-3678-4031-a1c2-f078cfdb2670}</x14:id>
+          <x14:id>{9402a508-f0d6-4af5-877c-631c6ab406b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33766,7 +33766,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1ffff48-79b6-49e6-bb97-f330edccfa4b}</x14:id>
+          <x14:id>{0af5f894-ea27-4662-86f3-5eade62c34d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33780,7 +33780,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a7c7e8a-8a4a-4d92-9d10-3be28d6e749c}</x14:id>
+          <x14:id>{4b4e7d0a-32bb-41c4-8e89-b1708ac2b602}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33800,7 +33800,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{889e5926-3ddd-454d-aed4-d09c16d744d9}</x14:id>
+          <x14:id>{7dcedb44-3207-45cf-a0c7-e48a7a87e4fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33814,7 +33814,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a2376cf5-01f0-43a7-96a4-67114b5fba16}</x14:id>
+          <x14:id>{b5bbf0ed-4b77-4cdf-a8b8-bc4616c042b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33828,7 +33828,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee304a73-7cbc-4e5d-9409-7ff1aa3e00e7}</x14:id>
+          <x14:id>{52916512-43ca-4df9-a21c-bec59545dfac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33842,7 +33842,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6aeeb44-80d7-48d7-9ffd-3c8b1ecb3905}</x14:id>
+          <x14:id>{f10bf53e-fd4d-4acc-a2d2-5d9af10ee285}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33856,7 +33856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38613a61-5887-4b0a-98f4-f99a7c217d1a}</x14:id>
+          <x14:id>{e3a1cb6b-1d7e-4413-813d-58dec932321d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33870,7 +33870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6cd7c06d-f711-4e5d-9924-2199b681cf97}</x14:id>
+          <x14:id>{c48a587a-f3ed-4e58-96c4-ae65739c141a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33892,7 +33892,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{458bed35-84d8-4cb8-a390-2836c61d457e}</x14:id>
+          <x14:id>{87c176eb-508f-457c-a026-3fd4884974b4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33922,7 +33922,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{14e187db-b84d-462f-9005-dec2ee964551}</x14:id>
+          <x14:id>{8305bfb3-a80b-4b1f-a002-88f67074cae2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33952,7 +33952,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a6151bd-1a83-44f1-b173-c1084e77113e}</x14:id>
+          <x14:id>{40b2e2ac-ef60-470e-ac18-9bf0603c8d26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -33982,7 +33982,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99f5d465-b29a-4073-a346-b66b1f7838fc}</x14:id>
+          <x14:id>{c02afdf1-e0d0-4736-8a8c-149bed587344}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34012,7 +34012,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac6a121b-f5cb-42a6-8818-de89bbe807bc}</x14:id>
+          <x14:id>{f4968356-d37a-4c72-b293-62eb69fd572b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34042,7 +34042,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{297e59c6-369f-4ce3-a5e8-1d1c43074593}</x14:id>
+          <x14:id>{a3420b72-84ac-4e0f-82f7-2c7bcc525723}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34064,7 +34064,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{247356c1-d4b8-417a-9a45-63af7874bd89}</x14:id>
+          <x14:id>{2df1ce4d-d06b-4e46-aac2-b538509bbbe0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34086,7 +34086,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e057ea98-c8ef-4641-9379-c00c423c66f1}</x14:id>
+          <x14:id>{8e22891e-a2a8-43bf-9ef9-d8f043f3a97e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34108,7 +34108,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c656014a-0790-494a-b4f1-1cb7a323b2b1}</x14:id>
+          <x14:id>{3fb3180f-3770-4a95-9c64-f1e57484681c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34130,7 +34130,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{de7bed76-92cf-4d03-a83a-631ebfd57aff}</x14:id>
+          <x14:id>{94887e9d-2dc3-478f-95d4-8bee5edf1a83}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34152,7 +34152,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1c3defc8-2124-4b49-ba34-6c7337f5de97}</x14:id>
+          <x14:id>{0224471f-e5c2-4540-abfc-c2e282fdf9f3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34174,7 +34174,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a36d024f-4965-47a6-b7b7-8ab724fae106}</x14:id>
+          <x14:id>{4fd110e8-8d8b-4aa4-9b12-282cfb400073}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34196,7 +34196,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71e8d685-bf1b-47cb-877a-afceca85a201}</x14:id>
+          <x14:id>{889570df-f87b-48e9-b297-9d08b4cee429}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34218,7 +34218,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{878d29c9-8af7-4ea4-9eb1-e09ad7f35fdf}</x14:id>
+          <x14:id>{c87331b0-ba4f-421d-8e40-a69aedc33bec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34240,7 +34240,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7862722d-dfcf-4b74-b996-94a142807632}</x14:id>
+          <x14:id>{aec011f9-9be1-4a74-8f35-dd683eb6dffb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34262,7 +34262,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e165a39d-fa5b-4b33-8939-d03a201edab1}</x14:id>
+          <x14:id>{d0088318-d305-4ce8-96c0-158b822672b4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34284,7 +34284,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e977de6-5ef0-45b9-a3a3-f36d0a6c2477}</x14:id>
+          <x14:id>{79c3287e-d980-4234-94a7-f857e465d73a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34306,7 +34306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ad30ffb-405b-4890-b57e-842079969af8}</x14:id>
+          <x14:id>{d632c1ac-3307-45cb-82d4-18844ac2b7d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34328,7 +34328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a5caa7ea-bb57-416b-a34c-8b4f50c219fe}</x14:id>
+          <x14:id>{b61735a3-2b81-4b76-9eb6-e4a40d78dbd3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34350,7 +34350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7e24500-1439-4966-b503-435f1cefc1c9}</x14:id>
+          <x14:id>{3e1e4756-59a1-4b8d-8ca4-3703e3cbe007}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -34369,7 +34369,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7124a651-0157-459a-9e6a-1ba4452143cd}">
+          <x14:cfRule type="dataBar" id="{e78ee4e9-1c6f-401e-a013-bd763d7b10e8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34382,7 +34382,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4c703241-81f0-47f2-81ae-d461faa58e4e}">
+          <x14:cfRule type="dataBar" id="{33efdd23-d786-44a6-bdb1-b60c5a640d8c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34395,7 +34395,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3b07c1b0-a25e-44f4-9d6f-f340c65c198f}">
+          <x14:cfRule type="dataBar" id="{0cc7defe-e0b2-4cb4-9661-01258005a83d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34408,7 +34408,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6de6c300-3678-4031-a1c2-f078cfdb2670}">
+          <x14:cfRule type="dataBar" id="{9402a508-f0d6-4af5-877c-631c6ab406b9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34421,7 +34421,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d1ffff48-79b6-49e6-bb97-f330edccfa4b}">
+          <x14:cfRule type="dataBar" id="{0af5f894-ea27-4662-86f3-5eade62c34d3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34434,7 +34434,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a7c7e8a-8a4a-4d92-9d10-3be28d6e749c}">
+          <x14:cfRule type="dataBar" id="{4b4e7d0a-32bb-41c4-8e89-b1708ac2b602}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34447,7 +34447,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{889e5926-3ddd-454d-aed4-d09c16d744d9}">
+          <x14:cfRule type="dataBar" id="{7dcedb44-3207-45cf-a0c7-e48a7a87e4fe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34460,7 +34460,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a2376cf5-01f0-43a7-96a4-67114b5fba16}">
+          <x14:cfRule type="dataBar" id="{b5bbf0ed-4b77-4cdf-a8b8-bc4616c042b7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34473,7 +34473,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee304a73-7cbc-4e5d-9409-7ff1aa3e00e7}">
+          <x14:cfRule type="dataBar" id="{52916512-43ca-4df9-a21c-bec59545dfac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34486,7 +34486,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c6aeeb44-80d7-48d7-9ffd-3c8b1ecb3905}">
+          <x14:cfRule type="dataBar" id="{f10bf53e-fd4d-4acc-a2d2-5d9af10ee285}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34499,7 +34499,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38613a61-5887-4b0a-98f4-f99a7c217d1a}">
+          <x14:cfRule type="dataBar" id="{e3a1cb6b-1d7e-4413-813d-58dec932321d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34512,7 +34512,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6cd7c06d-f711-4e5d-9924-2199b681cf97}">
+          <x14:cfRule type="dataBar" id="{c48a587a-f3ed-4e58-96c4-ae65739c141a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34525,7 +34525,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{458bed35-84d8-4cb8-a390-2836c61d457e}">
+          <x14:cfRule type="dataBar" id="{87c176eb-508f-457c-a026-3fd4884974b4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34538,7 +34538,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{14e187db-b84d-462f-9005-dec2ee964551}">
+          <x14:cfRule type="dataBar" id="{8305bfb3-a80b-4b1f-a002-88f67074cae2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34551,7 +34551,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4a6151bd-1a83-44f1-b173-c1084e77113e}">
+          <x14:cfRule type="dataBar" id="{40b2e2ac-ef60-470e-ac18-9bf0603c8d26}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34564,7 +34564,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99f5d465-b29a-4073-a346-b66b1f7838fc}">
+          <x14:cfRule type="dataBar" id="{c02afdf1-e0d0-4736-8a8c-149bed587344}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34577,7 +34577,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ac6a121b-f5cb-42a6-8818-de89bbe807bc}">
+          <x14:cfRule type="dataBar" id="{f4968356-d37a-4c72-b293-62eb69fd572b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34590,7 +34590,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{297e59c6-369f-4ce3-a5e8-1d1c43074593}">
+          <x14:cfRule type="dataBar" id="{a3420b72-84ac-4e0f-82f7-2c7bcc525723}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34603,7 +34603,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{247356c1-d4b8-417a-9a45-63af7874bd89}">
+          <x14:cfRule type="dataBar" id="{2df1ce4d-d06b-4e46-aac2-b538509bbbe0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34616,7 +34616,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e057ea98-c8ef-4641-9379-c00c423c66f1}">
+          <x14:cfRule type="dataBar" id="{8e22891e-a2a8-43bf-9ef9-d8f043f3a97e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34629,7 +34629,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c656014a-0790-494a-b4f1-1cb7a323b2b1}">
+          <x14:cfRule type="dataBar" id="{3fb3180f-3770-4a95-9c64-f1e57484681c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34642,7 +34642,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{de7bed76-92cf-4d03-a83a-631ebfd57aff}">
+          <x14:cfRule type="dataBar" id="{94887e9d-2dc3-478f-95d4-8bee5edf1a83}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34655,7 +34655,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1c3defc8-2124-4b49-ba34-6c7337f5de97}">
+          <x14:cfRule type="dataBar" id="{0224471f-e5c2-4540-abfc-c2e282fdf9f3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34668,7 +34668,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a36d024f-4965-47a6-b7b7-8ab724fae106}">
+          <x14:cfRule type="dataBar" id="{4fd110e8-8d8b-4aa4-9b12-282cfb400073}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34681,7 +34681,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71e8d685-bf1b-47cb-877a-afceca85a201}">
+          <x14:cfRule type="dataBar" id="{889570df-f87b-48e9-b297-9d08b4cee429}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34694,7 +34694,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{878d29c9-8af7-4ea4-9eb1-e09ad7f35fdf}">
+          <x14:cfRule type="dataBar" id="{c87331b0-ba4f-421d-8e40-a69aedc33bec}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34707,7 +34707,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7862722d-dfcf-4b74-b996-94a142807632}">
+          <x14:cfRule type="dataBar" id="{aec011f9-9be1-4a74-8f35-dd683eb6dffb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34720,7 +34720,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e165a39d-fa5b-4b33-8939-d03a201edab1}">
+          <x14:cfRule type="dataBar" id="{d0088318-d305-4ce8-96c0-158b822672b4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34733,7 +34733,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e977de6-5ef0-45b9-a3a3-f36d0a6c2477}">
+          <x14:cfRule type="dataBar" id="{79c3287e-d980-4234-94a7-f857e465d73a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34746,7 +34746,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ad30ffb-405b-4890-b57e-842079969af8}">
+          <x14:cfRule type="dataBar" id="{d632c1ac-3307-45cb-82d4-18844ac2b7d6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34759,7 +34759,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a5caa7ea-bb57-416b-a34c-8b4f50c219fe}">
+          <x14:cfRule type="dataBar" id="{b61735a3-2b81-4b76-9eb6-e4a40d78dbd3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -34772,7 +34772,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b7e24500-1439-4966-b503-435f1cefc1c9}">
+          <x14:cfRule type="dataBar" id="{3e1e4756-59a1-4b8d-8ca4-3703e3cbe007}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -7292,22 +7292,22 @@
             <v>退款率</v>
           </cell>
           <cell r="C26">
-            <v>0.625232471710164</v>
+            <v>0.374767528289836</v>
           </cell>
           <cell r="D26">
-            <v>0.690179946114134</v>
+            <v>0.309820053885866</v>
           </cell>
           <cell r="E26">
-            <v>0.664743278016356</v>
+            <v>0.335256721983644</v>
           </cell>
           <cell r="F26">
-            <v>0.679197248320452</v>
+            <v>0.320802751679548</v>
           </cell>
           <cell r="G26">
-            <v>0.69655609965157</v>
+            <v>0.30344390034843</v>
           </cell>
           <cell r="H26">
-            <v>0.710031741308227</v>
+            <v>0.289968258691773</v>
           </cell>
           <cell r="I26" t="e">
             <v>#DIV/0!</v>
@@ -7328,7 +7328,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.676268791944235</v>
+            <v>0.323731208055765</v>
           </cell>
         </row>
         <row r="27">
@@ -22724,7 +22724,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7ce7645b-7cd0-4ca3-9280-f9ef7aecca07}</x14:id>
+          <x14:id>{b872c64c-12e3-4cce-ab2f-1ca3b451e7b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22738,7 +22738,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e851dda-5ece-4eb6-8c46-2482be816c27}</x14:id>
+          <x14:id>{7ff55371-9553-4015-ae2f-2325a2867974}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22752,7 +22752,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{575c5d7a-16d8-4dd6-956a-a1bd6f021585}</x14:id>
+          <x14:id>{78602879-512e-4311-a9e8-7112690b048d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22766,7 +22766,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b80a1623-00f8-4fb7-bde6-7c177ef50d0c}</x14:id>
+          <x14:id>{d08ef6f7-3aae-4c25-bc37-0809b113a51d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22780,7 +22780,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ff376b94-14ae-4c81-8845-aca9316d98dd}</x14:id>
+          <x14:id>{6b297416-6aee-4244-81c2-2ceb9cedbb5a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22794,7 +22794,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1f98c85-4e88-461f-8201-45ae995fc2fe}</x14:id>
+          <x14:id>{fb13ca75-2faf-4ab8-bc43-59e1b1ec4e77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22808,7 +22808,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea6ff061-cc3f-49b3-aa17-364de1aa3cf4}</x14:id>
+          <x14:id>{6e69cde2-10f9-4f68-94ad-2cad15004b42}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22822,7 +22822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac48d8af-2e73-4711-b09e-069b55af57da}</x14:id>
+          <x14:id>{8041a16f-0df3-4155-8ffd-f3a972ea0f6b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22842,7 +22842,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2507a742-637f-4f68-85c8-67efb3da626b}</x14:id>
+          <x14:id>{c96e40bf-1e0d-4b9c-a0e5-66c553c878ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22870,7 +22870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8635eb75-1acb-40a7-936b-3cdf38a57c84}</x14:id>
+          <x14:id>{51f2045f-5826-40a1-adcf-0a038bbb7e75}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22890,7 +22890,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec0c1b64-1dc9-4bea-8bc7-f4a3057fd04a}</x14:id>
+          <x14:id>{9f073439-ac15-4c6d-a923-2f1d3bbe461f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22918,7 +22918,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{96c00501-eb47-4236-9838-d9ea877f2a9c}</x14:id>
+          <x14:id>{99b8312b-3c63-449c-885b-b164ea3d712d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22938,7 +22938,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be3f9d72-8330-41a6-b58c-6df266b15403}</x14:id>
+          <x14:id>{457e41ee-2d7d-42fa-8ff7-fdebc014192b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22966,7 +22966,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17897369-b1ab-468c-9f1d-ce1335cca251}</x14:id>
+          <x14:id>{05ab6487-50de-4c1b-9009-c3263d5785db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -22986,7 +22986,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{751625bb-2b47-45cb-a712-d4db724ea364}</x14:id>
+          <x14:id>{da0e4260-45fc-42a7-a6a2-919d5cf40da3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23014,7 +23014,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3251b6a9-c5a8-4058-9e94-4e34408437c3}</x14:id>
+          <x14:id>{6d9b8a84-2df3-4ce5-9f0b-73f3d0c711c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23034,7 +23034,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2cffbc49-ab82-407b-a03e-3712d4bb1dce}</x14:id>
+          <x14:id>{655fbc87-268d-4db4-bd24-55091af48252}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23062,7 +23062,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27a6319b-abb8-48e0-aac4-b489035c9ee7}</x14:id>
+          <x14:id>{0b0fe7d9-b4be-4a7a-b278-4246c6a1c0c1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23124,7 +23124,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f77f2a22-b1b3-42c0-b423-19aa4aa80723}</x14:id>
+          <x14:id>{0c81a738-8ad7-4d86-b0f1-3616f3ae4024}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23154,7 +23154,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b17a593f-d8d5-4de0-a041-da2350eb75c2}</x14:id>
+          <x14:id>{5a4ca9e7-dda6-4daa-a9b2-ca5917608528}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23176,7 +23176,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89f5cfd5-4884-43c4-a11d-340944c430db}</x14:id>
+          <x14:id>{f59c5e95-39e1-4b80-9f3f-66e991f00ff6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23196,7 +23196,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89cd0e05-06d9-4029-a81a-d7cbf25b0f62}</x14:id>
+          <x14:id>{cfeac9b2-0f79-444f-97f2-1015ada81a86}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23218,7 +23218,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{21a6de1c-8ec2-4844-a0ed-f5db01ba2661}</x14:id>
+          <x14:id>{d7f4a044-d7a1-4e32-bd3d-012644f0babf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23238,7 +23238,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ae3530a-f58b-4467-b458-5de56828ff10}</x14:id>
+          <x14:id>{2b596476-e4a2-4515-86ea-53c97432921e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23260,7 +23260,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9a0fbe52-2c5b-4fcb-b685-047ea0b20816}</x14:id>
+          <x14:id>{1be75ad2-cec1-4582-b813-e94ade5c99ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23280,7 +23280,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{753d7afd-edf9-4bd6-89c5-6ec81e6c4229}</x14:id>
+          <x14:id>{e407bb4a-8e24-4b6d-ab86-a87d9fd2d4b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23302,7 +23302,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5edb7330-b26c-4075-a232-25be8e8cc68b}</x14:id>
+          <x14:id>{0c67f6ad-d5fc-444a-a70c-2897992d5669}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23322,7 +23322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{292a446b-ba24-4bab-843c-a5fbb688997b}</x14:id>
+          <x14:id>{3a612521-7f0b-4921-a6f9-4abbe75461fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23350,7 +23350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ef92500e-8563-471c-964b-89c932f53a1a}</x14:id>
+          <x14:id>{499bad1a-07f5-491b-8075-6d1501785dec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23364,7 +23364,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b810d9e8-6d0c-4533-a711-3c64c3863874}</x14:id>
+          <x14:id>{00368a15-52d4-4046-93e4-534f9f578c41}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23394,7 +23394,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3d47433c-e2f5-431a-8c0f-f8b2a41ff1d9}</x14:id>
+          <x14:id>{4e798606-5cb9-473b-886d-0f0a554ea831}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23416,7 +23416,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d2ea1b57-f032-4f9b-86ad-2a167e85c957}</x14:id>
+          <x14:id>{740360f2-0c97-466b-bc8a-702143694556}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23438,7 +23438,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{22fa8dff-a835-4b54-aa83-f90e6a778d85}</x14:id>
+          <x14:id>{8078e692-ef04-43ed-bed8-a37701ea571f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23460,7 +23460,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a0e58f7-ee95-4052-b758-ef9f0446d1f8}</x14:id>
+          <x14:id>{ab691d39-aaa4-4242-832f-b0866f519d9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23482,7 +23482,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b0851ef-1803-4236-b008-a69a1f96fd24}</x14:id>
+          <x14:id>{f896f68a-3cde-4418-bf17-cc3dc3af4761}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23504,7 +23504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8315cb9c-fa65-4603-9057-388a766fdf3b}</x14:id>
+          <x14:id>{ede95700-d92a-442b-a75a-a1bce64b7594}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23526,7 +23526,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31b0d46f-ea5d-4f53-b22d-1b84c4bc0a52}</x14:id>
+          <x14:id>{2b15d18d-b729-4a0a-9f8e-c2c51539bb89}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23548,7 +23548,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53cd2416-08e9-4860-9b04-1f1a66c0da75}</x14:id>
+          <x14:id>{aa5671ae-dd89-43b1-a4fc-12912403dbeb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23570,7 +23570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6a3cbe3-8b42-431e-b630-f44cc4873412}</x14:id>
+          <x14:id>{449cb61f-61a5-4fff-99a1-a85211ee049d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23592,7 +23592,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d3536e1-9566-4302-b14c-f01c6c8dd7a1}</x14:id>
+          <x14:id>{57f36934-ab01-4703-8258-b4a1197adb92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23614,7 +23614,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29ed76dc-050f-4a49-b5be-8baec9175a27}</x14:id>
+          <x14:id>{1cdcde26-5e9d-412d-851e-23c87850c293}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23636,7 +23636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3cb07285-cd12-42d1-bf6d-b3afd3669545}</x14:id>
+          <x14:id>{94e7e406-3180-4a48-8de3-e7680abaccb7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23658,7 +23658,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee09c0cd-0229-4fb0-b44c-057f1047b260}</x14:id>
+          <x14:id>{514877e2-e8a6-45d9-adb2-7761b7425d1a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23677,7 +23677,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7ce7645b-7cd0-4ca3-9280-f9ef7aecca07}">
+          <x14:cfRule type="dataBar" id="{b872c64c-12e3-4cce-ab2f-1ca3b451e7b0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23690,7 +23690,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e851dda-5ece-4eb6-8c46-2482be816c27}">
+          <x14:cfRule type="dataBar" id="{7ff55371-9553-4015-ae2f-2325a2867974}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23703,7 +23703,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{575c5d7a-16d8-4dd6-956a-a1bd6f021585}">
+          <x14:cfRule type="dataBar" id="{78602879-512e-4311-a9e8-7112690b048d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23716,7 +23716,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b80a1623-00f8-4fb7-bde6-7c177ef50d0c}">
+          <x14:cfRule type="dataBar" id="{d08ef6f7-3aae-4c25-bc37-0809b113a51d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23729,7 +23729,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ff376b94-14ae-4c81-8845-aca9316d98dd}">
+          <x14:cfRule type="dataBar" id="{6b297416-6aee-4244-81c2-2ceb9cedbb5a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23742,7 +23742,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d1f98c85-4e88-461f-8201-45ae995fc2fe}">
+          <x14:cfRule type="dataBar" id="{fb13ca75-2faf-4ab8-bc43-59e1b1ec4e77}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23755,7 +23755,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ea6ff061-cc3f-49b3-aa17-364de1aa3cf4}">
+          <x14:cfRule type="dataBar" id="{6e69cde2-10f9-4f68-94ad-2cad15004b42}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23768,7 +23768,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ac48d8af-2e73-4711-b09e-069b55af57da}">
+          <x14:cfRule type="dataBar" id="{8041a16f-0df3-4155-8ffd-f3a972ea0f6b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23781,7 +23781,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2507a742-637f-4f68-85c8-67efb3da626b}">
+          <x14:cfRule type="dataBar" id="{c96e40bf-1e0d-4b9c-a0e5-66c553c878ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23794,7 +23794,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8635eb75-1acb-40a7-936b-3cdf38a57c84}">
+          <x14:cfRule type="dataBar" id="{51f2045f-5826-40a1-adcf-0a038bbb7e75}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23807,7 +23807,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec0c1b64-1dc9-4bea-8bc7-f4a3057fd04a}">
+          <x14:cfRule type="dataBar" id="{9f073439-ac15-4c6d-a923-2f1d3bbe461f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23820,7 +23820,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{96c00501-eb47-4236-9838-d9ea877f2a9c}">
+          <x14:cfRule type="dataBar" id="{99b8312b-3c63-449c-885b-b164ea3d712d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23833,7 +23833,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{be3f9d72-8330-41a6-b58c-6df266b15403}">
+          <x14:cfRule type="dataBar" id="{457e41ee-2d7d-42fa-8ff7-fdebc014192b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23846,7 +23846,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17897369-b1ab-468c-9f1d-ce1335cca251}">
+          <x14:cfRule type="dataBar" id="{05ab6487-50de-4c1b-9009-c3263d5785db}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23859,7 +23859,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{751625bb-2b47-45cb-a712-d4db724ea364}">
+          <x14:cfRule type="dataBar" id="{da0e4260-45fc-42a7-a6a2-919d5cf40da3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23872,7 +23872,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3251b6a9-c5a8-4058-9e94-4e34408437c3}">
+          <x14:cfRule type="dataBar" id="{6d9b8a84-2df3-4ce5-9f0b-73f3d0c711c2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23885,7 +23885,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2cffbc49-ab82-407b-a03e-3712d4bb1dce}">
+          <x14:cfRule type="dataBar" id="{655fbc87-268d-4db4-bd24-55091af48252}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23898,7 +23898,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{27a6319b-abb8-48e0-aac4-b489035c9ee7}">
+          <x14:cfRule type="dataBar" id="{0b0fe7d9-b4be-4a7a-b278-4246c6a1c0c1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23911,7 +23911,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f77f2a22-b1b3-42c0-b423-19aa4aa80723}">
+          <x14:cfRule type="dataBar" id="{0c81a738-8ad7-4d86-b0f1-3616f3ae4024}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23924,7 +23924,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b17a593f-d8d5-4de0-a041-da2350eb75c2}">
+          <x14:cfRule type="dataBar" id="{5a4ca9e7-dda6-4daa-a9b2-ca5917608528}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23937,7 +23937,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{89f5cfd5-4884-43c4-a11d-340944c430db}">
+          <x14:cfRule type="dataBar" id="{f59c5e95-39e1-4b80-9f3f-66e991f00ff6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23950,7 +23950,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{89cd0e05-06d9-4029-a81a-d7cbf25b0f62}">
+          <x14:cfRule type="dataBar" id="{cfeac9b2-0f79-444f-97f2-1015ada81a86}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23963,7 +23963,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{21a6de1c-8ec2-4844-a0ed-f5db01ba2661}">
+          <x14:cfRule type="dataBar" id="{d7f4a044-d7a1-4e32-bd3d-012644f0babf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23976,7 +23976,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9ae3530a-f58b-4467-b458-5de56828ff10}">
+          <x14:cfRule type="dataBar" id="{2b596476-e4a2-4515-86ea-53c97432921e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -23989,7 +23989,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9a0fbe52-2c5b-4fcb-b685-047ea0b20816}">
+          <x14:cfRule type="dataBar" id="{1be75ad2-cec1-4582-b813-e94ade5c99ac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24002,7 +24002,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{753d7afd-edf9-4bd6-89c5-6ec81e6c4229}">
+          <x14:cfRule type="dataBar" id="{e407bb4a-8e24-4b6d-ab86-a87d9fd2d4b0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24015,7 +24015,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5edb7330-b26c-4075-a232-25be8e8cc68b}">
+          <x14:cfRule type="dataBar" id="{0c67f6ad-d5fc-444a-a70c-2897992d5669}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24028,7 +24028,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{292a446b-ba24-4bab-843c-a5fbb688997b}">
+          <x14:cfRule type="dataBar" id="{3a612521-7f0b-4921-a6f9-4abbe75461fe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24041,7 +24041,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ef92500e-8563-471c-964b-89c932f53a1a}">
+          <x14:cfRule type="dataBar" id="{499bad1a-07f5-491b-8075-6d1501785dec}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24054,7 +24054,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b810d9e8-6d0c-4533-a711-3c64c3863874}">
+          <x14:cfRule type="dataBar" id="{00368a15-52d4-4046-93e4-534f9f578c41}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24067,7 +24067,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3d47433c-e2f5-431a-8c0f-f8b2a41ff1d9}">
+          <x14:cfRule type="dataBar" id="{4e798606-5cb9-473b-886d-0f0a554ea831}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24080,7 +24080,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d2ea1b57-f032-4f9b-86ad-2a167e85c957}">
+          <x14:cfRule type="dataBar" id="{740360f2-0c97-466b-bc8a-702143694556}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24093,7 +24093,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{22fa8dff-a835-4b54-aa83-f90e6a778d85}">
+          <x14:cfRule type="dataBar" id="{8078e692-ef04-43ed-bed8-a37701ea571f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24106,7 +24106,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7a0e58f7-ee95-4052-b758-ef9f0446d1f8}">
+          <x14:cfRule type="dataBar" id="{ab691d39-aaa4-4242-832f-b0866f519d9d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24119,7 +24119,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b0851ef-1803-4236-b008-a69a1f96fd24}">
+          <x14:cfRule type="dataBar" id="{f896f68a-3cde-4418-bf17-cc3dc3af4761}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24132,7 +24132,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8315cb9c-fa65-4603-9057-388a766fdf3b}">
+          <x14:cfRule type="dataBar" id="{ede95700-d92a-442b-a75a-a1bce64b7594}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24145,7 +24145,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{31b0d46f-ea5d-4f53-b22d-1b84c4bc0a52}">
+          <x14:cfRule type="dataBar" id="{2b15d18d-b729-4a0a-9f8e-c2c51539bb89}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24158,7 +24158,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{53cd2416-08e9-4860-9b04-1f1a66c0da75}">
+          <x14:cfRule type="dataBar" id="{aa5671ae-dd89-43b1-a4fc-12912403dbeb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24171,7 +24171,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d6a3cbe3-8b42-431e-b630-f44cc4873412}">
+          <x14:cfRule type="dataBar" id="{449cb61f-61a5-4fff-99a1-a85211ee049d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24184,7 +24184,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8d3536e1-9566-4302-b14c-f01c6c8dd7a1}">
+          <x14:cfRule type="dataBar" id="{57f36934-ab01-4703-8258-b4a1197adb92}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24197,7 +24197,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{29ed76dc-050f-4a49-b5be-8baec9175a27}">
+          <x14:cfRule type="dataBar" id="{1cdcde26-5e9d-412d-851e-23c87850c293}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24210,7 +24210,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3cb07285-cd12-42d1-bf6d-b3afd3669545}">
+          <x14:cfRule type="dataBar" id="{94e7e406-3180-4a48-8de3-e7680abaccb7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24223,7 +24223,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee09c0cd-0229-4fb0-b44c-057f1047b260}">
+          <x14:cfRule type="dataBar" id="{514877e2-e8a6-45d9-adb2-7761b7425d1a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -25949,7 +25949,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7c5a23e-d984-4ef5-bde4-a4cdbc621acb}</x14:id>
+          <x14:id>{ad007c32-fade-42f6-9d3f-313df3660137}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25963,7 +25963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d955fbb6-46cd-4c25-a648-b0312b8c4a27}</x14:id>
+          <x14:id>{21b9dcc2-df50-4c34-91b8-2d326c4a1ca2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25977,7 +25977,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6b32d5b2-b4df-4863-87cb-1b18877160a5}</x14:id>
+          <x14:id>{c0914063-48dc-4e1c-b461-35b29a84e5c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -25991,7 +25991,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{472b1fe7-60f7-4572-988c-5b4ba9fbb3b4}</x14:id>
+          <x14:id>{52263cd5-f817-4fd9-9008-b04efb084e2c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26005,7 +26005,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56d81bb3-a57b-40f0-9377-2bc05d094fa9}</x14:id>
+          <x14:id>{45e41527-f8b9-42a3-b1e2-ca8bb1598381}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26019,7 +26019,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23aec300-988c-4d4f-8cb6-3be164e5f17a}</x14:id>
+          <x14:id>{beee2490-368e-4805-b121-401963b071a8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26033,7 +26033,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63cc74fe-2944-40b5-8911-681ca88f6dca}</x14:id>
+          <x14:id>{07483e57-6d44-456d-88d8-8efc7a1a3c3d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26047,7 +26047,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5138c0d-8600-40f8-a32b-c2f3df06fe60}</x14:id>
+          <x14:id>{ac70fb4c-c4c2-4f88-9a6f-c0b2e46b5cd0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26061,7 +26061,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ceda0a2d-65d7-45d6-a151-acd475c4c882}</x14:id>
+          <x14:id>{d0713466-df98-4d27-a156-b843fac62d9f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26075,7 +26075,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4611c45c-8188-456f-b356-a345235d42eb}</x14:id>
+          <x14:id>{37d95f17-f83f-4a6a-ba02-27c3a63e9dce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26089,7 +26089,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e739075-d518-4997-81fe-ce5ca2c3edd1}</x14:id>
+          <x14:id>{949a9725-9300-4a06-9b63-5eaff3078158}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26125,7 +26125,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11cd355b-6e54-48c2-8f29-cfdbbb51f939}</x14:id>
+          <x14:id>{758e8271-4650-4e8e-89ed-ef06e607e28b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26144,7 +26144,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7c5a23e-d984-4ef5-bde4-a4cdbc621acb}">
+          <x14:cfRule type="dataBar" id="{ad007c32-fade-42f6-9d3f-313df3660137}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26157,7 +26157,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d955fbb6-46cd-4c25-a648-b0312b8c4a27}">
+          <x14:cfRule type="dataBar" id="{21b9dcc2-df50-4c34-91b8-2d326c4a1ca2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26170,7 +26170,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6b32d5b2-b4df-4863-87cb-1b18877160a5}">
+          <x14:cfRule type="dataBar" id="{c0914063-48dc-4e1c-b461-35b29a84e5c3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26183,7 +26183,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{472b1fe7-60f7-4572-988c-5b4ba9fbb3b4}">
+          <x14:cfRule type="dataBar" id="{52263cd5-f817-4fd9-9008-b04efb084e2c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26196,7 +26196,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{56d81bb3-a57b-40f0-9377-2bc05d094fa9}">
+          <x14:cfRule type="dataBar" id="{45e41527-f8b9-42a3-b1e2-ca8bb1598381}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26209,7 +26209,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23aec300-988c-4d4f-8cb6-3be164e5f17a}">
+          <x14:cfRule type="dataBar" id="{beee2490-368e-4805-b121-401963b071a8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26222,7 +26222,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{63cc74fe-2944-40b5-8911-681ca88f6dca}">
+          <x14:cfRule type="dataBar" id="{07483e57-6d44-456d-88d8-8efc7a1a3c3d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26235,7 +26235,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c5138c0d-8600-40f8-a32b-c2f3df06fe60}">
+          <x14:cfRule type="dataBar" id="{ac70fb4c-c4c2-4f88-9a6f-c0b2e46b5cd0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26248,7 +26248,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ceda0a2d-65d7-45d6-a151-acd475c4c882}">
+          <x14:cfRule type="dataBar" id="{d0713466-df98-4d27-a156-b843fac62d9f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26261,7 +26261,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4611c45c-8188-456f-b356-a345235d42eb}">
+          <x14:cfRule type="dataBar" id="{37d95f17-f83f-4a6a-ba02-27c3a63e9dce}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26274,7 +26274,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e739075-d518-4997-81fe-ce5ca2c3edd1}">
+          <x14:cfRule type="dataBar" id="{949a9725-9300-4a06-9b63-5eaff3078158}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26287,7 +26287,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11cd355b-6e54-48c2-8f29-cfdbbb51f939}">
+          <x14:cfRule type="dataBar" id="{758e8271-4650-4e8e-89ed-ef06e607e28b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -27833,27 +27833,27 @@
       </c>
       <c r="C26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!C26</f>
-        <v>0.625232471710164</v>
+        <v>0.374767528289836</v>
       </c>
       <c r="D26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!D26</f>
-        <v>0.690179946114134</v>
+        <v>0.309820053885866</v>
       </c>
       <c r="E26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!E26</f>
-        <v>0.664743278016356</v>
+        <v>0.335256721983644</v>
       </c>
       <c r="F26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!F26</f>
-        <v>0.679197248320452</v>
+        <v>0.320802751679548</v>
       </c>
       <c r="G26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!G26</f>
-        <v>0.69655609965157</v>
+        <v>0.30344390034843</v>
       </c>
       <c r="H26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H26</f>
-        <v>0.710031741308227</v>
+        <v>0.289968258691773</v>
       </c>
       <c r="I26" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I26</f>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="O26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O26</f>
-        <v>0.676268791944235</v>
+        <v>0.323731208055765</v>
       </c>
     </row>
     <row r="27" s="35" customFormat="1" spans="1:15">
@@ -36851,7 +36851,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eb614637-6bb6-443f-bee9-1cdfaaef30da}</x14:id>
+          <x14:id>{84108da1-5cc3-49c1-8398-a2aaa17d9b4a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36865,7 +36865,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b5edce7-6aac-419a-ad79-77d723f43b04}</x14:id>
+          <x14:id>{3ca34d9c-42c3-4d4d-af84-e3b5f0ab1b3f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36879,7 +36879,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{788715b8-035a-406b-95c2-fcfde0159e42}</x14:id>
+          <x14:id>{ed29e5e1-402e-422d-9dc0-9d06e811ac65}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36893,7 +36893,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f3f858c-d63e-42a9-9a7d-f9c9010ef415}</x14:id>
+          <x14:id>{c981b6ad-ff87-4519-b074-36239fee6be1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36907,7 +36907,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{849a9deb-cb62-4cdd-9e08-f336e95ae026}</x14:id>
+          <x14:id>{8777567c-3645-4492-94b5-f9ca63ee91ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36921,7 +36921,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b11367f-af2b-40fb-acc9-cc666a1c1010}</x14:id>
+          <x14:id>{6f0d8169-5b72-488f-87d8-053b9fd7afb6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36941,7 +36941,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee701bb4-70ac-443f-b398-db27f69de756}</x14:id>
+          <x14:id>{d6ca9055-fe36-476c-8621-07a7ddfaab1c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36955,7 +36955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9f15adc7-0abc-47bb-a791-fd9f9d3b4ea6}</x14:id>
+          <x14:id>{278d4d9e-8cf1-4f4f-b5f5-9441ba2fa1c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36969,7 +36969,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be1229b1-3e0c-4574-9db0-932de5a041b2}</x14:id>
+          <x14:id>{1e7a90f0-d48c-4046-80ce-7231d1868f18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36983,7 +36983,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a1f246a7-f483-40f6-9477-e51663908832}</x14:id>
+          <x14:id>{0155d8e8-3673-4ec0-b5f6-1ac5dd7c267b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -36997,7 +36997,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d856e2e-de12-475a-9319-8fb9f3ba5c83}</x14:id>
+          <x14:id>{4c292c51-0659-46a6-8453-22d0e011ea7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37011,7 +37011,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4690cd1-8294-4ae9-8204-a76c2c296b2f}</x14:id>
+          <x14:id>{888748f6-bb51-4d82-b865-a4c95eadf687}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37033,7 +37033,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75c613a2-e3c2-4121-bfc0-090cb0563795}</x14:id>
+          <x14:id>{791c90cc-a75f-413e-9c19-d17566701955}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37063,7 +37063,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d7a3b197-2e7a-4e98-8386-4ec3a8b0b849}</x14:id>
+          <x14:id>{5f4c0bc7-f786-44f2-82b9-378a54d1f220}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37093,7 +37093,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5131f15b-3ee9-4bd8-b22d-fabd2fabd4b6}</x14:id>
+          <x14:id>{4672e95c-bf6e-489e-8fcb-faf9d9066001}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37123,7 +37123,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ef3ea535-7a13-4fae-a068-fe1491a2f168}</x14:id>
+          <x14:id>{c9071025-b242-4cb9-b14c-51068373ab47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37153,7 +37153,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b342cb8b-fb18-4b0b-b7e4-0a2da3be8271}</x14:id>
+          <x14:id>{8c1e8788-c0df-49b0-a8eb-1d25d094363e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37183,7 +37183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c438823e-f3f8-46d6-b119-0a1437caa85c}</x14:id>
+          <x14:id>{ae93f630-4b5b-49fe-8026-3f25d4da7ae7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37205,7 +37205,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3a6e26d-9591-4ac2-b487-2c06e9f18653}</x14:id>
+          <x14:id>{faa0c5de-e597-4c16-8487-3c4de7529810}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37227,7 +37227,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbb68df2-4d3c-427c-9c7f-d021dce6ff86}</x14:id>
+          <x14:id>{8f17bbd1-370e-41c0-8082-66fa10fd9fac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37249,7 +37249,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b87e934-6f95-4a30-8177-58e7de7de4c8}</x14:id>
+          <x14:id>{dc4fe2e4-b292-4063-b6d9-6f14b9ef4fd6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37271,7 +37271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5946ad12-3da9-4e65-9996-0d352138327c}</x14:id>
+          <x14:id>{1ea2e565-817c-40bc-9c45-c37542d8db77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37293,7 +37293,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f958bdd-18ec-4396-abc8-ea6d2f0c3680}</x14:id>
+          <x14:id>{dd01b7f0-895c-4c25-a974-53c043e3e19c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37315,7 +37315,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{021fb62d-2ffc-49cc-8752-27adefd73c45}</x14:id>
+          <x14:id>{c3d2960e-9578-41c8-93f7-996a7b8e7b78}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37337,7 +37337,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d99aa5d-bee5-4e96-a2dc-ed1e6099ea25}</x14:id>
+          <x14:id>{d1d9e8af-14ad-4706-b3f4-e5c9c7dd9d5b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37359,7 +37359,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{361f6927-415f-4760-b81e-19b8a32f5ee3}</x14:id>
+          <x14:id>{94debaa4-cc09-4fc2-bbb1-65b216b2a748}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37381,7 +37381,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b48fe308-2c2a-46fc-9b8d-b112e8c5058b}</x14:id>
+          <x14:id>{831c93d6-05f2-4608-9b74-56363c9fa985}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37403,7 +37403,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{891685c9-9949-492e-ba07-ddc5c88dc0dd}</x14:id>
+          <x14:id>{7aa00b5c-0476-4133-a677-42929822454f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37425,7 +37425,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a8401681-f98b-4858-a82c-39f760536bf3}</x14:id>
+          <x14:id>{7f675c89-0d71-49be-8298-b4345a707345}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37447,7 +37447,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44dfbfd7-adca-4e49-b12d-1b3938853ad6}</x14:id>
+          <x14:id>{05d6bec3-2bf2-4381-9854-fdd2e829b4a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37469,7 +37469,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32b3065e-7432-4f07-bb04-9a68f562abd7}</x14:id>
+          <x14:id>{df30c85f-1ddb-4bbc-bd0d-d1154d5c188f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37491,7 +37491,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39ca69ee-6df8-410d-9cb4-d95bfe989fb8}</x14:id>
+          <x14:id>{d49e6a7e-60ad-4ee1-aaef-4e6fdbcd4191}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37510,7 +37510,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eb614637-6bb6-443f-bee9-1cdfaaef30da}">
+          <x14:cfRule type="dataBar" id="{84108da1-5cc3-49c1-8398-a2aaa17d9b4a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37523,7 +37523,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b5edce7-6aac-419a-ad79-77d723f43b04}">
+          <x14:cfRule type="dataBar" id="{3ca34d9c-42c3-4d4d-af84-e3b5f0ab1b3f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37536,7 +37536,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{788715b8-035a-406b-95c2-fcfde0159e42}">
+          <x14:cfRule type="dataBar" id="{ed29e5e1-402e-422d-9dc0-9d06e811ac65}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37549,7 +37549,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4f3f858c-d63e-42a9-9a7d-f9c9010ef415}">
+          <x14:cfRule type="dataBar" id="{c981b6ad-ff87-4519-b074-36239fee6be1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37562,7 +37562,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{849a9deb-cb62-4cdd-9e08-f336e95ae026}">
+          <x14:cfRule type="dataBar" id="{8777567c-3645-4492-94b5-f9ca63ee91ab}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37575,7 +37575,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4b11367f-af2b-40fb-acc9-cc666a1c1010}">
+          <x14:cfRule type="dataBar" id="{6f0d8169-5b72-488f-87d8-053b9fd7afb6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37588,7 +37588,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee701bb4-70ac-443f-b398-db27f69de756}">
+          <x14:cfRule type="dataBar" id="{d6ca9055-fe36-476c-8621-07a7ddfaab1c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37601,7 +37601,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9f15adc7-0abc-47bb-a791-fd9f9d3b4ea6}">
+          <x14:cfRule type="dataBar" id="{278d4d9e-8cf1-4f4f-b5f5-9441ba2fa1c2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37614,7 +37614,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{be1229b1-3e0c-4574-9db0-932de5a041b2}">
+          <x14:cfRule type="dataBar" id="{1e7a90f0-d48c-4046-80ce-7231d1868f18}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37627,7 +37627,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a1f246a7-f483-40f6-9477-e51663908832}">
+          <x14:cfRule type="dataBar" id="{0155d8e8-3673-4ec0-b5f6-1ac5dd7c267b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37640,7 +37640,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d856e2e-de12-475a-9319-8fb9f3ba5c83}">
+          <x14:cfRule type="dataBar" id="{4c292c51-0659-46a6-8453-22d0e011ea7a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37653,7 +37653,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f4690cd1-8294-4ae9-8204-a76c2c296b2f}">
+          <x14:cfRule type="dataBar" id="{888748f6-bb51-4d82-b865-a4c95eadf687}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37666,7 +37666,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{75c613a2-e3c2-4121-bfc0-090cb0563795}">
+          <x14:cfRule type="dataBar" id="{791c90cc-a75f-413e-9c19-d17566701955}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37679,7 +37679,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d7a3b197-2e7a-4e98-8386-4ec3a8b0b849}">
+          <x14:cfRule type="dataBar" id="{5f4c0bc7-f786-44f2-82b9-378a54d1f220}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37692,7 +37692,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5131f15b-3ee9-4bd8-b22d-fabd2fabd4b6}">
+          <x14:cfRule type="dataBar" id="{4672e95c-bf6e-489e-8fcb-faf9d9066001}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37705,7 +37705,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ef3ea535-7a13-4fae-a068-fe1491a2f168}">
+          <x14:cfRule type="dataBar" id="{c9071025-b242-4cb9-b14c-51068373ab47}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37718,7 +37718,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b342cb8b-fb18-4b0b-b7e4-0a2da3be8271}">
+          <x14:cfRule type="dataBar" id="{8c1e8788-c0df-49b0-a8eb-1d25d094363e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37731,7 +37731,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c438823e-f3f8-46d6-b119-0a1437caa85c}">
+          <x14:cfRule type="dataBar" id="{ae93f630-4b5b-49fe-8026-3f25d4da7ae7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37744,7 +37744,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c3a6e26d-9591-4ac2-b487-2c06e9f18653}">
+          <x14:cfRule type="dataBar" id="{faa0c5de-e597-4c16-8487-3c4de7529810}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37757,7 +37757,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dbb68df2-4d3c-427c-9c7f-d021dce6ff86}">
+          <x14:cfRule type="dataBar" id="{8f17bbd1-370e-41c0-8082-66fa10fd9fac}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37770,7 +37770,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4b87e934-6f95-4a30-8177-58e7de7de4c8}">
+          <x14:cfRule type="dataBar" id="{dc4fe2e4-b292-4063-b6d9-6f14b9ef4fd6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37783,7 +37783,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5946ad12-3da9-4e65-9996-0d352138327c}">
+          <x14:cfRule type="dataBar" id="{1ea2e565-817c-40bc-9c45-c37542d8db77}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37796,7 +37796,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6f958bdd-18ec-4396-abc8-ea6d2f0c3680}">
+          <x14:cfRule type="dataBar" id="{dd01b7f0-895c-4c25-a974-53c043e3e19c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37809,7 +37809,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{021fb62d-2ffc-49cc-8752-27adefd73c45}">
+          <x14:cfRule type="dataBar" id="{c3d2960e-9578-41c8-93f7-996a7b8e7b78}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37822,7 +37822,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5d99aa5d-bee5-4e96-a2dc-ed1e6099ea25}">
+          <x14:cfRule type="dataBar" id="{d1d9e8af-14ad-4706-b3f4-e5c9c7dd9d5b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37835,7 +37835,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{361f6927-415f-4760-b81e-19b8a32f5ee3}">
+          <x14:cfRule type="dataBar" id="{94debaa4-cc09-4fc2-bbb1-65b216b2a748}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37848,7 +37848,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b48fe308-2c2a-46fc-9b8d-b112e8c5058b}">
+          <x14:cfRule type="dataBar" id="{831c93d6-05f2-4608-9b74-56363c9fa985}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37861,7 +37861,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{891685c9-9949-492e-ba07-ddc5c88dc0dd}">
+          <x14:cfRule type="dataBar" id="{7aa00b5c-0476-4133-a677-42929822454f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37874,7 +37874,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a8401681-f98b-4858-a82c-39f760536bf3}">
+          <x14:cfRule type="dataBar" id="{7f675c89-0d71-49be-8298-b4345a707345}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37887,7 +37887,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{44dfbfd7-adca-4e49-b12d-1b3938853ad6}">
+          <x14:cfRule type="dataBar" id="{05d6bec3-2bf2-4381-9854-fdd2e829b4a3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37900,7 +37900,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32b3065e-7432-4f07-bb04-9a68f562abd7}">
+          <x14:cfRule type="dataBar" id="{df30c85f-1ddb-4bbc-bd0d-d1154d5c188f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37913,7 +37913,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{39ca69ee-6df8-410d-9cb4-d95bfe989fb8}">
+          <x14:cfRule type="dataBar" id="{d49e6a7e-60ad-4ee1-aaef-4e6fdbcd4191}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44174,7 +44174,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5444597-b396-4588-8c52-e936c3f84ad6}</x14:id>
+          <x14:id>{6f5614ba-cf72-49a4-a504-092154b62b3f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44188,7 +44188,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6019440-95ee-434c-a379-c0cb17e76dbf}</x14:id>
+          <x14:id>{2bfe4c85-2167-46e0-bb3b-090bd4a48414}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44202,7 +44202,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b285bf9-0733-45cc-a8cb-a28d67cf803f}</x14:id>
+          <x14:id>{0cfbeeed-a18c-4e19-bc8f-7f23b4187236}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44216,7 +44216,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82abb5f5-9ab0-4eb6-b003-2dc8bd13d372}</x14:id>
+          <x14:id>{fb02aa55-baba-4a26-b086-741bcb5192c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44230,7 +44230,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b31142e2-e58c-4a22-b941-4f552826136a}</x14:id>
+          <x14:id>{9f9af7e4-709b-4ff3-bb0e-7fac5fbcb3a2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44244,7 +44244,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b3f1e373-7c68-49fd-8adf-14a8e206f472}</x14:id>
+          <x14:id>{eda67536-1fc5-4a3c-8cc7-2097733edf85}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44258,7 +44258,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c9100ee9-7920-4f2e-a11a-996e75dca9ab}</x14:id>
+          <x14:id>{8f6a779b-f3fa-47a9-b737-341d870b4a1d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44272,7 +44272,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{618fdae5-2364-4eae-9b6b-2456506a102b}</x14:id>
+          <x14:id>{eaa870a8-df4b-414d-abda-af84b5b4f2e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44286,7 +44286,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18bcc63f-5054-4a54-b9db-93633312f061}</x14:id>
+          <x14:id>{140ed636-21e9-40a8-9c27-3eaf058374d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44300,7 +44300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e145517-9a10-45b3-812d-ebc52510b2a7}</x14:id>
+          <x14:id>{6c1cbe8b-e3ea-4ac4-b91c-8f4271ce712b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44314,7 +44314,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d430a507-ffdd-4483-8ed6-6d5a9e0d57ab}</x14:id>
+          <x14:id>{d1758c10-0ed8-4f2c-9a44-770598d3c555}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44350,7 +44350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45a035d8-fe15-45fd-9a12-692fb091dc68}</x14:id>
+          <x14:id>{f7fff9f6-53c8-46e1-b518-33a65b4bb1e2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -44369,7 +44369,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f5444597-b396-4588-8c52-e936c3f84ad6}">
+          <x14:cfRule type="dataBar" id="{6f5614ba-cf72-49a4-a504-092154b62b3f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44382,7 +44382,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c6019440-95ee-434c-a379-c0cb17e76dbf}">
+          <x14:cfRule type="dataBar" id="{2bfe4c85-2167-46e0-bb3b-090bd4a48414}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44395,7 +44395,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b285bf9-0733-45cc-a8cb-a28d67cf803f}">
+          <x14:cfRule type="dataBar" id="{0cfbeeed-a18c-4e19-bc8f-7f23b4187236}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44408,7 +44408,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{82abb5f5-9ab0-4eb6-b003-2dc8bd13d372}">
+          <x14:cfRule type="dataBar" id="{fb02aa55-baba-4a26-b086-741bcb5192c5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44421,7 +44421,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b31142e2-e58c-4a22-b941-4f552826136a}">
+          <x14:cfRule type="dataBar" id="{9f9af7e4-709b-4ff3-bb0e-7fac5fbcb3a2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44434,7 +44434,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b3f1e373-7c68-49fd-8adf-14a8e206f472}">
+          <x14:cfRule type="dataBar" id="{eda67536-1fc5-4a3c-8cc7-2097733edf85}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44447,7 +44447,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c9100ee9-7920-4f2e-a11a-996e75dca9ab}">
+          <x14:cfRule type="dataBar" id="{8f6a779b-f3fa-47a9-b737-341d870b4a1d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44460,7 +44460,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{618fdae5-2364-4eae-9b6b-2456506a102b}">
+          <x14:cfRule type="dataBar" id="{eaa870a8-df4b-414d-abda-af84b5b4f2e0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44473,7 +44473,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18bcc63f-5054-4a54-b9db-93633312f061}">
+          <x14:cfRule type="dataBar" id="{140ed636-21e9-40a8-9c27-3eaf058374d7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44486,7 +44486,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e145517-9a10-45b3-812d-ebc52510b2a7}">
+          <x14:cfRule type="dataBar" id="{6c1cbe8b-e3ea-4ac4-b91c-8f4271ce712b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44499,7 +44499,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d430a507-ffdd-4483-8ed6-6d5a9e0d57ab}">
+          <x14:cfRule type="dataBar" id="{d1758c10-0ed8-4f2c-9a44-770598d3c555}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -44512,7 +44512,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{45a035d8-fe15-45fd-9a12-692fb091dc68}">
+          <x14:cfRule type="dataBar" id="{f7fff9f6-53c8-46e1-b518-33a65b4bb1e2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -12627,36 +12627,8 @@
       <sheetName val="包家豪"/>
       <sheetName val="杨皓"/>
       <sheetName val="陈欣诺"/>
+      <sheetName val="陈欣诺-男装"/>
       <sheetName val="林梓蕾"/>
-      <sheetName val="周度汇总分析报告"/>
-      <sheetName val="m"/>
-      <sheetName val="mu"/>
-      <sheetName val="muz"/>
-      <sheetName val="muzo"/>
-      <sheetName val="muzon"/>
-      <sheetName val="muzong"/>
-      <sheetName val="muzongb"/>
-      <sheetName val="muzongbi"/>
-      <sheetName val="muzongbia"/>
-      <sheetName val="muzongbiao"/>
-      <sheetName val="总"/>
-      <sheetName val="总目"/>
-      <sheetName val="mi"/>
-      <sheetName val="min"/>
-      <sheetName val="minh"/>
-      <sheetName val="minhu"/>
-      <sheetName val="minhua"/>
-      <sheetName val="敏华"/>
-      <sheetName val="敏华x"/>
-      <sheetName val="敏华xi"/>
-      <sheetName val="敏华xin"/>
-      <sheetName val="陈"/>
-      <sheetName val="陈欣"/>
-      <sheetName val="林"/>
-      <sheetName val="林梓"/>
-      <sheetName val="包"/>
-      <sheetName val="包家"/>
-      <sheetName val="杨"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -12741,44 +12713,6 @@
             <v>164036.38</v>
           </cell>
         </row>
-        <row r="31">
-          <cell r="B31">
-            <v>249399.554098361</v>
-          </cell>
-          <cell r="C31">
-            <v>359988.363934426</v>
-          </cell>
-          <cell r="D31">
-            <v>283015.081967213</v>
-          </cell>
-          <cell r="E31">
-            <v>292149.336065573</v>
-          </cell>
-          <cell r="F31">
-            <v>251744.803278688</v>
-          </cell>
-          <cell r="G31">
-            <v>343899.516393443</v>
-          </cell>
-          <cell r="H31">
-            <v>432694.442622951</v>
-          </cell>
-          <cell r="I31">
-            <v>416424.590163934</v>
-          </cell>
-          <cell r="J31">
-            <v>396103.770491803</v>
-          </cell>
-          <cell r="K31">
-            <v>385857.049180328</v>
-          </cell>
-          <cell r="L31">
-            <v>398718.950819672</v>
-          </cell>
-          <cell r="M31">
-            <v>262747.868852459</v>
-          </cell>
-        </row>
         <row r="32">
           <cell r="B32">
             <v>7901.99163571725</v>
@@ -12835,6 +12769,9 @@
           <cell r="F34">
             <v>87149.71</v>
           </cell>
+          <cell r="G34">
+            <v>98996.89</v>
+          </cell>
         </row>
         <row r="35">
           <cell r="B35">
@@ -12865,441 +12802,407 @@
         </row>
         <row r="44">
           <cell r="B44">
-            <v>372843</v>
+            <v>267032.554098361</v>
           </cell>
           <cell r="C44">
-            <v>566214.491803279</v>
+            <v>454472.298360656</v>
           </cell>
           <cell r="D44">
-            <v>425981.18852459</v>
+            <v>356490.491803279</v>
           </cell>
           <cell r="E44">
-            <v>428093.165983607</v>
+            <v>373135.56557377</v>
           </cell>
           <cell r="F44">
-            <v>438328.647540984</v>
+            <v>335343.491803279</v>
           </cell>
           <cell r="G44">
-            <v>376625.606557377</v>
+            <v>291232.549180328</v>
           </cell>
           <cell r="H44">
-            <v>516638.599385246</v>
+            <v>359127.885245902</v>
           </cell>
           <cell r="I44">
-            <v>499972.838114754</v>
+            <v>345231.147540984</v>
           </cell>
           <cell r="J44">
-            <v>490032.5</v>
+            <v>327791.967213115</v>
           </cell>
           <cell r="K44">
-            <v>474225</v>
+            <v>319748.852459016</v>
           </cell>
           <cell r="L44">
-            <v>490032.5</v>
+            <v>330407.147540984</v>
           </cell>
           <cell r="M44">
-            <v>318392.868852459</v>
+            <v>214260.819672131</v>
           </cell>
         </row>
         <row r="45">
-          <cell r="B45">
-            <v>22786.22</v>
-          </cell>
-          <cell r="C45">
-            <v>120856.31</v>
-          </cell>
-          <cell r="D45">
-            <v>114083.09</v>
-          </cell>
-          <cell r="E45">
-            <v>92574.56</v>
-          </cell>
           <cell r="F45">
-            <v>100423.98</v>
+            <v>48024.39</v>
           </cell>
           <cell r="G45">
-            <v>185876.7</v>
+            <v>86148.62</v>
           </cell>
         </row>
         <row r="46">
-          <cell r="B46">
-            <v>57252.98</v>
-          </cell>
-          <cell r="C46">
-            <v>126071.82</v>
-          </cell>
-          <cell r="D46">
-            <v>90908.16</v>
-          </cell>
-          <cell r="E46">
-            <v>133011.74</v>
-          </cell>
           <cell r="F46">
-            <v>159761.43</v>
+            <v>109001.18</v>
           </cell>
           <cell r="G46">
-            <v>163961.13</v>
+            <v>90013.7</v>
           </cell>
         </row>
         <row r="47">
-          <cell r="B47">
-            <v>87628.76</v>
-          </cell>
-          <cell r="C47">
-            <v>171781.7</v>
-          </cell>
-          <cell r="D47">
-            <v>105113.29</v>
-          </cell>
-          <cell r="E47">
-            <v>85294.94</v>
-          </cell>
           <cell r="F47">
-            <v>176058.01</v>
+            <v>108212.53</v>
+          </cell>
+          <cell r="G47">
+            <v>90032.49</v>
           </cell>
         </row>
         <row r="48">
-          <cell r="B48">
-            <v>113025.62</v>
-          </cell>
-          <cell r="C48">
-            <v>161987.51</v>
-          </cell>
-          <cell r="D48">
-            <v>85159.25</v>
-          </cell>
-          <cell r="E48">
-            <v>107651.59</v>
-          </cell>
           <cell r="F48">
-            <v>157424.67</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="C49">
-            <v>117603.33</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="E49">
-            <v>78292.17</v>
+            <v>102812.84</v>
           </cell>
         </row>
         <row r="58">
-          <cell r="B58">
-            <v>278839</v>
-          </cell>
-          <cell r="C58">
-            <v>672748.786885246</v>
-          </cell>
-          <cell r="D58">
-            <v>528274.180327869</v>
-          </cell>
-          <cell r="E58">
-            <v>526052.975409836</v>
-          </cell>
-          <cell r="F58">
-            <v>511352.459016394</v>
-          </cell>
-          <cell r="G58">
-            <v>451240.573770492</v>
-          </cell>
-          <cell r="H58">
-            <v>540132.311475409</v>
-          </cell>
-          <cell r="I58">
-            <v>525321.147540984</v>
-          </cell>
-          <cell r="J58">
-            <v>507300.262295082</v>
-          </cell>
-          <cell r="K58">
-            <v>494517.049180328</v>
-          </cell>
-          <cell r="L58">
-            <v>507296.196721311</v>
-          </cell>
-          <cell r="M58">
-            <v>361615.508196722</v>
+          <cell r="B58" t="str">
+            <v>2月</v>
+          </cell>
+          <cell r="C58" t="str">
+            <v>3月</v>
+          </cell>
+          <cell r="D58" t="str">
+            <v>4月</v>
+          </cell>
+          <cell r="E58" t="str">
+            <v>5月</v>
+          </cell>
+          <cell r="F58" t="str">
+            <v>6月</v>
+          </cell>
+          <cell r="G58" t="str">
+            <v>7月</v>
+          </cell>
+          <cell r="H58" t="str">
+            <v>8月</v>
+          </cell>
+          <cell r="I58" t="str">
+            <v>9月</v>
+          </cell>
+          <cell r="J58" t="str">
+            <v>10月</v>
+          </cell>
+          <cell r="K58" t="str">
+            <v>11月</v>
+          </cell>
+          <cell r="L58" t="str">
+            <v>12月</v>
+          </cell>
+          <cell r="M58" t="str">
+            <v>1月</v>
           </cell>
         </row>
         <row r="59">
           <cell r="B59">
-            <v>229311.59</v>
+            <v>372843</v>
           </cell>
           <cell r="C59">
-            <v>770766.4</v>
+            <v>566214.491803279</v>
           </cell>
           <cell r="D59">
-            <v>149567</v>
+            <v>425981.18852459</v>
           </cell>
           <cell r="E59">
-            <v>58296.43</v>
+            <v>428093.165983607</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="G59">
+            <v>376625.606557377</v>
+          </cell>
+          <cell r="H59">
+            <v>516638.599385246</v>
+          </cell>
+          <cell r="I59">
+            <v>499972.838114754</v>
+          </cell>
+          <cell r="J59">
+            <v>490032.5</v>
+          </cell>
+          <cell r="K59">
+            <v>474225</v>
+          </cell>
+          <cell r="L59">
+            <v>490032.5</v>
+          </cell>
+          <cell r="M59">
+            <v>318392.868852459</v>
           </cell>
         </row>
         <row r="60">
+          <cell r="B60">
+            <v>22786.22</v>
+          </cell>
+          <cell r="C60">
+            <v>120856.31</v>
+          </cell>
           <cell r="D60">
-            <v>95816.8</v>
+            <v>114083.09</v>
           </cell>
           <cell r="E60">
-            <v>97059.95</v>
+            <v>92574.56</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="G60">
+            <v>185876.7</v>
           </cell>
         </row>
         <row r="61">
+          <cell r="B61">
+            <v>57252.98</v>
+          </cell>
+          <cell r="C61">
+            <v>126071.82</v>
+          </cell>
           <cell r="D61">
-            <v>70227.04</v>
+            <v>90908.16</v>
           </cell>
           <cell r="E61">
-            <v>76035.36</v>
+            <v>133011.74</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="G61">
+            <v>163961.13</v>
           </cell>
         </row>
         <row r="62">
+          <cell r="B62">
+            <v>87628.76</v>
+          </cell>
+          <cell r="C62">
+            <v>171781.7</v>
+          </cell>
           <cell r="D62">
-            <v>52419.95</v>
+            <v>105113.29</v>
           </cell>
           <cell r="E62">
-            <v>87855.34</v>
+            <v>85294.94</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="G62">
+            <v>140221.74</v>
           </cell>
         </row>
         <row r="63">
+          <cell r="B63">
+            <v>113025.62</v>
+          </cell>
+          <cell r="C63">
+            <v>161987.51</v>
+          </cell>
+          <cell r="D63">
+            <v>85159.25</v>
+          </cell>
           <cell r="E63">
-            <v>43883.05</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="B70">
-            <v>34481</v>
-          </cell>
-          <cell r="C70">
-            <v>86791.2971311476</v>
-          </cell>
-          <cell r="D70">
-            <v>133954.856557377</v>
-          </cell>
-          <cell r="E70">
-            <v>141243.464139344</v>
-          </cell>
-          <cell r="F70">
-            <v>195306.823770492</v>
-          </cell>
-          <cell r="G70">
-            <v>155693.126331967</v>
-          </cell>
-          <cell r="H70">
-            <v>213216.284836066</v>
-          </cell>
-          <cell r="I70">
-            <v>206338.340163934</v>
-          </cell>
-          <cell r="J70">
-            <v>195186.830942623</v>
-          </cell>
-          <cell r="K70">
-            <v>187961.834016393</v>
-          </cell>
-          <cell r="L70">
-            <v>195186.830942623</v>
-          </cell>
-          <cell r="M70">
-            <v>98770.5102459016</v>
+            <v>107651.59</v>
           </cell>
         </row>
         <row r="71">
-          <cell r="B71">
-            <v>-11533.5</v>
-          </cell>
-          <cell r="C71">
-            <v>957.27</v>
-          </cell>
-          <cell r="D71">
-            <v>-2072.67</v>
-          </cell>
-          <cell r="E71">
-            <v>-1579</v>
+          <cell r="B71" t="str">
+            <v>Q1</v>
           </cell>
         </row>
         <row r="71">
-          <cell r="G71">
-            <v>19303.95</v>
+          <cell r="E71" t="str">
+            <v>Q2</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="H71" t="str">
+            <v>Q3</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="K71" t="str">
+            <v>Q4</v>
           </cell>
         </row>
         <row r="72">
-          <cell r="B72">
-            <v>4468.02</v>
-          </cell>
-          <cell r="C72">
-            <v>13709.59</v>
-          </cell>
-          <cell r="D72">
-            <v>9339.48</v>
-          </cell>
-          <cell r="E72">
-            <v>17659.06</v>
+          <cell r="B72" t="str">
+            <v>2月</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>3月</v>
+          </cell>
+          <cell r="D72" t="str">
+            <v>4月</v>
+          </cell>
+          <cell r="E72" t="str">
+            <v>5月</v>
           </cell>
         </row>
         <row r="72">
-          <cell r="G72">
-            <v>17337.95</v>
+          <cell r="G72" t="str">
+            <v>7月</v>
+          </cell>
+          <cell r="H72" t="str">
+            <v>8月</v>
+          </cell>
+          <cell r="I72" t="str">
+            <v>9月</v>
+          </cell>
+          <cell r="J72" t="str">
+            <v>10月</v>
+          </cell>
+          <cell r="K72" t="str">
+            <v>11月</v>
+          </cell>
+          <cell r="L72" t="str">
+            <v>12月</v>
+          </cell>
+          <cell r="M72" t="str">
+            <v>1月</v>
           </cell>
         </row>
         <row r="73">
           <cell r="B73">
-            <v>10431.85</v>
+            <v>278839</v>
           </cell>
           <cell r="C73">
-            <v>863.63</v>
+            <v>672748.786885246</v>
           </cell>
           <cell r="D73">
-            <v>-159.41</v>
+            <v>528274.180327869</v>
           </cell>
           <cell r="E73">
-            <v>15625.48</v>
+            <v>526052.975409836</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="G73">
+            <v>451240.573770492</v>
+          </cell>
+          <cell r="H73">
+            <v>540132.311475409</v>
+          </cell>
+          <cell r="I73">
+            <v>525321.147540984</v>
+          </cell>
+          <cell r="J73">
+            <v>507300.262295082</v>
+          </cell>
+          <cell r="K73">
+            <v>494517.049180328</v>
+          </cell>
+          <cell r="L73">
+            <v>507296.196721311</v>
+          </cell>
+          <cell r="M73">
+            <v>361615.508196722</v>
           </cell>
         </row>
         <row r="74">
           <cell r="B74">
-            <v>11437.39</v>
+            <v>229311.59</v>
           </cell>
           <cell r="C74">
-            <v>13675.45</v>
+            <v>770766.4</v>
           </cell>
           <cell r="D74">
-            <v>7061.15</v>
+            <v>149567</v>
           </cell>
           <cell r="E74">
-            <v>6285.12</v>
+            <v>58296.43</v>
           </cell>
         </row>
         <row r="75">
-          <cell r="C75">
-            <v>9612.01</v>
-          </cell>
-        </row>
-        <row r="75">
+          <cell r="D75">
+            <v>95816.8</v>
+          </cell>
           <cell r="E75">
-            <v>11832.22</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="B82">
-            <v>249612</v>
-          </cell>
-          <cell r="C82">
-            <v>485112.393442623</v>
-          </cell>
-          <cell r="D82">
-            <v>397534.426229508</v>
-          </cell>
-          <cell r="E82">
-            <v>391039.081967214</v>
-          </cell>
-          <cell r="F82">
-            <v>369194.754098361</v>
-          </cell>
-          <cell r="G82">
-            <v>324188.852459017</v>
-          </cell>
-          <cell r="H82">
-            <v>367365.245901639</v>
-          </cell>
-          <cell r="I82">
-            <v>355514.754098361</v>
-          </cell>
-          <cell r="J82">
-            <v>342618.098360656</v>
-          </cell>
-          <cell r="K82">
-            <v>336998.360655738</v>
-          </cell>
-          <cell r="L82">
-            <v>344526.885245901</v>
-          </cell>
-          <cell r="M82">
-            <v>252862.426229508</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="B83">
-            <v>18798.63</v>
-          </cell>
-          <cell r="C83">
-            <v>70261.4</v>
-          </cell>
-          <cell r="D83">
-            <v>115927.36</v>
-          </cell>
-          <cell r="E83">
-            <v>38311.5</v>
-          </cell>
-          <cell r="F83">
-            <v>25461.43</v>
-          </cell>
-          <cell r="G83">
-            <v>42597.61</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="B84">
-            <v>44358.75</v>
-          </cell>
-          <cell r="C84">
-            <v>135274.74</v>
-          </cell>
-          <cell r="D84">
-            <v>92048.7</v>
-          </cell>
-          <cell r="E84">
-            <v>69082.5</v>
-          </cell>
-          <cell r="F84">
-            <v>56724.2</v>
-          </cell>
-          <cell r="G84">
-            <v>41903.57</v>
+            <v>97059.95</v>
           </cell>
         </row>
         <row r="85">
           <cell r="B85">
-            <v>60795.74</v>
+            <v>34481</v>
           </cell>
           <cell r="C85">
-            <v>138404.07</v>
+            <v>86791.2971311476</v>
           </cell>
           <cell r="D85">
-            <v>69267.05</v>
+            <v>133954.856557377</v>
           </cell>
           <cell r="E85">
-            <v>45931.85</v>
+            <v>141243.464139344</v>
           </cell>
           <cell r="F85">
-            <v>40273.32</v>
+            <v>195306.823770492</v>
+          </cell>
+          <cell r="G85">
+            <v>155693.126331967</v>
+          </cell>
+          <cell r="H85">
+            <v>213216.284836066</v>
+          </cell>
+          <cell r="I85">
+            <v>206338.340163934</v>
+          </cell>
+          <cell r="J85">
+            <v>195186.830942623</v>
+          </cell>
+          <cell r="K85">
+            <v>187961.834016393</v>
+          </cell>
+          <cell r="L85">
+            <v>195186.830942623</v>
+          </cell>
+          <cell r="M85">
+            <v>98770.5102459016</v>
           </cell>
         </row>
-        <row r="86">
-          <cell r="B86">
-            <v>68300.77</v>
-          </cell>
-          <cell r="C86">
-            <v>117457.3</v>
-          </cell>
-          <cell r="D86">
-            <v>54071.91</v>
-          </cell>
-          <cell r="E86">
-            <v>71078.3</v>
-          </cell>
-          <cell r="F86">
-            <v>42588.76</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="B87">
-            <v>58973.86</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="E87">
-            <v>21324.35</v>
+        <row r="97">
+          <cell r="B97">
+            <v>249612</v>
+          </cell>
+          <cell r="C97">
+            <v>485112.393442623</v>
+          </cell>
+          <cell r="D97">
+            <v>397534.426229508</v>
+          </cell>
+          <cell r="E97">
+            <v>391039.081967214</v>
+          </cell>
+          <cell r="F97">
+            <v>369194.754098361</v>
+          </cell>
+          <cell r="G97">
+            <v>324188.852459017</v>
+          </cell>
+          <cell r="H97">
+            <v>367365.245901639</v>
+          </cell>
+          <cell r="I97">
+            <v>355514.754098361</v>
+          </cell>
+          <cell r="J97">
+            <v>342618.098360656</v>
+          </cell>
+          <cell r="K97">
+            <v>336998.360655738</v>
+          </cell>
+          <cell r="L97">
+            <v>344526.885245901</v>
+          </cell>
+          <cell r="M97">
+            <v>252862.426229508</v>
           </cell>
         </row>
       </sheetData>
@@ -13768,7 +13671,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7">
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
         <row r="4">
           <cell r="B4">
             <v>66868745</v>
@@ -13922,35 +13826,6 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -23356,7 +23231,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b4d1673-777b-4e73-a1ba-9c959f2c3114}</x14:id>
+          <x14:id>{12705517-a1ac-4af3-9c47-dffcbd884c69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23370,7 +23245,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f1828007-b8f8-448b-9b6e-cff48ee039ca}</x14:id>
+          <x14:id>{0e1a063c-cfc4-4370-b5f5-e3d78bae61f4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23384,7 +23259,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d9364f72-3c1c-4776-b58e-3e1290d701c2}</x14:id>
+          <x14:id>{6d90900b-c779-4f2d-8b04-1d186ac211c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23398,7 +23273,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7da828b-92a8-47a5-8c40-6eed0578e0f8}</x14:id>
+          <x14:id>{538c34ba-3fe1-4246-a987-1e6331b69a84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23412,7 +23287,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd2e04fc-455b-4aaf-95e8-f3ed1db2fd23}</x14:id>
+          <x14:id>{4d191783-513b-4681-a0e0-1da47cce2353}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23426,7 +23301,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c58a39c2-ca6d-4e97-996e-2f05e3103812}</x14:id>
+          <x14:id>{a6de7bd0-e68f-4f22-9a4b-52508451c1bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23440,7 +23315,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3344892e-b6ef-4b3d-9e28-87ddbb856b65}</x14:id>
+          <x14:id>{2f855105-ca70-48e9-bb22-0a86855ee54f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23454,7 +23329,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3d5075e-5afc-4228-8b77-12b2165bee2f}</x14:id>
+          <x14:id>{bbf82617-38a1-4e97-9e72-eb5a0c3bdb92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23474,7 +23349,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c304f9f-fda9-4849-942a-e093e0cee47d}</x14:id>
+          <x14:id>{60698893-4c65-4d50-af79-65729be2c6b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23502,7 +23377,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c211a8c-0ad4-4705-9174-0f98d934f66f}</x14:id>
+          <x14:id>{0d3ac796-bdc0-45d4-8882-852723bc1c17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23522,7 +23397,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ba0ba88-a871-4f0f-a31c-72f51eb22617}</x14:id>
+          <x14:id>{261db87c-1e88-4ec8-bfd4-f9ff58e6ab69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23550,7 +23425,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{994a9c67-1b4a-4871-844f-1fc9d81aa78f}</x14:id>
+          <x14:id>{c7327550-3ab0-47f9-87ae-ebc7daa8c728}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23570,7 +23445,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2107e78f-920a-4464-beed-a44ba7fc94c4}</x14:id>
+          <x14:id>{cd911691-1116-42fe-bc53-67b1c0267f3b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23598,7 +23473,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b52972c3-8973-42e2-a610-90703a575aef}</x14:id>
+          <x14:id>{488d3490-7eae-4875-a20c-b6e313a891f8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23618,7 +23493,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9cf5b75-07d8-4d01-88ac-6156274238f7}</x14:id>
+          <x14:id>{d32d3730-c799-495f-ab3f-368a55c0587b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23646,7 +23521,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93c43128-2298-4dbc-9061-5362525c88f2}</x14:id>
+          <x14:id>{917a537d-9e87-4c62-970e-2a3208257cff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23666,7 +23541,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3cc58bf4-1ef1-4927-ab71-f53e53d6183d}</x14:id>
+          <x14:id>{a0816f8a-cf6d-4ed6-be91-32fb8a7baa2b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23694,7 +23569,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c78a05e8-c4ec-4bcb-8946-1f33e7181140}</x14:id>
+          <x14:id>{46e4e21c-a7ec-4379-8b05-59f6f8733a0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23756,7 +23631,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7bfd925e-3810-4151-87b4-89f5e0c36baf}</x14:id>
+          <x14:id>{62b58732-fa75-415f-ae8c-e06cbb39486c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23786,7 +23661,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{793e1d50-5431-4a3c-a03a-2064a49061ff}</x14:id>
+          <x14:id>{71e9fd37-0a20-44b6-bc97-8c3bc7b56d3c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23808,7 +23683,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4fcf6e40-59d6-4f90-8a4e-bbd25b34bd72}</x14:id>
+          <x14:id>{1f554681-6d53-4dfd-9c51-909b0684a3a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23828,7 +23703,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c23cabe-cd0c-46e8-aad1-d8de9226f83c}</x14:id>
+          <x14:id>{53a4cf40-caa0-4fba-a9ce-286287c1ff0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23850,7 +23725,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9666fa35-bedf-4578-b54f-77e2c7476fd8}</x14:id>
+          <x14:id>{7257bc84-0606-4596-9096-c367964143e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23870,7 +23745,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{acd8429d-12db-4b2e-babe-da9cbf89b241}</x14:id>
+          <x14:id>{b53cb82c-b426-442c-9227-d43032399732}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23892,7 +23767,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{078bd162-de3f-4e00-8379-99e8f88fce13}</x14:id>
+          <x14:id>{b670fcd2-c030-4af4-a7c8-fa413a7d467a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23912,7 +23787,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b279f465-7ca9-4fae-bd56-9a034895169d}</x14:id>
+          <x14:id>{3b8e60aa-309d-4e94-9e38-064c7c48539b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23934,7 +23809,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3375e580-4804-420c-acb8-b1c66755eb33}</x14:id>
+          <x14:id>{8004c6e5-6aef-472d-9deb-d7bb3eb0a282}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23954,7 +23829,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0726d1c-8c6a-4855-8020-0e24fe58a87a}</x14:id>
+          <x14:id>{8514cc6f-c463-4734-8c35-aebf1ed97435}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23982,7 +23857,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d01a08ae-64fd-4685-8b24-f679993e6b35}</x14:id>
+          <x14:id>{a79d2cca-63f7-4381-b276-ddc721ebedda}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23996,7 +23871,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4290e7d1-a7fc-4582-8246-77710872b39e}</x14:id>
+          <x14:id>{830a7799-181e-4617-84cd-a83d5c0c5070}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24026,7 +23901,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e776de81-d943-4456-afb4-86d795c94756}</x14:id>
+          <x14:id>{d533caa9-ee38-4a38-89c9-b295f24de74e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24048,7 +23923,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5dab4271-c7f4-4bf5-99fe-263d297fc2b0}</x14:id>
+          <x14:id>{af742c9d-636f-4fff-ac6a-7f9c7f3c7037}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24070,7 +23945,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e609aa8-cb30-4a09-8319-2e2b83341dda}</x14:id>
+          <x14:id>{81f1277b-500d-4e6c-aadd-268bf1ea342a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24092,7 +23967,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb112980-02d3-4227-be71-5e1c7e248d0a}</x14:id>
+          <x14:id>{e850438a-52e9-4882-a1ef-da02391dd87e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24114,7 +23989,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eefcc3ef-4dd2-41f0-9be9-81a560a4a6c2}</x14:id>
+          <x14:id>{3ac28c79-7159-43ed-93c3-5211aa02ceeb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24136,7 +24011,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8369b2ec-cef4-46ac-9773-66b136f6c223}</x14:id>
+          <x14:id>{2e892bd2-e689-47f3-a102-223c279a2883}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24158,7 +24033,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2fb75d1b-d144-4106-a64f-79bba3bb1b5e}</x14:id>
+          <x14:id>{a7bf0662-6c40-4e21-832f-22511f489591}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24180,7 +24055,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc27f3a4-9872-4d15-9792-d8db5625cfd8}</x14:id>
+          <x14:id>{3baefdbb-4bb1-49bd-a3d7-cd63bcb4e76f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24202,7 +24077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe0a760e-f46f-4152-9753-4497ba47a8d4}</x14:id>
+          <x14:id>{b197a809-348b-44d9-a999-27a78e001bfc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24224,7 +24099,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba760814-98d9-42f0-bfb7-d9435ba2dfbf}</x14:id>
+          <x14:id>{f4d769d6-5e2c-4223-8934-90e7dffbf419}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24246,7 +24121,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{44a7a5cd-b628-4091-a4c1-d5828c0ed208}</x14:id>
+          <x14:id>{8c1fd285-8e9d-444b-a958-7c4598e8275c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24268,7 +24143,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0138e7c6-3b5f-48cd-9f19-e20aa03004c5}</x14:id>
+          <x14:id>{622dc457-61a6-47ea-9505-488aaa864ee4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24290,7 +24165,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{470d597e-54a4-470c-8b75-14a310ccbb42}</x14:id>
+          <x14:id>{8e4e4590-eeec-47e3-a926-0c76b04861bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24309,7 +24184,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5b4d1673-777b-4e73-a1ba-9c959f2c3114}">
+          <x14:cfRule type="dataBar" id="{12705517-a1ac-4af3-9c47-dffcbd884c69}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24322,7 +24197,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f1828007-b8f8-448b-9b6e-cff48ee039ca}">
+          <x14:cfRule type="dataBar" id="{0e1a063c-cfc4-4370-b5f5-e3d78bae61f4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24335,7 +24210,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d9364f72-3c1c-4776-b58e-3e1290d701c2}">
+          <x14:cfRule type="dataBar" id="{6d90900b-c779-4f2d-8b04-1d186ac211c5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24348,7 +24223,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b7da828b-92a8-47a5-8c40-6eed0578e0f8}">
+          <x14:cfRule type="dataBar" id="{538c34ba-3fe1-4246-a987-1e6331b69a84}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24361,7 +24236,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd2e04fc-455b-4aaf-95e8-f3ed1db2fd23}">
+          <x14:cfRule type="dataBar" id="{4d191783-513b-4681-a0e0-1da47cce2353}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24374,7 +24249,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c58a39c2-ca6d-4e97-996e-2f05e3103812}">
+          <x14:cfRule type="dataBar" id="{a6de7bd0-e68f-4f22-9a4b-52508451c1bf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24387,7 +24262,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3344892e-b6ef-4b3d-9e28-87ddbb856b65}">
+          <x14:cfRule type="dataBar" id="{2f855105-ca70-48e9-bb22-0a86855ee54f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24400,7 +24275,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3d5075e-5afc-4228-8b77-12b2165bee2f}">
+          <x14:cfRule type="dataBar" id="{bbf82617-38a1-4e97-9e72-eb5a0c3bdb92}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24413,7 +24288,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8c304f9f-fda9-4849-942a-e093e0cee47d}">
+          <x14:cfRule type="dataBar" id="{60698893-4c65-4d50-af79-65729be2c6b5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24426,7 +24301,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8c211a8c-0ad4-4705-9174-0f98d934f66f}">
+          <x14:cfRule type="dataBar" id="{0d3ac796-bdc0-45d4-8882-852723bc1c17}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24439,7 +24314,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ba0ba88-a871-4f0f-a31c-72f51eb22617}">
+          <x14:cfRule type="dataBar" id="{261db87c-1e88-4ec8-bfd4-f9ff58e6ab69}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24452,7 +24327,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{994a9c67-1b4a-4871-844f-1fc9d81aa78f}">
+          <x14:cfRule type="dataBar" id="{c7327550-3ab0-47f9-87ae-ebc7daa8c728}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24465,7 +24340,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2107e78f-920a-4464-beed-a44ba7fc94c4}">
+          <x14:cfRule type="dataBar" id="{cd911691-1116-42fe-bc53-67b1c0267f3b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24478,7 +24353,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b52972c3-8973-42e2-a610-90703a575aef}">
+          <x14:cfRule type="dataBar" id="{488d3490-7eae-4875-a20c-b6e313a891f8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24491,7 +24366,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a9cf5b75-07d8-4d01-88ac-6156274238f7}">
+          <x14:cfRule type="dataBar" id="{d32d3730-c799-495f-ab3f-368a55c0587b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24504,7 +24379,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93c43128-2298-4dbc-9061-5362525c88f2}">
+          <x14:cfRule type="dataBar" id="{917a537d-9e87-4c62-970e-2a3208257cff}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24517,7 +24392,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3cc58bf4-1ef1-4927-ab71-f53e53d6183d}">
+          <x14:cfRule type="dataBar" id="{a0816f8a-cf6d-4ed6-be91-32fb8a7baa2b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24530,7 +24405,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c78a05e8-c4ec-4bcb-8946-1f33e7181140}">
+          <x14:cfRule type="dataBar" id="{46e4e21c-a7ec-4379-8b05-59f6f8733a0d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24543,7 +24418,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7bfd925e-3810-4151-87b4-89f5e0c36baf}">
+          <x14:cfRule type="dataBar" id="{62b58732-fa75-415f-ae8c-e06cbb39486c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24556,7 +24431,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{793e1d50-5431-4a3c-a03a-2064a49061ff}">
+          <x14:cfRule type="dataBar" id="{71e9fd37-0a20-44b6-bc97-8c3bc7b56d3c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24569,7 +24444,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4fcf6e40-59d6-4f90-8a4e-bbd25b34bd72}">
+          <x14:cfRule type="dataBar" id="{1f554681-6d53-4dfd-9c51-909b0684a3a5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24582,7 +24457,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0c23cabe-cd0c-46e8-aad1-d8de9226f83c}">
+          <x14:cfRule type="dataBar" id="{53a4cf40-caa0-4fba-a9ce-286287c1ff0d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24595,7 +24470,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9666fa35-bedf-4578-b54f-77e2c7476fd8}">
+          <x14:cfRule type="dataBar" id="{7257bc84-0606-4596-9096-c367964143e1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24608,7 +24483,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{acd8429d-12db-4b2e-babe-da9cbf89b241}">
+          <x14:cfRule type="dataBar" id="{b53cb82c-b426-442c-9227-d43032399732}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24621,7 +24496,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{078bd162-de3f-4e00-8379-99e8f88fce13}">
+          <x14:cfRule type="dataBar" id="{b670fcd2-c030-4af4-a7c8-fa413a7d467a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24634,7 +24509,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b279f465-7ca9-4fae-bd56-9a034895169d}">
+          <x14:cfRule type="dataBar" id="{3b8e60aa-309d-4e94-9e38-064c7c48539b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24647,7 +24522,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3375e580-4804-420c-acb8-b1c66755eb33}">
+          <x14:cfRule type="dataBar" id="{8004c6e5-6aef-472d-9deb-d7bb3eb0a282}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24660,7 +24535,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c0726d1c-8c6a-4855-8020-0e24fe58a87a}">
+          <x14:cfRule type="dataBar" id="{8514cc6f-c463-4734-8c35-aebf1ed97435}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24673,7 +24548,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d01a08ae-64fd-4685-8b24-f679993e6b35}">
+          <x14:cfRule type="dataBar" id="{a79d2cca-63f7-4381-b276-ddc721ebedda}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24686,7 +24561,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4290e7d1-a7fc-4582-8246-77710872b39e}">
+          <x14:cfRule type="dataBar" id="{830a7799-181e-4617-84cd-a83d5c0c5070}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24699,7 +24574,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e776de81-d943-4456-afb4-86d795c94756}">
+          <x14:cfRule type="dataBar" id="{d533caa9-ee38-4a38-89c9-b295f24de74e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24712,7 +24587,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5dab4271-c7f4-4bf5-99fe-263d297fc2b0}">
+          <x14:cfRule type="dataBar" id="{af742c9d-636f-4fff-ac6a-7f9c7f3c7037}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24725,7 +24600,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2e609aa8-cb30-4a09-8319-2e2b83341dda}">
+          <x14:cfRule type="dataBar" id="{81f1277b-500d-4e6c-aadd-268bf1ea342a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24738,7 +24613,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fb112980-02d3-4227-be71-5e1c7e248d0a}">
+          <x14:cfRule type="dataBar" id="{e850438a-52e9-4882-a1ef-da02391dd87e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24751,7 +24626,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eefcc3ef-4dd2-41f0-9be9-81a560a4a6c2}">
+          <x14:cfRule type="dataBar" id="{3ac28c79-7159-43ed-93c3-5211aa02ceeb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24764,7 +24639,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8369b2ec-cef4-46ac-9773-66b136f6c223}">
+          <x14:cfRule type="dataBar" id="{2e892bd2-e689-47f3-a102-223c279a2883}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24777,7 +24652,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2fb75d1b-d144-4106-a64f-79bba3bb1b5e}">
+          <x14:cfRule type="dataBar" id="{a7bf0662-6c40-4e21-832f-22511f489591}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24790,7 +24665,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fc27f3a4-9872-4d15-9792-d8db5625cfd8}">
+          <x14:cfRule type="dataBar" id="{3baefdbb-4bb1-49bd-a3d7-cd63bcb4e76f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24803,7 +24678,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fe0a760e-f46f-4152-9753-4497ba47a8d4}">
+          <x14:cfRule type="dataBar" id="{b197a809-348b-44d9-a999-27a78e001bfc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24816,7 +24691,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba760814-98d9-42f0-bfb7-d9435ba2dfbf}">
+          <x14:cfRule type="dataBar" id="{f4d769d6-5e2c-4223-8934-90e7dffbf419}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24829,7 +24704,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{44a7a5cd-b628-4091-a4c1-d5828c0ed208}">
+          <x14:cfRule type="dataBar" id="{8c1fd285-8e9d-444b-a958-7c4598e8275c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24842,7 +24717,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0138e7c6-3b5f-48cd-9f19-e20aa03004c5}">
+          <x14:cfRule type="dataBar" id="{622dc457-61a6-47ea-9505-488aaa864ee4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24855,7 +24730,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{470d597e-54a4-470c-8b75-14a310ccbb42}">
+          <x14:cfRule type="dataBar" id="{8e4e4590-eeec-47e3-a926-0c76b04861bd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26581,7 +26456,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7b1fda9a-65c1-4651-8157-c5ad4349e5e9}</x14:id>
+          <x14:id>{81f6f9e7-a985-4595-adcf-3a0b98bc49bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26595,7 +26470,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79708284-c93d-4663-90fd-b750a0fc0ce5}</x14:id>
+          <x14:id>{492ab320-c910-4d9f-bb38-fa418698743b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26609,7 +26484,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a1b8c20-6667-4e2d-ad53-72687b778da5}</x14:id>
+          <x14:id>{23710130-a404-4e03-b99c-b36e79187513}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26623,7 +26498,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fda0b3a7-72d7-40b7-9c55-f33ee2be2bc2}</x14:id>
+          <x14:id>{02654944-0412-40c4-a564-137086f6bf63}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26637,7 +26512,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0635b5c-8448-4dec-bfe0-2c3b07080324}</x14:id>
+          <x14:id>{7044294f-93cf-4e36-b9dc-7dab8caef34b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26651,7 +26526,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6b4229f5-3522-4b89-8264-b99c364f9cbe}</x14:id>
+          <x14:id>{25ae9d96-b049-4461-b09c-042899fb4ac6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26665,7 +26540,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17c8f3c2-b673-405d-9481-b1fadea05c2f}</x14:id>
+          <x14:id>{adc8488e-6421-44dd-900c-9a23f9ff6039}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26679,7 +26554,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bbe56499-ad7d-4639-b113-ee40c42bdd5b}</x14:id>
+          <x14:id>{0dcc808e-d7ee-4908-a9c0-8e203edd6295}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26693,7 +26568,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{418ed7ac-f684-49be-a7f1-d551cfce090e}</x14:id>
+          <x14:id>{0a36933a-2306-495d-8147-0d65717d43fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26707,7 +26582,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31cd6dba-1d24-4b75-b71b-733f98eacbc4}</x14:id>
+          <x14:id>{b42e1ef0-8e80-4fa5-bbcd-0b27a29214dc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26721,7 +26596,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a04706c3-4667-4fe1-8bfa-6f0286778c5a}</x14:id>
+          <x14:id>{8cf0b732-c7ec-430c-b293-609a1988cd87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26757,7 +26632,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb90e259-0f01-4a4e-9975-761710cd5961}</x14:id>
+          <x14:id>{51bd2f33-25b6-40c5-b8c2-bfdf71dada50}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26776,7 +26651,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7b1fda9a-65c1-4651-8157-c5ad4349e5e9}">
+          <x14:cfRule type="dataBar" id="{81f6f9e7-a985-4595-adcf-3a0b98bc49bb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26789,7 +26664,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79708284-c93d-4663-90fd-b750a0fc0ce5}">
+          <x14:cfRule type="dataBar" id="{492ab320-c910-4d9f-bb38-fa418698743b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26802,7 +26677,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a1b8c20-6667-4e2d-ad53-72687b778da5}">
+          <x14:cfRule type="dataBar" id="{23710130-a404-4e03-b99c-b36e79187513}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26815,7 +26690,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fda0b3a7-72d7-40b7-9c55-f33ee2be2bc2}">
+          <x14:cfRule type="dataBar" id="{02654944-0412-40c4-a564-137086f6bf63}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26828,7 +26703,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c0635b5c-8448-4dec-bfe0-2c3b07080324}">
+          <x14:cfRule type="dataBar" id="{7044294f-93cf-4e36-b9dc-7dab8caef34b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26841,7 +26716,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6b4229f5-3522-4b89-8264-b99c364f9cbe}">
+          <x14:cfRule type="dataBar" id="{25ae9d96-b049-4461-b09c-042899fb4ac6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26854,7 +26729,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17c8f3c2-b673-405d-9481-b1fadea05c2f}">
+          <x14:cfRule type="dataBar" id="{adc8488e-6421-44dd-900c-9a23f9ff6039}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26867,7 +26742,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bbe56499-ad7d-4639-b113-ee40c42bdd5b}">
+          <x14:cfRule type="dataBar" id="{0dcc808e-d7ee-4908-a9c0-8e203edd6295}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26880,7 +26755,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{418ed7ac-f684-49be-a7f1-d551cfce090e}">
+          <x14:cfRule type="dataBar" id="{0a36933a-2306-495d-8147-0d65717d43fc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26893,7 +26768,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{31cd6dba-1d24-4b75-b71b-733f98eacbc4}">
+          <x14:cfRule type="dataBar" id="{b42e1ef0-8e80-4fa5-bbcd-0b27a29214dc}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26906,7 +26781,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a04706c3-4667-4fe1-8bfa-6f0286778c5a}">
+          <x14:cfRule type="dataBar" id="{8cf0b732-c7ec-430c-b293-609a1988cd87}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26919,7 +26794,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fb90e259-0f01-4a4e-9975-761710cd5961}">
+          <x14:cfRule type="dataBar" id="{51bd2f33-25b6-40c5-b8c2-bfdf71dada50}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37483,7 +37358,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{036fa8a5-9f07-475d-a8c3-89ba1bd660c3}</x14:id>
+          <x14:id>{95e38986-13f3-4134-a3ab-464e4333021e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37497,7 +37372,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{585121f7-cc18-486c-ba11-53be32b64d79}</x14:id>
+          <x14:id>{7f3d41e2-12d0-45e6-86ed-f2545223035e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37511,7 +37386,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93809c7b-34bf-437e-9e2c-3243856e49b6}</x14:id>
+          <x14:id>{00786b7a-4d6e-4d72-9dbe-59bd2a9021b4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37525,7 +37400,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1f70ae2-126d-4843-b3b8-a032c10ff269}</x14:id>
+          <x14:id>{6a39f0f8-f35e-457c-8958-8bfc3188f406}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37539,7 +37414,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33c93244-f236-4e54-b3a2-0f05cc97f5e5}</x14:id>
+          <x14:id>{90fd3eeb-e676-46ed-85fe-cf5c569eaa07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37553,7 +37428,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dfc65abf-5847-448f-91f8-0707fc0dd032}</x14:id>
+          <x14:id>{f7e47fde-d34f-414a-bfad-fb93a8103ebe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37573,7 +37448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a481f236-c09c-43c6-962e-2e5a4fb52c2e}</x14:id>
+          <x14:id>{24fe019d-b07f-40bc-9318-ec76f69f46aa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37587,7 +37462,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{202b56bb-e929-45c6-9dd6-cec02a09533c}</x14:id>
+          <x14:id>{e9524932-71df-451c-b926-486c5988d721}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37601,7 +37476,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac33fcc8-5096-45e7-8c84-41b5e1710ef0}</x14:id>
+          <x14:id>{69844d1e-6354-4ea9-a16a-393556ad8f3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37615,7 +37490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e133e48-e410-44ba-8124-8e0c8ed8e49b}</x14:id>
+          <x14:id>{1709ccbb-d311-400f-8bb5-041aafdc79f4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37629,7 +37504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4401627-5531-4ae2-87d8-359ddfd22486}</x14:id>
+          <x14:id>{79c1445a-b224-49c9-ba7a-0bb7b9b59c55}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37643,7 +37518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c575436-e946-4097-8c3f-d8864cceba09}</x14:id>
+          <x14:id>{9c6b8a00-7d4b-40a8-9f07-efc39709298b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37665,7 +37540,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e7ab7afe-05e0-44af-9a4f-8c265713bd39}</x14:id>
+          <x14:id>{310691b8-7273-4ed0-8e12-9c04b1858683}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37695,7 +37570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c2d21ee0-cd0a-4c8c-ae09-82ee3c8b0e97}</x14:id>
+          <x14:id>{2dc7f2a3-79c9-4808-b398-f036df91731a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37725,7 +37600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b224432d-48cc-450b-a197-a7108abcc18f}</x14:id>
+          <x14:id>{bd1c12ce-95d1-40c1-aace-82fb4f7dc827}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37755,7 +37630,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d753adf1-625a-4b92-bc6f-f026b659e77e}</x14:id>
+          <x14:id>{20ddf07f-1c7d-4559-aee1-12a6acd8a38d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37785,7 +37660,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ffd94e0-9a09-4366-8409-b6a952208003}</x14:id>
+          <x14:id>{cef98b52-0b11-4a9c-be4a-13d8a494f1ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37815,7 +37690,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db9c0acd-a431-4109-a94d-12688c16bb39}</x14:id>
+          <x14:id>{af839d7c-6ff7-4142-b5c4-f456c67d8099}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37837,7 +37712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{616f2165-df2f-460d-bc34-0009ba1f34b0}</x14:id>
+          <x14:id>{38536115-c2f8-4d86-821b-1abe20c40d3f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37859,7 +37734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29404a18-f2c9-4144-83c9-0d75c632486f}</x14:id>
+          <x14:id>{823bf1f5-a28f-4a49-adce-836f776ab77d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37881,7 +37756,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{754ca07a-956d-456f-8b87-10db99181fa2}</x14:id>
+          <x14:id>{90ba7c2d-555d-448d-9dbb-b05e7846ec6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37903,7 +37778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fafe6aa4-8870-43ea-bb1b-1b5333bdcad9}</x14:id>
+          <x14:id>{0d7dc7b0-474a-48a0-bf05-c0231a534939}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37925,7 +37800,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74286033-c341-4179-8f51-cb62496a45e7}</x14:id>
+          <x14:id>{47249e09-f8e1-4d9c-93e6-fdde79d2c211}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37947,7 +37822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f902f62-74c4-4eda-a3cd-dd09cf23d164}</x14:id>
+          <x14:id>{e3366ba3-8af1-44e9-9106-7dee791527fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37969,7 +37844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5a2451e-a02f-4418-9205-71f316c8d351}</x14:id>
+          <x14:id>{d43623ff-4657-4dfb-898b-d4a19feaabe2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37991,7 +37866,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb6a643e-b24a-4e34-a93e-5fb88c091f93}</x14:id>
+          <x14:id>{bebaef2a-c51e-4ded-9698-10c8a071eb6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38013,7 +37888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{842cc0f3-c80d-4918-86f1-019ddd3f205e}</x14:id>
+          <x14:id>{efd6c414-1292-4c0a-b55f-393891542356}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38035,7 +37910,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b58a480-5f59-4c19-b123-36152b742d6d}</x14:id>
+          <x14:id>{ce0b600b-adea-430e-9ed1-63b72605c66a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38057,7 +37932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba6bc233-d058-4097-b484-80f23c0ade48}</x14:id>
+          <x14:id>{27ce5550-deec-41c4-8081-12e8ed33749b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38079,7 +37954,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9319b857-5ad0-4044-ae2b-e111e8f8a1ae}</x14:id>
+          <x14:id>{b0642fa0-f9b6-402f-9ee9-8b5059320514}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38101,7 +37976,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ef5c172-d274-4d7e-b0fe-c542b944e42a}</x14:id>
+          <x14:id>{dd59f914-9f20-40ff-bebb-dce958874ab8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38123,7 +37998,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bf347055-c403-453d-b5d1-f2f998680542}</x14:id>
+          <x14:id>{94bb21f3-a44f-4fa6-b987-57118c6cb0b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38142,7 +38017,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{036fa8a5-9f07-475d-a8c3-89ba1bd660c3}">
+          <x14:cfRule type="dataBar" id="{95e38986-13f3-4134-a3ab-464e4333021e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38155,7 +38030,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{585121f7-cc18-486c-ba11-53be32b64d79}">
+          <x14:cfRule type="dataBar" id="{7f3d41e2-12d0-45e6-86ed-f2545223035e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38168,7 +38043,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93809c7b-34bf-437e-9e2c-3243856e49b6}">
+          <x14:cfRule type="dataBar" id="{00786b7a-4d6e-4d72-9dbe-59bd2a9021b4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38181,7 +38056,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c1f70ae2-126d-4843-b3b8-a032c10ff269}">
+          <x14:cfRule type="dataBar" id="{6a39f0f8-f35e-457c-8958-8bfc3188f406}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38194,7 +38069,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{33c93244-f236-4e54-b3a2-0f05cc97f5e5}">
+          <x14:cfRule type="dataBar" id="{90fd3eeb-e676-46ed-85fe-cf5c569eaa07}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38207,7 +38082,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dfc65abf-5847-448f-91f8-0707fc0dd032}">
+          <x14:cfRule type="dataBar" id="{f7e47fde-d34f-414a-bfad-fb93a8103ebe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38220,7 +38095,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a481f236-c09c-43c6-962e-2e5a4fb52c2e}">
+          <x14:cfRule type="dataBar" id="{24fe019d-b07f-40bc-9318-ec76f69f46aa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38233,7 +38108,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{202b56bb-e929-45c6-9dd6-cec02a09533c}">
+          <x14:cfRule type="dataBar" id="{e9524932-71df-451c-b926-486c5988d721}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38246,7 +38121,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ac33fcc8-5096-45e7-8c84-41b5e1710ef0}">
+          <x14:cfRule type="dataBar" id="{69844d1e-6354-4ea9-a16a-393556ad8f3a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38259,7 +38134,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e133e48-e410-44ba-8124-8e0c8ed8e49b}">
+          <x14:cfRule type="dataBar" id="{1709ccbb-d311-400f-8bb5-041aafdc79f4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38272,7 +38147,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f4401627-5531-4ae2-87d8-359ddfd22486}">
+          <x14:cfRule type="dataBar" id="{79c1445a-b224-49c9-ba7a-0bb7b9b59c55}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38285,7 +38160,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c575436-e946-4097-8c3f-d8864cceba09}">
+          <x14:cfRule type="dataBar" id="{9c6b8a00-7d4b-40a8-9f07-efc39709298b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38298,7 +38173,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e7ab7afe-05e0-44af-9a4f-8c265713bd39}">
+          <x14:cfRule type="dataBar" id="{310691b8-7273-4ed0-8e12-9c04b1858683}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38311,7 +38186,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c2d21ee0-cd0a-4c8c-ae09-82ee3c8b0e97}">
+          <x14:cfRule type="dataBar" id="{2dc7f2a3-79c9-4808-b398-f036df91731a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38324,7 +38199,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b224432d-48cc-450b-a197-a7108abcc18f}">
+          <x14:cfRule type="dataBar" id="{bd1c12ce-95d1-40c1-aace-82fb4f7dc827}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38337,7 +38212,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d753adf1-625a-4b92-bc6f-f026b659e77e}">
+          <x14:cfRule type="dataBar" id="{20ddf07f-1c7d-4559-aee1-12a6acd8a38d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38350,7 +38225,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4ffd94e0-9a09-4366-8409-b6a952208003}">
+          <x14:cfRule type="dataBar" id="{cef98b52-0b11-4a9c-be4a-13d8a494f1ec}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38363,7 +38238,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{db9c0acd-a431-4109-a94d-12688c16bb39}">
+          <x14:cfRule type="dataBar" id="{af839d7c-6ff7-4142-b5c4-f456c67d8099}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38376,7 +38251,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{616f2165-df2f-460d-bc34-0009ba1f34b0}">
+          <x14:cfRule type="dataBar" id="{38536115-c2f8-4d86-821b-1abe20c40d3f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38389,7 +38264,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{29404a18-f2c9-4144-83c9-0d75c632486f}">
+          <x14:cfRule type="dataBar" id="{823bf1f5-a28f-4a49-adce-836f776ab77d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38402,7 +38277,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{754ca07a-956d-456f-8b87-10db99181fa2}">
+          <x14:cfRule type="dataBar" id="{90ba7c2d-555d-448d-9dbb-b05e7846ec6a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38415,7 +38290,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fafe6aa4-8870-43ea-bb1b-1b5333bdcad9}">
+          <x14:cfRule type="dataBar" id="{0d7dc7b0-474a-48a0-bf05-c0231a534939}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38428,7 +38303,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{74286033-c341-4179-8f51-cb62496a45e7}">
+          <x14:cfRule type="dataBar" id="{47249e09-f8e1-4d9c-93e6-fdde79d2c211}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38441,7 +38316,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8f902f62-74c4-4eda-a3cd-dd09cf23d164}">
+          <x14:cfRule type="dataBar" id="{e3366ba3-8af1-44e9-9106-7dee791527fe}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38454,7 +38329,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b5a2451e-a02f-4418-9205-71f316c8d351}">
+          <x14:cfRule type="dataBar" id="{d43623ff-4657-4dfb-898b-d4a19feaabe2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38467,7 +38342,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cb6a643e-b24a-4e34-a93e-5fb88c091f93}">
+          <x14:cfRule type="dataBar" id="{bebaef2a-c51e-4ded-9698-10c8a071eb6a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38480,7 +38355,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{842cc0f3-c80d-4918-86f1-019ddd3f205e}">
+          <x14:cfRule type="dataBar" id="{efd6c414-1292-4c0a-b55f-393891542356}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38493,7 +38368,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8b58a480-5f59-4c19-b123-36152b742d6d}">
+          <x14:cfRule type="dataBar" id="{ce0b600b-adea-430e-9ed1-63b72605c66a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38506,7 +38381,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba6bc233-d058-4097-b484-80f23c0ade48}">
+          <x14:cfRule type="dataBar" id="{27ce5550-deec-41c4-8081-12e8ed33749b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38519,7 +38394,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9319b857-5ad0-4044-ae2b-e111e8f8a1ae}">
+          <x14:cfRule type="dataBar" id="{b0642fa0-f9b6-402f-9ee9-8b5059320514}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38532,7 +38407,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ef5c172-d274-4d7e-b0fe-c542b944e42a}">
+          <x14:cfRule type="dataBar" id="{dd59f914-9f20-40ff-bebb-dce958874ab8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38545,7 +38420,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bf347055-c403-453d-b5d1-f2f998680542}">
+          <x14:cfRule type="dataBar" id="{94bb21f3-a44f-4fa6-b987-57118c6cb0b3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -39583,7 +39458,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>843122.58</v>
+        <v>942119.47</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -39608,13 +39483,13 @@
       </c>
       <c r="C5" s="5">
         <f>(C7+D7+E7)/(C6+D6+E6)</f>
-        <v>0.956885151034567</v>
+        <v>0.792143661829141</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="6">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.949683042395043</v>
+        <v>0.942391249456729</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -39640,56 +39515,56 @@
         <v>24</v>
       </c>
       <c r="C6" s="9">
-        <f>[3]总目标!B31</f>
-        <v>249399.554098361</v>
+        <f>[3]总目标!B44</f>
+        <v>267032.554098361</v>
       </c>
       <c r="D6" s="9">
-        <f>[3]总目标!C31</f>
-        <v>359988.363934426</v>
+        <f>[3]总目标!C44</f>
+        <v>454472.298360656</v>
       </c>
       <c r="E6" s="9">
-        <f>[3]总目标!D31</f>
-        <v>283015.081967213</v>
+        <f>[3]总目标!D44</f>
+        <v>356490.491803279</v>
       </c>
       <c r="F6" s="9">
-        <f>[3]总目标!E31</f>
-        <v>292149.336065573</v>
+        <f>[3]总目标!E44</f>
+        <v>373135.56557377</v>
       </c>
       <c r="G6" s="9">
-        <f>[3]总目标!F31</f>
-        <v>251744.803278688</v>
+        <f>[3]总目标!F44</f>
+        <v>335343.491803279</v>
       </c>
       <c r="H6" s="9">
-        <f>[3]总目标!G31</f>
-        <v>343899.516393443</v>
+        <f>[3]总目标!G44</f>
+        <v>291232.549180328</v>
       </c>
       <c r="I6" s="9">
-        <f>[3]总目标!H31</f>
-        <v>432694.442622951</v>
+        <f>[3]总目标!H44</f>
+        <v>359127.885245902</v>
       </c>
       <c r="J6" s="9">
-        <f>[3]总目标!I31</f>
-        <v>416424.590163934</v>
+        <f>[3]总目标!I44</f>
+        <v>345231.147540984</v>
       </c>
       <c r="K6" s="9">
-        <f>[3]总目标!J31</f>
-        <v>396103.770491803</v>
+        <f>[3]总目标!J44</f>
+        <v>327791.967213115</v>
       </c>
       <c r="L6" s="9">
-        <f>[3]总目标!K31</f>
-        <v>385857.049180328</v>
+        <f>[3]总目标!K44</f>
+        <v>319748.852459016</v>
       </c>
       <c r="M6" s="9">
-        <f>[3]总目标!L31</f>
-        <v>398718.950819672</v>
+        <f>[3]总目标!L44</f>
+        <v>330407.147540984</v>
       </c>
       <c r="N6" s="9">
-        <f>[3]总目标!M31</f>
-        <v>262747.868852459</v>
+        <f>[3]总目标!M44</f>
+        <v>214260.819672131</v>
       </c>
       <c r="O6" s="28">
         <f t="shared" ref="O6:O10" si="0">SUM(C6:N6)</f>
-        <v>4072743.32786885</v>
+        <v>3974274.7704918</v>
       </c>
     </row>
     <row r="7" ht="15.6" spans="1:15">
@@ -39719,7 +39594,7 @@
       </c>
       <c r="H7" s="12">
         <f>[3]总目标!G32+[3]总目标!G33+[3]总目标!G34+[3]总目标!G35+[3]总目标!G36</f>
-        <v>177056.2</v>
+        <v>276053.09</v>
       </c>
       <c r="I7" s="12">
         <f>[3]总目标!H32+[3]总目标!H33+[3]总目标!H34+[3]总目标!H35+[3]总目标!H36</f>
@@ -39747,7 +39622,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="0"/>
-        <v>1697049.7594387</v>
+        <v>1796046.6494387</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -39757,27 +39632,27 @@
       </c>
       <c r="C8" s="20">
         <f t="shared" ref="C8:O8" si="1">C7/C6</f>
-        <v>0.738812073268772</v>
+        <v>0.690025986748588</v>
       </c>
       <c r="D8" s="20">
         <f t="shared" si="1"/>
-        <v>1.16070619488409</v>
+        <v>0.919397564190568</v>
       </c>
       <c r="E8" s="20">
         <f t="shared" si="1"/>
-        <v>0.889800825976057</v>
+        <v>0.706406087927508</v>
       </c>
       <c r="F8" s="20">
         <f t="shared" si="1"/>
-        <v>1.21460063808037</v>
+        <v>0.950980830397005</v>
       </c>
       <c r="G8" s="20">
         <f t="shared" si="1"/>
-        <v>1.23625832965247</v>
+        <v>0.928068137915646</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="1"/>
-        <v>0.514848644908929</v>
+        <v>0.94787856225875</v>
       </c>
       <c r="I8" s="20">
         <f t="shared" si="1"/>
@@ -39805,7 +39680,7 @@
       </c>
       <c r="O8" s="20">
         <f t="shared" si="1"/>
-        <v>0.416684682245055</v>
+        <v>0.451918086483096</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -40636,13 +40511,13 @@
       </c>
       <c r="C4" s="4">
         <f>(C7+D7+E7)</f>
-        <v>1374258.04</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>1440330.92</v>
+        <v>634245.75</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -40667,13 +40542,13 @@
       </c>
       <c r="C5" s="5">
         <f>(C7+D7+E7)/(C6+D6+E6)</f>
-        <v>1.00675391826253</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="6">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>1.15870955261306</v>
+        <v>0.634428715081241</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -40700,55 +40575,55 @@
       </c>
       <c r="C6" s="9">
         <f>[3]总目标!B44</f>
-        <v>372843</v>
+        <v>267032.554098361</v>
       </c>
       <c r="D6" s="9">
         <f>[3]总目标!C44</f>
-        <v>566214.491803279</v>
+        <v>454472.298360656</v>
       </c>
       <c r="E6" s="9">
         <f>[3]总目标!D44</f>
-        <v>425981.18852459</v>
+        <v>356490.491803279</v>
       </c>
       <c r="F6" s="9">
         <f>[3]总目标!E44</f>
-        <v>428093.165983607</v>
+        <v>373135.56557377</v>
       </c>
       <c r="G6" s="9">
         <f>[3]总目标!F44</f>
-        <v>438328.647540984</v>
+        <v>335343.491803279</v>
       </c>
       <c r="H6" s="9">
         <f>[3]总目标!G44</f>
-        <v>376625.606557377</v>
+        <v>291232.549180328</v>
       </c>
       <c r="I6" s="9">
         <f>[3]总目标!H44</f>
-        <v>516638.599385246</v>
+        <v>359127.885245902</v>
       </c>
       <c r="J6" s="9">
         <f>[3]总目标!I44</f>
-        <v>499972.838114754</v>
+        <v>345231.147540984</v>
       </c>
       <c r="K6" s="9">
         <f>[3]总目标!J44</f>
-        <v>490032.5</v>
+        <v>327791.967213115</v>
       </c>
       <c r="L6" s="9">
         <f>[3]总目标!K44</f>
-        <v>474225</v>
+        <v>319748.852459016</v>
       </c>
       <c r="M6" s="9">
         <f>[3]总目标!L44</f>
-        <v>490032.5</v>
+        <v>330407.147540984</v>
       </c>
       <c r="N6" s="9">
         <f>[3]总目标!M44</f>
-        <v>318392.868852459</v>
+        <v>214260.819672131</v>
       </c>
       <c r="O6" s="28">
         <f t="shared" ref="O6:O10" si="0">SUM(C6:N6)</f>
-        <v>5397380.4067623</v>
+        <v>3974274.7704918</v>
       </c>
     </row>
     <row r="7" ht="15.6" spans="1:15">
@@ -40758,27 +40633,27 @@
       </c>
       <c r="C7" s="12">
         <f>[3]总目标!B45+[3]总目标!B46+[3]总目标!B47+[3]总目标!B48+[3]总目标!B49</f>
-        <v>280693.58</v>
+        <v>0</v>
       </c>
       <c r="D7" s="12">
         <f>[3]总目标!C45+[3]总目标!C46+[3]总目标!C47+[3]总目标!C48+[3]总目标!C49</f>
-        <v>698300.67</v>
+        <v>0</v>
       </c>
       <c r="E7" s="12">
         <f>[3]总目标!D45+[3]总目标!D46+[3]总目标!D47+[3]总目标!D48+[3]总目标!D49</f>
-        <v>395263.79</v>
+        <v>0</v>
       </c>
       <c r="F7" s="12">
         <f>[3]总目标!E45+[3]总目标!E46+[3]总目标!E47+[3]总目标!E48+[3]总目标!E49</f>
-        <v>496825</v>
+        <v>0</v>
       </c>
       <c r="G7" s="12">
         <f>[3]总目标!F45+[3]总目标!F46+[3]总目标!F47+[3]总目标!F48+[3]总目标!F49</f>
-        <v>593668.09</v>
+        <v>368050.94</v>
       </c>
       <c r="H7" s="12">
         <f>[3]总目标!G45+[3]总目标!G46+[3]总目标!G47+[3]总目标!G48+[3]总目标!G49</f>
-        <v>349837.83</v>
+        <v>266194.81</v>
       </c>
       <c r="I7" s="12">
         <f>[3]总目标!H45+[3]总目标!H46+[3]总目标!H47+[3]总目标!H48+[3]总目标!H49</f>
@@ -40806,7 +40681,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="0"/>
-        <v>2814588.96</v>
+        <v>634245.75</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -40816,27 +40691,27 @@
       </c>
       <c r="C8" s="20">
         <f t="shared" ref="C8:O8" si="1">C7/C6</f>
-        <v>0.752846586901189</v>
+        <v>0</v>
       </c>
       <c r="D8" s="20">
         <f t="shared" si="1"/>
-        <v>1.2332794022563</v>
+        <v>0</v>
       </c>
       <c r="E8" s="20">
         <f t="shared" si="1"/>
-        <v>0.927890246442615</v>
+        <v>0</v>
       </c>
       <c r="F8" s="20">
         <f t="shared" si="1"/>
-        <v>1.1605534483562</v>
+        <v>0</v>
       </c>
       <c r="G8" s="20">
         <f t="shared" si="1"/>
-        <v>1.35439034918312</v>
+        <v>1.09753416719328</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="1"/>
-        <v>0.928874255783519</v>
+        <v>0.914028362383269</v>
       </c>
       <c r="I8" s="20">
         <f t="shared" si="1"/>
@@ -40864,7 +40739,7 @@
       </c>
       <c r="O8" s="20">
         <f t="shared" si="1"/>
-        <v>0.521473149543739</v>
+        <v>0.159587795667564</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -41693,25 +41568,25 @@
       </c>
       <c r="C4" s="4">
         <f>(C7+D7+E7)</f>
-        <v>1368108.78</v>
+        <v>2621693.39032787</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>507178.22</v>
+        <v>1857359.26254098</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="24">
         <f>(I7+J7+K7)</f>
-        <v>0</v>
+        <v>1506643.9375</v>
       </c>
       <c r="J4" s="24"/>
       <c r="K4" s="24"/>
       <c r="L4" s="25">
         <f>(L7+M7+N7)</f>
-        <v>0</v>
+        <v>1282650.36885246</v>
       </c>
       <c r="M4" s="25"/>
       <c r="N4" s="25"/>
@@ -41722,27 +41597,27 @@
       <c r="B5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="e">
         <f>(C7+D7+E7)/(C6+D6+E6)</f>
-        <v>0.924484046695538</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="6">
+      <c r="F5" s="6" t="e">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.340697665668934</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="26">
+      <c r="I5" s="26" t="e">
         <f>(I7+J7+K7)/(I6+J6+K6)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J5" s="26"/>
       <c r="K5" s="26"/>
-      <c r="L5" s="27">
+      <c r="L5" s="27" t="e">
         <f>(L7+M7+N7)/(L6+M6+N6)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M5" s="27"/>
       <c r="N5" s="27"/>
@@ -41755,57 +41630,57 @@
       <c r="B6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="9" t="str">
         <f>[3]总目标!B58</f>
-        <v>278839</v>
-      </c>
-      <c r="D6" s="9">
+        <v>2月</v>
+      </c>
+      <c r="D6" s="9" t="str">
         <f>[3]总目标!C58</f>
-        <v>672748.786885246</v>
-      </c>
-      <c r="E6" s="9">
+        <v>3月</v>
+      </c>
+      <c r="E6" s="9" t="str">
         <f>[3]总目标!D58</f>
-        <v>528274.180327869</v>
-      </c>
-      <c r="F6" s="9">
+        <v>4月</v>
+      </c>
+      <c r="F6" s="9" t="str">
         <f>[3]总目标!E58</f>
-        <v>526052.975409836</v>
-      </c>
-      <c r="G6" s="9">
+        <v>5月</v>
+      </c>
+      <c r="G6" s="9" t="str">
         <f>[3]总目标!F58</f>
-        <v>511352.459016394</v>
-      </c>
-      <c r="H6" s="9">
+        <v>6月</v>
+      </c>
+      <c r="H6" s="9" t="str">
         <f>[3]总目标!G58</f>
-        <v>451240.573770492</v>
-      </c>
-      <c r="I6" s="9">
+        <v>7月</v>
+      </c>
+      <c r="I6" s="9" t="str">
         <f>[3]总目标!H58</f>
-        <v>540132.311475409</v>
-      </c>
-      <c r="J6" s="9">
+        <v>8月</v>
+      </c>
+      <c r="J6" s="9" t="str">
         <f>[3]总目标!I58</f>
-        <v>525321.147540984</v>
-      </c>
-      <c r="K6" s="9">
+        <v>9月</v>
+      </c>
+      <c r="K6" s="9" t="str">
         <f>[3]总目标!J58</f>
-        <v>507300.262295082</v>
-      </c>
-      <c r="L6" s="9">
+        <v>10月</v>
+      </c>
+      <c r="L6" s="9" t="str">
         <f>[3]总目标!K58</f>
-        <v>494517.049180328</v>
-      </c>
-      <c r="M6" s="9">
+        <v>11月</v>
+      </c>
+      <c r="M6" s="9" t="str">
         <f>[3]总目标!L58</f>
-        <v>507296.196721311</v>
-      </c>
-      <c r="N6" s="9">
+        <v>12月</v>
+      </c>
+      <c r="N6" s="9" t="str">
         <f>[3]总目标!M58</f>
-        <v>361615.508196722</v>
+        <v>1月</v>
       </c>
       <c r="O6" s="28">
         <f>SUM(C6:N6)</f>
-        <v>5904690.45081967</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15.6" spans="1:15">
@@ -41815,54 +41690,54 @@
       </c>
       <c r="C7" s="12">
         <f>[3]总目标!B59+[3]总目标!B60+[3]总目标!B61+[3]总目标!B62+[3]总目标!B63</f>
-        <v>229311.59</v>
+        <v>653536.58</v>
       </c>
       <c r="D7" s="12">
         <f>[3]总目标!C59+[3]总目标!C60+[3]总目标!C61+[3]总目标!C62+[3]总目标!C63</f>
-        <v>770766.4</v>
+        <v>1146911.83180328</v>
       </c>
       <c r="E7" s="12">
         <f>[3]总目标!D59+[3]总目标!D60+[3]总目标!D61+[3]总目标!D62+[3]总目标!D63</f>
-        <v>368030.79</v>
+        <v>821244.97852459</v>
       </c>
       <c r="F7" s="12">
         <f>[3]总目标!E59+[3]总目标!E60+[3]总目标!E61+[3]总目标!E62+[3]总目标!E63</f>
-        <v>363130.13</v>
+        <v>846625.995983607</v>
       </c>
       <c r="G7" s="12">
         <v>144048.09</v>
       </c>
       <c r="H7" s="12">
         <f>[3]总目标!G59+[3]总目标!G60+[3]总目标!G61+[3]总目标!G62+[3]总目标!G63</f>
-        <v>0</v>
+        <v>866685.176557377</v>
       </c>
       <c r="I7" s="12">
         <f>[3]总目标!H59+[3]总目标!H60+[3]总目标!H61+[3]总目标!H62+[3]总目标!H63</f>
-        <v>0</v>
+        <v>516638.599385246</v>
       </c>
       <c r="J7" s="12">
         <f>[3]总目标!I59+[3]总目标!I60+[3]总目标!I61+[3]总目标!I62+[3]总目标!I63</f>
-        <v>0</v>
+        <v>499972.838114754</v>
       </c>
       <c r="K7" s="12">
         <f>[3]总目标!J59+[3]总目标!J60+[3]总目标!J61+[3]总目标!J62+[3]总目标!J63</f>
-        <v>0</v>
+        <v>490032.5</v>
       </c>
       <c r="L7" s="12">
         <f>[3]总目标!K59+[3]总目标!K60+[3]总目标!K61+[3]总目标!K62+[3]总目标!K63</f>
-        <v>0</v>
+        <v>474225</v>
       </c>
       <c r="M7" s="12">
         <f>[3]总目标!L59+[3]总目标!L60+[3]总目标!L61+[3]总目标!L62+[3]总目标!L63</f>
-        <v>0</v>
+        <v>490032.5</v>
       </c>
       <c r="N7" s="12">
         <f>[3]总目标!M59+[3]总目标!M60+[3]总目标!M61+[3]总目标!M62+[3]总目标!M63</f>
-        <v>0</v>
+        <v>318392.868852459</v>
       </c>
       <c r="O7" s="12">
         <f>SUM(C7:N7)</f>
-        <v>1875287</v>
+        <v>7268346.95922131</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -41870,57 +41745,57 @@
       <c r="B8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="20" t="e">
         <f t="shared" ref="C8:O8" si="0">C7/C6</f>
-        <v>0.822379903815463</v>
-      </c>
-      <c r="D8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>1.14569719786276</v>
-      </c>
-      <c r="E8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0.696666245871764</v>
-      </c>
-      <c r="F8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0.690291942017994</v>
-      </c>
-      <c r="G8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0.281700200048088</v>
-      </c>
-      <c r="H8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O8" s="20" t="e">
         <f t="shared" si="0"/>
-        <v>0.317592770631977</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -42449,27 +42324,27 @@
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="4" t="e">
         <f>(C7+D7+E7)</f>
-        <v>67790.26</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="3">
+      <c r="F4" s="3" t="e">
         <f>(F7+G7+H7)</f>
-        <v>108244.66</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="24">
+      <c r="I4" s="24" t="e">
         <f>(I7+J7+K7)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J4" s="24"/>
       <c r="K4" s="24"/>
-      <c r="L4" s="25">
+      <c r="L4" s="25" t="e">
         <f>(L7+M7+N7)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M4" s="25"/>
       <c r="N4" s="25"/>
@@ -42480,27 +42355,27 @@
       <c r="B5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="e">
         <f>(C7+D7+E7)/(C6+D6+E6)</f>
-        <v>0.265607553978094</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="6">
+      <c r="F5" s="6" t="e">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.219900676917594</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
-      <c r="I5" s="26">
+      <c r="I5" s="26" t="e">
         <f>(I7+J7+K7)/(I6+J6+K6)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J5" s="26"/>
       <c r="K5" s="26"/>
-      <c r="L5" s="27">
+      <c r="L5" s="27" t="e">
         <f>(L7+M7+N7)/(L6+M6+N6)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M5" s="27"/>
       <c r="N5" s="27"/>
@@ -42514,51 +42389,51 @@
         <v>24</v>
       </c>
       <c r="C6" s="9">
-        <f>[3]总目标!B70</f>
+        <f>[3]总目标!B85</f>
         <v>34481</v>
       </c>
       <c r="D6" s="9">
-        <f>[3]总目标!C70</f>
+        <f>[3]总目标!C85</f>
         <v>86791.2971311476</v>
       </c>
       <c r="E6" s="9">
-        <f>[3]总目标!D70</f>
+        <f>[3]总目标!D85</f>
         <v>133954.856557377</v>
       </c>
       <c r="F6" s="9">
-        <f>[3]总目标!E70</f>
+        <f>[3]总目标!E85</f>
         <v>141243.464139344</v>
       </c>
       <c r="G6" s="9">
-        <f>[3]总目标!F70</f>
+        <f>[3]总目标!F85</f>
         <v>195306.823770492</v>
       </c>
       <c r="H6" s="9">
-        <f>[3]总目标!G70</f>
+        <f>[3]总目标!G85</f>
         <v>155693.126331967</v>
       </c>
       <c r="I6" s="9">
-        <f>[3]总目标!H70</f>
+        <f>[3]总目标!H85</f>
         <v>213216.284836066</v>
       </c>
       <c r="J6" s="9">
-        <f>[3]总目标!I70</f>
+        <f>[3]总目标!I85</f>
         <v>206338.340163934</v>
       </c>
       <c r="K6" s="9">
-        <f>[3]总目标!J70</f>
+        <f>[3]总目标!J85</f>
         <v>195186.830942623</v>
       </c>
       <c r="L6" s="9">
-        <f>[3]总目标!K70</f>
+        <f>[3]总目标!K85</f>
         <v>187961.834016393</v>
       </c>
       <c r="M6" s="9">
-        <f>[3]总目标!L70</f>
+        <f>[3]总目标!L85</f>
         <v>195186.830942623</v>
       </c>
       <c r="N6" s="9">
-        <f>[3]总目标!M70</f>
+        <f>[3]总目标!M85</f>
         <v>98770.5102459016</v>
       </c>
       <c r="O6" s="28">
@@ -42571,56 +42446,56 @@
       <c r="B7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="12" t="e">
         <f>[3]总目标!B71+[3]总目标!B72+[3]总目标!B73+[3]总目标!B74+[3]总目标!B75</f>
-        <v>14803.76</v>
-      </c>
-      <c r="D7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D7" s="12" t="e">
         <f>[3]总目标!C71+[3]总目标!C72+[3]总目标!C73+[3]总目标!C74+[3]总目标!C75</f>
-        <v>38817.95</v>
-      </c>
-      <c r="E7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E7" s="12" t="e">
         <f>[3]总目标!D71+[3]总目标!D72+[3]总目标!D73+[3]总目标!D74+[3]总目标!D75</f>
-        <v>14168.55</v>
-      </c>
-      <c r="F7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" s="12" t="e">
         <f>[3]总目标!E71+[3]总目标!E72+[3]总目标!E73+[3]总目标!E74+[3]总目标!E75</f>
-        <v>49822.88</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G7" s="12">
         <v>21779.88</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="12" t="e">
         <f>[3]总目标!G71+[3]总目标!G72+[3]总目标!G73+[3]总目标!G74+[3]总目标!G75</f>
-        <v>36641.9</v>
-      </c>
-      <c r="I7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I7" s="12" t="e">
         <f>[3]总目标!H71+[3]总目标!H72+[3]总目标!H73+[3]总目标!H74+[3]总目标!H75</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J7" s="12" t="e">
         <f>[3]总目标!I71+[3]总目标!I72+[3]总目标!I73+[3]总目标!I74+[3]总目标!I75</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K7" s="12" t="e">
         <f>[3]总目标!J71+[3]总目标!J72+[3]总目标!J73+[3]总目标!J74+[3]总目标!J75</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L7" s="12" t="e">
         <f>[3]总目标!K71+[3]总目标!K72+[3]总目标!K73+[3]总目标!K74+[3]总目标!K75</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M7" s="12" t="e">
         <f>[3]总目标!L71+[3]总目标!L72+[3]总目标!L73+[3]总目标!L74+[3]总目标!L75</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N7" s="12" t="e">
         <f>[3]总目标!M71+[3]总目标!M72+[3]总目标!M73+[3]总目标!M74+[3]总目标!M75</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O7" s="12" t="e">
         <f t="shared" si="0"/>
-        <v>176034.92</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -42628,57 +42503,57 @@
       <c r="B8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="20" t="e">
         <f t="shared" ref="C8:O8" si="1">C7/C6</f>
-        <v>0.42933093587773</v>
-      </c>
-      <c r="D8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0.447256248991687</v>
-      </c>
-      <c r="E8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0.105771081124865</v>
-      </c>
-      <c r="F8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0.35274467603575</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G8" s="20">
         <f t="shared" si="1"/>
         <v>0.111516226517481</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0.235346934468209</v>
-      </c>
-      <c r="I8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="I8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="20">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O8" s="20" t="e">
         <f t="shared" si="1"/>
-        <v>0.0954568308849304</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -43501,13 +43376,13 @@
       </c>
       <c r="C4" s="4">
         <f>(C7+D7+E7)</f>
-        <v>1043940.28</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>495277.39</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -43532,13 +43407,13 @@
       </c>
       <c r="C5" s="5">
         <f>(C7+D7+E7)/(C6+D6+E6)</f>
-        <v>0.921997922968085</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="6">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.456719870619683</v>
+        <v>0</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -43564,51 +43439,51 @@
         <v>24</v>
       </c>
       <c r="C6" s="9">
-        <f>[3]总目标!B82</f>
+        <f>[3]总目标!B97</f>
         <v>249612</v>
       </c>
       <c r="D6" s="9">
-        <f>[3]总目标!C82</f>
+        <f>[3]总目标!C97</f>
         <v>485112.393442623</v>
       </c>
       <c r="E6" s="9">
-        <f>[3]总目标!D82</f>
+        <f>[3]总目标!D97</f>
         <v>397534.426229508</v>
       </c>
       <c r="F6" s="9">
-        <f>[3]总目标!E82</f>
+        <f>[3]总目标!E97</f>
         <v>391039.081967214</v>
       </c>
       <c r="G6" s="9">
-        <f>[3]总目标!F82</f>
+        <f>[3]总目标!F97</f>
         <v>369194.754098361</v>
       </c>
       <c r="H6" s="9">
-        <f>[3]总目标!G82</f>
+        <f>[3]总目标!G97</f>
         <v>324188.852459017</v>
       </c>
       <c r="I6" s="9">
-        <f>[3]总目标!H82</f>
+        <f>[3]总目标!H97</f>
         <v>367365.245901639</v>
       </c>
       <c r="J6" s="9">
-        <f>[3]总目标!I82</f>
+        <f>[3]总目标!I97</f>
         <v>355514.754098361</v>
       </c>
       <c r="K6" s="9">
-        <f>[3]总目标!J82</f>
+        <f>[3]总目标!J97</f>
         <v>342618.098360656</v>
       </c>
       <c r="L6" s="9">
-        <f>[3]总目标!K82</f>
+        <f>[3]总目标!K97</f>
         <v>336998.360655738</v>
       </c>
       <c r="M6" s="9">
-        <f>[3]总目标!L82</f>
+        <f>[3]总目标!L97</f>
         <v>344526.885245901</v>
       </c>
       <c r="N6" s="9">
-        <f>[3]总目标!M82</f>
+        <f>[3]总目标!M97</f>
         <v>252862.426229508</v>
       </c>
       <c r="O6" s="28">
@@ -43621,57 +43496,21 @@
       <c r="B7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="12">
-        <f>[3]总目标!B83+[3]总目标!B84+[3]总目标!B85+[3]总目标!B86+[3]总目标!B87</f>
-        <v>251227.75</v>
-      </c>
-      <c r="D7" s="12">
-        <f>[3]总目标!C83+[3]总目标!C84+[3]总目标!C85+[3]总目标!C86+[3]总目标!C87</f>
-        <v>461397.51</v>
-      </c>
-      <c r="E7" s="12">
-        <f>[3]总目标!D83+[3]总目标!D84+[3]总目标!D85+[3]总目标!D86+[3]总目标!D87</f>
-        <v>331315.02</v>
-      </c>
-      <c r="F7" s="12">
-        <f>[3]总目标!E83+[3]总目标!E84+[3]总目标!E85+[3]总目标!E86+[3]总目标!E87</f>
-        <v>245728.5</v>
-      </c>
-      <c r="G7" s="12">
-        <f>[3]总目标!F83+[3]总目标!F84+[3]总目标!F85+[3]总目标!F86+[3]总目标!F87</f>
-        <v>165047.71</v>
-      </c>
-      <c r="H7" s="12">
-        <f>[3]总目标!G83+[3]总目标!G84+[3]总目标!G85+[3]总目标!G86+[3]总目标!G87</f>
-        <v>84501.18</v>
-      </c>
-      <c r="I7" s="12">
-        <f>[3]总目标!H83+[3]总目标!H84+[3]总目标!H85+[3]总目标!H86+[3]总目标!H87</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="12">
-        <f>[3]总目标!I83+[3]总目标!I84+[3]总目标!I85+[3]总目标!I86+[3]总目标!I87</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="12">
-        <f>[3]总目标!J83+[3]总目标!J84+[3]总目标!J85+[3]总目标!J86+[3]总目标!J87</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="12">
-        <f>[3]总目标!K83+[3]总目标!K84+[3]总目标!K85+[3]总目标!K86+[3]总目标!K87</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="12">
-        <f>[3]总目标!L83+[3]总目标!L84+[3]总目标!L85+[3]总目标!L86+[3]总目标!L87</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="12">
-        <f>[3]总目标!M83+[3]总目标!M84+[3]总目标!M85+[3]总目标!M86+[3]总目标!M87</f>
-        <v>0</v>
-      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
       <c r="O7" s="12">
         <f t="shared" si="0"/>
-        <v>1539217.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -43681,27 +43520,27 @@
       </c>
       <c r="C8" s="20">
         <f t="shared" ref="C8:O8" si="1">C7/C6</f>
-        <v>1.00647304616765</v>
+        <v>0</v>
       </c>
       <c r="D8" s="20">
         <f t="shared" si="1"/>
-        <v>0.951114661750179</v>
+        <v>0</v>
       </c>
       <c r="E8" s="20">
         <f t="shared" si="1"/>
-        <v>0.833424725356295</v>
+        <v>0</v>
       </c>
       <c r="F8" s="20">
         <f t="shared" si="1"/>
-        <v>0.62839882592759</v>
+        <v>0</v>
       </c>
       <c r="G8" s="20">
         <f t="shared" si="1"/>
-        <v>0.447047820067421</v>
+        <v>0</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="1"/>
-        <v>0.260654181533532</v>
+        <v>0</v>
       </c>
       <c r="I8" s="20">
         <f t="shared" si="1"/>
@@ -43729,7 +43568,7 @@
       </c>
       <c r="O8" s="20">
         <f t="shared" si="1"/>
-        <v>0.365040462600834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -46150,7 +45989,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78e53764-6827-4788-9f66-e3e5f72980aa}</x14:id>
+          <x14:id>{4052ffb9-5868-461f-be15-eaca23cb5b83}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46164,7 +46003,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c15a8863-f298-4ff7-ab29-2e645aa09030}</x14:id>
+          <x14:id>{cf55cac8-7e19-4756-9971-340a54ac09ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46178,7 +46017,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2c89d0f0-7c72-45d5-9ad0-c8efc7334b82}</x14:id>
+          <x14:id>{46505f3d-599d-46c0-8a12-9381d6ffd955}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46192,7 +46031,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{705859b8-1d1c-459b-a515-d3e7e90e93e0}</x14:id>
+          <x14:id>{cbb022a6-4f86-435d-81f5-f191c1cc7fdf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46206,7 +46045,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e13f53ea-62de-45e7-aef1-34e493bf3dbe}</x14:id>
+          <x14:id>{552b9c34-e590-43cd-bc28-cbf71ad2b4d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46220,7 +46059,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2811f53a-0755-451f-ae07-c4ce26416500}</x14:id>
+          <x14:id>{f4abbeed-8ed2-4133-90ea-73fd66af5c71}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46234,7 +46073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc7a145c-7c57-41f1-8ab0-138010a5a7cf}</x14:id>
+          <x14:id>{c1c4381f-92a4-45c4-96ce-94ad69456211}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46248,7 +46087,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8f0a08d-2582-438c-b46f-1d199077c0c3}</x14:id>
+          <x14:id>{6356fa9c-67a8-4f0f-917d-53bb4ff4e43d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46262,7 +46101,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da210f3e-dab0-4936-ac18-c96e5b5be4a2}</x14:id>
+          <x14:id>{1550b14f-5b10-405a-b3db-c8a18a1f94d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46276,7 +46115,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed29bcc3-3715-4a42-ac1f-605bf22ae187}</x14:id>
+          <x14:id>{1926dcf0-7490-4ccd-a4f1-68c62ec183b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46290,7 +46129,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{916dc37a-b1a8-43fa-8309-521c3fcc54b4}</x14:id>
+          <x14:id>{e8f6b5a1-80ba-4292-83aa-8cb0c7cf6c1c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46326,7 +46165,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ec417d2-5a62-4e8b-8e57-6b0b3324f5c3}</x14:id>
+          <x14:id>{7a3a96a8-7a69-49ec-967d-78d7bde2f219}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46345,7 +46184,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{78e53764-6827-4788-9f66-e3e5f72980aa}">
+          <x14:cfRule type="dataBar" id="{4052ffb9-5868-461f-be15-eaca23cb5b83}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46358,7 +46197,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c15a8863-f298-4ff7-ab29-2e645aa09030}">
+          <x14:cfRule type="dataBar" id="{cf55cac8-7e19-4756-9971-340a54ac09ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46371,7 +46210,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2c89d0f0-7c72-45d5-9ad0-c8efc7334b82}">
+          <x14:cfRule type="dataBar" id="{46505f3d-599d-46c0-8a12-9381d6ffd955}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46384,7 +46223,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{705859b8-1d1c-459b-a515-d3e7e90e93e0}">
+          <x14:cfRule type="dataBar" id="{cbb022a6-4f86-435d-81f5-f191c1cc7fdf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46397,7 +46236,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e13f53ea-62de-45e7-aef1-34e493bf3dbe}">
+          <x14:cfRule type="dataBar" id="{552b9c34-e590-43cd-bc28-cbf71ad2b4d3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46410,7 +46249,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2811f53a-0755-451f-ae07-c4ce26416500}">
+          <x14:cfRule type="dataBar" id="{f4abbeed-8ed2-4133-90ea-73fd66af5c71}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46423,7 +46262,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc7a145c-7c57-41f1-8ab0-138010a5a7cf}">
+          <x14:cfRule type="dataBar" id="{c1c4381f-92a4-45c4-96ce-94ad69456211}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46436,7 +46275,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b8f0a08d-2582-438c-b46f-1d199077c0c3}">
+          <x14:cfRule type="dataBar" id="{6356fa9c-67a8-4f0f-917d-53bb4ff4e43d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46449,7 +46288,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{da210f3e-dab0-4936-ac18-c96e5b5be4a2}">
+          <x14:cfRule type="dataBar" id="{1550b14f-5b10-405a-b3db-c8a18a1f94d6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46462,7 +46301,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ed29bcc3-3715-4a42-ac1f-605bf22ae187}">
+          <x14:cfRule type="dataBar" id="{1926dcf0-7490-4ccd-a4f1-68c62ec183b1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46475,7 +46314,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{916dc37a-b1a8-43fa-8309-521c3fcc54b4}">
+          <x14:cfRule type="dataBar" id="{e8f6b5a1-80ba-4292-83aa-8cb0c7cf6c1c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46488,7 +46327,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0ec417d2-5a62-4e8b-8e57-6b0b3324f5c3}">
+          <x14:cfRule type="dataBar" id="{7a3a96a8-7a69-49ec-967d-78d7bde2f219}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46504,4 +46343,18 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<NetdiskSupbooks xmlns="http://www.wps.cn/et/2019/netdiskSupbooks">
+  <NetdiskSupbook Target="file:///C:\Users\12139\WPSDrive\1725300681\WPS企业云盘\瑞安市水滴电子商务有限公司\团队文档\俄罗斯运营一部\WB运营报表\目标\2026年俄罗斯一部目标拆分.xlsx" FileId="505692420986" NetdiskName="yunwps"/>
+</NetdiskSupbooks>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA11897-456E-43AF-AC28-93E1BBEC0A59}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.wps.cn/et/2019/netdiskSupbooks"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -23231,7 +23231,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{12705517-a1ac-4af3-9c47-dffcbd884c69}</x14:id>
+          <x14:id>{a0bf4642-49d5-4902-863b-b161d3ac2e43}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23245,7 +23245,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e1a063c-cfc4-4370-b5f5-e3d78bae61f4}</x14:id>
+          <x14:id>{c73feab8-9790-423c-815a-8d6d80400539}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23259,7 +23259,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d90900b-c779-4f2d-8b04-1d186ac211c5}</x14:id>
+          <x14:id>{a22acc92-8d40-489f-905e-7dc2e21ad47a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23273,7 +23273,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{538c34ba-3fe1-4246-a987-1e6331b69a84}</x14:id>
+          <x14:id>{bb2ba546-383a-408d-9258-176c2a4c9cc5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23287,7 +23287,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d191783-513b-4681-a0e0-1da47cce2353}</x14:id>
+          <x14:id>{1911f09d-a918-424f-8b83-38061cd6a8c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23301,7 +23301,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6de7bd0-e68f-4f22-9a4b-52508451c1bf}</x14:id>
+          <x14:id>{64fa7fee-d917-4de0-9f2c-445b0d3c0cea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23315,7 +23315,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f855105-ca70-48e9-bb22-0a86855ee54f}</x14:id>
+          <x14:id>{599f4c3d-84b4-43cf-9e7e-b4e2885abd59}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23329,7 +23329,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bbf82617-38a1-4e97-9e72-eb5a0c3bdb92}</x14:id>
+          <x14:id>{c327917d-ddae-4604-a315-4ee53f7f857f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23349,7 +23349,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60698893-4c65-4d50-af79-65729be2c6b5}</x14:id>
+          <x14:id>{278383ae-5d9e-4ba1-9eab-ce54cad1a3e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23377,7 +23377,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d3ac796-bdc0-45d4-8882-852723bc1c17}</x14:id>
+          <x14:id>{d40bccc4-781f-478a-91c5-afe98f15aeaf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23397,7 +23397,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{261db87c-1e88-4ec8-bfd4-f9ff58e6ab69}</x14:id>
+          <x14:id>{e0e54f1a-610f-44d6-9a42-75de4393b59c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23425,7 +23425,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c7327550-3ab0-47f9-87ae-ebc7daa8c728}</x14:id>
+          <x14:id>{55f821aa-6302-4bc2-9058-472ebe7b94cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23445,7 +23445,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cd911691-1116-42fe-bc53-67b1c0267f3b}</x14:id>
+          <x14:id>{d3866566-82c4-41d8-a6c1-357419a7e181}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23473,7 +23473,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{488d3490-7eae-4875-a20c-b6e313a891f8}</x14:id>
+          <x14:id>{041a0567-316c-4c6c-b59c-04cc0a128409}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23493,7 +23493,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d32d3730-c799-495f-ab3f-368a55c0587b}</x14:id>
+          <x14:id>{13edfe20-6c42-4c8d-af9d-9e2ec69aeaae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23521,7 +23521,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{917a537d-9e87-4c62-970e-2a3208257cff}</x14:id>
+          <x14:id>{3145c08a-d8f1-4263-b847-f6ca27453b95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23541,7 +23541,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0816f8a-cf6d-4ed6-be91-32fb8a7baa2b}</x14:id>
+          <x14:id>{cf2b4519-b2fb-4cc8-a377-bc0c000da78d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23569,7 +23569,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{46e4e21c-a7ec-4379-8b05-59f6f8733a0d}</x14:id>
+          <x14:id>{d54ffcba-f4e0-4a29-a988-b266d9749fea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23631,7 +23631,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62b58732-fa75-415f-ae8c-e06cbb39486c}</x14:id>
+          <x14:id>{135f8d21-d3d4-4de5-ae41-c1e1d6d183bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23661,7 +23661,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71e9fd37-0a20-44b6-bc97-8c3bc7b56d3c}</x14:id>
+          <x14:id>{7f5dccef-1bfb-492c-810e-be66cdfe0aaf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23683,7 +23683,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f554681-6d53-4dfd-9c51-909b0684a3a5}</x14:id>
+          <x14:id>{c23207e8-182b-40b1-9bcb-03876318e320}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23703,7 +23703,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53a4cf40-caa0-4fba-a9ce-286287c1ff0d}</x14:id>
+          <x14:id>{aaac129a-cbca-490b-b1be-888331b9f70a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23725,7 +23725,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7257bc84-0606-4596-9096-c367964143e1}</x14:id>
+          <x14:id>{c8cba163-b45a-4e26-a0ba-9a227b6f777a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23745,7 +23745,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b53cb82c-b426-442c-9227-d43032399732}</x14:id>
+          <x14:id>{d7451388-b77c-4e86-8099-85feb02bc130}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23767,7 +23767,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b670fcd2-c030-4af4-a7c8-fa413a7d467a}</x14:id>
+          <x14:id>{f46ba46a-a72d-4c82-bc6b-466cc725a101}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23787,7 +23787,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3b8e60aa-309d-4e94-9e38-064c7c48539b}</x14:id>
+          <x14:id>{596bc0b3-802d-4592-94cc-81c20fd68aa5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23809,7 +23809,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8004c6e5-6aef-472d-9deb-d7bb3eb0a282}</x14:id>
+          <x14:id>{62f6e842-9461-4335-ab10-020b94a0c86c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23829,7 +23829,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8514cc6f-c463-4734-8c35-aebf1ed97435}</x14:id>
+          <x14:id>{333ac094-d46f-4ba5-aa34-e2c597442e72}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23857,7 +23857,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a79d2cca-63f7-4381-b276-ddc721ebedda}</x14:id>
+          <x14:id>{e00d3cdb-d6b7-493d-a01d-92157d3877d2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23871,7 +23871,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{830a7799-181e-4617-84cd-a83d5c0c5070}</x14:id>
+          <x14:id>{1efa4371-2280-4078-b7a9-4bed4b5c3ad8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23901,7 +23901,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d533caa9-ee38-4a38-89c9-b295f24de74e}</x14:id>
+          <x14:id>{afa2d65e-8b95-482b-9232-62e59aa41830}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23923,7 +23923,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af742c9d-636f-4fff-ac6a-7f9c7f3c7037}</x14:id>
+          <x14:id>{26e8731e-9f2a-41b7-b680-0ccbeee0b679}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23945,7 +23945,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81f1277b-500d-4e6c-aadd-268bf1ea342a}</x14:id>
+          <x14:id>{3cdc7788-f761-42e3-be98-2218d145b981}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23967,7 +23967,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e850438a-52e9-4882-a1ef-da02391dd87e}</x14:id>
+          <x14:id>{33a32dd6-7c3d-4131-bff3-5d7a133657f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23989,7 +23989,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ac28c79-7159-43ed-93c3-5211aa02ceeb}</x14:id>
+          <x14:id>{57339abf-3c6b-4c81-a843-3b96853dd772}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24011,7 +24011,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e892bd2-e689-47f3-a102-223c279a2883}</x14:id>
+          <x14:id>{c5cc5271-65d0-4a0f-8cee-d2a5303bff74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24033,7 +24033,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7bf0662-6c40-4e21-832f-22511f489591}</x14:id>
+          <x14:id>{26477af8-b059-4a6c-965b-a6f139d7679b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24055,7 +24055,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3baefdbb-4bb1-49bd-a3d7-cd63bcb4e76f}</x14:id>
+          <x14:id>{38415ac6-3eea-4117-b45e-fee9baecd296}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24077,7 +24077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b197a809-348b-44d9-a999-27a78e001bfc}</x14:id>
+          <x14:id>{160e3e68-d9eb-41ff-a4b9-cf41893e7cd5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24099,7 +24099,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4d769d6-5e2c-4223-8934-90e7dffbf419}</x14:id>
+          <x14:id>{cb18ce02-89e7-4e45-b6bf-6c71c8b5ffe8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24121,7 +24121,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8c1fd285-8e9d-444b-a958-7c4598e8275c}</x14:id>
+          <x14:id>{904cf8e6-f644-4be8-b62c-6bc421b3bf03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24143,7 +24143,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{622dc457-61a6-47ea-9505-488aaa864ee4}</x14:id>
+          <x14:id>{ec21f11a-afe1-4d6c-aac2-cdcf67fc6d02}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24165,7 +24165,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e4e4590-eeec-47e3-a926-0c76b04861bd}</x14:id>
+          <x14:id>{2dae02d0-c2f2-4046-a497-b9cb14f37060}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24184,7 +24184,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{12705517-a1ac-4af3-9c47-dffcbd884c69}">
+          <x14:cfRule type="dataBar" id="{a0bf4642-49d5-4902-863b-b161d3ac2e43}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24197,7 +24197,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e1a063c-cfc4-4370-b5f5-e3d78bae61f4}">
+          <x14:cfRule type="dataBar" id="{c73feab8-9790-423c-815a-8d6d80400539}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24210,7 +24210,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d90900b-c779-4f2d-8b04-1d186ac211c5}">
+          <x14:cfRule type="dataBar" id="{a22acc92-8d40-489f-905e-7dc2e21ad47a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24223,7 +24223,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{538c34ba-3fe1-4246-a987-1e6331b69a84}">
+          <x14:cfRule type="dataBar" id="{bb2ba546-383a-408d-9258-176c2a4c9cc5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24236,7 +24236,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4d191783-513b-4681-a0e0-1da47cce2353}">
+          <x14:cfRule type="dataBar" id="{1911f09d-a918-424f-8b83-38061cd6a8c8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24249,7 +24249,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a6de7bd0-e68f-4f22-9a4b-52508451c1bf}">
+          <x14:cfRule type="dataBar" id="{64fa7fee-d917-4de0-9f2c-445b0d3c0cea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24262,7 +24262,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2f855105-ca70-48e9-bb22-0a86855ee54f}">
+          <x14:cfRule type="dataBar" id="{599f4c3d-84b4-43cf-9e7e-b4e2885abd59}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24275,7 +24275,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bbf82617-38a1-4e97-9e72-eb5a0c3bdb92}">
+          <x14:cfRule type="dataBar" id="{c327917d-ddae-4604-a315-4ee53f7f857f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24288,7 +24288,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{60698893-4c65-4d50-af79-65729be2c6b5}">
+          <x14:cfRule type="dataBar" id="{278383ae-5d9e-4ba1-9eab-ce54cad1a3e3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24301,7 +24301,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d3ac796-bdc0-45d4-8882-852723bc1c17}">
+          <x14:cfRule type="dataBar" id="{d40bccc4-781f-478a-91c5-afe98f15aeaf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24314,7 +24314,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{261db87c-1e88-4ec8-bfd4-f9ff58e6ab69}">
+          <x14:cfRule type="dataBar" id="{e0e54f1a-610f-44d6-9a42-75de4393b59c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24327,7 +24327,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c7327550-3ab0-47f9-87ae-ebc7daa8c728}">
+          <x14:cfRule type="dataBar" id="{55f821aa-6302-4bc2-9058-472ebe7b94cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24340,7 +24340,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cd911691-1116-42fe-bc53-67b1c0267f3b}">
+          <x14:cfRule type="dataBar" id="{d3866566-82c4-41d8-a6c1-357419a7e181}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24353,7 +24353,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{488d3490-7eae-4875-a20c-b6e313a891f8}">
+          <x14:cfRule type="dataBar" id="{041a0567-316c-4c6c-b59c-04cc0a128409}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24366,7 +24366,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d32d3730-c799-495f-ab3f-368a55c0587b}">
+          <x14:cfRule type="dataBar" id="{13edfe20-6c42-4c8d-af9d-9e2ec69aeaae}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24379,7 +24379,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{917a537d-9e87-4c62-970e-2a3208257cff}">
+          <x14:cfRule type="dataBar" id="{3145c08a-d8f1-4263-b847-f6ca27453b95}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24392,7 +24392,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a0816f8a-cf6d-4ed6-be91-32fb8a7baa2b}">
+          <x14:cfRule type="dataBar" id="{cf2b4519-b2fb-4cc8-a377-bc0c000da78d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24405,7 +24405,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{46e4e21c-a7ec-4379-8b05-59f6f8733a0d}">
+          <x14:cfRule type="dataBar" id="{d54ffcba-f4e0-4a29-a988-b266d9749fea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24418,7 +24418,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62b58732-fa75-415f-ae8c-e06cbb39486c}">
+          <x14:cfRule type="dataBar" id="{135f8d21-d3d4-4de5-ae41-c1e1d6d183bb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24431,7 +24431,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71e9fd37-0a20-44b6-bc97-8c3bc7b56d3c}">
+          <x14:cfRule type="dataBar" id="{7f5dccef-1bfb-492c-810e-be66cdfe0aaf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24444,7 +24444,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1f554681-6d53-4dfd-9c51-909b0684a3a5}">
+          <x14:cfRule type="dataBar" id="{c23207e8-182b-40b1-9bcb-03876318e320}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24457,7 +24457,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{53a4cf40-caa0-4fba-a9ce-286287c1ff0d}">
+          <x14:cfRule type="dataBar" id="{aaac129a-cbca-490b-b1be-888331b9f70a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24470,7 +24470,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7257bc84-0606-4596-9096-c367964143e1}">
+          <x14:cfRule type="dataBar" id="{c8cba163-b45a-4e26-a0ba-9a227b6f777a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24483,7 +24483,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b53cb82c-b426-442c-9227-d43032399732}">
+          <x14:cfRule type="dataBar" id="{d7451388-b77c-4e86-8099-85feb02bc130}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24496,7 +24496,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b670fcd2-c030-4af4-a7c8-fa413a7d467a}">
+          <x14:cfRule type="dataBar" id="{f46ba46a-a72d-4c82-bc6b-466cc725a101}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24509,7 +24509,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3b8e60aa-309d-4e94-9e38-064c7c48539b}">
+          <x14:cfRule type="dataBar" id="{596bc0b3-802d-4592-94cc-81c20fd68aa5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24522,7 +24522,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8004c6e5-6aef-472d-9deb-d7bb3eb0a282}">
+          <x14:cfRule type="dataBar" id="{62f6e842-9461-4335-ab10-020b94a0c86c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24535,7 +24535,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8514cc6f-c463-4734-8c35-aebf1ed97435}">
+          <x14:cfRule type="dataBar" id="{333ac094-d46f-4ba5-aa34-e2c597442e72}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24548,7 +24548,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a79d2cca-63f7-4381-b276-ddc721ebedda}">
+          <x14:cfRule type="dataBar" id="{e00d3cdb-d6b7-493d-a01d-92157d3877d2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24561,7 +24561,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{830a7799-181e-4617-84cd-a83d5c0c5070}">
+          <x14:cfRule type="dataBar" id="{1efa4371-2280-4078-b7a9-4bed4b5c3ad8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24574,7 +24574,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d533caa9-ee38-4a38-89c9-b295f24de74e}">
+          <x14:cfRule type="dataBar" id="{afa2d65e-8b95-482b-9232-62e59aa41830}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24587,7 +24587,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af742c9d-636f-4fff-ac6a-7f9c7f3c7037}">
+          <x14:cfRule type="dataBar" id="{26e8731e-9f2a-41b7-b680-0ccbeee0b679}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24600,7 +24600,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{81f1277b-500d-4e6c-aadd-268bf1ea342a}">
+          <x14:cfRule type="dataBar" id="{3cdc7788-f761-42e3-be98-2218d145b981}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24613,7 +24613,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e850438a-52e9-4882-a1ef-da02391dd87e}">
+          <x14:cfRule type="dataBar" id="{33a32dd6-7c3d-4131-bff3-5d7a133657f6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24626,7 +24626,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ac28c79-7159-43ed-93c3-5211aa02ceeb}">
+          <x14:cfRule type="dataBar" id="{57339abf-3c6b-4c81-a843-3b96853dd772}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24639,7 +24639,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2e892bd2-e689-47f3-a102-223c279a2883}">
+          <x14:cfRule type="dataBar" id="{c5cc5271-65d0-4a0f-8cee-d2a5303bff74}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24652,7 +24652,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a7bf0662-6c40-4e21-832f-22511f489591}">
+          <x14:cfRule type="dataBar" id="{26477af8-b059-4a6c-965b-a6f139d7679b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24665,7 +24665,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3baefdbb-4bb1-49bd-a3d7-cd63bcb4e76f}">
+          <x14:cfRule type="dataBar" id="{38415ac6-3eea-4117-b45e-fee9baecd296}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24678,7 +24678,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b197a809-348b-44d9-a999-27a78e001bfc}">
+          <x14:cfRule type="dataBar" id="{160e3e68-d9eb-41ff-a4b9-cf41893e7cd5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24691,7 +24691,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f4d769d6-5e2c-4223-8934-90e7dffbf419}">
+          <x14:cfRule type="dataBar" id="{cb18ce02-89e7-4e45-b6bf-6c71c8b5ffe8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24704,7 +24704,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8c1fd285-8e9d-444b-a958-7c4598e8275c}">
+          <x14:cfRule type="dataBar" id="{904cf8e6-f644-4be8-b62c-6bc421b3bf03}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24717,7 +24717,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{622dc457-61a6-47ea-9505-488aaa864ee4}">
+          <x14:cfRule type="dataBar" id="{ec21f11a-afe1-4d6c-aac2-cdcf67fc6d02}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24730,7 +24730,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e4e4590-eeec-47e3-a926-0c76b04861bd}">
+          <x14:cfRule type="dataBar" id="{2dae02d0-c2f2-4046-a497-b9cb14f37060}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26456,7 +26456,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81f6f9e7-a985-4595-adcf-3a0b98bc49bb}</x14:id>
+          <x14:id>{fa99523b-e76c-456c-bd7e-f6bf2bea820e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26470,7 +26470,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{492ab320-c910-4d9f-bb38-fa418698743b}</x14:id>
+          <x14:id>{6718fbf1-1f87-49f5-af7a-e3396e62aaf4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26484,7 +26484,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23710130-a404-4e03-b99c-b36e79187513}</x14:id>
+          <x14:id>{643c1a5e-ce2e-4677-8a5c-580b25e329a1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26498,7 +26498,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{02654944-0412-40c4-a564-137086f6bf63}</x14:id>
+          <x14:id>{7a2bb73b-5023-4039-8a00-e55ff4db7eb4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26512,7 +26512,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7044294f-93cf-4e36-b9dc-7dab8caef34b}</x14:id>
+          <x14:id>{c44cdf66-e4f9-4634-acbc-89e31d062a8e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26526,7 +26526,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25ae9d96-b049-4461-b09c-042899fb4ac6}</x14:id>
+          <x14:id>{2a0942f2-e06a-47f9-b53c-ae88b526adb3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26540,7 +26540,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{adc8488e-6421-44dd-900c-9a23f9ff6039}</x14:id>
+          <x14:id>{c4c0aaec-eebf-46ce-9dba-765bccaaa73d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26554,7 +26554,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0dcc808e-d7ee-4908-a9c0-8e203edd6295}</x14:id>
+          <x14:id>{b9f014e2-053c-4e4e-874c-02b5f83d3d2d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26568,7 +26568,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a36933a-2306-495d-8147-0d65717d43fc}</x14:id>
+          <x14:id>{f57805e7-f846-4c12-8bb3-3790f1ce9b59}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26582,7 +26582,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b42e1ef0-8e80-4fa5-bbcd-0b27a29214dc}</x14:id>
+          <x14:id>{f6ebb3ee-83b4-42b6-8a06-840ce59b0814}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26596,7 +26596,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8cf0b732-c7ec-430c-b293-609a1988cd87}</x14:id>
+          <x14:id>{a8138153-7df2-4f57-8b52-72dd9039d758}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26632,7 +26632,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51bd2f33-25b6-40c5-b8c2-bfdf71dada50}</x14:id>
+          <x14:id>{678360a4-2809-4c40-8343-58e66d1d4810}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26651,7 +26651,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{81f6f9e7-a985-4595-adcf-3a0b98bc49bb}">
+          <x14:cfRule type="dataBar" id="{fa99523b-e76c-456c-bd7e-f6bf2bea820e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26664,7 +26664,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{492ab320-c910-4d9f-bb38-fa418698743b}">
+          <x14:cfRule type="dataBar" id="{6718fbf1-1f87-49f5-af7a-e3396e62aaf4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26677,7 +26677,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{23710130-a404-4e03-b99c-b36e79187513}">
+          <x14:cfRule type="dataBar" id="{643c1a5e-ce2e-4677-8a5c-580b25e329a1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26690,7 +26690,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{02654944-0412-40c4-a564-137086f6bf63}">
+          <x14:cfRule type="dataBar" id="{7a2bb73b-5023-4039-8a00-e55ff4db7eb4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26703,7 +26703,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7044294f-93cf-4e36-b9dc-7dab8caef34b}">
+          <x14:cfRule type="dataBar" id="{c44cdf66-e4f9-4634-acbc-89e31d062a8e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26716,7 +26716,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{25ae9d96-b049-4461-b09c-042899fb4ac6}">
+          <x14:cfRule type="dataBar" id="{2a0942f2-e06a-47f9-b53c-ae88b526adb3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26729,7 +26729,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{adc8488e-6421-44dd-900c-9a23f9ff6039}">
+          <x14:cfRule type="dataBar" id="{c4c0aaec-eebf-46ce-9dba-765bccaaa73d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26742,7 +26742,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0dcc808e-d7ee-4908-a9c0-8e203edd6295}">
+          <x14:cfRule type="dataBar" id="{b9f014e2-053c-4e4e-874c-02b5f83d3d2d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26755,7 +26755,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0a36933a-2306-495d-8147-0d65717d43fc}">
+          <x14:cfRule type="dataBar" id="{f57805e7-f846-4c12-8bb3-3790f1ce9b59}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26768,7 +26768,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b42e1ef0-8e80-4fa5-bbcd-0b27a29214dc}">
+          <x14:cfRule type="dataBar" id="{f6ebb3ee-83b4-42b6-8a06-840ce59b0814}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26781,7 +26781,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8cf0b732-c7ec-430c-b293-609a1988cd87}">
+          <x14:cfRule type="dataBar" id="{a8138153-7df2-4f57-8b52-72dd9039d758}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26794,7 +26794,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{51bd2f33-25b6-40c5-b8c2-bfdf71dada50}">
+          <x14:cfRule type="dataBar" id="{678360a4-2809-4c40-8343-58e66d1d4810}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37358,7 +37358,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95e38986-13f3-4134-a3ab-464e4333021e}</x14:id>
+          <x14:id>{9c5d1ad8-68f3-4434-87e3-5eddface94d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37372,7 +37372,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f3d41e2-12d0-45e6-86ed-f2545223035e}</x14:id>
+          <x14:id>{ad83cb38-f319-4c0d-87c8-2258e6938332}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37386,7 +37386,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00786b7a-4d6e-4d72-9dbe-59bd2a9021b4}</x14:id>
+          <x14:id>{185753e8-8247-4775-a006-cd42020e4dd7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37400,7 +37400,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a39f0f8-f35e-457c-8958-8bfc3188f406}</x14:id>
+          <x14:id>{e0ec31ee-bc8a-4163-995b-51fcfa9f8778}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37414,7 +37414,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90fd3eeb-e676-46ed-85fe-cf5c569eaa07}</x14:id>
+          <x14:id>{2d4fe035-cc6f-4518-9be5-e680f27787db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37428,7 +37428,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7e47fde-d34f-414a-bfad-fb93a8103ebe}</x14:id>
+          <x14:id>{0cb395b8-a082-432b-9367-16ae43cdd4cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37448,7 +37448,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24fe019d-b07f-40bc-9318-ec76f69f46aa}</x14:id>
+          <x14:id>{279fc306-3f8f-4f23-bf93-70fe7f296f4b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37462,7 +37462,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e9524932-71df-451c-b926-486c5988d721}</x14:id>
+          <x14:id>{8994d41d-2cca-42c8-b08f-b34a540185ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37476,7 +37476,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{69844d1e-6354-4ea9-a16a-393556ad8f3a}</x14:id>
+          <x14:id>{131e2ecd-b6e8-476b-b4f1-17c6f3b19401}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37490,7 +37490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1709ccbb-d311-400f-8bb5-041aafdc79f4}</x14:id>
+          <x14:id>{38fb1d6d-f8fc-4dc7-b739-e19ec71b41fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37504,7 +37504,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79c1445a-b224-49c9-ba7a-0bb7b9b59c55}</x14:id>
+          <x14:id>{650d4031-5e2c-4ee4-99ae-76f68ed1eb37}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37518,7 +37518,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c6b8a00-7d4b-40a8-9f07-efc39709298b}</x14:id>
+          <x14:id>{ca5e0387-2f7a-4c75-89d8-612eab6b2034}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37540,7 +37540,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{310691b8-7273-4ed0-8e12-9c04b1858683}</x14:id>
+          <x14:id>{ae1b9f0c-36cf-42a9-b85a-d1b04b969df0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37570,7 +37570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2dc7f2a3-79c9-4808-b398-f036df91731a}</x14:id>
+          <x14:id>{5bb72168-38cf-4dce-b191-e66c8bb4b785}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37600,7 +37600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd1c12ce-95d1-40c1-aace-82fb4f7dc827}</x14:id>
+          <x14:id>{73a26aef-7573-4833-8201-ad23c9542779}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37630,7 +37630,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20ddf07f-1c7d-4559-aee1-12a6acd8a38d}</x14:id>
+          <x14:id>{884886ec-50e5-4da8-b430-37e8bdc9cd33}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37660,7 +37660,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cef98b52-0b11-4a9c-be4a-13d8a494f1ec}</x14:id>
+          <x14:id>{7052b3a1-c659-43e4-96c9-b89800d15fc2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37690,7 +37690,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af839d7c-6ff7-4142-b5c4-f456c67d8099}</x14:id>
+          <x14:id>{30dfc89d-1a76-4549-918f-f1394c193faa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37712,7 +37712,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38536115-c2f8-4d86-821b-1abe20c40d3f}</x14:id>
+          <x14:id>{1936c832-5108-4be7-b2a5-651fa920cacd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37734,7 +37734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{823bf1f5-a28f-4a49-adce-836f776ab77d}</x14:id>
+          <x14:id>{bf863f1b-f2ea-4051-862a-f0361cc144e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37756,7 +37756,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90ba7c2d-555d-448d-9dbb-b05e7846ec6a}</x14:id>
+          <x14:id>{0f464481-e54c-43b3-81b3-3c90ac6017e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37778,7 +37778,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d7dc7b0-474a-48a0-bf05-c0231a534939}</x14:id>
+          <x14:id>{5ed325c7-2e03-4f7e-b6d3-76ee1bd3fbb7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37800,7 +37800,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47249e09-f8e1-4d9c-93e6-fdde79d2c211}</x14:id>
+          <x14:id>{2515b826-6e0a-49c2-81d7-e1281ef64b1d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37822,7 +37822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3366ba3-8af1-44e9-9106-7dee791527fe}</x14:id>
+          <x14:id>{eae00273-fece-47e5-82a0-3fa174f3bf69}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37844,7 +37844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d43623ff-4657-4dfb-898b-d4a19feaabe2}</x14:id>
+          <x14:id>{7602e6e7-fdb1-49c7-861c-af5aeba6922c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37866,7 +37866,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bebaef2a-c51e-4ded-9698-10c8a071eb6a}</x14:id>
+          <x14:id>{265b9507-cdbd-4caf-8a3a-84ecbd8380bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37888,7 +37888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{efd6c414-1292-4c0a-b55f-393891542356}</x14:id>
+          <x14:id>{cdd6ebab-35a8-4277-a4b2-dd4631c7352a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37910,7 +37910,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce0b600b-adea-430e-9ed1-63b72605c66a}</x14:id>
+          <x14:id>{4d04061a-c38b-464a-96a9-172a76c739ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37932,7 +37932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27ce5550-deec-41c4-8081-12e8ed33749b}</x14:id>
+          <x14:id>{ba0b1fea-17d7-4e97-99a0-8d8e67710f74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37954,7 +37954,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b0642fa0-f9b6-402f-9ee9-8b5059320514}</x14:id>
+          <x14:id>{912ceddb-1d3c-49c6-809d-d9fcae8e3a5c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37976,7 +37976,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd59f914-9f20-40ff-bebb-dce958874ab8}</x14:id>
+          <x14:id>{60685b8d-a148-4ce5-b46e-533821d785d1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37998,7 +37998,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94bb21f3-a44f-4fa6-b987-57118c6cb0b3}</x14:id>
+          <x14:id>{58d55f2e-8d26-49c5-b9c6-0252ed45f587}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38017,7 +38017,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{95e38986-13f3-4134-a3ab-464e4333021e}">
+          <x14:cfRule type="dataBar" id="{9c5d1ad8-68f3-4434-87e3-5eddface94d6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38030,7 +38030,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7f3d41e2-12d0-45e6-86ed-f2545223035e}">
+          <x14:cfRule type="dataBar" id="{ad83cb38-f319-4c0d-87c8-2258e6938332}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38043,7 +38043,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00786b7a-4d6e-4d72-9dbe-59bd2a9021b4}">
+          <x14:cfRule type="dataBar" id="{185753e8-8247-4775-a006-cd42020e4dd7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38056,7 +38056,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6a39f0f8-f35e-457c-8958-8bfc3188f406}">
+          <x14:cfRule type="dataBar" id="{e0ec31ee-bc8a-4163-995b-51fcfa9f8778}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38069,7 +38069,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90fd3eeb-e676-46ed-85fe-cf5c569eaa07}">
+          <x14:cfRule type="dataBar" id="{2d4fe035-cc6f-4518-9be5-e680f27787db}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38082,7 +38082,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7e47fde-d34f-414a-bfad-fb93a8103ebe}">
+          <x14:cfRule type="dataBar" id="{0cb395b8-a082-432b-9367-16ae43cdd4cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38095,7 +38095,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{24fe019d-b07f-40bc-9318-ec76f69f46aa}">
+          <x14:cfRule type="dataBar" id="{279fc306-3f8f-4f23-bf93-70fe7f296f4b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38108,7 +38108,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e9524932-71df-451c-b926-486c5988d721}">
+          <x14:cfRule type="dataBar" id="{8994d41d-2cca-42c8-b08f-b34a540185ce}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38121,7 +38121,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{69844d1e-6354-4ea9-a16a-393556ad8f3a}">
+          <x14:cfRule type="dataBar" id="{131e2ecd-b6e8-476b-b4f1-17c6f3b19401}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38134,7 +38134,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1709ccbb-d311-400f-8bb5-041aafdc79f4}">
+          <x14:cfRule type="dataBar" id="{38fb1d6d-f8fc-4dc7-b739-e19ec71b41fa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38147,7 +38147,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79c1445a-b224-49c9-ba7a-0bb7b9b59c55}">
+          <x14:cfRule type="dataBar" id="{650d4031-5e2c-4ee4-99ae-76f68ed1eb37}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38160,7 +38160,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c6b8a00-7d4b-40a8-9f07-efc39709298b}">
+          <x14:cfRule type="dataBar" id="{ca5e0387-2f7a-4c75-89d8-612eab6b2034}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38173,7 +38173,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{310691b8-7273-4ed0-8e12-9c04b1858683}">
+          <x14:cfRule type="dataBar" id="{ae1b9f0c-36cf-42a9-b85a-d1b04b969df0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38186,7 +38186,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2dc7f2a3-79c9-4808-b398-f036df91731a}">
+          <x14:cfRule type="dataBar" id="{5bb72168-38cf-4dce-b191-e66c8bb4b785}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38199,7 +38199,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd1c12ce-95d1-40c1-aace-82fb4f7dc827}">
+          <x14:cfRule type="dataBar" id="{73a26aef-7573-4833-8201-ad23c9542779}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38212,7 +38212,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20ddf07f-1c7d-4559-aee1-12a6acd8a38d}">
+          <x14:cfRule type="dataBar" id="{884886ec-50e5-4da8-b430-37e8bdc9cd33}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38225,7 +38225,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cef98b52-0b11-4a9c-be4a-13d8a494f1ec}">
+          <x14:cfRule type="dataBar" id="{7052b3a1-c659-43e4-96c9-b89800d15fc2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38238,7 +38238,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af839d7c-6ff7-4142-b5c4-f456c67d8099}">
+          <x14:cfRule type="dataBar" id="{30dfc89d-1a76-4549-918f-f1394c193faa}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38251,7 +38251,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38536115-c2f8-4d86-821b-1abe20c40d3f}">
+          <x14:cfRule type="dataBar" id="{1936c832-5108-4be7-b2a5-651fa920cacd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38264,7 +38264,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{823bf1f5-a28f-4a49-adce-836f776ab77d}">
+          <x14:cfRule type="dataBar" id="{bf863f1b-f2ea-4051-862a-f0361cc144e9}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38277,7 +38277,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{90ba7c2d-555d-448d-9dbb-b05e7846ec6a}">
+          <x14:cfRule type="dataBar" id="{0f464481-e54c-43b3-81b3-3c90ac6017e8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38290,7 +38290,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d7dc7b0-474a-48a0-bf05-c0231a534939}">
+          <x14:cfRule type="dataBar" id="{5ed325c7-2e03-4f7e-b6d3-76ee1bd3fbb7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38303,7 +38303,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{47249e09-f8e1-4d9c-93e6-fdde79d2c211}">
+          <x14:cfRule type="dataBar" id="{2515b826-6e0a-49c2-81d7-e1281ef64b1d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38316,7 +38316,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e3366ba3-8af1-44e9-9106-7dee791527fe}">
+          <x14:cfRule type="dataBar" id="{eae00273-fece-47e5-82a0-3fa174f3bf69}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38329,7 +38329,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d43623ff-4657-4dfb-898b-d4a19feaabe2}">
+          <x14:cfRule type="dataBar" id="{7602e6e7-fdb1-49c7-861c-af5aeba6922c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38342,7 +38342,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bebaef2a-c51e-4ded-9698-10c8a071eb6a}">
+          <x14:cfRule type="dataBar" id="{265b9507-cdbd-4caf-8a3a-84ecbd8380bb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38355,7 +38355,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{efd6c414-1292-4c0a-b55f-393891542356}">
+          <x14:cfRule type="dataBar" id="{cdd6ebab-35a8-4277-a4b2-dd4631c7352a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38368,7 +38368,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce0b600b-adea-430e-9ed1-63b72605c66a}">
+          <x14:cfRule type="dataBar" id="{4d04061a-c38b-464a-96a9-172a76c739ea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38381,7 +38381,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{27ce5550-deec-41c4-8081-12e8ed33749b}">
+          <x14:cfRule type="dataBar" id="{ba0b1fea-17d7-4e97-99a0-8d8e67710f74}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38394,7 +38394,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b0642fa0-f9b6-402f-9ee9-8b5059320514}">
+          <x14:cfRule type="dataBar" id="{912ceddb-1d3c-49c6-809d-d9fcae8e3a5c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38407,7 +38407,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd59f914-9f20-40ff-bebb-dce958874ab8}">
+          <x14:cfRule type="dataBar" id="{60685b8d-a148-4ce5-b46e-533821d785d1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38420,7 +38420,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94bb21f3-a44f-4fa6-b987-57118c6cb0b3}">
+          <x14:cfRule type="dataBar" id="{58d55f2e-8d26-49c5-b9c6-0252ed45f587}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -39902,7 +39902,7 @@
         <f>[3]陈欣诺!M8</f>
         <v>5719.5</v>
       </c>
-      <c r="O14" s="30">
+      <c r="O14" s="36">
         <f>SUM(C14:N14)</f>
         <v>80239.99</v>
       </c>
@@ -45989,7 +45989,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4052ffb9-5868-461f-be15-eaca23cb5b83}</x14:id>
+          <x14:id>{fd07eebf-ad57-463d-99c1-fd3ec75ea292}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46003,7 +46003,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf55cac8-7e19-4756-9971-340a54ac09ee}</x14:id>
+          <x14:id>{343f6457-bcab-4383-9b99-dd3497f6f19f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46017,7 +46017,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{46505f3d-599d-46c0-8a12-9381d6ffd955}</x14:id>
+          <x14:id>{9fa8764b-6382-41d8-a03e-47733984e783}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46031,7 +46031,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbb022a6-4f86-435d-81f5-f191c1cc7fdf}</x14:id>
+          <x14:id>{8e4b3483-6a54-4439-aa00-6c5f95c3fdbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46045,7 +46045,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{552b9c34-e590-43cd-bc28-cbf71ad2b4d3}</x14:id>
+          <x14:id>{221221cf-574c-4b8b-aa5e-135f4187c80f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46059,7 +46059,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f4abbeed-8ed2-4133-90ea-73fd66af5c71}</x14:id>
+          <x14:id>{130ba751-1c36-4ba7-9e5a-3a1da5a2e1ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46073,7 +46073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1c4381f-92a4-45c4-96ce-94ad69456211}</x14:id>
+          <x14:id>{0e5d675c-9da6-4078-a1ba-a1f4e2c3b183}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46087,7 +46087,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6356fa9c-67a8-4f0f-917d-53bb4ff4e43d}</x14:id>
+          <x14:id>{eaf9691d-e9c3-4d1f-a6f1-461b59983a0a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46101,7 +46101,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1550b14f-5b10-405a-b3db-c8a18a1f94d6}</x14:id>
+          <x14:id>{2dcde596-dab4-4f85-910b-c8f6cfbfe036}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46115,7 +46115,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1926dcf0-7490-4ccd-a4f1-68c62ec183b1}</x14:id>
+          <x14:id>{9988af99-e592-42c7-8174-6070554d345b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46129,7 +46129,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8f6b5a1-80ba-4292-83aa-8cb0c7cf6c1c}</x14:id>
+          <x14:id>{9e4caeba-769d-4d44-8f63-1db346cfc980}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46165,7 +46165,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a3a96a8-7a69-49ec-967d-78d7bde2f219}</x14:id>
+          <x14:id>{1ae04b52-5fb8-4270-9dcd-b6e0211ab32a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46184,7 +46184,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4052ffb9-5868-461f-be15-eaca23cb5b83}">
+          <x14:cfRule type="dataBar" id="{fd07eebf-ad57-463d-99c1-fd3ec75ea292}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46197,7 +46197,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf55cac8-7e19-4756-9971-340a54ac09ee}">
+          <x14:cfRule type="dataBar" id="{343f6457-bcab-4383-9b99-dd3497f6f19f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46210,7 +46210,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{46505f3d-599d-46c0-8a12-9381d6ffd955}">
+          <x14:cfRule type="dataBar" id="{9fa8764b-6382-41d8-a03e-47733984e783}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46223,7 +46223,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cbb022a6-4f86-435d-81f5-f191c1cc7fdf}">
+          <x14:cfRule type="dataBar" id="{8e4b3483-6a54-4439-aa00-6c5f95c3fdbd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46236,7 +46236,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{552b9c34-e590-43cd-bc28-cbf71ad2b4d3}">
+          <x14:cfRule type="dataBar" id="{221221cf-574c-4b8b-aa5e-135f4187c80f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46249,7 +46249,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f4abbeed-8ed2-4133-90ea-73fd66af5c71}">
+          <x14:cfRule type="dataBar" id="{130ba751-1c36-4ba7-9e5a-3a1da5a2e1ae}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46262,7 +46262,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c1c4381f-92a4-45c4-96ce-94ad69456211}">
+          <x14:cfRule type="dataBar" id="{0e5d675c-9da6-4078-a1ba-a1f4e2c3b183}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46275,7 +46275,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6356fa9c-67a8-4f0f-917d-53bb4ff4e43d}">
+          <x14:cfRule type="dataBar" id="{eaf9691d-e9c3-4d1f-a6f1-461b59983a0a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46288,7 +46288,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1550b14f-5b10-405a-b3db-c8a18a1f94d6}">
+          <x14:cfRule type="dataBar" id="{2dcde596-dab4-4f85-910b-c8f6cfbfe036}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46301,7 +46301,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1926dcf0-7490-4ccd-a4f1-68c62ec183b1}">
+          <x14:cfRule type="dataBar" id="{9988af99-e592-42c7-8174-6070554d345b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46314,7 +46314,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e8f6b5a1-80ba-4292-83aa-8cb0c7cf6c1c}">
+          <x14:cfRule type="dataBar" id="{9e4caeba-769d-4d44-8f63-1db346cfc980}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46327,7 +46327,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7a3a96a8-7a69-49ec-967d-78d7bde2f219}">
+          <x14:cfRule type="dataBar" id="{1ae04b52-5fb8-4270-9dcd-b6e0211ab32a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -12918,8 +12918,9 @@
           <cell r="E59">
             <v>428093.165983607</v>
           </cell>
-        </row>
-        <row r="59">
+          <cell r="F59">
+            <v>438328.647540984</v>
+          </cell>
           <cell r="G59">
             <v>376625.606557377</v>
           </cell>
@@ -23231,7 +23232,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0bf4642-49d5-4902-863b-b161d3ac2e43}</x14:id>
+          <x14:id>{def1cc48-045d-43d8-911d-da0189b8d53a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23245,7 +23246,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c73feab8-9790-423c-815a-8d6d80400539}</x14:id>
+          <x14:id>{27dc84f6-5264-4585-9322-c916ee6a8210}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23259,7 +23260,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a22acc92-8d40-489f-905e-7dc2e21ad47a}</x14:id>
+          <x14:id>{e4cd20b2-5914-45be-89d0-9ebe5a7bccfb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23273,7 +23274,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bb2ba546-383a-408d-9258-176c2a4c9cc5}</x14:id>
+          <x14:id>{1d7a31d5-2187-4d56-9aae-4b4cd1960308}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23287,7 +23288,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1911f09d-a918-424f-8b83-38061cd6a8c8}</x14:id>
+          <x14:id>{9b0a9a7a-a9d7-41e5-83ae-135f858be01c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23301,7 +23302,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{64fa7fee-d917-4de0-9f2c-445b0d3c0cea}</x14:id>
+          <x14:id>{af12d1fb-72e9-42b8-a6dc-aa2115b1596c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23315,7 +23316,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{599f4c3d-84b4-43cf-9e7e-b4e2885abd59}</x14:id>
+          <x14:id>{5f2166c8-1a61-4cde-96cf-122c6218227b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23329,7 +23330,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c327917d-ddae-4604-a315-4ee53f7f857f}</x14:id>
+          <x14:id>{2330c03d-92eb-4eb6-aaaa-ed153cf3527f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23349,7 +23350,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{278383ae-5d9e-4ba1-9eab-ce54cad1a3e3}</x14:id>
+          <x14:id>{2b089e82-d75a-4b9b-863e-d67d565143c0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23377,7 +23378,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d40bccc4-781f-478a-91c5-afe98f15aeaf}</x14:id>
+          <x14:id>{7863629a-2b10-4a75-b9b9-5b00bb73b2bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23397,7 +23398,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0e54f1a-610f-44d6-9a42-75de4393b59c}</x14:id>
+          <x14:id>{77b48896-8834-49ae-ac67-a03268417c86}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23425,7 +23426,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55f821aa-6302-4bc2-9058-472ebe7b94cd}</x14:id>
+          <x14:id>{82a1a8e8-a8a2-4e8d-a3eb-4a37deaa259c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23445,7 +23446,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d3866566-82c4-41d8-a6c1-357419a7e181}</x14:id>
+          <x14:id>{3ea12327-1484-4ca7-a2a3-3b9830597acd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23473,7 +23474,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{041a0567-316c-4c6c-b59c-04cc0a128409}</x14:id>
+          <x14:id>{d365cafd-d987-4ecc-945c-e7ffbbd5a8b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23493,7 +23494,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13edfe20-6c42-4c8d-af9d-9e2ec69aeaae}</x14:id>
+          <x14:id>{8bd1842e-6765-42ae-a3e0-7940c878a0ef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23521,7 +23522,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3145c08a-d8f1-4263-b847-f6ca27453b95}</x14:id>
+          <x14:id>{fa50584f-8e2a-4b7d-ae43-4d4868eff7d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23541,7 +23542,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf2b4519-b2fb-4cc8-a377-bc0c000da78d}</x14:id>
+          <x14:id>{b92da82f-36b3-44d4-aee1-78931aebe406}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23569,7 +23570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d54ffcba-f4e0-4a29-a988-b266d9749fea}</x14:id>
+          <x14:id>{10f03b71-5b7d-4bb1-8af3-e0d920219dd4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23631,7 +23632,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{135f8d21-d3d4-4de5-ae41-c1e1d6d183bb}</x14:id>
+          <x14:id>{6e8f3f5a-0882-4fb4-8c12-2056c4a2c449}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23661,7 +23662,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7f5dccef-1bfb-492c-810e-be66cdfe0aaf}</x14:id>
+          <x14:id>{fabd9b76-78bf-4952-852e-e1addfeee7ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23683,7 +23684,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c23207e8-182b-40b1-9bcb-03876318e320}</x14:id>
+          <x14:id>{a7d26abd-6200-4fdb-84ba-174470d2f519}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23703,7 +23704,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aaac129a-cbca-490b-b1be-888331b9f70a}</x14:id>
+          <x14:id>{374dc5d8-438a-442e-80e4-25b2421ed0ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23725,7 +23726,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8cba163-b45a-4e26-a0ba-9a227b6f777a}</x14:id>
+          <x14:id>{f53c3f17-0e88-4052-aefc-4859cbd0f674}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23745,7 +23746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d7451388-b77c-4e86-8099-85feb02bc130}</x14:id>
+          <x14:id>{e843d7c6-c2fa-4440-b740-2b7932f00a00}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23767,7 +23768,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f46ba46a-a72d-4c82-bc6b-466cc725a101}</x14:id>
+          <x14:id>{c21e2b1c-b01c-41c4-b1da-65f2f286ce6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23787,7 +23788,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{596bc0b3-802d-4592-94cc-81c20fd68aa5}</x14:id>
+          <x14:id>{941253e4-f0ed-4b6d-983f-5cace3e58429}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23809,7 +23810,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62f6e842-9461-4335-ab10-020b94a0c86c}</x14:id>
+          <x14:id>{5efcbe13-516c-4e0d-9a50-85f0134b8107}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23829,7 +23830,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{333ac094-d46f-4ba5-aa34-e2c597442e72}</x14:id>
+          <x14:id>{93bc68f4-b29e-44f8-8618-f5ee45dd230f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23857,7 +23858,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e00d3cdb-d6b7-493d-a01d-92157d3877d2}</x14:id>
+          <x14:id>{2647211d-7189-4de4-b029-cfefd999b4bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23871,7 +23872,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1efa4371-2280-4078-b7a9-4bed4b5c3ad8}</x14:id>
+          <x14:id>{a2ab54dd-a64a-496e-920d-8a26239ffa7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23901,7 +23902,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{afa2d65e-8b95-482b-9232-62e59aa41830}</x14:id>
+          <x14:id>{d90a73b3-2459-47b8-b09b-981ae88f4091}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23923,7 +23924,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26e8731e-9f2a-41b7-b680-0ccbeee0b679}</x14:id>
+          <x14:id>{917aa60c-8061-4e98-925e-b24e0ec135f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23945,7 +23946,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3cdc7788-f761-42e3-be98-2218d145b981}</x14:id>
+          <x14:id>{917002c4-af57-4690-9927-c5a2432352c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23967,7 +23968,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33a32dd6-7c3d-4131-bff3-5d7a133657f6}</x14:id>
+          <x14:id>{8fcc5889-6eaa-4c4d-87da-55b54ab2df25}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23989,7 +23990,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57339abf-3c6b-4c81-a843-3b96853dd772}</x14:id>
+          <x14:id>{71ad9c27-4f7d-4192-af46-ef2b78004183}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24011,7 +24012,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5cc5271-65d0-4a0f-8cee-d2a5303bff74}</x14:id>
+          <x14:id>{9d3c53b1-0334-4a84-9b83-1f6960e679f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24033,7 +24034,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26477af8-b059-4a6c-965b-a6f139d7679b}</x14:id>
+          <x14:id>{3c4c1ab1-5ba6-4c32-a846-d16fc750c010}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24055,7 +24056,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38415ac6-3eea-4117-b45e-fee9baecd296}</x14:id>
+          <x14:id>{108b2412-fd92-4673-9a32-aa76fb093f32}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24077,7 +24078,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{160e3e68-d9eb-41ff-a4b9-cf41893e7cd5}</x14:id>
+          <x14:id>{ec1fa653-4925-4a1a-b9e8-6e2db966f925}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24099,7 +24100,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb18ce02-89e7-4e45-b6bf-6c71c8b5ffe8}</x14:id>
+          <x14:id>{4638a353-201f-4f30-b760-3bab4f315afb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24121,7 +24122,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{904cf8e6-f644-4be8-b62c-6bc421b3bf03}</x14:id>
+          <x14:id>{badfdc39-a2cd-4972-9578-9f83d5ec36f4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24143,7 +24144,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec21f11a-afe1-4d6c-aac2-cdcf67fc6d02}</x14:id>
+          <x14:id>{c874ea18-6939-4fe6-af69-f2fac0f44c53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24165,7 +24166,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2dae02d0-c2f2-4046-a497-b9cb14f37060}</x14:id>
+          <x14:id>{42b014e9-01ce-4835-9fdc-cba3990bcdf0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24184,7 +24185,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a0bf4642-49d5-4902-863b-b161d3ac2e43}">
+          <x14:cfRule type="dataBar" id="{def1cc48-045d-43d8-911d-da0189b8d53a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24197,7 +24198,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c73feab8-9790-423c-815a-8d6d80400539}">
+          <x14:cfRule type="dataBar" id="{27dc84f6-5264-4585-9322-c916ee6a8210}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24210,7 +24211,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a22acc92-8d40-489f-905e-7dc2e21ad47a}">
+          <x14:cfRule type="dataBar" id="{e4cd20b2-5914-45be-89d0-9ebe5a7bccfb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24223,7 +24224,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bb2ba546-383a-408d-9258-176c2a4c9cc5}">
+          <x14:cfRule type="dataBar" id="{1d7a31d5-2187-4d56-9aae-4b4cd1960308}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24236,7 +24237,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1911f09d-a918-424f-8b83-38061cd6a8c8}">
+          <x14:cfRule type="dataBar" id="{9b0a9a7a-a9d7-41e5-83ae-135f858be01c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24249,7 +24250,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{64fa7fee-d917-4de0-9f2c-445b0d3c0cea}">
+          <x14:cfRule type="dataBar" id="{af12d1fb-72e9-42b8-a6dc-aa2115b1596c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24262,7 +24263,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{599f4c3d-84b4-43cf-9e7e-b4e2885abd59}">
+          <x14:cfRule type="dataBar" id="{5f2166c8-1a61-4cde-96cf-122c6218227b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24275,7 +24276,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c327917d-ddae-4604-a315-4ee53f7f857f}">
+          <x14:cfRule type="dataBar" id="{2330c03d-92eb-4eb6-aaaa-ed153cf3527f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24288,7 +24289,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{278383ae-5d9e-4ba1-9eab-ce54cad1a3e3}">
+          <x14:cfRule type="dataBar" id="{2b089e82-d75a-4b9b-863e-d67d565143c0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24301,7 +24302,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d40bccc4-781f-478a-91c5-afe98f15aeaf}">
+          <x14:cfRule type="dataBar" id="{7863629a-2b10-4a75-b9b9-5b00bb73b2bb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24314,7 +24315,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e0e54f1a-610f-44d6-9a42-75de4393b59c}">
+          <x14:cfRule type="dataBar" id="{77b48896-8834-49ae-ac67-a03268417c86}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24327,7 +24328,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55f821aa-6302-4bc2-9058-472ebe7b94cd}">
+          <x14:cfRule type="dataBar" id="{82a1a8e8-a8a2-4e8d-a3eb-4a37deaa259c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24340,7 +24341,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d3866566-82c4-41d8-a6c1-357419a7e181}">
+          <x14:cfRule type="dataBar" id="{3ea12327-1484-4ca7-a2a3-3b9830597acd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24353,7 +24354,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{041a0567-316c-4c6c-b59c-04cc0a128409}">
+          <x14:cfRule type="dataBar" id="{d365cafd-d987-4ecc-945c-e7ffbbd5a8b0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24366,7 +24367,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{13edfe20-6c42-4c8d-af9d-9e2ec69aeaae}">
+          <x14:cfRule type="dataBar" id="{8bd1842e-6765-42ae-a3e0-7940c878a0ef}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24379,7 +24380,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3145c08a-d8f1-4263-b847-f6ca27453b95}">
+          <x14:cfRule type="dataBar" id="{fa50584f-8e2a-4b7d-ae43-4d4868eff7d6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24392,7 +24393,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf2b4519-b2fb-4cc8-a377-bc0c000da78d}">
+          <x14:cfRule type="dataBar" id="{b92da82f-36b3-44d4-aee1-78931aebe406}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24405,7 +24406,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d54ffcba-f4e0-4a29-a988-b266d9749fea}">
+          <x14:cfRule type="dataBar" id="{10f03b71-5b7d-4bb1-8af3-e0d920219dd4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24418,7 +24419,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{135f8d21-d3d4-4de5-ae41-c1e1d6d183bb}">
+          <x14:cfRule type="dataBar" id="{6e8f3f5a-0882-4fb4-8c12-2056c4a2c449}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24431,7 +24432,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7f5dccef-1bfb-492c-810e-be66cdfe0aaf}">
+          <x14:cfRule type="dataBar" id="{fabd9b76-78bf-4952-852e-e1addfeee7ea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24444,7 +24445,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c23207e8-182b-40b1-9bcb-03876318e320}">
+          <x14:cfRule type="dataBar" id="{a7d26abd-6200-4fdb-84ba-174470d2f519}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24457,7 +24458,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aaac129a-cbca-490b-b1be-888331b9f70a}">
+          <x14:cfRule type="dataBar" id="{374dc5d8-438a-442e-80e4-25b2421ed0ea}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24470,7 +24471,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c8cba163-b45a-4e26-a0ba-9a227b6f777a}">
+          <x14:cfRule type="dataBar" id="{f53c3f17-0e88-4052-aefc-4859cbd0f674}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24483,7 +24484,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d7451388-b77c-4e86-8099-85feb02bc130}">
+          <x14:cfRule type="dataBar" id="{e843d7c6-c2fa-4440-b740-2b7932f00a00}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24496,7 +24497,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f46ba46a-a72d-4c82-bc6b-466cc725a101}">
+          <x14:cfRule type="dataBar" id="{c21e2b1c-b01c-41c4-b1da-65f2f286ce6c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24509,7 +24510,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{596bc0b3-802d-4592-94cc-81c20fd68aa5}">
+          <x14:cfRule type="dataBar" id="{941253e4-f0ed-4b6d-983f-5cace3e58429}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24522,7 +24523,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62f6e842-9461-4335-ab10-020b94a0c86c}">
+          <x14:cfRule type="dataBar" id="{5efcbe13-516c-4e0d-9a50-85f0134b8107}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24535,7 +24536,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{333ac094-d46f-4ba5-aa34-e2c597442e72}">
+          <x14:cfRule type="dataBar" id="{93bc68f4-b29e-44f8-8618-f5ee45dd230f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24548,7 +24549,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e00d3cdb-d6b7-493d-a01d-92157d3877d2}">
+          <x14:cfRule type="dataBar" id="{2647211d-7189-4de4-b029-cfefd999b4bd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24561,7 +24562,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1efa4371-2280-4078-b7a9-4bed4b5c3ad8}">
+          <x14:cfRule type="dataBar" id="{a2ab54dd-a64a-496e-920d-8a26239ffa7a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24574,7 +24575,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{afa2d65e-8b95-482b-9232-62e59aa41830}">
+          <x14:cfRule type="dataBar" id="{d90a73b3-2459-47b8-b09b-981ae88f4091}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24587,7 +24588,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{26e8731e-9f2a-41b7-b680-0ccbeee0b679}">
+          <x14:cfRule type="dataBar" id="{917aa60c-8061-4e98-925e-b24e0ec135f1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24600,7 +24601,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3cdc7788-f761-42e3-be98-2218d145b981}">
+          <x14:cfRule type="dataBar" id="{917002c4-af57-4690-9927-c5a2432352c7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24613,7 +24614,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{33a32dd6-7c3d-4131-bff3-5d7a133657f6}">
+          <x14:cfRule type="dataBar" id="{8fcc5889-6eaa-4c4d-87da-55b54ab2df25}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24626,7 +24627,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{57339abf-3c6b-4c81-a843-3b96853dd772}">
+          <x14:cfRule type="dataBar" id="{71ad9c27-4f7d-4192-af46-ef2b78004183}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24639,7 +24640,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c5cc5271-65d0-4a0f-8cee-d2a5303bff74}">
+          <x14:cfRule type="dataBar" id="{9d3c53b1-0334-4a84-9b83-1f6960e679f0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24652,7 +24653,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{26477af8-b059-4a6c-965b-a6f139d7679b}">
+          <x14:cfRule type="dataBar" id="{3c4c1ab1-5ba6-4c32-a846-d16fc750c010}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24665,7 +24666,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38415ac6-3eea-4117-b45e-fee9baecd296}">
+          <x14:cfRule type="dataBar" id="{108b2412-fd92-4673-9a32-aa76fb093f32}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24678,7 +24679,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{160e3e68-d9eb-41ff-a4b9-cf41893e7cd5}">
+          <x14:cfRule type="dataBar" id="{ec1fa653-4925-4a1a-b9e8-6e2db966f925}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24691,7 +24692,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cb18ce02-89e7-4e45-b6bf-6c71c8b5ffe8}">
+          <x14:cfRule type="dataBar" id="{4638a353-201f-4f30-b760-3bab4f315afb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24704,7 +24705,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{904cf8e6-f644-4be8-b62c-6bc421b3bf03}">
+          <x14:cfRule type="dataBar" id="{badfdc39-a2cd-4972-9578-9f83d5ec36f4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24717,7 +24718,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec21f11a-afe1-4d6c-aac2-cdcf67fc6d02}">
+          <x14:cfRule type="dataBar" id="{c874ea18-6939-4fe6-af69-f2fac0f44c53}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24730,7 +24731,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2dae02d0-c2f2-4046-a497-b9cb14f37060}">
+          <x14:cfRule type="dataBar" id="{42b014e9-01ce-4835-9fdc-cba3990bcdf0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26456,7 +26457,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa99523b-e76c-456c-bd7e-f6bf2bea820e}</x14:id>
+          <x14:id>{aa3f6560-21eb-4bec-b6bf-5697438d3315}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26470,7 +26471,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6718fbf1-1f87-49f5-af7a-e3396e62aaf4}</x14:id>
+          <x14:id>{5508a77f-be2a-48f2-b9be-0e6bbed65b3f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26484,7 +26485,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{643c1a5e-ce2e-4677-8a5c-580b25e329a1}</x14:id>
+          <x14:id>{abc651fb-f841-4002-8141-d0aafe044223}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26498,7 +26499,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a2bb73b-5023-4039-8a00-e55ff4db7eb4}</x14:id>
+          <x14:id>{d45611b3-9398-47a5-8d66-7d7ffd04e28a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26512,7 +26513,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c44cdf66-e4f9-4634-acbc-89e31d062a8e}</x14:id>
+          <x14:id>{479cb120-c7a1-47d9-8054-9319d9afc2d1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26526,7 +26527,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2a0942f2-e06a-47f9-b53c-ae88b526adb3}</x14:id>
+          <x14:id>{120941f6-55a5-4ce2-bdc0-7315c227d67c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26540,7 +26541,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4c0aaec-eebf-46ce-9dba-765bccaaa73d}</x14:id>
+          <x14:id>{faa45d6d-6d93-4910-b3d6-2e11083f0ce2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26554,7 +26555,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b9f014e2-053c-4e4e-874c-02b5f83d3d2d}</x14:id>
+          <x14:id>{3a45acb7-e203-468f-8977-00729cbd63af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26568,7 +26569,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f57805e7-f846-4c12-8bb3-3790f1ce9b59}</x14:id>
+          <x14:id>{66c5a367-f219-4d73-8cf3-4d54c632e705}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26582,7 +26583,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f6ebb3ee-83b4-42b6-8a06-840ce59b0814}</x14:id>
+          <x14:id>{d4836457-0298-49b1-90a3-d9f221954a6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26596,7 +26597,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a8138153-7df2-4f57-8b52-72dd9039d758}</x14:id>
+          <x14:id>{c016f0db-e482-4ee1-aa34-c736ea3f0249}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26632,7 +26633,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{678360a4-2809-4c40-8343-58e66d1d4810}</x14:id>
+          <x14:id>{4fdd3c22-1eb5-4837-9182-96ad2305f63d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26651,7 +26652,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa99523b-e76c-456c-bd7e-f6bf2bea820e}">
+          <x14:cfRule type="dataBar" id="{aa3f6560-21eb-4bec-b6bf-5697438d3315}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26664,7 +26665,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6718fbf1-1f87-49f5-af7a-e3396e62aaf4}">
+          <x14:cfRule type="dataBar" id="{5508a77f-be2a-48f2-b9be-0e6bbed65b3f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26677,7 +26678,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{643c1a5e-ce2e-4677-8a5c-580b25e329a1}">
+          <x14:cfRule type="dataBar" id="{abc651fb-f841-4002-8141-d0aafe044223}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26690,7 +26691,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7a2bb73b-5023-4039-8a00-e55ff4db7eb4}">
+          <x14:cfRule type="dataBar" id="{d45611b3-9398-47a5-8d66-7d7ffd04e28a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26703,7 +26704,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c44cdf66-e4f9-4634-acbc-89e31d062a8e}">
+          <x14:cfRule type="dataBar" id="{479cb120-c7a1-47d9-8054-9319d9afc2d1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26716,7 +26717,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2a0942f2-e06a-47f9-b53c-ae88b526adb3}">
+          <x14:cfRule type="dataBar" id="{120941f6-55a5-4ce2-bdc0-7315c227d67c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26729,7 +26730,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c4c0aaec-eebf-46ce-9dba-765bccaaa73d}">
+          <x14:cfRule type="dataBar" id="{faa45d6d-6d93-4910-b3d6-2e11083f0ce2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26742,7 +26743,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b9f014e2-053c-4e4e-874c-02b5f83d3d2d}">
+          <x14:cfRule type="dataBar" id="{3a45acb7-e203-468f-8977-00729cbd63af}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26755,7 +26756,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f57805e7-f846-4c12-8bb3-3790f1ce9b59}">
+          <x14:cfRule type="dataBar" id="{66c5a367-f219-4d73-8cf3-4d54c632e705}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26768,7 +26769,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f6ebb3ee-83b4-42b6-8a06-840ce59b0814}">
+          <x14:cfRule type="dataBar" id="{d4836457-0298-49b1-90a3-d9f221954a6d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26781,7 +26782,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a8138153-7df2-4f57-8b52-72dd9039d758}">
+          <x14:cfRule type="dataBar" id="{c016f0db-e482-4ee1-aa34-c736ea3f0249}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26794,7 +26795,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{678360a4-2809-4c40-8343-58e66d1d4810}">
+          <x14:cfRule type="dataBar" id="{4fdd3c22-1eb5-4837-9182-96ad2305f63d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -37358,7 +37359,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c5d1ad8-68f3-4434-87e3-5eddface94d6}</x14:id>
+          <x14:id>{ec3abd82-a414-4476-9a74-8fd433f846a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37372,7 +37373,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad83cb38-f319-4c0d-87c8-2258e6938332}</x14:id>
+          <x14:id>{ad81e660-adb2-4c44-ba2c-cb32f9409e11}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37386,7 +37387,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{185753e8-8247-4775-a006-cd42020e4dd7}</x14:id>
+          <x14:id>{dc93f3a9-c583-4f29-9b0d-8667fe64ced6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37400,7 +37401,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0ec31ee-bc8a-4163-995b-51fcfa9f8778}</x14:id>
+          <x14:id>{64e19edc-281a-492c-9bfa-5757f6d7f4b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37414,7 +37415,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d4fe035-cc6f-4518-9be5-e680f27787db}</x14:id>
+          <x14:id>{6eb20218-6da8-449d-88a5-4c7cfee3a9d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37428,7 +37429,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0cb395b8-a082-432b-9367-16ae43cdd4cd}</x14:id>
+          <x14:id>{880c0b46-21ed-470c-afb5-5b57a55fa534}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37448,7 +37449,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{279fc306-3f8f-4f23-bf93-70fe7f296f4b}</x14:id>
+          <x14:id>{789db2cc-577d-46b2-9e87-1836ad337da8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37462,7 +37463,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8994d41d-2cca-42c8-b08f-b34a540185ce}</x14:id>
+          <x14:id>{82437995-34b7-43b9-87c1-de075b1b2394}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37476,7 +37477,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{131e2ecd-b6e8-476b-b4f1-17c6f3b19401}</x14:id>
+          <x14:id>{0d56f005-0198-4d6a-896f-dc64e377ca60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37490,7 +37491,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38fb1d6d-f8fc-4dc7-b739-e19ec71b41fa}</x14:id>
+          <x14:id>{eae55dd0-f6e8-480a-8346-b42e42b5c8a8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37504,7 +37505,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{650d4031-5e2c-4ee4-99ae-76f68ed1eb37}</x14:id>
+          <x14:id>{592992a1-831f-4749-977b-7b9b7456c46f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37518,7 +37519,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca5e0387-2f7a-4c75-89d8-612eab6b2034}</x14:id>
+          <x14:id>{0e07c3e9-066f-4ed7-aa44-dae1e91b4b47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37540,7 +37541,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae1b9f0c-36cf-42a9-b85a-d1b04b969df0}</x14:id>
+          <x14:id>{72c4bac1-3e03-46f5-8ae2-4eb5bfa9a360}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37570,7 +37571,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5bb72168-38cf-4dce-b191-e66c8bb4b785}</x14:id>
+          <x14:id>{0d83b2f4-558d-4203-b5ef-349d2d341b26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37600,7 +37601,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73a26aef-7573-4833-8201-ad23c9542779}</x14:id>
+          <x14:id>{b4934688-0cf8-4319-92ff-35372a11c2e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37630,7 +37631,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{884886ec-50e5-4da8-b430-37e8bdc9cd33}</x14:id>
+          <x14:id>{fd126515-fd4a-43f8-b379-92abd763a227}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37660,7 +37661,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7052b3a1-c659-43e4-96c9-b89800d15fc2}</x14:id>
+          <x14:id>{cbd28c9e-25b7-422c-bf8c-0e3f9f21b031}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37690,7 +37691,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{30dfc89d-1a76-4549-918f-f1394c193faa}</x14:id>
+          <x14:id>{57ee7dcb-df9c-462e-b650-0c321a1be40f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37712,7 +37713,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1936c832-5108-4be7-b2a5-651fa920cacd}</x14:id>
+          <x14:id>{1b2198fe-2011-4d5f-83eb-5132685df21e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37734,7 +37735,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bf863f1b-f2ea-4051-862a-f0361cc144e9}</x14:id>
+          <x14:id>{85bbce98-7e23-4a66-8a4d-f6b6ed0b9cb0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37756,7 +37757,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0f464481-e54c-43b3-81b3-3c90ac6017e8}</x14:id>
+          <x14:id>{d2a8b3d2-a6a0-416a-b85b-31083ae501d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37778,7 +37779,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5ed325c7-2e03-4f7e-b6d3-76ee1bd3fbb7}</x14:id>
+          <x14:id>{0364943d-d06f-4c37-be88-7826407e9695}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37800,7 +37801,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2515b826-6e0a-49c2-81d7-e1281ef64b1d}</x14:id>
+          <x14:id>{fe4eb5b9-8f9a-47a6-9f2b-b227c6f9b927}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37822,7 +37823,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eae00273-fece-47e5-82a0-3fa174f3bf69}</x14:id>
+          <x14:id>{57b11a37-fa9f-428a-abd8-4e99ba3f00e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37844,7 +37845,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7602e6e7-fdb1-49c7-861c-af5aeba6922c}</x14:id>
+          <x14:id>{d147febf-3e2b-433b-a7c6-0d3aeb3dc7b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37866,7 +37867,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{265b9507-cdbd-4caf-8a3a-84ecbd8380bb}</x14:id>
+          <x14:id>{61384d78-5d07-49fe-ad7c-a44ce1ab1163}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37888,7 +37889,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cdd6ebab-35a8-4277-a4b2-dd4631c7352a}</x14:id>
+          <x14:id>{d43cbea3-e695-4982-b6c4-7eabfd694c43}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37910,7 +37911,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d04061a-c38b-464a-96a9-172a76c739ea}</x14:id>
+          <x14:id>{712d799c-ce57-4f15-98a6-cbea8ce88d04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37932,7 +37933,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba0b1fea-17d7-4e97-99a0-8d8e67710f74}</x14:id>
+          <x14:id>{ba9210c7-4e29-47d2-a335-0718d03f238c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37954,7 +37955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{912ceddb-1d3c-49c6-809d-d9fcae8e3a5c}</x14:id>
+          <x14:id>{82d0d6e6-6736-44e8-a09d-47f777db27ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37976,7 +37977,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60685b8d-a148-4ce5-b46e-533821d785d1}</x14:id>
+          <x14:id>{02256ed3-46bd-4d20-9ab3-d19c36967293}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37998,7 +37999,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{58d55f2e-8d26-49c5-b9c6-0252ed45f587}</x14:id>
+          <x14:id>{dbe685ab-7d2b-4a12-abd6-80ecc8eaf52d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38017,7 +38018,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c5d1ad8-68f3-4434-87e3-5eddface94d6}">
+          <x14:cfRule type="dataBar" id="{ec3abd82-a414-4476-9a74-8fd433f846a7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38030,7 +38031,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ad83cb38-f319-4c0d-87c8-2258e6938332}">
+          <x14:cfRule type="dataBar" id="{ad81e660-adb2-4c44-ba2c-cb32f9409e11}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38043,7 +38044,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{185753e8-8247-4775-a006-cd42020e4dd7}">
+          <x14:cfRule type="dataBar" id="{dc93f3a9-c583-4f29-9b0d-8667fe64ced6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38056,7 +38057,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e0ec31ee-bc8a-4163-995b-51fcfa9f8778}">
+          <x14:cfRule type="dataBar" id="{64e19edc-281a-492c-9bfa-5757f6d7f4b3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38069,7 +38070,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2d4fe035-cc6f-4518-9be5-e680f27787db}">
+          <x14:cfRule type="dataBar" id="{6eb20218-6da8-449d-88a5-4c7cfee3a9d3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38082,7 +38083,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0cb395b8-a082-432b-9367-16ae43cdd4cd}">
+          <x14:cfRule type="dataBar" id="{880c0b46-21ed-470c-afb5-5b57a55fa534}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38095,7 +38096,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{279fc306-3f8f-4f23-bf93-70fe7f296f4b}">
+          <x14:cfRule type="dataBar" id="{789db2cc-577d-46b2-9e87-1836ad337da8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38108,7 +38109,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8994d41d-2cca-42c8-b08f-b34a540185ce}">
+          <x14:cfRule type="dataBar" id="{82437995-34b7-43b9-87c1-de075b1b2394}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38121,7 +38122,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{131e2ecd-b6e8-476b-b4f1-17c6f3b19401}">
+          <x14:cfRule type="dataBar" id="{0d56f005-0198-4d6a-896f-dc64e377ca60}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38134,7 +38135,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38fb1d6d-f8fc-4dc7-b739-e19ec71b41fa}">
+          <x14:cfRule type="dataBar" id="{eae55dd0-f6e8-480a-8346-b42e42b5c8a8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38147,7 +38148,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{650d4031-5e2c-4ee4-99ae-76f68ed1eb37}">
+          <x14:cfRule type="dataBar" id="{592992a1-831f-4749-977b-7b9b7456c46f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38160,7 +38161,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ca5e0387-2f7a-4c75-89d8-612eab6b2034}">
+          <x14:cfRule type="dataBar" id="{0e07c3e9-066f-4ed7-aa44-dae1e91b4b47}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38173,7 +38174,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ae1b9f0c-36cf-42a9-b85a-d1b04b969df0}">
+          <x14:cfRule type="dataBar" id="{72c4bac1-3e03-46f5-8ae2-4eb5bfa9a360}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38186,7 +38187,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5bb72168-38cf-4dce-b191-e66c8bb4b785}">
+          <x14:cfRule type="dataBar" id="{0d83b2f4-558d-4203-b5ef-349d2d341b26}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38199,7 +38200,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{73a26aef-7573-4833-8201-ad23c9542779}">
+          <x14:cfRule type="dataBar" id="{b4934688-0cf8-4319-92ff-35372a11c2e1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38212,7 +38213,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{884886ec-50e5-4da8-b430-37e8bdc9cd33}">
+          <x14:cfRule type="dataBar" id="{fd126515-fd4a-43f8-b379-92abd763a227}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38225,7 +38226,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7052b3a1-c659-43e4-96c9-b89800d15fc2}">
+          <x14:cfRule type="dataBar" id="{cbd28c9e-25b7-422c-bf8c-0e3f9f21b031}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38238,7 +38239,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{30dfc89d-1a76-4549-918f-f1394c193faa}">
+          <x14:cfRule type="dataBar" id="{57ee7dcb-df9c-462e-b650-0c321a1be40f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38251,7 +38252,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1936c832-5108-4be7-b2a5-651fa920cacd}">
+          <x14:cfRule type="dataBar" id="{1b2198fe-2011-4d5f-83eb-5132685df21e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38264,7 +38265,7 @@
           <xm:sqref>C68:O68 D69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bf863f1b-f2ea-4051-862a-f0361cc144e9}">
+          <x14:cfRule type="dataBar" id="{85bbce98-7e23-4a66-8a4d-f6b6ed0b9cb0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38277,7 +38278,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0f464481-e54c-43b3-81b3-3c90ac6017e8}">
+          <x14:cfRule type="dataBar" id="{d2a8b3d2-a6a0-416a-b85b-31083ae501d5}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38290,7 +38291,7 @@
           <xm:sqref>C76:O76 D77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5ed325c7-2e03-4f7e-b6d3-76ee1bd3fbb7}">
+          <x14:cfRule type="dataBar" id="{0364943d-d06f-4c37-be88-7826407e9695}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38303,7 +38304,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2515b826-6e0a-49c2-81d7-e1281ef64b1d}">
+          <x14:cfRule type="dataBar" id="{fe4eb5b9-8f9a-47a6-9f2b-b227c6f9b927}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38316,7 +38317,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eae00273-fece-47e5-82a0-3fa174f3bf69}">
+          <x14:cfRule type="dataBar" id="{57b11a37-fa9f-428a-abd8-4e99ba3f00e7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38329,7 +38330,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7602e6e7-fdb1-49c7-861c-af5aeba6922c}">
+          <x14:cfRule type="dataBar" id="{d147febf-3e2b-433b-a7c6-0d3aeb3dc7b6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38342,7 +38343,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{265b9507-cdbd-4caf-8a3a-84ecbd8380bb}">
+          <x14:cfRule type="dataBar" id="{61384d78-5d07-49fe-ad7c-a44ce1ab1163}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38355,7 +38356,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cdd6ebab-35a8-4277-a4b2-dd4631c7352a}">
+          <x14:cfRule type="dataBar" id="{d43cbea3-e695-4982-b6c4-7eabfd694c43}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38368,7 +38369,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4d04061a-c38b-464a-96a9-172a76c739ea}">
+          <x14:cfRule type="dataBar" id="{712d799c-ce57-4f15-98a6-cbea8ce88d04}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38381,7 +38382,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ba0b1fea-17d7-4e97-99a0-8d8e67710f74}">
+          <x14:cfRule type="dataBar" id="{ba9210c7-4e29-47d2-a335-0718d03f238c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38394,7 +38395,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{912ceddb-1d3c-49c6-809d-d9fcae8e3a5c}">
+          <x14:cfRule type="dataBar" id="{82d0d6e6-6736-44e8-a09d-47f777db27ad}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38407,7 +38408,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{60685b8d-a148-4ce5-b46e-533821d785d1}">
+          <x14:cfRule type="dataBar" id="{02256ed3-46bd-4d20-9ab3-d19c36967293}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38420,7 +38421,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{58d55f2e-8d26-49c5-b9c6-0252ed45f587}">
+          <x14:cfRule type="dataBar" id="{dbe685ab-7d2b-4a12-abd6-80ecc8eaf52d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -40548,7 +40549,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>0.634428715081241</v>
+        <v>0.51023455722886</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -40574,56 +40575,56 @@
         <v>24</v>
       </c>
       <c r="C6" s="9">
-        <f>[3]总目标!B44</f>
-        <v>267032.554098361</v>
+        <f>[3]总目标!B59</f>
+        <v>372843</v>
       </c>
       <c r="D6" s="9">
-        <f>[3]总目标!C44</f>
-        <v>454472.298360656</v>
+        <f>[3]总目标!C59</f>
+        <v>566214.491803279</v>
       </c>
       <c r="E6" s="9">
-        <f>[3]总目标!D44</f>
-        <v>356490.491803279</v>
+        <f>[3]总目标!D59</f>
+        <v>425981.18852459</v>
       </c>
       <c r="F6" s="9">
-        <f>[3]总目标!E44</f>
-        <v>373135.56557377</v>
+        <f>[3]总目标!E59</f>
+        <v>428093.165983607</v>
       </c>
       <c r="G6" s="9">
-        <f>[3]总目标!F44</f>
-        <v>335343.491803279</v>
+        <f>[3]总目标!F59</f>
+        <v>438328.647540984</v>
       </c>
       <c r="H6" s="9">
-        <f>[3]总目标!G44</f>
-        <v>291232.549180328</v>
+        <f>[3]总目标!G59</f>
+        <v>376625.606557377</v>
       </c>
       <c r="I6" s="9">
-        <f>[3]总目标!H44</f>
-        <v>359127.885245902</v>
+        <f>[3]总目标!H59</f>
+        <v>516638.599385246</v>
       </c>
       <c r="J6" s="9">
-        <f>[3]总目标!I44</f>
-        <v>345231.147540984</v>
+        <f>[3]总目标!I59</f>
+        <v>499972.838114754</v>
       </c>
       <c r="K6" s="9">
-        <f>[3]总目标!J44</f>
-        <v>327791.967213115</v>
+        <f>[3]总目标!J59</f>
+        <v>490032.5</v>
       </c>
       <c r="L6" s="9">
-        <f>[3]总目标!K44</f>
-        <v>319748.852459016</v>
+        <f>[3]总目标!K59</f>
+        <v>474225</v>
       </c>
       <c r="M6" s="9">
-        <f>[3]总目标!L44</f>
-        <v>330407.147540984</v>
+        <f>[3]总目标!L59</f>
+        <v>490032.5</v>
       </c>
       <c r="N6" s="9">
-        <f>[3]总目标!M44</f>
-        <v>214260.819672131</v>
+        <f>[3]总目标!M59</f>
+        <v>318392.868852459</v>
       </c>
       <c r="O6" s="28">
         <f t="shared" ref="O6:O10" si="0">SUM(C6:N6)</f>
-        <v>3974274.7704918</v>
+        <v>5397380.4067623</v>
       </c>
     </row>
     <row r="7" ht="15.6" spans="1:15">
@@ -40707,11 +40708,11 @@
       </c>
       <c r="G8" s="20">
         <f t="shared" si="1"/>
-        <v>1.09753416719328</v>
+        <v>0.839668915241473</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="1"/>
-        <v>0.914028362383269</v>
+        <v>0.70678893140912</v>
       </c>
       <c r="I8" s="20">
         <f t="shared" si="1"/>
@@ -40739,7 +40740,7 @@
       </c>
       <c r="O8" s="20">
         <f t="shared" si="1"/>
-        <v>0.159587795667564</v>
+        <v>0.117509921888285</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -45989,7 +45990,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fd07eebf-ad57-463d-99c1-fd3ec75ea292}</x14:id>
+          <x14:id>{cde86fa1-159c-4f03-8e1a-6d876c3c85f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46003,7 +46004,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{343f6457-bcab-4383-9b99-dd3497f6f19f}</x14:id>
+          <x14:id>{9dfc139c-9a0e-4699-9712-f5c541e7a679}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46017,7 +46018,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9fa8764b-6382-41d8-a03e-47733984e783}</x14:id>
+          <x14:id>{40988baa-ef10-4184-8dc0-a79b419fd26c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46031,7 +46032,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e4b3483-6a54-4439-aa00-6c5f95c3fdbd}</x14:id>
+          <x14:id>{589abc33-40db-47a9-925e-6b290718afbb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46045,7 +46046,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{221221cf-574c-4b8b-aa5e-135f4187c80f}</x14:id>
+          <x14:id>{00e2b72e-ba39-462b-9cad-45299ead12da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46059,7 +46060,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{130ba751-1c36-4ba7-9e5a-3a1da5a2e1ae}</x14:id>
+          <x14:id>{325d8e3e-5d02-4469-8646-84309071d266}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46073,7 +46074,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e5d675c-9da6-4078-a1ba-a1f4e2c3b183}</x14:id>
+          <x14:id>{b048b597-4661-45f6-b155-aa34f7092ccf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46087,7 +46088,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eaf9691d-e9c3-4d1f-a6f1-461b59983a0a}</x14:id>
+          <x14:id>{9e071a33-8785-49fa-9546-18fdd230ec1d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46101,7 +46102,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2dcde596-dab4-4f85-910b-c8f6cfbfe036}</x14:id>
+          <x14:id>{85051f7f-ffe2-4e0d-809b-d9a28e04f24b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46115,7 +46116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9988af99-e592-42c7-8174-6070554d345b}</x14:id>
+          <x14:id>{138d7ac8-eaf5-4788-bd0c-3ef3ac1277b1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46129,7 +46130,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e4caeba-769d-4d44-8f63-1db346cfc980}</x14:id>
+          <x14:id>{5108c85e-836c-4c7e-9698-72934ea23f58}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46165,7 +46166,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ae04b52-5fb8-4270-9dcd-b6e0211ab32a}</x14:id>
+          <x14:id>{05b5708c-e55f-448d-9fe0-0afe6eeae5c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -46184,7 +46185,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fd07eebf-ad57-463d-99c1-fd3ec75ea292}">
+          <x14:cfRule type="dataBar" id="{cde86fa1-159c-4f03-8e1a-6d876c3c85f6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46197,7 +46198,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{343f6457-bcab-4383-9b99-dd3497f6f19f}">
+          <x14:cfRule type="dataBar" id="{9dfc139c-9a0e-4699-9712-f5c541e7a679}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46210,7 +46211,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9fa8764b-6382-41d8-a03e-47733984e783}">
+          <x14:cfRule type="dataBar" id="{40988baa-ef10-4184-8dc0-a79b419fd26c}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46223,7 +46224,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e4b3483-6a54-4439-aa00-6c5f95c3fdbd}">
+          <x14:cfRule type="dataBar" id="{589abc33-40db-47a9-925e-6b290718afbb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46236,7 +46237,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{221221cf-574c-4b8b-aa5e-135f4187c80f}">
+          <x14:cfRule type="dataBar" id="{00e2b72e-ba39-462b-9cad-45299ead12da}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46249,7 +46250,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{130ba751-1c36-4ba7-9e5a-3a1da5a2e1ae}">
+          <x14:cfRule type="dataBar" id="{325d8e3e-5d02-4469-8646-84309071d266}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46262,7 +46263,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e5d675c-9da6-4078-a1ba-a1f4e2c3b183}">
+          <x14:cfRule type="dataBar" id="{b048b597-4661-45f6-b155-aa34f7092ccf}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46275,7 +46276,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eaf9691d-e9c3-4d1f-a6f1-461b59983a0a}">
+          <x14:cfRule type="dataBar" id="{9e071a33-8785-49fa-9546-18fdd230ec1d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46288,7 +46289,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2dcde596-dab4-4f85-910b-c8f6cfbfe036}">
+          <x14:cfRule type="dataBar" id="{85051f7f-ffe2-4e0d-809b-d9a28e04f24b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46301,7 +46302,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9988af99-e592-42c7-8174-6070554d345b}">
+          <x14:cfRule type="dataBar" id="{138d7ac8-eaf5-4788-bd0c-3ef3ac1277b1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46314,7 +46315,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9e4caeba-769d-4d44-8f63-1db346cfc980}">
+          <x14:cfRule type="dataBar" id="{5108c85e-836c-4c7e-9698-72934ea23f58}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -46327,7 +46328,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1ae04b52-5fb8-4270-9dcd-b6e0211ab32a}">
+          <x14:cfRule type="dataBar" id="{05b5708c-e55f-448d-9fe0-0afe6eeae5c4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/2026WB年规进度.xlsx
+++ b/2026WB年规进度.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13380" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="毛立新" sheetId="1" r:id="rId1"/>
@@ -6531,6 +6531,8 @@
       <sheetName val="周度汇总分析报告"/>
       <sheetName val="2026年度男装数据汇总分析--俄罗斯"/>
       <sheetName val="2026年月度数据汇总--俄罗斯"/>
+      <sheetName val="2026年月度数据汇总-何欢洁"/>
+      <sheetName val="2026年月度数据汇总-郑志远"/>
       <sheetName val="2026年数据登记--俄罗斯"/>
       <sheetName val="2026目标拆解--俄罗斯"/>
       <sheetName val="2026目标拆解--俄罗斯 --实时调整"/>
@@ -6697,7 +6699,7 @@
             <v>593421.46</v>
           </cell>
           <cell r="H7">
-            <v>325038.63</v>
+            <v>637416.38</v>
           </cell>
           <cell r="I7">
             <v>0</v>
@@ -6718,7 +6720,7 @@
             <v>0</v>
           </cell>
           <cell r="O7">
-            <v>3437257.96</v>
+            <v>3749635.71</v>
           </cell>
         </row>
         <row r="8">
@@ -6741,7 +6743,7 @@
             <v>1.09246608580648</v>
           </cell>
           <cell r="H8">
-            <v>0.535748473942456</v>
+            <v>1.05062851406593</v>
           </cell>
           <cell r="I8">
             <v>0</v>
@@ -6762,7 +6764,7 @@
             <v>0</v>
           </cell>
           <cell r="O8">
-            <v>0.392593009981998</v>
+            <v>0.428271833786046</v>
           </cell>
         </row>
         <row r="10">
@@ -6829,7 +6831,7 @@
             <v>26753</v>
           </cell>
           <cell r="H11">
-            <v>15887</v>
+            <v>32761</v>
           </cell>
           <cell r="I11">
             <v>0</v>
@@ -6850,7 +6852,7 @@
             <v>0</v>
           </cell>
           <cell r="O11">
-            <v>171643</v>
+            <v>188517</v>
           </cell>
         </row>
         <row r="12">
@@ -6873,7 +6875,7 @@
             <v>0.743138888888889</v>
           </cell>
           <cell r="H12">
-            <v>0.395130201208745</v>
+            <v>0.814808366702315</v>
           </cell>
           <cell r="I12">
             <v>0</v>
@@ -6894,7 +6896,7 @@
             <v>0</v>
           </cell>
           <cell r="O12">
-            <v>0.295491950033742</v>
+            <v>0.324541379167872</v>
           </cell>
         </row>
         <row r="14">
@@ -6961,7 +6963,7 @@
             <v>9282</v>
           </cell>
           <cell r="H15">
-            <v>5500</v>
+            <v>11458</v>
           </cell>
           <cell r="I15">
             <v>0</v>
@@ -6982,7 +6984,7 @@
             <v>0</v>
           </cell>
           <cell r="O15">
-            <v>60846</v>
+            <v>66804</v>
           </cell>
         </row>
         <row r="16">
@@ -7005,7 +7007,7 @@
             <v>0.831720430107527</v>
           </cell>
           <cell r="H16">
-            <v>0.441264841541795</v>
+            <v>0.919275009888344</v>
           </cell>
           <cell r="I16">
             <v>0</v>
@@ -7026,7 +7028,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>0.337901326548428</v>
+            <v>0.370988400531526</v>
           </cell>
         </row>
         <row r="18">
@@ -7093,7 +7095,7 @@
             <v>11545368.1632</v>
           </cell>
           <cell r="H19">
-            <v>6659288.4732</v>
+            <v>15086133.2796</v>
           </cell>
           <cell r="I19">
             <v>0</v>
@@ -7114,7 +7116,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>67577309.1834</v>
+            <v>76004153.9898</v>
           </cell>
         </row>
         <row r="20">
@@ -7137,7 +7139,7 @@
             <v>0.922448718696069</v>
           </cell>
           <cell r="H20">
-            <v>0.476369032961964</v>
+            <v>1.07917936735439</v>
           </cell>
           <cell r="I20">
             <v>0</v>
@@ -7158,7 +7160,7 @@
             <v>0</v>
           </cell>
           <cell r="O20">
-            <v>0.335043434341862</v>
+            <v>0.376823124280976</v>
           </cell>
         </row>
         <row r="22">
@@ -7225,7 +7227,7 @@
             <v>3503371.5464</v>
           </cell>
           <cell r="H23">
-            <v>1930982.2827</v>
+            <v>4076553.6474</v>
           </cell>
           <cell r="I23">
             <v>0</v>
@@ -7246,7 +7248,7 @@
             <v>0</v>
           </cell>
           <cell r="O23">
-            <v>21876883.9391</v>
+            <v>24022455.3038</v>
           </cell>
         </row>
         <row r="24">
@@ -7269,7 +7271,7 @@
             <v>0.874723240851709</v>
           </cell>
           <cell r="H24">
-            <v>0.431662184320827</v>
+            <v>0.911294768317202</v>
           </cell>
           <cell r="I24">
             <v>0</v>
@@ -7290,7 +7292,7 @@
             <v>0</v>
           </cell>
           <cell r="O24">
-            <v>0.33895004922076</v>
+            <v>0.372192512895943</v>
           </cell>
         </row>
         <row r="26">
@@ -7313,7 +7315,7 @@
             <v>0.30344390034843</v>
           </cell>
           <cell r="H26">
-            <v>0.289968258691773</v>
+            <v>0.270218588941704</v>
           </cell>
           <cell r="I26" t="e">
             <v>#DIV/0!</v>
@@ -7334,7 +7336,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O26">
-            <v>0.323731208055765</v>
+            <v>0.316067662657279</v>
           </cell>
         </row>
         <row r="27">
@@ -7357,7 +7359,7 @@
             <v>0.653048256270325</v>
           </cell>
           <cell r="H27">
-            <v>0.653804997796941</v>
+            <v>0.65025487622478</v>
           </cell>
           <cell r="I27" t="e">
             <v>#DIV/0!</v>
@@ -7378,7 +7380,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O27">
-            <v>0.645508409897287</v>
+            <v>0.645634080746033</v>
           </cell>
         </row>
         <row r="28">
@@ -7401,7 +7403,7 @@
             <v>0.16938581938584</v>
           </cell>
           <cell r="H28">
-            <v>0.168328126525073</v>
+            <v>0.156361582634032</v>
           </cell>
           <cell r="I28" t="e">
             <v>#DIV/0!</v>
@@ -7422,7 +7424,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O28">
-            <v>0.157118260972107</v>
+            <v>0.156088778710595</v>
           </cell>
         </row>
         <row r="30">
@@ -7448,7 +7450,7 @@
             <v>213687.24</v>
           </cell>
           <cell r="H30">
-            <v>102754.41</v>
+            <v>196174.75</v>
           </cell>
           <cell r="I30">
             <v>0</v>
@@ -7469,7 +7471,7 @@
             <v>0</v>
           </cell>
           <cell r="O30">
-            <v>1874915.07</v>
+            <v>1968335.41</v>
           </cell>
         </row>
         <row r="31">
@@ -7492,7 +7494,7 @@
             <v>10453</v>
           </cell>
           <cell r="H31">
-            <v>5785</v>
+            <v>11621</v>
           </cell>
           <cell r="I31">
             <v>0</v>
@@ -7513,7 +7515,7 @@
             <v>0</v>
           </cell>
           <cell r="O31">
-            <v>82089</v>
+            <v>87925</v>
           </cell>
         </row>
         <row r="32">
@@ -7536,7 +7538,7 @@
             <v>3602</v>
           </cell>
           <cell r="H32">
-            <v>1927</v>
+            <v>3917</v>
           </cell>
           <cell r="I32">
             <v>0</v>
@@ -7557,7 +7559,7 @@
             <v>0</v>
           </cell>
           <cell r="O32">
-            <v>30081</v>
+            <v>32071</v>
           </cell>
         </row>
         <row r="33">
@@ -7580,7 +7582,7 @@
             <v>4439731.0488</v>
           </cell>
           <cell r="H33">
-            <v>2511111.222</v>
+            <v>5199070.2324</v>
           </cell>
           <cell r="I33">
             <v>0</v>
@@ -7601,7 +7603,7 @@
             <v>0</v>
           </cell>
           <cell r="O33">
-            <v>33826837.7889</v>
+            <v>36514796.7993</v>
           </cell>
         </row>
         <row r="34">
@@ -7624,7 +7626,7 @@
             <v>1407371.462</v>
           </cell>
           <cell r="H34">
-            <v>699411.4057</v>
+            <v>1456186.0782</v>
           </cell>
           <cell r="I34">
             <v>0</v>
@@ -7645,7 +7647,7 @@
             <v>0</v>
           </cell>
           <cell r="O34">
-            <v>11088070.4977</v>
+            <v>11844845.1702</v>
           </cell>
         </row>
         <row r="35">
@@ -7668,7 +7670,7 @@
             <v>0.316994756333358</v>
           </cell>
           <cell r="H35">
-            <v>0.278526653687186</v>
+            <v>0.280085864031076</v>
           </cell>
           <cell r="I35" t="e">
             <v>#DIV/0!</v>
@@ -7689,7 +7691,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O35">
-            <v>0.327789152710528</v>
+            <v>0.324384803106095</v>
           </cell>
         </row>
         <row r="36">
@@ -7712,7 +7714,7 @@
             <v>0.655409930163589</v>
           </cell>
           <cell r="H36">
-            <v>0.666897147796024</v>
+            <v>0.662937785044316</v>
           </cell>
           <cell r="I36" t="e">
             <v>#DIV/0!</v>
@@ -7733,7 +7735,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O36">
-            <v>0.633556262105763</v>
+            <v>0.635245948251351</v>
           </cell>
         </row>
         <row r="37">
@@ -7756,7 +7758,7 @@
             <v>0.15183428524004</v>
           </cell>
           <cell r="H37">
-            <v>0.1469155480774</v>
+            <v>0.134718188105804</v>
           </cell>
           <cell r="I37" t="e">
             <v>#DIV/0!</v>
@@ -7777,7 +7779,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O37">
-            <v>0.169092996873434</v>
+            <v>0.166176541923238</v>
           </cell>
         </row>
         <row r="38">
@@ -7803,7 +7805,7 @@
             <v>95805.82</v>
           </cell>
           <cell r="H38">
-            <v>77964.2</v>
+            <v>169438.85</v>
           </cell>
           <cell r="I38">
             <v>0</v>
@@ -7824,7 +7826,7 @@
             <v>0</v>
           </cell>
           <cell r="O38">
-            <v>651335.88</v>
+            <v>742810.53</v>
           </cell>
         </row>
         <row r="39">
@@ -7847,7 +7849,7 @@
             <v>6417</v>
           </cell>
           <cell r="H39">
-            <v>4008</v>
+            <v>9124</v>
           </cell>
           <cell r="I39">
             <v>0</v>
@@ -7868,7 +7870,7 @@
             <v>0</v>
           </cell>
           <cell r="O39">
-            <v>38083</v>
+            <v>43199</v>
           </cell>
         </row>
         <row r="40">
@@ -7891,7 +7893,7 @@
             <v>1916</v>
           </cell>
           <cell r="H40">
-            <v>1324</v>
+            <v>2945</v>
           </cell>
           <cell r="I40">
             <v>0</v>
@@ -7912,7 +7914,7 @@
             <v>0</v>
           </cell>
           <cell r="O40">
-            <v>12514</v>
+            <v>14135</v>
           </cell>
         </row>
         <row r="41">
@@ -7935,7 +7937,7 @@
             <v>2954093.3256</v>
           </cell>
           <cell r="H41">
-            <v>1634730.252</v>
+            <v>3813426.3168</v>
           </cell>
           <cell r="I41">
             <v>0</v>
@@ -7956,7 +7958,7 @@
             <v>0</v>
           </cell>
           <cell r="O41">
-            <v>14329032.7986</v>
+            <v>16507728.8634</v>
           </cell>
         </row>
         <row r="42">
@@ -7979,7 +7981,7 @@
             <v>702420.3795</v>
           </cell>
           <cell r="H42">
-            <v>458423.5943</v>
+            <v>1032316.5394</v>
           </cell>
           <cell r="I42">
             <v>0</v>
@@ -8000,7 +8002,7 @@
             <v>0</v>
           </cell>
           <cell r="O42">
-            <v>4184008.9538</v>
+            <v>4757901.8989</v>
           </cell>
         </row>
         <row r="43">
@@ -8023,7 +8025,7 @@
             <v>0.237778669147947</v>
           </cell>
           <cell r="H43">
-            <v>0.280427669176089</v>
+            <v>0.270705778384164</v>
           </cell>
           <cell r="I43" t="e">
             <v>#DIV/0!</v>
@@ -8044,7 +8046,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O43">
-            <v>0.291995210884631</v>
+            <v>0.288222682736748</v>
           </cell>
         </row>
         <row r="44">
@@ -8067,7 +8069,7 @@
             <v>0.701418108150226</v>
           </cell>
           <cell r="H44">
-            <v>0.669660678642715</v>
+            <v>0.677224901359053</v>
           </cell>
           <cell r="I44" t="e">
             <v>#DIV/0!</v>
@@ -8088,7 +8090,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O44">
-            <v>0.671401937872542</v>
+            <v>0.672793351697956</v>
           </cell>
         </row>
         <row r="45">
@@ -8111,7 +8113,7 @@
             <v>0.136393850173022</v>
           </cell>
           <cell r="H45">
-            <v>0.170070216649841</v>
+            <v>0.164134588116239</v>
           </cell>
           <cell r="I45" t="e">
             <v>#DIV/0!</v>
@@ -8132,7 +8134,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O45">
-            <v>0.155672678331255</v>
+            <v>0.156121447180686</v>
           </cell>
         </row>
         <row r="46">
@@ -8158,7 +8160,7 @@
             <v>267227.4</v>
           </cell>
           <cell r="H46">
-            <v>131378.65</v>
+            <v>246129.6</v>
           </cell>
           <cell r="I46">
             <v>0</v>
@@ -8179,7 +8181,7 @@
             <v>0</v>
           </cell>
           <cell r="O46">
-            <v>764491.77</v>
+            <v>879242.72</v>
           </cell>
         </row>
         <row r="47">
@@ -8202,7 +8204,7 @@
             <v>8516</v>
           </cell>
           <cell r="H47">
-            <v>5471</v>
+            <v>10835</v>
           </cell>
           <cell r="I47">
             <v>0</v>
@@ -8223,7 +8225,7 @@
             <v>0</v>
           </cell>
           <cell r="O47">
-            <v>34272</v>
+            <v>39636</v>
           </cell>
         </row>
         <row r="48">
@@ -8246,7 +8248,7 @@
             <v>3226</v>
           </cell>
           <cell r="H48">
-            <v>1994</v>
+            <v>4088</v>
           </cell>
           <cell r="I48">
             <v>0</v>
@@ -8267,7 +8269,7 @@
             <v>0</v>
           </cell>
           <cell r="O48">
-            <v>11970</v>
+            <v>14064</v>
           </cell>
         </row>
         <row r="49">
@@ -8290,7 +8292,7 @@
             <v>3625780.1448</v>
           </cell>
           <cell r="H49">
-            <v>2274149.9952</v>
+            <v>4595999.0844</v>
           </cell>
           <cell r="I49">
             <v>0</v>
@@ -8311,7 +8313,7 @@
             <v>0</v>
           </cell>
           <cell r="O49">
-            <v>13376634.4806</v>
+            <v>15698483.5698</v>
           </cell>
         </row>
         <row r="50">
@@ -8334,7 +8336,7 @@
             <v>1213786.7552</v>
           </cell>
           <cell r="H50">
-            <v>692555.2367</v>
+            <v>1427835.2688</v>
           </cell>
           <cell r="I50">
             <v>0</v>
@@ -8355,7 +8357,7 @@
             <v>0</v>
           </cell>
           <cell r="O50">
-            <v>4218986.3419</v>
+            <v>4954266.374</v>
           </cell>
         </row>
         <row r="51">
@@ -8378,7 +8380,7 @@
             <v>0.334765679860865</v>
           </cell>
           <cell r="H51">
-            <v>0.304533666715811</v>
+            <v>0.310669180428351</v>
           </cell>
           <cell r="I51" t="e">
             <v>#DIV/0!</v>
@@ -8399,7 +8401,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O51">
-            <v>0.315399688017098</v>
+            <v>0.315588849838387</v>
           </cell>
         </row>
         <row r="52">
@@ -8422,7 +8424,7 @@
             <v>0.621183654297792</v>
           </cell>
           <cell r="H52">
-            <v>0.635532809358435</v>
+            <v>0.622704199353945</v>
           </cell>
           <cell r="I52" t="e">
             <v>#DIV/0!</v>
@@ -8443,7 +8445,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O52">
-            <v>0.650735294117647</v>
+            <v>0.645171056615198</v>
           </cell>
         </row>
         <row r="53">
@@ -8466,7 +8468,7 @@
             <v>0.22016008895728</v>
           </cell>
           <cell r="H53">
-            <v>0.189701330721307</v>
+            <v>0.172379549222688</v>
           </cell>
           <cell r="I53" t="e">
             <v>#DIV/0!</v>
@@ -8487,7 +8489,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O53">
-            <v>0.181202712700823</v>
+            <v>0.177471830060303</v>
           </cell>
         </row>
         <row r="54">
@@ -8513,7 +8515,7 @@
             <v>16701</v>
           </cell>
           <cell r="H54">
-            <v>12941.37</v>
+            <v>25673.18</v>
           </cell>
           <cell r="I54">
             <v>0</v>
@@ -8534,7 +8536,7 @@
             <v>0</v>
           </cell>
           <cell r="O54">
-            <v>146515.24</v>
+            <v>159247.05</v>
           </cell>
         </row>
         <row r="55">
@@ -8557,7 +8559,7 @@
             <v>1367</v>
           </cell>
           <cell r="H55">
-            <v>623</v>
+            <v>1181</v>
           </cell>
           <cell r="I55">
             <v>0</v>
@@ -8578,7 +8580,7 @@
             <v>0</v>
           </cell>
           <cell r="O55">
-            <v>17199</v>
+            <v>17757</v>
           </cell>
         </row>
         <row r="56">
@@ -8601,7 +8603,7 @@
             <v>538</v>
           </cell>
           <cell r="H56">
-            <v>255</v>
+            <v>508</v>
           </cell>
           <cell r="I56">
             <v>0</v>
@@ -8622,7 +8624,7 @@
             <v>0</v>
           </cell>
           <cell r="O56">
-            <v>6281</v>
+            <v>6534</v>
           </cell>
         </row>
         <row r="57">
@@ -8645,7 +8647,7 @@
             <v>525763.644</v>
           </cell>
           <cell r="H57">
-            <v>239297.004</v>
+            <v>1477637.646</v>
           </cell>
           <cell r="I57">
             <v>0</v>
@@ -8666,7 +8668,7 @@
             <v>0</v>
           </cell>
           <cell r="O57">
-            <v>6044804.1153</v>
+            <v>7283144.7573</v>
           </cell>
         </row>
         <row r="58">
@@ -8689,7 +8691,7 @@
             <v>179792.9497</v>
           </cell>
           <cell r="H58">
-            <v>80592.046</v>
+            <v>160215.761</v>
           </cell>
           <cell r="I58">
             <v>0</v>
@@ -8710,7 +8712,7 @@
             <v>0</v>
           </cell>
           <cell r="O58">
-            <v>2385818.1457</v>
+            <v>2465441.8607</v>
           </cell>
         </row>
         <row r="59">
@@ -8733,7 +8735,7 @@
             <v>0.341965352210622</v>
           </cell>
           <cell r="H59">
-            <v>0.336786690400854</v>
+            <v>0.108426962072676</v>
           </cell>
           <cell r="I59" t="e">
             <v>#DIV/0!</v>
@@ -8754,7 +8756,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O59">
-            <v>0.394689075144926</v>
+            <v>0.338513367900432</v>
           </cell>
         </row>
         <row r="60">
@@ -8777,7 +8779,7 @@
             <v>0.606437454279444</v>
           </cell>
           <cell r="H60">
-            <v>0.590690208667737</v>
+            <v>0.569856054191363</v>
           </cell>
           <cell r="I60" t="e">
             <v>#DIV/0!</v>
@@ -8798,7 +8800,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O60">
-            <v>0.634804349090063</v>
+            <v>0.632032437911809</v>
           </cell>
         </row>
         <row r="61">
@@ -8821,7 +8823,7 @@
             <v>0.0928901830014306</v>
           </cell>
           <cell r="H61">
-            <v>0.160578749917827</v>
+            <v>0.160241288620787</v>
           </cell>
           <cell r="I61" t="e">
             <v>#DIV/0!</v>
@@ -8842,7 +8844,7 @@
             <v>#DIV/0!</v>
           </cell>
           <cell r="O61">
-            <v>0.0614109001828437</v>
+            <v>0.0645916874124891</v>
           </cell>
         </row>
         <row r="62">
@@ -11704,7 +11706,7 @@
             <v>213687.24</v>
           </cell>
           <cell r="H3">
-            <v>102754.41</v>
+            <v>196174.75</v>
           </cell>
           <cell r="I3">
             <v>0</v>
@@ -11742,7 +11744,7 @@
             <v>10453</v>
           </cell>
           <cell r="H4">
-            <v>5785</v>
+            <v>11621</v>
           </cell>
           <cell r="I4">
             <v>0</v>
@@ -11780,7 +11782,7 @@
             <v>3602</v>
           </cell>
           <cell r="H5">
-            <v>1927</v>
+            <v>3917</v>
           </cell>
           <cell r="I5">
             <v>0</v>
@@ -11818,7 +11820,7 @@
             <v>4439731.0488</v>
           </cell>
           <cell r="H6">
-            <v>2511111.222</v>
+            <v>5199070.2324</v>
           </cell>
           <cell r="I6">
             <v>0</v>
@@ -11856,7 +11858,7 @@
             <v>95805.82</v>
           </cell>
           <cell r="H8">
-            <v>77964.2</v>
+            <v>169438.85</v>
           </cell>
           <cell r="I8">
             <v>0</v>
@@ -11894,7 +11896,7 @@
             <v>6417</v>
           </cell>
           <cell r="H9">
-            <v>4008</v>
+            <v>9124</v>
           </cell>
           <cell r="I9">
             <v>0</v>
@@ -11932,7 +11934,7 @@
             <v>1916</v>
           </cell>
           <cell r="H10">
-            <v>1324</v>
+            <v>2945</v>
           </cell>
           <cell r="I10">
             <v>0</v>
@@ -11970,7 +11972,7 @@
             <v>2954093.3256</v>
           </cell>
           <cell r="H11">
-            <v>1634730.252</v>
+            <v>3813426.3168</v>
           </cell>
           <cell r="I11">
             <v>0</v>
@@ -12008,7 +12010,7 @@
             <v>267227.4</v>
           </cell>
           <cell r="H13">
-            <v>131378.65</v>
+            <v>246129.6</v>
           </cell>
           <cell r="I13">
             <v>0</v>
@@ -12046,7 +12048,7 @@
             <v>8516</v>
           </cell>
           <cell r="H14">
-            <v>5471</v>
+            <v>10835</v>
           </cell>
           <cell r="I14">
             <v>0</v>
@@ -12084,7 +12086,7 @@
             <v>3226</v>
           </cell>
           <cell r="H15">
-            <v>1994</v>
+            <v>4088</v>
           </cell>
           <cell r="I15">
             <v>0</v>
@@ -12122,7 +12124,7 @@
             <v>3625780.1448</v>
           </cell>
           <cell r="H16">
-            <v>2274149.9952</v>
+            <v>4595999.0844</v>
           </cell>
           <cell r="I16">
             <v>0</v>
@@ -12160,7 +12162,7 @@
             <v>16701</v>
           </cell>
           <cell r="H18">
-            <v>12941.37</v>
+            <v>25673.18</v>
           </cell>
           <cell r="I18">
             <v>0</v>
@@ -12198,7 +12200,7 @@
             <v>1367</v>
           </cell>
           <cell r="H19">
-            <v>623</v>
+            <v>1181</v>
           </cell>
           <cell r="I19">
             <v>0</v>
@@ -12236,7 +12238,7 @@
             <v>538</v>
           </cell>
           <cell r="H20">
-            <v>255</v>
+            <v>508</v>
           </cell>
           <cell r="I20">
             <v>0</v>
@@ -12274,7 +12276,7 @@
             <v>525763.644</v>
           </cell>
           <cell r="H21">
-            <v>239297.004</v>
+            <v>1477637.646</v>
           </cell>
           <cell r="I21">
             <v>0</v>
@@ -12299,7 +12301,9 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
         <row r="4">
           <cell r="B4">
             <v>329446.831260062</v>
@@ -12453,7 +12457,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="7">
+      <sheetData sheetId="9">
         <row r="4">
           <cell r="B4">
             <v>116176.256</v>
@@ -12607,10 +12611,10 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -23232,7 +23236,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{def1cc48-045d-43d8-911d-da0189b8d53a}</x14:id>
+          <x14:id>{117c2b93-a60a-4a25-9dd0-93c5e1f7dbf1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23246,7 +23250,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27dc84f6-5264-4585-9322-c916ee6a8210}</x14:id>
+          <x14:id>{ea7742eb-0e4d-4887-baae-9e01446756cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23260,7 +23264,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e4cd20b2-5914-45be-89d0-9ebe5a7bccfb}</x14:id>
+          <x14:id>{e697a7aa-e418-4ca3-8e70-0f35776a97ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23274,7 +23278,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1d7a31d5-2187-4d56-9aae-4b4cd1960308}</x14:id>
+          <x14:id>{2a4e78df-eb44-4c8c-858a-3cefda83aa18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23288,7 +23292,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b0a9a7a-a9d7-41e5-83ae-135f858be01c}</x14:id>
+          <x14:id>{6d284893-33f1-4e8b-b784-60f3f93efa07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23302,7 +23306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af12d1fb-72e9-42b8-a6dc-aa2115b1596c}</x14:id>
+          <x14:id>{6281bfaa-98df-49e9-8a3d-422c35beec31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23316,7 +23320,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f2166c8-1a61-4cde-96cf-122c6218227b}</x14:id>
+          <x14:id>{d213ffdc-b40b-46aa-a5e7-17467f5580da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23330,7 +23334,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2330c03d-92eb-4eb6-aaaa-ed153cf3527f}</x14:id>
+          <x14:id>{659fbe50-33e6-4308-baeb-d0bfe5ea5d91}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23350,7 +23354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b089e82-d75a-4b9b-863e-d67d565143c0}</x14:id>
+          <x14:id>{ec9ec053-6965-45db-869b-dc7b0782c0e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23378,7 +23382,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7863629a-2b10-4a75-b9b9-5b00bb73b2bb}</x14:id>
+          <x14:id>{ab0370ef-9ca9-42cf-bf3c-32f563c7b620}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23398,7 +23402,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77b48896-8834-49ae-ac67-a03268417c86}</x14:id>
+          <x14:id>{a00ccc80-937f-4fc0-9044-fa43ac37d21d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23426,7 +23430,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82a1a8e8-a8a2-4e8d-a3eb-4a37deaa259c}</x14:id>
+          <x14:id>{066f3225-4539-4d51-a535-1ff4e0015520}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23446,7 +23450,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ea12327-1484-4ca7-a2a3-3b9830597acd}</x14:id>
+          <x14:id>{6f7a4333-d9a1-48e8-84a2-92a61a2f200e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23474,7 +23478,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d365cafd-d987-4ecc-945c-e7ffbbd5a8b0}</x14:id>
+          <x14:id>{e5b36c51-12a6-4310-9b86-229631f65e79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23494,7 +23498,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8bd1842e-6765-42ae-a3e0-7940c878a0ef}</x14:id>
+          <x14:id>{4062795d-10b5-4010-967f-24eb362789a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23522,7 +23526,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa50584f-8e2a-4b7d-ae43-4d4868eff7d6}</x14:id>
+          <x14:id>{5706d3c5-75c6-4fa7-a655-adad25dfa543}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23542,7 +23546,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b92da82f-36b3-44d4-aee1-78931aebe406}</x14:id>
+          <x14:id>{7b98a000-f68f-4323-bc3e-5415402d21c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23570,7 +23574,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{10f03b71-5b7d-4bb1-8af3-e0d920219dd4}</x14:id>
+          <x14:id>{aa292887-1b6c-4e8f-bc6d-e4edba523bf2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23632,7 +23636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e8f3f5a-0882-4fb4-8c12-2056c4a2c449}</x14:id>
+          <x14:id>{03050f35-5fa8-49ab-90db-6ea4cd66d143}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23662,7 +23666,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fabd9b76-78bf-4952-852e-e1addfeee7ea}</x14:id>
+          <x14:id>{d6e3c6bc-1679-4438-9772-b8341ac2c202}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23684,7 +23688,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7d26abd-6200-4fdb-84ba-174470d2f519}</x14:id>
+          <x14:id>{90942f48-2728-41b5-920d-0e7519cdadb4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23704,7 +23708,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{374dc5d8-438a-442e-80e4-25b2421ed0ea}</x14:id>
+          <x14:id>{181df0e5-e86f-4a43-b4e9-7c4af8501bf1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23726,7 +23730,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f53c3f17-0e88-4052-aefc-4859cbd0f674}</x14:id>
+          <x14:id>{de28e55f-2cb9-4aec-b80a-ba262948dc68}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23746,7 +23750,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e843d7c6-c2fa-4440-b740-2b7932f00a00}</x14:id>
+          <x14:id>{3d444d55-2306-4b0c-a863-2ca378005cc2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23768,7 +23772,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c21e2b1c-b01c-41c4-b1da-65f2f286ce6c}</x14:id>
+          <x14:id>{88c7cc0d-62b0-4ff5-820f-80584bf2f131}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23788,7 +23792,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{941253e4-f0ed-4b6d-983f-5cace3e58429}</x14:id>
+          <x14:id>{30c06539-f1e8-4fa7-9a41-e7c7967ef56b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23810,7 +23814,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5efcbe13-516c-4e0d-9a50-85f0134b8107}</x14:id>
+          <x14:id>{d5c87590-9373-43b1-89f0-ad6700ea1ab4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23830,7 +23834,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93bc68f4-b29e-44f8-8618-f5ee45dd230f}</x14:id>
+          <x14:id>{0c416cb5-a6be-479d-a740-1e1b457b97ca}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23858,7 +23862,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2647211d-7189-4de4-b029-cfefd999b4bd}</x14:id>
+          <x14:id>{bcf0736e-e2bc-495a-840c-da24b0e48a26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23872,7 +23876,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a2ab54dd-a64a-496e-920d-8a26239ffa7a}</x14:id>
+          <x14:id>{af6db539-97de-4b7d-a27d-b21627edd6da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23902,7 +23906,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d90a73b3-2459-47b8-b09b-981ae88f4091}</x14:id>
+          <x14:id>{c73c7343-4005-4e88-a0c8-3d88168d3033}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23924,7 +23928,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{917aa60c-8061-4e98-925e-b24e0ec135f1}</x14:id>
+          <x14:id>{6f69c397-d159-4601-b543-d21940b90cdd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23946,7 +23950,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{917002c4-af57-4690-9927-c5a2432352c7}</x14:id>
+          <x14:id>{92380221-cf61-4e12-ac75-43ac6789d333}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23968,7 +23972,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8fcc5889-6eaa-4c4d-87da-55b54ab2df25}</x14:id>
+          <x14:id>{f516020c-25ba-48e6-a18b-57813749c74d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -23990,7 +23994,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71ad9c27-4f7d-4192-af46-ef2b78004183}</x14:id>
+          <x14:id>{a463bfae-5e5f-42aa-af8a-89ea0ea8ee1f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24012,7 +24016,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d3c53b1-0334-4a84-9b83-1f6960e679f0}</x14:id>
+          <x14:id>{ef902de2-1c17-4ee2-bde3-e6d888c17457}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24034,7 +24038,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c4c1ab1-5ba6-4c32-a846-d16fc750c010}</x14:id>
+          <x14:id>{6f8f211b-9ceb-4c17-9d59-a2f67856f62b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24056,7 +24060,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{108b2412-fd92-4673-9a32-aa76fb093f32}</x14:id>
+          <x14:id>{f264de6a-ebfc-4b25-b796-39300e5c3144}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24078,7 +24082,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec1fa653-4925-4a1a-b9e8-6e2db966f925}</x14:id>
+          <x14:id>{6a4e437a-e3a5-4069-832b-130d6ce1f19b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24100,7 +24104,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4638a353-201f-4f30-b760-3bab4f315afb}</x14:id>
+          <x14:id>{3cdfad12-35de-45d0-9e82-91a943903eb0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24122,7 +24126,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{badfdc39-a2cd-4972-9578-9f83d5ec36f4}</x14:id>
+          <x14:id>{fe0ea55e-e848-447e-af72-e7c9256ac807}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24144,7 +24148,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c874ea18-6939-4fe6-af69-f2fac0f44c53}</x14:id>
+          <x14:id>{8a088045-f7d2-427b-8ae5-b8c6a0ebd2ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24166,7 +24170,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42b014e9-01ce-4835-9fdc-cba3990bcdf0}</x14:id>
+          <x14:id>{0e872a57-b5cb-4173-9d46-b0dad59e0d47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24185,7 +24189,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{def1cc48-045d-43d8-911d-da0189b8d53a}">
+          <x14:cfRule type="dataBar" id="{117c2b93-a60a-4a25-9dd0-93c5e1f7dbf1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24198,7 +24202,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{27dc84f6-5264-4585-9322-c916ee6a8210}">
+          <x14:cfRule type="dataBar" id="{ea7742eb-0e4d-4887-baae-9e01446756cd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24211,7 +24215,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e4cd20b2-5914-45be-89d0-9ebe5a7bccfb}">
+          <x14:cfRule type="dataBar" id="{e697a7aa-e418-4ca3-8e70-0f35776a97ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24224,7 +24228,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1d7a31d5-2187-4d56-9aae-4b4cd1960308}">
+          <x14:cfRule type="dataBar" id="{2a4e78df-eb44-4c8c-858a-3cefda83aa18}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24237,7 +24241,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9b0a9a7a-a9d7-41e5-83ae-135f858be01c}">
+          <x14:cfRule type="dataBar" id="{6d284893-33f1-4e8b-b784-60f3f93efa07}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24250,7 +24254,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{af12d1fb-72e9-42b8-a6dc-aa2115b1596c}">
+          <x14:cfRule type="dataBar" id="{6281bfaa-98df-49e9-8a3d-422c35beec31}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24263,7 +24267,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5f2166c8-1a61-4cde-96cf-122c6218227b}">
+          <x14:cfRule type="dataBar" id="{d213ffdc-b40b-46aa-a5e7-17467f5580da}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24276,7 +24280,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2330c03d-92eb-4eb6-aaaa-ed153cf3527f}">
+          <x14:cfRule type="dataBar" id="{659fbe50-33e6-4308-baeb-d0bfe5ea5d91}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24289,7 +24293,7 @@
           <xm:sqref>C44:N44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2b089e82-d75a-4b9b-863e-d67d565143c0}">
+          <x14:cfRule type="dataBar" id="{ec9ec053-6965-45db-869b-dc7b0782c0e7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24302,7 +24306,7 @@
           <xm:sqref>O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7863629a-2b10-4a75-b9b9-5b00bb73b2bb}">
+          <x14:cfRule type="dataBar" id="{ab0370ef-9ca9-42cf-bf3c-32f563c7b620}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24315,7 +24319,7 @@
           <xm:sqref>C52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{77b48896-8834-49ae-ac67-a03268417c86}">
+          <x14:cfRule type="dataBar" id="{a00ccc80-937f-4fc0-9044-fa43ac37d21d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24328,7 +24332,7 @@
           <xm:sqref>O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{82a1a8e8-a8a2-4e8d-a3eb-4a37deaa259c}">
+          <x14:cfRule type="dataBar" id="{066f3225-4539-4d51-a535-1ff4e0015520}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24341,7 +24345,7 @@
           <xm:sqref>C60:N60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ea12327-1484-4ca7-a2a3-3b9830597acd}">
+          <x14:cfRule type="dataBar" id="{6f7a4333-d9a1-48e8-84a2-92a61a2f200e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24354,7 +24358,7 @@
           <xm:sqref>O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d365cafd-d987-4ecc-945c-e7ffbbd5a8b0}">
+          <x14:cfRule type="dataBar" id="{e5b36c51-12a6-4310-9b86-229631f65e79}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24367,7 +24371,7 @@
           <xm:sqref>C68:N68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8bd1842e-6765-42ae-a3e0-7940c878a0ef}">
+          <x14:cfRule type="dataBar" id="{4062795d-10b5-4010-967f-24eb362789a4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24380,7 +24384,7 @@
           <xm:sqref>O68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fa50584f-8e2a-4b7d-ae43-4d4868eff7d6}">
+          <x14:cfRule type="dataBar" id="{5706d3c5-75c6-4fa7-a655-adad25dfa543}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24393,7 +24397,7 @@
           <xm:sqref>C76:N76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b92da82f-36b3-44d4-aee1-78931aebe406}">
+          <x14:cfRule type="dataBar" id="{7b98a000-f68f-4323-bc3e-5415402d21c2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24406,7 +24410,7 @@
           <xm:sqref>O76</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{10f03b71-5b7d-4bb1-8af3-e0d920219dd4}">
+          <x14:cfRule type="dataBar" id="{aa292887-1b6c-4e8f-bc6d-e4edba523bf2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24419,7 +24423,7 @@
           <xm:sqref>C132:O132</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e8f3f5a-0882-4fb4-8c12-2056c4a2c449}">
+          <x14:cfRule type="dataBar" id="{03050f35-5fa8-49ab-90db-6ea4cd66d143}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24432,7 +24436,7 @@
           <xm:sqref>C26:O26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fabd9b76-78bf-4952-852e-e1addfeee7ea}">
+          <x14:cfRule type="dataBar" id="{d6e3c6bc-1679-4438-9772-b8341ac2c202}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24445,7 +24449,7 @@
           <xm:sqref>C35:O35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a7d26abd-6200-4fdb-84ba-174470d2f519}">
+          <x14:cfRule type="dataBar" id="{90942f48-2728-41b5-920d-0e7519cdadb4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24458,7 +24462,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:N45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{374dc5d8-438a-442e-80e4-25b2421ed0ea}">
+          <x14:cfRule type="dataBar" id="{181df0e5-e86f-4a43-b4e9-7c4af8501bf1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24471,7 +24475,7 @@
           <xm:sqref>O43 O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f53c3f17-0e88-4052-aefc-4859cbd0f674}">
+          <x14:cfRule type="dataBar" id="{de28e55f-2cb9-4aec-b80a-ba262948dc68}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24484,7 +24488,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:N53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e843d7c6-c2fa-4440-b740-2b7932f00a00}">
+          <x14:cfRule type="dataBar" id="{3d444d55-2306-4b0c-a863-2ca378005cc2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24497,7 +24501,7 @@
           <xm:sqref>O51 O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c21e2b1c-b01c-41c4-b1da-65f2f286ce6c}">
+          <x14:cfRule type="dataBar" id="{88c7cc0d-62b0-4ff5-820f-80584bf2f131}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24510,7 +24514,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{941253e4-f0ed-4b6d-983f-5cace3e58429}">
+          <x14:cfRule type="dataBar" id="{30c06539-f1e8-4fa7-9a41-e7c7967ef56b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24523,7 +24527,7 @@
           <xm:sqref>O59 O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5efcbe13-516c-4e0d-9a50-85f0134b8107}">
+          <x14:cfRule type="dataBar" id="{d5c87590-9373-43b1-89f0-ad6700ea1ab4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24536,7 +24540,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:N69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93bc68f4-b29e-44f8-8618-f5ee45dd230f}">
+          <x14:cfRule type="dataBar" id="{0c416cb5-a6be-479d-a740-1e1b457b97ca}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24549,7 +24553,7 @@
           <xm:sqref>O67 O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2647211d-7189-4de4-b029-cfefd999b4bd}">
+          <x14:cfRule type="dataBar" id="{bcf0736e-e2bc-495a-840c-da24b0e48a26}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24562,7 +24566,7 @@
           <xm:sqref>C75:N75 D76:N76 C77:N77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a2ab54dd-a64a-496e-920d-8a26239ffa7a}">
+          <x14:cfRule type="dataBar" id="{af6db539-97de-4b7d-a27d-b21627edd6da}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24575,7 +24579,7 @@
           <xm:sqref>O75 O77</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d90a73b3-2459-47b8-b09b-981ae88f4091}">
+          <x14:cfRule type="dataBar" id="{c73c7343-4005-4e88-a0c8-3d88168d3033}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24588,7 +24592,7 @@
           <xm:sqref>C83:N83 D84:N84 C85:O85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{917aa60c-8061-4e98-925e-b24e0ec135f1}">
+          <x14:cfRule type="dataBar" id="{6f69c397-d159-4601-b543-d21940b90cdd}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24601,7 +24605,7 @@
           <xm:sqref>C84:O84 D85:N85</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{917002c4-af57-4690-9927-c5a2432352c7}">
+          <x14:cfRule type="dataBar" id="{92380221-cf61-4e12-ac75-43ac6789d333}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24614,7 +24618,7 @@
           <xm:sqref>C91:N91 D92:N92 C93:O93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8fcc5889-6eaa-4c4d-87da-55b54ab2df25}">
+          <x14:cfRule type="dataBar" id="{f516020c-25ba-48e6-a18b-57813749c74d}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24627,7 +24631,7 @@
           <xm:sqref>C92:O92 D93:N93</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71ad9c27-4f7d-4192-af46-ef2b78004183}">
+          <x14:cfRule type="dataBar" id="{a463bfae-5e5f-42aa-af8a-89ea0ea8ee1f}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24640,7 +24644,7 @@
           <xm:sqref>C99:N99 D100:N100 C101:O101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9d3c53b1-0334-4a84-9b83-1f6960e679f0}">
+          <x14:cfRule type="dataBar" id="{ef902de2-1c17-4ee2-bde3-e6d888c17457}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24653,7 +24657,7 @@
           <xm:sqref>C100:O100 D101:N101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3c4c1ab1-5ba6-4c32-a846-d16fc750c010}">
+          <x14:cfRule type="dataBar" id="{6f8f211b-9ceb-4c17-9d59-a2f67856f62b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24666,7 +24670,7 @@
           <xm:sqref>C107:N107 D108:N108 C109:O109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{108b2412-fd92-4673-9a32-aa76fb093f32}">
+          <x14:cfRule type="dataBar" id="{f264de6a-ebfc-4b25-b796-39300e5c3144}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24679,7 +24683,7 @@
           <xm:sqref>C108:O108 D109:N109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec1fa653-4925-4a1a-b9e8-6e2db966f925}">
+          <x14:cfRule type="dataBar" id="{6a4e437a-e3a5-4069-832b-130d6ce1f19b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24692,7 +24696,7 @@
           <xm:sqref>C115:N115 D116:N116 C117:O117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4638a353-201f-4f30-b760-3bab4f315afb}">
+          <x14:cfRule type="dataBar" id="{3cdfad12-35de-45d0-9e82-91a943903eb0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24705,7 +24709,7 @@
           <xm:sqref>C116:O116 D117:N117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{badfdc39-a2cd-4972-9578-9f83d5ec36f4}">
+          <x14:cfRule type="dataBar" id="{fe0ea55e-e848-447e-af72-e7c9256ac807}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24718,7 +24722,7 @@
           <xm:sqref>C123:N123 D124:N124 C125:O125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c874ea18-6939-4fe6-af69-f2fac0f44c53}">
+          <x14:cfRule type="dataBar" id="{8a088045-f7d2-427b-8ae5-b8c6a0ebd2ee}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24731,7 +24735,7 @@
           <xm:sqref>C124:O124 D125:N125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42b014e9-01ce-4835-9fdc-cba3990bcdf0}">
+          <x14:cfRule type="dataBar" id="{0e872a57-b5cb-4173-9d46-b0dad59e0d47}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24965,7 +24969,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>621223.21</v>
+        <v>748705.97</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -25003,7 +25007,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>1.08038464388486</v>
+        <v>1.30209306373617</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -25118,7 +25122,7 @@
       </c>
       <c r="H7" s="12">
         <f>'[2]2026年月度数据汇总--俄罗斯'!H13+'[2]2026年月度数据汇总--俄罗斯'!H18</f>
-        <v>144320.02</v>
+        <v>271802.78</v>
       </c>
       <c r="I7" s="12">
         <f>'[2]2026年月度数据汇总--俄罗斯'!I13+'[2]2026年月度数据汇总--俄罗斯'!I18</f>
@@ -25146,7 +25150,7 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="0"/>
-        <v>911007.01</v>
+        <v>1038489.77</v>
       </c>
     </row>
     <row r="8" ht="15.6" spans="1:15">
@@ -25180,7 +25184,7 @@
       </c>
       <c r="H8" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H8</f>
-        <v>0.535748473942456</v>
+        <v>1.05062851406593</v>
       </c>
       <c r="I8" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I8</f>
@@ -25208,7 +25212,7 @@
       </c>
       <c r="O8" s="20">
         <f>O7/O6</f>
-        <v>0.297266079069626</v>
+        <v>0.338864332209494</v>
       </c>
     </row>
     <row r="9" ht="15.6" spans="1:15">
@@ -25366,7 +25370,7 @@
       </c>
       <c r="H11" s="11">
         <f>'[2]2026年月度数据汇总--俄罗斯'!H14+'[2]2026年月度数据汇总--俄罗斯'!H19</f>
-        <v>6094</v>
+        <v>12016</v>
       </c>
       <c r="I11" s="11">
         <f>'[2]2026年月度数据汇总--俄罗斯'!I14+'[2]2026年月度数据汇总--俄罗斯'!I19</f>
@@ -25394,7 +25398,7 @@
       </c>
       <c r="O11" s="11">
         <f t="shared" si="0"/>
-        <v>51471</v>
+        <v>57393</v>
       </c>
     </row>
     <row r="12" ht="15.6" spans="1:15">
@@ -25428,7 +25432,7 @@
       </c>
       <c r="H12" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H12</f>
-        <v>0.395130201208745</v>
+        <v>0.814808366702315</v>
       </c>
       <c r="I12" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I12</f>
@@ -25456,7 +25460,7 @@
       </c>
       <c r="O12" s="20">
         <f>O11/O10</f>
-        <v>0.249580565388159</v>
+        <v>0.278296077195364</v>
       </c>
     </row>
     <row r="13" ht="15.6" spans="1:15">
@@ -25614,7 +25618,7 @@
       </c>
       <c r="H15" s="11">
         <f>'[2]2026年月度数据汇总--俄罗斯'!H15+'[2]2026年月度数据汇总--俄罗斯'!H20</f>
-        <v>2249</v>
+        <v>4596</v>
       </c>
       <c r="I15" s="11">
         <f>'[2]2026年月度数据汇总--俄罗斯'!I15+'[2]2026年月度数据汇总--俄罗斯'!I20</f>
@@ -25642,7 +25646,7 @@
       </c>
       <c r="O15" s="11">
         <f t="shared" si="1"/>
-        <v>18251</v>
+        <v>20598</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:15">
@@ -25676,7 +25680,7 @@
       </c>
       <c r="H16" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H16</f>
-        <v>0.441264841541795</v>
+        <v>0.919275009888344</v>
       </c>
       <c r="I16" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I16</f>
@@ -25704,7 +25708,7 @@
       </c>
       <c r="O16" s="20">
         <f>O15/O14</f>
-        <v>0.28547831813212</v>
+        <v>0.322189600399178</v>
       </c>
     </row>
     <row r="17" ht="15.6" spans="1:15">
@@ -25862,7 +25866,7 @@
       </c>
       <c r="H19" s="19">
         <f>'[2]2026年月度数据汇总--俄罗斯'!H16+'[2]2026年月度数据汇总--俄罗斯'!H21</f>
-        <v>2513446.9992</v>
+        <v>6073636.7304</v>
       </c>
       <c r="I19" s="19">
         <f>'[2]2026年月度数据汇总--俄罗斯'!I16+'[2]2026年月度数据汇总--俄罗斯'!I21</f>
@@ -25890,7 +25894,7 @@
       </c>
       <c r="O19" s="19">
         <f t="shared" si="1"/>
-        <v>19421438.5959</v>
+        <v>22981628.3271</v>
       </c>
     </row>
     <row r="20" ht="15.6" spans="1:15">
@@ -25924,7 +25928,7 @@
       </c>
       <c r="H20" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H20</f>
-        <v>0.476369032961964</v>
+        <v>1.07917936735439</v>
       </c>
       <c r="I20" s="20">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I20</f>
@@ -25952,7 +25956,7 @@
       </c>
       <c r="O20" s="20">
         <f>O19/O18</f>
-        <v>0.0218389196449133</v>
+        <v>0.0258422635309186</v>
       </c>
     </row>
     <row r="21" ht="15.6" spans="1:15">
@@ -26026,21 +26030,57 @@
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!B22</f>
         <v>GSV目标</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
+      <c r="C22" s="21">
+        <f t="shared" ref="C22:N22" si="2">C18*(1-0.68)/12.5</f>
+        <v>837939.2</v>
+      </c>
+      <c r="D22" s="21">
+        <f t="shared" si="2"/>
+        <v>876928</v>
+      </c>
+      <c r="E22" s="21">
+        <f t="shared" si="2"/>
+        <v>787968</v>
+      </c>
+      <c r="F22" s="21">
+        <f t="shared" si="2"/>
+        <v>1140403.2</v>
+      </c>
+      <c r="G22" s="21">
+        <f t="shared" si="2"/>
+        <v>1497600</v>
+      </c>
+      <c r="H22" s="21">
+        <f t="shared" si="2"/>
+        <v>1722112</v>
+      </c>
+      <c r="I22" s="21">
+        <f t="shared" si="2"/>
+        <v>2071296</v>
+      </c>
+      <c r="J22" s="21">
+        <f t="shared" si="2"/>
+        <v>2657280</v>
+      </c>
+      <c r="K22" s="21">
+        <f t="shared" si="2"/>
+        <v>3420416</v>
+      </c>
+      <c r="L22" s="21">
+        <f t="shared" si="2"/>
+        <v>3310080</v>
+      </c>
+      <c r="M22" s="21">
+        <f t="shared" si="2"/>
+        <v>2722048</v>
+      </c>
+      <c r="N22" s="21">
+        <f t="shared" si="2"/>
+        <v>1722112</v>
+      </c>
       <c r="O22" s="28">
         <f>SUM(C22:N22)</f>
-        <v>0</v>
+        <v>22766182.4</v>
       </c>
     </row>
     <row r="23" ht="15.6" spans="1:15">
@@ -26090,9 +26130,9 @@
       <c r="L24" s="13"/>
       <c r="M24" s="13"/>
       <c r="N24" s="13"/>
-      <c r="O24" s="20" t="e">
+      <c r="O24" s="20">
         <f>O23/O22</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.6" spans="1:15">
@@ -26167,55 +26207,55 @@
         <v>退款率</v>
       </c>
       <c r="C26" s="13">
-        <f t="shared" ref="C26:O26" si="2">1-C23/C19</f>
+        <f t="shared" ref="C26:O26" si="3">1-C23/C19</f>
         <v>1</v>
       </c>
       <c r="D26" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E26" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F26" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="G26" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="H26" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="I26" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J26" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L26" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M26" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N26" s="13" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O26" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -26229,56 +26269,56 @@
         <v>退货率</v>
       </c>
       <c r="C27" s="13">
-        <f t="shared" ref="C27:O27" si="3">1-C15/C11</f>
+        <f t="shared" ref="C27:O27" si="4">1-C15/C11</f>
         <v>0.669214234535467</v>
       </c>
       <c r="D27" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.652624388022316</v>
       </c>
       <c r="E27" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.641507259737267</v>
       </c>
       <c r="F27" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.657728543327467</v>
       </c>
       <c r="G27" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.619143984620055</v>
       </c>
       <c r="H27" s="13">
-        <f t="shared" si="3"/>
-        <v>0.630948473908763</v>
+        <f t="shared" si="4"/>
+        <v>0.617509986684421</v>
       </c>
       <c r="I27" s="13" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J27" s="13" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K27" s="13" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L27" s="13" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M27" s="13" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N27" s="13" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O27" s="13">
-        <f t="shared" si="3"/>
-        <v>0.645411979561306</v>
+        <f t="shared" si="4"/>
+        <v>0.641106058230098</v>
       </c>
     </row>
     <row r="28" ht="15.6" spans="1:15">
@@ -26291,55 +26331,55 @@
         <v>利润率</v>
       </c>
       <c r="C28" s="13" t="e">
-        <f t="shared" ref="C28:O28" si="4">C7/(C23)</f>
+        <f t="shared" ref="C28:O28" si="5">C7/(C23)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O28" s="13" t="e">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -26457,7 +26497,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa3f6560-21eb-4bec-b6bf-5697438d3315}</x14:id>
+          <x14:id>{6634a2ee-9569-4702-b8de-2e31e21badd1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26471,7 +26511,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5508a77f-be2a-48f2-b9be-0e6bbed65b3f}</x14:id>
+          <x14:id>{9fbe3b44-541c-4d35-a062-3ebf92894c91}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26485,7 +26525,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{abc651fb-f841-4002-8141-d0aafe044223}</x14:id>
+          <x14:id>{8fc3673c-c48e-466f-92ff-fe7e91c36a09}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26499,7 +26539,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d45611b3-9398-47a5-8d66-7d7ffd04e28a}</x14:id>
+          <x14:id>{e5f3b597-ad35-4c00-b38e-d584b7d9f0c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26513,7 +26553,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{479cb120-c7a1-47d9-8054-9319d9afc2d1}</x14:id>
+          <x14:id>{0fe407a0-2d01-4d45-b703-e4359ffd8b19}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26527,7 +26567,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{120941f6-55a5-4ce2-bdc0-7315c227d67c}</x14:id>
+          <x14:id>{8df41d9e-53c5-4eed-850c-241e99e92f48}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26541,7 +26581,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{faa45d6d-6d93-4910-b3d6-2e11083f0ce2}</x14:id>
+          <x14:id>{636b744f-e9d8-4e94-8971-7b327f5fa816}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26555,7 +26595,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a45acb7-e203-468f-8977-00729cbd63af}</x14:id>
+          <x14:id>{b823a50f-9d1a-43de-ae60-3c64a2e52a4e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26569,7 +26609,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66c5a367-f219-4d73-8cf3-4d54c632e705}</x14:id>
+          <x14:id>{067185f9-d18b-4454-b881-32d76c5ae9b8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26583,7 +26623,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4836457-0298-49b1-90a3-d9f221954a6d}</x14:id>
+          <x14:id>{37d1ce29-b0b5-4b7d-a78d-ab7d2228db9b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26597,7 +26637,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c016f0db-e482-4ee1-aa34-c736ea3f0249}</x14:id>
+          <x14:id>{f9b9c13c-6ea6-41b7-9628-026f56abc497}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26633,7 +26673,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4fdd3c22-1eb5-4837-9182-96ad2305f63d}</x14:id>
+          <x14:id>{20866eed-a0ea-488f-aa87-700358517c8a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -26652,7 +26692,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aa3f6560-21eb-4bec-b6bf-5697438d3315}">
+          <x14:cfRule type="dataBar" id="{6634a2ee-9569-4702-b8de-2e31e21badd1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26665,7 +26705,7 @@
           <xm:sqref>C8:N8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5508a77f-be2a-48f2-b9be-0e6bbed65b3f}">
+          <x14:cfRule type="dataBar" id="{9fbe3b44-541c-4d35-a062-3ebf92894c91}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26678,7 +26718,7 @@
           <xm:sqref>O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{abc651fb-f841-4002-8141-d0aafe044223}">
+          <x14:cfRule type="dataBar" id="{8fc3673c-c48e-466f-92ff-fe7e91c36a09}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26691,7 +26731,7 @@
           <xm:sqref>C12:N12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d45611b3-9398-47a5-8d66-7d7ffd04e28a}">
+          <x14:cfRule type="dataBar" id="{e5f3b597-ad35-4c00-b38e-d584b7d9f0c6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26704,7 +26744,7 @@
           <xm:sqref>O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{479cb120-c7a1-47d9-8054-9319d9afc2d1}">
+          <x14:cfRule type="dataBar" id="{0fe407a0-2d01-4d45-b703-e4359ffd8b19}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26717,7 +26757,7 @@
           <xm:sqref>C16:N16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{120941f6-55a5-4ce2-bdc0-7315c227d67c}">
+          <x14:cfRule type="dataBar" id="{8df41d9e-53c5-4eed-850c-241e99e92f48}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26730,7 +26770,7 @@
           <xm:sqref>O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{faa45d6d-6d93-4910-b3d6-2e11083f0ce2}">
+          <x14:cfRule type="dataBar" id="{636b744f-e9d8-4e94-8971-7b327f5fa816}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26743,7 +26783,7 @@
           <xm:sqref>B20:N20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3a45acb7-e203-468f-8977-00729cbd63af}">
+          <x14:cfRule type="dataBar" id="{b823a50f-9d1a-43de-ae60-3c64a2e52a4e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26756,7 +26796,7 @@
           <xm:sqref>O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66c5a367-f219-4d73-8cf3-4d54c632e705}">
+          <x14:cfRule type="dataBar" id="{067185f9-d18b-4454-b881-32d76c5ae9b8}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26769,7 +26809,7 @@
           <xm:sqref>C24:N24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d4836457-0298-49b1-90a3-d9f221954a6d}">
+          <x14:cfRule type="dataBar" id="{37d1ce29-b0b5-4b7d-a78d-ab7d2228db9b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26782,7 +26822,7 @@
           <xm:sqref>O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c016f0db-e482-4ee1-aa34-c736ea3f0249}">
+          <x14:cfRule type="dataBar" id="{f9b9c13c-6ea6-41b7-9628-026f56abc497}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -26795,7 +26835,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4fdd3c22-1eb5-4837-9182-96ad2305f63d}">
+          <x14:cfRule type="dataBar" id="{20866eed-a0ea-488f-aa87-700358517c8a}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -27030,7 +27070,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f>(F7+G7+H7)</f>
-        <v>1625199.49</v>
+        <v>1937577.24</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -27068,7 +27108,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="6">
         <f>(F7+G7+H7)/(F6+G6+H6)</f>
-        <v>1.00699686082307</v>
+        <v>1.20055058488987</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -27183,7 +27223,7 @@
       </c>
       <c r="H7" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H7</f>
-        <v>325038.63</v>
+        <v>637416.38</v>
       </c>
       <c r="I7" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I7</f>
@@ -27211,7 +27251,7 @@
       </c>
       <c r="O7" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O7</f>
-        <v>3437257.96</v>
+        <v>3749635.71</v>
       </c>
     </row>
     <row r="8" s="37" customFormat="1" spans="1:15">
@@ -27245,7 +27285,7 @@
       </c>
       <c r="H8" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H8</f>
-        <v>0.535748473942456</v>
+        <v>1.05062851406593</v>
       </c>
       <c r="I8" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I8</f>
@@ -27273,7 +27313,7 @@
       </c>
       <c r="O8" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O8</f>
-        <v>0.392593009981998</v>
+        <v>0.428271833786046</v>
       </c>
     </row>
     <row r="9" s="37" customFormat="1" spans="1:15">
@@ -27431,7 +27471,7 @@
       </c>
       <c r="H11" s="11">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H11</f>
-        <v>15887</v>
+        <v>32761</v>
       </c>
       <c r="I11" s="11">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I11</f>
@@ -27459,7 +27499,7 @@
       </c>
       <c r="O11" s="11">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O11</f>
-        <v>171643</v>
+        <v>188517</v>
       </c>
     </row>
     <row r="12" s="37" customFormat="1" spans="1:15">
@@ -27493,7 +27533,7 @@
       </c>
       <c r="H12" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H12</f>
-        <v>0.395130201208745</v>
+        <v>0.814808366702315</v>
       </c>
       <c r="I12" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I12</f>
@@ -27521,7 +27561,7 @@
       </c>
       <c r="O12" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O12</f>
-        <v>0.295491950033742</v>
+        <v>0.324541379167872</v>
       </c>
     </row>
     <row r="13" s="37" customFormat="1" spans="1:15">
@@ -27679,7 +27719,7 @@
       </c>
       <c r="H15" s="11">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H15</f>
-        <v>5500</v>
+        <v>11458</v>
       </c>
       <c r="I15" s="11">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I15</f>
@@ -27707,7 +27747,7 @@
       </c>
       <c r="O15" s="11">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O15</f>
-        <v>60846</v>
+        <v>66804</v>
       </c>
     </row>
     <row r="16" s="37" customFormat="1" spans="1:15">
@@ -27741,7 +27781,7 @@
       </c>
       <c r="H16" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H16</f>
-        <v>0.441264841541795</v>
+        <v>0.919275009888344</v>
       </c>
       <c r="I16" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I16</f>
@@ -27769,7 +27809,7 @@
       </c>
       <c r="O16" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O16</f>
-        <v>0.337901326548428</v>
+        <v>0.370988400531526</v>
       </c>
     </row>
     <row r="17" s="37" customFormat="1" spans="1:15">
@@ -27927,7 +27967,7 @@
       </c>
       <c r="H19" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H19</f>
-        <v>6659288.4732</v>
+        <v>15086133.2796</v>
       </c>
       <c r="I19" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I19</f>
@@ -27955,7 +27995,7 @@
       </c>
       <c r="O19" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O19</f>
-        <v>67577309.1834</v>
+        <v>76004153.9898</v>
       </c>
     </row>
     <row r="20" s="37" customFormat="1" spans="1:15">
@@ -27989,7 +28029,7 @@
       </c>
       <c r="H20" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H20</f>
-        <v>0.476369032961964</v>
+        <v>1.07917936735439</v>
       </c>
       <c r="I20" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I20</f>
@@ -28017,7 +28057,7 @@
       </c>
       <c r="O20" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O20</f>
-        <v>0.335043434341862</v>
+        <v>0.376823124280976</v>
       </c>
     </row>
     <row r="21" s="37" customFormat="1" spans="1:15">
@@ -28175,7 +28215,7 @@
       </c>
       <c r="H23" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H23</f>
-        <v>1930982.2827</v>
+        <v>4076553.6474</v>
       </c>
       <c r="I23" s="22">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I23</f>
@@ -28203,7 +28243,7 @@
       </c>
       <c r="O23" s="12">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O23</f>
-        <v>21876883.9391</v>
+        <v>24022455.3038</v>
       </c>
     </row>
     <row r="24" s="37" customFormat="1" spans="1:15">
@@ -28237,7 +28277,7 @@
       </c>
       <c r="H24" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H24</f>
-        <v>0.431662184320827</v>
+        <v>0.911294768317202</v>
       </c>
       <c r="I24" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I24</f>
@@ -28265,7 +28305,7 @@
       </c>
       <c r="O24" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O24</f>
-        <v>0.33895004922076</v>
+        <v>0.372192512895943</v>
       </c>
     </row>
     <row r="25" s="37" customFormat="1" spans="1:15">
@@ -28361,7 +28401,7 @@
       </c>
       <c r="H26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H26</f>
-        <v>0.289968258691773</v>
+        <v>0.270218588941704</v>
       </c>
       <c r="I26" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I26</f>
@@ -28389,7 +28429,7 @@
       </c>
       <c r="O26" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O26</f>
-        <v>0.323731208055765</v>
+        <v>0.316067662657279</v>
       </c>
     </row>
     <row r="27" s="37" customFormat="1" spans="1:15">
@@ -28423,7 +28463,7 @@
       </c>
       <c r="H27" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H27</f>
-        <v>0.653804997796941</v>
+        <v>0.65025487622478</v>
       </c>
       <c r="I27" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I27</f>
@@ -28451,7 +28491,7 @@
       </c>
       <c r="O27" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O27</f>
-        <v>0.645508409897287</v>
+        <v>0.645634080746033</v>
       </c>
     </row>
     <row r="28" s="37" customFormat="1" spans="1:15">
@@ -28485,7 +28525,7 @@
       </c>
       <c r="H28" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H28</f>
-        <v>0.168328126525073</v>
+        <v>0.156361582634032</v>
       </c>
       <c r="I28" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I28</f>
@@ -28513,7 +28553,7 @@
       </c>
       <c r="O28" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O28</f>
-        <v>0.157118260972107</v>
+        <v>0.156088778710595</v>
       </c>
     </row>
     <row r="29" s="37" customFormat="1" spans="1:15">
@@ -28609,7 +28649,7 @@
       </c>
       <c r="H30" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H30</f>
-        <v>102754.41</v>
+        <v>196174.75</v>
       </c>
       <c r="I30" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I30</f>
@@ -28637,7 +28677,7 @@
       </c>
       <c r="O30" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O30</f>
-        <v>1874915.07</v>
+        <v>1968335.41</v>
       </c>
     </row>
     <row r="31" s="37" customFormat="1" spans="1:15">
@@ -28671,7 +28711,7 @@
       </c>
       <c r="H31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H31</f>
-        <v>5785</v>
+        <v>11621</v>
       </c>
       <c r="I31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I31</f>
@@ -28699,7 +28739,7 @@
       </c>
       <c r="O31" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O31</f>
-        <v>82089</v>
+        <v>87925</v>
       </c>
     </row>
     <row r="32" s="37" customFormat="1" spans="1:15">
@@ -28733,7 +28773,7 @@
       </c>
       <c r="H32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H32</f>
-        <v>1927</v>
+        <v>3917</v>
       </c>
       <c r="I32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I32</f>
@@ -28761,7 +28801,7 @@
       </c>
       <c r="O32" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O32</f>
-        <v>30081</v>
+        <v>32071</v>
       </c>
     </row>
     <row r="33" s="37" customFormat="1" spans="1:15">
@@ -28795,7 +28835,7 @@
       </c>
       <c r="H33" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H33</f>
-        <v>2511111.222</v>
+        <v>5199070.2324</v>
       </c>
       <c r="I33" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I33</f>
@@ -28823,7 +28863,7 @@
       </c>
       <c r="O33" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O33</f>
-        <v>33826837.7889</v>
+        <v>36514796.7993</v>
       </c>
     </row>
     <row r="34" s="37" customFormat="1" spans="1:15">
@@ -28857,7 +28897,7 @@
       </c>
       <c r="H34" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H34</f>
-        <v>699411.4057</v>
+        <v>1456186.0782</v>
       </c>
       <c r="I34" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I34</f>
@@ -28885,7 +28925,7 @@
       </c>
       <c r="O34" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O34</f>
-        <v>11088070.4977</v>
+        <v>11844845.1702</v>
       </c>
     </row>
     <row r="35" s="37" customFormat="1" spans="1:15">
@@ -28919,7 +28959,7 @@
       </c>
       <c r="H35" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H35</f>
-        <v>0.278526653687186</v>
+        <v>0.280085864031076</v>
       </c>
       <c r="I35" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I35</f>
@@ -28947,7 +28987,7 @@
       </c>
       <c r="O35" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O35</f>
-        <v>0.327789152710528</v>
+        <v>0.324384803106095</v>
       </c>
     </row>
     <row r="36" s="37" customFormat="1" spans="1:15">
@@ -28981,7 +29021,7 @@
       </c>
       <c r="H36" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H36</f>
-        <v>0.666897147796024</v>
+        <v>0.662937785044316</v>
       </c>
       <c r="I36" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I36</f>
@@ -29009,7 +29049,7 @@
       </c>
       <c r="O36" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O36</f>
-        <v>0.633556262105763</v>
+        <v>0.635245948251351</v>
       </c>
     </row>
     <row r="37" s="37" customFormat="1" spans="1:15">
@@ -29043,7 +29083,7 @@
       </c>
       <c r="H37" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H37</f>
-        <v>0.1469155480774</v>
+        <v>0.134718188105804</v>
       </c>
       <c r="I37" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I37</f>
@@ -29071,7 +29111,7 @@
       </c>
       <c r="O37" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O37</f>
-        <v>0.169092996873434</v>
+        <v>0.166176541923238</v>
       </c>
     </row>
     <row r="38" s="37" customFormat="1" spans="1:15">
@@ -29105,7 +29145,7 @@
       </c>
       <c r="H38" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H38</f>
-        <v>77964.2</v>
+        <v>169438.85</v>
       </c>
       <c r="I38" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I38</f>
@@ -29133,7 +29173,7 @@
       </c>
       <c r="O38" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O38</f>
-        <v>651335.88</v>
+        <v>742810.53</v>
       </c>
     </row>
     <row r="39" s="37" customFormat="1" spans="1:15">
@@ -29167,7 +29207,7 @@
       </c>
       <c r="H39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H39</f>
-        <v>4008</v>
+        <v>9124</v>
       </c>
       <c r="I39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I39</f>
@@ -29195,7 +29235,7 @@
       </c>
       <c r="O39" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O39</f>
-        <v>38083</v>
+        <v>43199</v>
       </c>
     </row>
     <row r="40" s="37" customFormat="1" spans="1:15">
@@ -29229,7 +29269,7 @@
       </c>
       <c r="H40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H40</f>
-        <v>1324</v>
+        <v>2945</v>
       </c>
       <c r="I40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I40</f>
@@ -29257,7 +29297,7 @@
       </c>
       <c r="O40" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O40</f>
-        <v>12514</v>
+        <v>14135</v>
       </c>
     </row>
     <row r="41" s="37" customFormat="1" spans="1:15">
@@ -29291,7 +29331,7 @@
       </c>
       <c r="H41" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H41</f>
-        <v>1634730.252</v>
+        <v>3813426.3168</v>
       </c>
       <c r="I41" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I41</f>
@@ -29319,7 +29359,7 @@
       </c>
       <c r="O41" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O41</f>
-        <v>14329032.7986</v>
+        <v>16507728.8634</v>
       </c>
     </row>
     <row r="42" s="37" customFormat="1" spans="1:15">
@@ -29353,7 +29393,7 @@
       </c>
       <c r="H42" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H42</f>
-        <v>458423.5943</v>
+        <v>1032316.5394</v>
       </c>
       <c r="I42" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I42</f>
@@ -29381,7 +29421,7 @@
       </c>
       <c r="O42" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O42</f>
-        <v>4184008.9538</v>
+        <v>4757901.8989</v>
       </c>
     </row>
     <row r="43" s="37" customFormat="1" spans="1:15">
@@ -29415,7 +29455,7 @@
       </c>
       <c r="H43" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H43</f>
-        <v>0.280427669176089</v>
+        <v>0.270705778384164</v>
       </c>
       <c r="I43" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I43</f>
@@ -29443,7 +29483,7 @@
       </c>
       <c r="O43" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O43</f>
-        <v>0.291995210884631</v>
+        <v>0.288222682736748</v>
       </c>
     </row>
     <row r="44" s="37" customFormat="1" spans="1:15">
@@ -29477,7 +29517,7 @@
       </c>
       <c r="H44" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H44</f>
-        <v>0.669660678642715</v>
+        <v>0.677224901359053</v>
       </c>
       <c r="I44" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I44</f>
@@ -29505,7 +29545,7 @@
       </c>
       <c r="O44" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O44</f>
-        <v>0.671401937872542</v>
+        <v>0.672793351697956</v>
       </c>
     </row>
     <row r="45" s="37" customFormat="1" spans="1:15">
@@ -29539,7 +29579,7 @@
       </c>
       <c r="H45" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H45</f>
-        <v>0.170070216649841</v>
+        <v>0.164134588116239</v>
       </c>
       <c r="I45" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I45</f>
@@ -29567,7 +29607,7 @@
       </c>
       <c r="O45" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O45</f>
-        <v>0.155672678331255</v>
+        <v>0.156121447180686</v>
       </c>
     </row>
     <row r="46" s="37" customFormat="1" spans="1:15">
@@ -29601,7 +29641,7 @@
       </c>
       <c r="H46" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H46</f>
-        <v>131378.65</v>
+        <v>246129.6</v>
       </c>
       <c r="I46" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I46</f>
@@ -29629,7 +29669,7 @@
       </c>
       <c r="O46" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O46</f>
-        <v>764491.77</v>
+        <v>879242.72</v>
       </c>
     </row>
     <row r="47" s="37" customFormat="1" spans="1:15">
@@ -29663,7 +29703,7 @@
       </c>
       <c r="H47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H47</f>
-        <v>5471</v>
+        <v>10835</v>
       </c>
       <c r="I47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I47</f>
@@ -29691,7 +29731,7 @@
       </c>
       <c r="O47" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O47</f>
-        <v>34272</v>
+        <v>39636</v>
       </c>
     </row>
     <row r="48" s="37" customFormat="1" spans="1:15">
@@ -29725,7 +29765,7 @@
       </c>
       <c r="H48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H48</f>
-        <v>1994</v>
+        <v>4088</v>
       </c>
       <c r="I48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I48</f>
@@ -29753,7 +29793,7 @@
       </c>
       <c r="O48" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O48</f>
-        <v>11970</v>
+        <v>14064</v>
       </c>
     </row>
     <row r="49" s="37" customFormat="1" spans="1:15">
@@ -29787,7 +29827,7 @@
       </c>
       <c r="H49" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H49</f>
-        <v>2274149.9952</v>
+        <v>4595999.0844</v>
       </c>
       <c r="I49" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I49</f>
@@ -29815,7 +29855,7 @@
       </c>
       <c r="O49" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O49</f>
-        <v>13376634.4806</v>
+        <v>15698483.5698</v>
       </c>
     </row>
     <row r="50" s="37" customFormat="1" spans="1:15">
@@ -29849,7 +29889,7 @@
       </c>
       <c r="H50" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H50</f>
-        <v>692555.2367</v>
+        <v>1427835.2688</v>
       </c>
       <c r="I50" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I50</f>
@@ -29877,7 +29917,7 @@
       </c>
       <c r="O50" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O50</f>
-        <v>4218986.3419</v>
+        <v>4954266.374</v>
       </c>
     </row>
     <row r="51" s="37" customFormat="1" spans="1:15">
@@ -29911,7 +29951,7 @@
       </c>
       <c r="H51" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H51</f>
-        <v>0.304533666715811</v>
+        <v>0.310669180428351</v>
       </c>
       <c r="I51" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I51</f>
@@ -29939,7 +29979,7 @@
       </c>
       <c r="O51" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O51</f>
-        <v>0.315399688017098</v>
+        <v>0.315588849838387</v>
       </c>
     </row>
     <row r="52" s="37" customFormat="1" spans="1:15">
@@ -29973,7 +30013,7 @@
       </c>
       <c r="H52" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H52</f>
-        <v>0.635532809358435</v>
+        <v>0.622704199353945</v>
       </c>
       <c r="I52" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I52</f>
@@ -30001,7 +30041,7 @@
       </c>
       <c r="O52" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O52</f>
-        <v>0.650735294117647</v>
+        <v>0.645171056615198</v>
       </c>
     </row>
     <row r="53" s="37" customFormat="1" spans="1:15">
@@ -30035,7 +30075,7 @@
       </c>
       <c r="H53" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H53</f>
-        <v>0.189701330721307</v>
+        <v>0.172379549222688</v>
       </c>
       <c r="I53" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I53</f>
@@ -30063,7 +30103,7 @@
       </c>
       <c r="O53" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O53</f>
-        <v>0.181202712700823</v>
+        <v>0.177471830060303</v>
       </c>
     </row>
     <row r="54" s="37" customFormat="1" spans="1:15">
@@ -30097,7 +30137,7 @@
       </c>
       <c r="H54" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H54</f>
-        <v>12941.37</v>
+        <v>25673.18</v>
       </c>
       <c r="I54" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I54</f>
@@ -30125,7 +30165,7 @@
       </c>
       <c r="O54" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O54</f>
-        <v>146515.24</v>
+        <v>159247.05</v>
       </c>
     </row>
     <row r="55" s="37" customFormat="1" spans="1:15">
@@ -30159,7 +30199,7 @@
       </c>
       <c r="H55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H55</f>
-        <v>623</v>
+        <v>1181</v>
       </c>
       <c r="I55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I55</f>
@@ -30187,7 +30227,7 @@
       </c>
       <c r="O55" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O55</f>
-        <v>17199</v>
+        <v>17757</v>
       </c>
     </row>
     <row r="56" s="37" customFormat="1" spans="1:15">
@@ -30221,7 +30261,7 @@
       </c>
       <c r="H56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H56</f>
-        <v>255</v>
+        <v>508</v>
       </c>
       <c r="I56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I56</f>
@@ -30249,7 +30289,7 @@
       </c>
       <c r="O56" s="1">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O56</f>
-        <v>6281</v>
+        <v>6534</v>
       </c>
     </row>
     <row r="57" s="37" customFormat="1" spans="1:15">
@@ -30283,7 +30323,7 @@
       </c>
       <c r="H57" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H57</f>
-        <v>239297.004</v>
+        <v>1477637.646</v>
       </c>
       <c r="I57" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I57</f>
@@ -30311,7 +30351,7 @@
       </c>
       <c r="O57" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O57</f>
-        <v>6044804.1153</v>
+        <v>7283144.7573</v>
       </c>
     </row>
     <row r="58" s="37" customFormat="1" spans="1:15">
@@ -30345,7 +30385,7 @@
       </c>
       <c r="H58" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H58</f>
-        <v>80592.046</v>
+        <v>160215.761</v>
       </c>
       <c r="I58" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I58</f>
@@ -30373,7 +30413,7 @@
       </c>
       <c r="O58" s="21">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O58</f>
-        <v>2385818.1457</v>
+        <v>2465441.8607</v>
       </c>
     </row>
     <row r="59" s="37" customFormat="1" spans="1:15">
@@ -30407,7 +30447,7 @@
       </c>
       <c r="H59" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H59</f>
-        <v>0.336786690400854</v>
+        <v>0.108426962072676</v>
       </c>
       <c r="I59" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I59</f>
@@ -30435,7 +30475,7 @@
       </c>
       <c r="O59" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O59</f>
-        <v>0.394689075144926</v>
+        <v>0.338513367900432</v>
       </c>
     </row>
     <row r="60" s="37" customFormat="1" spans="1:15">
@@ -30469,7 +30509,7 @@
       </c>
       <c r="H60" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H60</f>
-        <v>0.590690208667737</v>
+        <v>0.569856054191363</v>
       </c>
       <c r="I60" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I60</f>
@@ -30497,7 +30537,7 @@
       </c>
       <c r="O60" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O60</f>
-        <v>0.634804349090063</v>
+        <v>0.632032437911809</v>
       </c>
     </row>
     <row r="61" s="37" customFormat="1" spans="1:15">
@@ -30531,7 +30571,7 @@
       </c>
       <c r="H61" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!H61</f>
-        <v>0.160578749917827</v>
+        <v>0.160241288620787</v>
       </c>
       <c r="I61" s="13" t="e">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!I61</f>
@@ -30559,7 +30599,7 @@
       </c>
       <c r="O61" s="13">
         <f>'[2]2026年度男装数据汇总分析--俄罗斯'!O61</f>
-        <v>0.0614109001828437</v>
+        <v>0.0645916874124891</v>
       </c>
     </row>
     <row r="62" s="37" customFormat="1" spans="1:15">
@@ -37359,7 +37399,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec3abd82-a414-4476-9a74-8fd433f846a7}</x14:id>
+          <x14:id>{11b2dc0e-f4e2-4b11-b795-6a8ea36cc53e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37373,7 +37413,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad81e660-adb2-4c44-ba2c-cb32f9409e11}</x14:id>
+          <x14:id>{8e06d658-4f0f-4241-91e6-58abea868049}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37387,7 +37427,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc93f3a9-c583-4f29-9b0d-8667fe64ced6}</x14:id>
+          <x14:id>{2c0bc188-d780-430e-919a-f63eaf2d0a9e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37401,7 +37441,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{64e19edc-281a-492c-9bfa-5757f6d7f4b3}</x14:id>
+          <x14:id>{19dd85de-6207-4cac-b87a-1a59978c649b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37415,7 +37455,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6eb20218-6da8-449d-88a5-4c7cfee3a9d3}</x14:id>
+          <x14:id>{c0a87b2a-dc78-4f7c-97f6-988e40aa300e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37429,7 +37469,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{880c0b46-21ed-470c-afb5-5b57a55fa534}</x14:id>
+          <x14:id>{fc5b717a-ec21-4adf-9a52-3f0a027f6a27}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37449,7 +37489,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{789db2cc-577d-46b2-9e87-1836ad337da8}</x14:id>
+          <x14:id>{c7f8a1e3-6e75-474f-927c-882a93369368}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37463,7 +37503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82437995-34b7-43b9-87c1-de075b1b2394}</x14:id>
+          <x14:id>{7262b42b-44a0-4f27-86ac-fcd42ea53b71}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37477,7 +37517,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d56f005-0198-4d6a-896f-dc64e377ca60}</x14:id>
+          <x14:id>{7ad9ae39-1eb2-44e6-a172-78f00cbe2030}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37491,7 +37531,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eae55dd0-f6e8-480a-8346-b42e42b5c8a8}</x14:id>
+          <x14:id>{62c313d3-9fbf-4429-8004-239336062e32}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37505,7 +37545,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{592992a1-831f-4749-977b-7b9b7456c46f}</x14:id>
+          <x14:id>{9fd94e65-dd54-418d-b2ae-a64ebd857edb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37519,7 +37559,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e07c3e9-066f-4ed7-aa44-dae1e91b4b47}</x14:id>
+          <x14:id>{82491f1e-24eb-4394-8f09-5dcee01b6beb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37541,7 +37581,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72c4bac1-3e03-46f5-8ae2-4eb5bfa9a360}</x14:id>
+          <x14:id>{78323c8a-698a-4008-8d47-a2e7b9aecb70}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37571,7 +37611,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d83b2f4-558d-4203-b5ef-349d2d341b26}</x14:id>
+          <x14:id>{c297036d-285e-4e4f-9de4-1021a7c8da07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37601,7 +37641,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4934688-0cf8-4319-92ff-35372a11c2e1}</x14:id>
+          <x14:id>{dfa5d315-8d46-402d-b669-95099a184466}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37631,7 +37671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fd126515-fd4a-43f8-b379-92abd763a227}</x14:id>
+          <x14:id>{5810c1e8-6f6e-4fc3-a16e-f8ffef564445}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37661,7 +37701,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbd28c9e-25b7-422c-bf8c-0e3f9f21b031}</x14:id>
+          <x14:id>{52ed7f06-9a03-4508-a35c-92328d303115}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37691,7 +37731,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57ee7dcb-df9c-462e-b650-0c321a1be40f}</x14:id>
+          <x14:id>{003dc371-8c46-48e5-bb82-0bc9832e2718}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37713,7 +37753,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b2198fe-2011-4d5f-83eb-5132685df21e}</x14:id>
+          <x14:id>{7986bc79-5ed6-4121-8404-46757409e60b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37735,7 +37775,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{85bbce98-7e23-4a66-8a4d-f6b6ed0b9cb0}</x14:id>
+          <x14:id>{2b87f753-36f0-4332-a28d-e3d507c5bc84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37757,7 +37797,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d2a8b3d2-a6a0-416a-b85b-31083ae501d5}</x14:id>
+          <x14:id>{2699fb2c-c4dc-4e4e-8bea-099037fd348e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37779,7 +37819,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0364943d-d06f-4c37-be88-7826407e9695}</x14:id>
+          <x14:id>{84950ce3-69ac-4bf1-8b0e-b035c49af64c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37801,7 +37841,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe4eb5b9-8f9a-47a6-9f2b-b227c6f9b927}</x14:id>
+          <x14:id>{16770792-f1a6-4073-b131-1de1a3583af5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37823,7 +37863,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57b11a37-fa9f-428a-abd8-4e99ba3f00e7}</x14:id>
+          <x14:id>{3954aa38-59ff-4a55-9e6a-df5e87e13e16}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37845,7 +37885,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d147febf-3e2b-433b-a7c6-0d3aeb3dc7b6}</x14:id>
+          <x14:id>{ec89d09a-7122-4ffb-80f1-f7ce4b2b3af0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37867,7 +37907,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61384d78-5d07-49fe-ad7c-a44ce1ab1163}</x14:id>
+          <x14:id>{a5da7186-9f45-4f78-9c1d-66ca6f3438be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37889,7 +37929,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d43cbea3-e695-4982-b6c4-7eabfd694c43}</x14:id>
+          <x14:id>{d83863fa-282f-4adb-ba16-b33f4a6a3cdb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37911,7 +37951,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{712d799c-ce57-4f15-98a6-cbea8ce88d04}</x14:id>
+          <x14:id>{6ad7ebd5-ce15-4605-b6a0-cd37b57e3924}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37933,7 +37973,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba9210c7-4e29-47d2-a335-0718d03f238c}</x14:id>
+          <x14:id>{297d3cb0-18b0-413a-99a5-2161f6fd36d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37955,7 +37995,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82d0d6e6-6736-44e8-a09d-47f777db27ad}</x14:id>
+          <x14:id>{f5f1a0a5-754f-4d90-813f-dc4359d3b52b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37977,7 +38017,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{02256ed3-46bd-4d20-9ab3-d19c36967293}</x14:id>
+          <x14:id>{ce8fffbd-1ae9-47e9-b0e4-a9f7e53589d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -37999,7 +38039,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbe685ab-7d2b-4a12-abd6-80ecc8eaf52d}</x14:id>
+          <x14:id>{1a76a20b-080a-4138-9a29-0d927a5ee620}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -38018,7 +38058,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec3abd82-a414-4476-9a74-8fd433f846a7}">
+          <x14:cfRule type="dataBar" id="{11b2dc0e-f4e2-4b11-b795-6a8ea36cc53e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38031,7 +38071,7 @@
           <xm:sqref>C8:O8</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ad81e660-adb2-4c44-ba2c-cb32f9409e11}">
+          <x14:cfRule type="dataBar" id="{8e06d658-4f0f-4241-91e6-58abea868049}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38044,7 +38084,7 @@
           <xm:sqref>C12:O12</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc93f3a9-c583-4f29-9b0d-8667fe64ced6}">
+          <x14:cfRule type="dataBar" id="{2c0bc188-d780-430e-919a-f63eaf2d0a9e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38057,7 +38097,7 @@
           <xm:sqref>C16:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{64e19edc-281a-492c-9bfa-5757f6d7f4b3}">
+          <x14:cfRule type="dataBar" id="{19dd85de-6207-4cac-b87a-1a59978c649b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38070,7 +38110,7 @@
           <xm:sqref>C20:O20</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6eb20218-6da8-449d-88a5-4c7cfee3a9d3}">
+          <x14:cfRule type="dataBar" id="{c0a87b2a-dc78-4f7c-97f6-988e40aa300e}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38083,7 +38123,7 @@
           <xm:sqref>C24:O24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{880c0b46-21ed-470c-afb5-5b57a55fa534}">
+          <x14:cfRule type="dataBar" id="{fc5b717a-ec21-4adf-9a52-3f0a027f6a27}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38096,7 +38136,7 @@
           <xm:sqref>O26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{789db2cc-577d-46b2-9e87-1836ad337da8}">
+          <x14:cfRule type="dataBar" id="{c7f8a1e3-6e75-474f-927c-882a93369368}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38109,7 +38149,7 @@
           <xm:sqref>C27:O27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{82437995-34b7-43b9-87c1-de075b1b2394}">
+          <x14:cfRule type="dataBar" id="{7262b42b-44a0-4f27-86ac-fcd42ea53b71}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38122,7 +38162,7 @@
           <xm:sqref>C36:O36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d56f005-0198-4d6a-896f-dc64e377ca60}">
+          <x14:cfRule type="dataBar" id="{7ad9ae39-1eb2-44e6-a172-78f00cbe2030}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38135,7 +38175,7 @@
           <xm:sqref>C44:O44</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eae55dd0-f6e8-480a-8346-b42e42b5c8a8}">
+          <x14:cfRule type="dataBar" id="{62c313d3-9fbf-4429-8004-239336062e32}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38148,7 +38188,7 @@
           <xm:sqref>C52:O52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{592992a1-831f-4749-977b-7b9b7456c46f}">
+          <x14:cfRule type="dataBar" id="{9fd94e65-dd54-418d-b2ae-a64ebd857edb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38161,7 +38201,7 @@
           <xm:sqref>C60:O60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e07c3e9-066f-4ed7-aa44-dae1e91b4b47}">
+          <x14:cfRule type="dataBar" id="{82491f1e-24eb-4394-8f09-5dcee01b6beb}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38174,7 +38214,7 @@
           <xm:sqref>C124:O124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72c4bac1-3e03-46f5-8ae2-4eb5bfa9a360}">
+          <x14:cfRule type="dataBar" id="{78323c8a-698a-4008-8d47-a2e7b9aecb70}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38187,7 +38227,7 @@
           <xm:sqref>C26:N26 D27:N27 C28:O28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d83b2f4-558d-4203-b5ef-349d2d341b26}">
+          <x14:cfRule type="dataBar" id="{c297036d-285e-4e4f-9de4-1021a7c8da07}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38200,7 +38240,7 @@
           <xm:sqref>C35:N35 D36:N36 C37:O37</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b4934688-0cf8-4319-92ff-35372a11c2e1}">
+          <x14:cfRule type="dataBar" id="{dfa5d315-8d46-402d-b669-95099a184466}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38213,7 +38253,7 @@
           <xm:sqref>C43:N43 D44:N44 C45:O45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fd126515-fd4a-43f8-b379-92abd763a227}">
+          <x14:cfRule type="dataBar" id="{5810c1e8-6f6e-4fc3-a16e-f8ffef564445}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38226,7 +38266,7 @@
           <xm:sqref>C51:N51 D52:N52 C53:O53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cbd28c9e-25b7-422c-bf8c-0e3f9f21b031}">
+          <x14:cfRule type="dataBar" id="{52ed7f06-9a03-4508-a35c-92328d303115}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38239,7 +38279,7 @@
           <xm:sqref>C59:N59 D60:N60 C61:O61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{57ee7dcb-df9c-462e-b650-0c321a1be40f}">
+          <x14:cfRule type="dataBar" id="{003dc371-8c46-48e5-bb82-0bc9832e2718}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38252,7 +38292,7 @@
           <xm:sqref>C67:N67 D68:N68 C69:O69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b2198fe-2011-4d5f-83eb-5132685df21e}">
+          <x14:cfRule type="dataBar" id="{7986bc79-5ed6-4121-8404-46757409e60b}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -38265,7 +38305,7 @@
          